--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -57895,6 +57895,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>2023820</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>8.33199977874756</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>8.07199954986572</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>8.26799964904785</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>8.07999992370605</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -57918,6 +57918,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>1682662</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>8.22000026702881</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>8.04800033569336</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>8.0600004196167</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>8.17199993133545</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -57941,6 +57941,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>2437871</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>8.37199974060059</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>8.14999961853027</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>8.17199993133545</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>8.36999988555908</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -57964,6 +57964,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>2846086</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>8.52000045776367</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>8.38399982452393</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>8.39999961853027</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>8.4399995803833</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -57805,22 +57805,22 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2498" t="n">
-        <v>1780141</v>
+        <v>1312228</v>
       </c>
       <c r="C2498" t="n">
-        <v>8.41399955749512</v>
+        <v>8.41199970245361</v>
       </c>
       <c r="D2498" t="n">
-        <v>8.25599956512451</v>
+        <v>8.33399963378906</v>
       </c>
       <c r="E2498" t="n">
-        <v>8.33600044250488</v>
+        <v>8.37399959564209</v>
       </c>
       <c r="F2498" t="n">
-        <v>8.40200042724609</v>
+        <v>8.33399963378906</v>
       </c>
       <c r="G2498" t="s">
         <v>7</v>
@@ -57828,22 +57828,22 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2499" t="n">
-        <v>2551970</v>
+        <v>1780141</v>
       </c>
       <c r="C2499" t="n">
-        <v>8.48999977111816</v>
+        <v>8.41399955749512</v>
       </c>
       <c r="D2499" t="n">
-        <v>8.28400039672852</v>
+        <v>8.25599956512451</v>
       </c>
       <c r="E2499" t="n">
-        <v>8.38000011444092</v>
+        <v>8.33600044250488</v>
       </c>
       <c r="F2499" t="n">
-        <v>8.29599952697754</v>
+        <v>8.40200042724609</v>
       </c>
       <c r="G2499" t="s">
         <v>7</v>
@@ -57851,22 +57851,22 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2500" t="n">
-        <v>1562839</v>
+        <v>2551970</v>
       </c>
       <c r="C2500" t="n">
-        <v>8.39799976348877</v>
+        <v>8.48999977111816</v>
       </c>
       <c r="D2500" t="n">
-        <v>8.26599979400635</v>
+        <v>8.28400039672852</v>
       </c>
       <c r="E2500" t="n">
-        <v>8.29399967193604</v>
+        <v>8.38000011444092</v>
       </c>
       <c r="F2500" t="n">
-        <v>8.27799987792969</v>
+        <v>8.29599952697754</v>
       </c>
       <c r="G2500" t="s">
         <v>7</v>
@@ -57874,22 +57874,22 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2501" t="n">
-        <v>1670193</v>
+        <v>1562839</v>
       </c>
       <c r="C2501" t="n">
-        <v>8.37600040435791</v>
+        <v>8.39799976348877</v>
       </c>
       <c r="D2501" t="n">
-        <v>8.26000022888184</v>
+        <v>8.26599979400635</v>
       </c>
       <c r="E2501" t="n">
-        <v>8.29199981689453</v>
+        <v>8.29399967193604</v>
       </c>
       <c r="F2501" t="n">
-        <v>8.28400039672852</v>
+        <v>8.27799987792969</v>
       </c>
       <c r="G2501" t="s">
         <v>7</v>
@@ -57897,22 +57897,22 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2502" t="n">
-        <v>2023820</v>
+        <v>1670193</v>
       </c>
       <c r="C2502" t="n">
-        <v>8.33199977874756</v>
+        <v>8.37600040435791</v>
       </c>
       <c r="D2502" t="n">
-        <v>8.07199954986572</v>
+        <v>8.26000022888184</v>
       </c>
       <c r="E2502" t="n">
-        <v>8.26799964904785</v>
+        <v>8.29199981689453</v>
       </c>
       <c r="F2502" t="n">
-        <v>8.07999992370605</v>
+        <v>8.28400039672852</v>
       </c>
       <c r="G2502" t="s">
         <v>7</v>
@@ -57920,22 +57920,22 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2503" t="n">
-        <v>1682662</v>
+        <v>2023820</v>
       </c>
       <c r="C2503" t="n">
-        <v>8.22000026702881</v>
+        <v>8.33199977874756</v>
       </c>
       <c r="D2503" t="n">
-        <v>8.04800033569336</v>
+        <v>8.07199954986572</v>
       </c>
       <c r="E2503" t="n">
-        <v>8.0600004196167</v>
+        <v>8.26799964904785</v>
       </c>
       <c r="F2503" t="n">
-        <v>8.17199993133545</v>
+        <v>8.07999992370605</v>
       </c>
       <c r="G2503" t="s">
         <v>7</v>
@@ -57943,22 +57943,22 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2504" t="n">
-        <v>2437871</v>
+        <v>1682662</v>
       </c>
       <c r="C2504" t="n">
-        <v>8.37199974060059</v>
+        <v>8.22000026702881</v>
       </c>
       <c r="D2504" t="n">
-        <v>8.14999961853027</v>
+        <v>8.04800033569336</v>
       </c>
       <c r="E2504" t="n">
+        <v>8.0600004196167</v>
+      </c>
+      <c r="F2504" t="n">
         <v>8.17199993133545</v>
-      </c>
-      <c r="F2504" t="n">
-        <v>8.36999988555908</v>
       </c>
       <c r="G2504" t="s">
         <v>7</v>
@@ -57966,24 +57966,47 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2505" t="n">
-        <v>2846086</v>
+        <v>2437871</v>
       </c>
       <c r="C2505" t="n">
-        <v>8.52000045776367</v>
+        <v>8.37199974060059</v>
       </c>
       <c r="D2505" t="n">
-        <v>8.38399982452393</v>
+        <v>8.14999961853027</v>
       </c>
       <c r="E2505" t="n">
-        <v>8.39999961853027</v>
+        <v>8.17199993133545</v>
       </c>
       <c r="F2505" t="n">
-        <v>8.4399995803833</v>
+        <v>8.36999988555908</v>
       </c>
       <c r="G2505" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>10491343</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>8.39000034332275</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>8.47999954223633</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>8.44999980926514</v>
+      </c>
+      <c r="G2506" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -58279,8 +58279,31 @@
       <c r="E2518" t="n">
         <v>8.24600028991699</v>
       </c>
-      <c r="F2518"/>
+      <c r="F2518" t="n">
+        <v>8.13000011444092</v>
+      </c>
       <c r="G2518" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>1849371</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>8.22200012207031</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>8.12199974060059</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>8.17199993133545</v>
+      </c>
+      <c r="F2519"/>
+      <c r="G2519" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -58302,8 +58302,31 @@
       <c r="E2519" t="n">
         <v>8.17199993133545</v>
       </c>
-      <c r="F2519"/>
+      <c r="F2519" t="n">
+        <v>8.19999980926514</v>
+      </c>
       <c r="G2519" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2520">
+      <c r="A2520" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2520" t="n">
+        <v>1908833</v>
+      </c>
+      <c r="C2520" t="n">
+        <v>8.17800045013428</v>
+      </c>
+      <c r="D2520" t="n">
+        <v>8.05399990081787</v>
+      </c>
+      <c r="E2520" t="n">
+        <v>8.17800045013428</v>
+      </c>
+      <c r="F2520"/>
+      <c r="G2520" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -58325,8 +58325,31 @@
       <c r="E2520" t="n">
         <v>8.17800045013428</v>
       </c>
-      <c r="F2520"/>
+      <c r="F2520" t="n">
+        <v>8.07400035858154</v>
+      </c>
       <c r="G2520" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>2288185</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>8.20400047302246</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>8.04800033569336</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>8.0600004196167</v>
+      </c>
+      <c r="F2521"/>
+      <c r="G2521" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -58348,8 +58348,31 @@
       <c r="E2521" t="n">
         <v>8.0600004196167</v>
       </c>
-      <c r="F2521"/>
+      <c r="F2521" t="n">
+        <v>8.14999961853027</v>
+      </c>
       <c r="G2521" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2522">
+      <c r="A2522" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2522" t="n">
+        <v>1681495</v>
+      </c>
+      <c r="C2522" t="n">
+        <v>8.25800037384033</v>
+      </c>
+      <c r="D2522" t="n">
+        <v>8.14599990844727</v>
+      </c>
+      <c r="E2522" t="n">
+        <v>8.23600006103516</v>
+      </c>
+      <c r="F2522"/>
+      <c r="G2522" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -58378,6 +58378,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2523">
+      <c r="A2523" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2523" t="n">
+        <v>1286753</v>
+      </c>
+      <c r="C2523" t="n">
+        <v>8.27000045776367</v>
+      </c>
+      <c r="D2523" t="n">
+        <v>8.18000030517578</v>
+      </c>
+      <c r="E2523" t="n">
+        <v>8.19799995422363</v>
+      </c>
+      <c r="F2523" t="n">
+        <v>8.2519998550415</v>
+      </c>
+      <c r="G2523" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2" t="n">
-        <v>2.47833728790283</v>
+        <v>2.47833704948425</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G3" t="n">
-        <v>2.39468574523926</v>
+        <v>2.39468598365784</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G5" t="n">
-        <v>2.07256388664246</v>
+        <v>2.07256436347961</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08005523681641</v>
+        <v>2.08005571365356</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>2.00389456748962</v>
+        <v>2.0038948059082</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G8" t="n">
-        <v>1.97392988204956</v>
+        <v>1.97393000125885</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9976521730423</v>
+        <v>1.99765253067017</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G10" t="n">
-        <v>1.95769929885864</v>
+        <v>1.95769894123077</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G11" t="n">
-        <v>1.97268176078796</v>
+        <v>1.97268152236938</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95645081996918</v>
+        <v>1.95645070075989</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G14" t="n">
-        <v>2.03885388374329</v>
+        <v>2.03885364532471</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>2.05383610725403</v>
+        <v>2.05383634567261</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G17" t="n">
-        <v>2.08005523681641</v>
+        <v>2.08005571365356</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G18" t="n">
-        <v>2.10627460479736</v>
+        <v>2.10627436637878</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G19" t="n">
-        <v>2.10752320289612</v>
+        <v>2.10752296447754</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0413510799408</v>
+        <v>2.04135084152222</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G22" t="n">
-        <v>2.00888919830322</v>
+        <v>2.00888895988464</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12874817848206</v>
+        <v>2.12874841690063</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G25" t="n">
-        <v>2.23237657546997</v>
+        <v>2.23237609863281</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G26" t="n">
-        <v>2.19991445541382</v>
+        <v>2.19991397857666</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G27" t="n">
-        <v>2.14248204231262</v>
+        <v>2.14248180389404</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G28" t="n">
-        <v>2.20241141319275</v>
+        <v>2.20241189002991</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G30" t="n">
-        <v>2.26983261108398</v>
+        <v>2.26983237266541</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G32" t="n">
-        <v>2.29355478286743</v>
+        <v>2.29355454444885</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G33" t="n">
-        <v>2.35098671913147</v>
+        <v>2.35098695755005</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>2.27857208251953</v>
+        <v>2.27857232093811</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G36" t="n">
-        <v>2.29230570793152</v>
+        <v>2.2923059463501</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G39" t="n">
-        <v>2.3272647857666</v>
+        <v>2.32726502418518</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G40" t="n">
-        <v>2.33350777626038</v>
+        <v>2.3335075378418</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G41" t="n">
-        <v>2.38095188140869</v>
+        <v>2.38095164299011</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G42" t="n">
-        <v>2.34599256515503</v>
+        <v>2.34599328041077</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G43" t="n">
-        <v>2.3846971988678</v>
+        <v>2.38469743728638</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G44" t="n">
-        <v>2.38095188140869</v>
+        <v>2.38095164299011</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G45" t="n">
-        <v>2.3846971988678</v>
+        <v>2.38469743728638</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.75</v>
       </c>
       <c r="G46" t="n">
-        <v>2.34099912643433</v>
+        <v>2.34099888801575</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G47" t="n">
-        <v>2.36097574234009</v>
+        <v>2.36097550392151</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>2.32851338386536</v>
+        <v>2.32851314544678</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G49" t="n">
-        <v>2.33600449562073</v>
+        <v>2.33600473403931</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G50" t="n">
-        <v>2.37221193313599</v>
+        <v>2.37221169471741</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>2.32851338386536</v>
+        <v>2.32851314544678</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.76799988746643</v>
       </c>
       <c r="G54" t="n">
-        <v>2.3522355556488</v>
+        <v>2.35223531723022</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G55" t="n">
-        <v>2.38220024108887</v>
+        <v>2.38220047950745</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G57" t="n">
-        <v>2.34599256515503</v>
+        <v>2.34599328041077</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G59" t="n">
-        <v>2.30978560447693</v>
+        <v>2.30978536605835</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17868947982788</v>
+        <v>2.17868971824646</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G63" t="n">
-        <v>2.21364808082581</v>
+        <v>2.21364855766296</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G64" t="n">
-        <v>2.27982044219971</v>
+        <v>2.27982068061829</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>2.27857208251953</v>
+        <v>2.27857232093811</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>2.2910578250885</v>
+        <v>2.29105758666992</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G69" t="n">
-        <v>2.36222386360168</v>
+        <v>2.36222410202026</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G70" t="n">
-        <v>2.36097574234009</v>
+        <v>2.36097550392151</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36846613883972</v>
+        <v>2.3684663772583</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>2.3784544467926</v>
+        <v>2.37845492362976</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G73" t="n">
-        <v>2.358478307724</v>
+        <v>2.35847854614258</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.3846971988678</v>
+        <v>2.38469743728638</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G75" t="n">
-        <v>2.3784544467926</v>
+        <v>2.37845492362976</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G77" t="n">
-        <v>2.38095188140869</v>
+        <v>2.38095164299011</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.75</v>
       </c>
       <c r="G79" t="n">
-        <v>2.34099912643433</v>
+        <v>2.34099888801575</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.75</v>
       </c>
       <c r="G80" t="n">
-        <v>2.34099912643433</v>
+        <v>2.34099888801575</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G82" t="n">
-        <v>2.3434956073761</v>
+        <v>2.34349536895752</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G83" t="n">
-        <v>2.3784544467926</v>
+        <v>2.37845492362976</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G84" t="n">
-        <v>2.38969159126282</v>
+        <v>2.3896918296814</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>2.39094018936157</v>
+        <v>2.39093995094299</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G86" t="n">
-        <v>2.40841937065125</v>
+        <v>2.40841960906982</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G88" t="n">
-        <v>2.40717124938965</v>
+        <v>2.40717101097107</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G89" t="n">
-        <v>2.42839598655701</v>
+        <v>2.42839622497559</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G92" t="n">
-        <v>2.44212985038757</v>
+        <v>2.44212961196899</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G93" t="n">
-        <v>2.42964482307434</v>
+        <v>2.42964434623718</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G94" t="n">
-        <v>2.47584009170532</v>
+        <v>2.4758403301239</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G95" t="n">
-        <v>2.4671003818512</v>
+        <v>2.46710062026978</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G96" t="n">
-        <v>2.48707699775696</v>
+        <v>2.48707723617554</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G99" t="n">
-        <v>2.4671003818512</v>
+        <v>2.46710062026978</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G100" t="n">
-        <v>2.55574631690979</v>
+        <v>2.55574584007263</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G101" t="n">
-        <v>2.56948018074036</v>
+        <v>2.56948065757751</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G102" t="n">
-        <v>2.5832142829895</v>
+        <v>2.58321404457092</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G103" t="n">
-        <v>2.53576993942261</v>
+        <v>2.53576946258545</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G105" t="n">
-        <v>2.56698298454285</v>
+        <v>2.56698322296143</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G106" t="n">
-        <v>2.56074070930481</v>
+        <v>2.56074047088623</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>2.52203583717346</v>
+        <v>2.52203607559204</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G108" t="n">
-        <v>2.53077578544617</v>
+        <v>2.53077530860901</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>2.58446288108826</v>
+        <v>2.5844624042511</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>4.10799980163574</v>
       </c>
       <c r="G111" t="n">
-        <v>2.56448602676392</v>
+        <v>2.56448578834534</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>4.2519998550415</v>
       </c>
       <c r="G113" t="n">
-        <v>2.65438008308411</v>
+        <v>2.65438032150269</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>2.63690114021301</v>
+        <v>2.63690066337585</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>2.59694766998291</v>
+        <v>2.59694814682007</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G116" t="n">
-        <v>2.58571124076843</v>
+        <v>2.58571147918701</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G117" t="n">
-        <v>2.58695983886719</v>
+        <v>2.58695960044861</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G118" t="n">
-        <v>2.54825520515442</v>
+        <v>2.54825496673584</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>2.60319042205811</v>
+        <v>2.60319066047668</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>2.59070563316345</v>
+        <v>2.59070539474487</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G124" t="n">
-        <v>2.63190674781799</v>
+        <v>2.63190698623657</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G125" t="n">
-        <v>2.63690114021301</v>
+        <v>2.63690066337585</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G126" t="n">
-        <v>2.65937471389771</v>
+        <v>2.65937495231628</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>4.34800004959106</v>
       </c>
       <c r="G127" t="n">
-        <v>2.71431040763855</v>
+        <v>2.71430993080139</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G128" t="n">
-        <v>2.71930408477783</v>
+        <v>2.71930432319641</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G129" t="n">
-        <v>2.7642514705658</v>
+        <v>2.76425123214722</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G130" t="n">
-        <v>2.77299070358276</v>
+        <v>2.77299094200134</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G132" t="n">
-        <v>2.79047012329102</v>
+        <v>2.79047060012817</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G133" t="n">
-        <v>2.88036489486694</v>
+        <v>2.88036513328552</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G134" t="n">
-        <v>2.8916015625</v>
+        <v>2.89160132408142</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84166026115417</v>
+        <v>2.84166049957275</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G136" t="n">
-        <v>2.87911653518677</v>
+        <v>2.87911605834961</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G137" t="n">
-        <v>2.92780900001526</v>
+        <v>2.92780876159668</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G138" t="n">
-        <v>2.96670126914978</v>
+        <v>2.96670150756836</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G139" t="n">
-        <v>3.02132749557495</v>
+        <v>3.02132725715637</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G140" t="n">
-        <v>2.96410059928894</v>
+        <v>2.9640998840332</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G141" t="n">
-        <v>3.00441932678223</v>
+        <v>3.00441908836365</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G142" t="n">
-        <v>2.95889806747437</v>
+        <v>2.95889759063721</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>4.38199996948242</v>
       </c>
       <c r="G143" t="n">
-        <v>2.84964632987976</v>
+        <v>2.84964609146118</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G144" t="n">
-        <v>3.00051760673523</v>
+        <v>3.00051784515381</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G145" t="n">
-        <v>3.06424736976624</v>
+        <v>3.06424760818481</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G147" t="n">
-        <v>3.14748692512512</v>
+        <v>3.1474871635437</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G148" t="n">
-        <v>3.09286117553711</v>
+        <v>3.09286141395569</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G149" t="n">
-        <v>3.10716772079468</v>
+        <v>3.10716795921326</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>3.08505749702454</v>
+        <v>3.08505725860596</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G151" t="n">
-        <v>3.11236977577209</v>
+        <v>3.11237025260925</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G152" t="n">
-        <v>3.05124115943909</v>
+        <v>3.05124163627625</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G153" t="n">
-        <v>2.96280002593994</v>
+        <v>2.96279978752136</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G154" t="n">
-        <v>2.98100876808167</v>
+        <v>2.98100852966309</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G156" t="n">
-        <v>2.97190380096436</v>
+        <v>2.97190403938293</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G157" t="n">
-        <v>2.9875111579895</v>
+        <v>2.98751163482666</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G158" t="n">
-        <v>3.02262783050537</v>
+        <v>3.02262806892395</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G159" t="n">
-        <v>3.02783012390137</v>
+        <v>3.02783036231995</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G160" t="n">
-        <v>2.9875111579895</v>
+        <v>2.98751163482666</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>3.0109224319458</v>
+        <v>3.01092267036438</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G162" t="n">
-        <v>3.02262783050537</v>
+        <v>3.02262806892395</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.00441932678223</v>
+        <v>3.00441908836365</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90947461128235</v>
+        <v>2.90947413444519</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G165" t="n">
-        <v>2.8990695476532</v>
+        <v>2.89907002449036</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G167" t="n">
-        <v>2.87565851211548</v>
+        <v>2.8756582736969</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G169" t="n">
-        <v>2.89126539230347</v>
+        <v>2.89126563072205</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G171" t="n">
-        <v>2.85875010490417</v>
+        <v>2.85875058174133</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>2.86785531044006</v>
+        <v>2.86785483360291</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G173" t="n">
-        <v>2.96410059928894</v>
+        <v>2.9640998840332</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>2.97190380096436</v>
+        <v>2.97190403938293</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>2.95239472389221</v>
+        <v>2.95239448547363</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G177" t="n">
-        <v>2.99141311645508</v>
+        <v>2.99141335487366</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G178" t="n">
-        <v>2.97580552101135</v>
+        <v>2.97580599784851</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G179" t="n">
-        <v>2.97190380096436</v>
+        <v>2.97190403938293</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G180" t="n">
-        <v>2.99531483650208</v>
+        <v>2.99531507492065</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.04343771934509</v>
+        <v>3.04343795776367</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>3.03693461418152</v>
+        <v>3.0369348526001</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G183" t="n">
-        <v>3.04343771934509</v>
+        <v>3.04343795776367</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>3.0109224319458</v>
+        <v>3.01092267036438</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G185" t="n">
-        <v>2.99271392822266</v>
+        <v>2.99271368980408</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G186" t="n">
-        <v>3.00051760673523</v>
+        <v>3.00051784515381</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G187" t="n">
-        <v>2.96410059928894</v>
+        <v>2.9640998840332</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.02392840385437</v>
+        <v>3.02392864227295</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G189" t="n">
-        <v>3.08765888214111</v>
+        <v>3.08765864372253</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>3.12147498130798</v>
+        <v>3.12147450447083</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G192" t="n">
-        <v>3.14748692512512</v>
+        <v>3.1474871635437</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>4.82399988174438</v>
       </c>
       <c r="G193" t="n">
-        <v>3.13708138465881</v>
+        <v>3.13708186149597</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G194" t="n">
-        <v>3.16569542884827</v>
+        <v>3.16569519042969</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G195" t="n">
-        <v>3.16179323196411</v>
+        <v>3.16179347038269</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>3.14098334312439</v>
+        <v>3.14098429679871</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G197" t="n">
-        <v>3.07335162162781</v>
+        <v>3.07335186004639</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G199" t="n">
-        <v>3.15789198875427</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G201" t="n">
-        <v>3.15789198875427</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G204" t="n">
-        <v>3.11757326126099</v>
+        <v>3.11757278442383</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G207" t="n">
-        <v>3.09546279907227</v>
+        <v>3.09546232223511</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G210" t="n">
-        <v>3.08505749702454</v>
+        <v>3.08505725860596</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G213" t="n">
-        <v>3.06164646148682</v>
+        <v>3.0616466999054</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G214" t="n">
-        <v>3.09936380386353</v>
+        <v>3.0993640422821</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G215" t="n">
-        <v>3.10976934432983</v>
+        <v>3.10976886749268</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G216" t="n">
-        <v>3.09025931358337</v>
+        <v>3.09026002883911</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G217" t="n">
-        <v>3.09936380386353</v>
+        <v>3.0993640422821</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G218" t="n">
-        <v>3.08765888214111</v>
+        <v>3.08765864372253</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.02392840385437</v>
+        <v>3.02392864227295</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G221" t="n">
-        <v>3.0304319858551</v>
+        <v>3.03043174743652</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G222" t="n">
-        <v>3.0304319858551</v>
+        <v>3.03043174743652</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G223" t="n">
-        <v>3.04864025115967</v>
+        <v>3.04864048957825</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.02392840385437</v>
+        <v>3.02392864227295</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G225" t="n">
-        <v>3.04603910446167</v>
+        <v>3.04603862762451</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G226" t="n">
-        <v>3.07075119018555</v>
+        <v>3.07075095176697</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G230" t="n">
-        <v>3.09546279907227</v>
+        <v>3.09546232223511</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G233" t="n">
-        <v>3.06945013999939</v>
+        <v>3.06944990158081</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G235" t="n">
-        <v>3.03303289413452</v>
+        <v>3.03303265571594</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G237" t="n">
-        <v>3.0304319858551</v>
+        <v>3.03043174743652</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G238" t="n">
-        <v>3.03173232078552</v>
+        <v>3.0317325592041</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G239" t="n">
-        <v>3.07985520362854</v>
+        <v>3.07985472679138</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G240" t="n">
-        <v>3.09156060218811</v>
+        <v>3.09156084060669</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G242" t="n">
-        <v>3.07335162162781</v>
+        <v>3.07335186004639</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G243" t="n">
-        <v>3.07725381851196</v>
+        <v>3.07725405693054</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G244" t="n">
-        <v>3.09546279907227</v>
+        <v>3.09546232223511</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>3.14098334312439</v>
+        <v>3.14098429679871</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G248" t="n">
-        <v>3.34257888793945</v>
+        <v>3.34257912635803</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>3.31656670570374</v>
+        <v>3.31656694412231</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>3.27104568481445</v>
+        <v>3.27104592323303</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G253" t="n">
-        <v>3.26129078865051</v>
+        <v>3.26129055023193</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>3.3003089427948</v>
+        <v>3.30030846595764</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G255" t="n">
-        <v>3.28730249404907</v>
+        <v>3.28730273246765</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G257" t="n">
-        <v>3.32306957244873</v>
+        <v>3.32306981086731</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>3.31981873512268</v>
+        <v>3.3198184967041</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>3.31656670570374</v>
+        <v>3.31656694412231</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>3.35233330726624</v>
+        <v>3.35233378410339</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G262" t="n">
-        <v>3.35233330726624</v>
+        <v>3.35233378410339</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G263" t="n">
-        <v>3.39135217666626</v>
+        <v>3.39135241508484</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G264" t="n">
-        <v>3.36208844184875</v>
+        <v>3.3620879650116</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G265" t="n">
-        <v>3.39460349082947</v>
+        <v>3.39460372924805</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G266" t="n">
-        <v>3.4076099395752</v>
+        <v>3.40760970115662</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>3.44662857055664</v>
+        <v>3.44662809371948</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>3.3815975189209</v>
+        <v>3.38159728050232</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.31656670570374</v>
+        <v>3.31656694412231</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.40110659599304</v>
+        <v>3.40110731124878</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>3.39460349082947</v>
+        <v>3.39460372924805</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G277" t="n">
-        <v>3.39460349082947</v>
+        <v>3.39460372924805</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G279" t="n">
-        <v>3.44987964630127</v>
+        <v>3.44987940788269</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>3.46613740921021</v>
+        <v>3.46613788604736</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.25</v>
       </c>
       <c r="G284" t="n">
-        <v>3.41411256790161</v>
+        <v>3.41411328315735</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>3.38484907150269</v>
+        <v>3.38484883308411</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38484907150269</v>
+        <v>3.38484883308411</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>3.40110659599304</v>
+        <v>3.40110731124878</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G290" t="n">
-        <v>3.32306957244873</v>
+        <v>3.32306981086731</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>3.30681157112122</v>
+        <v>3.30681204795837</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32306957244873</v>
+        <v>3.32306981086731</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G294" t="n">
-        <v>3.31006407737732</v>
+        <v>3.31006383895874</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.25153541564941</v>
+        <v>3.25153613090515</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G296" t="n">
-        <v>3.18130254745483</v>
+        <v>3.18130278587341</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G297" t="n">
-        <v>3.238529920578</v>
+        <v>3.23852944374084</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G298" t="n">
-        <v>3.27104568481445</v>
+        <v>3.27104592323303</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G299" t="n">
-        <v>3.26454210281372</v>
+        <v>3.2645423412323</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G300" t="n">
-        <v>3.24503302574158</v>
+        <v>3.24503254890442</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>3.18650484085083</v>
+        <v>3.18650531768799</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G303" t="n">
-        <v>3.16959738731384</v>
+        <v>3.16959667205811</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G304" t="n">
-        <v>3.16959738731384</v>
+        <v>3.16959667205811</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G305" t="n">
-        <v>3.20731544494629</v>
+        <v>3.20731496810913</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G306" t="n">
-        <v>3.23202705383301</v>
+        <v>3.23202657699585</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G307" t="n">
-        <v>3.21121692657471</v>
+        <v>3.21121716499329</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G308" t="n">
-        <v>3.22942543029785</v>
+        <v>3.22942566871643</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G309" t="n">
-        <v>3.24503302574158</v>
+        <v>3.24503254890442</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G310" t="n">
-        <v>3.27104568481445</v>
+        <v>3.27104592323303</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22942543029785</v>
+        <v>3.22942566871643</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G312" t="n">
-        <v>3.20081186294556</v>
+        <v>3.20081210136414</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G313" t="n">
-        <v>3.22292232513428</v>
+        <v>3.22292256355286</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>3.18650484085083</v>
+        <v>3.18650531768799</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G317" t="n">
-        <v>3.21772027015686</v>
+        <v>3.21772003173828</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G318" t="n">
-        <v>3.14748692512512</v>
+        <v>3.1474871635437</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G319" t="n">
-        <v>3.11236977577209</v>
+        <v>3.11237025260925</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>2.98816156387329</v>
+        <v>2.98816108703613</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02913117408752</v>
+        <v>3.02913093566895</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G323" t="n">
-        <v>2.9159779548645</v>
+        <v>2.91597771644592</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>2.8743577003479</v>
+        <v>2.87435817718506</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G327" t="n">
-        <v>2.89646816253662</v>
+        <v>2.89646792411804</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G328" t="n">
-        <v>2.91662788391113</v>
+        <v>2.91662836074829</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>2.83533930778503</v>
+        <v>2.83533954620361</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G331" t="n">
-        <v>2.85159707069397</v>
+        <v>2.85159754753113</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G332" t="n">
-        <v>2.9016706943512</v>
+        <v>2.90167093276978</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G333" t="n">
-        <v>2.98360919952393</v>
+        <v>2.9836094379425</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.51700019836426</v>
       </c>
       <c r="G334" t="n">
-        <v>2.93743801116943</v>
+        <v>2.93743753433228</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G335" t="n">
-        <v>2.9159779548645</v>
+        <v>2.91597771644592</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.41699981689453</v>
       </c>
       <c r="G336" t="n">
-        <v>2.87240695953369</v>
+        <v>2.87240648269653</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.36700010299683</v>
       </c>
       <c r="G337" t="n">
-        <v>2.83989191055298</v>
+        <v>2.83989143371582</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G338" t="n">
-        <v>2.80412435531616</v>
+        <v>2.80412459373474</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.6269998550415</v>
       </c>
       <c r="G342" t="n">
-        <v>3.00897192955017</v>
+        <v>3.00897121429443</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>2.95889806747437</v>
+        <v>2.95889759063721</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.02913117408752</v>
+        <v>3.02913093566895</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.76300001144409</v>
       </c>
       <c r="G345" t="n">
-        <v>3.09741353988647</v>
+        <v>3.09741306304932</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.75099992752075</v>
       </c>
       <c r="G346" t="n">
-        <v>3.08960962295532</v>
+        <v>3.08960914611816</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>3.07595276832581</v>
+        <v>3.07595300674438</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G348" t="n">
-        <v>3.05709457397461</v>
+        <v>3.05709409713745</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>4.81899976730347</v>
       </c>
       <c r="G350" t="n">
-        <v>3.13383030891418</v>
+        <v>3.13382983207703</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G352" t="n">
-        <v>3.06945013999939</v>
+        <v>3.06944990158081</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G353" t="n">
-        <v>3.09936380386353</v>
+        <v>3.0993640422821</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>4.71700000762939</v>
       </c>
       <c r="G354" t="n">
-        <v>3.0674991607666</v>
+        <v>3.06749939918518</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G356" t="n">
-        <v>3.16959738731384</v>
+        <v>3.16959667205811</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G357" t="n">
-        <v>3.15789198875427</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>4.86899995803833</v>
       </c>
       <c r="G358" t="n">
-        <v>3.16634607315063</v>
+        <v>3.16634559631348</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>4.83699989318848</v>
       </c>
       <c r="G359" t="n">
-        <v>3.14553618431091</v>
+        <v>3.14553570747375</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G360" t="n">
-        <v>3.2203209400177</v>
+        <v>3.22032117843628</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.00400018692017</v>
       </c>
       <c r="G361" t="n">
-        <v>3.25413727760315</v>
+        <v>3.25413751602173</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G362" t="n">
-        <v>3.31006407737732</v>
+        <v>3.31006383895874</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G364" t="n">
-        <v>3.32697176933289</v>
+        <v>3.32697129249573</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>5.12599992752075</v>
       </c>
       <c r="G365" t="n">
-        <v>3.33347487449646</v>
+        <v>3.33347463607788</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G368" t="n">
-        <v>3.35038232803345</v>
+        <v>3.35038304328918</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.32957315444946</v>
+        <v>3.32957291603088</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>5.17399978637695</v>
       </c>
       <c r="G371" t="n">
-        <v>3.36468935012817</v>
+        <v>3.36468958854675</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>5.26399993896484</v>
       </c>
       <c r="G375" t="n">
-        <v>3.4232165813446</v>
+        <v>3.42321705818176</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G376" t="n">
-        <v>3.47264075279236</v>
+        <v>3.47264003753662</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>5.36600017547607</v>
       </c>
       <c r="G377" t="n">
-        <v>3.48954844474792</v>
+        <v>3.4895486831665</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G378" t="n">
-        <v>3.45053005218506</v>
+        <v>3.45053029060364</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G380" t="n">
-        <v>3.44922947883606</v>
+        <v>3.44922924041748</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>5.33799982070923</v>
       </c>
       <c r="G381" t="n">
-        <v>3.4713397026062</v>
+        <v>3.47133946418762</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G382" t="n">
-        <v>3.34518051147461</v>
+        <v>3.34518027305603</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>5.08799982070923</v>
       </c>
       <c r="G383" t="n">
-        <v>3.308762550354</v>
+        <v>3.30876326560974</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>5.06799983978271</v>
       </c>
       <c r="G386" t="n">
-        <v>3.29575681686401</v>
+        <v>3.29575657844543</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>4.95100021362305</v>
       </c>
       <c r="G388" t="n">
-        <v>3.21967172622681</v>
+        <v>3.21967124938965</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>5</v>
       </c>
       <c r="G389" t="n">
-        <v>3.25153541564941</v>
+        <v>3.25153613090515</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>3.24985384941101</v>
+        <v>3.24985408782959</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G392" t="n">
-        <v>3.30670285224915</v>
+        <v>3.30670261383057</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G393" t="n">
-        <v>3.3134708404541</v>
+        <v>3.31347060203552</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>3.01839852333069</v>
+        <v>3.01839804649353</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G400" t="n">
-        <v>3.05359077453613</v>
+        <v>3.05359053611755</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>4.63800001144409</v>
       </c>
       <c r="G401" t="n">
-        <v>3.13886332511902</v>
+        <v>3.1388635635376</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.5770001411438</v>
       </c>
       <c r="G403" t="n">
-        <v>3.09758043289185</v>
+        <v>3.097580909729</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>3.09961080551147</v>
+        <v>3.09961128234863</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G405" t="n">
-        <v>3.06509518623352</v>
+        <v>3.0650954246521</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G406" t="n">
-        <v>3.19841909408569</v>
+        <v>3.19841933250427</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.86299991607666</v>
       </c>
       <c r="G407" t="n">
-        <v>3.29113698005676</v>
+        <v>3.29113674163818</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G411" t="n">
-        <v>3.24511647224426</v>
+        <v>3.24511671066284</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.82299995422363</v>
       </c>
       <c r="G412" t="n">
-        <v>3.26406574249268</v>
+        <v>3.26406621932983</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G415" t="n">
-        <v>3.17405557632446</v>
+        <v>3.17405533790588</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G416" t="n">
-        <v>3.15916657447815</v>
+        <v>3.15916705131531</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>4.73099994659424</v>
       </c>
       <c r="G417" t="n">
-        <v>3.20180296897888</v>
+        <v>3.20180320739746</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G419" t="n">
-        <v>3.18759083747864</v>
+        <v>3.18759059906006</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G420" t="n">
-        <v>3.19571280479431</v>
+        <v>3.19571256637573</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.65700006484985</v>
       </c>
       <c r="G421" t="n">
-        <v>3.15172219276428</v>
+        <v>3.15172243118286</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G422" t="n">
-        <v>3.21330857276917</v>
+        <v>3.21330833435059</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G425" t="n">
-        <v>3.27286434173584</v>
+        <v>3.27286386489868</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G426" t="n">
-        <v>3.23361110687256</v>
+        <v>3.23361134529114</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G427" t="n">
-        <v>3.19841909408569</v>
+        <v>3.19841933250427</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>3.25526809692383</v>
+        <v>3.25526857376099</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G432" t="n">
-        <v>3.30534934997559</v>
+        <v>3.30534911155701</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G433" t="n">
-        <v>3.30128860473633</v>
+        <v>3.30128836631775</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G434" t="n">
-        <v>3.30128860473633</v>
+        <v>3.30128836631775</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G436" t="n">
-        <v>3.30399584770203</v>
+        <v>3.30399560928345</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G437" t="n">
-        <v>3.26677322387695</v>
+        <v>3.26677346229553</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.26203632354736</v>
+        <v>3.26203584671021</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G439" t="n">
-        <v>3.31279373168945</v>
+        <v>3.31279349327087</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G440" t="n">
-        <v>3.3134708404541</v>
+        <v>3.31347060203552</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.9210000038147</v>
       </c>
       <c r="G442" t="n">
-        <v>3.33038949966431</v>
+        <v>3.33038997650146</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.83900022506714</v>
       </c>
       <c r="G443" t="n">
-        <v>3.27489495277405</v>
+        <v>3.27489447593689</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G444" t="n">
-        <v>3.27963209152222</v>
+        <v>3.27963161468506</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G445" t="n">
-        <v>3.27286434173584</v>
+        <v>3.27286386489868</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G446" t="n">
-        <v>3.27963209152222</v>
+        <v>3.27963161468506</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.97200012207031</v>
       </c>
       <c r="G447" t="n">
-        <v>3.36490559577942</v>
+        <v>3.36490511894226</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G449" t="n">
-        <v>3.30670285224915</v>
+        <v>3.30670261383057</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G451" t="n">
-        <v>3.27015686035156</v>
+        <v>3.27015662193298</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.85099983215332</v>
       </c>
       <c r="G452" t="n">
-        <v>3.28301548957825</v>
+        <v>3.28301525115967</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G453" t="n">
-        <v>3.25729846954346</v>
+        <v>3.25729823112488</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.79300022125244</v>
       </c>
       <c r="G455" t="n">
-        <v>3.24376320838928</v>
+        <v>3.2437629699707</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G456" t="n">
-        <v>3.28639984130859</v>
+        <v>3.28640007972717</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G457" t="n">
-        <v>3.19368195533752</v>
+        <v>3.19368147850037</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G458" t="n">
-        <v>3.15645980834961</v>
+        <v>3.15645956993103</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.67399978637695</v>
       </c>
       <c r="G459" t="n">
-        <v>3.16322755813599</v>
+        <v>3.16322708129883</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G460" t="n">
-        <v>3.16728782653809</v>
+        <v>3.16728806495667</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.65100002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>3.1476616859436</v>
+        <v>3.14766144752502</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G463" t="n">
-        <v>3.11314630508423</v>
+        <v>3.11314654350281</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>3.19097518920898</v>
+        <v>3.19097542762756</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G466" t="n">
-        <v>3.18894410133362</v>
+        <v>3.18894481658936</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.73400020599365</v>
       </c>
       <c r="G469" t="n">
-        <v>3.20383405685425</v>
+        <v>3.20383381843567</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G470" t="n">
-        <v>3.32632946968079</v>
+        <v>3.32632875442505</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>3.35001587867737</v>
+        <v>3.35001611709595</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.94600009918213</v>
       </c>
       <c r="G472" t="n">
-        <v>3.34730911254883</v>
+        <v>3.34730887413025</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G474" t="n">
-        <v>3.30128860473633</v>
+        <v>3.30128836631775</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G475" t="n">
-        <v>3.30940961837769</v>
+        <v>3.30940985679626</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>3.2417323589325</v>
+        <v>3.24173259735107</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.89300012588501</v>
       </c>
       <c r="G479" t="n">
-        <v>3.31144022941589</v>
+        <v>3.31143999099731</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.80100011825562</v>
       </c>
       <c r="G481" t="n">
-        <v>3.24917793273926</v>
+        <v>3.2491774559021</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>3.24511647224426</v>
+        <v>3.24511671066284</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.67399978637695</v>
       </c>
       <c r="G484" t="n">
-        <v>3.16322755813599</v>
+        <v>3.16322708129883</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G485" t="n">
-        <v>3.16864156723022</v>
+        <v>3.16864132881165</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.74900007247925</v>
       </c>
       <c r="G487" t="n">
-        <v>3.21398496627808</v>
+        <v>3.21398568153381</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G488" t="n">
-        <v>3.13818645477295</v>
+        <v>3.13818693161011</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G489" t="n">
-        <v>3.11043930053711</v>
+        <v>3.11043953895569</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G490" t="n">
-        <v>3.07321643829346</v>
+        <v>3.07321667671204</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G491" t="n">
-        <v>3.09690356254578</v>
+        <v>3.09690403938293</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G492" t="n">
-        <v>3.06847929954529</v>
+        <v>3.06847906112671</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.46700000762939</v>
       </c>
       <c r="G493" t="n">
-        <v>3.02313542366028</v>
+        <v>3.02313566207886</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.46099996566772</v>
       </c>
       <c r="G495" t="n">
-        <v>3.01907444000244</v>
+        <v>3.01907515525818</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.59100008010864</v>
       </c>
       <c r="G496" t="n">
-        <v>3.10705542564392</v>
+        <v>3.1070556640625</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.51100015640259</v>
       </c>
       <c r="G499" t="n">
-        <v>3.05291366577148</v>
+        <v>3.05291342735291</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>3.09961080551147</v>
+        <v>3.09961128234863</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G504" t="n">
-        <v>3.09419679641724</v>
+        <v>3.09419631958008</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G505" t="n">
-        <v>3.11314630508423</v>
+        <v>3.11314654350281</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G506" t="n">
-        <v>3.09148907661438</v>
+        <v>3.09148955345154</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G507" t="n">
-        <v>3.0874285697937</v>
+        <v>3.08742880821228</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G509" t="n">
-        <v>3.13277292251587</v>
+        <v>3.13277244567871</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.68900012969971</v>
       </c>
       <c r="G510" t="n">
-        <v>3.17337870597839</v>
+        <v>3.17337894439697</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.77199983596802</v>
       </c>
       <c r="G511" t="n">
-        <v>3.22955083847046</v>
+        <v>3.22955107688904</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G512" t="n">
-        <v>3.27895498275757</v>
+        <v>3.27895474433899</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.85900020599365</v>
       </c>
       <c r="G513" t="n">
-        <v>3.28842997550964</v>
+        <v>3.28843021392822</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G514" t="n">
-        <v>3.3398642539978</v>
+        <v>3.33986449241638</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G515" t="n">
-        <v>3.26203632354736</v>
+        <v>3.26203584671021</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G516" t="n">
-        <v>3.29993510246277</v>
+        <v>3.29993557929993</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G518" t="n">
-        <v>3.19368195533752</v>
+        <v>3.19368147850037</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G519" t="n">
-        <v>3.21601510047913</v>
+        <v>3.21601557731628</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>4.72700023651123</v>
       </c>
       <c r="G520" t="n">
-        <v>3.19909644126892</v>
+        <v>3.19909620285034</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G521" t="n">
-        <v>3.15984320640564</v>
+        <v>3.15984344482422</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G522" t="n">
-        <v>3.16390371322632</v>
+        <v>3.1639039516449</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G524" t="n">
-        <v>3.17405557632446</v>
+        <v>3.17405533790588</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G526" t="n">
-        <v>3.25120711326599</v>
+        <v>3.25120735168457</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>4.72700023651123</v>
       </c>
       <c r="G529" t="n">
-        <v>3.19909644126892</v>
+        <v>3.19909620285034</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G530" t="n">
-        <v>3.21736907958984</v>
+        <v>3.21736931800842</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>4.76300001144409</v>
       </c>
       <c r="G531" t="n">
-        <v>3.22346019744873</v>
+        <v>3.22345995903015</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>4.82299995422363</v>
       </c>
       <c r="G532" t="n">
-        <v>3.26406574249268</v>
+        <v>3.26406621932983</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G533" t="n">
-        <v>3.24714684486389</v>
+        <v>3.24714660644531</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G536" t="n">
-        <v>3.3060257434845</v>
+        <v>3.30602598190308</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>3.43799638748169</v>
+        <v>3.43799662590027</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G539" t="n">
-        <v>3.45829916000366</v>
+        <v>3.45829939842224</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.13600015640259</v>
       </c>
       <c r="G540" t="n">
-        <v>3.47589516639709</v>
+        <v>3.47589564323425</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.10799980163574</v>
       </c>
       <c r="G541" t="n">
-        <v>3.4569456577301</v>
+        <v>3.45694541931152</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.0939998626709</v>
       </c>
       <c r="G543" t="n">
-        <v>3.44747066497803</v>
+        <v>3.44747090339661</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G544" t="n">
-        <v>3.44611787796021</v>
+        <v>3.44611763954163</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G547" t="n">
-        <v>3.42581415176392</v>
+        <v>3.4258143901825</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G548" t="n">
-        <v>3.4650673866272</v>
+        <v>3.46506762504578</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G549" t="n">
-        <v>3.49349188804626</v>
+        <v>3.49349141120911</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.2039999961853</v>
       </c>
       <c r="G550" t="n">
-        <v>3.52191591262817</v>
+        <v>3.52191615104675</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G551" t="n">
-        <v>3.46642065048218</v>
+        <v>3.46642088890076</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G553" t="n">
-        <v>3.52868390083313</v>
+        <v>3.52868366241455</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G554" t="n">
-        <v>3.5503396987915</v>
+        <v>3.55034041404724</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G555" t="n">
-        <v>3.49755215644836</v>
+        <v>3.49755191802979</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>3.52597641944885</v>
+        <v>3.52597618103027</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G557" t="n">
-        <v>3.53003716468811</v>
+        <v>3.53003692626953</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G558" t="n">
-        <v>3.52056241035461</v>
+        <v>3.52056264877319</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>5.25400018692017</v>
       </c>
       <c r="G559" t="n">
-        <v>3.55575466156006</v>
+        <v>3.55575442314148</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>5.25</v>
       </c>
       <c r="G560" t="n">
-        <v>3.5530469417572</v>
+        <v>3.55304741859436</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>3.52597641944885</v>
+        <v>3.52597618103027</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>3.52597641944885</v>
+        <v>3.52597618103027</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.25</v>
       </c>
       <c r="G564" t="n">
-        <v>3.5530469417572</v>
+        <v>3.55304741859436</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G565" t="n">
-        <v>3.49755215644836</v>
+        <v>3.49755191802979</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G570" t="n">
-        <v>3.53545117378235</v>
+        <v>3.53545165061951</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G573" t="n">
-        <v>3.48266339302063</v>
+        <v>3.48266267776489</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G574" t="n">
-        <v>3.46100640296936</v>
+        <v>3.46100664138794</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.22800016403198</v>
       </c>
       <c r="G577" t="n">
-        <v>3.53815865516663</v>
+        <v>3.53815817832947</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G578" t="n">
-        <v>3.52868390083313</v>
+        <v>3.52868366241455</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.22599983215332</v>
       </c>
       <c r="G579" t="n">
-        <v>3.53680515289307</v>
+        <v>3.53680467605591</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G580" t="n">
-        <v>3.53951168060303</v>
+        <v>3.53951215744019</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G581" t="n">
-        <v>3.52462339401245</v>
+        <v>3.52462315559387</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>5.2039999961853</v>
       </c>
       <c r="G582" t="n">
-        <v>3.52191591262817</v>
+        <v>3.52191615104675</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>3.52597641944885</v>
+        <v>3.52597618103027</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.30800008773804</v>
       </c>
       <c r="G585" t="n">
-        <v>3.59230065345764</v>
+        <v>3.59229969978333</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>5.26599979400635</v>
       </c>
       <c r="G587" t="n">
-        <v>3.56387543678284</v>
+        <v>3.56387567520142</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G588" t="n">
-        <v>3.6044819355011</v>
+        <v>3.60448217391968</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G589" t="n">
-        <v>3.59906768798828</v>
+        <v>3.59906792640686</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G590" t="n">
-        <v>3.5584614276886</v>
+        <v>3.55846166610718</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G592" t="n">
-        <v>3.62207841873169</v>
+        <v>3.62207818031311</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G593" t="n">
-        <v>3.67622017860413</v>
+        <v>3.67621970176697</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.46799993515015</v>
       </c>
       <c r="G594" t="n">
-        <v>3.7005832195282</v>
+        <v>3.70058393478394</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>5.42600011825562</v>
       </c>
       <c r="G595" t="n">
-        <v>3.67215919494629</v>
+        <v>3.67215895652771</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>3.6545627117157</v>
+        <v>3.65456318855286</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>3.6545627117157</v>
+        <v>3.65456318855286</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>3.6545627117157</v>
+        <v>3.65456318855286</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.69516849517822</v>
+        <v>3.69516921043396</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G602" t="n">
-        <v>3.70464420318604</v>
+        <v>3.70464396476746</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>5.49399995803833</v>
       </c>
       <c r="G603" t="n">
-        <v>3.71817946434021</v>
+        <v>3.71817898750305</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>5.48199987411499</v>
       </c>
       <c r="G604" t="n">
-        <v>3.71005797386169</v>
+        <v>3.71005868911743</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>5.50799989700317</v>
       </c>
       <c r="G605" t="n">
-        <v>3.72765374183655</v>
+        <v>3.72765421867371</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>5.5</v>
       </c>
       <c r="G606" t="n">
-        <v>3.72223925590515</v>
+        <v>3.72224020957947</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>5.50400018692017</v>
       </c>
       <c r="G609" t="n">
-        <v>3.72494745254517</v>
+        <v>3.72494769096375</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>5.49200010299683</v>
       </c>
       <c r="G611" t="n">
-        <v>3.71682643890381</v>
+        <v>3.71682548522949</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G612" t="n">
-        <v>3.75607895851135</v>
+        <v>3.75607872009277</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G613" t="n">
-        <v>3.72359323501587</v>
+        <v>3.72359347343445</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>5.52199983596802</v>
       </c>
       <c r="G614" t="n">
-        <v>3.7371289730072</v>
+        <v>3.73712921142578</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>5.5460000038147</v>
       </c>
       <c r="G615" t="n">
-        <v>3.75337147712708</v>
+        <v>3.7533712387085</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G616" t="n">
-        <v>3.75201821327209</v>
+        <v>3.75201845169067</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G617" t="n">
-        <v>3.79533076286316</v>
+        <v>3.79533123970032</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G618" t="n">
-        <v>3.78856348991394</v>
+        <v>3.78856420516968</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G620" t="n">
-        <v>3.76555371284485</v>
+        <v>3.76555347442627</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G621" t="n">
-        <v>3.72359323501587</v>
+        <v>3.72359347343445</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G622" t="n">
-        <v>3.70464420318604</v>
+        <v>3.70464396476746</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>5.52600002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>3.73983597755432</v>
+        <v>3.7398362159729</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G624" t="n">
-        <v>3.76555371284485</v>
+        <v>3.76555347442627</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>5.53399991989136</v>
       </c>
       <c r="G628" t="n">
-        <v>3.74524998664856</v>
+        <v>3.74524974822998</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G629" t="n">
-        <v>3.76284575462341</v>
+        <v>3.76284599304199</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G632" t="n">
-        <v>3.71547245979309</v>
+        <v>3.71547198295593</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G635" t="n">
-        <v>3.70870494842529</v>
+        <v>3.70870423316956</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G637" t="n">
-        <v>3.78179597854614</v>
+        <v>3.78179550170898</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G638" t="n">
-        <v>3.81157350540161</v>
+        <v>3.81157374382019</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G639" t="n">
-        <v>3.83864426612854</v>
+        <v>3.83864498138428</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G640" t="n">
-        <v>3.90632128715515</v>
+        <v>3.90632176399231</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>3.90496778488159</v>
+        <v>3.90496826171875</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>3.95402979850769</v>
+        <v>3.95403027534485</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>4.03142166137695</v>
+        <v>4.03142213821411</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>5.72200012207031</v>
       </c>
       <c r="G647" t="n">
-        <v>4.02579355239868</v>
+        <v>4.02579307556152</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>5.70800018310547</v>
       </c>
       <c r="G648" t="n">
-        <v>4.01594305038452</v>
+        <v>4.01594352722168</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94699430465698</v>
+        <v>3.94699478149414</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G650" t="n">
-        <v>3.93292307853699</v>
+        <v>3.93292331695557</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>5.85799980163574</v>
       </c>
       <c r="G654" t="n">
-        <v>4.12147808074951</v>
+        <v>4.12147760391235</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G655" t="n">
-        <v>4.13695621490479</v>
+        <v>4.13695669174194</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G660" t="n">
-        <v>4.13695621490479</v>
+        <v>4.13695669174194</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>4.1580638885498</v>
+        <v>4.15806341171265</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G665" t="n">
-        <v>4.25656270980835</v>
+        <v>4.25656318664551</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>4.26359844207764</v>
+        <v>4.26359796524048</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>5.89799976348877</v>
       </c>
       <c r="G672" t="n">
-        <v>4.14962005615234</v>
+        <v>4.14962100982666</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>4.2495265007019</v>
+        <v>4.24952697753906</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G677" t="n">
-        <v>4.30299711227417</v>
+        <v>4.30299806594849</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>4.32691860198975</v>
+        <v>4.3269190788269</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>6.12799978256226</v>
       </c>
       <c r="G679" t="n">
-        <v>4.31144046783447</v>
+        <v>4.31143999099731</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G680" t="n">
-        <v>4.34943246841431</v>
+        <v>4.34943342208862</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G681" t="n">
-        <v>4.36772584915161</v>
+        <v>4.36772489547729</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>6.22800016403198</v>
       </c>
       <c r="G682" t="n">
-        <v>4.38179636001587</v>
+        <v>4.38179683685303</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G685" t="n">
-        <v>4.35506153106689</v>
+        <v>4.35506200790405</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G686" t="n">
-        <v>4.21434879302979</v>
+        <v>4.21434831619263</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>6.02199983596802</v>
       </c>
       <c r="G688" t="n">
-        <v>4.23686218261719</v>
+        <v>4.2368631362915</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G690" t="n">
-        <v>4.19464826583862</v>
+        <v>4.19464874267578</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>4.13695621490479</v>
+        <v>4.13695669174194</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G694" t="n">
-        <v>4.02297925949097</v>
+        <v>4.02297878265381</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G695" t="n">
-        <v>4.10740661621094</v>
+        <v>4.10740613937378</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>5.7979998588562</v>
       </c>
       <c r="G698" t="n">
-        <v>4.07926464080811</v>
+        <v>4.07926416397095</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>5.83400011062622</v>
       </c>
       <c r="G700" t="n">
-        <v>4.10459280014038</v>
+        <v>4.10459232330322</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G701" t="n">
-        <v>3.93855142593384</v>
+        <v>3.93855166435242</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G702" t="n">
-        <v>3.98357963562012</v>
+        <v>3.98357915878296</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>5.6560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97935795783997</v>
+        <v>3.97935843467712</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G706" t="n">
-        <v>4.12007093429565</v>
+        <v>4.12007141113281</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G707" t="n">
-        <v>4.03845739364624</v>
+        <v>4.0384578704834</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>5.72200012207031</v>
       </c>
       <c r="G709" t="n">
-        <v>4.02579355239868</v>
+        <v>4.02579307556152</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G712" t="n">
-        <v>4.10740661621094</v>
+        <v>4.10740613937378</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G714" t="n">
-        <v>4.15524959564209</v>
+        <v>4.15524911880493</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G715" t="n">
-        <v>4.15102767944336</v>
+        <v>4.15102815628052</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G716" t="n">
-        <v>4.1580638885498</v>
+        <v>4.15806341171265</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>5.91800022125244</v>
       </c>
       <c r="G718" t="n">
-        <v>4.16369247436523</v>
+        <v>4.16369199752808</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G721" t="n">
-        <v>4.02860736846924</v>
+        <v>4.0286078453064</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>5.63600015640259</v>
       </c>
       <c r="G722" t="n">
-        <v>3.96528673171997</v>
+        <v>3.96528697013855</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G723" t="n">
-        <v>3.92870163917542</v>
+        <v>3.92870211601257</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.00468683242798</v>
+        <v>4.00468635559082</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G725" t="n">
-        <v>3.96387958526611</v>
+        <v>3.96387934684753</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>5.61399984359741</v>
       </c>
       <c r="G726" t="n">
-        <v>3.94980835914612</v>
+        <v>3.94980788230896</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>4.00327968597412</v>
+        <v>4.00327920913696</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G729" t="n">
-        <v>4.00327968597412</v>
+        <v>4.00327920913696</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G731" t="n">
-        <v>4.07082176208496</v>
+        <v>4.0708212852478</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G732" t="n">
-        <v>4.15524959564209</v>
+        <v>4.15524911880493</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G733" t="n">
-        <v>4.11584949493408</v>
+        <v>4.11584901809692</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>5.97399997711182</v>
       </c>
       <c r="G734" t="n">
-        <v>4.20309162139893</v>
+        <v>4.20309209823608</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G735" t="n">
-        <v>4.14258527755737</v>
+        <v>4.14258480072021</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>5.73199987411499</v>
       </c>
       <c r="G738" t="n">
-        <v>4.03282880783081</v>
+        <v>4.03282928466797</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G739" t="n">
-        <v>4.11584949493408</v>
+        <v>4.11584901809692</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G740" t="n">
-        <v>4.12851333618164</v>
+        <v>4.1285138130188</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G741" t="n">
-        <v>4.18339157104492</v>
+        <v>4.18339204788208</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G742" t="n">
-        <v>4.10740661621094</v>
+        <v>4.10740613937378</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G743" t="n">
-        <v>4.06660079956055</v>
+        <v>4.06659984588623</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G744" t="n">
-        <v>4.01031541824341</v>
+        <v>4.01031494140625</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G746" t="n">
-        <v>4.03845739364624</v>
+        <v>4.0384578704834</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G747" t="n">
-        <v>4.00890827178955</v>
+        <v>4.00890779495239</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G752" t="n">
-        <v>4.02297925949097</v>
+        <v>4.02297878265381</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G753" t="n">
-        <v>3.99061489105225</v>
+        <v>3.99061560630798</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03142166137695</v>
+        <v>4.03142213821411</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G755" t="n">
-        <v>4.03142166137695</v>
+        <v>4.03142213821411</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G756" t="n">
-        <v>4.02297925949097</v>
+        <v>4.02297878265381</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G758" t="n">
-        <v>4.06660079956055</v>
+        <v>4.06659984588623</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G759" t="n">
-        <v>4.05815744400024</v>
+        <v>4.0581579208374</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>5.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>4.07222938537598</v>
+        <v>4.07222890853882</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G763" t="n">
-        <v>4.16509866714478</v>
+        <v>4.16509962081909</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G766" t="n">
-        <v>4.12288522720337</v>
+        <v>4.12288475036621</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>5.97599983215332</v>
       </c>
       <c r="G768" t="n">
-        <v>4.20449924468994</v>
+        <v>4.20449829101562</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>5.83400011062622</v>
       </c>
       <c r="G770" t="n">
-        <v>4.10459280014038</v>
+        <v>4.10459232330322</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>5.7480001449585</v>
       </c>
       <c r="G772" t="n">
-        <v>4.04408597946167</v>
+        <v>4.04408645629883</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>5.76599979400635</v>
       </c>
       <c r="G773" t="n">
-        <v>4.05675029754639</v>
+        <v>4.05674982070923</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G776" t="n">
-        <v>4.06660079956055</v>
+        <v>4.06659984588623</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G777" t="n">
-        <v>4.0412712097168</v>
+        <v>4.04127168655396</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G778" t="n">
-        <v>4.05534362792969</v>
+        <v>4.05534315109253</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G784" t="n">
-        <v>3.87663841247559</v>
+        <v>3.87663793563843</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G785" t="n">
-        <v>3.84849524497986</v>
+        <v>3.84849548339844</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G786" t="n">
-        <v>3.78517460823059</v>
+        <v>3.78517436981201</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>5.43599987030029</v>
       </c>
       <c r="G787" t="n">
-        <v>3.82457423210144</v>
+        <v>3.82457399368286</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>5.5</v>
       </c>
       <c r="G788" t="n">
-        <v>3.8696014881134</v>
+        <v>3.86960220336914</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>5.43599987030029</v>
       </c>
       <c r="G790" t="n">
-        <v>3.82457423210144</v>
+        <v>3.82457399368286</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>5.49200010299683</v>
       </c>
       <c r="G791" t="n">
-        <v>3.86397433280945</v>
+        <v>3.86397314071655</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G792" t="n">
-        <v>3.95402979850769</v>
+        <v>3.95403027534485</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G793" t="n">
-        <v>3.93151593208313</v>
+        <v>3.93151569366455</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G794" t="n">
-        <v>3.93855142593384</v>
+        <v>3.93855166435242</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G795" t="n">
-        <v>3.98639392852783</v>
+        <v>3.98639416694641</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G796" t="n">
-        <v>3.95121598243713</v>
+        <v>3.95121574401855</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>3.96106576919556</v>
+        <v>3.9610652923584</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G798" t="n">
-        <v>3.83020257949829</v>
+        <v>3.83020210266113</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91744470596313</v>
+        <v>3.91744446754456</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G800" t="n">
-        <v>3.91040921211243</v>
+        <v>3.91040897369385</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85553121566772</v>
+        <v>3.85553073883057</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G802" t="n">
-        <v>3.85130977630615</v>
+        <v>3.85131001472473</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>3.92588710784912</v>
+        <v>3.92588758468628</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G806" t="n">
-        <v>3.99061489105225</v>
+        <v>3.99061560630798</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G807" t="n">
-        <v>3.96247243881226</v>
+        <v>3.96247339248657</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G810" t="n">
-        <v>4.05815744400024</v>
+        <v>4.0581579208374</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>5.78399991989136</v>
       </c>
       <c r="G811" t="n">
-        <v>4.0694146156311</v>
+        <v>4.06941413879395</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G812" t="n">
-        <v>4.0272011756897</v>
+        <v>4.02720069885254</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G813" t="n">
-        <v>4.01031541824341</v>
+        <v>4.01031494140625</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>5.80200004577637</v>
       </c>
       <c r="G815" t="n">
-        <v>4.08207893371582</v>
+        <v>4.08207845687866</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30581140518188</v>
+        <v>4.30581092834473</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G822" t="n">
-        <v>4.22842025756836</v>
+        <v>4.2284197807312</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>6.07800006866455</v>
       </c>
       <c r="G823" t="n">
-        <v>4.2762622833252</v>
+        <v>4.27626276016235</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G825" t="n">
-        <v>4.27063417434692</v>
+        <v>4.27063369750977</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G827" t="n">
-        <v>4.31988334655762</v>
+        <v>4.31988286972046</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>6.05800008773804</v>
       </c>
       <c r="G829" t="n">
-        <v>4.26219129562378</v>
+        <v>4.26219177246094</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G830" t="n">
-        <v>4.25656270980835</v>
+        <v>4.25656318664551</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G832" t="n">
-        <v>4.35506153106689</v>
+        <v>4.35506200790405</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>6.29400014877319</v>
       </c>
       <c r="G833" t="n">
-        <v>4.42823219299316</v>
+        <v>4.42823266983032</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>4.32691860198975</v>
+        <v>4.3269190788269</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G836" t="n">
-        <v>4.12851333618164</v>
+        <v>4.1285138130188</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G837" t="n">
-        <v>4.0412712097168</v>
+        <v>4.04127168655396</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G838" t="n">
-        <v>4.08348512649536</v>
+        <v>4.08348560333252</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G839" t="n">
-        <v>4.08067178726196</v>
+        <v>4.0806713104248</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>3.91181540489197</v>
+        <v>3.91181564331055</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G842" t="n">
-        <v>3.96106576919556</v>
+        <v>3.9610652923584</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G844" t="n">
-        <v>4.08067178726196</v>
+        <v>4.0806713104248</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G845" t="n">
-        <v>3.91744470596313</v>
+        <v>3.91744446754456</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G846" t="n">
-        <v>3.56988334655762</v>
+        <v>3.56988382339478</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>4.78700017929077</v>
       </c>
       <c r="G847" t="n">
-        <v>3.36796092987061</v>
+        <v>3.36796116828918</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>3.35248231887817</v>
+        <v>3.35248255729675</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>2.89305567741394</v>
+        <v>2.89305520057678</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G851" t="n">
-        <v>3.01688265800476</v>
+        <v>3.01688289642334</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G852" t="n">
-        <v>3.13086009025574</v>
+        <v>3.13085985183716</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G853" t="n">
-        <v>3.15478157997131</v>
+        <v>3.15478134155273</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>4.56099987030029</v>
       </c>
       <c r="G854" t="n">
-        <v>3.20895504951477</v>
+        <v>3.20895528793335</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G855" t="n">
-        <v>3.07457518577576</v>
+        <v>3.07457494735718</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G857" t="n">
-        <v>3.21247363090515</v>
+        <v>3.21247339248657</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G858" t="n">
-        <v>3.24483752250671</v>
+        <v>3.24483728408813</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>3.20121669769287</v>
+        <v>3.20121645927429</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>4.85900020599365</v>
       </c>
       <c r="G861" t="n">
-        <v>3.41861772537231</v>
+        <v>3.41861796379089</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>4.98899984359741</v>
       </c>
       <c r="G862" t="n">
-        <v>3.51008129119873</v>
+        <v>3.51008057594299</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G863" t="n">
-        <v>3.30252933502197</v>
+        <v>3.30252981185913</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G864" t="n">
-        <v>3.40525031089783</v>
+        <v>3.40524983406067</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G865" t="n">
-        <v>3.43479990959167</v>
+        <v>3.43480014801025</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>3.39821410179138</v>
+        <v>3.39821457862854</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G869" t="n">
-        <v>3.39680695533752</v>
+        <v>3.39680743217468</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G871" t="n">
-        <v>3.44042801856995</v>
+        <v>3.4404284954071</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G872" t="n">
-        <v>3.47138500213623</v>
+        <v>3.47138452529907</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G873" t="n">
-        <v>3.41932082176208</v>
+        <v>3.41932129859924</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G874" t="n">
-        <v>3.42072820663452</v>
+        <v>3.4207284450531</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G876" t="n">
-        <v>3.46294188499451</v>
+        <v>3.46294260025024</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G877" t="n">
-        <v>3.37710785865784</v>
+        <v>3.37710762023926</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G878" t="n">
-        <v>3.42213535308838</v>
+        <v>3.42213582992554</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G880" t="n">
-        <v>3.41509985923767</v>
+        <v>3.41510009765625</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>3.42635703086853</v>
+        <v>3.42635726928711</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G882" t="n">
-        <v>3.59169483184814</v>
+        <v>3.59169459342957</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G884" t="n">
-        <v>3.54596209526062</v>
+        <v>3.54596304893494</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>4.90799999237061</v>
       </c>
       <c r="G885" t="n">
-        <v>3.45309257507324</v>
+        <v>3.45309209823608</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G888" t="n">
-        <v>3.47701358795166</v>
+        <v>3.4770131111145</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G889" t="n">
-        <v>3.46997809410095</v>
+        <v>3.46997761726379</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G891" t="n">
-        <v>3.46857118606567</v>
+        <v>3.46857094764709</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G892" t="n">
-        <v>3.55299878120422</v>
+        <v>3.55299854278564</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G893" t="n">
-        <v>3.57692694664001</v>
+        <v>3.57692718505859</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G895" t="n">
-        <v>3.50748705863953</v>
+        <v>3.50748682022095</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G898" t="n">
-        <v>3.59022426605225</v>
+        <v>3.59022450447083</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G899" t="n">
-        <v>3.57101774215698</v>
+        <v>3.5710175037384</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G901" t="n">
-        <v>3.64489030838013</v>
+        <v>3.64489078521729</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G902" t="n">
-        <v>3.60943126678467</v>
+        <v>3.60943150520325</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>3.65671014785767</v>
+        <v>3.65670990943909</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G905" t="n">
-        <v>3.8266179561615</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>5.25</v>
       </c>
       <c r="G906" t="n">
-        <v>3.87832880020142</v>
+        <v>3.87832856178284</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G907" t="n">
-        <v>3.8266179561615</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G909" t="n">
-        <v>3.76013231277466</v>
+        <v>3.76013207435608</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>4.94600009918213</v>
       </c>
       <c r="G911" t="n">
-        <v>3.6537549495697</v>
+        <v>3.65375518798828</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>3.75274515151978</v>
+        <v>3.75274538993835</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G913" t="n">
-        <v>3.8266179561615</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G915" t="n">
-        <v>3.88571643829346</v>
+        <v>3.88571572303772</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G918" t="n">
-        <v>3.88571643829346</v>
+        <v>3.88571572303772</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>5.25</v>
       </c>
       <c r="G919" t="n">
-        <v>3.87832880020142</v>
+        <v>3.87832856178284</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G921" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G922" t="n">
-        <v>3.81923007965088</v>
+        <v>3.81923079490662</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>3.81923007965088</v>
+        <v>3.81923079490662</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>3.86355400085449</v>
+        <v>3.86355376243591</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.85986089706421</v>
+        <v>3.85986065864563</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G928" t="n">
-        <v>3.8967969417572</v>
+        <v>3.89679741859436</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G929" t="n">
-        <v>3.93742728233337</v>
+        <v>3.93742704391479</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>3.88202285766602</v>
+        <v>3.88202261924744</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>5.125</v>
       </c>
       <c r="G931" t="n">
-        <v>3.78598809242249</v>
+        <v>3.78598785400391</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G932" t="n">
-        <v>3.79337501525879</v>
+        <v>3.79337549209595</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G933" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>3.80076217651367</v>
+        <v>3.80076193809509</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G936" t="n">
-        <v>3.80445599555969</v>
+        <v>3.80445575714111</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G937" t="n">
-        <v>3.86355400085449</v>
+        <v>3.86355376243591</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G938" t="n">
-        <v>3.90049123764038</v>
+        <v>3.90049147605896</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G939" t="n">
-        <v>3.94850778579712</v>
+        <v>3.94850826263428</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G940" t="n">
-        <v>3.93004035949707</v>
+        <v>3.93003964424133</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G942" t="n">
-        <v>3.8746349811554</v>
+        <v>3.87463450431824</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G943" t="n">
-        <v>3.9522020816803</v>
+        <v>3.95220136642456</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G944" t="n">
-        <v>4.0777850151062</v>
+        <v>4.07778549194336</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G945" t="n">
-        <v>4.08517360687256</v>
+        <v>4.0851731300354</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G947" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868772506714</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G948" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868772506714</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>3.98544502258301</v>
+        <v>3.98544454574585</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G951" t="n">
-        <v>3.98913764953613</v>
+        <v>3.98913812637329</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>4.10364103317261</v>
+        <v>4.10364055633545</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G961" t="n">
-        <v>4.08147954940796</v>
+        <v>4.0814790725708</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>5.5</v>
       </c>
       <c r="G962" t="n">
-        <v>4.06301069259644</v>
+        <v>4.06301116943359</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G963" t="n">
-        <v>4.12949752807617</v>
+        <v>4.12949705123901</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G964" t="n">
-        <v>4.11841535568237</v>
+        <v>4.11841583251953</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G966" t="n">
-        <v>3.98913764953613</v>
+        <v>3.98913812637329</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G967" t="n">
-        <v>3.95958924293518</v>
+        <v>3.9595890045166</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>3.98544502258301</v>
+        <v>3.98544454574585</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G969" t="n">
-        <v>3.95958924293518</v>
+        <v>3.9595890045166</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G971" t="n">
-        <v>4.00760650634766</v>
+        <v>4.00760698318481</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G972" t="n">
-        <v>3.90049123764038</v>
+        <v>3.90049147605896</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G973" t="n">
-        <v>3.99652552604675</v>
+        <v>3.99652576446533</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>4.0113000869751</v>
+        <v>4.01130056381226</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>4.00760650634766</v>
+        <v>4.00760698318481</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G977" t="n">
-        <v>4.0113000869751</v>
+        <v>4.01130056381226</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.94112133979797</v>
+        <v>3.94112110137939</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99652552604675</v>
+        <v>3.99652576446533</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G980" t="n">
-        <v>4.00760650634766</v>
+        <v>4.00760698318481</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G981" t="n">
-        <v>3.98913764953613</v>
+        <v>3.98913812637329</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G983" t="n">
-        <v>3.93742728233337</v>
+        <v>3.93742704391479</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G984" t="n">
-        <v>3.97805714607239</v>
+        <v>3.97805738449097</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G985" t="n">
-        <v>3.97436356544495</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G986" t="n">
-        <v>3.98175072669983</v>
+        <v>3.98175096511841</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G987" t="n">
-        <v>3.9522020816803</v>
+        <v>3.95220136642456</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>5.5</v>
       </c>
       <c r="G988" t="n">
-        <v>4.06301069259644</v>
+        <v>4.06301116943359</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G989" t="n">
-        <v>4.0149941444397</v>
+        <v>4.01499366760254</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G990" t="n">
-        <v>3.97805714607239</v>
+        <v>3.97805738449097</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G993" t="n">
-        <v>3.90418386459351</v>
+        <v>3.90418457984924</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G994" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>3.72688961029053</v>
+        <v>3.72688937187195</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G997" t="n">
-        <v>3.79337501525879</v>
+        <v>3.79337549209595</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>3.86355400085449</v>
+        <v>3.86355376243591</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>3.86355400085449</v>
+        <v>3.86355376243591</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.81923007965088</v>
+        <v>3.81923079490662</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.77859973907471</v>
+        <v>3.77859997749329</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.76013231277466</v>
+        <v>3.76013207435608</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.72688961029053</v>
+        <v>3.72688937187195</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.55328798294067</v>
+        <v>3.55328822135925</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.66557455062866</v>
+        <v>3.66557478904724</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.70103430747986</v>
+        <v>3.70103406906128</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.83400464057922</v>
+        <v>3.83400535583496</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.90787792205811</v>
+        <v>3.90787768363953</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.93004035949707</v>
+        <v>3.93003964424133</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.86724853515625</v>
+        <v>3.86724829673767</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.93742728233337</v>
+        <v>3.93742704391479</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.90049123764038</v>
+        <v>3.90049147605896</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.95958924293518</v>
+        <v>3.9595890045166</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.98175072669983</v>
+        <v>3.98175096511841</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.97436356544495</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.99283170700073</v>
+        <v>3.99283218383789</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.00760650634766</v>
+        <v>4.00760698318481</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.97436356544495</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.95589566230774</v>
+        <v>3.95589542388916</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.98913764953613</v>
+        <v>3.98913812637329</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.90418386459351</v>
+        <v>3.90418457984924</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.90787792205811</v>
+        <v>3.90787768363953</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.94850778579712</v>
+        <v>3.94850826263428</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>5.25</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.87832880020142</v>
+        <v>3.87832856178284</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.81923007965088</v>
+        <v>3.81923079490662</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.77121329307556</v>
+        <v>3.77121305465698</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.75274515151978</v>
+        <v>3.75274538993835</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.75274515151978</v>
+        <v>3.75274538993835</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.80076217651367</v>
+        <v>3.80076193809509</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.73427605628967</v>
+        <v>3.73427629470825</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>4.93599987030029</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.6463680267334</v>
+        <v>3.64636778831482</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.73427605628967</v>
+        <v>3.73427629470825</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.82292413711548</v>
+        <v>3.8229238986969</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.84139204025269</v>
+        <v>3.84139251708984</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.8266179561615</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.78968119621277</v>
+        <v>3.78968167304993</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.86355400085449</v>
+        <v>3.86355376243591</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.80445599555969</v>
+        <v>3.80445575714111</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>5.125</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.78598809242249</v>
+        <v>3.78598785400391</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.71211504936218</v>
+        <v>3.7121148109436</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.76382517814636</v>
+        <v>3.76382541656494</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.75274515151978</v>
+        <v>3.75274538993835</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.69734048843384</v>
+        <v>3.69734025001526</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.65523266792297</v>
+        <v>3.65523242950439</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.64341306686401</v>
+        <v>3.64341330528259</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>5</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.69364595413208</v>
+        <v>3.69364619255066</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.73058319091797</v>
+        <v>3.73058342933655</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.67443943023682</v>
+        <v>3.67443919181824</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.65523266792297</v>
+        <v>3.65523242950439</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.75274515151978</v>
+        <v>3.75274538993835</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.77121329307556</v>
+        <v>3.77121305465698</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.77859973907471</v>
+        <v>3.77859997749329</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.82292413711548</v>
+        <v>3.8229238986969</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.82292413711548</v>
+        <v>3.8229238986969</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.80445599555969</v>
+        <v>3.80445575714111</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.8266179561615</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.75274515151978</v>
+        <v>3.75274538993835</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.74166440963745</v>
+        <v>3.74166417121887</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.71211504936218</v>
+        <v>3.7121148109436</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.70103430747986</v>
+        <v>3.70103406906128</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.71950197219849</v>
+        <v>3.71950173377991</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.70103430747986</v>
+        <v>3.70103406906128</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.67148470878601</v>
+        <v>3.67148447036743</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.69734048843384</v>
+        <v>3.69734025001526</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.64489030838013</v>
+        <v>3.64489078521729</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.60204410552979</v>
+        <v>3.60204434394836</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.65966510772705</v>
+        <v>3.65966486930847</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.63602542877197</v>
+        <v>3.63602590560913</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>5.125</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.78598809242249</v>
+        <v>3.78598785400391</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.81923007965088</v>
+        <v>3.81923079490662</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.87094187736511</v>
+        <v>3.87094140052795</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.90049123764038</v>
+        <v>3.90049147605896</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.94112133979797</v>
+        <v>3.94112110137939</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.90049123764038</v>
+        <v>3.90049147605896</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.93742728233337</v>
+        <v>3.93742704391479</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1112" t="n">
-        <v>4.07039880752563</v>
+        <v>4.07039833068848</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.07409143447876</v>
+        <v>4.07409191131592</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.13319063186646</v>
+        <v>4.1331901550293</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.10364103317261</v>
+        <v>4.10364055633545</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.08886671066284</v>
+        <v>4.08886623382568</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.08074045181274</v>
+        <v>4.0807409286499</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G1120" t="n">
-        <v>4.06448841094971</v>
+        <v>4.06448888778687</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.98913764953613</v>
+        <v>3.98913812637329</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>5.37799978256226</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.97288632392883</v>
+        <v>3.97288584709167</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.95367980003357</v>
+        <v>3.95367932319641</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.94776916503906</v>
+        <v>3.94776940345764</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.9906153678894</v>
+        <v>3.99061608314514</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1127" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868772506714</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>5.44199991226196</v>
       </c>
       <c r="G1129" t="n">
-        <v>4.02016496658325</v>
+        <v>4.02016448974609</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1130" t="n">
-        <v>4.05562353134155</v>
+        <v>4.05562448501587</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1131" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868772506714</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.99948048591614</v>
+        <v>3.99948024749756</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.00095844268799</v>
+        <v>4.00095796585083</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.99948048591614</v>
+        <v>3.99948024749756</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>5.5</v>
       </c>
       <c r="G1137" t="n">
-        <v>4.06301069259644</v>
+        <v>4.06301116943359</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>5.44799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.02459716796875</v>
+        <v>4.02459669113159</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.08517360687256</v>
+        <v>4.0851731300354</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.11029052734375</v>
+        <v>4.11029005050659</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>5.49200010299683</v>
       </c>
       <c r="G1145" t="n">
-        <v>4.05710124969482</v>
+        <v>4.05710172653198</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1146" t="n">
-        <v>4.08074045181274</v>
+        <v>4.0807409286499</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G1147" t="n">
-        <v>4.16495561599731</v>
+        <v>4.16495609283447</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.280198097229</v>
+        <v>4.28019762039185</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>5.49599981307983</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.25089311599731</v>
+        <v>4.25089263916016</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G1154" t="n">
-        <v>4.20139217376709</v>
+        <v>4.20139169692993</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1156" t="n">
-        <v>4.19829845428467</v>
+        <v>4.19829797744751</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1161" t="n">
-        <v>4.26172161102295</v>
+        <v>4.26172113418579</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.3096752166748</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G1166" t="n">
-        <v>4.33597230911255</v>
+        <v>4.33597278594971</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G1168" t="n">
-        <v>4.35608291625977</v>
+        <v>4.35608243942261</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1169" t="n">
-        <v>4.42414522171021</v>
+        <v>4.42414569854736</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.3885669708252</v>
+        <v>4.38856744766235</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1171" t="n">
-        <v>4.37155103683472</v>
+        <v>4.37155151367188</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>5.62599992752075</v>
       </c>
       <c r="G1172" t="n">
-        <v>4.35144138336182</v>
+        <v>4.35144186019897</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.27719068527222</v>
+        <v>4.27719020843506</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G1181" t="n">
-        <v>4.30658102035522</v>
+        <v>4.30658149719238</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>5.57800006866455</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.3143162727356</v>
+        <v>4.31431579589844</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.3096752166748</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.32978534698486</v>
+        <v>4.32978487014771</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>5.62200021743774</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.34834814071655</v>
+        <v>4.34834861755371</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.35298824310303</v>
+        <v>4.35298871994019</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.3096752166748</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.16890668869019</v>
+        <v>4.1689076423645</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.27719068527222</v>
+        <v>4.27719020843506</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>5.71199989318848</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.41795873641968</v>
+        <v>4.41795825958252</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>5.71400022506714</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.41950607299805</v>
+        <v>4.41950559616089</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G1202" t="n">
-        <v>4.43033409118652</v>
+        <v>4.43033361434937</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G1203" t="n">
-        <v>4.39784860610962</v>
+        <v>4.39784908294678</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.41177082061768</v>
+        <v>4.41177129745483</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1205" t="n">
-        <v>4.41177082061768</v>
+        <v>4.41177129745483</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>5.73199987411499</v>
       </c>
       <c r="G1206" t="n">
-        <v>4.43342733383179</v>
+        <v>4.43342685699463</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1207" t="n">
-        <v>4.45817804336548</v>
+        <v>4.45817756652832</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.46591281890869</v>
+        <v>4.46591234207153</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.49066352844238</v>
+        <v>4.49066305160522</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.56646108627319</v>
+        <v>4.56646156311035</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>5.97200012207031</v>
       </c>
       <c r="G1216" t="n">
-        <v>4.61905670166016</v>
+        <v>4.619056224823</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.63761901855469</v>
+        <v>4.63761854171753</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.60203981399536</v>
+        <v>4.60204029083252</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>5.81199979782104</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.4953031539917</v>
+        <v>4.49530363082886</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.37928628921509</v>
+        <v>4.37928676605225</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>5.61399984359741</v>
       </c>
       <c r="G1223" t="n">
-        <v>4.34216022491455</v>
+        <v>4.34215974807739</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>5.68400001525879</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.39630174636841</v>
+        <v>4.39630222320557</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.30039358139038</v>
+        <v>4.30039405822754</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1231" t="n">
-        <v>4.269455909729</v>
+        <v>4.26945543289185</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.33133268356323</v>
+        <v>4.33133220672607</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>5.52199983596802</v>
       </c>
       <c r="G1234" t="n">
-        <v>4.27100276947021</v>
+        <v>4.27100229263306</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>5.62200021743774</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.34834814071655</v>
+        <v>4.34834861755371</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.35608291625977</v>
+        <v>4.35608243942261</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.45508480072021</v>
+        <v>4.45508432388306</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>5.49599981307983</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.25089311599731</v>
+        <v>4.25089263916016</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1251" t="n">
-        <v>4.29265880584717</v>
+        <v>4.29265928268433</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.21222019195557</v>
+        <v>4.21222066879272</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>5.44199991226196</v>
       </c>
       <c r="G1255" t="n">
-        <v>4.20912647247314</v>
+        <v>4.2091269493103</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.22304821014404</v>
+        <v>4.2230486869812</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.22304821014404</v>
+        <v>4.2230486869812</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1259" t="n">
-        <v>4.29265880584717</v>
+        <v>4.29265928268433</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.33133268356323</v>
+        <v>4.33133220672607</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.37155103683472</v>
+        <v>4.37155151367188</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1266" t="n">
-        <v>4.24625205993652</v>
+        <v>4.24625158309937</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1268" t="n">
-        <v>4.30812835693359</v>
+        <v>4.30812883377075</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33415,7 +33415,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1271" t="n">
-        <v>4.434974193573</v>
+        <v>4.43497467041016</v>
       </c>
       <c r="H1271" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G1272" t="n">
-        <v>4.40403652191162</v>
+        <v>4.40403699874878</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.35298824310303</v>
+        <v>4.35298871994019</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>5.60200023651123</v>
       </c>
       <c r="G1276" t="n">
-        <v>4.33287954330444</v>
+        <v>4.33287906646729</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.33133268356323</v>
+        <v>4.33133220672607</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>5.5460000038147</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.2895655632019</v>
+        <v>4.28956508636475</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1281" t="n">
-        <v>4.29265880584717</v>
+        <v>4.29265928268433</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.35298824310303</v>
+        <v>4.35298871994019</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.25862741470337</v>
+        <v>4.25862693786621</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1287" t="n">
-        <v>4.29265880584717</v>
+        <v>4.29265928268433</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G1288" t="n">
-        <v>4.30658102035522</v>
+        <v>4.30658149719238</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G1290" t="n">
-        <v>4.31276941299438</v>
+        <v>4.31276988983154</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1292" t="n">
-        <v>4.51850748062134</v>
+        <v>4.51850700378418</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G1293" t="n">
-        <v>4.52160167694092</v>
+        <v>4.52160120010376</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1295" t="n">
-        <v>4.46591281890869</v>
+        <v>4.46591234207153</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>5.7480001449585</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.44580316543579</v>
+        <v>4.44580268859863</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>5.82200002670288</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.50303792953491</v>
+        <v>4.50303840637207</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>5.77799987792969</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.46900653839111</v>
+        <v>4.46900606155396</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1306" t="n">
-        <v>4.54789876937866</v>
+        <v>4.54789924621582</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1308" t="n">
-        <v>4.66700983047485</v>
+        <v>4.66701030731201</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1311" t="n">
-        <v>4.65154075622559</v>
+        <v>4.65154123306274</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1313" t="n">
-        <v>4.51850748062134</v>
+        <v>4.51850700378418</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.46281957626343</v>
+        <v>4.46281862258911</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1315" t="n">
-        <v>4.44270944595337</v>
+        <v>4.44270896911621</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>5.82200002670288</v>
       </c>
       <c r="G1316" t="n">
-        <v>4.50303792953491</v>
+        <v>4.50303840637207</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.5277886390686</v>
+        <v>4.52778911590576</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G1318" t="n">
-        <v>4.54171085357666</v>
+        <v>4.54171133041382</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.53861713409424</v>
+        <v>4.5386176109314</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.53861713409424</v>
+        <v>4.5386176109314</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G1324" t="n">
-        <v>4.51541376113892</v>
+        <v>4.51541328430176</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1325" t="n">
-        <v>4.45508480072021</v>
+        <v>4.45508432388306</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1326" t="n">
-        <v>4.45817804336548</v>
+        <v>4.45817756652832</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G1327" t="n">
-        <v>4.49066352844238</v>
+        <v>4.49066305160522</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>5.93599987030029</v>
       </c>
       <c r="G1328" t="n">
-        <v>4.59121179580688</v>
+        <v>4.59121227264404</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G1329" t="n">
-        <v>4.5277886390686</v>
+        <v>4.52778911590576</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>4.53861713409424</v>
+        <v>4.5386176109314</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.56646108627319</v>
+        <v>4.56646156311035</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>5.98400020599365</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.62833786010742</v>
+        <v>4.62833738327026</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G1334" t="n">
-        <v>4.39784860610962</v>
+        <v>4.39784908294678</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1335" t="n">
-        <v>4.31740951538086</v>
+        <v>4.3174090385437</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>5.52600002288818</v>
       </c>
       <c r="G1336" t="n">
-        <v>4.27409696578979</v>
+        <v>4.27409648895264</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.43188047409058</v>
+        <v>4.43188095092773</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.3885669708252</v>
+        <v>4.38856744766235</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.35453510284424</v>
+        <v>4.3545355796814</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.45508480072021</v>
+        <v>4.45508432388306</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>5.77799987792969</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.46900653839111</v>
+        <v>4.46900606155396</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.32978534698486</v>
+        <v>4.32978487014771</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1356" t="n">
-        <v>4.16890668869019</v>
+        <v>4.1689076423645</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>5.64200019836426</v>
       </c>
       <c r="G1357" t="n">
-        <v>4.36381673812866</v>
+        <v>4.36381721496582</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>5.52199983596802</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.27100276947021</v>
+        <v>4.27100229263306</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>5.64200019836426</v>
       </c>
       <c r="G1366" t="n">
-        <v>4.36381673812866</v>
+        <v>4.36381721496582</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>5.73199987411499</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.43342733383179</v>
+        <v>4.43342685699463</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.45817804336548</v>
+        <v>4.45817756652832</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>5.82399988174438</v>
       </c>
       <c r="G1373" t="n">
-        <v>4.50458574295044</v>
+        <v>4.50458526611328</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.45508480072021</v>
+        <v>4.45508432388306</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.68711948394775</v>
+        <v>4.68711996078491</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G1380" t="n">
-        <v>4.72966003417969</v>
+        <v>4.72965955734253</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.70645666122437</v>
+        <v>4.70645618438721</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.7915358543396</v>
+        <v>4.79153633117676</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>4.83020877838135</v>
+        <v>4.83020830154419</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G1387" t="n">
-        <v>4.84954500198364</v>
+        <v>4.84954452514648</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.77993392944336</v>
+        <v>4.77993488311768</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.803138256073</v>
+        <v>4.80313777923584</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.77993392944336</v>
+        <v>4.77993488311768</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>4.79927062988281</v>
+        <v>4.79927015304565</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G1396" t="n">
-        <v>4.72966003417969</v>
+        <v>4.72965955734253</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G1397" t="n">
-        <v>4.72966003417969</v>
+        <v>4.72965955734253</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.83020877838135</v>
+        <v>4.83020830154419</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.77993392944336</v>
+        <v>4.77993488311768</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>4.83794355392456</v>
+        <v>4.8379430770874</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.94235897064209</v>
+        <v>4.94235944747925</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G1408" t="n">
-        <v>4.98037004470825</v>
+        <v>4.98036956787109</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G1413" t="n">
-        <v>4.8469672203064</v>
+        <v>4.84696769714355</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1414" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909461975098</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1416" t="n">
-        <v>4.83079719543457</v>
+        <v>4.83079767227173</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.83079719543457</v>
+        <v>4.83079767227173</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1418" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909461975098</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1419" t="n">
-        <v>4.81058406829834</v>
+        <v>4.8105845451355</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.83079719543457</v>
+        <v>4.83079767227173</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1421" t="n">
-        <v>4.66505479812622</v>
+        <v>4.66505432128906</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.26888847351074</v>
+        <v>4.2688889503479</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1432" t="n">
-        <v>4.49526882171631</v>
+        <v>4.49526929855347</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.43463134765625</v>
+        <v>4.43463182449341</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>5.61499977111816</v>
       </c>
       <c r="G1434" t="n">
-        <v>4.53973627090454</v>
+        <v>4.5397367477417</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.49122667312622</v>
+        <v>4.49122619628906</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1437" t="n">
-        <v>4.52760982513428</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1438" t="n">
-        <v>4.52760982513428</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1440" t="n">
-        <v>4.42250394821167</v>
+        <v>4.42250347137451</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1441" t="n">
-        <v>4.43463134765625</v>
+        <v>4.43463182449341</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41037654876709</v>
+        <v>4.41037607192993</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.41037654876709</v>
+        <v>4.41037607192993</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1446" t="n">
-        <v>4.26080322265625</v>
+        <v>4.26080369949341</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.32548379898071</v>
+        <v>4.32548332214355</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.26484680175781</v>
+        <v>4.26484632492065</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G1451" t="n">
-        <v>4.20016574859619</v>
+        <v>4.20016622543335</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>4.27293109893799</v>
+        <v>4.27293062210083</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.27293109893799</v>
+        <v>4.27293062210083</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.39824867248535</v>
+        <v>4.39824914932251</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.43463134765625</v>
+        <v>4.43463182449341</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.41846132278442</v>
+        <v>4.41846179962158</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1462" t="n">
-        <v>4.42250394821167</v>
+        <v>4.42250347137451</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1463" t="n">
-        <v>4.45888662338257</v>
+        <v>4.45888614654541</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.4386739730835</v>
+        <v>4.43867349624634</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1467" t="n">
-        <v>4.43463134765625</v>
+        <v>4.43463182449341</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>5.61499977111816</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.53973627090454</v>
+        <v>4.5397367477417</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1469" t="n">
-        <v>4.5761194229126</v>
+        <v>4.57611846923828</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.59633255004883</v>
+        <v>4.59633207321167</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1471" t="n">
-        <v>4.52356624603271</v>
+        <v>4.52356672286987</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1472" t="n">
-        <v>4.56803464889526</v>
+        <v>4.56803417205811</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G1473" t="n">
-        <v>4.50739669799805</v>
+        <v>4.50739622116089</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.45888662338257</v>
+        <v>4.45888614654541</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.26888847351074</v>
+        <v>4.2688889503479</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1478" t="n">
-        <v>4.28505897521973</v>
+        <v>4.28505849838257</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G1479" t="n">
-        <v>4.15165567398071</v>
+        <v>4.15165615081787</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.12740135192871</v>
+        <v>4.12740087509155</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.15165567398071</v>
+        <v>4.15165615081787</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>4.20420837402344</v>
+        <v>4.20420789718628</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1491" t="n">
-        <v>4.13548564910889</v>
+        <v>4.13548517227173</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1494" t="n">
-        <v>4.17995357513428</v>
+        <v>4.17995309829712</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G1495" t="n">
-        <v>4.15974092483521</v>
+        <v>4.15974140167236</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.9665093421936</v>
+        <v>3.96650910377502</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.89859509468079</v>
+        <v>3.89859461784363</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.85493588447571</v>
+        <v>3.85493564605713</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39421,7 +39421,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.95033931732178</v>
+        <v>3.9503390789032</v>
       </c>
       <c r="H1502" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.85493588447571</v>
+        <v>3.85493564605713</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.8565526008606</v>
+        <v>3.85655283927917</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.80157494544983</v>
+        <v>3.80157518386841</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.89374375343323</v>
+        <v>3.89374399185181</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.8678719997406</v>
+        <v>3.86787176132202</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.91961574554443</v>
+        <v>3.91961598396301</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.84361696243286</v>
+        <v>3.84361743927002</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.97621130943298</v>
+        <v>3.9762110710144</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1521" t="n">
-        <v>4.27293109893799</v>
+        <v>4.27293062210083</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1523" t="n">
-        <v>4.19612407684326</v>
+        <v>4.1961236000061</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.26484680175781</v>
+        <v>4.26484632492065</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G1525" t="n">
-        <v>4.15974092483521</v>
+        <v>4.15974140167236</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1530" t="n">
-        <v>4.49122667312622</v>
+        <v>4.49122619628906</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G1532" t="n">
-        <v>4.41846132278442</v>
+        <v>4.41846179962158</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1533" t="n">
-        <v>4.43463134765625</v>
+        <v>4.43463182449341</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40305,7 +40305,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1536" t="n">
-        <v>4.48718357086182</v>
+        <v>4.48718404769897</v>
       </c>
       <c r="H1536" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.52760982513428</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1539" t="n">
-        <v>4.52356624603271</v>
+        <v>4.52356672286987</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.59633255004883</v>
+        <v>4.59633207321167</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>4.52760982513428</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G1544" t="n">
-        <v>4.53165149688721</v>
+        <v>4.53165102005005</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1546" t="n">
-        <v>4.55994939804077</v>
+        <v>4.55994892120361</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1547" t="n">
-        <v>4.55994939804077</v>
+        <v>4.55994892120361</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G1548" t="n">
-        <v>4.50739669799805</v>
+        <v>4.50739622116089</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G1549" t="n">
-        <v>4.56399154663086</v>
+        <v>4.56399202346802</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40721,7 +40721,7 @@
         <v>5.63500022888184</v>
       </c>
       <c r="G1552" t="n">
-        <v>4.55590629577637</v>
+        <v>4.55590724945068</v>
       </c>
       <c r="H1552" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1553" t="n">
-        <v>4.54377937316895</v>
+        <v>4.54377889633179</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G1555" t="n">
-        <v>4.41846132278442</v>
+        <v>4.41846179962158</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>4.32548379898071</v>
+        <v>4.32548332214355</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1558" t="n">
-        <v>4.27293109893799</v>
+        <v>4.27293062210083</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1559" t="n">
-        <v>4.35782384872437</v>
+        <v>4.35782432556152</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1561" t="n">
-        <v>4.32548379898071</v>
+        <v>4.32548332214355</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1564" t="n">
-        <v>4.28505897521973</v>
+        <v>4.28505849838257</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1565" t="n">
-        <v>4.19612407684326</v>
+        <v>4.1961236000061</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1568" t="n">
-        <v>4.33356952667236</v>
+        <v>4.33356857299805</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.25676107406616</v>
+        <v>4.256760597229</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.41037654876709</v>
+        <v>4.41037607192993</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1576" t="n">
-        <v>4.39824867248535</v>
+        <v>4.39824914932251</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>4.49526882171631</v>
+        <v>4.49526929855347</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1585" t="n">
-        <v>4.4386739730835</v>
+        <v>4.43867349624634</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1591" t="n">
-        <v>4.49526882171631</v>
+        <v>4.49526929855347</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.56803464889526</v>
+        <v>4.56803417205811</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1595" t="n">
-        <v>4.52760982513428</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>5.61499977111816</v>
       </c>
       <c r="G1596" t="n">
-        <v>4.53973627090454</v>
+        <v>4.5397367477417</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>4.41037654876709</v>
+        <v>4.41037607192993</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1605" t="n">
-        <v>4.3295259475708</v>
+        <v>4.32952642440796</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1609" t="n">
-        <v>4.26888847351074</v>
+        <v>4.2688889503479</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>4.27293109893799</v>
+        <v>4.27293062210083</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1613" t="n">
-        <v>4.25676107406616</v>
+        <v>4.256760597229</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1615" t="n">
-        <v>4.23654842376709</v>
+        <v>4.23654890060425</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1618" t="n">
-        <v>4.3295259475708</v>
+        <v>4.32952642440796</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G1621" t="n">
-        <v>4.50739669799805</v>
+        <v>4.50739622116089</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.45888662338257</v>
+        <v>4.45888614654541</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1624" t="n">
-        <v>4.42250394821167</v>
+        <v>4.42250347137451</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G1626" t="n">
-        <v>4.48718357086182</v>
+        <v>4.48718404769897</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.49122667312622</v>
+        <v>4.49122619628906</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.53165149688721</v>
+        <v>4.53165102005005</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>5.80499982833862</v>
       </c>
       <c r="G1633" t="n">
-        <v>4.69335126876831</v>
+        <v>4.69335174560547</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1635" t="n">
-        <v>4.83079719543457</v>
+        <v>4.83079767227173</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G1636" t="n">
-        <v>4.8469672203064</v>
+        <v>4.84696769714355</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1638" t="n">
-        <v>4.78632926940918</v>
+        <v>4.78632974624634</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>5.99499988555908</v>
       </c>
       <c r="G1641" t="n">
-        <v>4.8469672203064</v>
+        <v>4.84696769714355</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1642" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909461975098</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G1645" t="n">
-        <v>4.77420282363892</v>
+        <v>4.7742018699646</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G1646" t="n">
-        <v>4.70952177047729</v>
+        <v>4.70952224731445</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>5.75500011444092</v>
       </c>
       <c r="G1649" t="n">
-        <v>4.65292692184448</v>
+        <v>4.65292644500732</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G1651" t="n">
-        <v>4.72569179534912</v>
+        <v>4.72569227218628</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G1653" t="n">
-        <v>4.72569179534912</v>
+        <v>4.72569227218628</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>5.875</v>
       </c>
       <c r="G1655" t="n">
-        <v>4.74994659423828</v>
+        <v>4.74994707107544</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1656" t="n">
-        <v>4.78632926940918</v>
+        <v>4.78632974624634</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1657" t="n">
-        <v>4.83079719543457</v>
+        <v>4.83079767227173</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G1658" t="n">
-        <v>4.79037237167358</v>
+        <v>4.79037189483643</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1661" t="n">
-        <v>4.63271427154541</v>
+        <v>4.63271474838257</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -66048,6 +66048,32 @@
         <v>8.52000045776367</v>
       </c>
       <c r="H2526" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2527">
+      <c r="A2527" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2527" t="n">
+        <v>2216818</v>
+      </c>
+      <c r="C2527" t="n">
+        <v>8.61999988555908</v>
+      </c>
+      <c r="D2527" t="n">
+        <v>8.47599983215332</v>
+      </c>
+      <c r="E2527" t="n">
+        <v>8.47599983215332</v>
+      </c>
+      <c r="F2527" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="G2527" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="H2527" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -572,7 +572,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0038948059082</v>
+        <v>2.00389456748962</v>
       </c>
       <c r="H7" t="n">
         <v>20054402</v>
@@ -630,7 +630,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99765229225159</v>
+        <v>1.9976521730423</v>
       </c>
       <c r="H9" t="n">
         <v>7415318</v>
@@ -688,7 +688,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G11" t="n">
-        <v>1.97268164157867</v>
+        <v>1.97268187999725</v>
       </c>
       <c r="H11" t="n">
         <v>9571640</v>
@@ -775,7 +775,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G14" t="n">
-        <v>2.03885388374329</v>
+        <v>2.03885364532471</v>
       </c>
       <c r="H14" t="n">
         <v>7099278</v>
@@ -804,7 +804,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>2.05383634567261</v>
+        <v>2.05383610725403</v>
       </c>
       <c r="H15" t="n">
         <v>2202715</v>
@@ -891,7 +891,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G18" t="n">
-        <v>2.10627484321594</v>
+        <v>2.10627460479736</v>
       </c>
       <c r="H18" t="n">
         <v>7328944</v>
@@ -949,7 +949,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G20" t="n">
-        <v>2.08504939079285</v>
+        <v>2.08504915237427</v>
       </c>
       <c r="H20" t="n">
         <v>5666890</v>
@@ -978,7 +978,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G21" t="n">
-        <v>2.04135060310364</v>
+        <v>2.04135084152222</v>
       </c>
       <c r="H21" t="n">
         <v>6033410</v>
@@ -1007,7 +1007,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G22" t="n">
-        <v>2.00888895988464</v>
+        <v>2.00888919830322</v>
       </c>
       <c r="H22" t="n">
         <v>5833873</v>
@@ -1065,7 +1065,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G24" t="n">
-        <v>2.19367170333862</v>
+        <v>2.1936719417572</v>
       </c>
       <c r="H24" t="n">
         <v>6839861</v>
@@ -1123,7 +1123,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G26" t="n">
-        <v>2.19991421699524</v>
+        <v>2.1999146938324</v>
       </c>
       <c r="H26" t="n">
         <v>4376808</v>
@@ -1210,7 +1210,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20615720748901</v>
+        <v>2.20615696907043</v>
       </c>
       <c r="H29" t="n">
         <v>7212643</v>
@@ -1268,7 +1268,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G31" t="n">
-        <v>2.24611043930054</v>
+        <v>2.24611020088196</v>
       </c>
       <c r="H31" t="n">
         <v>6356152</v>
@@ -1326,7 +1326,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G33" t="n">
-        <v>2.35098695755005</v>
+        <v>2.35098719596863</v>
       </c>
       <c r="H33" t="n">
         <v>5873476</v>
@@ -1355,7 +1355,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G34" t="n">
-        <v>2.29480290412903</v>
+        <v>2.29480314254761</v>
       </c>
       <c r="H34" t="n">
         <v>4189580</v>
@@ -1413,7 +1413,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G36" t="n">
-        <v>2.29230570793152</v>
+        <v>2.2923059463501</v>
       </c>
       <c r="H36" t="n">
         <v>1759291</v>
@@ -1442,7 +1442,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G37" t="n">
-        <v>2.31852507591248</v>
+        <v>2.31852531433105</v>
       </c>
       <c r="H37" t="n">
         <v>1256671</v>
@@ -1471,7 +1471,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G38" t="n">
-        <v>2.30728816986084</v>
+        <v>2.30728888511658</v>
       </c>
       <c r="H38" t="n">
         <v>1605686</v>
@@ -1500,7 +1500,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G39" t="n">
-        <v>2.32726502418518</v>
+        <v>2.32726454734802</v>
       </c>
       <c r="H39" t="n">
         <v>1980797</v>
@@ -1529,7 +1529,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G40" t="n">
-        <v>2.33350777626038</v>
+        <v>2.33350729942322</v>
       </c>
       <c r="H40" t="n">
         <v>1373552</v>
@@ -1703,7 +1703,7 @@
         <v>3.75</v>
       </c>
       <c r="G46" t="n">
-        <v>2.34099888801575</v>
+        <v>2.34099864959717</v>
       </c>
       <c r="H46" t="n">
         <v>3939834</v>
@@ -1732,7 +1732,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G47" t="n">
-        <v>2.36097550392151</v>
+        <v>2.36097526550293</v>
       </c>
       <c r="H47" t="n">
         <v>3063904</v>
@@ -1761,7 +1761,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>2.32851314544678</v>
+        <v>2.32851362228394</v>
       </c>
       <c r="H48" t="n">
         <v>3129507</v>
@@ -1790,7 +1790,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G49" t="n">
-        <v>2.33600473403931</v>
+        <v>2.33600449562073</v>
       </c>
       <c r="H49" t="n">
         <v>2305779</v>
@@ -1877,7 +1877,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>2.32851314544678</v>
+        <v>2.32851362228394</v>
       </c>
       <c r="H52" t="n">
         <v>3089208</v>
@@ -1964,7 +1964,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G55" t="n">
-        <v>2.38220024108887</v>
+        <v>2.38220047950745</v>
       </c>
       <c r="H55" t="n">
         <v>3773445</v>
@@ -2051,7 +2051,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G58" t="n">
-        <v>2.33101034164429</v>
+        <v>2.33101058006287</v>
       </c>
       <c r="H58" t="n">
         <v>1647322</v>
@@ -2080,7 +2080,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G59" t="n">
-        <v>2.30978536605835</v>
+        <v>2.30978560447693</v>
       </c>
       <c r="H59" t="n">
         <v>1834154</v>
@@ -2109,7 +2109,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G60" t="n">
-        <v>2.25609827041626</v>
+        <v>2.25609874725342</v>
       </c>
       <c r="H60" t="n">
         <v>2504991</v>
@@ -2167,7 +2167,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>2.19741749763489</v>
+        <v>2.19741773605347</v>
       </c>
       <c r="H62" t="n">
         <v>2603411</v>
@@ -2341,7 +2341,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G68" t="n">
-        <v>2.34474444389343</v>
+        <v>2.34474420547485</v>
       </c>
       <c r="H68" t="n">
         <v>2555015</v>
@@ -2370,7 +2370,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G69" t="n">
-        <v>2.36222386360168</v>
+        <v>2.36222362518311</v>
       </c>
       <c r="H69" t="n">
         <v>2429548</v>
@@ -2399,7 +2399,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G70" t="n">
-        <v>2.36097550392151</v>
+        <v>2.36097526550293</v>
       </c>
       <c r="H70" t="n">
         <v>2975719</v>
@@ -2428,7 +2428,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36846661567688</v>
+        <v>2.36846613883972</v>
       </c>
       <c r="H71" t="n">
         <v>2188039</v>
@@ -2457,7 +2457,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>2.3784544467926</v>
+        <v>2.37845492362976</v>
       </c>
       <c r="H72" t="n">
         <v>2905887</v>
@@ -2486,7 +2486,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G73" t="n">
-        <v>2.35847854614258</v>
+        <v>2.358478307724</v>
       </c>
       <c r="H73" t="n">
         <v>2244613</v>
@@ -2544,7 +2544,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G75" t="n">
-        <v>2.3784544467926</v>
+        <v>2.37845492362976</v>
       </c>
       <c r="H75" t="n">
         <v>1737173</v>
@@ -2631,7 +2631,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.36596941947937</v>
+        <v>2.36596965789795</v>
       </c>
       <c r="H78" t="n">
         <v>3734574</v>
@@ -2660,7 +2660,7 @@
         <v>3.75</v>
       </c>
       <c r="G79" t="n">
-        <v>2.34099888801575</v>
+        <v>2.34099864959717</v>
       </c>
       <c r="H79" t="n">
         <v>1542324</v>
@@ -2689,7 +2689,7 @@
         <v>3.75</v>
       </c>
       <c r="G80" t="n">
-        <v>2.34099888801575</v>
+        <v>2.34099864959717</v>
       </c>
       <c r="H80" t="n">
         <v>1407964</v>
@@ -2747,7 +2747,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G82" t="n">
-        <v>2.3434956073761</v>
+        <v>2.34349632263184</v>
       </c>
       <c r="H82" t="n">
         <v>2040278</v>
@@ -2776,7 +2776,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G83" t="n">
-        <v>2.3784544467926</v>
+        <v>2.37845492362976</v>
       </c>
       <c r="H83" t="n">
         <v>1929343</v>
@@ -2921,7 +2921,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G88" t="n">
-        <v>2.40717101097107</v>
+        <v>2.40717124938965</v>
       </c>
       <c r="H88" t="n">
         <v>1733460</v>
@@ -3124,7 +3124,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G95" t="n">
-        <v>2.46710062026978</v>
+        <v>2.4671003818512</v>
       </c>
       <c r="H95" t="n">
         <v>9713560</v>
@@ -3153,7 +3153,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G96" t="n">
-        <v>2.48707747459412</v>
+        <v>2.48707699775696</v>
       </c>
       <c r="H96" t="n">
         <v>3180469</v>
@@ -3182,7 +3182,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G97" t="n">
-        <v>2.49331998825073</v>
+        <v>2.49331974983215</v>
       </c>
       <c r="H97" t="n">
         <v>3138380</v>
@@ -3240,7 +3240,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G99" t="n">
-        <v>2.46710062026978</v>
+        <v>2.4671003818512</v>
       </c>
       <c r="H99" t="n">
         <v>2383108</v>
@@ -3269,7 +3269,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G100" t="n">
-        <v>2.55574655532837</v>
+        <v>2.55574631690979</v>
       </c>
       <c r="H100" t="n">
         <v>3927765</v>
@@ -3327,7 +3327,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G102" t="n">
-        <v>2.58321452140808</v>
+        <v>2.58321404457092</v>
       </c>
       <c r="H102" t="n">
         <v>2760372</v>
@@ -3356,7 +3356,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G103" t="n">
-        <v>2.53576993942261</v>
+        <v>2.53576946258545</v>
       </c>
       <c r="H103" t="n">
         <v>2303291</v>
@@ -3385,7 +3385,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>2.53452134132385</v>
+        <v>2.53452086448669</v>
       </c>
       <c r="H104" t="n">
         <v>1897980</v>
@@ -3472,7 +3472,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>2.52203607559204</v>
+        <v>2.52203583717346</v>
       </c>
       <c r="H107" t="n">
         <v>1747900</v>
@@ -3501,7 +3501,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G108" t="n">
-        <v>2.53077578544617</v>
+        <v>2.53077554702759</v>
       </c>
       <c r="H108" t="n">
         <v>1847937</v>
@@ -3617,7 +3617,7 @@
         <v>4.19399976730347</v>
       </c>
       <c r="G112" t="n">
-        <v>2.61817288398743</v>
+        <v>2.61817264556885</v>
       </c>
       <c r="H112" t="n">
         <v>4192093</v>
@@ -3704,7 +3704,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>2.59694814682007</v>
+        <v>2.59694790840149</v>
       </c>
       <c r="H115" t="n">
         <v>2393218</v>
@@ -3762,7 +3762,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G117" t="n">
-        <v>2.58695960044861</v>
+        <v>2.58696007728577</v>
       </c>
       <c r="H117" t="n">
         <v>1464984</v>
@@ -3791,7 +3791,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G118" t="n">
-        <v>2.54825496673584</v>
+        <v>2.54825472831726</v>
       </c>
       <c r="H118" t="n">
         <v>3067347</v>
@@ -3820,7 +3820,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G119" t="n">
-        <v>2.66436886787415</v>
+        <v>2.66436910629272</v>
       </c>
       <c r="H119" t="n">
         <v>3299496</v>
@@ -3878,7 +3878,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G121" t="n">
-        <v>2.57822012901306</v>
+        <v>2.57822036743164</v>
       </c>
       <c r="H121" t="n">
         <v>2971262</v>
@@ -3936,7 +3936,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>2.59070563316345</v>
+        <v>2.59070539474487</v>
       </c>
       <c r="H123" t="n">
         <v>2382000</v>
@@ -4023,7 +4023,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G126" t="n">
-        <v>2.65937471389771</v>
+        <v>2.65937495231628</v>
       </c>
       <c r="H126" t="n">
         <v>3604147</v>
@@ -4081,7 +4081,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G128" t="n">
-        <v>2.71930432319641</v>
+        <v>2.71930384635925</v>
       </c>
       <c r="H128" t="n">
         <v>2807710</v>
@@ -4110,7 +4110,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G129" t="n">
-        <v>2.7642514705658</v>
+        <v>2.76425123214722</v>
       </c>
       <c r="H129" t="n">
         <v>2632642</v>
@@ -4139,7 +4139,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G130" t="n">
-        <v>2.77299070358276</v>
+        <v>2.77299118041992</v>
       </c>
       <c r="H130" t="n">
         <v>2184181</v>
@@ -4226,7 +4226,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G133" t="n">
-        <v>2.88036489486694</v>
+        <v>2.88036465644836</v>
       </c>
       <c r="H133" t="n">
         <v>4112711</v>
@@ -4255,7 +4255,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G134" t="n">
-        <v>2.8916015625</v>
+        <v>2.89160180091858</v>
       </c>
       <c r="H134" t="n">
         <v>4018664</v>
@@ -4313,7 +4313,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G136" t="n">
-        <v>2.87911653518677</v>
+        <v>2.87911629676819</v>
       </c>
       <c r="H136" t="n">
         <v>3254919</v>
@@ -4342,7 +4342,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G137" t="n">
-        <v>2.92780900001526</v>
+        <v>2.92780923843384</v>
       </c>
       <c r="H137" t="n">
         <v>3356588</v>
@@ -4400,7 +4400,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G139" t="n">
-        <v>3.02132725715637</v>
+        <v>3.02132701873779</v>
       </c>
       <c r="H139" t="n">
         <v>2869145</v>
@@ -4429,7 +4429,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G140" t="n">
-        <v>2.96410036087036</v>
+        <v>2.96410012245178</v>
       </c>
       <c r="H140" t="n">
         <v>2722633</v>
@@ -4458,7 +4458,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G141" t="n">
-        <v>3.00441908836365</v>
+        <v>3.00441932678223</v>
       </c>
       <c r="H141" t="n">
         <v>1874966</v>
@@ -4487,7 +4487,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G142" t="n">
-        <v>2.95889806747437</v>
+        <v>2.95889759063721</v>
       </c>
       <c r="H142" t="n">
         <v>2895383</v>
@@ -4545,7 +4545,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G144" t="n">
-        <v>3.00051736831665</v>
+        <v>3.00051712989807</v>
       </c>
       <c r="H144" t="n">
         <v>4692148</v>
@@ -4574,7 +4574,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G145" t="n">
-        <v>3.06424760818481</v>
+        <v>3.06424784660339</v>
       </c>
       <c r="H145" t="n">
         <v>6488921</v>
@@ -4603,7 +4603,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G146" t="n">
-        <v>3.11106967926025</v>
+        <v>3.11106944084167</v>
       </c>
       <c r="H146" t="n">
         <v>5229765</v>
@@ -4632,7 +4632,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G147" t="n">
-        <v>3.1474871635437</v>
+        <v>3.14748668670654</v>
       </c>
       <c r="H147" t="n">
         <v>3102001</v>
@@ -4661,7 +4661,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G148" t="n">
-        <v>3.09286117553711</v>
+        <v>3.09286093711853</v>
       </c>
       <c r="H148" t="n">
         <v>2668807</v>
@@ -4719,7 +4719,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>3.08505702018738</v>
+        <v>3.08505725860596</v>
       </c>
       <c r="H150" t="n">
         <v>1877264</v>
@@ -4777,7 +4777,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G152" t="n">
-        <v>3.05124068260193</v>
+        <v>3.05124139785767</v>
       </c>
       <c r="H152" t="n">
         <v>2693512</v>
@@ -4864,7 +4864,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>3.06294703483582</v>
+        <v>3.06294727325439</v>
       </c>
       <c r="H155" t="n">
         <v>4104980</v>
@@ -4893,7 +4893,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G156" t="n">
-        <v>2.97190427780151</v>
+        <v>2.97190380096436</v>
       </c>
       <c r="H156" t="n">
         <v>3155336</v>
@@ -4922,7 +4922,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G157" t="n">
-        <v>2.98751139640808</v>
+        <v>2.9875111579895</v>
       </c>
       <c r="H157" t="n">
         <v>3210418</v>
@@ -4951,7 +4951,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G158" t="n">
-        <v>3.02262783050537</v>
+        <v>3.02262759208679</v>
       </c>
       <c r="H158" t="n">
         <v>1663568</v>
@@ -4980,7 +4980,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G159" t="n">
-        <v>3.02782988548279</v>
+        <v>3.02783060073853</v>
       </c>
       <c r="H159" t="n">
         <v>1415379</v>
@@ -5009,7 +5009,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G160" t="n">
-        <v>2.98751139640808</v>
+        <v>2.9875111579895</v>
       </c>
       <c r="H160" t="n">
         <v>1883587</v>
@@ -5038,7 +5038,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>3.01092267036438</v>
+        <v>3.01092290878296</v>
       </c>
       <c r="H161" t="n">
         <v>1440176</v>
@@ -5067,7 +5067,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G162" t="n">
-        <v>3.02262783050537</v>
+        <v>3.02262759208679</v>
       </c>
       <c r="H162" t="n">
         <v>1812459</v>
@@ -5096,7 +5096,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.00441908836365</v>
+        <v>3.00441932678223</v>
       </c>
       <c r="H163" t="n">
         <v>1330854</v>
@@ -5125,7 +5125,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90947437286377</v>
+        <v>2.90947461128235</v>
       </c>
       <c r="H164" t="n">
         <v>2136959</v>
@@ -5183,7 +5183,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G166" t="n">
-        <v>2.84054160118103</v>
+        <v>2.84054207801819</v>
       </c>
       <c r="H166" t="n">
         <v>2317524</v>
@@ -5212,7 +5212,7 @@
         <v>4.42199993133545</v>
       </c>
       <c r="G167" t="n">
-        <v>2.87565875053406</v>
+        <v>2.87565851211548</v>
       </c>
       <c r="H167" t="n">
         <v>2400029</v>
@@ -5270,7 +5270,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G169" t="n">
-        <v>2.89126563072205</v>
+        <v>2.8912661075592</v>
       </c>
       <c r="H169" t="n">
         <v>1777949</v>
@@ -5299,7 +5299,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G170" t="n">
-        <v>2.85094666481018</v>
+        <v>2.8509464263916</v>
       </c>
       <c r="H170" t="n">
         <v>1064924</v>
@@ -5328,7 +5328,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G171" t="n">
-        <v>2.85875034332275</v>
+        <v>2.85875058174133</v>
       </c>
       <c r="H171" t="n">
         <v>1637236</v>
@@ -5357,7 +5357,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>2.86785459518433</v>
+        <v>2.86785483360291</v>
       </c>
       <c r="H172" t="n">
         <v>1480885</v>
@@ -5386,7 +5386,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G173" t="n">
-        <v>2.96410036087036</v>
+        <v>2.96410012245178</v>
       </c>
       <c r="H173" t="n">
         <v>3258572</v>
@@ -5415,7 +5415,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G174" t="n">
-        <v>2.94459080696106</v>
+        <v>2.94459128379822</v>
       </c>
       <c r="H174" t="n">
         <v>1407321</v>
@@ -5444,7 +5444,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>2.97190427780151</v>
+        <v>2.97190380096436</v>
       </c>
       <c r="H175" t="n">
         <v>2547097</v>
@@ -5531,7 +5531,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G178" t="n">
-        <v>2.97580528259277</v>
+        <v>2.97580599784851</v>
       </c>
       <c r="H178" t="n">
         <v>677556</v>
@@ -5560,7 +5560,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G179" t="n">
-        <v>2.97190427780151</v>
+        <v>2.97190380096436</v>
       </c>
       <c r="H179" t="n">
         <v>1152290</v>
@@ -5589,7 +5589,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G180" t="n">
-        <v>2.99531507492065</v>
+        <v>2.99531483650208</v>
       </c>
       <c r="H180" t="n">
         <v>1233361</v>
@@ -5618,7 +5618,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.04343748092651</v>
+        <v>3.04343771934509</v>
       </c>
       <c r="H181" t="n">
         <v>2063226</v>
@@ -5647,7 +5647,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>3.0369348526001</v>
+        <v>3.03693461418152</v>
       </c>
       <c r="H182" t="n">
         <v>1063094</v>
@@ -5676,7 +5676,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G183" t="n">
-        <v>3.04343748092651</v>
+        <v>3.04343771934509</v>
       </c>
       <c r="H183" t="n">
         <v>1602739</v>
@@ -5705,7 +5705,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>3.01092267036438</v>
+        <v>3.01092290878296</v>
       </c>
       <c r="H184" t="n">
         <v>1202620</v>
@@ -5734,7 +5734,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G185" t="n">
-        <v>2.99271392822266</v>
+        <v>2.99271416664124</v>
       </c>
       <c r="H185" t="n">
         <v>1171053</v>
@@ -5763,7 +5763,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G186" t="n">
-        <v>3.00051736831665</v>
+        <v>3.00051712989807</v>
       </c>
       <c r="H186" t="n">
         <v>943190</v>
@@ -5792,7 +5792,7 @@
         <v>4.55800008773804</v>
       </c>
       <c r="G187" t="n">
-        <v>2.96410036087036</v>
+        <v>2.96410012245178</v>
       </c>
       <c r="H187" t="n">
         <v>1895908</v>
@@ -5821,7 +5821,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.02392888069153</v>
+        <v>3.02392864227295</v>
       </c>
       <c r="H188" t="n">
         <v>2591123</v>
@@ -5850,7 +5850,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G189" t="n">
-        <v>3.08765864372253</v>
+        <v>3.08765840530396</v>
       </c>
       <c r="H189" t="n">
         <v>1958346</v>
@@ -5908,7 +5908,7 @@
         <v>4.78800010681152</v>
       </c>
       <c r="G191" t="n">
-        <v>3.11367106437683</v>
+        <v>3.11367130279541</v>
       </c>
       <c r="H191" t="n">
         <v>1110454</v>
@@ -5937,7 +5937,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G192" t="n">
-        <v>3.1474871635437</v>
+        <v>3.14748668670654</v>
       </c>
       <c r="H192" t="n">
         <v>1481236</v>
@@ -5966,7 +5966,7 @@
         <v>4.82399988174438</v>
       </c>
       <c r="G193" t="n">
-        <v>3.13708162307739</v>
+        <v>3.13708233833313</v>
       </c>
       <c r="H193" t="n">
         <v>1245683</v>
@@ -5995,7 +5995,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G194" t="n">
-        <v>3.16569519042969</v>
+        <v>3.16569590568542</v>
       </c>
       <c r="H194" t="n">
         <v>1182663</v>
@@ -6024,7 +6024,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G195" t="n">
-        <v>3.16179323196411</v>
+        <v>3.16179347038269</v>
       </c>
       <c r="H195" t="n">
         <v>1627563</v>
@@ -6053,7 +6053,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>3.14098358154297</v>
+        <v>3.14098381996155</v>
       </c>
       <c r="H196" t="n">
         <v>649672</v>
@@ -6082,7 +6082,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G197" t="n">
-        <v>3.07335186004639</v>
+        <v>3.07335162162781</v>
       </c>
       <c r="H197" t="n">
         <v>1172588</v>
@@ -6140,7 +6140,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G199" t="n">
-        <v>3.15789151191711</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H199" t="n">
         <v>1018979</v>
@@ -6169,7 +6169,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G200" t="n">
-        <v>3.14228367805481</v>
+        <v>3.14228439331055</v>
       </c>
       <c r="H200" t="n">
         <v>1062261</v>
@@ -6198,7 +6198,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G201" t="n">
-        <v>3.15789151191711</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H201" t="n">
         <v>1683946</v>
@@ -6227,7 +6227,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G202" t="n">
-        <v>3.14228367805481</v>
+        <v>3.14228439331055</v>
       </c>
       <c r="H202" t="n">
         <v>1384943</v>
@@ -6256,7 +6256,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G203" t="n">
-        <v>3.12407565116882</v>
+        <v>3.1240758895874</v>
       </c>
       <c r="H203" t="n">
         <v>767697</v>
@@ -6285,7 +6285,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G204" t="n">
-        <v>3.11757302284241</v>
+        <v>3.11757278442383</v>
       </c>
       <c r="H204" t="n">
         <v>1282121</v>
@@ -6314,7 +6314,7 @@
         <v>4.81400012969971</v>
       </c>
       <c r="G205" t="n">
-        <v>3.13057923316956</v>
+        <v>3.1305787563324</v>
       </c>
       <c r="H205" t="n">
         <v>612186</v>
@@ -6343,7 +6343,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.10846853256226</v>
+        <v>3.10846900939941</v>
       </c>
       <c r="H206" t="n">
         <v>937602</v>
@@ -6430,7 +6430,7 @@
         <v>4.77199983596802</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10326552391052</v>
+        <v>3.10326528549194</v>
       </c>
       <c r="H209" t="n">
         <v>1033833</v>
@@ -6459,7 +6459,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G210" t="n">
-        <v>3.08505702018738</v>
+        <v>3.08505725860596</v>
       </c>
       <c r="H210" t="n">
         <v>1269558</v>
@@ -6488,7 +6488,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G211" t="n">
-        <v>3.12277507781982</v>
+        <v>3.12277555465698</v>
       </c>
       <c r="H211" t="n">
         <v>1352033</v>
@@ -6517,7 +6517,7 @@
         <v>4.76200008392334</v>
       </c>
       <c r="G212" t="n">
-        <v>3.09676313400269</v>
+        <v>3.09676289558411</v>
       </c>
       <c r="H212" t="n">
         <v>1254427</v>
@@ -6546,7 +6546,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G213" t="n">
-        <v>3.06164622306824</v>
+        <v>3.0616466999054</v>
       </c>
       <c r="H213" t="n">
         <v>1372679</v>
@@ -6575,7 +6575,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G214" t="n">
-        <v>3.09936380386353</v>
+        <v>3.0993640422821</v>
       </c>
       <c r="H214" t="n">
         <v>2019085</v>
@@ -6604,7 +6604,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G215" t="n">
-        <v>3.10976934432983</v>
+        <v>3.10976910591125</v>
       </c>
       <c r="H215" t="n">
         <v>2759009</v>
@@ -6633,7 +6633,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G216" t="n">
-        <v>3.09025955200195</v>
+        <v>3.09025979042053</v>
       </c>
       <c r="H216" t="n">
         <v>1133242</v>
@@ -6662,7 +6662,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G217" t="n">
-        <v>3.09936380386353</v>
+        <v>3.0993640422821</v>
       </c>
       <c r="H217" t="n">
         <v>2335811</v>
@@ -6691,7 +6691,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G218" t="n">
-        <v>3.08765864372253</v>
+        <v>3.08765840530396</v>
       </c>
       <c r="H218" t="n">
         <v>1410451</v>
@@ -6749,7 +6749,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.02392888069153</v>
+        <v>3.02392864227295</v>
       </c>
       <c r="H220" t="n">
         <v>1539498</v>
@@ -6778,7 +6778,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G221" t="n">
-        <v>3.03043174743652</v>
+        <v>3.03043127059937</v>
       </c>
       <c r="H221" t="n">
         <v>1713520</v>
@@ -6807,7 +6807,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G222" t="n">
-        <v>3.03043174743652</v>
+        <v>3.03043127059937</v>
       </c>
       <c r="H222" t="n">
         <v>1111692</v>
@@ -6836,7 +6836,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G223" t="n">
-        <v>3.04864072799683</v>
+        <v>3.04864025115967</v>
       </c>
       <c r="H223" t="n">
         <v>1146321</v>
@@ -6865,7 +6865,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.02392888069153</v>
+        <v>3.02392864227295</v>
       </c>
       <c r="H224" t="n">
         <v>1103008</v>
@@ -6894,7 +6894,7 @@
         <v>4.68400001525879</v>
       </c>
       <c r="G225" t="n">
-        <v>3.04603910446167</v>
+        <v>3.04603886604309</v>
       </c>
       <c r="H225" t="n">
         <v>883299</v>
@@ -6923,7 +6923,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G226" t="n">
-        <v>3.07075047492981</v>
+        <v>3.07075119018555</v>
       </c>
       <c r="H226" t="n">
         <v>1748215</v>
@@ -6952,7 +6952,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>3.10196542739868</v>
+        <v>3.1019651889801</v>
       </c>
       <c r="H227" t="n">
         <v>1868854</v>
@@ -6981,7 +6981,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G228" t="n">
-        <v>3.12797737121582</v>
+        <v>3.12797784805298</v>
       </c>
       <c r="H228" t="n">
         <v>1859111</v>
@@ -7068,7 +7068,7 @@
         <v>4.75</v>
       </c>
       <c r="G231" t="n">
-        <v>3.08895874023438</v>
+        <v>3.08895897865295</v>
       </c>
       <c r="H231" t="n">
         <v>1731154</v>
@@ -7097,7 +7097,7 @@
         <v>4.75799989700317</v>
       </c>
       <c r="G232" t="n">
-        <v>3.09416151046753</v>
+        <v>3.09416174888611</v>
       </c>
       <c r="H232" t="n">
         <v>2197051</v>
@@ -7126,7 +7126,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G233" t="n">
-        <v>3.06944990158081</v>
+        <v>3.06945013999939</v>
       </c>
       <c r="H233" t="n">
         <v>2513489</v>
@@ -7184,7 +7184,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G235" t="n">
-        <v>3.03303265571594</v>
+        <v>3.0330331325531</v>
       </c>
       <c r="H235" t="n">
         <v>2592607</v>
@@ -7213,7 +7213,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G236" t="n">
-        <v>2.96930265426636</v>
+        <v>2.96930241584778</v>
       </c>
       <c r="H236" t="n">
         <v>2237180</v>
@@ -7242,7 +7242,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G237" t="n">
-        <v>3.03043174743652</v>
+        <v>3.03043127059937</v>
       </c>
       <c r="H237" t="n">
         <v>2780174</v>
@@ -7271,7 +7271,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G238" t="n">
-        <v>3.03173208236694</v>
+        <v>3.03173232078552</v>
       </c>
       <c r="H238" t="n">
         <v>1498059</v>
@@ -7329,7 +7329,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G240" t="n">
-        <v>3.09156084060669</v>
+        <v>3.09156060218811</v>
       </c>
       <c r="H240" t="n">
         <v>3955428</v>
@@ -7358,7 +7358,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G241" t="n">
-        <v>3.10586738586426</v>
+        <v>3.10586714744568</v>
       </c>
       <c r="H241" t="n">
         <v>1298047</v>
@@ -7387,7 +7387,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G242" t="n">
-        <v>3.07335186004639</v>
+        <v>3.07335162162781</v>
       </c>
       <c r="H242" t="n">
         <v>1121811</v>
@@ -7474,7 +7474,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G245" t="n">
-        <v>3.11497187614441</v>
+        <v>3.11497116088867</v>
       </c>
       <c r="H245" t="n">
         <v>1121552</v>
@@ -7503,7 +7503,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>3.14098358154297</v>
+        <v>3.14098381996155</v>
       </c>
       <c r="H246" t="n">
         <v>1767243</v>
@@ -7561,7 +7561,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G248" t="n">
-        <v>3.34257936477661</v>
+        <v>3.34257888793945</v>
       </c>
       <c r="H248" t="n">
         <v>8302472</v>
@@ -7590,7 +7590,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24893546104431</v>
+        <v>3.24893450737</v>
       </c>
       <c r="H249" t="n">
         <v>3278337</v>
@@ -7619,7 +7619,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>3.31656670570374</v>
+        <v>3.31656694412231</v>
       </c>
       <c r="H250" t="n">
         <v>2795501</v>
@@ -7677,7 +7677,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>3.27104496955872</v>
+        <v>3.27104520797729</v>
       </c>
       <c r="H252" t="n">
         <v>6428942</v>
@@ -7706,7 +7706,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G253" t="n">
-        <v>3.26129031181335</v>
+        <v>3.26129055023193</v>
       </c>
       <c r="H253" t="n">
         <v>1973997</v>
@@ -7735,7 +7735,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>3.30030918121338</v>
+        <v>3.3003089427948</v>
       </c>
       <c r="H254" t="n">
         <v>3004311</v>
@@ -7793,7 +7793,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G256" t="n">
-        <v>3.28079986572266</v>
+        <v>3.28080010414124</v>
       </c>
       <c r="H256" t="n">
         <v>1188363</v>
@@ -7822,7 +7822,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G257" t="n">
-        <v>3.32306981086731</v>
+        <v>3.32307028770447</v>
       </c>
       <c r="H257" t="n">
         <v>2418189</v>
@@ -7851,7 +7851,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>3.3198184967041</v>
+        <v>3.31981873512268</v>
       </c>
       <c r="H258" t="n">
         <v>2955797</v>
@@ -7880,7 +7880,7 @@
         <v>5.125</v>
       </c>
       <c r="G259" t="n">
-        <v>3.33282446861267</v>
+        <v>3.33282494544983</v>
       </c>
       <c r="H259" t="n">
         <v>2280185</v>
@@ -7909,7 +7909,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>3.31656670570374</v>
+        <v>3.31656694412231</v>
       </c>
       <c r="H260" t="n">
         <v>2506308</v>
@@ -7938,7 +7938,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>3.35233402252197</v>
+        <v>3.35233330726624</v>
       </c>
       <c r="H261" t="n">
         <v>2738338</v>
@@ -7967,7 +7967,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G262" t="n">
-        <v>3.35233402252197</v>
+        <v>3.35233330726624</v>
       </c>
       <c r="H262" t="n">
         <v>2922943</v>
@@ -8025,7 +8025,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G264" t="n">
-        <v>3.36208844184875</v>
+        <v>3.3620879650116</v>
       </c>
       <c r="H264" t="n">
         <v>3024002</v>
@@ -8054,7 +8054,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G265" t="n">
-        <v>3.39460349082947</v>
+        <v>3.39460325241089</v>
       </c>
       <c r="H265" t="n">
         <v>2474383</v>
@@ -8083,7 +8083,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G266" t="n">
-        <v>3.40760970115662</v>
+        <v>3.40760922431946</v>
       </c>
       <c r="H266" t="n">
         <v>3425548</v>
@@ -8112,7 +8112,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>3.47914338111877</v>
+        <v>3.47914385795593</v>
       </c>
       <c r="H267" t="n">
         <v>2730053</v>
@@ -8141,7 +8141,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>3.44662857055664</v>
+        <v>3.44662833213806</v>
       </c>
       <c r="H268" t="n">
         <v>2838765</v>
@@ -8199,7 +8199,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>3.3815975189209</v>
+        <v>3.38159728050232</v>
       </c>
       <c r="H270" t="n">
         <v>1740172</v>
@@ -8257,7 +8257,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.31656670570374</v>
+        <v>3.31656694412231</v>
       </c>
       <c r="H272" t="n">
         <v>1936166</v>
@@ -8286,7 +8286,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.40110683441162</v>
+        <v>3.40110659599304</v>
       </c>
       <c r="H273" t="n">
         <v>2058521</v>
@@ -8315,7 +8315,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>3.39460349082947</v>
+        <v>3.39460325241089</v>
       </c>
       <c r="H274" t="n">
         <v>1754265</v>
@@ -8344,7 +8344,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G275" t="n">
-        <v>3.45963454246521</v>
+        <v>3.45963478088379</v>
       </c>
       <c r="H275" t="n">
         <v>3167757</v>
@@ -8373,7 +8373,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>3.3750946521759</v>
+        <v>3.37509417533875</v>
       </c>
       <c r="H276" t="n">
         <v>3443370</v>
@@ -8402,7 +8402,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G277" t="n">
-        <v>3.39460349082947</v>
+        <v>3.39460325241089</v>
       </c>
       <c r="H277" t="n">
         <v>1741298</v>
@@ -8431,7 +8431,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G278" t="n">
-        <v>3.43687343597412</v>
+        <v>3.4368736743927</v>
       </c>
       <c r="H278" t="n">
         <v>4607010</v>
@@ -8460,7 +8460,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G279" t="n">
-        <v>3.44987964630127</v>
+        <v>3.44987988471985</v>
       </c>
       <c r="H279" t="n">
         <v>3731719</v>
@@ -8489,7 +8489,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>3.44012475013733</v>
+        <v>3.44012498855591</v>
       </c>
       <c r="H280" t="n">
         <v>5567621</v>
@@ -8518,7 +8518,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>3.46613740921021</v>
+        <v>3.46613693237305</v>
       </c>
       <c r="H281" t="n">
         <v>3172733</v>
@@ -8547,7 +8547,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.44337630271912</v>
+        <v>3.44337701797485</v>
       </c>
       <c r="H282" t="n">
         <v>1589890</v>
@@ -8576,7 +8576,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G283" t="n">
-        <v>3.43687343597412</v>
+        <v>3.4368736743927</v>
       </c>
       <c r="H283" t="n">
         <v>1954309</v>
@@ -8605,7 +8605,7 @@
         <v>5.25</v>
       </c>
       <c r="G284" t="n">
-        <v>3.41411232948303</v>
+        <v>3.41411304473877</v>
       </c>
       <c r="H284" t="n">
         <v>2645545</v>
@@ -8634,7 +8634,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>3.38484907150269</v>
+        <v>3.38484883308411</v>
       </c>
       <c r="H285" t="n">
         <v>1879710</v>
@@ -8663,7 +8663,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38484907150269</v>
+        <v>3.38484883308411</v>
       </c>
       <c r="H286" t="n">
         <v>3135720</v>
@@ -8692,7 +8692,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>3.40110683441162</v>
+        <v>3.40110659599304</v>
       </c>
       <c r="H287" t="n">
         <v>1466206</v>
@@ -8750,7 +8750,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G289" t="n">
-        <v>3.3750946521759</v>
+        <v>3.37509417533875</v>
       </c>
       <c r="H289" t="n">
         <v>2203324</v>
@@ -8779,7 +8779,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G290" t="n">
-        <v>3.32306981086731</v>
+        <v>3.32307028770447</v>
       </c>
       <c r="H290" t="n">
         <v>1986354</v>
@@ -8808,7 +8808,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>3.30681228637695</v>
+        <v>3.30681252479553</v>
       </c>
       <c r="H291" t="n">
         <v>1233863</v>
@@ -8837,7 +8837,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32306981086731</v>
+        <v>3.32307028770447</v>
       </c>
       <c r="H292" t="n">
         <v>1239019</v>
@@ -8924,7 +8924,7 @@
         <v>5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.25153660774231</v>
+        <v>3.25153589248657</v>
       </c>
       <c r="H295" t="n">
         <v>2285101</v>
@@ -9011,7 +9011,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G298" t="n">
-        <v>3.27104496955872</v>
+        <v>3.27104520797729</v>
       </c>
       <c r="H298" t="n">
         <v>1818628</v>
@@ -9040,7 +9040,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G299" t="n">
-        <v>3.26454210281372</v>
+        <v>3.2645423412323</v>
       </c>
       <c r="H299" t="n">
         <v>2225454</v>
@@ -9069,7 +9069,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G300" t="n">
-        <v>3.245032787323</v>
+        <v>3.24503231048584</v>
       </c>
       <c r="H300" t="n">
         <v>2694727</v>
@@ -9098,7 +9098,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>3.18650555610657</v>
+        <v>3.18650507926941</v>
       </c>
       <c r="H301" t="n">
         <v>3560333</v>
@@ -9156,7 +9156,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G303" t="n">
-        <v>3.16959714889526</v>
+        <v>3.16959738731384</v>
       </c>
       <c r="H303" t="n">
         <v>1765252</v>
@@ -9185,7 +9185,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G304" t="n">
-        <v>3.16959714889526</v>
+        <v>3.16959738731384</v>
       </c>
       <c r="H304" t="n">
         <v>1332188</v>
@@ -9214,7 +9214,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G305" t="n">
-        <v>3.20731544494629</v>
+        <v>3.20731592178345</v>
       </c>
       <c r="H305" t="n">
         <v>2083690</v>
@@ -9243,7 +9243,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G306" t="n">
-        <v>3.23202681541443</v>
+        <v>3.23202633857727</v>
       </c>
       <c r="H306" t="n">
         <v>1936665</v>
@@ -9301,7 +9301,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G308" t="n">
-        <v>3.22942614555359</v>
+        <v>3.22942495346069</v>
       </c>
       <c r="H308" t="n">
         <v>1536056</v>
@@ -9330,7 +9330,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G309" t="n">
-        <v>3.245032787323</v>
+        <v>3.24503231048584</v>
       </c>
       <c r="H309" t="n">
         <v>1332232</v>
@@ -9359,7 +9359,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G310" t="n">
-        <v>3.27104496955872</v>
+        <v>3.27104520797729</v>
       </c>
       <c r="H310" t="n">
         <v>1565332</v>
@@ -9388,7 +9388,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22942614555359</v>
+        <v>3.22942495346069</v>
       </c>
       <c r="H311" t="n">
         <v>1793873</v>
@@ -9417,7 +9417,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G312" t="n">
-        <v>3.20081210136414</v>
+        <v>3.20081186294556</v>
       </c>
       <c r="H312" t="n">
         <v>1847100</v>
@@ -9446,7 +9446,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G313" t="n">
-        <v>3.22292232513428</v>
+        <v>3.2229220867157</v>
       </c>
       <c r="H313" t="n">
         <v>1435060</v>
@@ -9475,7 +9475,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>3.18650555610657</v>
+        <v>3.18650507926941</v>
       </c>
       <c r="H314" t="n">
         <v>2572604</v>
@@ -9562,7 +9562,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G317" t="n">
-        <v>3.21771955490112</v>
+        <v>3.21772027015686</v>
       </c>
       <c r="H317" t="n">
         <v>2118644</v>
@@ -9591,7 +9591,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G318" t="n">
-        <v>3.1474871635437</v>
+        <v>3.14748668670654</v>
       </c>
       <c r="H318" t="n">
         <v>3105576</v>
@@ -9649,7 +9649,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>2.98816156387329</v>
+        <v>2.98816132545471</v>
       </c>
       <c r="H320" t="n">
         <v>3568087</v>
@@ -9678,7 +9678,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02913093566895</v>
+        <v>3.02913117408752</v>
       </c>
       <c r="H321" t="n">
         <v>2708506</v>
@@ -9765,7 +9765,7 @@
         <v>4.46400022506714</v>
       </c>
       <c r="G324" t="n">
-        <v>2.9029712677002</v>
+        <v>2.90297198295593</v>
       </c>
       <c r="H324" t="n">
         <v>1575080</v>
@@ -9794,7 +9794,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>2.87435793876648</v>
+        <v>2.87435817718506</v>
       </c>
       <c r="H325" t="n">
         <v>2067484</v>
@@ -9823,7 +9823,7 @@
         <v>4.44899988174438</v>
       </c>
       <c r="G326" t="n">
-        <v>2.89321660995483</v>
+        <v>2.89321637153625</v>
       </c>
       <c r="H326" t="n">
         <v>2452173</v>
@@ -9968,7 +9968,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G331" t="n">
-        <v>2.85159730911255</v>
+        <v>2.85159707069397</v>
       </c>
       <c r="H331" t="n">
         <v>1725510</v>
@@ -9997,7 +9997,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G332" t="n">
-        <v>2.90167045593262</v>
+        <v>2.90167093276978</v>
       </c>
       <c r="H332" t="n">
         <v>1748521</v>
@@ -10026,7 +10026,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G333" t="n">
-        <v>2.98360919952393</v>
+        <v>2.98360896110535</v>
       </c>
       <c r="H333" t="n">
         <v>2476508</v>
@@ -10055,7 +10055,7 @@
         <v>4.51700019836426</v>
       </c>
       <c r="G334" t="n">
-        <v>2.93743777275085</v>
+        <v>2.93743753433228</v>
       </c>
       <c r="H334" t="n">
         <v>1748762</v>
@@ -10142,7 +10142,7 @@
         <v>4.36700010299683</v>
       </c>
       <c r="G337" t="n">
-        <v>2.83989143371582</v>
+        <v>2.8398916721344</v>
       </c>
       <c r="H337" t="n">
         <v>2476410</v>
@@ -10258,7 +10258,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G341" t="n">
-        <v>2.96214938163757</v>
+        <v>2.96214914321899</v>
       </c>
       <c r="H341" t="n">
         <v>2619175</v>
@@ -10287,7 +10287,7 @@
         <v>4.6269998550415</v>
       </c>
       <c r="G342" t="n">
-        <v>3.00897097587585</v>
+        <v>3.00897073745728</v>
       </c>
       <c r="H342" t="n">
         <v>2893991</v>
@@ -10316,7 +10316,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>2.95889806747437</v>
+        <v>2.95889759063721</v>
       </c>
       <c r="H343" t="n">
         <v>1778217</v>
@@ -10345,7 +10345,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.02913093566895</v>
+        <v>3.02913117408752</v>
       </c>
       <c r="H344" t="n">
         <v>3824795</v>
@@ -10374,7 +10374,7 @@
         <v>4.76300001144409</v>
       </c>
       <c r="G345" t="n">
-        <v>3.09741353988647</v>
+        <v>3.09741306304932</v>
       </c>
       <c r="H345" t="n">
         <v>5092398</v>
@@ -10403,7 +10403,7 @@
         <v>4.75099992752075</v>
       </c>
       <c r="G346" t="n">
-        <v>3.08960914611816</v>
+        <v>3.08960938453674</v>
       </c>
       <c r="H346" t="n">
         <v>5127661</v>
@@ -10432,7 +10432,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>3.07595300674438</v>
+        <v>3.07595348358154</v>
       </c>
       <c r="H347" t="n">
         <v>2942590</v>
@@ -10461,7 +10461,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G348" t="n">
-        <v>3.05709433555603</v>
+        <v>3.05709457397461</v>
       </c>
       <c r="H348" t="n">
         <v>7156105</v>
@@ -10490,7 +10490,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>3.11497187614441</v>
+        <v>3.11497116088867</v>
       </c>
       <c r="H349" t="n">
         <v>3060245</v>
@@ -10519,7 +10519,7 @@
         <v>4.81899976730347</v>
       </c>
       <c r="G350" t="n">
-        <v>3.13383054733276</v>
+        <v>3.13382983207703</v>
       </c>
       <c r="H350" t="n">
         <v>1614575</v>
@@ -10577,7 +10577,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G352" t="n">
-        <v>3.06944990158081</v>
+        <v>3.06945013999939</v>
       </c>
       <c r="H352" t="n">
         <v>2541060</v>
@@ -10606,7 +10606,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G353" t="n">
-        <v>3.09936380386353</v>
+        <v>3.0993640422821</v>
       </c>
       <c r="H353" t="n">
         <v>1982170</v>
@@ -10664,7 +10664,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>3.11497187614441</v>
+        <v>3.11497116088867</v>
       </c>
       <c r="H355" t="n">
         <v>1626051</v>
@@ -10693,7 +10693,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G356" t="n">
-        <v>3.16959714889526</v>
+        <v>3.16959738731384</v>
       </c>
       <c r="H356" t="n">
         <v>2821934</v>
@@ -10722,7 +10722,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G357" t="n">
-        <v>3.15789151191711</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H357" t="n">
         <v>1742932</v>
@@ -10751,7 +10751,7 @@
         <v>4.86899995803833</v>
       </c>
       <c r="G358" t="n">
-        <v>3.16634559631348</v>
+        <v>3.16634583473206</v>
       </c>
       <c r="H358" t="n">
         <v>2094883</v>
@@ -10809,7 +10809,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G360" t="n">
-        <v>3.22032165527344</v>
+        <v>3.2203209400177</v>
       </c>
       <c r="H360" t="n">
         <v>2518130</v>
@@ -10896,7 +10896,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G363" t="n">
-        <v>3.33087348937988</v>
+        <v>3.33087372779846</v>
       </c>
       <c r="H363" t="n">
         <v>2412747</v>
@@ -10925,7 +10925,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G364" t="n">
-        <v>3.32697200775146</v>
+        <v>3.32697153091431</v>
       </c>
       <c r="H364" t="n">
         <v>1980411</v>
@@ -10954,7 +10954,7 @@
         <v>5.12599992752075</v>
       </c>
       <c r="G365" t="n">
-        <v>3.33347463607788</v>
+        <v>3.3334743976593</v>
       </c>
       <c r="H365" t="n">
         <v>1692898</v>
@@ -11041,7 +11041,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G368" t="n">
-        <v>3.35038304328918</v>
+        <v>3.35038280487061</v>
       </c>
       <c r="H368" t="n">
         <v>4112376</v>
@@ -11070,7 +11070,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G369" t="n">
-        <v>3.37769556045532</v>
+        <v>3.37769532203674</v>
       </c>
       <c r="H369" t="n">
         <v>1844080</v>
@@ -11099,7 +11099,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.32957243919373</v>
+        <v>3.32957291603088</v>
       </c>
       <c r="H370" t="n">
         <v>2607705</v>
@@ -11128,7 +11128,7 @@
         <v>5.17399978637695</v>
       </c>
       <c r="G371" t="n">
-        <v>3.36468935012817</v>
+        <v>3.36468911170959</v>
       </c>
       <c r="H371" t="n">
         <v>3253120</v>
@@ -11157,7 +11157,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G372" t="n">
-        <v>3.31136393547058</v>
+        <v>3.31136441230774</v>
       </c>
       <c r="H372" t="n">
         <v>2889659</v>
@@ -11215,7 +11215,7 @@
         <v>5.18200016021729</v>
       </c>
       <c r="G374" t="n">
-        <v>3.36989235877991</v>
+        <v>3.36989212036133</v>
       </c>
       <c r="H374" t="n">
         <v>1389515</v>
@@ -11244,7 +11244,7 @@
         <v>5.26399993896484</v>
       </c>
       <c r="G375" t="n">
-        <v>3.42321729660034</v>
+        <v>3.42321705818176</v>
       </c>
       <c r="H375" t="n">
         <v>1573143</v>
@@ -11273,7 +11273,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G376" t="n">
-        <v>3.47264051437378</v>
+        <v>3.47264099121094</v>
       </c>
       <c r="H376" t="n">
         <v>1857454</v>
@@ -11302,7 +11302,7 @@
         <v>5.36600017547607</v>
       </c>
       <c r="G377" t="n">
-        <v>3.4895486831665</v>
+        <v>3.48954820632935</v>
       </c>
       <c r="H377" t="n">
         <v>2580956</v>
@@ -11331,7 +11331,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G378" t="n">
-        <v>3.45053052902222</v>
+        <v>3.45053005218506</v>
       </c>
       <c r="H378" t="n">
         <v>2351824</v>
@@ -11360,7 +11360,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>3.44012475013733</v>
+        <v>3.44012498855591</v>
       </c>
       <c r="H379" t="n">
         <v>1895196</v>
@@ -11389,7 +11389,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G380" t="n">
-        <v>3.44922947883606</v>
+        <v>3.44922924041748</v>
       </c>
       <c r="H380" t="n">
         <v>1754549</v>
@@ -11418,7 +11418,7 @@
         <v>5.33799982070923</v>
       </c>
       <c r="G381" t="n">
-        <v>3.4713397026062</v>
+        <v>3.47134041786194</v>
       </c>
       <c r="H381" t="n">
         <v>1497682</v>
@@ -11476,7 +11476,7 @@
         <v>5.08799982070923</v>
       </c>
       <c r="G383" t="n">
-        <v>3.308762550354</v>
+        <v>3.30876278877258</v>
       </c>
       <c r="H383" t="n">
         <v>5272263</v>
@@ -11505,7 +11505,7 @@
         <v>5.02799987792969</v>
       </c>
       <c r="G384" t="n">
-        <v>3.26974487304688</v>
+        <v>3.2697446346283</v>
       </c>
       <c r="H384" t="n">
         <v>1785202</v>
@@ -11621,7 +11621,7 @@
         <v>4.95100021362305</v>
       </c>
       <c r="G388" t="n">
-        <v>3.21967124938965</v>
+        <v>3.21967101097107</v>
       </c>
       <c r="H388" t="n">
         <v>3209554</v>
@@ -11650,7 +11650,7 @@
         <v>5</v>
       </c>
       <c r="G389" t="n">
-        <v>3.25153660774231</v>
+        <v>3.25153589248657</v>
       </c>
       <c r="H389" t="n">
         <v>2087897</v>
@@ -11679,7 +11679,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>3.24828481674194</v>
+        <v>3.24828457832336</v>
       </c>
       <c r="H390" t="n">
         <v>4048165</v>
@@ -11708,7 +11708,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>3.24985361099243</v>
+        <v>3.24985432624817</v>
       </c>
       <c r="H391" t="n">
         <v>2600372</v>
@@ -11737,7 +11737,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G392" t="n">
-        <v>3.30670285224915</v>
+        <v>3.30670237541199</v>
       </c>
       <c r="H392" t="n">
         <v>2056574</v>
@@ -11795,7 +11795,7 @@
         <v>4.75699996948242</v>
       </c>
       <c r="G394" t="n">
-        <v>3.21939945220947</v>
+        <v>3.21939969062805</v>
       </c>
       <c r="H394" t="n">
         <v>2650692</v>
@@ -11824,7 +11824,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G395" t="n">
-        <v>3.14157056808472</v>
+        <v>3.1415708065033</v>
       </c>
       <c r="H395" t="n">
         <v>3871076</v>
@@ -11853,7 +11853,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>3.09622693061829</v>
+        <v>3.09622716903687</v>
       </c>
       <c r="H396" t="n">
         <v>2935650</v>
@@ -11882,7 +11882,7 @@
         <v>4.34800004959106</v>
       </c>
       <c r="G397" t="n">
-        <v>2.94259977340698</v>
+        <v>2.94260001182556</v>
       </c>
       <c r="H397" t="n">
         <v>6648350</v>
@@ -11911,7 +11911,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G398" t="n">
-        <v>3.03193354606628</v>
+        <v>3.03193378448486</v>
       </c>
       <c r="H398" t="n">
         <v>9267016</v>
@@ -11940,7 +11940,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>3.01839804649353</v>
+        <v>3.01839828491211</v>
       </c>
       <c r="H399" t="n">
         <v>5346504</v>
@@ -11969,7 +11969,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G400" t="n">
-        <v>3.05359053611755</v>
+        <v>3.05359077453613</v>
       </c>
       <c r="H400" t="n">
         <v>3701214</v>
@@ -11998,7 +11998,7 @@
         <v>4.63800001144409</v>
       </c>
       <c r="G401" t="n">
-        <v>3.13886332511902</v>
+        <v>3.1388635635376</v>
       </c>
       <c r="H401" t="n">
         <v>4000775</v>
@@ -12085,7 +12085,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>3.0996105670929</v>
+        <v>3.09961080551147</v>
       </c>
       <c r="H404" t="n">
         <v>1736977</v>
@@ -12114,7 +12114,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G405" t="n">
-        <v>3.06509566307068</v>
+        <v>3.0650954246521</v>
       </c>
       <c r="H405" t="n">
         <v>2327673</v>
@@ -12143,7 +12143,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G406" t="n">
-        <v>3.19841933250427</v>
+        <v>3.19841885566711</v>
       </c>
       <c r="H406" t="n">
         <v>2827673</v>
@@ -12172,7 +12172,7 @@
         <v>4.86299991607666</v>
       </c>
       <c r="G407" t="n">
-        <v>3.29113698005676</v>
+        <v>3.29113674163818</v>
       </c>
       <c r="H407" t="n">
         <v>4461113</v>
@@ -12259,7 +12259,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G410" t="n">
-        <v>3.23225784301758</v>
+        <v>3.232257604599</v>
       </c>
       <c r="H410" t="n">
         <v>3867738</v>
@@ -12288,7 +12288,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G411" t="n">
-        <v>3.24511647224426</v>
+        <v>3.24511694908142</v>
       </c>
       <c r="H411" t="n">
         <v>1310689</v>
@@ -12317,7 +12317,7 @@
         <v>4.82299995422363</v>
       </c>
       <c r="G412" t="n">
-        <v>3.26406598091125</v>
+        <v>3.26406574249268</v>
       </c>
       <c r="H412" t="n">
         <v>2369613</v>
@@ -12346,7 +12346,7 @@
         <v>4.89900016784668</v>
       </c>
       <c r="G413" t="n">
-        <v>3.31550049781799</v>
+        <v>3.31550097465515</v>
       </c>
       <c r="H413" t="n">
         <v>2936084</v>
@@ -12433,7 +12433,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G416" t="n">
-        <v>3.15916681289673</v>
+        <v>3.15916657447815</v>
       </c>
       <c r="H416" t="n">
         <v>2121412</v>
@@ -12462,7 +12462,7 @@
         <v>4.73099994659424</v>
       </c>
       <c r="G417" t="n">
-        <v>3.20180320739746</v>
+        <v>3.20180296897888</v>
       </c>
       <c r="H417" t="n">
         <v>2797354</v>
@@ -12491,7 +12491,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G418" t="n">
-        <v>3.2112774848938</v>
+        <v>3.21127772331238</v>
       </c>
       <c r="H418" t="n">
         <v>2248878</v>
@@ -12549,7 +12549,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G420" t="n">
-        <v>3.19571208953857</v>
+        <v>3.19571232795715</v>
       </c>
       <c r="H420" t="n">
         <v>2199299</v>
@@ -12578,7 +12578,7 @@
         <v>4.65700006484985</v>
       </c>
       <c r="G421" t="n">
-        <v>3.15172219276428</v>
+        <v>3.1517219543457</v>
       </c>
       <c r="H421" t="n">
         <v>1401951</v>
@@ -12665,7 +12665,7 @@
         <v>4.81099987030029</v>
       </c>
       <c r="G424" t="n">
-        <v>3.2559449672699</v>
+        <v>3.25594425201416</v>
       </c>
       <c r="H424" t="n">
         <v>1826570</v>
@@ -12723,7 +12723,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G426" t="n">
-        <v>3.23361134529114</v>
+        <v>3.23361110687256</v>
       </c>
       <c r="H426" t="n">
         <v>1009632</v>
@@ -12752,7 +12752,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G427" t="n">
-        <v>3.19841933250427</v>
+        <v>3.19841885566711</v>
       </c>
       <c r="H427" t="n">
         <v>1835351</v>
@@ -12781,7 +12781,7 @@
         <v>4.7039999961853</v>
       </c>
       <c r="G428" t="n">
-        <v>3.18353056907654</v>
+        <v>3.18353033065796</v>
       </c>
       <c r="H428" t="n">
         <v>1407066</v>
@@ -12810,7 +12810,7 @@
         <v>4.74700021743774</v>
       </c>
       <c r="G429" t="n">
-        <v>3.2126317024231</v>
+        <v>3.21263194084167</v>
       </c>
       <c r="H429" t="n">
         <v>1510889</v>
@@ -12839,7 +12839,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G430" t="n">
-        <v>3.19977283477783</v>
+        <v>3.19977307319641</v>
       </c>
       <c r="H430" t="n">
         <v>1634802</v>
@@ -12868,7 +12868,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>3.25526785850525</v>
+        <v>3.25526809692383</v>
       </c>
       <c r="H431" t="n">
         <v>2483950</v>
@@ -12897,7 +12897,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G432" t="n">
-        <v>3.30534934997559</v>
+        <v>3.30534887313843</v>
       </c>
       <c r="H432" t="n">
         <v>1839177</v>
@@ -12926,7 +12926,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G433" t="n">
-        <v>3.30128860473633</v>
+        <v>3.30128812789917</v>
       </c>
       <c r="H433" t="n">
         <v>1687533</v>
@@ -12955,7 +12955,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G434" t="n">
-        <v>3.30128860473633</v>
+        <v>3.30128812789917</v>
       </c>
       <c r="H434" t="n">
         <v>1560000</v>
@@ -12984,7 +12984,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>3.29587459564209</v>
+        <v>3.29587435722351</v>
       </c>
       <c r="H435" t="n">
         <v>1955017</v>
@@ -13042,7 +13042,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G437" t="n">
-        <v>3.26677346229553</v>
+        <v>3.26677322387695</v>
       </c>
       <c r="H437" t="n">
         <v>1711303</v>
@@ -13071,7 +13071,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.26203632354736</v>
+        <v>3.26203584671021</v>
       </c>
       <c r="H438" t="n">
         <v>1301307</v>
@@ -13100,7 +13100,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G439" t="n">
-        <v>3.31279325485229</v>
+        <v>3.31279373168945</v>
       </c>
       <c r="H439" t="n">
         <v>1709004</v>
@@ -13187,7 +13187,7 @@
         <v>4.9210000038147</v>
       </c>
       <c r="G442" t="n">
-        <v>3.33038949966431</v>
+        <v>3.33038973808289</v>
       </c>
       <c r="H442" t="n">
         <v>2566951</v>
@@ -13216,7 +13216,7 @@
         <v>4.83900022506714</v>
       </c>
       <c r="G443" t="n">
-        <v>3.27489447593689</v>
+        <v>3.27489495277405</v>
       </c>
       <c r="H443" t="n">
         <v>3411353</v>
@@ -13245,7 +13245,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G444" t="n">
-        <v>3.27963185310364</v>
+        <v>3.27963209152222</v>
       </c>
       <c r="H444" t="n">
         <v>2129347</v>
@@ -13303,7 +13303,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G446" t="n">
-        <v>3.27963185310364</v>
+        <v>3.27963209152222</v>
       </c>
       <c r="H446" t="n">
         <v>944767</v>
@@ -13332,7 +13332,7 @@
         <v>4.97200012207031</v>
       </c>
       <c r="G447" t="n">
-        <v>3.36490488052368</v>
+        <v>3.36490559577942</v>
       </c>
       <c r="H447" t="n">
         <v>1912325</v>
@@ -13390,7 +13390,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G449" t="n">
-        <v>3.30670285224915</v>
+        <v>3.30670237541199</v>
       </c>
       <c r="H449" t="n">
         <v>1660537</v>
@@ -13448,7 +13448,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G451" t="n">
-        <v>3.27015662193298</v>
+        <v>3.27015686035156</v>
       </c>
       <c r="H451" t="n">
         <v>1321199</v>
@@ -13477,7 +13477,7 @@
         <v>4.85099983215332</v>
       </c>
       <c r="G452" t="n">
-        <v>3.28301596641541</v>
+        <v>3.28301548957825</v>
       </c>
       <c r="H452" t="n">
         <v>1483194</v>
@@ -13506,7 +13506,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G453" t="n">
-        <v>3.25729894638062</v>
+        <v>3.25729870796204</v>
       </c>
       <c r="H453" t="n">
         <v>2300362</v>
@@ -13564,7 +13564,7 @@
         <v>4.79300022125244</v>
       </c>
       <c r="G455" t="n">
-        <v>3.24376320838928</v>
+        <v>3.24376344680786</v>
       </c>
       <c r="H455" t="n">
         <v>1781968</v>
@@ -13622,7 +13622,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G457" t="n">
-        <v>3.19368171691895</v>
+        <v>3.19368195533752</v>
       </c>
       <c r="H457" t="n">
         <v>1943294</v>
@@ -13767,7 +13767,7 @@
         <v>4.69099998474121</v>
       </c>
       <c r="G462" t="n">
-        <v>3.17473220825195</v>
+        <v>3.17473268508911</v>
       </c>
       <c r="H462" t="n">
         <v>1001054</v>
@@ -13825,7 +13825,7 @@
         <v>4.65399980545044</v>
       </c>
       <c r="G464" t="n">
-        <v>3.14969182014465</v>
+        <v>3.14969158172607</v>
       </c>
       <c r="H464" t="n">
         <v>2108233</v>
@@ -13854,7 +13854,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>3.19097471237183</v>
+        <v>3.19097495079041</v>
       </c>
       <c r="H465" t="n">
         <v>1623544</v>
@@ -13912,7 +13912,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G467" t="n">
-        <v>3.1916515827179</v>
+        <v>3.19165134429932</v>
       </c>
       <c r="H467" t="n">
         <v>1729164</v>
@@ -13970,7 +13970,7 @@
         <v>4.73400020599365</v>
       </c>
       <c r="G469" t="n">
-        <v>3.20383381843567</v>
+        <v>3.20383358001709</v>
       </c>
       <c r="H469" t="n">
         <v>1416699</v>
@@ -13999,7 +13999,7 @@
         <v>4.91499996185303</v>
       </c>
       <c r="G470" t="n">
-        <v>3.32632923126221</v>
+        <v>3.32632875442505</v>
       </c>
       <c r="H470" t="n">
         <v>2700767</v>
@@ -14115,7 +14115,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G474" t="n">
-        <v>3.30128860473633</v>
+        <v>3.30128812789917</v>
       </c>
       <c r="H474" t="n">
         <v>1802455</v>
@@ -14173,7 +14173,7 @@
         <v>4.88700008392334</v>
       </c>
       <c r="G476" t="n">
-        <v>3.30737972259521</v>
+        <v>3.30737948417664</v>
       </c>
       <c r="H476" t="n">
         <v>1146119</v>
@@ -14202,7 +14202,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>3.24173283576965</v>
+        <v>3.24173259735107</v>
       </c>
       <c r="H477" t="n">
         <v>1901964</v>
@@ -14260,7 +14260,7 @@
         <v>4.89300012588501</v>
       </c>
       <c r="G479" t="n">
-        <v>3.31144046783447</v>
+        <v>3.31143999099731</v>
       </c>
       <c r="H479" t="n">
         <v>2157559</v>
@@ -14289,7 +14289,7 @@
         <v>4.77299976348877</v>
       </c>
       <c r="G480" t="n">
-        <v>3.23022699356079</v>
+        <v>3.23022723197937</v>
       </c>
       <c r="H480" t="n">
         <v>1732034</v>
@@ -14318,7 +14318,7 @@
         <v>4.80100011825562</v>
       </c>
       <c r="G481" t="n">
-        <v>3.24917674064636</v>
+        <v>3.24917697906494</v>
       </c>
       <c r="H481" t="n">
         <v>1464371</v>
@@ -14347,7 +14347,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G482" t="n">
-        <v>3.27421736717224</v>
+        <v>3.27421760559082</v>
       </c>
       <c r="H482" t="n">
         <v>1373526</v>
@@ -14376,7 +14376,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>3.24511647224426</v>
+        <v>3.24511694908142</v>
       </c>
       <c r="H483" t="n">
         <v>1486476</v>
@@ -14434,7 +14434,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G485" t="n">
-        <v>3.16864204406738</v>
+        <v>3.16864132881165</v>
       </c>
       <c r="H485" t="n">
         <v>1484153</v>
@@ -14463,7 +14463,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G486" t="n">
-        <v>3.18623757362366</v>
+        <v>3.18623781204224</v>
       </c>
       <c r="H486" t="n">
         <v>1512230</v>
@@ -14492,7 +14492,7 @@
         <v>4.74900007247925</v>
       </c>
       <c r="G487" t="n">
-        <v>3.21398520469666</v>
+        <v>3.21398544311523</v>
       </c>
       <c r="H487" t="n">
         <v>1301677</v>
@@ -14521,7 +14521,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G488" t="n">
-        <v>3.13818693161011</v>
+        <v>3.13818669319153</v>
       </c>
       <c r="H488" t="n">
         <v>1964476</v>
@@ -14550,7 +14550,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G489" t="n">
-        <v>3.11043930053711</v>
+        <v>3.11043906211853</v>
       </c>
       <c r="H489" t="n">
         <v>2196021</v>
@@ -14637,7 +14637,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G492" t="n">
-        <v>3.06847929954529</v>
+        <v>3.06847953796387</v>
       </c>
       <c r="H492" t="n">
         <v>2212633</v>
@@ -14666,7 +14666,7 @@
         <v>4.46700000762939</v>
       </c>
       <c r="G493" t="n">
-        <v>3.02313566207886</v>
+        <v>3.0231351852417</v>
       </c>
       <c r="H493" t="n">
         <v>2373270</v>
@@ -14695,7 +14695,7 @@
         <v>4.42899990081787</v>
       </c>
       <c r="G494" t="n">
-        <v>2.99741840362549</v>
+        <v>2.99741864204407</v>
       </c>
       <c r="H494" t="n">
         <v>1532051</v>
@@ -14724,7 +14724,7 @@
         <v>4.46099996566772</v>
       </c>
       <c r="G495" t="n">
-        <v>3.0190749168396</v>
+        <v>3.01907515525818</v>
       </c>
       <c r="H495" t="n">
         <v>1580807</v>
@@ -14753,7 +14753,7 @@
         <v>4.59100008010864</v>
       </c>
       <c r="G496" t="n">
-        <v>3.10705542564392</v>
+        <v>3.1070556640625</v>
       </c>
       <c r="H496" t="n">
         <v>2125874</v>
@@ -14782,7 +14782,7 @@
         <v>4.48299980163574</v>
       </c>
       <c r="G497" t="n">
-        <v>3.03396368026733</v>
+        <v>3.03396391868591</v>
       </c>
       <c r="H497" t="n">
         <v>1643380</v>
@@ -14811,7 +14811,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G498" t="n">
-        <v>3.06171178817749</v>
+        <v>3.06171154975891</v>
       </c>
       <c r="H498" t="n">
         <v>1895816</v>
@@ -14869,7 +14869,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G500" t="n">
-        <v>3.10096406936646</v>
+        <v>3.10096430778503</v>
       </c>
       <c r="H500" t="n">
         <v>5398178</v>
@@ -14898,7 +14898,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G501" t="n">
-        <v>3.0955502986908</v>
+        <v>3.09554982185364</v>
       </c>
       <c r="H501" t="n">
         <v>2496826</v>
@@ -14927,7 +14927,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>3.0996105670929</v>
+        <v>3.09961080551147</v>
       </c>
       <c r="H502" t="n">
         <v>2967574</v>
@@ -14956,7 +14956,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G503" t="n">
-        <v>3.13751006126404</v>
+        <v>3.13751029968262</v>
       </c>
       <c r="H503" t="n">
         <v>2998067</v>
@@ -14985,7 +14985,7 @@
         <v>4.57200002670288</v>
       </c>
       <c r="G504" t="n">
-        <v>3.09419703483582</v>
+        <v>3.09419655799866</v>
       </c>
       <c r="H504" t="n">
         <v>2292625</v>
@@ -15130,7 +15130,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G509" t="n">
-        <v>3.13277268409729</v>
+        <v>3.13277244567871</v>
       </c>
       <c r="H509" t="n">
         <v>1539652</v>
@@ -15188,7 +15188,7 @@
         <v>4.77199983596802</v>
       </c>
       <c r="G511" t="n">
-        <v>3.2295503616333</v>
+        <v>3.22955083847046</v>
       </c>
       <c r="H511" t="n">
         <v>3039388</v>
@@ -15217,7 +15217,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G512" t="n">
-        <v>3.27895474433899</v>
+        <v>3.27895498275757</v>
       </c>
       <c r="H512" t="n">
         <v>3534102</v>
@@ -15246,7 +15246,7 @@
         <v>4.85900020599365</v>
       </c>
       <c r="G513" t="n">
-        <v>3.28842973709106</v>
+        <v>3.2884304523468</v>
       </c>
       <c r="H513" t="n">
         <v>2192149</v>
@@ -15304,7 +15304,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G515" t="n">
-        <v>3.26203632354736</v>
+        <v>3.26203584671021</v>
       </c>
       <c r="H515" t="n">
         <v>2936871</v>
@@ -15333,7 +15333,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G516" t="n">
-        <v>3.29993486404419</v>
+        <v>3.29993534088135</v>
       </c>
       <c r="H516" t="n">
         <v>1635283</v>
@@ -15391,7 +15391,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G518" t="n">
-        <v>3.19368171691895</v>
+        <v>3.19368195533752</v>
       </c>
       <c r="H518" t="n">
         <v>2274690</v>
@@ -15420,7 +15420,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G519" t="n">
-        <v>3.21601510047913</v>
+        <v>3.21601557731628</v>
       </c>
       <c r="H519" t="n">
         <v>1641709</v>
@@ -15507,7 +15507,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G522" t="n">
-        <v>3.16390442848206</v>
+        <v>3.1639039516449</v>
       </c>
       <c r="H522" t="n">
         <v>1528824</v>
@@ -15652,7 +15652,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G527" t="n">
-        <v>3.20654082298279</v>
+        <v>3.20654058456421</v>
       </c>
       <c r="H527" t="n">
         <v>2520823</v>
@@ -15681,7 +15681,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G528" t="n">
-        <v>3.18623757362366</v>
+        <v>3.18623781204224</v>
       </c>
       <c r="H528" t="n">
         <v>1648716</v>
@@ -15768,7 +15768,7 @@
         <v>4.76300001144409</v>
       </c>
       <c r="G531" t="n">
-        <v>3.22346019744873</v>
+        <v>3.22345995903015</v>
       </c>
       <c r="H531" t="n">
         <v>1028637</v>
@@ -15797,7 +15797,7 @@
         <v>4.82299995422363</v>
       </c>
       <c r="G532" t="n">
-        <v>3.26406598091125</v>
+        <v>3.26406574249268</v>
       </c>
       <c r="H532" t="n">
         <v>1349990</v>
@@ -15826,7 +15826,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G533" t="n">
-        <v>3.24714660644531</v>
+        <v>3.24714708328247</v>
       </c>
       <c r="H533" t="n">
         <v>2020327</v>
@@ -15855,7 +15855,7 @@
         <v>4.88700008392334</v>
       </c>
       <c r="G534" t="n">
-        <v>3.30737972259521</v>
+        <v>3.30737948417664</v>
       </c>
       <c r="H534" t="n">
         <v>1901945</v>
@@ -15884,7 +15884,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G535" t="n">
-        <v>3.27083373069763</v>
+        <v>3.27083396911621</v>
       </c>
       <c r="H535" t="n">
         <v>1725682</v>
@@ -15913,7 +15913,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G536" t="n">
-        <v>3.30602598190308</v>
+        <v>3.30602622032166</v>
       </c>
       <c r="H536" t="n">
         <v>1643389</v>
@@ -15942,7 +15942,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G537" t="n">
-        <v>3.37302613258362</v>
+        <v>3.3730263710022</v>
       </c>
       <c r="H537" t="n">
         <v>2305052</v>
@@ -16000,7 +16000,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G539" t="n">
-        <v>3.4582998752594</v>
+        <v>3.45829939842224</v>
       </c>
       <c r="H539" t="n">
         <v>1917483</v>
@@ -16029,7 +16029,7 @@
         <v>5.13600015640259</v>
       </c>
       <c r="G540" t="n">
-        <v>3.47589540481567</v>
+        <v>3.47589564323425</v>
       </c>
       <c r="H540" t="n">
         <v>3297195</v>
@@ -16116,7 +16116,7 @@
         <v>5.0939998626709</v>
       </c>
       <c r="G543" t="n">
-        <v>3.44747090339661</v>
+        <v>3.44747114181519</v>
       </c>
       <c r="H543" t="n">
         <v>2157833</v>
@@ -16145,7 +16145,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G544" t="n">
-        <v>3.44611740112305</v>
+        <v>3.44611763954163</v>
       </c>
       <c r="H544" t="n">
         <v>2699606</v>
@@ -16203,7 +16203,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G546" t="n">
-        <v>3.38114786148071</v>
+        <v>3.3811469078064</v>
       </c>
       <c r="H546" t="n">
         <v>1085876</v>
@@ -16232,7 +16232,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G547" t="n">
-        <v>3.42581391334534</v>
+        <v>3.42581415176392</v>
       </c>
       <c r="H547" t="n">
         <v>1842177</v>
@@ -16261,7 +16261,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G548" t="n">
-        <v>3.46506690979004</v>
+        <v>3.46506667137146</v>
       </c>
       <c r="H548" t="n">
         <v>2083576</v>
@@ -16290,7 +16290,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G549" t="n">
-        <v>3.49349188804626</v>
+        <v>3.49349164962769</v>
       </c>
       <c r="H549" t="n">
         <v>2357386</v>
@@ -16319,7 +16319,7 @@
         <v>5.2039999961853</v>
       </c>
       <c r="G550" t="n">
-        <v>3.52191567420959</v>
+        <v>3.52191591262817</v>
       </c>
       <c r="H550" t="n">
         <v>2534910</v>
@@ -16348,7 +16348,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G551" t="n">
-        <v>3.46642065048218</v>
+        <v>3.46642136573792</v>
       </c>
       <c r="H551" t="n">
         <v>5238374</v>
@@ -16406,7 +16406,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G553" t="n">
-        <v>3.52868342399597</v>
+        <v>3.52868390083313</v>
       </c>
       <c r="H553" t="n">
         <v>2232096</v>
@@ -16464,7 +16464,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G555" t="n">
-        <v>3.4975528717041</v>
+        <v>3.49755191802979</v>
       </c>
       <c r="H555" t="n">
         <v>2295662</v>
@@ -16493,7 +16493,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>3.52597665786743</v>
+        <v>3.52597689628601</v>
       </c>
       <c r="H556" t="n">
         <v>1458761</v>
@@ -16522,7 +16522,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G557" t="n">
-        <v>3.53003716468811</v>
+        <v>3.53003740310669</v>
       </c>
       <c r="H557" t="n">
         <v>1783120</v>
@@ -16551,7 +16551,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G558" t="n">
-        <v>3.52056241035461</v>
+        <v>3.52056217193604</v>
       </c>
       <c r="H558" t="n">
         <v>1626237</v>
@@ -16580,7 +16580,7 @@
         <v>5.25400018692017</v>
       </c>
       <c r="G559" t="n">
-        <v>3.55575489997864</v>
+        <v>3.55575442314148</v>
       </c>
       <c r="H559" t="n">
         <v>2277905</v>
@@ -16609,7 +16609,7 @@
         <v>5.25</v>
       </c>
       <c r="G560" t="n">
-        <v>3.5530469417572</v>
+        <v>3.55304718017578</v>
       </c>
       <c r="H560" t="n">
         <v>1235834</v>
@@ -16638,7 +16638,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>3.52597665786743</v>
+        <v>3.52597689628601</v>
       </c>
       <c r="H561" t="n">
         <v>1874069</v>
@@ -16667,7 +16667,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>3.52597665786743</v>
+        <v>3.52597689628601</v>
       </c>
       <c r="H562" t="n">
         <v>2322938</v>
@@ -16696,7 +16696,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G563" t="n">
-        <v>3.55169439315796</v>
+        <v>3.5516939163208</v>
       </c>
       <c r="H563" t="n">
         <v>2286330</v>
@@ -16725,7 +16725,7 @@
         <v>5.25</v>
       </c>
       <c r="G564" t="n">
-        <v>3.5530469417572</v>
+        <v>3.55304718017578</v>
       </c>
       <c r="H564" t="n">
         <v>1436011</v>
@@ -16754,7 +16754,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G565" t="n">
-        <v>3.4975528717041</v>
+        <v>3.49755191802979</v>
       </c>
       <c r="H565" t="n">
         <v>2827660</v>
@@ -16841,7 +16841,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G568" t="n">
-        <v>3.57199692726135</v>
+        <v>3.57199645042419</v>
       </c>
       <c r="H568" t="n">
         <v>2087253</v>
@@ -16899,7 +16899,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G570" t="n">
-        <v>3.53545117378235</v>
+        <v>3.53545188903809</v>
       </c>
       <c r="H570" t="n">
         <v>1542313</v>
@@ -16928,7 +16928,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G571" t="n">
-        <v>3.57199692726135</v>
+        <v>3.57199645042419</v>
       </c>
       <c r="H571" t="n">
         <v>1790300</v>
@@ -16957,7 +16957,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G572" t="n">
-        <v>3.56116843223572</v>
+        <v>3.56116914749146</v>
       </c>
       <c r="H572" t="n">
         <v>1415150</v>
@@ -16986,7 +16986,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G573" t="n">
-        <v>3.48266267776489</v>
+        <v>3.48266315460205</v>
       </c>
       <c r="H573" t="n">
         <v>1783474</v>
@@ -17015,7 +17015,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G574" t="n">
-        <v>3.46100687980652</v>
+        <v>3.4610071182251</v>
       </c>
       <c r="H574" t="n">
         <v>1543318</v>
@@ -17131,7 +17131,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G578" t="n">
-        <v>3.52868342399597</v>
+        <v>3.52868390083313</v>
       </c>
       <c r="H578" t="n">
         <v>1509818</v>
@@ -17160,7 +17160,7 @@
         <v>5.22599983215332</v>
       </c>
       <c r="G579" t="n">
-        <v>3.53680491447449</v>
+        <v>3.53680467605591</v>
       </c>
       <c r="H579" t="n">
         <v>1824415</v>
@@ -17218,7 +17218,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G581" t="n">
-        <v>3.52462339401245</v>
+        <v>3.52462267875671</v>
       </c>
       <c r="H581" t="n">
         <v>885610</v>
@@ -17247,7 +17247,7 @@
         <v>5.2039999961853</v>
       </c>
       <c r="G582" t="n">
-        <v>3.52191567420959</v>
+        <v>3.52191591262817</v>
       </c>
       <c r="H582" t="n">
         <v>832020</v>
@@ -17276,7 +17276,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>3.52597665786743</v>
+        <v>3.52597689628601</v>
       </c>
       <c r="H583" t="n">
         <v>1461214</v>
@@ -17305,7 +17305,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G584" t="n">
-        <v>3.57199692726135</v>
+        <v>3.57199645042419</v>
       </c>
       <c r="H584" t="n">
         <v>1630171</v>
@@ -17334,7 +17334,7 @@
         <v>5.30800008773804</v>
       </c>
       <c r="G585" t="n">
-        <v>3.59229969978333</v>
+        <v>3.59230041503906</v>
       </c>
       <c r="H585" t="n">
         <v>1423370</v>
@@ -17363,7 +17363,7 @@
         <v>5.2960000038147</v>
       </c>
       <c r="G586" t="n">
-        <v>3.58417868614197</v>
+        <v>3.58417892456055</v>
       </c>
       <c r="H586" t="n">
         <v>1279020</v>
@@ -17450,7 +17450,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G589" t="n">
-        <v>3.5990674495697</v>
+        <v>3.59906768798828</v>
       </c>
       <c r="H589" t="n">
         <v>1973752</v>
@@ -17595,7 +17595,7 @@
         <v>5.46799993515015</v>
       </c>
       <c r="G594" t="n">
-        <v>3.70058298110962</v>
+        <v>3.7005832195282</v>
       </c>
       <c r="H594" t="n">
         <v>2310453</v>
@@ -17624,7 +17624,7 @@
         <v>5.42600011825562</v>
       </c>
       <c r="G595" t="n">
-        <v>3.67215943336487</v>
+        <v>3.67215919494629</v>
       </c>
       <c r="H595" t="n">
         <v>1706877</v>
@@ -17682,7 +17682,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G597" t="n">
-        <v>3.63561344146729</v>
+        <v>3.63561367988586</v>
       </c>
       <c r="H597" t="n">
         <v>1711423</v>
@@ -17798,7 +17798,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.69516944885254</v>
+        <v>3.69516921043396</v>
       </c>
       <c r="H601" t="n">
         <v>1443702</v>
@@ -17827,7 +17827,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G602" t="n">
-        <v>3.70464396476746</v>
+        <v>3.70464420318604</v>
       </c>
       <c r="H602" t="n">
         <v>2150629</v>
@@ -17856,7 +17856,7 @@
         <v>5.49399995803833</v>
       </c>
       <c r="G603" t="n">
-        <v>3.71817970275879</v>
+        <v>3.71817922592163</v>
       </c>
       <c r="H603" t="n">
         <v>1154586</v>
@@ -17914,7 +17914,7 @@
         <v>5.50799989700317</v>
       </c>
       <c r="G605" t="n">
-        <v>3.72765398025513</v>
+        <v>3.72765421867371</v>
       </c>
       <c r="H605" t="n">
         <v>1275899</v>
@@ -17972,7 +17972,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G607" t="n">
-        <v>3.68840146064758</v>
+        <v>3.68840169906616</v>
       </c>
       <c r="H607" t="n">
         <v>1876065</v>
@@ -18001,7 +18001,7 @@
         <v>5.47599983215332</v>
       </c>
       <c r="G608" t="n">
-        <v>3.70599770545959</v>
+        <v>3.70599746704102</v>
       </c>
       <c r="H608" t="n">
         <v>1415141</v>
@@ -18030,7 +18030,7 @@
         <v>5.50400018692017</v>
       </c>
       <c r="G609" t="n">
-        <v>3.72494721412659</v>
+        <v>3.72494697570801</v>
       </c>
       <c r="H609" t="n">
         <v>2248836</v>
@@ -18059,7 +18059,7 @@
         <v>5.43400001525879</v>
       </c>
       <c r="G610" t="n">
-        <v>3.67757248878479</v>
+        <v>3.67757296562195</v>
       </c>
       <c r="H610" t="n">
         <v>2056524</v>
@@ -18088,7 +18088,7 @@
         <v>5.49200010299683</v>
       </c>
       <c r="G611" t="n">
-        <v>3.71682572364807</v>
+        <v>3.71682596206665</v>
       </c>
       <c r="H611" t="n">
         <v>1932836</v>
@@ -18117,7 +18117,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G612" t="n">
-        <v>3.75607848167419</v>
+        <v>3.75607895851135</v>
       </c>
       <c r="H612" t="n">
         <v>1506760</v>
@@ -18146,7 +18146,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G613" t="n">
-        <v>3.72359347343445</v>
+        <v>3.72359371185303</v>
       </c>
       <c r="H613" t="n">
         <v>1644649</v>
@@ -18175,7 +18175,7 @@
         <v>5.52199983596802</v>
       </c>
       <c r="G614" t="n">
-        <v>3.73712849617004</v>
+        <v>3.73712873458862</v>
       </c>
       <c r="H614" t="n">
         <v>2119896</v>
@@ -18204,7 +18204,7 @@
         <v>5.5460000038147</v>
       </c>
       <c r="G615" t="n">
-        <v>3.75337195396423</v>
+        <v>3.75337171554565</v>
       </c>
       <c r="H615" t="n">
         <v>1536356</v>
@@ -18233,7 +18233,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G616" t="n">
-        <v>3.75201821327209</v>
+        <v>3.75201797485352</v>
       </c>
       <c r="H616" t="n">
         <v>1891956</v>
@@ -18262,7 +18262,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G617" t="n">
-        <v>3.79533076286316</v>
+        <v>3.79533123970032</v>
       </c>
       <c r="H617" t="n">
         <v>2151430</v>
@@ -18291,7 +18291,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G618" t="n">
-        <v>3.78856348991394</v>
+        <v>3.78856372833252</v>
       </c>
       <c r="H618" t="n">
         <v>1967546</v>
@@ -18320,7 +18320,7 @@
         <v>5.53200006484985</v>
       </c>
       <c r="G619" t="n">
-        <v>3.74389719963074</v>
+        <v>3.74389624595642</v>
       </c>
       <c r="H619" t="n">
         <v>1713013</v>
@@ -18349,7 +18349,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G620" t="n">
-        <v>3.76555323600769</v>
+        <v>3.76555371284485</v>
       </c>
       <c r="H620" t="n">
         <v>1306555</v>
@@ -18378,7 +18378,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G621" t="n">
-        <v>3.72359347343445</v>
+        <v>3.72359371185303</v>
       </c>
       <c r="H621" t="n">
         <v>1285528</v>
@@ -18407,7 +18407,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G622" t="n">
-        <v>3.70464396476746</v>
+        <v>3.70464420318604</v>
       </c>
       <c r="H622" t="n">
         <v>2574109</v>
@@ -18465,7 +18465,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G624" t="n">
-        <v>3.76555323600769</v>
+        <v>3.76555371284485</v>
       </c>
       <c r="H624" t="n">
         <v>1476786</v>
@@ -18523,7 +18523,7 @@
         <v>5.5479998588562</v>
       </c>
       <c r="G626" t="n">
-        <v>3.75472474098206</v>
+        <v>3.75472497940063</v>
       </c>
       <c r="H626" t="n">
         <v>1113837</v>
@@ -18552,7 +18552,7 @@
         <v>5.5479998588562</v>
       </c>
       <c r="G627" t="n">
-        <v>3.75472474098206</v>
+        <v>3.75472497940063</v>
       </c>
       <c r="H627" t="n">
         <v>1184740</v>
@@ -18697,7 +18697,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G632" t="n">
-        <v>3.71547222137451</v>
+        <v>3.71547198295593</v>
       </c>
       <c r="H632" t="n">
         <v>1133632</v>
@@ -18726,7 +18726,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G633" t="n">
-        <v>3.77908897399902</v>
+        <v>3.7790892124176</v>
       </c>
       <c r="H633" t="n">
         <v>2716436</v>
@@ -18755,7 +18755,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G634" t="n">
-        <v>3.72630047798157</v>
+        <v>3.72630095481873</v>
       </c>
       <c r="H634" t="n">
         <v>1954633</v>
@@ -18784,7 +18784,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G635" t="n">
-        <v>3.70870518684387</v>
+        <v>3.70870447158813</v>
       </c>
       <c r="H635" t="n">
         <v>1383579</v>
@@ -18813,7 +18813,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G636" t="n">
-        <v>3.74254322052002</v>
+        <v>3.74254250526428</v>
       </c>
       <c r="H636" t="n">
         <v>1612433</v>
@@ -18842,7 +18842,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G637" t="n">
-        <v>3.78179574012756</v>
+        <v>3.78179597854614</v>
       </c>
       <c r="H637" t="n">
         <v>2256127</v>
@@ -18929,7 +18929,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G640" t="n">
-        <v>3.90632104873657</v>
+        <v>3.90632200241089</v>
       </c>
       <c r="H640" t="n">
         <v>2212740</v>
@@ -18958,7 +18958,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>3.90496826171875</v>
+        <v>3.90496754646301</v>
       </c>
       <c r="H641" t="n">
         <v>3062452</v>
@@ -18987,7 +18987,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>3.95403027534485</v>
+        <v>3.95402979850769</v>
       </c>
       <c r="H642" t="n">
         <v>2173043</v>
@@ -19016,7 +19016,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G643" t="n">
-        <v>3.9920220375061</v>
+        <v>3.99202227592468</v>
       </c>
       <c r="H643" t="n">
         <v>1845403</v>
@@ -19045,7 +19045,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>4.03142213821411</v>
+        <v>4.03142166137695</v>
       </c>
       <c r="H644" t="n">
         <v>1861798</v>
@@ -19074,7 +19074,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G645" t="n">
-        <v>4.03423643112183</v>
+        <v>4.03423690795898</v>
       </c>
       <c r="H645" t="n">
         <v>1881231</v>
@@ -19103,7 +19103,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G646" t="n">
-        <v>4.06800699234009</v>
+        <v>4.06800746917725</v>
       </c>
       <c r="H646" t="n">
         <v>2196920</v>
@@ -19190,7 +19190,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94699430465698</v>
+        <v>3.9469940662384</v>
       </c>
       <c r="H649" t="n">
         <v>2336188</v>
@@ -19219,7 +19219,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G650" t="n">
-        <v>3.93292307853699</v>
+        <v>3.93292236328125</v>
       </c>
       <c r="H650" t="n">
         <v>1268362</v>
@@ -19248,7 +19248,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G651" t="n">
-        <v>3.98780107498169</v>
+        <v>3.98780131340027</v>
       </c>
       <c r="H651" t="n">
         <v>1959746</v>
@@ -19335,7 +19335,7 @@
         <v>5.85799980163574</v>
       </c>
       <c r="G654" t="n">
-        <v>4.12147808074951</v>
+        <v>4.12147855758667</v>
       </c>
       <c r="H654" t="n">
         <v>2577078</v>
@@ -19364,7 +19364,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G655" t="n">
-        <v>4.1369571685791</v>
+        <v>4.13695669174194</v>
       </c>
       <c r="H655" t="n">
         <v>2552046</v>
@@ -19451,7 +19451,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G658" t="n">
-        <v>4.14117813110352</v>
+        <v>4.14117765426636</v>
       </c>
       <c r="H658" t="n">
         <v>1808264</v>
@@ -19509,7 +19509,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G660" t="n">
-        <v>4.1369571685791</v>
+        <v>4.13695669174194</v>
       </c>
       <c r="H660" t="n">
         <v>2035992</v>
@@ -19538,7 +19538,7 @@
         <v>5.92799997329712</v>
       </c>
       <c r="G661" t="n">
-        <v>4.17072772979736</v>
+        <v>4.17072820663452</v>
       </c>
       <c r="H661" t="n">
         <v>2282492</v>
@@ -19596,7 +19596,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G663" t="n">
-        <v>4.3072190284729</v>
+        <v>4.30721950531006</v>
       </c>
       <c r="H663" t="n">
         <v>3197524</v>
@@ -19625,7 +19625,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G664" t="n">
-        <v>4.25796937942505</v>
+        <v>4.25796985626221</v>
       </c>
       <c r="H664" t="n">
         <v>2726415</v>
@@ -19654,7 +19654,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G665" t="n">
-        <v>4.25656270980835</v>
+        <v>4.25656223297119</v>
       </c>
       <c r="H665" t="n">
         <v>2888209</v>
@@ -19683,7 +19683,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G666" t="n">
-        <v>4.29174089431763</v>
+        <v>4.29174041748047</v>
       </c>
       <c r="H666" t="n">
         <v>3628929</v>
@@ -19741,7 +19741,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>4.26359796524048</v>
+        <v>4.26359844207764</v>
       </c>
       <c r="H668" t="n">
         <v>1452344</v>
@@ -19828,7 +19828,7 @@
         <v>5.90799999237061</v>
       </c>
       <c r="G671" t="n">
-        <v>4.15665626525879</v>
+        <v>4.15665674209595</v>
       </c>
       <c r="H671" t="n">
         <v>2723118</v>
@@ -19857,7 +19857,7 @@
         <v>5.89799976348877</v>
       </c>
       <c r="G672" t="n">
-        <v>4.1496205329895</v>
+        <v>4.14962100982666</v>
       </c>
       <c r="H672" t="n">
         <v>1584912</v>
@@ -20002,7 +20002,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G677" t="n">
-        <v>4.30299711227417</v>
+        <v>4.30299758911133</v>
       </c>
       <c r="H677" t="n">
         <v>1999919</v>
@@ -20031,7 +20031,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>4.3269190788269</v>
+        <v>4.32691955566406</v>
       </c>
       <c r="H678" t="n">
         <v>2624174</v>
@@ -20089,7 +20089,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G680" t="n">
-        <v>4.34943294525146</v>
+        <v>4.34943342208862</v>
       </c>
       <c r="H680" t="n">
         <v>2137342</v>
@@ -20234,7 +20234,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G685" t="n">
-        <v>4.35506200790405</v>
+        <v>4.35506153106689</v>
       </c>
       <c r="H685" t="n">
         <v>1975271</v>
@@ -20263,7 +20263,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G686" t="n">
-        <v>4.21434831619263</v>
+        <v>4.21434879302979</v>
       </c>
       <c r="H686" t="n">
         <v>2662580</v>
@@ -20350,7 +20350,7 @@
         <v>5.97200012207031</v>
       </c>
       <c r="G689" t="n">
-        <v>4.20168447494507</v>
+        <v>4.20168495178223</v>
       </c>
       <c r="H689" t="n">
         <v>1594823</v>
@@ -20408,7 +20408,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G691" t="n">
-        <v>4.14117813110352</v>
+        <v>4.14117765426636</v>
       </c>
       <c r="H691" t="n">
         <v>1961556</v>
@@ -20437,7 +20437,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>4.1369571685791</v>
+        <v>4.13695669174194</v>
       </c>
       <c r="H692" t="n">
         <v>1951320</v>
@@ -20466,7 +20466,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G693" t="n">
-        <v>4.06378555297852</v>
+        <v>4.06378602981567</v>
       </c>
       <c r="H693" t="n">
         <v>3390209</v>
@@ -20495,7 +20495,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G694" t="n">
-        <v>4.02297973632812</v>
+        <v>4.02297878265381</v>
       </c>
       <c r="H694" t="n">
         <v>3651847</v>
@@ -20553,7 +20553,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G696" t="n">
-        <v>4.11022138595581</v>
+        <v>4.11022090911865</v>
       </c>
       <c r="H696" t="n">
         <v>3717587</v>
@@ -20640,7 +20640,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>4.10177755355835</v>
+        <v>4.10177803039551</v>
       </c>
       <c r="H699" t="n">
         <v>1720119</v>
@@ -20698,7 +20698,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G701" t="n">
-        <v>3.93855142593384</v>
+        <v>3.93855166435242</v>
       </c>
       <c r="H701" t="n">
         <v>5230571</v>
@@ -20727,7 +20727,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G702" t="n">
-        <v>3.98357963562012</v>
+        <v>3.98358011245728</v>
       </c>
       <c r="H702" t="n">
         <v>1900172</v>
@@ -20785,7 +20785,7 @@
         <v>5.6560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97935795783997</v>
+        <v>3.9793586730957</v>
       </c>
       <c r="H704" t="n">
         <v>3234030</v>
@@ -20814,7 +20814,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G705" t="n">
-        <v>3.9920220375061</v>
+        <v>3.99202227592468</v>
       </c>
       <c r="H705" t="n">
         <v>2966146</v>
@@ -20872,7 +20872,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G707" t="n">
-        <v>4.03845691680908</v>
+        <v>4.03845739364624</v>
       </c>
       <c r="H707" t="n">
         <v>1576596</v>
@@ -21046,7 +21046,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G713" t="n">
-        <v>4.03423643112183</v>
+        <v>4.03423690795898</v>
       </c>
       <c r="H713" t="n">
         <v>1504144</v>
@@ -21075,7 +21075,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G714" t="n">
-        <v>4.15524959564209</v>
+        <v>4.15524911880493</v>
       </c>
       <c r="H714" t="n">
         <v>2551492</v>
@@ -21162,7 +21162,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G717" t="n">
-        <v>4.11022138595581</v>
+        <v>4.11022090911865</v>
       </c>
       <c r="H717" t="n">
         <v>1397730</v>
@@ -21365,7 +21365,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.00468635559082</v>
+        <v>4.00468587875366</v>
       </c>
       <c r="H724" t="n">
         <v>2590263</v>
@@ -21394,7 +21394,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G725" t="n">
-        <v>3.96388006210327</v>
+        <v>3.96387982368469</v>
       </c>
       <c r="H725" t="n">
         <v>1624360</v>
@@ -21423,7 +21423,7 @@
         <v>5.61399984359741</v>
       </c>
       <c r="G726" t="n">
-        <v>3.94980883598328</v>
+        <v>3.9498085975647</v>
       </c>
       <c r="H726" t="n">
         <v>2078476</v>
@@ -21539,7 +21539,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G730" t="n">
-        <v>4.00609350204468</v>
+        <v>4.00609397888184</v>
       </c>
       <c r="H730" t="n">
         <v>5585827</v>
@@ -21597,7 +21597,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G732" t="n">
-        <v>4.15524959564209</v>
+        <v>4.15524911880493</v>
       </c>
       <c r="H732" t="n">
         <v>3095858</v>
@@ -21626,7 +21626,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G733" t="n">
-        <v>4.11584997177124</v>
+        <v>4.11584949493408</v>
       </c>
       <c r="H733" t="n">
         <v>1880368</v>
@@ -21684,7 +21684,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G735" t="n">
-        <v>4.14258527755737</v>
+        <v>4.14258480072021</v>
       </c>
       <c r="H735" t="n">
         <v>2133876</v>
@@ -21800,7 +21800,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G739" t="n">
-        <v>4.11584997177124</v>
+        <v>4.11584949493408</v>
       </c>
       <c r="H739" t="n">
         <v>2831520</v>
@@ -21916,7 +21916,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G743" t="n">
-        <v>4.06660079956055</v>
+        <v>4.06659984588623</v>
       </c>
       <c r="H743" t="n">
         <v>1924712</v>
@@ -21945,7 +21945,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G744" t="n">
-        <v>4.01031541824341</v>
+        <v>4.01031494140625</v>
       </c>
       <c r="H744" t="n">
         <v>1958168</v>
@@ -21974,7 +21974,7 @@
         <v>5.75600004196167</v>
       </c>
       <c r="G745" t="n">
-        <v>4.04971504211426</v>
+        <v>4.0497145652771</v>
       </c>
       <c r="H745" t="n">
         <v>1957667</v>
@@ -22003,7 +22003,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G746" t="n">
-        <v>4.03845691680908</v>
+        <v>4.03845739364624</v>
       </c>
       <c r="H746" t="n">
         <v>1299311</v>
@@ -22061,7 +22061,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G748" t="n">
-        <v>3.99624371528625</v>
+        <v>3.99624347686768</v>
       </c>
       <c r="H748" t="n">
         <v>1909085</v>
@@ -22090,7 +22090,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G749" t="n">
-        <v>3.9920220375061</v>
+        <v>3.99202227592468</v>
       </c>
       <c r="H749" t="n">
         <v>1654695</v>
@@ -22119,7 +22119,7 @@
         <v>5.67799997329712</v>
       </c>
       <c r="G750" t="n">
-        <v>3.99483609199524</v>
+        <v>3.99483704566956</v>
       </c>
       <c r="H750" t="n">
         <v>3183705</v>
@@ -22177,7 +22177,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G752" t="n">
-        <v>4.02297973632812</v>
+        <v>4.02297878265381</v>
       </c>
       <c r="H752" t="n">
         <v>1504461</v>
@@ -22206,7 +22206,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G753" t="n">
-        <v>3.99061489105225</v>
+        <v>3.99061512947083</v>
       </c>
       <c r="H753" t="n">
         <v>1519156</v>
@@ -22235,7 +22235,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03142213821411</v>
+        <v>4.03142166137695</v>
       </c>
       <c r="H754" t="n">
         <v>1468194</v>
@@ -22264,7 +22264,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G755" t="n">
-        <v>4.03142213821411</v>
+        <v>4.03142166137695</v>
       </c>
       <c r="H755" t="n">
         <v>1178469</v>
@@ -22293,7 +22293,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G756" t="n">
-        <v>4.02297973632812</v>
+        <v>4.02297878265381</v>
       </c>
       <c r="H756" t="n">
         <v>1303279</v>
@@ -22322,7 +22322,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G757" t="n">
-        <v>4.00187206268311</v>
+        <v>4.00187253952026</v>
       </c>
       <c r="H757" t="n">
         <v>2492570</v>
@@ -22351,7 +22351,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G758" t="n">
-        <v>4.06660079956055</v>
+        <v>4.06659984588623</v>
       </c>
       <c r="H758" t="n">
         <v>2043707</v>
@@ -22380,7 +22380,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G759" t="n">
-        <v>4.05815696716309</v>
+        <v>4.0581579208374</v>
       </c>
       <c r="H759" t="n">
         <v>2104505</v>
@@ -22409,7 +22409,7 @@
         <v>5.78800010681152</v>
       </c>
       <c r="G760" t="n">
-        <v>4.07222938537598</v>
+        <v>4.07222890853882</v>
       </c>
       <c r="H760" t="n">
         <v>1078677</v>
@@ -22467,7 +22467,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G762" t="n">
-        <v>4.15243482589722</v>
+        <v>4.15243530273438</v>
       </c>
       <c r="H762" t="n">
         <v>2701376</v>
@@ -22525,7 +22525,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10037136077881</v>
+        <v>4.10037088394165</v>
       </c>
       <c r="H764" t="n">
         <v>2677873</v>
@@ -22554,7 +22554,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G765" t="n">
-        <v>4.14821338653564</v>
+        <v>4.1482138633728</v>
       </c>
       <c r="H765" t="n">
         <v>2373233</v>
@@ -22583,7 +22583,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G766" t="n">
-        <v>4.12288570404053</v>
+        <v>4.12288475036621</v>
       </c>
       <c r="H766" t="n">
         <v>1229876</v>
@@ -22670,7 +22670,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G769" t="n">
-        <v>4.14117813110352</v>
+        <v>4.14117765426636</v>
       </c>
       <c r="H769" t="n">
         <v>2385144</v>
@@ -22844,7 +22844,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G775" t="n">
-        <v>4.01312971115112</v>
+        <v>4.01312923431396</v>
       </c>
       <c r="H775" t="n">
         <v>1157213</v>
@@ -22873,7 +22873,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G776" t="n">
-        <v>4.06660079956055</v>
+        <v>4.06659984588623</v>
       </c>
       <c r="H776" t="n">
         <v>1321194</v>
@@ -22989,7 +22989,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G780" t="n">
-        <v>4.01312971115112</v>
+        <v>4.01312923431396</v>
       </c>
       <c r="H780" t="n">
         <v>1816209</v>
@@ -23018,7 +23018,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G781" t="n">
-        <v>3.83864521980286</v>
+        <v>3.83864569664001</v>
       </c>
       <c r="H781" t="n">
         <v>4756331</v>
@@ -23047,7 +23047,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G782" t="n">
-        <v>3.900559425354</v>
+        <v>3.90055918693542</v>
       </c>
       <c r="H782" t="n">
         <v>3299250</v>
@@ -23076,7 +23076,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G783" t="n">
-        <v>3.914630651474</v>
+        <v>3.91463088989258</v>
       </c>
       <c r="H783" t="n">
         <v>2410040</v>
@@ -23105,7 +23105,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G784" t="n">
-        <v>3.87663793563843</v>
+        <v>3.87663841247559</v>
       </c>
       <c r="H784" t="n">
         <v>1880712</v>
@@ -23163,7 +23163,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G786" t="n">
-        <v>3.78517508506775</v>
+        <v>3.78517484664917</v>
       </c>
       <c r="H786" t="n">
         <v>2931931</v>
@@ -23192,7 +23192,7 @@
         <v>5.43599987030029</v>
       </c>
       <c r="G787" t="n">
-        <v>3.82457375526428</v>
+        <v>3.82457423210144</v>
       </c>
       <c r="H787" t="n">
         <v>3245860</v>
@@ -23221,7 +23221,7 @@
         <v>5.5</v>
       </c>
       <c r="G788" t="n">
-        <v>3.8696014881134</v>
+        <v>3.86960244178772</v>
       </c>
       <c r="H788" t="n">
         <v>1885870</v>
@@ -23250,7 +23250,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G789" t="n">
-        <v>3.82035279273987</v>
+        <v>3.82035255432129</v>
       </c>
       <c r="H789" t="n">
         <v>2128253</v>
@@ -23279,7 +23279,7 @@
         <v>5.43599987030029</v>
       </c>
       <c r="G790" t="n">
-        <v>3.82457375526428</v>
+        <v>3.82457423210144</v>
       </c>
       <c r="H790" t="n">
         <v>2623020</v>
@@ -23308,7 +23308,7 @@
         <v>5.49200010299683</v>
       </c>
       <c r="G791" t="n">
-        <v>3.86397433280945</v>
+        <v>3.86397337913513</v>
       </c>
       <c r="H791" t="n">
         <v>2307388</v>
@@ -23337,7 +23337,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G792" t="n">
-        <v>3.95403027534485</v>
+        <v>3.95402979850769</v>
       </c>
       <c r="H792" t="n">
         <v>3429073</v>
@@ -23366,7 +23366,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G793" t="n">
-        <v>3.93151545524597</v>
+        <v>3.93151593208313</v>
       </c>
       <c r="H793" t="n">
         <v>2352694</v>
@@ -23395,7 +23395,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G794" t="n">
-        <v>3.93855142593384</v>
+        <v>3.93855166435242</v>
       </c>
       <c r="H794" t="n">
         <v>2148060</v>
@@ -23424,7 +23424,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G795" t="n">
-        <v>3.98639392852783</v>
+        <v>3.98639345169067</v>
       </c>
       <c r="H795" t="n">
         <v>7441044</v>
@@ -23453,7 +23453,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G796" t="n">
-        <v>3.95121550559998</v>
+        <v>3.95121598243713</v>
       </c>
       <c r="H796" t="n">
         <v>945346</v>
@@ -23482,7 +23482,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>3.96106576919556</v>
+        <v>3.9610652923584</v>
       </c>
       <c r="H797" t="n">
         <v>1004925</v>
@@ -23511,7 +23511,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G798" t="n">
-        <v>3.83020305633545</v>
+        <v>3.83020257949829</v>
       </c>
       <c r="H798" t="n">
         <v>4716102</v>
@@ -23540,7 +23540,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91744470596313</v>
+        <v>3.91744422912598</v>
       </c>
       <c r="H799" t="n">
         <v>2867974</v>
@@ -23569,7 +23569,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G800" t="n">
-        <v>3.91040968894958</v>
+        <v>3.91040873527527</v>
       </c>
       <c r="H800" t="n">
         <v>2353232</v>
@@ -23627,7 +23627,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G802" t="n">
-        <v>3.85130977630615</v>
+        <v>3.85130953788757</v>
       </c>
       <c r="H802" t="n">
         <v>2319002</v>
@@ -23656,7 +23656,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>3.92588686943054</v>
+        <v>3.92588782310486</v>
       </c>
       <c r="H803" t="n">
         <v>3693207</v>
@@ -23743,7 +23743,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G806" t="n">
-        <v>3.99061489105225</v>
+        <v>3.99061512947083</v>
       </c>
       <c r="H806" t="n">
         <v>2564951</v>
@@ -23772,7 +23772,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G807" t="n">
-        <v>3.96247243881226</v>
+        <v>3.96247267723083</v>
       </c>
       <c r="H807" t="n">
         <v>3565769</v>
@@ -23801,7 +23801,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G808" t="n">
-        <v>3.9920220375061</v>
+        <v>3.99202227592468</v>
       </c>
       <c r="H808" t="n">
         <v>2720971</v>
@@ -23830,7 +23830,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G809" t="n">
-        <v>3.99624371528625</v>
+        <v>3.99624347686768</v>
       </c>
       <c r="H809" t="n">
         <v>1734134</v>
@@ -23859,7 +23859,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G810" t="n">
-        <v>4.05815696716309</v>
+        <v>4.0581579208374</v>
       </c>
       <c r="H810" t="n">
         <v>2220985</v>
@@ -23888,7 +23888,7 @@
         <v>5.78399991989136</v>
       </c>
       <c r="G811" t="n">
-        <v>4.0694146156311</v>
+        <v>4.06941413879395</v>
       </c>
       <c r="H811" t="n">
         <v>1348599</v>
@@ -23917,7 +23917,7 @@
         <v>5.72399997711182</v>
       </c>
       <c r="G812" t="n">
-        <v>4.0272011756897</v>
+        <v>4.02720022201538</v>
       </c>
       <c r="H812" t="n">
         <v>1351874</v>
@@ -23946,7 +23946,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G813" t="n">
-        <v>4.01031541824341</v>
+        <v>4.01031494140625</v>
       </c>
       <c r="H813" t="n">
         <v>1717511</v>
@@ -23975,7 +23975,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G814" t="n">
-        <v>4.06378555297852</v>
+        <v>4.06378602981567</v>
       </c>
       <c r="H814" t="n">
         <v>4365856</v>
@@ -24033,7 +24033,7 @@
         <v>5.86199998855591</v>
       </c>
       <c r="G816" t="n">
-        <v>4.12429189682007</v>
+        <v>4.12429237365723</v>
       </c>
       <c r="H816" t="n">
         <v>4378895</v>
@@ -24091,7 +24091,7 @@
         <v>6.14400005340576</v>
       </c>
       <c r="G818" t="n">
-        <v>4.32269763946533</v>
+        <v>4.32269716262817</v>
       </c>
       <c r="H818" t="n">
         <v>2983134</v>
@@ -24120,7 +24120,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30581140518188</v>
+        <v>4.30581188201904</v>
       </c>
       <c r="H819" t="n">
         <v>2440838</v>
@@ -24149,7 +24149,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G820" t="n">
-        <v>4.2185697555542</v>
+        <v>4.21857023239136</v>
       </c>
       <c r="H820" t="n">
         <v>3588873</v>
@@ -24207,7 +24207,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G822" t="n">
-        <v>4.22842073440552</v>
+        <v>4.2284197807312</v>
       </c>
       <c r="H822" t="n">
         <v>2927455</v>
@@ -24236,7 +24236,7 @@
         <v>6.07800006866455</v>
       </c>
       <c r="G823" t="n">
-        <v>4.2762622833252</v>
+        <v>4.27626276016235</v>
       </c>
       <c r="H823" t="n">
         <v>2652568</v>
@@ -24294,7 +24294,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G825" t="n">
-        <v>4.27063417434692</v>
+        <v>4.27063369750977</v>
       </c>
       <c r="H825" t="n">
         <v>1721301</v>
@@ -24323,7 +24323,7 @@
         <v>6.07200002670288</v>
       </c>
       <c r="G826" t="n">
-        <v>4.27204132080078</v>
+        <v>4.27204084396362</v>
       </c>
       <c r="H826" t="n">
         <v>1331440</v>
@@ -24439,7 +24439,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G830" t="n">
-        <v>4.25656270980835</v>
+        <v>4.25656223297119</v>
       </c>
       <c r="H830" t="n">
         <v>1830667</v>
@@ -24468,7 +24468,7 @@
         <v>6.10400009155273</v>
       </c>
       <c r="G831" t="n">
-        <v>4.29455471038818</v>
+        <v>4.29455518722534</v>
       </c>
       <c r="H831" t="n">
         <v>1364600</v>
@@ -24497,7 +24497,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G832" t="n">
-        <v>4.35506200790405</v>
+        <v>4.35506153106689</v>
       </c>
       <c r="H832" t="n">
         <v>2276022</v>
@@ -24526,7 +24526,7 @@
         <v>6.29400014877319</v>
       </c>
       <c r="G833" t="n">
-        <v>4.42823266983032</v>
+        <v>4.42823171615601</v>
       </c>
       <c r="H833" t="n">
         <v>1836726</v>
@@ -24555,7 +24555,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>4.3269190788269</v>
+        <v>4.32691955566406</v>
       </c>
       <c r="H834" t="n">
         <v>2639151</v>
@@ -24584,7 +24584,7 @@
         <v>6.14400005340576</v>
       </c>
       <c r="G835" t="n">
-        <v>4.32269763946533</v>
+        <v>4.32269716262817</v>
       </c>
       <c r="H835" t="n">
         <v>1938197</v>
@@ -24671,7 +24671,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G838" t="n">
-        <v>4.08348608016968</v>
+        <v>4.08348560333252</v>
       </c>
       <c r="H838" t="n">
         <v>2885826</v>
@@ -24700,7 +24700,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G839" t="n">
-        <v>4.08067178726196</v>
+        <v>4.0806713104248</v>
       </c>
       <c r="H839" t="n">
         <v>4239735</v>
@@ -24758,7 +24758,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>3.91181588172913</v>
+        <v>3.91181612014771</v>
       </c>
       <c r="H841" t="n">
         <v>4148352</v>
@@ -24787,7 +24787,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G842" t="n">
-        <v>3.96106576919556</v>
+        <v>3.9610652923584</v>
       </c>
       <c r="H842" t="n">
         <v>3104286</v>
@@ -24845,7 +24845,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G844" t="n">
-        <v>4.08067178726196</v>
+        <v>4.0806713104248</v>
       </c>
       <c r="H844" t="n">
         <v>5643990</v>
@@ -24874,7 +24874,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G845" t="n">
-        <v>3.91744470596313</v>
+        <v>3.91744422912598</v>
       </c>
       <c r="H845" t="n">
         <v>3403862</v>
@@ -24903,7 +24903,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G846" t="n">
-        <v>3.5698835849762</v>
+        <v>3.56988406181335</v>
       </c>
       <c r="H846" t="n">
         <v>6000576</v>
@@ -25077,7 +25077,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G852" t="n">
-        <v>3.13085961341858</v>
+        <v>3.13085985183716</v>
       </c>
       <c r="H852" t="n">
         <v>5086607</v>
@@ -25193,7 +25193,7 @@
         <v>4.25899982452393</v>
       </c>
       <c r="G856" t="n">
-        <v>2.99647927284241</v>
+        <v>2.99647903442383</v>
       </c>
       <c r="H856" t="n">
         <v>4507664</v>
@@ -25251,7 +25251,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G858" t="n">
-        <v>3.24483752250671</v>
+        <v>3.24483728408813</v>
       </c>
       <c r="H858" t="n">
         <v>3787328</v>
@@ -25309,7 +25309,7 @@
         <v>4.57100009918213</v>
       </c>
       <c r="G860" t="n">
-        <v>3.21599149703979</v>
+        <v>3.21599125862122</v>
       </c>
       <c r="H860" t="n">
         <v>2461394</v>
@@ -25338,7 +25338,7 @@
         <v>4.85900020599365</v>
       </c>
       <c r="G861" t="n">
-        <v>3.41861796379089</v>
+        <v>3.41861820220947</v>
       </c>
       <c r="H861" t="n">
         <v>2743317</v>
@@ -25367,7 +25367,7 @@
         <v>4.98899984359741</v>
       </c>
       <c r="G862" t="n">
-        <v>3.51008081436157</v>
+        <v>3.51008129119873</v>
       </c>
       <c r="H862" t="n">
         <v>3920930</v>
@@ -25425,7 +25425,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G864" t="n">
-        <v>3.40524983406067</v>
+        <v>3.40525007247925</v>
       </c>
       <c r="H864" t="n">
         <v>1508109</v>
@@ -25483,7 +25483,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G866" t="n">
-        <v>3.38554954528809</v>
+        <v>3.3855504989624</v>
       </c>
       <c r="H866" t="n">
         <v>2520981</v>
@@ -25541,7 +25541,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G868" t="n">
-        <v>3.31800818443298</v>
+        <v>3.3180079460144</v>
       </c>
       <c r="H868" t="n">
         <v>2606733</v>
@@ -25599,7 +25599,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G870" t="n">
-        <v>3.41228532791138</v>
+        <v>3.41228556632996</v>
       </c>
       <c r="H870" t="n">
         <v>2460427</v>
@@ -25628,7 +25628,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G871" t="n">
-        <v>3.44042778015137</v>
+        <v>3.44042801856995</v>
       </c>
       <c r="H871" t="n">
         <v>2347024</v>
@@ -25657,7 +25657,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G872" t="n">
-        <v>3.47138476371765</v>
+        <v>3.47138547897339</v>
       </c>
       <c r="H872" t="n">
         <v>2886869</v>
@@ -25686,7 +25686,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G873" t="n">
-        <v>3.41932129859924</v>
+        <v>3.41932153701782</v>
       </c>
       <c r="H873" t="n">
         <v>1883840</v>
@@ -25715,7 +25715,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G874" t="n">
-        <v>3.42072868347168</v>
+        <v>3.42072820663452</v>
       </c>
       <c r="H874" t="n">
         <v>1580035</v>
@@ -25744,7 +25744,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G875" t="n">
-        <v>3.29408717155457</v>
+        <v>3.29408693313599</v>
       </c>
       <c r="H875" t="n">
         <v>1885170</v>
@@ -25773,7 +25773,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G876" t="n">
-        <v>3.46294212341309</v>
+        <v>3.46294236183167</v>
       </c>
       <c r="H876" t="n">
         <v>1912585</v>
@@ -25802,7 +25802,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G877" t="n">
-        <v>3.37710785865784</v>
+        <v>3.3771071434021</v>
       </c>
       <c r="H877" t="n">
         <v>2311934</v>
@@ -25831,7 +25831,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G878" t="n">
-        <v>3.42213582992554</v>
+        <v>3.42213535308838</v>
       </c>
       <c r="H878" t="n">
         <v>1632555</v>
@@ -25860,7 +25860,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G879" t="n">
-        <v>3.41228532791138</v>
+        <v>3.41228556632996</v>
       </c>
       <c r="H879" t="n">
         <v>2283546</v>
@@ -25889,7 +25889,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G880" t="n">
-        <v>3.41510009765625</v>
+        <v>3.41510033607483</v>
       </c>
       <c r="H880" t="n">
         <v>2751793</v>
@@ -25918,7 +25918,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>3.42635726928711</v>
+        <v>3.42635703086853</v>
       </c>
       <c r="H881" t="n">
         <v>1909832</v>
@@ -25947,7 +25947,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G882" t="n">
-        <v>3.59169435501099</v>
+        <v>3.59169459342957</v>
       </c>
       <c r="H882" t="n">
         <v>3976280</v>
@@ -26063,7 +26063,7 @@
         <v>4.91599988937378</v>
       </c>
       <c r="G886" t="n">
-        <v>3.45872068405151</v>
+        <v>3.45872020721436</v>
       </c>
       <c r="H886" t="n">
         <v>1673122</v>
@@ -26092,7 +26092,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G887" t="n">
-        <v>3.50797033309937</v>
+        <v>3.50797057151794</v>
       </c>
       <c r="H887" t="n">
         <v>939668</v>
@@ -26121,7 +26121,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G888" t="n">
-        <v>3.47701358795166</v>
+        <v>3.47701334953308</v>
       </c>
       <c r="H888" t="n">
         <v>1537490</v>
@@ -26179,7 +26179,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G890" t="n">
-        <v>3.48264217376709</v>
+        <v>3.48264169692993</v>
       </c>
       <c r="H890" t="n">
         <v>1701329</v>
@@ -26208,7 +26208,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G891" t="n">
-        <v>3.46857047080994</v>
+        <v>3.46857023239136</v>
       </c>
       <c r="H891" t="n">
         <v>2602511</v>
@@ -26237,7 +26237,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G892" t="n">
-        <v>3.55299854278564</v>
+        <v>3.55299878120422</v>
       </c>
       <c r="H892" t="n">
         <v>3832249</v>
@@ -26266,7 +26266,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G893" t="n">
-        <v>3.57692694664001</v>
+        <v>3.57692718505859</v>
       </c>
       <c r="H893" t="n">
         <v>5729697</v>
@@ -26295,7 +26295,7 @@
         <v>4.67399978637695</v>
       </c>
       <c r="G894" t="n">
-        <v>3.45282053947449</v>
+        <v>3.45282077789307</v>
       </c>
       <c r="H894" t="n">
         <v>5069170</v>
@@ -26324,7 +26324,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G895" t="n">
-        <v>3.50748658180237</v>
+        <v>3.50748705863953</v>
       </c>
       <c r="H895" t="n">
         <v>2423241</v>
@@ -26382,7 +26382,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.52817130088806</v>
+        <v>3.52817106246948</v>
       </c>
       <c r="H897" t="n">
         <v>1536527</v>
@@ -26440,7 +26440,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G899" t="n">
-        <v>3.5710175037384</v>
+        <v>3.57101726531982</v>
       </c>
       <c r="H899" t="n">
         <v>1897548</v>
@@ -26469,7 +26469,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G900" t="n">
-        <v>3.5444233417511</v>
+        <v>3.54442310333252</v>
       </c>
       <c r="H900" t="n">
         <v>2992412</v>
@@ -26498,7 +26498,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G901" t="n">
-        <v>3.64489006996155</v>
+        <v>3.64489030838013</v>
       </c>
       <c r="H901" t="n">
         <v>3984576</v>
@@ -26527,7 +26527,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G902" t="n">
-        <v>3.60943150520325</v>
+        <v>3.60943126678467</v>
       </c>
       <c r="H902" t="n">
         <v>4042772</v>
@@ -26556,7 +26556,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>3.65671014785767</v>
+        <v>3.65670967102051</v>
       </c>
       <c r="H903" t="n">
         <v>2167799</v>
@@ -26585,7 +26585,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G904" t="n">
-        <v>3.73797011375427</v>
+        <v>3.73797035217285</v>
       </c>
       <c r="H904" t="n">
         <v>2834004</v>
@@ -26614,7 +26614,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G905" t="n">
-        <v>3.8266179561615</v>
+        <v>3.82661747932434</v>
       </c>
       <c r="H905" t="n">
         <v>2792947</v>
@@ -26672,7 +26672,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G907" t="n">
-        <v>3.8266179561615</v>
+        <v>3.82661747932434</v>
       </c>
       <c r="H907" t="n">
         <v>3358447</v>
@@ -26701,7 +26701,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G908" t="n">
-        <v>3.85247302055359</v>
+        <v>3.85247349739075</v>
       </c>
       <c r="H908" t="n">
         <v>2032208</v>
@@ -26730,7 +26730,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G909" t="n">
-        <v>3.76013231277466</v>
+        <v>3.76013255119324</v>
       </c>
       <c r="H909" t="n">
         <v>3188797</v>
@@ -26759,7 +26759,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G910" t="n">
-        <v>3.7158088684082</v>
+        <v>3.71580839157104</v>
       </c>
       <c r="H910" t="n">
         <v>2743541</v>
@@ -26788,7 +26788,7 @@
         <v>4.94600009918213</v>
       </c>
       <c r="G911" t="n">
-        <v>3.65375566482544</v>
+        <v>3.65375518798828</v>
       </c>
       <c r="H911" t="n">
         <v>4498942</v>
@@ -26846,7 +26846,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G913" t="n">
-        <v>3.8266179561615</v>
+        <v>3.82661747932434</v>
       </c>
       <c r="H913" t="n">
         <v>4189234</v>
@@ -26875,7 +26875,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G914" t="n">
-        <v>3.91157174110413</v>
+        <v>3.91157150268555</v>
       </c>
       <c r="H914" t="n">
         <v>3512294</v>
@@ -26904,7 +26904,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G915" t="n">
-        <v>3.88571643829346</v>
+        <v>3.8857159614563</v>
       </c>
       <c r="H915" t="n">
         <v>3188279</v>
@@ -26933,7 +26933,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93373417854309</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H916" t="n">
         <v>2794030</v>
@@ -26991,7 +26991,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G918" t="n">
-        <v>3.88571643829346</v>
+        <v>3.8857159614563</v>
       </c>
       <c r="H918" t="n">
         <v>2502322</v>
@@ -27078,7 +27078,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G921" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H921" t="n">
         <v>3095595</v>
@@ -27194,7 +27194,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355423927307</v>
       </c>
       <c r="H925" t="n">
         <v>1571648</v>
@@ -27223,7 +27223,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G926" t="n">
-        <v>3.91526532173157</v>
+        <v>3.91526579856873</v>
       </c>
       <c r="H926" t="n">
         <v>1897590</v>
@@ -27252,7 +27252,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.85986042022705</v>
+        <v>3.85986065864563</v>
       </c>
       <c r="H927" t="n">
         <v>790824</v>
@@ -27281,7 +27281,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G928" t="n">
-        <v>3.8967969417572</v>
+        <v>3.89679718017578</v>
       </c>
       <c r="H928" t="n">
         <v>1385968</v>
@@ -27310,7 +27310,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G929" t="n">
-        <v>3.93742728233337</v>
+        <v>3.93742680549622</v>
       </c>
       <c r="H929" t="n">
         <v>2225983</v>
@@ -27368,7 +27368,7 @@
         <v>5.125</v>
       </c>
       <c r="G931" t="n">
-        <v>3.78598761558533</v>
+        <v>3.78598809242249</v>
       </c>
       <c r="H931" t="n">
         <v>2346143</v>
@@ -27397,7 +27397,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G932" t="n">
-        <v>3.79337501525879</v>
+        <v>3.79337549209595</v>
       </c>
       <c r="H932" t="n">
         <v>2175651</v>
@@ -27426,7 +27426,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G933" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H933" t="n">
         <v>1504744</v>
@@ -27484,7 +27484,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>3.80076217651367</v>
+        <v>3.80076241493225</v>
       </c>
       <c r="H935" t="n">
         <v>2443627</v>
@@ -27513,7 +27513,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G936" t="n">
-        <v>3.80445599555969</v>
+        <v>3.80445623397827</v>
       </c>
       <c r="H936" t="n">
         <v>1769531</v>
@@ -27542,7 +27542,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G937" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355423927307</v>
       </c>
       <c r="H937" t="n">
         <v>2386659</v>
@@ -27571,7 +27571,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G938" t="n">
-        <v>3.90049076080322</v>
+        <v>3.90049028396606</v>
       </c>
       <c r="H938" t="n">
         <v>1613100</v>
@@ -27600,7 +27600,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G939" t="n">
-        <v>3.94850873947144</v>
+        <v>3.9485080242157</v>
       </c>
       <c r="H939" t="n">
         <v>2557114</v>
@@ -27629,7 +27629,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G940" t="n">
-        <v>3.93003988265991</v>
+        <v>3.93003964424133</v>
       </c>
       <c r="H940" t="n">
         <v>1145389</v>
@@ -27687,7 +27687,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G942" t="n">
-        <v>3.87463545799255</v>
+        <v>3.8746349811554</v>
       </c>
       <c r="H942" t="n">
         <v>2057182</v>
@@ -27716,7 +27716,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G943" t="n">
-        <v>3.95220160484314</v>
+        <v>3.95220184326172</v>
       </c>
       <c r="H943" t="n">
         <v>3126340</v>
@@ -27745,7 +27745,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G944" t="n">
-        <v>4.0777850151062</v>
+        <v>4.07778596878052</v>
       </c>
       <c r="H944" t="n">
         <v>3399468</v>
@@ -27803,7 +27803,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H946" t="n">
         <v>2526362</v>
@@ -27890,7 +27890,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H949" t="n">
         <v>1923021</v>
@@ -27919,7 +27919,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>3.98544454574585</v>
+        <v>3.98544430732727</v>
       </c>
       <c r="H950" t="n">
         <v>2544347</v>
@@ -27948,7 +27948,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G951" t="n">
-        <v>3.98913860321045</v>
+        <v>3.98913884162903</v>
       </c>
       <c r="H951" t="n">
         <v>1899163</v>
@@ -27977,7 +27977,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G952" t="n">
-        <v>4.04454278945923</v>
+        <v>4.04454326629639</v>
       </c>
       <c r="H952" t="n">
         <v>2144893</v>
@@ -28035,7 +28035,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G954" t="n">
-        <v>4.18120718002319</v>
+        <v>4.18120765686035</v>
       </c>
       <c r="H954" t="n">
         <v>3125503</v>
@@ -28093,7 +28093,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>4.20336961746216</v>
+        <v>4.20337009429932</v>
       </c>
       <c r="H956" t="n">
         <v>2050585</v>
@@ -28122,7 +28122,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>4.18859481811523</v>
+        <v>4.18859529495239</v>
       </c>
       <c r="H957" t="n">
         <v>1720771</v>
@@ -28151,7 +28151,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G958" t="n">
-        <v>4.17751407623291</v>
+        <v>4.17751455307007</v>
       </c>
       <c r="H958" t="n">
         <v>2277890</v>
@@ -28180,7 +28180,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>4.12210893630981</v>
+        <v>4.12210941314697</v>
       </c>
       <c r="H959" t="n">
         <v>1853234</v>
@@ -28209,7 +28209,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G960" t="n">
-        <v>4.18859481811523</v>
+        <v>4.18859529495239</v>
       </c>
       <c r="H960" t="n">
         <v>1985046</v>
@@ -28267,7 +28267,7 @@
         <v>5.5</v>
       </c>
       <c r="G962" t="n">
-        <v>4.06301069259644</v>
+        <v>4.06301164627075</v>
       </c>
       <c r="H962" t="n">
         <v>2219206</v>
@@ -28325,7 +28325,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G964" t="n">
-        <v>4.11841583251953</v>
+        <v>4.11841630935669</v>
       </c>
       <c r="H964" t="n">
         <v>1601622</v>
@@ -28354,7 +28354,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H965" t="n">
         <v>1639295</v>
@@ -28383,7 +28383,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G966" t="n">
-        <v>3.98913860321045</v>
+        <v>3.98913884162903</v>
       </c>
       <c r="H966" t="n">
         <v>1127368</v>
@@ -28412,7 +28412,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G967" t="n">
-        <v>3.95958876609802</v>
+        <v>3.95958948135376</v>
       </c>
       <c r="H967" t="n">
         <v>1898539</v>
@@ -28441,7 +28441,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>3.98544454574585</v>
+        <v>3.98544430732727</v>
       </c>
       <c r="H968" t="n">
         <v>2469349</v>
@@ -28470,7 +28470,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G969" t="n">
-        <v>3.95958876609802</v>
+        <v>3.95958948135376</v>
       </c>
       <c r="H969" t="n">
         <v>1553786</v>
@@ -28528,7 +28528,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G971" t="n">
-        <v>4.00760698318481</v>
+        <v>4.0076060295105</v>
       </c>
       <c r="H971" t="n">
         <v>1247670</v>
@@ -28557,7 +28557,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G972" t="n">
-        <v>3.90049076080322</v>
+        <v>3.90049028396606</v>
       </c>
       <c r="H972" t="n">
         <v>2466907</v>
@@ -28586,7 +28586,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G973" t="n">
-        <v>3.99652600288391</v>
+        <v>3.99652552604675</v>
       </c>
       <c r="H973" t="n">
         <v>1022879</v>
@@ -28644,7 +28644,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>4.0113000869751</v>
+        <v>4.01129961013794</v>
       </c>
       <c r="H975" t="n">
         <v>1291408</v>
@@ -28673,7 +28673,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>4.00760698318481</v>
+        <v>4.0076060295105</v>
       </c>
       <c r="H976" t="n">
         <v>1962131</v>
@@ -28702,7 +28702,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G977" t="n">
-        <v>4.0113000869751</v>
+        <v>4.01129961013794</v>
       </c>
       <c r="H977" t="n">
         <v>1569022</v>
@@ -28731,7 +28731,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.94112133979797</v>
+        <v>3.94112038612366</v>
       </c>
       <c r="H978" t="n">
         <v>1454082</v>
@@ -28760,7 +28760,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99652600288391</v>
+        <v>3.99652552604675</v>
       </c>
       <c r="H979" t="n">
         <v>1645876</v>
@@ -28789,7 +28789,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G980" t="n">
-        <v>4.00760698318481</v>
+        <v>4.0076060295105</v>
       </c>
       <c r="H980" t="n">
         <v>1519105</v>
@@ -28818,7 +28818,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G981" t="n">
-        <v>3.98913860321045</v>
+        <v>3.98913884162903</v>
       </c>
       <c r="H981" t="n">
         <v>1899740</v>
@@ -28847,7 +28847,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>4.00021982192993</v>
+        <v>4.00021934509277</v>
       </c>
       <c r="H982" t="n">
         <v>2939840</v>
@@ -28876,7 +28876,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G983" t="n">
-        <v>3.93742728233337</v>
+        <v>3.93742680549622</v>
       </c>
       <c r="H983" t="n">
         <v>2526310</v>
@@ -28905,7 +28905,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G984" t="n">
-        <v>3.97805762290955</v>
+        <v>3.97805738449097</v>
       </c>
       <c r="H984" t="n">
         <v>1253572</v>
@@ -28934,7 +28934,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G985" t="n">
-        <v>3.9743640422821</v>
+        <v>3.97436332702637</v>
       </c>
       <c r="H985" t="n">
         <v>1083034</v>
@@ -28992,7 +28992,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G987" t="n">
-        <v>3.95220160484314</v>
+        <v>3.95220184326172</v>
       </c>
       <c r="H987" t="n">
         <v>958950</v>
@@ -29021,7 +29021,7 @@
         <v>5.5</v>
       </c>
       <c r="G988" t="n">
-        <v>4.06301069259644</v>
+        <v>4.06301164627075</v>
       </c>
       <c r="H988" t="n">
         <v>1871716</v>
@@ -29079,7 +29079,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G990" t="n">
-        <v>3.97805762290955</v>
+        <v>3.97805738449097</v>
       </c>
       <c r="H990" t="n">
         <v>1250603</v>
@@ -29108,7 +29108,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G991" t="n">
-        <v>3.93373417854309</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H991" t="n">
         <v>1650357</v>
@@ -29137,7 +29137,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G992" t="n">
-        <v>3.91526532173157</v>
+        <v>3.91526579856873</v>
       </c>
       <c r="H992" t="n">
         <v>1317171</v>
@@ -29195,7 +29195,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G994" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H994" t="n">
         <v>5985952</v>
@@ -29224,7 +29224,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>3.72688889503479</v>
+        <v>3.72688961029053</v>
       </c>
       <c r="H995" t="n">
         <v>2989212</v>
@@ -29253,7 +29253,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G996" t="n">
-        <v>3.80815005302429</v>
+        <v>3.80814957618713</v>
       </c>
       <c r="H996" t="n">
         <v>2614866</v>
@@ -29282,7 +29282,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G997" t="n">
-        <v>3.79337501525879</v>
+        <v>3.79337549209595</v>
       </c>
       <c r="H997" t="n">
         <v>1790034</v>
@@ -29311,7 +29311,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355423927307</v>
       </c>
       <c r="H998" t="n">
         <v>2779886</v>
@@ -29340,7 +29340,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355423927307</v>
       </c>
       <c r="H999" t="n">
         <v>2215137</v>
@@ -29369,7 +29369,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.88941025733948</v>
+        <v>3.88940954208374</v>
       </c>
       <c r="H1000" t="n">
         <v>2403958</v>
@@ -29398,7 +29398,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H1001" t="n">
         <v>1891362</v>
@@ -29456,7 +29456,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.77860045433044</v>
+        <v>3.77860021591187</v>
       </c>
       <c r="H1003" t="n">
         <v>1050566</v>
@@ -29514,7 +29514,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.76013231277466</v>
+        <v>3.76013255119324</v>
       </c>
       <c r="H1005" t="n">
         <v>1739532</v>
@@ -29543,7 +29543,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.73797011375427</v>
+        <v>3.73797035217285</v>
       </c>
       <c r="H1006" t="n">
         <v>1078704</v>
@@ -29572,7 +29572,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.81184315681458</v>
+        <v>3.811842918396</v>
       </c>
       <c r="H1007" t="n">
         <v>1145488</v>
@@ -29601,7 +29601,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.72688889503479</v>
+        <v>3.72688961029053</v>
       </c>
       <c r="H1008" t="n">
         <v>1959502</v>
@@ -29630,7 +29630,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.72319555282593</v>
+        <v>3.72319579124451</v>
       </c>
       <c r="H1009" t="n">
         <v>1279485</v>
@@ -29659,7 +29659,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.55328774452209</v>
+        <v>3.55328822135925</v>
       </c>
       <c r="H1010" t="n">
         <v>2471336</v>
@@ -29688,7 +29688,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.56806206703186</v>
+        <v>3.56806254386902</v>
       </c>
       <c r="H1011" t="n">
         <v>2665724</v>
@@ -29717,7 +29717,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.66557502746582</v>
+        <v>3.6655752658844</v>
       </c>
       <c r="H1012" t="n">
         <v>1986330</v>
@@ -29746,7 +29746,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.66853022575378</v>
+        <v>3.66852998733521</v>
       </c>
       <c r="H1013" t="n">
         <v>2470620</v>
@@ -29775,7 +29775,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.7010338306427</v>
+        <v>3.70103406906128</v>
       </c>
       <c r="H1014" t="n">
         <v>2774127</v>
@@ -29804,7 +29804,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.83400511741638</v>
+        <v>3.83400535583496</v>
       </c>
       <c r="H1015" t="n">
         <v>2422991</v>
@@ -29920,7 +29920,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.93003988265991</v>
+        <v>3.93003964424133</v>
       </c>
       <c r="H1019" t="n">
         <v>1796510</v>
@@ -29978,7 +29978,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.93373417854309</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H1021" t="n">
         <v>1911921</v>
@@ -30036,7 +30036,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.93742728233337</v>
+        <v>3.93742680549622</v>
       </c>
       <c r="H1023" t="n">
         <v>2555555</v>
@@ -30065,7 +30065,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.90049076080322</v>
+        <v>3.90049028396606</v>
       </c>
       <c r="H1024" t="n">
         <v>1912482</v>
@@ -30094,7 +30094,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.93373417854309</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H1025" t="n">
         <v>1560177</v>
@@ -30123,7 +30123,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.95958876609802</v>
+        <v>3.95958948135376</v>
       </c>
       <c r="H1026" t="n">
         <v>1785365</v>
@@ -30181,7 +30181,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.9632830619812</v>
+        <v>3.96328258514404</v>
       </c>
       <c r="H1028" t="n">
         <v>1394632</v>
@@ -30210,7 +30210,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.9743640422821</v>
+        <v>3.97436332702637</v>
       </c>
       <c r="H1029" t="n">
         <v>1375106</v>
@@ -30239,7 +30239,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.99283218383789</v>
+        <v>3.99283194541931</v>
       </c>
       <c r="H1030" t="n">
         <v>1587588</v>
@@ -30268,7 +30268,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.96697664260864</v>
+        <v>3.96697616577148</v>
       </c>
       <c r="H1031" t="n">
         <v>904133</v>
@@ -30297,7 +30297,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.00760698318481</v>
+        <v>4.0076060295105</v>
       </c>
       <c r="H1032" t="n">
         <v>927282</v>
@@ -30326,7 +30326,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.9743640422821</v>
+        <v>3.97436332702637</v>
       </c>
       <c r="H1033" t="n">
         <v>2221291</v>
@@ -30355,7 +30355,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.95589566230774</v>
+        <v>3.95589542388916</v>
       </c>
       <c r="H1034" t="n">
         <v>2699430</v>
@@ -30384,7 +30384,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.98913860321045</v>
+        <v>3.98913884162903</v>
       </c>
       <c r="H1035" t="n">
         <v>1652889</v>
@@ -30471,7 +30471,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.94850873947144</v>
+        <v>3.9485080242157</v>
       </c>
       <c r="H1038" t="n">
         <v>1605404</v>
@@ -30500,7 +30500,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.91157174110413</v>
+        <v>3.91157150268555</v>
       </c>
       <c r="H1039" t="n">
         <v>1245963</v>
@@ -30587,7 +30587,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.77121329307556</v>
+        <v>3.7712128162384</v>
       </c>
       <c r="H1042" t="n">
         <v>1471582</v>
@@ -30616,7 +30616,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.81184315681458</v>
+        <v>3.811842918396</v>
       </c>
       <c r="H1043" t="n">
         <v>1959948</v>
@@ -30703,7 +30703,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.80076217651367</v>
+        <v>3.80076241493225</v>
       </c>
       <c r="H1046" t="n">
         <v>3242125</v>
@@ -30761,7 +30761,7 @@
         <v>4.93599987030029</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.6463680267334</v>
+        <v>3.64636754989624</v>
       </c>
       <c r="H1048" t="n">
         <v>2603514</v>
@@ -30848,7 +30848,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H1051" t="n">
         <v>864928</v>
@@ -30877,7 +30877,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.82292461395264</v>
+        <v>3.82292413711548</v>
       </c>
       <c r="H1052" t="n">
         <v>997301</v>
@@ -30935,7 +30935,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.8266179561615</v>
+        <v>3.82661747932434</v>
       </c>
       <c r="H1054" t="n">
         <v>1737746</v>
@@ -30993,7 +30993,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355423927307</v>
       </c>
       <c r="H1056" t="n">
         <v>2123824</v>
@@ -31051,7 +31051,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.80445599555969</v>
+        <v>3.80445623397827</v>
       </c>
       <c r="H1058" t="n">
         <v>1626587</v>
@@ -31080,7 +31080,7 @@
         <v>5.125</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.78598761558533</v>
+        <v>3.78598809242249</v>
       </c>
       <c r="H1059" t="n">
         <v>1492843</v>
@@ -31109,7 +31109,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.71211528778076</v>
+        <v>3.71211457252502</v>
       </c>
       <c r="H1060" t="n">
         <v>2056469</v>
@@ -31254,7 +31254,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.69734048843384</v>
+        <v>3.6973397731781</v>
       </c>
       <c r="H1065" t="n">
         <v>1531944</v>
@@ -31283,7 +31283,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.7158088684082</v>
+        <v>3.71580839157104</v>
       </c>
       <c r="H1066" t="n">
         <v>1548248</v>
@@ -31312,7 +31312,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.65523290634155</v>
+        <v>3.65523242950439</v>
       </c>
       <c r="H1067" t="n">
         <v>2042790</v>
@@ -31370,7 +31370,7 @@
         <v>5</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.69364643096924</v>
+        <v>3.69364666938782</v>
       </c>
       <c r="H1069" t="n">
         <v>1936550</v>
@@ -31399,7 +31399,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.72319555282593</v>
+        <v>3.72319579124451</v>
       </c>
       <c r="H1070" t="n">
         <v>2008248</v>
@@ -31486,7 +31486,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.65818810462952</v>
+        <v>3.65818786621094</v>
       </c>
       <c r="H1073" t="n">
         <v>2521086</v>
@@ -31515,7 +31515,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.67443919181824</v>
+        <v>3.6744396686554</v>
       </c>
       <c r="H1074" t="n">
         <v>1922675</v>
@@ -31544,7 +31544,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.65523290634155</v>
+        <v>3.65523242950439</v>
       </c>
       <c r="H1075" t="n">
         <v>1931556</v>
@@ -31602,7 +31602,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.77121329307556</v>
+        <v>3.7712128162384</v>
       </c>
       <c r="H1077" t="n">
         <v>3016029</v>
@@ -31631,7 +31631,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.77860045433044</v>
+        <v>3.77860021591187</v>
       </c>
       <c r="H1078" t="n">
         <v>2245609</v>
@@ -31660,7 +31660,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.82292461395264</v>
+        <v>3.82292413711548</v>
       </c>
       <c r="H1079" t="n">
         <v>3127369</v>
@@ -31689,7 +31689,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.77490711212158</v>
+        <v>3.77490663528442</v>
       </c>
       <c r="H1080" t="n">
         <v>2155949</v>
@@ -31718,7 +31718,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.82292461395264</v>
+        <v>3.82292413711548</v>
       </c>
       <c r="H1081" t="n">
         <v>2606261</v>
@@ -31747,7 +31747,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.80445599555969</v>
+        <v>3.80445623397827</v>
       </c>
       <c r="H1082" t="n">
         <v>1112150</v>
@@ -31805,7 +31805,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.8266179561615</v>
+        <v>3.82661747932434</v>
       </c>
       <c r="H1084" t="n">
         <v>1656774</v>
@@ -31863,7 +31863,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.74166369438171</v>
+        <v>3.74166393280029</v>
       </c>
       <c r="H1086" t="n">
         <v>1637484</v>
@@ -31892,7 +31892,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.71211528778076</v>
+        <v>3.71211457252502</v>
       </c>
       <c r="H1087" t="n">
         <v>1534349</v>
@@ -31921,7 +31921,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.7010338306427</v>
+        <v>3.70103406906128</v>
       </c>
       <c r="H1088" t="n">
         <v>1677269</v>
@@ -31979,7 +31979,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.7010338306427</v>
+        <v>3.70103406906128</v>
       </c>
       <c r="H1090" t="n">
         <v>1683278</v>
@@ -32008,7 +32008,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.72319555282593</v>
+        <v>3.72319579124451</v>
       </c>
       <c r="H1091" t="n">
         <v>3177909</v>
@@ -32037,7 +32037,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.67148423194885</v>
+        <v>3.67148447036743</v>
       </c>
       <c r="H1092" t="n">
         <v>2201932</v>
@@ -32066,7 +32066,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G1093" t="n">
-        <v>3.60647678375244</v>
+        <v>3.60647630691528</v>
       </c>
       <c r="H1093" t="n">
         <v>3832513</v>
@@ -32095,7 +32095,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.69734048843384</v>
+        <v>3.6973397731781</v>
       </c>
       <c r="H1094" t="n">
         <v>2549290</v>
@@ -32124,7 +32124,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G1095" t="n">
-        <v>3.64489006996155</v>
+        <v>3.64489030838013</v>
       </c>
       <c r="H1095" t="n">
         <v>1955127</v>
@@ -32153,7 +32153,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.60204434394836</v>
+        <v>3.60204458236694</v>
       </c>
       <c r="H1096" t="n">
         <v>2719554</v>
@@ -32182,7 +32182,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.65966510772705</v>
+        <v>3.65966463088989</v>
       </c>
       <c r="H1097" t="n">
         <v>3749789</v>
@@ -32211,7 +32211,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.63602542877197</v>
+        <v>3.63602519035339</v>
       </c>
       <c r="H1098" t="n">
         <v>2381518</v>
@@ -32240,7 +32240,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G1099" t="n">
-        <v>3.708420753479</v>
+        <v>3.70842099189758</v>
       </c>
       <c r="H1099" t="n">
         <v>2336262</v>
@@ -32269,7 +32269,7 @@
         <v>5.125</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.78598761558533</v>
+        <v>3.78598809242249</v>
       </c>
       <c r="H1100" t="n">
         <v>4530532</v>
@@ -32327,7 +32327,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1102" t="n">
-        <v>3.85616707801819</v>
+        <v>3.85616660118103</v>
       </c>
       <c r="H1102" t="n">
         <v>3204637</v>
@@ -32385,7 +32385,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.90049076080322</v>
+        <v>3.90049028396606</v>
       </c>
       <c r="H1104" t="n">
         <v>2675850</v>
@@ -32414,7 +32414,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.93373417854309</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H1105" t="n">
         <v>2497840</v>
@@ -32443,7 +32443,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.94112133979797</v>
+        <v>3.94112038612366</v>
       </c>
       <c r="H1106" t="n">
         <v>2467377</v>
@@ -32472,7 +32472,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.90049076080322</v>
+        <v>3.90049028396606</v>
       </c>
       <c r="H1107" t="n">
         <v>2996418</v>
@@ -32501,7 +32501,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.93742728233337</v>
+        <v>3.93742680549622</v>
       </c>
       <c r="H1108" t="n">
         <v>4601585</v>
@@ -32530,7 +32530,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.93373417854309</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H1109" t="n">
         <v>3123703</v>
@@ -32588,7 +32588,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H1111" t="n">
         <v>2094736</v>
@@ -32733,7 +32733,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.08886671066284</v>
+        <v>4.08886623382568</v>
       </c>
       <c r="H1116" t="n">
         <v>1978671</v>
@@ -32762,7 +32762,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.08074045181274</v>
+        <v>4.0807409286499</v>
       </c>
       <c r="H1117" t="n">
         <v>1466310</v>
@@ -32820,7 +32820,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1119" t="n">
-        <v>4.07483005523682</v>
+        <v>4.07483053207397</v>
       </c>
       <c r="H1119" t="n">
         <v>2019828</v>
@@ -32878,7 +32878,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.98913860321045</v>
+        <v>3.98913884162903</v>
       </c>
       <c r="H1121" t="n">
         <v>2065025</v>
@@ -32907,7 +32907,7 @@
         <v>5.37799978256226</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.97288632392883</v>
+        <v>3.97288608551025</v>
       </c>
       <c r="H1122" t="n">
         <v>1740931</v>
@@ -32936,7 +32936,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.95367884635925</v>
+        <v>3.95367908477783</v>
       </c>
       <c r="H1123" t="n">
         <v>4816518</v>
@@ -32965,7 +32965,7 @@
         <v>5.36600017547607</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.96402168273926</v>
+        <v>3.96402215957642</v>
       </c>
       <c r="H1124" t="n">
         <v>1759915</v>
@@ -32994,7 +32994,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.94776916503906</v>
+        <v>3.94776940345764</v>
       </c>
       <c r="H1125" t="n">
         <v>1564931</v>
@@ -33023,7 +33023,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.99061584472656</v>
+        <v>3.99061512947083</v>
       </c>
       <c r="H1126" t="n">
         <v>2028839</v>
@@ -33081,7 +33081,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.99357080459595</v>
+        <v>3.99357104301453</v>
       </c>
       <c r="H1128" t="n">
         <v>2794257</v>
@@ -33110,7 +33110,7 @@
         <v>5.44199991226196</v>
       </c>
       <c r="G1129" t="n">
-        <v>4.02016496658325</v>
+        <v>4.02016448974609</v>
       </c>
       <c r="H1129" t="n">
         <v>2210950</v>
@@ -33139,7 +33139,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1130" t="n">
-        <v>4.05562353134155</v>
+        <v>4.05562400817871</v>
       </c>
       <c r="H1130" t="n">
         <v>1660238</v>
@@ -33197,7 +33197,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1132" t="n">
-        <v>4.00982189178467</v>
+        <v>4.00982236862183</v>
       </c>
       <c r="H1132" t="n">
         <v>824423</v>
@@ -33313,7 +33313,7 @@
         <v>5.42199993133545</v>
       </c>
       <c r="G1136" t="n">
-        <v>4.00539064407349</v>
+        <v>4.00539016723633</v>
       </c>
       <c r="H1136" t="n">
         <v>1582993</v>
@@ -33342,7 +33342,7 @@
         <v>5.5</v>
       </c>
       <c r="G1137" t="n">
-        <v>4.06301069259644</v>
+        <v>4.06301164627075</v>
       </c>
       <c r="H1137" t="n">
         <v>1683942</v>
@@ -33371,7 +33371,7 @@
         <v>5.44799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.02459716796875</v>
+        <v>4.02459764480591</v>
       </c>
       <c r="H1138" t="n">
         <v>2263497</v>
@@ -33400,7 +33400,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.00686740875244</v>
+        <v>4.0068678855896</v>
       </c>
       <c r="H1139" t="n">
         <v>4662672</v>
@@ -33429,7 +33429,7 @@
         <v>5.46400022506714</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.03641700744629</v>
+        <v>4.03641653060913</v>
       </c>
       <c r="H1140" t="n">
         <v>2351103</v>
@@ -33487,7 +33487,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G1142" t="n">
-        <v>4.11029052734375</v>
+        <v>4.11029005050659</v>
       </c>
       <c r="H1142" t="n">
         <v>2253085</v>
@@ -33603,7 +33603,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1146" t="n">
-        <v>4.08074045181274</v>
+        <v>4.0807409286499</v>
       </c>
       <c r="H1146" t="n">
         <v>2135034</v>
@@ -33661,7 +33661,7 @@
         <v>5.62599992752075</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.15609169006348</v>
+        <v>4.15609121322632</v>
       </c>
       <c r="H1148" t="n">
         <v>1717707</v>
@@ -33690,7 +33690,7 @@
         <v>5.62599992752075</v>
       </c>
       <c r="G1149" t="n">
-        <v>4.15609169006348</v>
+        <v>4.15609121322632</v>
       </c>
       <c r="H1149" t="n">
         <v>2064703</v>
@@ -33748,7 +33748,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.28019762039185</v>
+        <v>4.28019714355469</v>
       </c>
       <c r="H1151" t="n">
         <v>5383718</v>
@@ -33835,7 +33835,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G1154" t="n">
-        <v>4.20139169692993</v>
+        <v>4.20139217376709</v>
       </c>
       <c r="H1154" t="n">
         <v>1854970</v>
@@ -33893,7 +33893,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1156" t="n">
-        <v>4.19829845428467</v>
+        <v>4.19829797744751</v>
       </c>
       <c r="H1156" t="n">
         <v>1532118</v>
@@ -33922,7 +33922,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1157" t="n">
-        <v>4.18746995925903</v>
+        <v>4.18747043609619</v>
       </c>
       <c r="H1157" t="n">
         <v>1217874</v>
@@ -33951,7 +33951,7 @@
         <v>5.43400001525879</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.20293855667114</v>
+        <v>4.2029390335083</v>
       </c>
       <c r="H1158" t="n">
         <v>1718866</v>
@@ -34038,7 +34038,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1161" t="n">
-        <v>4.26172161102295</v>
+        <v>4.26172113418579</v>
       </c>
       <c r="H1161" t="n">
         <v>2431783</v>
@@ -34096,7 +34096,7 @@
         <v>5.56199979782104</v>
       </c>
       <c r="G1163" t="n">
-        <v>4.30194044113159</v>
+        <v>4.30194091796875</v>
       </c>
       <c r="H1163" t="n">
         <v>2111611</v>
@@ -34125,7 +34125,7 @@
         <v>5.56199979782104</v>
       </c>
       <c r="G1164" t="n">
-        <v>4.30194044113159</v>
+        <v>4.30194091796875</v>
       </c>
       <c r="H1164" t="n">
         <v>793235</v>
@@ -34154,7 +34154,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.30967473983765</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1165" t="n">
         <v>1393951</v>
@@ -34183,7 +34183,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G1166" t="n">
-        <v>4.33597278594971</v>
+        <v>4.33597230911255</v>
       </c>
       <c r="H1166" t="n">
         <v>1231867</v>
@@ -34241,7 +34241,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G1168" t="n">
-        <v>4.35608243942261</v>
+        <v>4.35608196258545</v>
       </c>
       <c r="H1168" t="n">
         <v>1659780</v>
@@ -34270,7 +34270,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1169" t="n">
-        <v>4.42414569854736</v>
+        <v>4.42414617538452</v>
       </c>
       <c r="H1169" t="n">
         <v>2741388</v>
@@ -34299,7 +34299,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.3885669708252</v>
+        <v>4.38856744766235</v>
       </c>
       <c r="H1170" t="n">
         <v>1857442</v>
@@ -34328,7 +34328,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1171" t="n">
-        <v>4.37155151367188</v>
+        <v>4.37155199050903</v>
       </c>
       <c r="H1171" t="n">
         <v>2785219</v>
@@ -34386,7 +34386,7 @@
         <v>5.60400009155273</v>
       </c>
       <c r="G1173" t="n">
-        <v>4.33442544937134</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H1173" t="n">
         <v>1090170</v>
@@ -34415,7 +34415,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.26636123657227</v>
+        <v>4.26636171340942</v>
       </c>
       <c r="H1174" t="n">
         <v>1518206</v>
@@ -34531,7 +34531,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.29575300216675</v>
+        <v>4.29575347900391</v>
       </c>
       <c r="H1178" t="n">
         <v>725516</v>
@@ -34560,7 +34560,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G1179" t="n">
-        <v>4.26326847076416</v>
+        <v>4.26326894760132</v>
       </c>
       <c r="H1179" t="n">
         <v>1866419</v>
@@ -34647,7 +34647,7 @@
         <v>5.57800006866455</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.31431579589844</v>
+        <v>4.3143162727356</v>
       </c>
       <c r="H1182" t="n">
         <v>832865</v>
@@ -34676,7 +34676,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.30967473983765</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1183" t="n">
         <v>942466</v>
@@ -34734,7 +34734,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.26636123657227</v>
+        <v>4.26636171340942</v>
       </c>
       <c r="H1185" t="n">
         <v>2720593</v>
@@ -34850,7 +34850,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.35298871994019</v>
+        <v>4.35298824310303</v>
       </c>
       <c r="H1189" t="n">
         <v>1139569</v>
@@ -34879,7 +34879,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.30967473983765</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1190" t="n">
         <v>1530588</v>
@@ -34908,7 +34908,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.31586265563965</v>
+        <v>4.31586360931396</v>
       </c>
       <c r="H1191" t="n">
         <v>1923267</v>
@@ -34937,7 +34937,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.19211053848267</v>
+        <v>4.19211006164551</v>
       </c>
       <c r="H1192" t="n">
         <v>3583053</v>
@@ -34966,7 +34966,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.16890668869019</v>
+        <v>4.16890716552734</v>
       </c>
       <c r="H1193" t="n">
         <v>2467655</v>
@@ -34995,7 +34995,7 @@
         <v>5.41200017929077</v>
       </c>
       <c r="G1194" t="n">
-        <v>4.18592357635498</v>
+        <v>4.18592262268066</v>
       </c>
       <c r="H1194" t="n">
         <v>1940332</v>
@@ -35169,7 +35169,7 @@
         <v>5.71199989318848</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.41795921325684</v>
+        <v>4.41795825958252</v>
       </c>
       <c r="H1200" t="n">
         <v>1137264</v>
@@ -35227,7 +35227,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G1202" t="n">
-        <v>4.43033409118652</v>
+        <v>4.43033361434937</v>
       </c>
       <c r="H1202" t="n">
         <v>865108</v>
@@ -35256,7 +35256,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G1203" t="n">
-        <v>4.39784860610962</v>
+        <v>4.39784908294678</v>
       </c>
       <c r="H1203" t="n">
         <v>679597</v>
@@ -35401,7 +35401,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.46591281890869</v>
+        <v>4.46591329574585</v>
       </c>
       <c r="H1208" t="n">
         <v>912025</v>
@@ -35430,7 +35430,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.49066305160522</v>
+        <v>4.49066352844238</v>
       </c>
       <c r="H1209" t="n">
         <v>1030178</v>
@@ -35459,7 +35459,7 @@
         <v>5.85799980163574</v>
       </c>
       <c r="G1210" t="n">
-        <v>4.53088283538818</v>
+        <v>4.53088235855103</v>
       </c>
       <c r="H1210" t="n">
         <v>896304</v>
@@ -35517,7 +35517,7 @@
         <v>5.94399976730347</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.59739923477173</v>
+        <v>4.59739971160889</v>
       </c>
       <c r="H1212" t="n">
         <v>1352473</v>
@@ -35546,7 +35546,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G1213" t="n">
-        <v>4.59430646896362</v>
+        <v>4.59430551528931</v>
       </c>
       <c r="H1213" t="n">
         <v>1486951</v>
@@ -35575,7 +35575,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.56646156311035</v>
+        <v>4.56646108627319</v>
       </c>
       <c r="H1214" t="n">
         <v>1560619</v>
@@ -35604,7 +35604,7 @@
         <v>5.97599983215332</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.62214994430542</v>
+        <v>4.62214946746826</v>
       </c>
       <c r="H1215" t="n">
         <v>1971571</v>
@@ -35691,7 +35691,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.60204029083252</v>
+        <v>4.60203981399536</v>
       </c>
       <c r="H1218" t="n">
         <v>1107426</v>
@@ -35749,7 +35749,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.37928581237793</v>
+        <v>4.37928676605225</v>
       </c>
       <c r="H1220" t="n">
         <v>2263938</v>
@@ -35807,7 +35807,7 @@
         <v>5.60400009155273</v>
       </c>
       <c r="G1222" t="n">
-        <v>4.33442544937134</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H1222" t="n">
         <v>1114889</v>
@@ -35894,7 +35894,7 @@
         <v>5.68400001525879</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.39630174636841</v>
+        <v>4.39630222320557</v>
       </c>
       <c r="H1225" t="n">
         <v>950072</v>
@@ -35923,7 +35923,7 @@
         <v>5.62400007247925</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.34989547729492</v>
+        <v>4.34989404678345</v>
       </c>
       <c r="H1226" t="n">
         <v>1092880</v>
@@ -36010,7 +36010,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.30039358139038</v>
+        <v>4.30039405822754</v>
       </c>
       <c r="H1229" t="n">
         <v>2431673</v>
@@ -36039,7 +36039,7 @@
         <v>5.55200004577637</v>
       </c>
       <c r="G1230" t="n">
-        <v>4.2942066192627</v>
+        <v>4.29420614242554</v>
       </c>
       <c r="H1230" t="n">
         <v>1372530</v>
@@ -36068,7 +36068,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1231" t="n">
-        <v>4.26945543289185</v>
+        <v>4.269455909729</v>
       </c>
       <c r="H1231" t="n">
         <v>2728071</v>
@@ -36097,7 +36097,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1232" t="n">
-        <v>4.31895637512207</v>
+        <v>4.31895732879639</v>
       </c>
       <c r="H1232" t="n">
         <v>2153425</v>
@@ -36126,7 +36126,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.33133220672607</v>
+        <v>4.33133172988892</v>
       </c>
       <c r="H1233" t="n">
         <v>1241734</v>
@@ -36213,7 +36213,7 @@
         <v>5.67600011825562</v>
       </c>
       <c r="G1236" t="n">
-        <v>4.39011430740356</v>
+        <v>4.39011478424072</v>
       </c>
       <c r="H1236" t="n">
         <v>4396498</v>
@@ -36242,7 +36242,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.35608243942261</v>
+        <v>4.35608196258545</v>
       </c>
       <c r="H1237" t="n">
         <v>2406077</v>
@@ -36329,7 +36329,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.45508432388306</v>
+        <v>4.45508480072021</v>
       </c>
       <c r="H1240" t="n">
         <v>1716303</v>
@@ -36445,7 +36445,7 @@
         <v>5.55200004577637</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.2942066192627</v>
+        <v>4.29420614242554</v>
       </c>
       <c r="H1244" t="n">
         <v>1630612</v>
@@ -36619,7 +36619,7 @@
         <v>5.53399991989136</v>
       </c>
       <c r="G1250" t="n">
-        <v>4.28028392791748</v>
+        <v>4.28028345108032</v>
       </c>
       <c r="H1250" t="n">
         <v>1738466</v>
@@ -36764,7 +36764,7 @@
         <v>5.44199991226196</v>
       </c>
       <c r="G1255" t="n">
-        <v>4.2091269493103</v>
+        <v>4.20912647247314</v>
       </c>
       <c r="H1255" t="n">
         <v>1458684</v>
@@ -36793,7 +36793,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.2230486869812</v>
+        <v>4.22304821014404</v>
       </c>
       <c r="H1256" t="n">
         <v>1755024</v>
@@ -36822,7 +36822,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.2230486869812</v>
+        <v>4.22304821014404</v>
       </c>
       <c r="H1257" t="n">
         <v>1186601</v>
@@ -36909,7 +36909,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.32205009460449</v>
+        <v>4.32205057144165</v>
       </c>
       <c r="H1260" t="n">
         <v>1687840</v>
@@ -36938,7 +36938,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.33133220672607</v>
+        <v>4.33133172988892</v>
       </c>
       <c r="H1261" t="n">
         <v>1051490</v>
@@ -36967,7 +36967,7 @@
         <v>5.60400009155273</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.33442544937134</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H1262" t="n">
         <v>1526278</v>
@@ -36996,7 +36996,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.37155151367188</v>
+        <v>4.37155199050903</v>
       </c>
       <c r="H1263" t="n">
         <v>1329328</v>
@@ -37025,7 +37025,7 @@
         <v>5.62400007247925</v>
       </c>
       <c r="G1264" t="n">
-        <v>4.34989547729492</v>
+        <v>4.34989404678345</v>
       </c>
       <c r="H1264" t="n">
         <v>1336031</v>
@@ -37054,7 +37054,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.27255010604858</v>
+        <v>4.27254962921143</v>
       </c>
       <c r="H1265" t="n">
         <v>2499950</v>
@@ -37083,7 +37083,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1266" t="n">
-        <v>4.24625205993652</v>
+        <v>4.24625253677368</v>
       </c>
       <c r="H1266" t="n">
         <v>2523989</v>
@@ -37170,7 +37170,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G1269" t="n">
-        <v>4.34525394439697</v>
+        <v>4.34525442123413</v>
       </c>
       <c r="H1269" t="n">
         <v>1484679</v>
@@ -37286,7 +37286,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1273" t="n">
-        <v>4.36227035522461</v>
+        <v>4.36226987838745</v>
       </c>
       <c r="H1273" t="n">
         <v>889879</v>
@@ -37344,7 +37344,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.35298871994019</v>
+        <v>4.35298824310303</v>
       </c>
       <c r="H1275" t="n">
         <v>910027</v>
@@ -37373,7 +37373,7 @@
         <v>5.60200023651123</v>
       </c>
       <c r="G1276" t="n">
-        <v>4.33287858963013</v>
+        <v>4.33287906646729</v>
       </c>
       <c r="H1276" t="n">
         <v>765113</v>
@@ -37402,7 +37402,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.33133220672607</v>
+        <v>4.33133172988892</v>
       </c>
       <c r="H1277" t="n">
         <v>1902172</v>
@@ -37489,7 +37489,7 @@
         <v>5.60400009155273</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.33442544937134</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H1280" t="n">
         <v>1912958</v>
@@ -37547,7 +37547,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.35298871994019</v>
+        <v>4.35298824310303</v>
       </c>
       <c r="H1282" t="n">
         <v>1370173</v>
@@ -37576,7 +37576,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1283" t="n">
-        <v>4.33906698226929</v>
+        <v>4.33906650543213</v>
       </c>
       <c r="H1283" t="n">
         <v>1777724</v>
@@ -37750,7 +37750,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.32205009460449</v>
+        <v>4.32205057144165</v>
       </c>
       <c r="H1289" t="n">
         <v>1160885</v>
@@ -37837,7 +37837,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1292" t="n">
-        <v>4.51850748062134</v>
+        <v>4.5185079574585</v>
       </c>
       <c r="H1292" t="n">
         <v>2866024</v>
@@ -37924,7 +37924,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1295" t="n">
-        <v>4.46591281890869</v>
+        <v>4.46591329574585</v>
       </c>
       <c r="H1295" t="n">
         <v>1753198</v>
@@ -38011,7 +38011,7 @@
         <v>5.7480001449585</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.44580268859863</v>
+        <v>4.44580316543579</v>
       </c>
       <c r="H1298" t="n">
         <v>2108694</v>
@@ -38040,7 +38040,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.5014910697937</v>
+        <v>4.50149154663086</v>
       </c>
       <c r="H1299" t="n">
         <v>1594043</v>
@@ -38272,7 +38272,7 @@
         <v>6.0019998550415</v>
       </c>
       <c r="G1307" t="n">
-        <v>4.64225912094116</v>
+        <v>4.64225959777832</v>
       </c>
       <c r="H1307" t="n">
         <v>935718</v>
@@ -38330,7 +38330,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.68093252182007</v>
+        <v>4.68093204498291</v>
       </c>
       <c r="H1309" t="n">
         <v>1125437</v>
@@ -38359,7 +38359,7 @@
         <v>6.08799982070923</v>
       </c>
       <c r="G1310" t="n">
-        <v>4.70877647399902</v>
+        <v>4.70877599716187</v>
       </c>
       <c r="H1310" t="n">
         <v>996941</v>
@@ -38388,7 +38388,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G1311" t="n">
-        <v>4.65154075622559</v>
+        <v>4.65154123306274</v>
       </c>
       <c r="H1311" t="n">
         <v>1323070</v>
@@ -38446,7 +38446,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1313" t="n">
-        <v>4.51850748062134</v>
+        <v>4.5185079574585</v>
       </c>
       <c r="H1313" t="n">
         <v>1666783</v>
@@ -38475,7 +38475,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1314" t="n">
-        <v>4.46281909942627</v>
+        <v>4.46281862258911</v>
       </c>
       <c r="H1314" t="n">
         <v>1341448</v>
@@ -38504,7 +38504,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1315" t="n">
-        <v>4.44270896911621</v>
+        <v>4.44270944595337</v>
       </c>
       <c r="H1315" t="n">
         <v>962142</v>
@@ -38591,7 +38591,7 @@
         <v>5.87200021743774</v>
       </c>
       <c r="G1318" t="n">
-        <v>4.54171133041382</v>
+        <v>4.54171085357666</v>
       </c>
       <c r="H1318" t="n">
         <v>1140255</v>
@@ -38649,7 +38649,7 @@
         <v>5.89200019836426</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.55718040466309</v>
+        <v>4.55717992782593</v>
       </c>
       <c r="H1320" t="n">
         <v>517814</v>
@@ -38678,7 +38678,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.53861713409424</v>
+        <v>4.53861665725708</v>
       </c>
       <c r="H1321" t="n">
         <v>1062972</v>
@@ -38707,7 +38707,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.53861713409424</v>
+        <v>4.53861665725708</v>
       </c>
       <c r="H1322" t="n">
         <v>890715</v>
@@ -38736,7 +38736,7 @@
         <v>5.93800020217896</v>
       </c>
       <c r="G1323" t="n">
-        <v>4.59275960922241</v>
+        <v>4.59275913238525</v>
       </c>
       <c r="H1323" t="n">
         <v>932007</v>
@@ -38794,7 +38794,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1325" t="n">
-        <v>4.45508432388306</v>
+        <v>4.45508480072021</v>
       </c>
       <c r="H1325" t="n">
         <v>1934280</v>
@@ -38852,7 +38852,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G1327" t="n">
-        <v>4.49066305160522</v>
+        <v>4.49066352844238</v>
       </c>
       <c r="H1327" t="n">
         <v>1114675</v>
@@ -38881,7 +38881,7 @@
         <v>5.93599987030029</v>
       </c>
       <c r="G1328" t="n">
-        <v>4.59121179580688</v>
+        <v>4.59121227264404</v>
       </c>
       <c r="H1328" t="n">
         <v>1235229</v>
@@ -38939,7 +38939,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>4.53861713409424</v>
+        <v>4.53861665725708</v>
       </c>
       <c r="H1330" t="n">
         <v>863041</v>
@@ -38968,7 +38968,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.56646156311035</v>
+        <v>4.56646108627319</v>
       </c>
       <c r="H1331" t="n">
         <v>1234389</v>
@@ -39055,7 +39055,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G1334" t="n">
-        <v>4.39784860610962</v>
+        <v>4.39784908294678</v>
       </c>
       <c r="H1334" t="n">
         <v>1292083</v>
@@ -39142,7 +39142,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G1337" t="n">
-        <v>4.38237953186035</v>
+        <v>4.38238000869751</v>
       </c>
       <c r="H1337" t="n">
         <v>1667829</v>
@@ -39229,7 +39229,7 @@
         <v>5.61800003051758</v>
       </c>
       <c r="G1340" t="n">
-        <v>4.34525394439697</v>
+        <v>4.34525442123413</v>
       </c>
       <c r="H1340" t="n">
         <v>1956136</v>
@@ -39258,7 +39258,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.3885669708252</v>
+        <v>4.38856744766235</v>
       </c>
       <c r="H1341" t="n">
         <v>1355316</v>
@@ -39403,7 +39403,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.26636123657227</v>
+        <v>4.26636171340942</v>
       </c>
       <c r="H1346" t="n">
         <v>1668922</v>
@@ -39490,7 +39490,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.45508432388306</v>
+        <v>4.45508480072021</v>
       </c>
       <c r="H1349" t="n">
         <v>2859179</v>
@@ -39664,7 +39664,7 @@
         <v>5.34800004959106</v>
       </c>
       <c r="G1355" t="n">
-        <v>4.1364221572876</v>
+        <v>4.13642168045044</v>
       </c>
       <c r="H1355" t="n">
         <v>2866264</v>
@@ -39693,7 +39693,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1356" t="n">
-        <v>4.16890668869019</v>
+        <v>4.16890716552734</v>
       </c>
       <c r="H1356" t="n">
         <v>2103223</v>
@@ -39722,7 +39722,7 @@
         <v>5.64200019836426</v>
       </c>
       <c r="G1357" t="n">
-        <v>4.36381721496582</v>
+        <v>4.36381673812866</v>
       </c>
       <c r="H1357" t="n">
         <v>2566365</v>
@@ -39867,7 +39867,7 @@
         <v>5.46799993515015</v>
       </c>
       <c r="G1362" t="n">
-        <v>4.22923612594604</v>
+        <v>4.2292366027832</v>
       </c>
       <c r="H1362" t="n">
         <v>2578413</v>
@@ -39954,7 +39954,7 @@
         <v>5.60400009155273</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.33442544937134</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H1365" t="n">
         <v>1104569</v>
@@ -39983,7 +39983,7 @@
         <v>5.64200019836426</v>
       </c>
       <c r="G1366" t="n">
-        <v>4.36381721496582</v>
+        <v>4.36381673812866</v>
       </c>
       <c r="H1366" t="n">
         <v>1344597</v>
@@ -40070,7 +40070,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.38237953186035</v>
+        <v>4.38238000869751</v>
       </c>
       <c r="H1369" t="n">
         <v>1134945</v>
@@ -40244,7 +40244,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.45508432388306</v>
+        <v>4.45508480072021</v>
       </c>
       <c r="H1375" t="n">
         <v>1102525</v>
@@ -40360,7 +40360,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.68711948394775</v>
+        <v>4.68711996078491</v>
       </c>
       <c r="H1379" t="n">
         <v>1520621</v>
@@ -40447,7 +40447,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G1382" t="n">
-        <v>4.70258903503418</v>
+        <v>4.70258855819702</v>
       </c>
       <c r="H1382" t="n">
         <v>1735024</v>
@@ -40476,7 +40476,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.7915358543396</v>
+        <v>4.79153633117676</v>
       </c>
       <c r="H1383" t="n">
         <v>1874085</v>
@@ -40505,7 +40505,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>4.83020877838135</v>
+        <v>4.83020830154419</v>
       </c>
       <c r="H1384" t="n">
         <v>3183045</v>
@@ -40534,7 +40534,7 @@
         <v>6.375</v>
       </c>
       <c r="G1385" t="n">
-        <v>4.93075704574585</v>
+        <v>4.93075752258301</v>
       </c>
       <c r="H1385" t="n">
         <v>2260746</v>
@@ -40679,7 +40679,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.77993440628052</v>
+        <v>4.77993392944336</v>
       </c>
       <c r="H1390" t="n">
         <v>1169448</v>
@@ -40708,7 +40708,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.803138256073</v>
+        <v>4.80313777923584</v>
       </c>
       <c r="H1391" t="n">
         <v>1131913</v>
@@ -40737,7 +40737,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.77993440628052</v>
+        <v>4.77993392944336</v>
       </c>
       <c r="H1392" t="n">
         <v>855211</v>
@@ -40795,7 +40795,7 @@
         <v>6.20499992370605</v>
       </c>
       <c r="G1394" t="n">
-        <v>4.79927015304565</v>
+        <v>4.79927062988281</v>
       </c>
       <c r="H1394" t="n">
         <v>1304575</v>
@@ -40969,7 +40969,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.83020877838135</v>
+        <v>4.83020830154419</v>
       </c>
       <c r="H1400" t="n">
         <v>1446658</v>
@@ -40998,7 +40998,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G1401" t="n">
-        <v>4.71032381057739</v>
+        <v>4.71032333374023</v>
       </c>
       <c r="H1401" t="n">
         <v>1308144</v>
@@ -41027,7 +41027,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.77993440628052</v>
+        <v>4.77993392944336</v>
       </c>
       <c r="H1402" t="n">
         <v>1402848</v>
@@ -41143,7 +41143,7 @@
         <v>6.25500011444092</v>
       </c>
       <c r="G1406" t="n">
-        <v>4.83794355392456</v>
+        <v>4.8379430770874</v>
       </c>
       <c r="H1406" t="n">
         <v>977411</v>
@@ -41172,7 +41172,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.94235944747925</v>
+        <v>4.94235897064209</v>
       </c>
       <c r="H1407" t="n">
         <v>1771579</v>
@@ -41259,7 +41259,7 @@
         <v>6.10500001907349</v>
       </c>
       <c r="G1410" t="n">
-        <v>4.93590259552002</v>
+        <v>4.93590307235718</v>
       </c>
       <c r="H1410" t="n">
         <v>945057</v>
@@ -41375,7 +41375,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1414" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909557342529</v>
       </c>
       <c r="H1414" t="n">
         <v>1962697</v>
@@ -41404,7 +41404,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>4.8146276473999</v>
+        <v>4.81462717056274</v>
       </c>
       <c r="H1415" t="n">
         <v>1272371</v>
@@ -41491,7 +41491,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1418" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909557342529</v>
       </c>
       <c r="H1418" t="n">
         <v>620812</v>
@@ -41665,7 +41665,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1424" t="n">
-        <v>4.35378170013428</v>
+        <v>4.35378122329712</v>
       </c>
       <c r="H1424" t="n">
         <v>1270670</v>
@@ -41723,7 +41723,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.34165382385254</v>
+        <v>4.34165334701538</v>
       </c>
       <c r="H1426" t="n">
         <v>2221165</v>
@@ -41752,7 +41752,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>4.51548147201538</v>
+        <v>4.51548194885254</v>
       </c>
       <c r="H1427" t="n">
         <v>3316711</v>
@@ -41810,7 +41810,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1429" t="n">
-        <v>4.31739902496338</v>
+        <v>4.31739854812622</v>
       </c>
       <c r="H1429" t="n">
         <v>1611484</v>
@@ -41897,7 +41897,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1432" t="n">
-        <v>4.49526882171631</v>
+        <v>4.49526929855347</v>
       </c>
       <c r="H1432" t="n">
         <v>3261356</v>
@@ -41926,7 +41926,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.43463230133057</v>
+        <v>4.43463182449341</v>
       </c>
       <c r="H1433" t="n">
         <v>1570844</v>
@@ -41984,7 +41984,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1435" t="n">
-        <v>4.53569459915161</v>
+        <v>4.53569412231445</v>
       </c>
       <c r="H1435" t="n">
         <v>1289642</v>
@@ -42013,7 +42013,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.49122667312622</v>
+        <v>4.49122619628906</v>
       </c>
       <c r="H1436" t="n">
         <v>2205200</v>
@@ -42042,7 +42042,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1437" t="n">
-        <v>4.52760934829712</v>
+        <v>4.52760887145996</v>
       </c>
       <c r="H1437" t="n">
         <v>1165445</v>
@@ -42071,7 +42071,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1438" t="n">
-        <v>4.52760934829712</v>
+        <v>4.52760887145996</v>
       </c>
       <c r="H1438" t="n">
         <v>713087</v>
@@ -42129,7 +42129,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1440" t="n">
-        <v>4.42250394821167</v>
+        <v>4.42250347137451</v>
       </c>
       <c r="H1440" t="n">
         <v>1861474</v>
@@ -42158,7 +42158,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1441" t="n">
-        <v>4.43463230133057</v>
+        <v>4.43463182449341</v>
       </c>
       <c r="H1441" t="n">
         <v>1049671</v>
@@ -42216,7 +42216,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41037654876709</v>
+        <v>4.41037607192993</v>
       </c>
       <c r="H1443" t="n">
         <v>607592</v>
@@ -42245,7 +42245,7 @@
         <v>5.5</v>
       </c>
       <c r="G1444" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1444" t="n">
         <v>813805</v>
@@ -42274,7 +42274,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.41037654876709</v>
+        <v>4.41037607192993</v>
       </c>
       <c r="H1445" t="n">
         <v>1041891</v>
@@ -42419,7 +42419,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.2648458480835</v>
+        <v>4.26484632492065</v>
       </c>
       <c r="H1450" t="n">
         <v>1355393</v>
@@ -42448,7 +42448,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G1451" t="n">
-        <v>4.20016574859619</v>
+        <v>4.20016622543335</v>
       </c>
       <c r="H1451" t="n">
         <v>1487711</v>
@@ -42535,7 +42535,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.39824914932251</v>
+        <v>4.39824867248535</v>
       </c>
       <c r="H1454" t="n">
         <v>1670735</v>
@@ -42593,7 +42593,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.47101402282715</v>
+        <v>4.47101449966431</v>
       </c>
       <c r="H1456" t="n">
         <v>742411</v>
@@ -42622,7 +42622,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1457" t="n">
-        <v>4.51143884658813</v>
+        <v>4.51143932342529</v>
       </c>
       <c r="H1457" t="n">
         <v>1442214</v>
@@ -42651,7 +42651,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.43463230133057</v>
+        <v>4.43463182449341</v>
       </c>
       <c r="H1458" t="n">
         <v>685505</v>
@@ -42680,7 +42680,7 @@
         <v>5.5</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1459" t="n">
         <v>477914</v>
@@ -42767,7 +42767,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1462" t="n">
-        <v>4.42250394821167</v>
+        <v>4.42250347137451</v>
       </c>
       <c r="H1462" t="n">
         <v>620839</v>
@@ -42796,7 +42796,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1463" t="n">
-        <v>4.45888662338257</v>
+        <v>4.45888614654541</v>
       </c>
       <c r="H1463" t="n">
         <v>804156</v>
@@ -42854,7 +42854,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G1465" t="n">
-        <v>4.46697187423706</v>
+        <v>4.4669713973999</v>
       </c>
       <c r="H1465" t="n">
         <v>582752</v>
@@ -42883,7 +42883,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1466" t="n">
-        <v>4.43867349624634</v>
+        <v>4.4386739730835</v>
       </c>
       <c r="H1466" t="n">
         <v>746162</v>
@@ -42912,7 +42912,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1467" t="n">
-        <v>4.43463230133057</v>
+        <v>4.43463182449341</v>
       </c>
       <c r="H1467" t="n">
         <v>766608</v>
@@ -42970,7 +42970,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1469" t="n">
-        <v>4.57611894607544</v>
+        <v>4.5761194229126</v>
       </c>
       <c r="H1469" t="n">
         <v>984917</v>
@@ -42999,7 +42999,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.59633207321167</v>
+        <v>4.59633159637451</v>
       </c>
       <c r="H1470" t="n">
         <v>537994</v>
@@ -43057,7 +43057,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1472" t="n">
-        <v>4.56803464889526</v>
+        <v>4.56803417205811</v>
       </c>
       <c r="H1472" t="n">
         <v>1539554</v>
@@ -43115,7 +43115,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.45888662338257</v>
+        <v>4.45888614654541</v>
       </c>
       <c r="H1474" t="n">
         <v>840017</v>
@@ -43144,7 +43144,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1475" t="n">
-        <v>4.46292877197266</v>
+        <v>4.46292924880981</v>
       </c>
       <c r="H1475" t="n">
         <v>416843</v>
@@ -43173,7 +43173,7 @@
         <v>5.375</v>
       </c>
       <c r="G1476" t="n">
-        <v>4.34569597244263</v>
+        <v>4.34569644927979</v>
       </c>
       <c r="H1476" t="n">
         <v>993472</v>
@@ -43260,7 +43260,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G1479" t="n">
-        <v>4.15165567398071</v>
+        <v>4.15165662765503</v>
       </c>
       <c r="H1479" t="n">
         <v>1494755</v>
@@ -43347,7 +43347,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G1482" t="n">
-        <v>4.15165567398071</v>
+        <v>4.15165662765503</v>
       </c>
       <c r="H1482" t="n">
         <v>596442</v>
@@ -43434,7 +43434,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1485" t="n">
-        <v>4.07484817504883</v>
+        <v>4.07484865188599</v>
       </c>
       <c r="H1485" t="n">
         <v>1262652</v>
@@ -43492,7 +43492,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.22442054748535</v>
+        <v>4.22442102432251</v>
       </c>
       <c r="H1487" t="n">
         <v>1158444</v>
@@ -43579,7 +43579,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1490" t="n">
-        <v>4.17186880111694</v>
+        <v>4.17186784744263</v>
       </c>
       <c r="H1490" t="n">
         <v>1375840</v>
@@ -43608,7 +43608,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1491" t="n">
-        <v>4.13548612594604</v>
+        <v>4.13548564910889</v>
       </c>
       <c r="H1491" t="n">
         <v>2769308</v>
@@ -43637,7 +43637,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1492" t="n">
-        <v>4.17591094970703</v>
+        <v>4.17591142654419</v>
       </c>
       <c r="H1492" t="n">
         <v>1409717</v>
@@ -43695,7 +43695,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1494" t="n">
-        <v>4.17995405197144</v>
+        <v>4.17995357513428</v>
       </c>
       <c r="H1494" t="n">
         <v>1163458</v>
@@ -43811,7 +43811,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.96650886535645</v>
+        <v>3.96650862693787</v>
       </c>
       <c r="H1498" t="n">
         <v>3821543</v>
@@ -43840,7 +43840,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.89859461784363</v>
+        <v>3.89859485626221</v>
       </c>
       <c r="H1499" t="n">
         <v>1854115</v>
@@ -43898,7 +43898,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.86140418052673</v>
+        <v>3.86140370368958</v>
       </c>
       <c r="H1501" t="n">
         <v>1461342</v>
@@ -44043,7 +44043,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1506" t="n">
-        <v>3.86463785171509</v>
+        <v>3.86463809013367</v>
       </c>
       <c r="H1506" t="n">
         <v>823047</v>
@@ -44072,7 +44072,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G1507" t="n">
-        <v>3.85655307769775</v>
+        <v>3.85655283927917</v>
       </c>
       <c r="H1507" t="n">
         <v>873029</v>
@@ -44130,7 +44130,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G1509" t="n">
-        <v>3.72395849227905</v>
+        <v>3.72395873069763</v>
       </c>
       <c r="H1509" t="n">
         <v>2042948</v>
@@ -44159,7 +44159,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68353366851807</v>
+        <v>3.68353319168091</v>
       </c>
       <c r="H1510" t="n">
         <v>2103298</v>
@@ -44188,7 +44188,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.80157494544983</v>
+        <v>3.80157446861267</v>
       </c>
       <c r="H1511" t="n">
         <v>1571045</v>
@@ -44246,7 +44246,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.8678719997406</v>
+        <v>3.86787176132202</v>
       </c>
       <c r="H1513" t="n">
         <v>1307537</v>
@@ -44275,7 +44275,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.86463785171509</v>
+        <v>3.86463809013367</v>
       </c>
       <c r="H1514" t="n">
         <v>875290</v>
@@ -44304,7 +44304,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.91961622238159</v>
+        <v>3.91961598396301</v>
       </c>
       <c r="H1515" t="n">
         <v>1359512</v>
@@ -44333,7 +44333,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.8436164855957</v>
+        <v>3.84361743927002</v>
       </c>
       <c r="H1516" t="n">
         <v>1206345</v>
@@ -44391,7 +44391,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1518" t="n">
-        <v>4.07484817504883</v>
+        <v>4.07484865188599</v>
       </c>
       <c r="H1518" t="n">
         <v>1113680</v>
@@ -44420,7 +44420,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1519" t="n">
-        <v>4.08293294906616</v>
+        <v>4.08293342590332</v>
       </c>
       <c r="H1519" t="n">
         <v>1247281</v>
@@ -44449,7 +44449,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1520" t="n">
-        <v>4.30122852325439</v>
+        <v>4.30122900009155</v>
       </c>
       <c r="H1520" t="n">
         <v>1917323</v>
@@ -44536,7 +44536,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1523" t="n">
-        <v>4.1961236000061</v>
+        <v>4.19612312316895</v>
       </c>
       <c r="H1523" t="n">
         <v>844298</v>
@@ -44565,7 +44565,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.2648458480835</v>
+        <v>4.26484632492065</v>
       </c>
       <c r="H1524" t="n">
         <v>1623441</v>
@@ -44623,7 +44623,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1526" t="n">
-        <v>4.30122852325439</v>
+        <v>4.30122900009155</v>
       </c>
       <c r="H1526" t="n">
         <v>1854425</v>
@@ -44681,7 +44681,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1528" t="n">
-        <v>4.31739902496338</v>
+        <v>4.31739854812622</v>
       </c>
       <c r="H1528" t="n">
         <v>696576</v>
@@ -44710,7 +44710,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G1529" t="n">
-        <v>4.36995124816895</v>
+        <v>4.3699517250061</v>
       </c>
       <c r="H1529" t="n">
         <v>1003519</v>
@@ -44739,7 +44739,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1530" t="n">
-        <v>4.49122667312622</v>
+        <v>4.49122619628906</v>
       </c>
       <c r="H1530" t="n">
         <v>1546905</v>
@@ -44826,7 +44826,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1533" t="n">
-        <v>4.43463230133057</v>
+        <v>4.43463182449341</v>
       </c>
       <c r="H1533" t="n">
         <v>1031900</v>
@@ -44855,7 +44855,7 @@
         <v>5.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1534" t="n">
         <v>921443</v>
@@ -44942,7 +44942,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1537" t="n">
-        <v>4.51143884658813</v>
+        <v>4.51143932342529</v>
       </c>
       <c r="H1537" t="n">
         <v>813948</v>
@@ -44971,7 +44971,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.52760934829712</v>
+        <v>4.52760887145996</v>
       </c>
       <c r="H1538" t="n">
         <v>645027</v>
@@ -45029,7 +45029,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.59633207321167</v>
+        <v>4.59633159637451</v>
       </c>
       <c r="H1540" t="n">
         <v>615561</v>
@@ -45058,7 +45058,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G1541" t="n">
-        <v>4.60441732406616</v>
+        <v>4.60441637039185</v>
       </c>
       <c r="H1541" t="n">
         <v>601240</v>
@@ -45116,7 +45116,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>4.52760934829712</v>
+        <v>4.52760887145996</v>
       </c>
       <c r="H1543" t="n">
         <v>850493</v>
@@ -45290,7 +45290,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G1549" t="n">
-        <v>4.56399154663086</v>
+        <v>4.56399202346802</v>
       </c>
       <c r="H1549" t="n">
         <v>803941</v>
@@ -45319,7 +45319,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1550" t="n">
-        <v>4.51143884658813</v>
+        <v>4.51143932342529</v>
       </c>
       <c r="H1550" t="n">
         <v>923873</v>
@@ -45406,7 +45406,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1553" t="n">
-        <v>4.54377937316895</v>
+        <v>4.54377889633179</v>
       </c>
       <c r="H1553" t="n">
         <v>1267082</v>
@@ -45522,7 +45522,7 @@
         <v>5.375</v>
       </c>
       <c r="G1557" t="n">
-        <v>4.34569597244263</v>
+        <v>4.34569644927979</v>
       </c>
       <c r="H1557" t="n">
         <v>961032</v>
@@ -45580,7 +45580,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1559" t="n">
-        <v>4.35782384872437</v>
+        <v>4.35782432556152</v>
       </c>
       <c r="H1559" t="n">
         <v>1131431</v>
@@ -45667,7 +45667,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G1562" t="n">
-        <v>4.28910112380981</v>
+        <v>4.28910160064697</v>
       </c>
       <c r="H1562" t="n">
         <v>1496786</v>
@@ -45696,7 +45696,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G1563" t="n">
-        <v>4.24059152603149</v>
+        <v>4.24059057235718</v>
       </c>
       <c r="H1563" t="n">
         <v>685775</v>
@@ -45754,7 +45754,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1565" t="n">
-        <v>4.1961236000061</v>
+        <v>4.19612312316895</v>
       </c>
       <c r="H1565" t="n">
         <v>1024402</v>
@@ -45841,7 +45841,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1568" t="n">
-        <v>4.33356857299805</v>
+        <v>4.33356904983521</v>
       </c>
       <c r="H1568" t="n">
         <v>2077805</v>
@@ -45957,7 +45957,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1572" t="n">
-        <v>4.35378170013428</v>
+        <v>4.35378122329712</v>
       </c>
       <c r="H1572" t="n">
         <v>732182</v>
@@ -45986,7 +45986,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.41037654876709</v>
+        <v>4.41037607192993</v>
       </c>
       <c r="H1573" t="n">
         <v>912828</v>
@@ -46073,7 +46073,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1576" t="n">
-        <v>4.39824914932251</v>
+        <v>4.39824867248535</v>
       </c>
       <c r="H1576" t="n">
         <v>679678</v>
@@ -46189,7 +46189,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G1580" t="n">
-        <v>4.32144165039062</v>
+        <v>4.32144117355347</v>
       </c>
       <c r="H1580" t="n">
         <v>925140</v>
@@ -46276,7 +46276,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>4.49526882171631</v>
+        <v>4.49526929855347</v>
       </c>
       <c r="H1583" t="n">
         <v>969811</v>
@@ -46334,7 +46334,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1585" t="n">
-        <v>4.43867349624634</v>
+        <v>4.4386739730835</v>
       </c>
       <c r="H1585" t="n">
         <v>849158</v>
@@ -46421,7 +46421,7 @@
         <v>5.375</v>
       </c>
       <c r="G1588" t="n">
-        <v>4.34569597244263</v>
+        <v>4.34569644927979</v>
       </c>
       <c r="H1588" t="n">
         <v>1071353</v>
@@ -46450,7 +46450,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G1589" t="n">
-        <v>4.46697187423706</v>
+        <v>4.4669713973999</v>
       </c>
       <c r="H1589" t="n">
         <v>1216816</v>
@@ -46508,7 +46508,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1591" t="n">
-        <v>4.49526882171631</v>
+        <v>4.49526929855347</v>
       </c>
       <c r="H1591" t="n">
         <v>1284240</v>
@@ -46566,7 +46566,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.56803464889526</v>
+        <v>4.56803417205811</v>
       </c>
       <c r="H1593" t="n">
         <v>842156</v>
@@ -46595,7 +46595,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G1594" t="n">
-        <v>4.58016157150269</v>
+        <v>4.58016204833984</v>
       </c>
       <c r="H1594" t="n">
         <v>653054</v>
@@ -46624,7 +46624,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1595" t="n">
-        <v>4.52760934829712</v>
+        <v>4.52760887145996</v>
       </c>
       <c r="H1595" t="n">
         <v>834135</v>
@@ -46711,7 +46711,7 @@
         <v>5.5</v>
       </c>
       <c r="G1598" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1598" t="n">
         <v>3511367</v>
@@ -46740,7 +46740,7 @@
         <v>5.5</v>
       </c>
       <c r="G1599" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1599" t="n">
         <v>1445698</v>
@@ -46769,7 +46769,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G1600" t="n">
-        <v>4.39420604705811</v>
+        <v>4.39420652389526</v>
       </c>
       <c r="H1600" t="n">
         <v>1557745</v>
@@ -46827,7 +46827,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>4.41037654876709</v>
+        <v>4.41037607192993</v>
       </c>
       <c r="H1602" t="n">
         <v>929946</v>
@@ -46856,7 +46856,7 @@
         <v>5.375</v>
       </c>
       <c r="G1603" t="n">
-        <v>4.34569597244263</v>
+        <v>4.34569644927979</v>
       </c>
       <c r="H1603" t="n">
         <v>1792699</v>
@@ -46943,7 +46943,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G1606" t="n">
-        <v>4.42654657363892</v>
+        <v>4.42654705047607</v>
       </c>
       <c r="H1606" t="n">
         <v>1104679</v>
@@ -46972,7 +46972,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1607" t="n">
-        <v>4.35378170013428</v>
+        <v>4.35378122329712</v>
       </c>
       <c r="H1607" t="n">
         <v>1646514</v>
@@ -47059,7 +47059,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G1610" t="n">
-        <v>4.2931432723999</v>
+        <v>4.29314374923706</v>
       </c>
       <c r="H1610" t="n">
         <v>928006</v>
@@ -47117,7 +47117,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1612" t="n">
-        <v>4.25271892547607</v>
+        <v>4.25271844863892</v>
       </c>
       <c r="H1612" t="n">
         <v>1159127</v>
@@ -47262,7 +47262,7 @@
         <v>5.375</v>
       </c>
       <c r="G1617" t="n">
-        <v>4.34569597244263</v>
+        <v>4.34569644927979</v>
       </c>
       <c r="H1617" t="n">
         <v>1794082</v>
@@ -47320,7 +47320,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1619" t="n">
-        <v>4.51143884658813</v>
+        <v>4.51143932342529</v>
       </c>
       <c r="H1619" t="n">
         <v>3669259</v>
@@ -47349,7 +47349,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.35378170013428</v>
+        <v>4.35378122329712</v>
       </c>
       <c r="H1620" t="n">
         <v>6654047</v>
@@ -47436,7 +47436,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.45888662338257</v>
+        <v>4.45888614654541</v>
       </c>
       <c r="H1623" t="n">
         <v>2049447</v>
@@ -47465,7 +47465,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1624" t="n">
-        <v>4.42250394821167</v>
+        <v>4.42250347137451</v>
       </c>
       <c r="H1624" t="n">
         <v>1754976</v>
@@ -47552,7 +47552,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.49122667312622</v>
+        <v>4.49122619628906</v>
       </c>
       <c r="H1627" t="n">
         <v>973647</v>
@@ -47697,7 +47697,7 @@
         <v>5.69500017166138</v>
       </c>
       <c r="G1632" t="n">
-        <v>4.60441732406616</v>
+        <v>4.60441637039185</v>
       </c>
       <c r="H1632" t="n">
         <v>1007673</v>
@@ -47987,7 +47987,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1642" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909557342529</v>
       </c>
       <c r="H1642" t="n">
         <v>1008256</v>
@@ -48045,7 +48045,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G1644" t="n">
-        <v>4.79845762252808</v>
+        <v>4.79845714569092</v>
       </c>
       <c r="H1644" t="n">
         <v>2019385</v>
@@ -48074,7 +48074,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G1645" t="n">
-        <v>4.77420234680176</v>
+        <v>4.7742018699646</v>
       </c>
       <c r="H1645" t="n">
         <v>2097226</v>
@@ -48103,7 +48103,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G1646" t="n">
-        <v>4.70952177047729</v>
+        <v>4.70952224731445</v>
       </c>
       <c r="H1646" t="n">
         <v>2045186</v>
@@ -48132,7 +48132,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1647" t="n">
-        <v>4.74590492248535</v>
+        <v>4.74590444564819</v>
       </c>
       <c r="H1647" t="n">
         <v>3334279</v>
@@ -48509,7 +48509,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G1660" t="n">
-        <v>4.75803184509277</v>
+        <v>4.75803232192993</v>
       </c>
       <c r="H1660" t="n">
         <v>1836881</v>
@@ -48567,7 +48567,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1662" t="n">
-        <v>4.68122482299805</v>
+        <v>4.68122434616089</v>
       </c>
       <c r="H1662" t="n">
         <v>2378742</v>
@@ -48596,7 +48596,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1663" t="n">
-        <v>4.61957883834839</v>
+        <v>4.61957836151123</v>
       </c>
       <c r="H1663" t="n">
         <v>2140583</v>
@@ -48654,7 +48654,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G1665" t="n">
-        <v>4.55565500259399</v>
+        <v>4.55565452575684</v>
       </c>
       <c r="H1665" t="n">
         <v>2029497</v>
@@ -48683,7 +48683,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G1666" t="n">
-        <v>4.47042274475098</v>
+        <v>4.47042226791382</v>
       </c>
       <c r="H1666" t="n">
         <v>2102275</v>
@@ -48857,7 +48857,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1672" t="n">
-        <v>4.70054912567139</v>
+        <v>4.70054864883423</v>
       </c>
       <c r="H1672" t="n">
         <v>2050602</v>
@@ -48886,7 +48886,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1673" t="n">
-        <v>4.70054912567139</v>
+        <v>4.70054864883423</v>
       </c>
       <c r="H1673" t="n">
         <v>1541904</v>
@@ -49002,7 +49002,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1677" t="n">
-        <v>4.7559494972229</v>
+        <v>4.75594997406006</v>
       </c>
       <c r="H1677" t="n">
         <v>1397081</v>
@@ -49118,7 +49118,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1681" t="n">
-        <v>4.66219472885132</v>
+        <v>4.66219425201416</v>
       </c>
       <c r="H1681" t="n">
         <v>3252351</v>
@@ -49205,7 +49205,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G1684" t="n">
-        <v>4.66645622253418</v>
+        <v>4.66645669937134</v>
       </c>
       <c r="H1684" t="n">
         <v>856641</v>
@@ -49263,7 +49263,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1686" t="n">
-        <v>4.55139350891113</v>
+        <v>4.55139303207397</v>
       </c>
       <c r="H1686" t="n">
         <v>1402780</v>
@@ -49495,7 +49495,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1694" t="n">
-        <v>4.61957883834839</v>
+        <v>4.61957836151123</v>
       </c>
       <c r="H1694" t="n">
         <v>790019</v>
@@ -49524,7 +49524,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1695" t="n">
-        <v>4.55139350891113</v>
+        <v>4.55139303207397</v>
       </c>
       <c r="H1695" t="n">
         <v>1686646</v>
@@ -49553,7 +49553,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1696" t="n">
-        <v>4.44059133529663</v>
+        <v>4.44059181213379</v>
       </c>
       <c r="H1696" t="n">
         <v>2132887</v>
@@ -49582,7 +49582,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1697" t="n">
-        <v>4.44059133529663</v>
+        <v>4.44059181213379</v>
       </c>
       <c r="H1697" t="n">
         <v>1099288</v>
@@ -49727,7 +49727,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1702" t="n">
-        <v>4.49599170684814</v>
+        <v>4.4959921836853</v>
       </c>
       <c r="H1702" t="n">
         <v>1476280</v>
@@ -49756,7 +49756,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1703" t="n">
-        <v>4.49599170684814</v>
+        <v>4.4959921836853</v>
       </c>
       <c r="H1703" t="n">
         <v>1137567</v>
@@ -49814,7 +49814,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1705" t="n">
-        <v>4.54287004470825</v>
+        <v>4.54286956787109</v>
       </c>
       <c r="H1705" t="n">
         <v>1657478</v>
@@ -49843,7 +49843,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1706" t="n">
-        <v>4.5599160194397</v>
+        <v>4.55991649627686</v>
       </c>
       <c r="H1706" t="n">
         <v>1398766</v>
@@ -49872,7 +49872,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1707" t="n">
-        <v>4.56843900680542</v>
+        <v>4.56843948364258</v>
       </c>
       <c r="H1707" t="n">
         <v>1457718</v>
@@ -50046,7 +50046,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1713" t="n">
-        <v>4.56843900680542</v>
+        <v>4.56843948364258</v>
       </c>
       <c r="H1713" t="n">
         <v>1988065</v>
@@ -50162,7 +50162,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1717" t="n">
-        <v>4.35962104797363</v>
+        <v>4.35962057113647</v>
       </c>
       <c r="H1717" t="n">
         <v>1685606</v>
@@ -50220,7 +50220,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1719" t="n">
-        <v>4.3979754447937</v>
+        <v>4.39797496795654</v>
       </c>
       <c r="H1719" t="n">
         <v>1927099</v>
@@ -50336,7 +50336,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G1723" t="n">
-        <v>4.41928339004517</v>
+        <v>4.41928291320801</v>
       </c>
       <c r="H1723" t="n">
         <v>762554</v>
@@ -50365,7 +50365,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1724" t="n">
-        <v>4.35535955429077</v>
+        <v>4.35535907745361</v>
       </c>
       <c r="H1724" t="n">
         <v>1584988</v>
@@ -50452,7 +50452,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1727" t="n">
-        <v>4.3042197227478</v>
+        <v>4.30422019958496</v>
       </c>
       <c r="H1727" t="n">
         <v>1350694</v>
@@ -50510,7 +50510,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1729" t="n">
-        <v>4.35962104797363</v>
+        <v>4.35962057113647</v>
       </c>
       <c r="H1729" t="n">
         <v>1750702</v>
@@ -50568,7 +50568,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1731" t="n">
-        <v>4.44059133529663</v>
+        <v>4.44059181213379</v>
       </c>
       <c r="H1731" t="n">
         <v>837532</v>
@@ -50916,7 +50916,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1743" t="n">
-        <v>4.54287004470825</v>
+        <v>4.54286956787109</v>
       </c>
       <c r="H1743" t="n">
         <v>1447614</v>
@@ -50945,7 +50945,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G1744" t="n">
-        <v>4.47042274475098</v>
+        <v>4.47042226791382</v>
       </c>
       <c r="H1744" t="n">
         <v>1815807</v>
@@ -50974,7 +50974,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G1745" t="n">
-        <v>4.55565500259399</v>
+        <v>4.55565452575684</v>
       </c>
       <c r="H1745" t="n">
         <v>2099530</v>
@@ -51090,7 +51090,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G1749" t="n">
-        <v>4.52156162261963</v>
+        <v>4.52156209945679</v>
       </c>
       <c r="H1749" t="n">
         <v>1341662</v>
@@ -51380,7 +51380,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1759" t="n">
-        <v>4.09966278076172</v>
+        <v>4.09966325759888</v>
       </c>
       <c r="H1759" t="n">
         <v>2615910</v>
@@ -51496,7 +51496,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G1763" t="n">
-        <v>4.22410202026367</v>
+        <v>4.22410154342651</v>
       </c>
       <c r="H1763" t="n">
         <v>1789059</v>
@@ -51525,7 +51525,7 @@
         <v>4.98199987411499</v>
       </c>
       <c r="G1764" t="n">
-        <v>4.24626207351685</v>
+        <v>4.246262550354</v>
       </c>
       <c r="H1764" t="n">
         <v>1463183</v>
@@ -51583,7 +51583,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G1766" t="n">
-        <v>4.20535039901733</v>
+        <v>4.20535087585449</v>
       </c>
       <c r="H1766" t="n">
         <v>1414902</v>
@@ -51641,7 +51641,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1768" t="n">
-        <v>4.3042197227478</v>
+        <v>4.30422019958496</v>
       </c>
       <c r="H1768" t="n">
         <v>3656588</v>
@@ -51757,7 +51757,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G1772" t="n">
-        <v>4.0706844329834</v>
+        <v>4.07068395614624</v>
       </c>
       <c r="H1772" t="n">
         <v>1878134</v>
@@ -51815,7 +51815,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G1774" t="n">
-        <v>4.09454917907715</v>
+        <v>4.09454870223999</v>
       </c>
       <c r="H1774" t="n">
         <v>1879953</v>
@@ -51844,7 +51844,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G1775" t="n">
-        <v>4.02977323532104</v>
+        <v>4.02977275848389</v>
       </c>
       <c r="H1775" t="n">
         <v>1653698</v>
@@ -51902,7 +51902,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1777" t="n">
-        <v>4.03999996185303</v>
+        <v>4.04000043869019</v>
       </c>
       <c r="H1777" t="n">
         <v>1986204</v>
@@ -52192,7 +52192,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G1787" t="n">
-        <v>4.12182283401489</v>
+        <v>4.12182331085205</v>
       </c>
       <c r="H1787" t="n">
         <v>1067660</v>
@@ -52279,7 +52279,7 @@
         <v>4.94600009918213</v>
       </c>
       <c r="G1790" t="n">
-        <v>4.21557903289795</v>
+        <v>4.21557855606079</v>
       </c>
       <c r="H1790" t="n">
         <v>1526245</v>
@@ -52308,7 +52308,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G1791" t="n">
-        <v>4.2829122543335</v>
+        <v>4.28291177749634</v>
       </c>
       <c r="H1791" t="n">
         <v>1734255</v>
@@ -52395,7 +52395,7 @@
         <v>4.97800016403198</v>
       </c>
       <c r="G1794" t="n">
-        <v>4.24285268783569</v>
+        <v>4.24285316467285</v>
       </c>
       <c r="H1794" t="n">
         <v>1177122</v>
@@ -52424,7 +52424,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1795" t="n">
-        <v>4.3042197227478</v>
+        <v>4.30422019958496</v>
       </c>
       <c r="H1795" t="n">
         <v>996539</v>
@@ -52453,7 +52453,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1796" t="n">
-        <v>4.32978963851929</v>
+        <v>4.32979011535645</v>
       </c>
       <c r="H1796" t="n">
         <v>1142008</v>
@@ -52511,7 +52511,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1798" t="n">
-        <v>4.28717422485352</v>
+        <v>4.28717374801636</v>
       </c>
       <c r="H1798" t="n">
         <v>1956553</v>
@@ -52569,7 +52569,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1800" t="n">
-        <v>4.35962104797363</v>
+        <v>4.35962057113647</v>
       </c>
       <c r="H1800" t="n">
         <v>2840968</v>
@@ -52656,7 +52656,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G1803" t="n">
-        <v>4.41928339004517</v>
+        <v>4.41928291320801</v>
       </c>
       <c r="H1803" t="n">
         <v>1450257</v>
@@ -52830,7 +52830,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1809" t="n">
-        <v>4.44059133529663</v>
+        <v>4.44059181213379</v>
       </c>
       <c r="H1809" t="n">
         <v>1210812</v>
@@ -52859,7 +52859,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G1810" t="n">
-        <v>4.44059133529663</v>
+        <v>4.44059181213379</v>
       </c>
       <c r="H1810" t="n">
         <v>3201819</v>
@@ -53062,7 +53062,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1817" t="n">
-        <v>4.40223693847656</v>
+        <v>4.40223741531372</v>
       </c>
       <c r="H1817" t="n">
         <v>1248063</v>
@@ -53091,7 +53091,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1818" t="n">
-        <v>4.40223693847656</v>
+        <v>4.40223741531372</v>
       </c>
       <c r="H1818" t="n">
         <v>882199</v>
@@ -53149,7 +53149,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1820" t="n">
-        <v>4.36388206481934</v>
+        <v>4.36388254165649</v>
       </c>
       <c r="H1820" t="n">
         <v>2508155</v>
@@ -53178,7 +53178,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1821" t="n">
-        <v>4.3042197227478</v>
+        <v>4.30422019958496</v>
       </c>
       <c r="H1821" t="n">
         <v>2549442</v>
@@ -53236,7 +53236,7 @@
         <v>5.125</v>
       </c>
       <c r="G1823" t="n">
-        <v>4.36814403533936</v>
+        <v>4.36814451217651</v>
       </c>
       <c r="H1823" t="n">
         <v>1564402</v>
@@ -53410,7 +53410,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G1829" t="n">
-        <v>4.55565500259399</v>
+        <v>4.55565452575684</v>
       </c>
       <c r="H1829" t="n">
         <v>2406775</v>
@@ -53787,7 +53787,7 @@
         <v>5.18499994277954</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.41928339004517</v>
+        <v>4.41928291320801</v>
       </c>
       <c r="H1842" t="n">
         <v>2473588</v>
@@ -53903,7 +53903,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.34683609008789</v>
+        <v>4.34683561325073</v>
       </c>
       <c r="H1846" t="n">
         <v>1562721</v>
@@ -53932,7 +53932,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.35535955429077</v>
+        <v>4.35535907745361</v>
       </c>
       <c r="H1847" t="n">
         <v>2060142</v>
@@ -54019,7 +54019,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1850" t="n">
-        <v>4.36388206481934</v>
+        <v>4.36388254165649</v>
       </c>
       <c r="H1850" t="n">
         <v>2151228</v>
@@ -54048,7 +54048,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1851" t="n">
-        <v>4.35962104797363</v>
+        <v>4.35962057113647</v>
       </c>
       <c r="H1851" t="n">
         <v>2019422</v>
@@ -54077,7 +54077,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1852" t="n">
-        <v>4.35962104797363</v>
+        <v>4.35962057113647</v>
       </c>
       <c r="H1852" t="n">
         <v>1503487</v>
@@ -54106,7 +54106,7 @@
         <v>5.125</v>
       </c>
       <c r="G1853" t="n">
-        <v>4.36814403533936</v>
+        <v>4.36814451217651</v>
       </c>
       <c r="H1853" t="n">
         <v>1597297</v>
@@ -54280,7 +54280,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G1859" t="n">
-        <v>4.2829122543335</v>
+        <v>4.28291177749634</v>
       </c>
       <c r="H1859" t="n">
         <v>2591002</v>
@@ -54396,7 +54396,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1863" t="n">
-        <v>4.34683609008789</v>
+        <v>4.34683561325073</v>
       </c>
       <c r="H1863" t="n">
         <v>1665913</v>
@@ -54425,7 +54425,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1864" t="n">
-        <v>4.35535955429077</v>
+        <v>4.35535907745361</v>
       </c>
       <c r="H1864" t="n">
         <v>1376570</v>
@@ -54541,7 +54541,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1868" t="n">
-        <v>4.5599160194397</v>
+        <v>4.55991649627686</v>
       </c>
       <c r="H1868" t="n">
         <v>3562288</v>
@@ -54599,7 +54599,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1870" t="n">
-        <v>4.5599160194397</v>
+        <v>4.55991649627686</v>
       </c>
       <c r="H1870" t="n">
         <v>2800813</v>
@@ -54686,7 +54686,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1873" t="n">
-        <v>4.54287004470825</v>
+        <v>4.54286956787109</v>
       </c>
       <c r="H1873" t="n">
         <v>5635538</v>
@@ -54744,7 +54744,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1875" t="n">
-        <v>4.49599170684814</v>
+        <v>4.4959921836853</v>
       </c>
       <c r="H1875" t="n">
         <v>1559091</v>
@@ -54802,7 +54802,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.3979754447937</v>
+        <v>4.39797496795654</v>
       </c>
       <c r="H1877" t="n">
         <v>3203860</v>
@@ -54860,7 +54860,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G1879" t="n">
-        <v>4.54713153839111</v>
+        <v>4.54713106155396</v>
       </c>
       <c r="H1879" t="n">
         <v>2216421</v>
@@ -54889,7 +54889,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1880" t="n">
-        <v>4.55139350891113</v>
+        <v>4.55139303207397</v>
       </c>
       <c r="H1880" t="n">
         <v>2711182</v>
@@ -54976,7 +54976,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G1883" t="n">
-        <v>4.55139350891113</v>
+        <v>4.55139303207397</v>
       </c>
       <c r="H1883" t="n">
         <v>2432348</v>
@@ -55034,7 +55034,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G1885" t="n">
-        <v>4.54713153839111</v>
+        <v>4.54713106155396</v>
       </c>
       <c r="H1885" t="n">
         <v>1252438</v>
@@ -55121,7 +55121,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1888" t="n">
-        <v>4.40223693847656</v>
+        <v>4.40223741531372</v>
       </c>
       <c r="H1888" t="n">
         <v>1476657</v>
@@ -55237,7 +55237,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1892" t="n">
-        <v>4.32978963851929</v>
+        <v>4.32979011535645</v>
       </c>
       <c r="H1892" t="n">
         <v>2482203</v>
@@ -55324,7 +55324,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1895" t="n">
-        <v>4.28717422485352</v>
+        <v>4.28717374801636</v>
       </c>
       <c r="H1895" t="n">
         <v>2044106</v>
@@ -55382,7 +55382,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G1897" t="n">
-        <v>4.37666702270508</v>
+        <v>4.37666749954224</v>
       </c>
       <c r="H1897" t="n">
         <v>2429389</v>
@@ -55440,7 +55440,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1899" t="n">
-        <v>4.3979754447937</v>
+        <v>4.39797496795654</v>
       </c>
       <c r="H1899" t="n">
         <v>2104566</v>
@@ -55469,7 +55469,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1900" t="n">
-        <v>4.36388206481934</v>
+        <v>4.36388254165649</v>
       </c>
       <c r="H1900" t="n">
         <v>1879378</v>
@@ -55527,7 +55527,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G1902" t="n">
-        <v>4.47042274475098</v>
+        <v>4.47042226791382</v>
       </c>
       <c r="H1902" t="n">
         <v>1826427</v>
@@ -55614,7 +55614,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.47042274475098</v>
+        <v>4.47042226791382</v>
       </c>
       <c r="H1905" t="n">
         <v>2234186</v>
@@ -55701,7 +55701,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1908" t="n">
-        <v>4.49599170684814</v>
+        <v>4.4959921836853</v>
       </c>
       <c r="H1908" t="n">
         <v>2997154</v>
@@ -55788,7 +55788,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1911" t="n">
-        <v>4.5897479057312</v>
+        <v>4.58974742889404</v>
       </c>
       <c r="H1911" t="n">
         <v>3273989</v>
@@ -55904,7 +55904,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G1915" t="n">
-        <v>4.61531734466553</v>
+        <v>4.61531686782837</v>
       </c>
       <c r="H1915" t="n">
         <v>4714774</v>
@@ -73658,6 +73658,64 @@
         <v>2216818</v>
       </c>
       <c r="I2527" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2528">
+      <c r="A2528" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2528" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2528" t="n">
+        <v>8.60999965667725</v>
+      </c>
+      <c r="D2528" t="n">
+        <v>8.64999961853027</v>
+      </c>
+      <c r="E2528" t="n">
+        <v>8.53600025177002</v>
+      </c>
+      <c r="F2528" t="n">
+        <v>8.5939998626709</v>
+      </c>
+      <c r="G2528" t="n">
+        <v>8.5939998626709</v>
+      </c>
+      <c r="H2528" t="n">
+        <v>2025160</v>
+      </c>
+      <c r="I2528" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2529">
+      <c r="A2529" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2529" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2529" t="n">
+        <v>8.61800003051758</v>
+      </c>
+      <c r="D2529" t="n">
+        <v>8.81799983978271</v>
+      </c>
+      <c r="E2529" t="n">
+        <v>8.60999965667725</v>
+      </c>
+      <c r="F2529" t="n">
+        <v>8.77000045776367</v>
+      </c>
+      <c r="G2529" t="n">
+        <v>8.77000045776367</v>
+      </c>
+      <c r="H2529" t="n">
+        <v>4325145</v>
+      </c>
+      <c r="I2529" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -514,7 +514,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G5" t="n">
-        <v>2.07256436347961</v>
+        <v>2.07256412506104</v>
       </c>
       <c r="H5" t="n">
         <v>25466044</v>
@@ -543,7 +543,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08005571365356</v>
+        <v>2.08005547523499</v>
       </c>
       <c r="H6" t="n">
         <v>30431584</v>
@@ -572,7 +572,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0038948059082</v>
+        <v>2.00389504432678</v>
       </c>
       <c r="H7" t="n">
         <v>20054402</v>
@@ -601,7 +601,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G8" t="n">
-        <v>1.97392988204956</v>
+        <v>1.97393012046814</v>
       </c>
       <c r="H8" t="n">
         <v>14428295</v>
@@ -659,7 +659,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G10" t="n">
-        <v>1.95769929885864</v>
+        <v>1.95769917964935</v>
       </c>
       <c r="H10" t="n">
         <v>12484141</v>
@@ -688,7 +688,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G11" t="n">
-        <v>1.97268199920654</v>
+        <v>1.97268152236938</v>
       </c>
       <c r="H11" t="n">
         <v>9571640</v>
@@ -717,7 +717,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95645081996918</v>
+        <v>1.9564505815506</v>
       </c>
       <c r="H12" t="n">
         <v>4499554</v>
@@ -746,7 +746,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G13" t="n">
-        <v>2.01513171195984</v>
+        <v>2.01513195037842</v>
       </c>
       <c r="H13" t="n">
         <v>6390924</v>
@@ -804,7 +804,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>2.05383658409119</v>
+        <v>2.05383610725403</v>
       </c>
       <c r="H15" t="n">
         <v>2202715</v>
@@ -862,7 +862,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G17" t="n">
-        <v>2.08005571365356</v>
+        <v>2.08005547523499</v>
       </c>
       <c r="H17" t="n">
         <v>5610251</v>
@@ -891,7 +891,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G18" t="n">
-        <v>2.10627460479736</v>
+        <v>2.10627436637878</v>
       </c>
       <c r="H18" t="n">
         <v>7328944</v>
@@ -920,7 +920,7 @@
         <v>3.37599992752075</v>
       </c>
       <c r="G19" t="n">
-        <v>2.10752296447754</v>
+        <v>2.10752320289612</v>
       </c>
       <c r="H19" t="n">
         <v>6618545</v>
@@ -949,7 +949,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G20" t="n">
-        <v>2.08504939079285</v>
+        <v>2.08504962921143</v>
       </c>
       <c r="H20" t="n">
         <v>5666890</v>
@@ -978,7 +978,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0413510799408</v>
+        <v>2.04135060310364</v>
       </c>
       <c r="H21" t="n">
         <v>6033410</v>
@@ -1007,7 +1007,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G22" t="n">
-        <v>2.00888919830322</v>
+        <v>2.00888872146606</v>
       </c>
       <c r="H22" t="n">
         <v>5833873</v>
@@ -1036,7 +1036,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12874817848206</v>
+        <v>2.12874841690063</v>
       </c>
       <c r="H23" t="n">
         <v>6586280</v>
@@ -1065,7 +1065,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G24" t="n">
-        <v>2.19367170333862</v>
+        <v>2.19367218017578</v>
       </c>
       <c r="H24" t="n">
         <v>6839861</v>
@@ -1094,7 +1094,7 @@
         <v>3.57599997520447</v>
       </c>
       <c r="G25" t="n">
-        <v>2.23237633705139</v>
+        <v>2.23237657546997</v>
       </c>
       <c r="H25" t="n">
         <v>6100234</v>
@@ -1123,7 +1123,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G26" t="n">
-        <v>2.19991493225098</v>
+        <v>2.1999146938324</v>
       </c>
       <c r="H26" t="n">
         <v>4376808</v>
@@ -1152,7 +1152,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G27" t="n">
-        <v>2.1424822807312</v>
+        <v>2.14248180389404</v>
       </c>
       <c r="H27" t="n">
         <v>5168471</v>
@@ -1181,7 +1181,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G28" t="n">
-        <v>2.20241189002991</v>
+        <v>2.20241165161133</v>
       </c>
       <c r="H28" t="n">
         <v>5589161</v>
@@ -1210,7 +1210,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20615673065186</v>
+        <v>2.20615696907043</v>
       </c>
       <c r="H29" t="n">
         <v>7212643</v>
@@ -1239,7 +1239,7 @@
         <v>3.63599991798401</v>
       </c>
       <c r="G30" t="n">
-        <v>2.26983237266541</v>
+        <v>2.26983213424683</v>
       </c>
       <c r="H30" t="n">
         <v>7461224</v>
@@ -1297,7 +1297,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G32" t="n">
-        <v>2.29355478286743</v>
+        <v>2.29355454444885</v>
       </c>
       <c r="H32" t="n">
         <v>4092166</v>
@@ -1326,7 +1326,7 @@
         <v>3.76600003242493</v>
       </c>
       <c r="G33" t="n">
-        <v>2.35098648071289</v>
+        <v>2.35098695755005</v>
       </c>
       <c r="H33" t="n">
         <v>5873476</v>
@@ -1355,7 +1355,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G34" t="n">
-        <v>2.29480314254761</v>
+        <v>2.29480290412903</v>
       </c>
       <c r="H34" t="n">
         <v>4189580</v>
@@ -1413,7 +1413,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G36" t="n">
-        <v>2.29230570793152</v>
+        <v>2.29230618476868</v>
       </c>
       <c r="H36" t="n">
         <v>1759291</v>
@@ -1442,7 +1442,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G37" t="n">
-        <v>2.3185248374939</v>
+        <v>2.31852531433105</v>
       </c>
       <c r="H37" t="n">
         <v>1256671</v>
@@ -1500,7 +1500,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G39" t="n">
-        <v>2.3272647857666</v>
+        <v>2.32726526260376</v>
       </c>
       <c r="H39" t="n">
         <v>1980797</v>
@@ -1558,7 +1558,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G41" t="n">
-        <v>2.38095211982727</v>
+        <v>2.38095164299011</v>
       </c>
       <c r="H41" t="n">
         <v>2062784</v>
@@ -1587,7 +1587,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G42" t="n">
-        <v>2.34599256515503</v>
+        <v>2.34599280357361</v>
       </c>
       <c r="H42" t="n">
         <v>2886613</v>
@@ -1616,7 +1616,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G43" t="n">
-        <v>2.38469743728638</v>
+        <v>2.3846971988678</v>
       </c>
       <c r="H43" t="n">
         <v>2605147</v>
@@ -1645,7 +1645,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G44" t="n">
-        <v>2.38095211982727</v>
+        <v>2.38095164299011</v>
       </c>
       <c r="H44" t="n">
         <v>3468958</v>
@@ -1674,7 +1674,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G45" t="n">
-        <v>2.38469743728638</v>
+        <v>2.3846971988678</v>
       </c>
       <c r="H45" t="n">
         <v>1750587</v>
@@ -1732,7 +1732,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G47" t="n">
-        <v>2.36097550392151</v>
+        <v>2.36097574234009</v>
       </c>
       <c r="H47" t="n">
         <v>3063904</v>
@@ -1761,7 +1761,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>2.32851338386536</v>
+        <v>2.32851362228394</v>
       </c>
       <c r="H48" t="n">
         <v>3129507</v>
@@ -1790,7 +1790,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G49" t="n">
-        <v>2.33600497245789</v>
+        <v>2.33600473403931</v>
       </c>
       <c r="H49" t="n">
         <v>2305779</v>
@@ -1819,7 +1819,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G50" t="n">
-        <v>2.37221193313599</v>
+        <v>2.37221217155457</v>
       </c>
       <c r="H50" t="n">
         <v>3317379</v>
@@ -1848,7 +1848,7 @@
         <v>3.73600006103516</v>
       </c>
       <c r="G51" t="n">
-        <v>2.33225893974304</v>
+        <v>2.33225917816162</v>
       </c>
       <c r="H51" t="n">
         <v>3319886</v>
@@ -1877,7 +1877,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>2.32851338386536</v>
+        <v>2.32851362228394</v>
       </c>
       <c r="H52" t="n">
         <v>3089208</v>
@@ -1906,7 +1906,7 @@
         <v>3.73200011253357</v>
       </c>
       <c r="G53" t="n">
-        <v>2.32976222038269</v>
+        <v>2.32976174354553</v>
       </c>
       <c r="H53" t="n">
         <v>2828030</v>
@@ -1964,7 +1964,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G55" t="n">
-        <v>2.38220047950745</v>
+        <v>2.38220024108887</v>
       </c>
       <c r="H55" t="n">
         <v>3773445</v>
@@ -1993,7 +1993,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G56" t="n">
-        <v>2.31477975845337</v>
+        <v>2.31477952003479</v>
       </c>
       <c r="H56" t="n">
         <v>3360031</v>
@@ -2022,7 +2022,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G57" t="n">
-        <v>2.34599256515503</v>
+        <v>2.34599280357361</v>
       </c>
       <c r="H57" t="n">
         <v>2216469</v>
@@ -2051,7 +2051,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G58" t="n">
-        <v>2.33101034164429</v>
+        <v>2.33101058006287</v>
       </c>
       <c r="H58" t="n">
         <v>1647322</v>
@@ -2109,7 +2109,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G60" t="n">
-        <v>2.25609850883484</v>
+        <v>2.25609874725342</v>
       </c>
       <c r="H60" t="n">
         <v>2504991</v>
@@ -2138,7 +2138,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17868971824646</v>
+        <v>2.17868947982788</v>
       </c>
       <c r="H61" t="n">
         <v>5521766</v>
@@ -2167,7 +2167,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G62" t="n">
-        <v>2.19741749763489</v>
+        <v>2.19741773605347</v>
       </c>
       <c r="H62" t="n">
         <v>2603411</v>
@@ -2196,7 +2196,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G63" t="n">
-        <v>2.21364831924438</v>
+        <v>2.21364855766296</v>
       </c>
       <c r="H63" t="n">
         <v>2357805</v>
@@ -2312,7 +2312,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>2.29105734825134</v>
+        <v>2.29105758666992</v>
       </c>
       <c r="H67" t="n">
         <v>2558214</v>
@@ -2370,7 +2370,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G69" t="n">
-        <v>2.36222362518311</v>
+        <v>2.36222386360168</v>
       </c>
       <c r="H69" t="n">
         <v>2429548</v>
@@ -2399,7 +2399,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G70" t="n">
-        <v>2.36097550392151</v>
+        <v>2.36097574234009</v>
       </c>
       <c r="H70" t="n">
         <v>2975719</v>
@@ -2428,7 +2428,7 @@
         <v>3.79399991035461</v>
       </c>
       <c r="G71" t="n">
-        <v>2.36846661567688</v>
+        <v>2.3684663772583</v>
       </c>
       <c r="H71" t="n">
         <v>2188039</v>
@@ -2457,7 +2457,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G72" t="n">
-        <v>2.37845468521118</v>
+        <v>2.3784544467926</v>
       </c>
       <c r="H72" t="n">
         <v>2905887</v>
@@ -2515,7 +2515,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.38469743728638</v>
+        <v>2.3846971988678</v>
       </c>
       <c r="H74" t="n">
         <v>1520764</v>
@@ -2544,7 +2544,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G75" t="n">
-        <v>2.37845468521118</v>
+        <v>2.3784544467926</v>
       </c>
       <c r="H75" t="n">
         <v>1737173</v>
@@ -2573,7 +2573,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G76" t="n">
-        <v>2.36721801757812</v>
+        <v>2.36721777915955</v>
       </c>
       <c r="H76" t="n">
         <v>1733373</v>
@@ -2602,7 +2602,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G77" t="n">
-        <v>2.38095211982727</v>
+        <v>2.38095164299011</v>
       </c>
       <c r="H77" t="n">
         <v>2013014</v>
@@ -2631,7 +2631,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.36596918106079</v>
+        <v>2.36596941947937</v>
       </c>
       <c r="H78" t="n">
         <v>3734574</v>
@@ -2718,7 +2718,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G81" t="n">
-        <v>2.36721801757812</v>
+        <v>2.36721777915955</v>
       </c>
       <c r="H81" t="n">
         <v>1985720</v>
@@ -2747,7 +2747,7 @@
         <v>3.75399994850159</v>
       </c>
       <c r="G82" t="n">
-        <v>2.3434956073761</v>
+        <v>2.34349584579468</v>
       </c>
       <c r="H82" t="n">
         <v>2040278</v>
@@ -2776,7 +2776,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G83" t="n">
-        <v>2.37845468521118</v>
+        <v>2.3784544467926</v>
       </c>
       <c r="H83" t="n">
         <v>1929343</v>
@@ -2805,7 +2805,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G84" t="n">
-        <v>2.38969111442566</v>
+        <v>2.38969135284424</v>
       </c>
       <c r="H84" t="n">
         <v>1165087</v>
@@ -2863,7 +2863,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G86" t="n">
-        <v>2.40841960906982</v>
+        <v>2.40841937065125</v>
       </c>
       <c r="H86" t="n">
         <v>1569946</v>
@@ -2950,7 +2950,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G89" t="n">
-        <v>2.42839598655701</v>
+        <v>2.42839622497559</v>
       </c>
       <c r="H89" t="n">
         <v>2000160</v>
@@ -3066,7 +3066,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G93" t="n">
-        <v>2.4296441078186</v>
+        <v>2.42964482307434</v>
       </c>
       <c r="H93" t="n">
         <v>1529490</v>
@@ -3124,7 +3124,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G95" t="n">
-        <v>2.4671003818512</v>
+        <v>2.46710062026978</v>
       </c>
       <c r="H95" t="n">
         <v>9713560</v>
@@ -3182,7 +3182,7 @@
         <v>3.99399995803833</v>
       </c>
       <c r="G97" t="n">
-        <v>2.49331998825073</v>
+        <v>2.49331951141357</v>
       </c>
       <c r="H97" t="n">
         <v>3138380</v>
@@ -3211,7 +3211,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G98" t="n">
-        <v>2.46335506439209</v>
+        <v>2.46335458755493</v>
       </c>
       <c r="H98" t="n">
         <v>2677473</v>
@@ -3240,7 +3240,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G99" t="n">
-        <v>2.4671003818512</v>
+        <v>2.46710062026978</v>
       </c>
       <c r="H99" t="n">
         <v>2383108</v>
@@ -3269,7 +3269,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G100" t="n">
-        <v>2.55574655532837</v>
+        <v>2.55574631690979</v>
       </c>
       <c r="H100" t="n">
         <v>3927765</v>
@@ -3472,7 +3472,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>2.52203607559204</v>
+        <v>2.52203631401062</v>
       </c>
       <c r="H107" t="n">
         <v>1747900</v>
@@ -3501,7 +3501,7 @@
         <v>4.05399990081787</v>
       </c>
       <c r="G108" t="n">
-        <v>2.53077530860901</v>
+        <v>2.53077578544617</v>
       </c>
       <c r="H108" t="n">
         <v>1847937</v>
@@ -3530,7 +3530,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G109" t="n">
-        <v>2.58071708679199</v>
+        <v>2.58071684837341</v>
       </c>
       <c r="H109" t="n">
         <v>2152114</v>
@@ -3559,7 +3559,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>2.58446264266968</v>
+        <v>2.5844624042511</v>
       </c>
       <c r="H110" t="n">
         <v>1654975</v>
@@ -3588,7 +3588,7 @@
         <v>4.10799980163574</v>
       </c>
       <c r="G111" t="n">
-        <v>2.5644862651825</v>
+        <v>2.56448554992676</v>
       </c>
       <c r="H111" t="n">
         <v>1505349</v>
@@ -3675,7 +3675,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>2.63690090179443</v>
+        <v>2.63690114021301</v>
       </c>
       <c r="H114" t="n">
         <v>2609947</v>
@@ -3704,7 +3704,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>2.59694790840149</v>
+        <v>2.59694766998291</v>
       </c>
       <c r="H115" t="n">
         <v>2393218</v>
@@ -3733,7 +3733,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G116" t="n">
-        <v>2.58571100234985</v>
+        <v>2.58571147918701</v>
       </c>
       <c r="H116" t="n">
         <v>2970660</v>
@@ -3791,7 +3791,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G118" t="n">
-        <v>2.548255443573</v>
+        <v>2.54825520515442</v>
       </c>
       <c r="H118" t="n">
         <v>3067347</v>
@@ -3820,7 +3820,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G119" t="n">
-        <v>2.66436910629272</v>
+        <v>2.66436886787415</v>
       </c>
       <c r="H119" t="n">
         <v>3299496</v>
@@ -3849,7 +3849,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G120" t="n">
-        <v>2.62816119194031</v>
+        <v>2.62816166877747</v>
       </c>
       <c r="H120" t="n">
         <v>2350140</v>
@@ -3878,7 +3878,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G121" t="n">
-        <v>2.57822012901306</v>
+        <v>2.57821989059448</v>
       </c>
       <c r="H121" t="n">
         <v>2971262</v>
@@ -3907,7 +3907,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>2.60319042205811</v>
+        <v>2.60319066047668</v>
       </c>
       <c r="H122" t="n">
         <v>2478837</v>
@@ -3994,7 +3994,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G125" t="n">
-        <v>2.63690090179443</v>
+        <v>2.63690114021301</v>
       </c>
       <c r="H125" t="n">
         <v>1568341</v>
@@ -4023,7 +4023,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G126" t="n">
-        <v>2.65937495231628</v>
+        <v>2.65937471389771</v>
       </c>
       <c r="H126" t="n">
         <v>3604147</v>
@@ -4052,7 +4052,7 @@
         <v>4.34800004959106</v>
       </c>
       <c r="G127" t="n">
-        <v>2.71430993080139</v>
+        <v>2.71431016921997</v>
       </c>
       <c r="H127" t="n">
         <v>3044744</v>
@@ -4081,7 +4081,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G128" t="n">
-        <v>2.71930408477783</v>
+        <v>2.71930456161499</v>
       </c>
       <c r="H128" t="n">
         <v>2807710</v>
@@ -4110,7 +4110,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G129" t="n">
-        <v>2.76425170898438</v>
+        <v>2.76425123214722</v>
       </c>
       <c r="H129" t="n">
         <v>2632642</v>
@@ -4139,7 +4139,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G130" t="n">
-        <v>2.77299094200134</v>
+        <v>2.77299118041992</v>
       </c>
       <c r="H130" t="n">
         <v>2184181</v>
@@ -4168,7 +4168,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G131" t="n">
-        <v>2.73178958892822</v>
+        <v>2.73178935050964</v>
       </c>
       <c r="H131" t="n">
         <v>2678363</v>
@@ -4197,7 +4197,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G132" t="n">
-        <v>2.79047036170959</v>
+        <v>2.79047012329102</v>
       </c>
       <c r="H132" t="n">
         <v>2165558</v>
@@ -4226,7 +4226,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G133" t="n">
-        <v>2.88036465644836</v>
+        <v>2.88036489486694</v>
       </c>
       <c r="H133" t="n">
         <v>4112711</v>
@@ -4284,7 +4284,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84166073799133</v>
+        <v>2.84166026115417</v>
       </c>
       <c r="H135" t="n">
         <v>4094332</v>
@@ -4371,7 +4371,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G138" t="n">
-        <v>2.96670079231262</v>
+        <v>2.96670150756836</v>
       </c>
       <c r="H138" t="n">
         <v>3149602</v>
@@ -4400,7 +4400,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G139" t="n">
-        <v>3.02132701873779</v>
+        <v>3.02132725715637</v>
       </c>
       <c r="H139" t="n">
         <v>2869145</v>
@@ -4458,7 +4458,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G141" t="n">
-        <v>3.00441908836365</v>
+        <v>3.00441884994507</v>
       </c>
       <c r="H141" t="n">
         <v>1874966</v>
@@ -4632,7 +4632,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G147" t="n">
-        <v>3.14748692512512</v>
+        <v>3.14748668670654</v>
       </c>
       <c r="H147" t="n">
         <v>3102001</v>
@@ -4690,7 +4690,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G149" t="n">
-        <v>3.10716772079468</v>
+        <v>3.10716795921326</v>
       </c>
       <c r="H149" t="n">
         <v>2358075</v>
@@ -4719,7 +4719,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>3.08505749702454</v>
+        <v>3.08505702018738</v>
       </c>
       <c r="H150" t="n">
         <v>1877264</v>
@@ -4748,7 +4748,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G151" t="n">
-        <v>3.11237025260925</v>
+        <v>3.11237049102783</v>
       </c>
       <c r="H151" t="n">
         <v>4202424</v>
@@ -4777,7 +4777,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G152" t="n">
-        <v>3.05124187469482</v>
+        <v>3.05124092102051</v>
       </c>
       <c r="H152" t="n">
         <v>2693512</v>
@@ -4806,7 +4806,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G153" t="n">
-        <v>2.96279978752136</v>
+        <v>2.96280002593994</v>
       </c>
       <c r="H153" t="n">
         <v>3978290</v>
@@ -4835,7 +4835,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G154" t="n">
-        <v>2.98100781440735</v>
+        <v>2.98100829124451</v>
       </c>
       <c r="H154" t="n">
         <v>1741047</v>
@@ -4893,7 +4893,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G156" t="n">
-        <v>2.97190451622009</v>
+        <v>2.97190403938293</v>
       </c>
       <c r="H156" t="n">
         <v>3155336</v>
@@ -4922,7 +4922,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G157" t="n">
-        <v>2.98751139640808</v>
+        <v>2.98751163482666</v>
       </c>
       <c r="H157" t="n">
         <v>3210418</v>
@@ -4951,7 +4951,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G158" t="n">
-        <v>3.02262783050537</v>
+        <v>3.02262759208679</v>
       </c>
       <c r="H158" t="n">
         <v>1663568</v>
@@ -4980,7 +4980,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G159" t="n">
-        <v>3.02783036231995</v>
+        <v>3.02783012390137</v>
       </c>
       <c r="H159" t="n">
         <v>1415379</v>
@@ -5009,7 +5009,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G160" t="n">
-        <v>2.98751139640808</v>
+        <v>2.98751163482666</v>
       </c>
       <c r="H160" t="n">
         <v>1883587</v>
@@ -5038,7 +5038,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>3.01092267036438</v>
+        <v>3.0109224319458</v>
       </c>
       <c r="H161" t="n">
         <v>1440176</v>
@@ -5067,7 +5067,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G162" t="n">
-        <v>3.02262783050537</v>
+        <v>3.02262759208679</v>
       </c>
       <c r="H162" t="n">
         <v>1812459</v>
@@ -5096,7 +5096,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.00441908836365</v>
+        <v>3.00441884994507</v>
       </c>
       <c r="H163" t="n">
         <v>1330854</v>
@@ -5125,7 +5125,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90947437286377</v>
+        <v>2.90947484970093</v>
       </c>
       <c r="H164" t="n">
         <v>2136959</v>
@@ -5241,7 +5241,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90687322616577</v>
+        <v>2.90687298774719</v>
       </c>
       <c r="H168" t="n">
         <v>2203554</v>
@@ -5270,7 +5270,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G169" t="n">
-        <v>2.89126586914062</v>
+        <v>2.8912661075592</v>
       </c>
       <c r="H169" t="n">
         <v>1777949</v>
@@ -5328,7 +5328,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G171" t="n">
-        <v>2.85875034332275</v>
+        <v>2.85875058174133</v>
       </c>
       <c r="H171" t="n">
         <v>1637236</v>
@@ -5357,7 +5357,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>2.86785483360291</v>
+        <v>2.86785459518433</v>
       </c>
       <c r="H172" t="n">
         <v>1480885</v>
@@ -5415,7 +5415,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G174" t="n">
-        <v>2.94459104537964</v>
+        <v>2.94459128379822</v>
       </c>
       <c r="H174" t="n">
         <v>1407321</v>
@@ -5444,7 +5444,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>2.97190451622009</v>
+        <v>2.97190403938293</v>
       </c>
       <c r="H175" t="n">
         <v>2547097</v>
@@ -5473,7 +5473,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>2.95239472389221</v>
+        <v>2.95239496231079</v>
       </c>
       <c r="H176" t="n">
         <v>2291148</v>
@@ -5560,7 +5560,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G179" t="n">
-        <v>2.97190451622009</v>
+        <v>2.97190403938293</v>
       </c>
       <c r="H179" t="n">
         <v>1152290</v>
@@ -5589,7 +5589,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G180" t="n">
-        <v>2.99531531333923</v>
+        <v>2.99531507492065</v>
       </c>
       <c r="H180" t="n">
         <v>1233361</v>
@@ -5705,7 +5705,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>3.01092267036438</v>
+        <v>3.0109224319458</v>
       </c>
       <c r="H184" t="n">
         <v>1202620</v>
@@ -5734,7 +5734,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G185" t="n">
-        <v>2.99271416664124</v>
+        <v>2.99271368980408</v>
       </c>
       <c r="H185" t="n">
         <v>1171053</v>
@@ -5821,7 +5821,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.02392840385437</v>
+        <v>3.02392864227295</v>
       </c>
       <c r="H188" t="n">
         <v>2591123</v>
@@ -5850,7 +5850,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G189" t="n">
-        <v>3.08765864372253</v>
+        <v>3.08765888214111</v>
       </c>
       <c r="H189" t="n">
         <v>1958346</v>
@@ -5908,7 +5908,7 @@
         <v>4.78800010681152</v>
       </c>
       <c r="G191" t="n">
-        <v>3.11367130279541</v>
+        <v>3.11367082595825</v>
       </c>
       <c r="H191" t="n">
         <v>1110454</v>
@@ -5937,7 +5937,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G192" t="n">
-        <v>3.14748692512512</v>
+        <v>3.14748668670654</v>
       </c>
       <c r="H192" t="n">
         <v>1481236</v>
@@ -5995,7 +5995,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G194" t="n">
-        <v>3.16569566726685</v>
+        <v>3.16569542884827</v>
       </c>
       <c r="H194" t="n">
         <v>1182663</v>
@@ -6053,7 +6053,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>3.14098334312439</v>
+        <v>3.14098381996155</v>
       </c>
       <c r="H196" t="n">
         <v>649672</v>
@@ -6082,7 +6082,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G197" t="n">
-        <v>3.07335162162781</v>
+        <v>3.07335138320923</v>
       </c>
       <c r="H197" t="n">
         <v>1172588</v>
@@ -6111,7 +6111,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G198" t="n">
-        <v>3.1435854434967</v>
+        <v>3.14358520507812</v>
       </c>
       <c r="H198" t="n">
         <v>1316763</v>
@@ -6140,7 +6140,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G199" t="n">
-        <v>3.15789198875427</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H199" t="n">
         <v>1018979</v>
@@ -6169,7 +6169,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G200" t="n">
-        <v>3.14228391647339</v>
+        <v>3.14228439331055</v>
       </c>
       <c r="H200" t="n">
         <v>1062261</v>
@@ -6198,7 +6198,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G201" t="n">
-        <v>3.15789198875427</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H201" t="n">
         <v>1683946</v>
@@ -6227,7 +6227,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G202" t="n">
-        <v>3.14228391647339</v>
+        <v>3.14228439331055</v>
       </c>
       <c r="H202" t="n">
         <v>1384943</v>
@@ -6256,7 +6256,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G203" t="n">
-        <v>3.12407636642456</v>
+        <v>3.12407612800598</v>
       </c>
       <c r="H203" t="n">
         <v>767697</v>
@@ -6285,7 +6285,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G204" t="n">
-        <v>3.11757254600525</v>
+        <v>3.11757326126099</v>
       </c>
       <c r="H204" t="n">
         <v>1282121</v>
@@ -6343,7 +6343,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.10846924781799</v>
+        <v>3.10846853256226</v>
       </c>
       <c r="H206" t="n">
         <v>937602</v>
@@ -6372,7 +6372,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G207" t="n">
-        <v>3.09546208381653</v>
+        <v>3.09546232223511</v>
       </c>
       <c r="H207" t="n">
         <v>479531</v>
@@ -6401,7 +6401,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G208" t="n">
-        <v>3.08245587348938</v>
+        <v>3.08245611190796</v>
       </c>
       <c r="H208" t="n">
         <v>1265229</v>
@@ -6430,7 +6430,7 @@
         <v>4.77199983596802</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10326552391052</v>
+        <v>3.1032657623291</v>
       </c>
       <c r="H209" t="n">
         <v>1033833</v>
@@ -6459,7 +6459,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G210" t="n">
-        <v>3.08505749702454</v>
+        <v>3.08505702018738</v>
       </c>
       <c r="H210" t="n">
         <v>1269558</v>
@@ -6604,7 +6604,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G215" t="n">
-        <v>3.10976910591125</v>
+        <v>3.10976934432983</v>
       </c>
       <c r="H215" t="n">
         <v>2759009</v>
@@ -6633,7 +6633,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G216" t="n">
-        <v>3.09026002883911</v>
+        <v>3.09025955200195</v>
       </c>
       <c r="H216" t="n">
         <v>1133242</v>
@@ -6691,7 +6691,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G218" t="n">
-        <v>3.08765864372253</v>
+        <v>3.08765888214111</v>
       </c>
       <c r="H218" t="n">
         <v>1410451</v>
@@ -6720,7 +6720,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G219" t="n">
-        <v>3.05774426460266</v>
+        <v>3.0577449798584</v>
       </c>
       <c r="H219" t="n">
         <v>1659908</v>
@@ -6749,7 +6749,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.02392840385437</v>
+        <v>3.02392864227295</v>
       </c>
       <c r="H220" t="n">
         <v>1539498</v>
@@ -6778,7 +6778,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G221" t="n">
-        <v>3.03043174743652</v>
+        <v>3.03043103218079</v>
       </c>
       <c r="H221" t="n">
         <v>1713520</v>
@@ -6807,7 +6807,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G222" t="n">
-        <v>3.03043174743652</v>
+        <v>3.03043103218079</v>
       </c>
       <c r="H222" t="n">
         <v>1111692</v>
@@ -6836,7 +6836,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G223" t="n">
-        <v>3.04864025115967</v>
+        <v>3.04864096641541</v>
       </c>
       <c r="H223" t="n">
         <v>1146321</v>
@@ -6865,7 +6865,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.02392840385437</v>
+        <v>3.02392864227295</v>
       </c>
       <c r="H224" t="n">
         <v>1103008</v>
@@ -6952,7 +6952,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G227" t="n">
-        <v>3.1019651889801</v>
+        <v>3.10196566581726</v>
       </c>
       <c r="H227" t="n">
         <v>1868854</v>
@@ -7039,7 +7039,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G230" t="n">
-        <v>3.09546208381653</v>
+        <v>3.09546232223511</v>
       </c>
       <c r="H230" t="n">
         <v>1964842</v>
@@ -7068,7 +7068,7 @@
         <v>4.75</v>
       </c>
       <c r="G231" t="n">
-        <v>3.08895897865295</v>
+        <v>3.08895945549011</v>
       </c>
       <c r="H231" t="n">
         <v>1731154</v>
@@ -7155,7 +7155,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G234" t="n">
-        <v>3.01222276687622</v>
+        <v>3.0122230052948</v>
       </c>
       <c r="H234" t="n">
         <v>2554522</v>
@@ -7184,7 +7184,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G235" t="n">
-        <v>3.0330331325531</v>
+        <v>3.03303265571594</v>
       </c>
       <c r="H235" t="n">
         <v>2592607</v>
@@ -7242,7 +7242,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G237" t="n">
-        <v>3.03043174743652</v>
+        <v>3.03043103218079</v>
       </c>
       <c r="H237" t="n">
         <v>2780174</v>
@@ -7271,7 +7271,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G238" t="n">
-        <v>3.03173232078552</v>
+        <v>3.03173184394836</v>
       </c>
       <c r="H238" t="n">
         <v>1498059</v>
@@ -7329,7 +7329,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G240" t="n">
-        <v>3.09156060218811</v>
+        <v>3.09156107902527</v>
       </c>
       <c r="H240" t="n">
         <v>3955428</v>
@@ -7358,7 +7358,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G241" t="n">
-        <v>3.10586714744568</v>
+        <v>3.10586738586426</v>
       </c>
       <c r="H241" t="n">
         <v>1298047</v>
@@ -7387,7 +7387,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G242" t="n">
-        <v>3.07335162162781</v>
+        <v>3.07335138320923</v>
       </c>
       <c r="H242" t="n">
         <v>1121811</v>
@@ -7445,7 +7445,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G244" t="n">
-        <v>3.09546208381653</v>
+        <v>3.09546232223511</v>
       </c>
       <c r="H244" t="n">
         <v>906408</v>
@@ -7474,7 +7474,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G245" t="n">
-        <v>3.11497139930725</v>
+        <v>3.11497163772583</v>
       </c>
       <c r="H245" t="n">
         <v>1121552</v>
@@ -7503,7 +7503,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>3.14098334312439</v>
+        <v>3.14098381996155</v>
       </c>
       <c r="H246" t="n">
         <v>1767243</v>
@@ -7561,7 +7561,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G248" t="n">
-        <v>3.34257888793945</v>
+        <v>3.34257841110229</v>
       </c>
       <c r="H248" t="n">
         <v>8302472</v>
@@ -7590,7 +7590,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24893474578857</v>
+        <v>3.24893450737</v>
       </c>
       <c r="H249" t="n">
         <v>3278337</v>
@@ -7619,7 +7619,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>3.31656646728516</v>
+        <v>3.31656670570374</v>
       </c>
       <c r="H250" t="n">
         <v>2795501</v>
@@ -7677,7 +7677,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>3.27104520797729</v>
+        <v>3.27104496955872</v>
       </c>
       <c r="H252" t="n">
         <v>6428942</v>
@@ -7706,7 +7706,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G253" t="n">
-        <v>3.26129078865051</v>
+        <v>3.26129031181335</v>
       </c>
       <c r="H253" t="n">
         <v>1973997</v>
@@ -7735,7 +7735,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>3.3003089427948</v>
+        <v>3.30030870437622</v>
       </c>
       <c r="H254" t="n">
         <v>3004311</v>
@@ -7764,7 +7764,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G255" t="n">
-        <v>3.28730225563049</v>
+        <v>3.28730249404907</v>
       </c>
       <c r="H255" t="n">
         <v>1842881</v>
@@ -7822,7 +7822,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G257" t="n">
-        <v>3.32307052612305</v>
+        <v>3.32306981086731</v>
       </c>
       <c r="H257" t="n">
         <v>2418189</v>
@@ -7851,7 +7851,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>3.3198184967041</v>
+        <v>3.31981825828552</v>
       </c>
       <c r="H258" t="n">
         <v>2955797</v>
@@ -7909,7 +7909,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>3.31656646728516</v>
+        <v>3.31656670570374</v>
       </c>
       <c r="H260" t="n">
         <v>2506308</v>
@@ -7938,7 +7938,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>3.35233402252197</v>
+        <v>3.35233378410339</v>
       </c>
       <c r="H261" t="n">
         <v>2738338</v>
@@ -7967,7 +7967,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G262" t="n">
-        <v>3.35233402252197</v>
+        <v>3.35233378410339</v>
       </c>
       <c r="H262" t="n">
         <v>2922943</v>
@@ -7996,7 +7996,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G263" t="n">
-        <v>3.39135265350342</v>
+        <v>3.39135241508484</v>
       </c>
       <c r="H263" t="n">
         <v>2984962</v>
@@ -8025,7 +8025,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G264" t="n">
-        <v>3.36208868026733</v>
+        <v>3.36208820343018</v>
       </c>
       <c r="H264" t="n">
         <v>3024002</v>
@@ -8054,7 +8054,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G265" t="n">
-        <v>3.39460372924805</v>
+        <v>3.39460349082947</v>
       </c>
       <c r="H265" t="n">
         <v>2474383</v>
@@ -8083,7 +8083,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G266" t="n">
-        <v>3.40760946273804</v>
+        <v>3.40760970115662</v>
       </c>
       <c r="H266" t="n">
         <v>3425548</v>
@@ -8112,7 +8112,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>3.47914338111877</v>
+        <v>3.47914361953735</v>
       </c>
       <c r="H267" t="n">
         <v>2730053</v>
@@ -8228,7 +8228,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>3.33607602119446</v>
+        <v>3.33607625961304</v>
       </c>
       <c r="H271" t="n">
         <v>1843477</v>
@@ -8257,7 +8257,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.31656646728516</v>
+        <v>3.31656670570374</v>
       </c>
       <c r="H272" t="n">
         <v>1936166</v>
@@ -8315,7 +8315,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>3.39460372924805</v>
+        <v>3.39460349082947</v>
       </c>
       <c r="H274" t="n">
         <v>1754265</v>
@@ -8344,7 +8344,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G275" t="n">
-        <v>3.45963454246521</v>
+        <v>3.45963478088379</v>
       </c>
       <c r="H275" t="n">
         <v>3167757</v>
@@ -8373,7 +8373,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>3.37509441375732</v>
+        <v>3.37509417533875</v>
       </c>
       <c r="H276" t="n">
         <v>3443370</v>
@@ -8402,7 +8402,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G277" t="n">
-        <v>3.39460372924805</v>
+        <v>3.39460349082947</v>
       </c>
       <c r="H277" t="n">
         <v>1741298</v>
@@ -8431,7 +8431,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G278" t="n">
-        <v>3.43687391281128</v>
+        <v>3.43687319755554</v>
       </c>
       <c r="H278" t="n">
         <v>4607010</v>
@@ -8460,7 +8460,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G279" t="n">
-        <v>3.44987964630127</v>
+        <v>3.44987940788269</v>
       </c>
       <c r="H279" t="n">
         <v>3731719</v>
@@ -8489,7 +8489,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>3.44012546539307</v>
+        <v>3.44012522697449</v>
       </c>
       <c r="H280" t="n">
         <v>5567621</v>
@@ -8518,7 +8518,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>3.46613717079163</v>
+        <v>3.46613740921021</v>
       </c>
       <c r="H281" t="n">
         <v>3172733</v>
@@ -8576,7 +8576,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G283" t="n">
-        <v>3.43687391281128</v>
+        <v>3.43687319755554</v>
       </c>
       <c r="H283" t="n">
         <v>1954309</v>
@@ -8605,7 +8605,7 @@
         <v>5.25</v>
       </c>
       <c r="G284" t="n">
-        <v>3.41411280632019</v>
+        <v>3.41411256790161</v>
       </c>
       <c r="H284" t="n">
         <v>2645545</v>
@@ -8634,7 +8634,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>3.38484811782837</v>
+        <v>3.38484954833984</v>
       </c>
       <c r="H285" t="n">
         <v>1879710</v>
@@ -8663,7 +8663,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38484811782837</v>
+        <v>3.38484954833984</v>
       </c>
       <c r="H286" t="n">
         <v>3135720</v>
@@ -8750,7 +8750,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G289" t="n">
-        <v>3.37509441375732</v>
+        <v>3.37509417533875</v>
       </c>
       <c r="H289" t="n">
         <v>2203324</v>
@@ -8779,7 +8779,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G290" t="n">
-        <v>3.32307052612305</v>
+        <v>3.32306981086731</v>
       </c>
       <c r="H290" t="n">
         <v>1986354</v>
@@ -8837,7 +8837,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32307052612305</v>
+        <v>3.32306981086731</v>
       </c>
       <c r="H292" t="n">
         <v>1239019</v>
@@ -8866,7 +8866,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G293" t="n">
-        <v>3.33607602119446</v>
+        <v>3.33607625961304</v>
       </c>
       <c r="H293" t="n">
         <v>1087147</v>
@@ -8924,7 +8924,7 @@
         <v>5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.25153613090515</v>
+        <v>3.25153565406799</v>
       </c>
       <c r="H295" t="n">
         <v>2285101</v>
@@ -8953,7 +8953,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G296" t="n">
-        <v>3.18130350112915</v>
+        <v>3.18130278587341</v>
       </c>
       <c r="H296" t="n">
         <v>3278283</v>
@@ -8982,7 +8982,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G297" t="n">
-        <v>3.238529920578</v>
+        <v>3.23852968215942</v>
       </c>
       <c r="H297" t="n">
         <v>2508428</v>
@@ -9011,7 +9011,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G298" t="n">
-        <v>3.27104520797729</v>
+        <v>3.27104496955872</v>
       </c>
       <c r="H298" t="n">
         <v>1818628</v>
@@ -9040,7 +9040,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G299" t="n">
-        <v>3.26454257965088</v>
+        <v>3.2645423412323</v>
       </c>
       <c r="H299" t="n">
         <v>2225454</v>
@@ -9069,7 +9069,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G300" t="n">
-        <v>3.24503302574158</v>
+        <v>3.245032787323</v>
       </c>
       <c r="H300" t="n">
         <v>2694727</v>
@@ -9127,7 +9127,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>3.16699600219727</v>
+        <v>3.16699576377869</v>
       </c>
       <c r="H302" t="n">
         <v>2028450</v>
@@ -9156,7 +9156,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G303" t="n">
-        <v>3.16959691047668</v>
+        <v>3.16959738731384</v>
       </c>
       <c r="H303" t="n">
         <v>1765252</v>
@@ -9185,7 +9185,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G304" t="n">
-        <v>3.16959691047668</v>
+        <v>3.16959738731384</v>
       </c>
       <c r="H304" t="n">
         <v>1332188</v>
@@ -9243,7 +9243,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G306" t="n">
-        <v>3.23202681541443</v>
+        <v>3.23202657699585</v>
       </c>
       <c r="H306" t="n">
         <v>1936665</v>
@@ -9301,7 +9301,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G308" t="n">
-        <v>3.22942543029785</v>
+        <v>3.22942566871643</v>
       </c>
       <c r="H308" t="n">
         <v>1536056</v>
@@ -9330,7 +9330,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G309" t="n">
-        <v>3.24503302574158</v>
+        <v>3.245032787323</v>
       </c>
       <c r="H309" t="n">
         <v>1332232</v>
@@ -9359,7 +9359,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G310" t="n">
-        <v>3.27104520797729</v>
+        <v>3.27104496955872</v>
       </c>
       <c r="H310" t="n">
         <v>1565332</v>
@@ -9388,7 +9388,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22942543029785</v>
+        <v>3.22942566871643</v>
       </c>
       <c r="H311" t="n">
         <v>1793873</v>
@@ -9417,7 +9417,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G312" t="n">
-        <v>3.20081210136414</v>
+        <v>3.20081186294556</v>
       </c>
       <c r="H312" t="n">
         <v>1847100</v>
@@ -9504,7 +9504,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G315" t="n">
-        <v>3.16699600219727</v>
+        <v>3.16699576377869</v>
       </c>
       <c r="H315" t="n">
         <v>2426852</v>
@@ -9533,7 +9533,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G316" t="n">
-        <v>3.23462820053101</v>
+        <v>3.23462796211243</v>
       </c>
       <c r="H316" t="n">
         <v>3281061</v>
@@ -9562,7 +9562,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G317" t="n">
-        <v>3.2177197933197</v>
+        <v>3.21771955490112</v>
       </c>
       <c r="H317" t="n">
         <v>2118644</v>
@@ -9591,7 +9591,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G318" t="n">
-        <v>3.14748692512512</v>
+        <v>3.14748668670654</v>
       </c>
       <c r="H318" t="n">
         <v>3105576</v>
@@ -9620,7 +9620,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G319" t="n">
-        <v>3.11237025260925</v>
+        <v>3.11237049102783</v>
       </c>
       <c r="H319" t="n">
         <v>3378437</v>
@@ -9649,7 +9649,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>2.98816156387329</v>
+        <v>2.98816132545471</v>
       </c>
       <c r="H320" t="n">
         <v>3568087</v>
@@ -9678,7 +9678,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02913093566895</v>
+        <v>3.02913117408752</v>
       </c>
       <c r="H321" t="n">
         <v>2708506</v>
@@ -9707,7 +9707,7 @@
         <v>4.51399993896484</v>
       </c>
       <c r="G322" t="n">
-        <v>2.93548703193665</v>
+        <v>2.93548679351807</v>
       </c>
       <c r="H322" t="n">
         <v>2918956</v>
@@ -9736,7 +9736,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G323" t="n">
-        <v>2.91597747802734</v>
+        <v>2.91597771644592</v>
       </c>
       <c r="H323" t="n">
         <v>2401875</v>
@@ -9852,7 +9852,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G327" t="n">
-        <v>2.89646863937378</v>
+        <v>2.89646816253662</v>
       </c>
       <c r="H327" t="n">
         <v>1295172</v>
@@ -9881,7 +9881,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G328" t="n">
-        <v>2.91662812232971</v>
+        <v>2.91662788391113</v>
       </c>
       <c r="H328" t="n">
         <v>1203275</v>
@@ -9910,7 +9910,7 @@
         <v>4.40799999237061</v>
       </c>
       <c r="G329" t="n">
-        <v>2.86655426025391</v>
+        <v>2.86655402183533</v>
       </c>
       <c r="H329" t="n">
         <v>1853389</v>
@@ -9939,7 +9939,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>2.83533978462219</v>
+        <v>2.83533954620361</v>
       </c>
       <c r="H330" t="n">
         <v>1994170</v>
@@ -10055,7 +10055,7 @@
         <v>4.51700019836426</v>
       </c>
       <c r="G334" t="n">
-        <v>2.93743801116943</v>
+        <v>2.93743753433228</v>
       </c>
       <c r="H334" t="n">
         <v>1748762</v>
@@ -10084,7 +10084,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G335" t="n">
-        <v>2.91597747802734</v>
+        <v>2.91597771644592</v>
       </c>
       <c r="H335" t="n">
         <v>2587095</v>
@@ -10142,7 +10142,7 @@
         <v>4.36700010299683</v>
       </c>
       <c r="G337" t="n">
-        <v>2.83989119529724</v>
+        <v>2.8398916721344</v>
       </c>
       <c r="H337" t="n">
         <v>2476410</v>
@@ -10171,7 +10171,7 @@
         <v>4.31199979782104</v>
       </c>
       <c r="G338" t="n">
-        <v>2.80412459373474</v>
+        <v>2.80412483215332</v>
       </c>
       <c r="H338" t="n">
         <v>2947079</v>
@@ -10200,7 +10200,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G339" t="n">
-        <v>2.80022287368774</v>
+        <v>2.8002233505249</v>
       </c>
       <c r="H339" t="n">
         <v>2824441</v>
@@ -10229,7 +10229,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G340" t="n">
-        <v>2.88476252555847</v>
+        <v>2.88476276397705</v>
       </c>
       <c r="H340" t="n">
         <v>2977096</v>
@@ -10258,7 +10258,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G341" t="n">
-        <v>2.96214938163757</v>
+        <v>2.96214914321899</v>
       </c>
       <c r="H341" t="n">
         <v>2619175</v>
@@ -10287,7 +10287,7 @@
         <v>4.6269998550415</v>
       </c>
       <c r="G342" t="n">
-        <v>3.00897121429443</v>
+        <v>3.00897097587585</v>
       </c>
       <c r="H342" t="n">
         <v>2893991</v>
@@ -10345,7 +10345,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.02913093566895</v>
+        <v>3.02913117408752</v>
       </c>
       <c r="H344" t="n">
         <v>3824795</v>
@@ -10374,7 +10374,7 @@
         <v>4.76300001144409</v>
       </c>
       <c r="G345" t="n">
-        <v>3.09741353988647</v>
+        <v>3.09741282463074</v>
       </c>
       <c r="H345" t="n">
         <v>5092398</v>
@@ -10403,7 +10403,7 @@
         <v>4.75099992752075</v>
       </c>
       <c r="G346" t="n">
-        <v>3.0896098613739</v>
+        <v>3.08960938453674</v>
       </c>
       <c r="H346" t="n">
         <v>5127661</v>
@@ -10432,7 +10432,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>3.07595300674438</v>
+        <v>3.07595276832581</v>
       </c>
       <c r="H347" t="n">
         <v>2942590</v>
@@ -10461,7 +10461,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G348" t="n">
-        <v>3.05709433555603</v>
+        <v>3.05709409713745</v>
       </c>
       <c r="H348" t="n">
         <v>7156105</v>
@@ -10490,7 +10490,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>3.11497139930725</v>
+        <v>3.11497163772583</v>
       </c>
       <c r="H349" t="n">
         <v>3060245</v>
@@ -10635,7 +10635,7 @@
         <v>4.71700000762939</v>
       </c>
       <c r="G354" t="n">
-        <v>3.06749939918518</v>
+        <v>3.06749892234802</v>
       </c>
       <c r="H354" t="n">
         <v>2504013</v>
@@ -10664,7 +10664,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>3.11497139930725</v>
+        <v>3.11497163772583</v>
       </c>
       <c r="H355" t="n">
         <v>1626051</v>
@@ -10693,7 +10693,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G356" t="n">
-        <v>3.16959691047668</v>
+        <v>3.16959738731384</v>
       </c>
       <c r="H356" t="n">
         <v>2821934</v>
@@ -10722,7 +10722,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G357" t="n">
-        <v>3.15789198875427</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H357" t="n">
         <v>1742932</v>
@@ -10751,7 +10751,7 @@
         <v>4.86899995803833</v>
       </c>
       <c r="G358" t="n">
-        <v>3.16634559631348</v>
+        <v>3.1663453578949</v>
       </c>
       <c r="H358" t="n">
         <v>2094883</v>
@@ -10780,7 +10780,7 @@
         <v>4.83699989318848</v>
       </c>
       <c r="G359" t="n">
-        <v>3.14553570747375</v>
+        <v>3.14553546905518</v>
       </c>
       <c r="H359" t="n">
         <v>2245367</v>
@@ -10838,7 +10838,7 @@
         <v>5.00400018692017</v>
       </c>
       <c r="G361" t="n">
-        <v>3.25413727760315</v>
+        <v>3.25413751602173</v>
       </c>
       <c r="H361" t="n">
         <v>1842202</v>
@@ -10925,7 +10925,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G364" t="n">
-        <v>3.32697200775146</v>
+        <v>3.32697176933289</v>
       </c>
       <c r="H364" t="n">
         <v>1980411</v>
@@ -10954,7 +10954,7 @@
         <v>5.12599992752075</v>
       </c>
       <c r="G365" t="n">
-        <v>3.3334743976593</v>
+        <v>3.33347463607788</v>
       </c>
       <c r="H365" t="n">
         <v>1692898</v>
@@ -10983,7 +10983,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>3.29055428504944</v>
+        <v>3.29055404663086</v>
       </c>
       <c r="H366" t="n">
         <v>1867370</v>
@@ -11012,7 +11012,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G367" t="n">
-        <v>3.29705786705017</v>
+        <v>3.29705762863159</v>
       </c>
       <c r="H367" t="n">
         <v>1408912</v>
@@ -11041,7 +11041,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G368" t="n">
-        <v>3.35038208961487</v>
+        <v>3.35038304328918</v>
       </c>
       <c r="H368" t="n">
         <v>4112376</v>
@@ -11070,7 +11070,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G369" t="n">
-        <v>3.37769508361816</v>
+        <v>3.37769532203674</v>
       </c>
       <c r="H369" t="n">
         <v>1844080</v>
@@ -11099,7 +11099,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.3295726776123</v>
+        <v>3.32957291603088</v>
       </c>
       <c r="H370" t="n">
         <v>2607705</v>
@@ -11128,7 +11128,7 @@
         <v>5.17399978637695</v>
       </c>
       <c r="G371" t="n">
-        <v>3.36468982696533</v>
+        <v>3.36468911170959</v>
       </c>
       <c r="H371" t="n">
         <v>3253120</v>
@@ -11157,7 +11157,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G372" t="n">
-        <v>3.31136441230774</v>
+        <v>3.31136417388916</v>
       </c>
       <c r="H372" t="n">
         <v>2889659</v>
@@ -11186,7 +11186,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G373" t="n">
-        <v>3.3763952255249</v>
+        <v>3.37639474868774</v>
       </c>
       <c r="H373" t="n">
         <v>3697566</v>
@@ -11273,7 +11273,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G376" t="n">
-        <v>3.4726402759552</v>
+        <v>3.47264099121094</v>
       </c>
       <c r="H376" t="n">
         <v>1857454</v>
@@ -11331,7 +11331,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G378" t="n">
-        <v>3.45053029060364</v>
+        <v>3.45053052902222</v>
       </c>
       <c r="H378" t="n">
         <v>2351824</v>
@@ -11360,7 +11360,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>3.44012546539307</v>
+        <v>3.44012522697449</v>
       </c>
       <c r="H379" t="n">
         <v>1895196</v>
@@ -11389,7 +11389,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G380" t="n">
-        <v>3.44922947883606</v>
+        <v>3.44922971725464</v>
       </c>
       <c r="H380" t="n">
         <v>1754549</v>
@@ -11476,7 +11476,7 @@
         <v>5.08799982070923</v>
       </c>
       <c r="G383" t="n">
-        <v>3.30876278877258</v>
+        <v>3.308762550354</v>
       </c>
       <c r="H383" t="n">
         <v>5272263</v>
@@ -11534,7 +11534,7 @@
         <v>5.08599996566772</v>
       </c>
       <c r="G385" t="n">
-        <v>3.30746293067932</v>
+        <v>3.30746221542358</v>
       </c>
       <c r="H385" t="n">
         <v>1760932</v>
@@ -11563,7 +11563,7 @@
         <v>5.06799983978271</v>
       </c>
       <c r="G386" t="n">
-        <v>3.29575681686401</v>
+        <v>3.29575705528259</v>
       </c>
       <c r="H386" t="n">
         <v>2179242</v>
@@ -11592,7 +11592,7 @@
         <v>5.08599996566772</v>
       </c>
       <c r="G387" t="n">
-        <v>3.30746293067932</v>
+        <v>3.30746221542358</v>
       </c>
       <c r="H387" t="n">
         <v>2188502</v>
@@ -11621,7 +11621,7 @@
         <v>4.95100021362305</v>
       </c>
       <c r="G388" t="n">
-        <v>3.21967077255249</v>
+        <v>3.21967148780823</v>
       </c>
       <c r="H388" t="n">
         <v>3209554</v>
@@ -11650,7 +11650,7 @@
         <v>5</v>
       </c>
       <c r="G389" t="n">
-        <v>3.25153613090515</v>
+        <v>3.25153565406799</v>
       </c>
       <c r="H389" t="n">
         <v>2087897</v>
@@ -11679,7 +11679,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>3.24828433990479</v>
+        <v>3.24828457832336</v>
       </c>
       <c r="H390" t="n">
         <v>4048165</v>
@@ -11737,7 +11737,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G392" t="n">
-        <v>3.30670285224915</v>
+        <v>3.30670261383057</v>
       </c>
       <c r="H392" t="n">
         <v>2056574</v>
@@ -11766,7 +11766,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31347012519836</v>
+        <v>3.31347060203552</v>
       </c>
       <c r="H393" t="n">
         <v>2725352</v>
@@ -11795,7 +11795,7 @@
         <v>4.75699996948242</v>
       </c>
       <c r="G394" t="n">
-        <v>3.21939897537231</v>
+        <v>3.21939945220947</v>
       </c>
       <c r="H394" t="n">
         <v>2650692</v>
@@ -11853,7 +11853,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>3.09622693061829</v>
+        <v>3.09622669219971</v>
       </c>
       <c r="H396" t="n">
         <v>2935650</v>
@@ -11911,7 +11911,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G398" t="n">
-        <v>3.03193330764771</v>
+        <v>3.03193354606628</v>
       </c>
       <c r="H398" t="n">
         <v>9267016</v>
@@ -11940,7 +11940,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>3.01839828491211</v>
+        <v>3.01839876174927</v>
       </c>
       <c r="H399" t="n">
         <v>5346504</v>
@@ -11969,7 +11969,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G400" t="n">
-        <v>3.05359053611755</v>
+        <v>3.05359077453613</v>
       </c>
       <c r="H400" t="n">
         <v>3701214</v>
@@ -11998,7 +11998,7 @@
         <v>4.63800001144409</v>
       </c>
       <c r="G401" t="n">
-        <v>3.13886332511902</v>
+        <v>3.1388635635376</v>
       </c>
       <c r="H401" t="n">
         <v>4000775</v>
@@ -12027,7 +12027,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G402" t="n">
-        <v>3.11856007575989</v>
+        <v>3.11856031417847</v>
       </c>
       <c r="H402" t="n">
         <v>3095485</v>
@@ -12085,7 +12085,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>3.09961032867432</v>
+        <v>3.0996105670929</v>
       </c>
       <c r="H404" t="n">
         <v>1736977</v>
@@ -12114,7 +12114,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G405" t="n">
-        <v>3.06509566307068</v>
+        <v>3.0650954246521</v>
       </c>
       <c r="H405" t="n">
         <v>2327673</v>
@@ -12143,7 +12143,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G406" t="n">
-        <v>3.19841885566711</v>
+        <v>3.19841909408569</v>
       </c>
       <c r="H406" t="n">
         <v>2827673</v>
@@ -12172,7 +12172,7 @@
         <v>4.86299991607666</v>
       </c>
       <c r="G407" t="n">
-        <v>3.29113721847534</v>
+        <v>3.29113698005676</v>
       </c>
       <c r="H407" t="n">
         <v>4461113</v>
@@ -12201,7 +12201,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G408" t="n">
-        <v>3.24579358100891</v>
+        <v>3.24579334259033</v>
       </c>
       <c r="H408" t="n">
         <v>3902612</v>
@@ -12230,7 +12230,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G409" t="n">
-        <v>3.26541924476624</v>
+        <v>3.26541948318481</v>
       </c>
       <c r="H409" t="n">
         <v>4143408</v>
@@ -12259,7 +12259,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G410" t="n">
-        <v>3.23225784301758</v>
+        <v>3.23225808143616</v>
       </c>
       <c r="H410" t="n">
         <v>3867738</v>
@@ -12288,7 +12288,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G411" t="n">
-        <v>3.24511671066284</v>
+        <v>3.24511647224426</v>
       </c>
       <c r="H411" t="n">
         <v>1310689</v>
@@ -12317,7 +12317,7 @@
         <v>4.82299995422363</v>
       </c>
       <c r="G412" t="n">
-        <v>3.26406621932983</v>
+        <v>3.26406598091125</v>
       </c>
       <c r="H412" t="n">
         <v>2369613</v>
@@ -12346,7 +12346,7 @@
         <v>4.89900016784668</v>
       </c>
       <c r="G413" t="n">
-        <v>3.31550097465515</v>
+        <v>3.31550049781799</v>
       </c>
       <c r="H413" t="n">
         <v>2936084</v>
@@ -12462,7 +12462,7 @@
         <v>4.73099994659424</v>
       </c>
       <c r="G417" t="n">
-        <v>3.20180320739746</v>
+        <v>3.2018027305603</v>
       </c>
       <c r="H417" t="n">
         <v>2797354</v>
@@ -12520,7 +12520,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G419" t="n">
-        <v>3.1875913143158</v>
+        <v>3.18759083747864</v>
       </c>
       <c r="H419" t="n">
         <v>1998018</v>
@@ -12578,7 +12578,7 @@
         <v>4.65700006484985</v>
       </c>
       <c r="G421" t="n">
-        <v>3.15172243118286</v>
+        <v>3.15172219276428</v>
       </c>
       <c r="H421" t="n">
         <v>1401951</v>
@@ -12607,7 +12607,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G422" t="n">
-        <v>3.21330833435059</v>
+        <v>3.21330857276917</v>
       </c>
       <c r="H422" t="n">
         <v>1706417</v>
@@ -12636,7 +12636,7 @@
         <v>4.74200010299683</v>
       </c>
       <c r="G423" t="n">
-        <v>3.20924782752991</v>
+        <v>3.20924758911133</v>
       </c>
       <c r="H423" t="n">
         <v>967378</v>
@@ -12665,7 +12665,7 @@
         <v>4.81099987030029</v>
       </c>
       <c r="G424" t="n">
-        <v>3.25594472885132</v>
+        <v>3.25594520568848</v>
       </c>
       <c r="H424" t="n">
         <v>1826570</v>
@@ -12723,7 +12723,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G426" t="n">
-        <v>3.23361110687256</v>
+        <v>3.23361134529114</v>
       </c>
       <c r="H426" t="n">
         <v>1009632</v>
@@ -12752,7 +12752,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G427" t="n">
-        <v>3.19841885566711</v>
+        <v>3.19841909408569</v>
       </c>
       <c r="H427" t="n">
         <v>1835351</v>
@@ -12781,7 +12781,7 @@
         <v>4.7039999961853</v>
       </c>
       <c r="G428" t="n">
-        <v>3.18353033065796</v>
+        <v>3.18353056907654</v>
       </c>
       <c r="H428" t="n">
         <v>1407066</v>
@@ -12810,7 +12810,7 @@
         <v>4.74700021743774</v>
       </c>
       <c r="G429" t="n">
-        <v>3.21263194084167</v>
+        <v>3.2126317024231</v>
       </c>
       <c r="H429" t="n">
         <v>1510889</v>
@@ -12839,7 +12839,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G430" t="n">
-        <v>3.19977331161499</v>
+        <v>3.19977283477783</v>
       </c>
       <c r="H430" t="n">
         <v>1634802</v>
@@ -12868,7 +12868,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>3.25526833534241</v>
+        <v>3.25526809692383</v>
       </c>
       <c r="H431" t="n">
         <v>2483950</v>
@@ -12897,7 +12897,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G432" t="n">
-        <v>3.30534911155701</v>
+        <v>3.30534887313843</v>
       </c>
       <c r="H432" t="n">
         <v>1839177</v>
@@ -12984,7 +12984,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>3.29587483406067</v>
+        <v>3.29587411880493</v>
       </c>
       <c r="H435" t="n">
         <v>1955017</v>
@@ -13042,7 +13042,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G437" t="n">
-        <v>3.26677346229553</v>
+        <v>3.26677322387695</v>
       </c>
       <c r="H437" t="n">
         <v>1711303</v>
@@ -13071,7 +13071,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.26203560829163</v>
+        <v>3.26203584671021</v>
       </c>
       <c r="H438" t="n">
         <v>1301307</v>
@@ -13100,7 +13100,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G439" t="n">
-        <v>3.31279373168945</v>
+        <v>3.31279349327087</v>
       </c>
       <c r="H439" t="n">
         <v>1709004</v>
@@ -13129,7 +13129,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G440" t="n">
-        <v>3.31347012519836</v>
+        <v>3.31347060203552</v>
       </c>
       <c r="H440" t="n">
         <v>941165</v>
@@ -13158,7 +13158,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G441" t="n">
-        <v>3.28504610061646</v>
+        <v>3.2850456237793</v>
       </c>
       <c r="H441" t="n">
         <v>1233016</v>
@@ -13187,7 +13187,7 @@
         <v>4.9210000038147</v>
       </c>
       <c r="G442" t="n">
-        <v>3.33038973808289</v>
+        <v>3.33038997650146</v>
       </c>
       <c r="H442" t="n">
         <v>2566951</v>
@@ -13245,7 +13245,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G444" t="n">
-        <v>3.27963209152222</v>
+        <v>3.27963185310364</v>
       </c>
       <c r="H444" t="n">
         <v>2129347</v>
@@ -13303,7 +13303,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G446" t="n">
-        <v>3.27963209152222</v>
+        <v>3.27963185310364</v>
       </c>
       <c r="H446" t="n">
         <v>944767</v>
@@ -13332,7 +13332,7 @@
         <v>4.97200012207031</v>
       </c>
       <c r="G447" t="n">
-        <v>3.36490511894226</v>
+        <v>3.36490535736084</v>
       </c>
       <c r="H447" t="n">
         <v>1912325</v>
@@ -13361,7 +13361,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G448" t="n">
-        <v>3.34527826309204</v>
+        <v>3.34527802467346</v>
       </c>
       <c r="H448" t="n">
         <v>2299462</v>
@@ -13390,7 +13390,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G449" t="n">
-        <v>3.30670285224915</v>
+        <v>3.30670261383057</v>
       </c>
       <c r="H449" t="n">
         <v>1660537</v>
@@ -13419,7 +13419,7 @@
         <v>4.80299997329712</v>
       </c>
       <c r="G450" t="n">
-        <v>3.25053071975708</v>
+        <v>3.2505304813385</v>
       </c>
       <c r="H450" t="n">
         <v>1784763</v>
@@ -13448,7 +13448,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G451" t="n">
-        <v>3.27015662193298</v>
+        <v>3.27015709877014</v>
       </c>
       <c r="H451" t="n">
         <v>1321199</v>
@@ -13477,7 +13477,7 @@
         <v>4.85099983215332</v>
       </c>
       <c r="G452" t="n">
-        <v>3.28301596641541</v>
+        <v>3.28301525115967</v>
       </c>
       <c r="H452" t="n">
         <v>1483194</v>
@@ -13506,7 +13506,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G453" t="n">
-        <v>3.25729846954346</v>
+        <v>3.25729894638062</v>
       </c>
       <c r="H453" t="n">
         <v>2300362</v>
@@ -13535,7 +13535,7 @@
         <v>4.75500011444092</v>
       </c>
       <c r="G454" t="n">
-        <v>3.21804571151733</v>
+        <v>3.21804594993591</v>
       </c>
       <c r="H454" t="n">
         <v>1335173</v>
@@ -13564,7 +13564,7 @@
         <v>4.79300022125244</v>
       </c>
       <c r="G455" t="n">
-        <v>3.24376368522644</v>
+        <v>3.24376344680786</v>
       </c>
       <c r="H455" t="n">
         <v>1781968</v>
@@ -13593,7 +13593,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G456" t="n">
-        <v>3.28639984130859</v>
+        <v>3.28639960289001</v>
       </c>
       <c r="H456" t="n">
         <v>1593265</v>
@@ -13622,7 +13622,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G457" t="n">
-        <v>3.19368171691895</v>
+        <v>3.19368195533752</v>
       </c>
       <c r="H457" t="n">
         <v>1943294</v>
@@ -13651,7 +13651,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G458" t="n">
-        <v>3.15645980834961</v>
+        <v>3.15645933151245</v>
       </c>
       <c r="H458" t="n">
         <v>3075593</v>
@@ -13680,7 +13680,7 @@
         <v>4.67399978637695</v>
       </c>
       <c r="G459" t="n">
-        <v>3.16322755813599</v>
+        <v>3.16322731971741</v>
       </c>
       <c r="H459" t="n">
         <v>1391304</v>
@@ -13709,7 +13709,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G460" t="n">
-        <v>3.16728782653809</v>
+        <v>3.16728758811951</v>
       </c>
       <c r="H460" t="n">
         <v>1168931</v>
@@ -13738,7 +13738,7 @@
         <v>4.65100002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>3.14766144752502</v>
+        <v>3.14766216278076</v>
       </c>
       <c r="H461" t="n">
         <v>2765596</v>
@@ -13767,7 +13767,7 @@
         <v>4.69099998474121</v>
       </c>
       <c r="G462" t="n">
-        <v>3.17473220825195</v>
+        <v>3.17473196983337</v>
       </c>
       <c r="H462" t="n">
         <v>1001054</v>
@@ -13796,7 +13796,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G463" t="n">
-        <v>3.11314606666565</v>
+        <v>3.11314654350281</v>
       </c>
       <c r="H463" t="n">
         <v>1536584</v>
@@ -13825,7 +13825,7 @@
         <v>4.65399980545044</v>
       </c>
       <c r="G464" t="n">
-        <v>3.14969110488892</v>
+        <v>3.14969158172607</v>
       </c>
       <c r="H464" t="n">
         <v>2108233</v>
@@ -13912,7 +13912,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G467" t="n">
-        <v>3.1916515827179</v>
+        <v>3.19165205955505</v>
       </c>
       <c r="H467" t="n">
         <v>1729164</v>
@@ -14028,7 +14028,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>3.35001611709595</v>
+        <v>3.35001564025879</v>
       </c>
       <c r="H471" t="n">
         <v>1495616</v>
@@ -14057,7 +14057,7 @@
         <v>4.94600009918213</v>
       </c>
       <c r="G472" t="n">
-        <v>3.34730935096741</v>
+        <v>3.34730887413025</v>
       </c>
       <c r="H472" t="n">
         <v>2401792</v>
@@ -14144,7 +14144,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G475" t="n">
-        <v>3.30940961837769</v>
+        <v>3.30940937995911</v>
       </c>
       <c r="H475" t="n">
         <v>1828737</v>
@@ -14202,7 +14202,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>3.24173259735107</v>
+        <v>3.24173283576965</v>
       </c>
       <c r="H477" t="n">
         <v>1901964</v>
@@ -14231,7 +14231,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G478" t="n">
-        <v>3.31008672714233</v>
+        <v>3.3100860118866</v>
       </c>
       <c r="H478" t="n">
         <v>2378226</v>
@@ -14260,7 +14260,7 @@
         <v>4.89300012588501</v>
       </c>
       <c r="G479" t="n">
-        <v>3.31144022941589</v>
+        <v>3.31143999099731</v>
       </c>
       <c r="H479" t="n">
         <v>2157559</v>
@@ -14289,7 +14289,7 @@
         <v>4.77299976348877</v>
       </c>
       <c r="G480" t="n">
-        <v>3.23022723197937</v>
+        <v>3.23022747039795</v>
       </c>
       <c r="H480" t="n">
         <v>1732034</v>
@@ -14318,7 +14318,7 @@
         <v>4.80100011825562</v>
       </c>
       <c r="G481" t="n">
-        <v>3.24917697906494</v>
+        <v>3.24917721748352</v>
       </c>
       <c r="H481" t="n">
         <v>1464371</v>
@@ -14347,7 +14347,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G482" t="n">
-        <v>3.2742178440094</v>
+        <v>3.27421712875366</v>
       </c>
       <c r="H482" t="n">
         <v>1373526</v>
@@ -14376,7 +14376,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>3.24511671066284</v>
+        <v>3.24511647224426</v>
       </c>
       <c r="H483" t="n">
         <v>1486476</v>
@@ -14405,7 +14405,7 @@
         <v>4.67399978637695</v>
       </c>
       <c r="G484" t="n">
-        <v>3.16322755813599</v>
+        <v>3.16322731971741</v>
       </c>
       <c r="H484" t="n">
         <v>2597690</v>
@@ -14434,7 +14434,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G485" t="n">
-        <v>3.1686418056488</v>
+        <v>3.16864156723022</v>
       </c>
       <c r="H485" t="n">
         <v>1484153</v>
@@ -14463,7 +14463,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G486" t="n">
-        <v>3.18623757362366</v>
+        <v>3.18623733520508</v>
       </c>
       <c r="H486" t="n">
         <v>1512230</v>
@@ -14579,7 +14579,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G490" t="n">
-        <v>3.07321715354919</v>
+        <v>3.07321667671204</v>
       </c>
       <c r="H490" t="n">
         <v>2048852</v>
@@ -14608,7 +14608,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G491" t="n">
-        <v>3.09690403938293</v>
+        <v>3.09690380096436</v>
       </c>
       <c r="H491" t="n">
         <v>2371411</v>
@@ -14637,7 +14637,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G492" t="n">
-        <v>3.06847953796387</v>
+        <v>3.06847929954529</v>
       </c>
       <c r="H492" t="n">
         <v>2212633</v>
@@ -14666,7 +14666,7 @@
         <v>4.46700000762939</v>
       </c>
       <c r="G493" t="n">
-        <v>3.02313542366028</v>
+        <v>3.02313590049744</v>
       </c>
       <c r="H493" t="n">
         <v>2373270</v>
@@ -14695,7 +14695,7 @@
         <v>4.42899990081787</v>
       </c>
       <c r="G494" t="n">
-        <v>2.99741840362549</v>
+        <v>2.99741792678833</v>
       </c>
       <c r="H494" t="n">
         <v>1532051</v>
@@ -14724,7 +14724,7 @@
         <v>4.46099996566772</v>
       </c>
       <c r="G495" t="n">
-        <v>3.0190749168396</v>
+        <v>3.01907515525818</v>
       </c>
       <c r="H495" t="n">
         <v>1580807</v>
@@ -14753,7 +14753,7 @@
         <v>4.59100008010864</v>
       </c>
       <c r="G496" t="n">
-        <v>3.10705494880676</v>
+        <v>3.10705542564392</v>
       </c>
       <c r="H496" t="n">
         <v>2125874</v>
@@ -14811,7 +14811,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G498" t="n">
-        <v>3.06171202659607</v>
+        <v>3.06171154975891</v>
       </c>
       <c r="H498" t="n">
         <v>1895816</v>
@@ -14840,7 +14840,7 @@
         <v>4.51100015640259</v>
       </c>
       <c r="G499" t="n">
-        <v>3.05291366577148</v>
+        <v>3.05291390419006</v>
       </c>
       <c r="H499" t="n">
         <v>5324720</v>
@@ -14869,7 +14869,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G500" t="n">
-        <v>3.10096454620361</v>
+        <v>3.10096430778503</v>
       </c>
       <c r="H500" t="n">
         <v>5398178</v>
@@ -14927,7 +14927,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>3.09961032867432</v>
+        <v>3.0996105670929</v>
       </c>
       <c r="H502" t="n">
         <v>2967574</v>
@@ -14956,7 +14956,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G503" t="n">
-        <v>3.13751029968262</v>
+        <v>3.13751006126404</v>
       </c>
       <c r="H503" t="n">
         <v>2998067</v>
@@ -15014,7 +15014,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G505" t="n">
-        <v>3.11314606666565</v>
+        <v>3.11314654350281</v>
       </c>
       <c r="H505" t="n">
         <v>3009630</v>
@@ -15072,7 +15072,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G507" t="n">
-        <v>3.08742833137512</v>
+        <v>3.08742904663086</v>
       </c>
       <c r="H507" t="n">
         <v>2891161</v>
@@ -15101,7 +15101,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G508" t="n">
-        <v>3.11856007575989</v>
+        <v>3.11856031417847</v>
       </c>
       <c r="H508" t="n">
         <v>3410234</v>
@@ -15217,7 +15217,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G512" t="n">
-        <v>3.27895474433899</v>
+        <v>3.27895498275757</v>
       </c>
       <c r="H512" t="n">
         <v>3534102</v>
@@ -15246,7 +15246,7 @@
         <v>4.85900020599365</v>
       </c>
       <c r="G513" t="n">
-        <v>3.28842997550964</v>
+        <v>3.28842973709106</v>
       </c>
       <c r="H513" t="n">
         <v>2192149</v>
@@ -15275,7 +15275,7 @@
         <v>4.93499994277954</v>
       </c>
       <c r="G514" t="n">
-        <v>3.33986449241638</v>
+        <v>3.3398642539978</v>
       </c>
       <c r="H514" t="n">
         <v>3038252</v>
@@ -15304,7 +15304,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G515" t="n">
-        <v>3.26203560829163</v>
+        <v>3.26203584671021</v>
       </c>
       <c r="H515" t="n">
         <v>2936871</v>
@@ -15362,7 +15362,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G517" t="n">
-        <v>3.24308633804321</v>
+        <v>3.24308609962463</v>
       </c>
       <c r="H517" t="n">
         <v>1997692</v>
@@ -15391,7 +15391,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G518" t="n">
-        <v>3.19368171691895</v>
+        <v>3.19368195533752</v>
       </c>
       <c r="H518" t="n">
         <v>2274690</v>
@@ -15420,7 +15420,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G519" t="n">
-        <v>3.21601581573486</v>
+        <v>3.21601510047913</v>
       </c>
       <c r="H519" t="n">
         <v>1641709</v>
@@ -15478,7 +15478,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G521" t="n">
-        <v>3.1598436832428</v>
+        <v>3.15984320640564</v>
       </c>
       <c r="H521" t="n">
         <v>2101028</v>
@@ -15536,7 +15536,7 @@
         <v>4.63399982452393</v>
       </c>
       <c r="G523" t="n">
-        <v>3.13615655899048</v>
+        <v>3.1361563205719</v>
       </c>
       <c r="H523" t="n">
         <v>1235650</v>
@@ -15594,7 +15594,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G525" t="n">
-        <v>3.24308633804321</v>
+        <v>3.24308609962463</v>
       </c>
       <c r="H525" t="n">
         <v>1846766</v>
@@ -15623,7 +15623,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G526" t="n">
-        <v>3.25120782852173</v>
+        <v>3.25120735168457</v>
       </c>
       <c r="H526" t="n">
         <v>2223187</v>
@@ -15652,7 +15652,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G527" t="n">
-        <v>3.20654034614563</v>
+        <v>3.20654106140137</v>
       </c>
       <c r="H527" t="n">
         <v>2520823</v>
@@ -15681,7 +15681,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G528" t="n">
-        <v>3.18623757362366</v>
+        <v>3.18623733520508</v>
       </c>
       <c r="H528" t="n">
         <v>1648716</v>
@@ -15739,7 +15739,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G530" t="n">
-        <v>3.21736884117126</v>
+        <v>3.21736931800842</v>
       </c>
       <c r="H530" t="n">
         <v>2817438</v>
@@ -15768,7 +15768,7 @@
         <v>4.76300001144409</v>
       </c>
       <c r="G531" t="n">
-        <v>3.22346043586731</v>
+        <v>3.22345948219299</v>
       </c>
       <c r="H531" t="n">
         <v>1028637</v>
@@ -15797,7 +15797,7 @@
         <v>4.82299995422363</v>
       </c>
       <c r="G532" t="n">
-        <v>3.26406621932983</v>
+        <v>3.26406598091125</v>
       </c>
       <c r="H532" t="n">
         <v>1349990</v>
@@ -15884,7 +15884,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G535" t="n">
-        <v>3.27083420753479</v>
+        <v>3.27083349227905</v>
       </c>
       <c r="H535" t="n">
         <v>1725682</v>
@@ -15913,7 +15913,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G536" t="n">
-        <v>3.3060257434845</v>
+        <v>3.30602622032166</v>
       </c>
       <c r="H536" t="n">
         <v>1643389</v>
@@ -15942,7 +15942,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G537" t="n">
-        <v>3.37302589416504</v>
+        <v>3.3730263710022</v>
       </c>
       <c r="H537" t="n">
         <v>2305052</v>
@@ -15971,7 +15971,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>3.43799662590027</v>
+        <v>3.43799614906311</v>
       </c>
       <c r="H538" t="n">
         <v>2263118</v>
@@ -16000,7 +16000,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G539" t="n">
-        <v>3.4582998752594</v>
+        <v>3.45829916000366</v>
       </c>
       <c r="H539" t="n">
         <v>1917483</v>
@@ -16058,7 +16058,7 @@
         <v>5.10799980163574</v>
       </c>
       <c r="G541" t="n">
-        <v>3.4569456577301</v>
+        <v>3.45694541931152</v>
       </c>
       <c r="H541" t="n">
         <v>3139338</v>
@@ -16087,7 +16087,7 @@
         <v>5.13199996948242</v>
       </c>
       <c r="G542" t="n">
-        <v>3.47318863868713</v>
+        <v>3.47318840026855</v>
       </c>
       <c r="H542" t="n">
         <v>2196030</v>
@@ -16116,7 +16116,7 @@
         <v>5.0939998626709</v>
       </c>
       <c r="G543" t="n">
-        <v>3.44747161865234</v>
+        <v>3.44747114181519</v>
       </c>
       <c r="H543" t="n">
         <v>2157833</v>
@@ -16145,7 +16145,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G544" t="n">
-        <v>3.44611787796021</v>
+        <v>3.44611740112305</v>
       </c>
       <c r="H544" t="n">
         <v>2699606</v>
@@ -16174,7 +16174,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G545" t="n">
-        <v>3.36084461212158</v>
+        <v>3.360844373703</v>
       </c>
       <c r="H545" t="n">
         <v>2043930</v>
@@ -16203,7 +16203,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G546" t="n">
-        <v>3.38114738464355</v>
+        <v>3.38114714622498</v>
       </c>
       <c r="H546" t="n">
         <v>1085876</v>
@@ -16261,7 +16261,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G548" t="n">
-        <v>3.46506690979004</v>
+        <v>3.4650673866272</v>
       </c>
       <c r="H548" t="n">
         <v>2083576</v>
@@ -16290,7 +16290,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G549" t="n">
-        <v>3.49349188804626</v>
+        <v>3.49349141120911</v>
       </c>
       <c r="H549" t="n">
         <v>2357386</v>
@@ -16348,7 +16348,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G551" t="n">
-        <v>3.46642088890076</v>
+        <v>3.46642065048218</v>
       </c>
       <c r="H551" t="n">
         <v>5238374</v>
@@ -16377,7 +16377,7 @@
         <v>5.13199996948242</v>
       </c>
       <c r="G552" t="n">
-        <v>3.47318863868713</v>
+        <v>3.47318840026855</v>
       </c>
       <c r="H552" t="n">
         <v>2635040</v>
@@ -16406,7 +16406,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G553" t="n">
-        <v>3.52868366241455</v>
+        <v>3.52868413925171</v>
       </c>
       <c r="H553" t="n">
         <v>2232096</v>
@@ -16435,7 +16435,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G554" t="n">
-        <v>3.55033993721008</v>
+        <v>3.55034041404724</v>
       </c>
       <c r="H554" t="n">
         <v>1779745</v>
@@ -16464,7 +16464,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G555" t="n">
-        <v>3.49755239486694</v>
+        <v>3.49755263328552</v>
       </c>
       <c r="H555" t="n">
         <v>2295662</v>
@@ -16493,7 +16493,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>3.52597618103027</v>
+        <v>3.52597641944885</v>
       </c>
       <c r="H556" t="n">
         <v>1458761</v>
@@ -16522,7 +16522,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G557" t="n">
-        <v>3.53003740310669</v>
+        <v>3.53003764152527</v>
       </c>
       <c r="H557" t="n">
         <v>1783120</v>
@@ -16609,7 +16609,7 @@
         <v>5.25</v>
       </c>
       <c r="G560" t="n">
-        <v>3.55304765701294</v>
+        <v>3.5530469417572</v>
       </c>
       <c r="H560" t="n">
         <v>1235834</v>
@@ -16638,7 +16638,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>3.52597618103027</v>
+        <v>3.52597641944885</v>
       </c>
       <c r="H561" t="n">
         <v>1874069</v>
@@ -16667,7 +16667,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>3.52597618103027</v>
+        <v>3.52597641944885</v>
       </c>
       <c r="H562" t="n">
         <v>2322938</v>
@@ -16696,7 +16696,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G563" t="n">
-        <v>3.55169367790222</v>
+        <v>3.55169415473938</v>
       </c>
       <c r="H563" t="n">
         <v>2286330</v>
@@ -16725,7 +16725,7 @@
         <v>5.25</v>
       </c>
       <c r="G564" t="n">
-        <v>3.55304765701294</v>
+        <v>3.5530469417572</v>
       </c>
       <c r="H564" t="n">
         <v>1436011</v>
@@ -16754,7 +16754,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G565" t="n">
-        <v>3.49755239486694</v>
+        <v>3.49755263328552</v>
       </c>
       <c r="H565" t="n">
         <v>2827660</v>
@@ -16783,7 +16783,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G566" t="n">
-        <v>3.56658244132996</v>
+        <v>3.56658267974854</v>
       </c>
       <c r="H566" t="n">
         <v>2847559</v>
@@ -16812,7 +16812,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G567" t="n">
-        <v>3.57335019111633</v>
+        <v>3.57335042953491</v>
       </c>
       <c r="H567" t="n">
         <v>2865590</v>
@@ -16841,7 +16841,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G568" t="n">
-        <v>3.57199740409851</v>
+        <v>3.57199716567993</v>
       </c>
       <c r="H568" t="n">
         <v>2087253</v>
@@ -16870,7 +16870,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G569" t="n">
-        <v>3.51514792442322</v>
+        <v>3.51514840126038</v>
       </c>
       <c r="H569" t="n">
         <v>1833579</v>
@@ -16899,7 +16899,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G570" t="n">
-        <v>3.53545093536377</v>
+        <v>3.53545188903809</v>
       </c>
       <c r="H570" t="n">
         <v>1542313</v>
@@ -16928,7 +16928,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G571" t="n">
-        <v>3.57199740409851</v>
+        <v>3.57199716567993</v>
       </c>
       <c r="H571" t="n">
         <v>1790300</v>
@@ -16986,7 +16986,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G573" t="n">
-        <v>3.48266291618347</v>
+        <v>3.48266315460205</v>
       </c>
       <c r="H573" t="n">
         <v>1783474</v>
@@ -17015,7 +17015,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G574" t="n">
-        <v>3.46100640296936</v>
+        <v>3.46100687980652</v>
       </c>
       <c r="H574" t="n">
         <v>1543318</v>
@@ -17044,7 +17044,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G575" t="n">
-        <v>3.53139066696167</v>
+        <v>3.53139042854309</v>
       </c>
       <c r="H575" t="n">
         <v>2004664</v>
@@ -17073,7 +17073,7 @@
         <v>5.21799993515015</v>
       </c>
       <c r="G576" t="n">
-        <v>3.53139066696167</v>
+        <v>3.53139042854309</v>
       </c>
       <c r="H576" t="n">
         <v>1478815</v>
@@ -17102,7 +17102,7 @@
         <v>5.22800016403198</v>
       </c>
       <c r="G577" t="n">
-        <v>3.53815865516663</v>
+        <v>3.53815841674805</v>
       </c>
       <c r="H577" t="n">
         <v>1120215</v>
@@ -17131,7 +17131,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G578" t="n">
-        <v>3.52868366241455</v>
+        <v>3.52868413925171</v>
       </c>
       <c r="H578" t="n">
         <v>1509818</v>
@@ -17189,7 +17189,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G580" t="n">
-        <v>3.53951191902161</v>
+        <v>3.53951215744019</v>
       </c>
       <c r="H580" t="n">
         <v>1222175</v>
@@ -17218,7 +17218,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G581" t="n">
-        <v>3.52462315559387</v>
+        <v>3.52462291717529</v>
       </c>
       <c r="H581" t="n">
         <v>885610</v>
@@ -17276,7 +17276,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>3.52597618103027</v>
+        <v>3.52597641944885</v>
       </c>
       <c r="H583" t="n">
         <v>1461214</v>
@@ -17305,7 +17305,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G584" t="n">
-        <v>3.57199740409851</v>
+        <v>3.57199716567993</v>
       </c>
       <c r="H584" t="n">
         <v>1630171</v>
@@ -17334,7 +17334,7 @@
         <v>5.30800008773804</v>
       </c>
       <c r="G585" t="n">
-        <v>3.59230041503906</v>
+        <v>3.59230017662048</v>
       </c>
       <c r="H585" t="n">
         <v>1423370</v>
@@ -17363,7 +17363,7 @@
         <v>5.2960000038147</v>
       </c>
       <c r="G586" t="n">
-        <v>3.58417940139771</v>
+        <v>3.58417916297913</v>
       </c>
       <c r="H586" t="n">
         <v>1279020</v>
@@ -17392,7 +17392,7 @@
         <v>5.26599979400635</v>
       </c>
       <c r="G587" t="n">
-        <v>3.56387615203857</v>
+        <v>3.56387567520142</v>
       </c>
       <c r="H587" t="n">
         <v>1702241</v>
@@ -17421,7 +17421,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G588" t="n">
-        <v>3.6044819355011</v>
+        <v>3.60448265075684</v>
       </c>
       <c r="H588" t="n">
         <v>1839170</v>
@@ -17450,7 +17450,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G589" t="n">
-        <v>3.5990674495697</v>
+        <v>3.59906792640686</v>
       </c>
       <c r="H589" t="n">
         <v>1973752</v>
@@ -17479,7 +17479,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G590" t="n">
-        <v>3.55846166610718</v>
+        <v>3.5584614276886</v>
       </c>
       <c r="H590" t="n">
         <v>1762263</v>
@@ -17508,7 +17508,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G591" t="n">
-        <v>3.56658244132996</v>
+        <v>3.56658267974854</v>
       </c>
       <c r="H591" t="n">
         <v>1538701</v>
@@ -17566,7 +17566,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G593" t="n">
-        <v>3.67621946334839</v>
+        <v>3.67621994018555</v>
       </c>
       <c r="H593" t="n">
         <v>2817879</v>
@@ -17595,7 +17595,7 @@
         <v>5.46799993515015</v>
       </c>
       <c r="G594" t="n">
-        <v>3.7005832195282</v>
+        <v>3.70058369636536</v>
       </c>
       <c r="H594" t="n">
         <v>2310453</v>
@@ -17624,7 +17624,7 @@
         <v>5.42600011825562</v>
       </c>
       <c r="G595" t="n">
-        <v>3.67215943336487</v>
+        <v>3.67215919494629</v>
       </c>
       <c r="H595" t="n">
         <v>1706877</v>
@@ -17653,7 +17653,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G596" t="n">
-        <v>3.66133046150208</v>
+        <v>3.6613302230835</v>
       </c>
       <c r="H596" t="n">
         <v>1826392</v>
@@ -17682,7 +17682,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G597" t="n">
-        <v>3.63561344146729</v>
+        <v>3.63561415672302</v>
       </c>
       <c r="H597" t="n">
         <v>1711423</v>
@@ -17711,7 +17711,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>3.65456295013428</v>
+        <v>3.65456366539001</v>
       </c>
       <c r="H598" t="n">
         <v>1477720</v>
@@ -17740,7 +17740,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>3.65456295013428</v>
+        <v>3.65456366539001</v>
       </c>
       <c r="H599" t="n">
         <v>3456376</v>
@@ -17769,7 +17769,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>3.65456295013428</v>
+        <v>3.65456366539001</v>
       </c>
       <c r="H600" t="n">
         <v>1001970</v>
@@ -17798,7 +17798,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.69516968727112</v>
+        <v>3.69516897201538</v>
       </c>
       <c r="H601" t="n">
         <v>1443702</v>
@@ -17885,7 +17885,7 @@
         <v>5.48199987411499</v>
       </c>
       <c r="G604" t="n">
-        <v>3.71005773544312</v>
+        <v>3.71005797386169</v>
       </c>
       <c r="H604" t="n">
         <v>1629370</v>
@@ -17914,7 +17914,7 @@
         <v>5.50799989700317</v>
       </c>
       <c r="G605" t="n">
-        <v>3.72765445709229</v>
+        <v>3.72765374183655</v>
       </c>
       <c r="H605" t="n">
         <v>1275899</v>
@@ -17943,7 +17943,7 @@
         <v>5.5</v>
       </c>
       <c r="G606" t="n">
-        <v>3.72223949432373</v>
+        <v>3.72223997116089</v>
       </c>
       <c r="H606" t="n">
         <v>1602470</v>
@@ -17972,7 +17972,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G607" t="n">
-        <v>3.688401222229</v>
+        <v>3.68840169906616</v>
       </c>
       <c r="H607" t="n">
         <v>1876065</v>
@@ -18001,7 +18001,7 @@
         <v>5.47599983215332</v>
       </c>
       <c r="G608" t="n">
-        <v>3.70599794387817</v>
+        <v>3.70599699020386</v>
       </c>
       <c r="H608" t="n">
         <v>1415141</v>
@@ -18030,7 +18030,7 @@
         <v>5.50400018692017</v>
       </c>
       <c r="G609" t="n">
-        <v>3.72494745254517</v>
+        <v>3.72494673728943</v>
       </c>
       <c r="H609" t="n">
         <v>2248836</v>
@@ -18059,7 +18059,7 @@
         <v>5.43400001525879</v>
       </c>
       <c r="G610" t="n">
-        <v>3.67757320404053</v>
+        <v>3.67757344245911</v>
       </c>
       <c r="H610" t="n">
         <v>2056524</v>
@@ -18175,7 +18175,7 @@
         <v>5.52199983596802</v>
       </c>
       <c r="G614" t="n">
-        <v>3.7371289730072</v>
+        <v>3.73712873458862</v>
       </c>
       <c r="H614" t="n">
         <v>2119896</v>
@@ -18204,7 +18204,7 @@
         <v>5.5460000038147</v>
       </c>
       <c r="G615" t="n">
-        <v>3.75337195396423</v>
+        <v>3.75337171554565</v>
       </c>
       <c r="H615" t="n">
         <v>1536356</v>
@@ -18233,7 +18233,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G616" t="n">
-        <v>3.75201797485352</v>
+        <v>3.75201773643494</v>
       </c>
       <c r="H616" t="n">
         <v>1891956</v>
@@ -18262,7 +18262,7 @@
         <v>5.60799980163574</v>
       </c>
       <c r="G617" t="n">
-        <v>3.79533076286316</v>
+        <v>3.79533100128174</v>
       </c>
       <c r="H617" t="n">
         <v>2151430</v>
@@ -18291,7 +18291,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G618" t="n">
-        <v>3.78856325149536</v>
+        <v>3.78856372833252</v>
       </c>
       <c r="H618" t="n">
         <v>1967546</v>
@@ -18320,7 +18320,7 @@
         <v>5.53200006484985</v>
       </c>
       <c r="G619" t="n">
-        <v>3.74389696121216</v>
+        <v>3.743896484375</v>
       </c>
       <c r="H619" t="n">
         <v>1713013</v>
@@ -18436,7 +18436,7 @@
         <v>5.52600002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>3.7398362159729</v>
+        <v>3.73983597755432</v>
       </c>
       <c r="H623" t="n">
         <v>1474177</v>
@@ -18523,7 +18523,7 @@
         <v>5.5479998588562</v>
       </c>
       <c r="G626" t="n">
-        <v>3.75472497940063</v>
+        <v>3.75472474098206</v>
       </c>
       <c r="H626" t="n">
         <v>1113837</v>
@@ -18552,7 +18552,7 @@
         <v>5.5479998588562</v>
       </c>
       <c r="G627" t="n">
-        <v>3.75472497940063</v>
+        <v>3.75472474098206</v>
       </c>
       <c r="H627" t="n">
         <v>1184740</v>
@@ -18668,7 +18668,7 @@
         <v>5.51399993896484</v>
       </c>
       <c r="G631" t="n">
-        <v>3.73171496391296</v>
+        <v>3.73171448707581</v>
       </c>
       <c r="H631" t="n">
         <v>1085790</v>
@@ -18726,7 +18726,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G633" t="n">
-        <v>3.77908873558044</v>
+        <v>3.77908849716187</v>
       </c>
       <c r="H633" t="n">
         <v>2716436</v>
@@ -18755,7 +18755,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G634" t="n">
-        <v>3.72630071640015</v>
+        <v>3.72630023956299</v>
       </c>
       <c r="H634" t="n">
         <v>1954633</v>
@@ -18784,7 +18784,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G635" t="n">
-        <v>3.70870447158813</v>
+        <v>3.70870471000671</v>
       </c>
       <c r="H635" t="n">
         <v>1383579</v>
@@ -18813,7 +18813,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G636" t="n">
-        <v>3.74254369735718</v>
+        <v>3.74254298210144</v>
       </c>
       <c r="H636" t="n">
         <v>1612433</v>
@@ -18842,7 +18842,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G637" t="n">
-        <v>3.78179574012756</v>
+        <v>3.78179550170898</v>
       </c>
       <c r="H637" t="n">
         <v>2256127</v>
@@ -18871,7 +18871,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G638" t="n">
-        <v>3.81157422065735</v>
+        <v>3.81157350540161</v>
       </c>
       <c r="H638" t="n">
         <v>2561720</v>
@@ -18900,7 +18900,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G639" t="n">
-        <v>3.83864450454712</v>
+        <v>3.8386447429657</v>
       </c>
       <c r="H639" t="n">
         <v>3190537</v>
@@ -18929,7 +18929,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G640" t="n">
-        <v>3.90632128715515</v>
+        <v>3.90632152557373</v>
       </c>
       <c r="H640" t="n">
         <v>2212740</v>
@@ -18958,7 +18958,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>3.90496826171875</v>
+        <v>3.90496802330017</v>
       </c>
       <c r="H641" t="n">
         <v>3062452</v>
@@ -18987,7 +18987,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>3.95403003692627</v>
+        <v>3.95403027534485</v>
       </c>
       <c r="H642" t="n">
         <v>2173043</v>
@@ -19016,7 +19016,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G643" t="n">
-        <v>3.9920220375061</v>
+        <v>3.99202227592468</v>
       </c>
       <c r="H643" t="n">
         <v>1845403</v>
@@ -19045,7 +19045,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>4.03142261505127</v>
+        <v>4.03142213821411</v>
       </c>
       <c r="H644" t="n">
         <v>1861798</v>
@@ -19074,7 +19074,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G645" t="n">
-        <v>4.03423595428467</v>
+        <v>4.03423643112183</v>
       </c>
       <c r="H645" t="n">
         <v>1881231</v>
@@ -19132,7 +19132,7 @@
         <v>5.72200012207031</v>
       </c>
       <c r="G647" t="n">
-        <v>4.02579355239868</v>
+        <v>4.02579307556152</v>
       </c>
       <c r="H647" t="n">
         <v>1241978</v>
@@ -19190,7 +19190,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94699454307556</v>
+        <v>3.9469940662384</v>
       </c>
       <c r="H649" t="n">
         <v>2336188</v>
@@ -19219,7 +19219,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G650" t="n">
-        <v>3.93292355537415</v>
+        <v>3.93292284011841</v>
       </c>
       <c r="H650" t="n">
         <v>1268362</v>
@@ -19248,7 +19248,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G651" t="n">
-        <v>3.98780107498169</v>
+        <v>3.98780083656311</v>
       </c>
       <c r="H651" t="n">
         <v>1959746</v>
@@ -19277,7 +19277,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G652" t="n">
-        <v>4.03564357757568</v>
+        <v>4.03564310073853</v>
       </c>
       <c r="H652" t="n">
         <v>2387126</v>
@@ -19306,7 +19306,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>4.08770704269409</v>
+        <v>4.08770656585693</v>
       </c>
       <c r="H653" t="n">
         <v>2342463</v>
@@ -19364,7 +19364,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G655" t="n">
-        <v>4.13695621490479</v>
+        <v>4.13695669174194</v>
       </c>
       <c r="H655" t="n">
         <v>2552046</v>
@@ -19422,7 +19422,7 @@
         <v>5.89400005340576</v>
       </c>
       <c r="G657" t="n">
-        <v>4.14680624008179</v>
+        <v>4.14680671691895</v>
       </c>
       <c r="H657" t="n">
         <v>1210457</v>
@@ -19451,7 +19451,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G658" t="n">
-        <v>4.14117813110352</v>
+        <v>4.14117765426636</v>
       </c>
       <c r="H658" t="n">
         <v>1808264</v>
@@ -19480,7 +19480,7 @@
         <v>5.83599996566772</v>
       </c>
       <c r="G659" t="n">
-        <v>4.10599946975708</v>
+        <v>4.1060004234314</v>
       </c>
       <c r="H659" t="n">
         <v>1770544</v>
@@ -19509,7 +19509,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G660" t="n">
-        <v>4.13695621490479</v>
+        <v>4.13695669174194</v>
       </c>
       <c r="H660" t="n">
         <v>2035992</v>
@@ -19538,7 +19538,7 @@
         <v>5.92799997329712</v>
       </c>
       <c r="G661" t="n">
-        <v>4.17072725296021</v>
+        <v>4.17072820663452</v>
       </c>
       <c r="H661" t="n">
         <v>2282492</v>
@@ -19567,7 +19567,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>4.15806341171265</v>
+        <v>4.1580638885498</v>
       </c>
       <c r="H662" t="n">
         <v>1559189</v>
@@ -19596,7 +19596,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G663" t="n">
-        <v>4.30721950531006</v>
+        <v>4.3072190284729</v>
       </c>
       <c r="H663" t="n">
         <v>3197524</v>
@@ -19625,7 +19625,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G664" t="n">
-        <v>4.25796937942505</v>
+        <v>4.25796985626221</v>
       </c>
       <c r="H664" t="n">
         <v>2726415</v>
@@ -19712,7 +19712,7 @@
         <v>6.10599994659424</v>
       </c>
       <c r="G667" t="n">
-        <v>4.29596185684204</v>
+        <v>4.2959623336792</v>
       </c>
       <c r="H667" t="n">
         <v>1422499</v>
@@ -19770,7 +19770,7 @@
         <v>6.03800010681152</v>
       </c>
       <c r="G669" t="n">
-        <v>4.24811935424805</v>
+        <v>4.24811983108521</v>
       </c>
       <c r="H669" t="n">
         <v>1609756</v>
@@ -19857,7 +19857,7 @@
         <v>5.89799976348877</v>
       </c>
       <c r="G672" t="n">
-        <v>4.14962100982666</v>
+        <v>4.1496205329895</v>
       </c>
       <c r="H672" t="n">
         <v>1584912</v>
@@ -19886,7 +19886,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24249124526978</v>
+        <v>4.24249172210693</v>
       </c>
       <c r="H673" t="n">
         <v>3177119</v>
@@ -19944,7 +19944,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G675" t="n">
-        <v>4.25937700271606</v>
+        <v>4.25937652587891</v>
       </c>
       <c r="H675" t="n">
         <v>1962436</v>
@@ -19973,7 +19973,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>4.24952745437622</v>
+        <v>4.2495265007019</v>
       </c>
       <c r="H676" t="n">
         <v>1557634</v>
@@ -20002,7 +20002,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G677" t="n">
-        <v>4.30299806594849</v>
+        <v>4.30299758911133</v>
       </c>
       <c r="H677" t="n">
         <v>1999919</v>
@@ -20031,7 +20031,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>4.32691860198975</v>
+        <v>4.3269190788269</v>
       </c>
       <c r="H678" t="n">
         <v>2624174</v>
@@ -20147,7 +20147,7 @@
         <v>6.22800016403198</v>
       </c>
       <c r="G682" t="n">
-        <v>4.38179731369019</v>
+        <v>4.38179683685303</v>
       </c>
       <c r="H682" t="n">
         <v>1578337</v>
@@ -20263,7 +20263,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G686" t="n">
-        <v>4.21434879302979</v>
+        <v>4.21434831619263</v>
       </c>
       <c r="H686" t="n">
         <v>2662580</v>
@@ -20321,7 +20321,7 @@
         <v>6.02199983596802</v>
       </c>
       <c r="G688" t="n">
-        <v>4.23686265945435</v>
+        <v>4.2368631362915</v>
       </c>
       <c r="H688" t="n">
         <v>1209817</v>
@@ -20408,7 +20408,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G691" t="n">
-        <v>4.14117813110352</v>
+        <v>4.14117765426636</v>
       </c>
       <c r="H691" t="n">
         <v>1961556</v>
@@ -20437,7 +20437,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>4.13695621490479</v>
+        <v>4.13695669174194</v>
       </c>
       <c r="H692" t="n">
         <v>1951320</v>
@@ -20495,7 +20495,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G694" t="n">
-        <v>4.02297878265381</v>
+        <v>4.02297925949097</v>
       </c>
       <c r="H694" t="n">
         <v>3651847</v>
@@ -20611,7 +20611,7 @@
         <v>5.7979998588562</v>
       </c>
       <c r="G698" t="n">
-        <v>4.07926368713379</v>
+        <v>4.07926416397095</v>
       </c>
       <c r="H698" t="n">
         <v>1588223</v>
@@ -20640,7 +20640,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>4.10177850723267</v>
+        <v>4.10177803039551</v>
       </c>
       <c r="H699" t="n">
         <v>1720119</v>
@@ -20669,7 +20669,7 @@
         <v>5.83400011062622</v>
       </c>
       <c r="G700" t="n">
-        <v>4.10459280014038</v>
+        <v>4.10459327697754</v>
       </c>
       <c r="H700" t="n">
         <v>1324347</v>
@@ -20698,7 +20698,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G701" t="n">
-        <v>3.93855118751526</v>
+        <v>3.93855166435242</v>
       </c>
       <c r="H701" t="n">
         <v>5230571</v>
@@ -20785,7 +20785,7 @@
         <v>5.6560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97935819625854</v>
+        <v>3.97935795783997</v>
       </c>
       <c r="H704" t="n">
         <v>3234030</v>
@@ -20814,7 +20814,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G705" t="n">
-        <v>3.9920220375061</v>
+        <v>3.99202227592468</v>
       </c>
       <c r="H705" t="n">
         <v>2966146</v>
@@ -20843,7 +20843,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G706" t="n">
-        <v>4.12007141113281</v>
+        <v>4.12007093429565</v>
       </c>
       <c r="H706" t="n">
         <v>1986363</v>
@@ -20872,7 +20872,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G707" t="n">
-        <v>4.03845739364624</v>
+        <v>4.0384578704834</v>
       </c>
       <c r="H707" t="n">
         <v>1576596</v>
@@ -20930,7 +20930,7 @@
         <v>5.72200012207031</v>
       </c>
       <c r="G709" t="n">
-        <v>4.02579355239868</v>
+        <v>4.02579307556152</v>
       </c>
       <c r="H709" t="n">
         <v>1515013</v>
@@ -20959,7 +20959,7 @@
         <v>5.71600008010864</v>
       </c>
       <c r="G710" t="n">
-        <v>4.02157211303711</v>
+        <v>4.02157163619995</v>
       </c>
       <c r="H710" t="n">
         <v>958675</v>
@@ -21046,7 +21046,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G713" t="n">
-        <v>4.03423595428467</v>
+        <v>4.03423643112183</v>
       </c>
       <c r="H713" t="n">
         <v>1504144</v>
@@ -21075,7 +21075,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G714" t="n">
-        <v>4.15524959564209</v>
+        <v>4.15524911880493</v>
       </c>
       <c r="H714" t="n">
         <v>2551492</v>
@@ -21104,7 +21104,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G715" t="n">
-        <v>4.15102815628052</v>
+        <v>4.15102767944336</v>
       </c>
       <c r="H715" t="n">
         <v>2968608</v>
@@ -21133,7 +21133,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G716" t="n">
-        <v>4.15806341171265</v>
+        <v>4.1580638885498</v>
       </c>
       <c r="H716" t="n">
         <v>1279957</v>
@@ -21249,7 +21249,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G720" t="n">
-        <v>4.11866426467896</v>
+        <v>4.11866474151611</v>
       </c>
       <c r="H720" t="n">
         <v>1719641</v>
@@ -21278,7 +21278,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G721" t="n">
-        <v>4.02860736846924</v>
+        <v>4.0286078453064</v>
       </c>
       <c r="H721" t="n">
         <v>2105949</v>
@@ -21394,7 +21394,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G725" t="n">
-        <v>3.96387958526611</v>
+        <v>3.96387934684753</v>
       </c>
       <c r="H725" t="n">
         <v>1624360</v>
@@ -21452,7 +21452,7 @@
         <v>5.70599985122681</v>
       </c>
       <c r="G727" t="n">
-        <v>4.01453638076782</v>
+        <v>4.01453685760498</v>
       </c>
       <c r="H727" t="n">
         <v>2047080</v>
@@ -21481,7 +21481,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>4.00327920913696</v>
+        <v>4.00328016281128</v>
       </c>
       <c r="H728" t="n">
         <v>2005242</v>
@@ -21510,7 +21510,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G729" t="n">
-        <v>4.00327920913696</v>
+        <v>4.00328016281128</v>
       </c>
       <c r="H729" t="n">
         <v>2079379</v>
@@ -21597,7 +21597,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G732" t="n">
-        <v>4.15524959564209</v>
+        <v>4.15524911880493</v>
       </c>
       <c r="H732" t="n">
         <v>3095858</v>
@@ -21626,7 +21626,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G733" t="n">
-        <v>4.11584997177124</v>
+        <v>4.11584949493408</v>
       </c>
       <c r="H733" t="n">
         <v>1880368</v>
@@ -21742,7 +21742,7 @@
         <v>5.85200023651123</v>
       </c>
       <c r="G737" t="n">
-        <v>4.11725616455078</v>
+        <v>4.1172571182251</v>
       </c>
       <c r="H737" t="n">
         <v>1979133</v>
@@ -21771,7 +21771,7 @@
         <v>5.73199987411499</v>
       </c>
       <c r="G738" t="n">
-        <v>4.03282833099365</v>
+        <v>4.03282880783081</v>
       </c>
       <c r="H738" t="n">
         <v>4229823</v>
@@ -21800,7 +21800,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G739" t="n">
-        <v>4.11584997177124</v>
+        <v>4.11584949493408</v>
       </c>
       <c r="H739" t="n">
         <v>2831520</v>
@@ -21829,7 +21829,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G740" t="n">
-        <v>4.1285138130188</v>
+        <v>4.12851333618164</v>
       </c>
       <c r="H740" t="n">
         <v>1788578</v>
@@ -21858,7 +21858,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G741" t="n">
-        <v>4.18339252471924</v>
+        <v>4.18339204788208</v>
       </c>
       <c r="H741" t="n">
         <v>1616448</v>
@@ -21916,7 +21916,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G743" t="n">
-        <v>4.06660032272339</v>
+        <v>4.06660079956055</v>
       </c>
       <c r="H743" t="n">
         <v>1924712</v>
@@ -21945,7 +21945,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G744" t="n">
-        <v>4.01031541824341</v>
+        <v>4.01031494140625</v>
       </c>
       <c r="H744" t="n">
         <v>1958168</v>
@@ -22003,7 +22003,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G746" t="n">
-        <v>4.03845739364624</v>
+        <v>4.0384578704834</v>
       </c>
       <c r="H746" t="n">
         <v>1299311</v>
@@ -22061,7 +22061,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G748" t="n">
-        <v>3.9962432384491</v>
+        <v>3.99624347686768</v>
       </c>
       <c r="H748" t="n">
         <v>1909085</v>
@@ -22090,7 +22090,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G749" t="n">
-        <v>3.9920220375061</v>
+        <v>3.99202227592468</v>
       </c>
       <c r="H749" t="n">
         <v>1654695</v>
@@ -22119,7 +22119,7 @@
         <v>5.67799997329712</v>
       </c>
       <c r="G750" t="n">
-        <v>3.99483704566956</v>
+        <v>3.9948365688324</v>
       </c>
       <c r="H750" t="n">
         <v>3183705</v>
@@ -22148,7 +22148,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G751" t="n">
-        <v>3.96810078620911</v>
+        <v>3.96810102462769</v>
       </c>
       <c r="H751" t="n">
         <v>1754026</v>
@@ -22177,7 +22177,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G752" t="n">
-        <v>4.02297878265381</v>
+        <v>4.02297925949097</v>
       </c>
       <c r="H752" t="n">
         <v>1504461</v>
@@ -22235,7 +22235,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03142261505127</v>
+        <v>4.03142213821411</v>
       </c>
       <c r="H754" t="n">
         <v>1468194</v>
@@ -22264,7 +22264,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G755" t="n">
-        <v>4.03142261505127</v>
+        <v>4.03142213821411</v>
       </c>
       <c r="H755" t="n">
         <v>1178469</v>
@@ -22293,7 +22293,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G756" t="n">
-        <v>4.02297878265381</v>
+        <v>4.02297925949097</v>
       </c>
       <c r="H756" t="n">
         <v>1303279</v>
@@ -22322,7 +22322,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G757" t="n">
-        <v>4.00187206268311</v>
+        <v>4.00187253952026</v>
       </c>
       <c r="H757" t="n">
         <v>2492570</v>
@@ -22351,7 +22351,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G758" t="n">
-        <v>4.06660032272339</v>
+        <v>4.06660079956055</v>
       </c>
       <c r="H758" t="n">
         <v>2043707</v>
@@ -22438,7 +22438,7 @@
         <v>5.8439998626709</v>
       </c>
       <c r="G761" t="n">
-        <v>4.11162805557251</v>
+        <v>4.11162757873535</v>
       </c>
       <c r="H761" t="n">
         <v>1901181</v>
@@ -22467,7 +22467,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G762" t="n">
-        <v>4.15243530273438</v>
+        <v>4.15243482589722</v>
       </c>
       <c r="H762" t="n">
         <v>2701376</v>
@@ -22554,7 +22554,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G765" t="n">
-        <v>4.14821290969849</v>
+        <v>4.14821338653564</v>
       </c>
       <c r="H765" t="n">
         <v>2373233</v>
@@ -22583,7 +22583,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G766" t="n">
-        <v>4.12288570404053</v>
+        <v>4.12288522720337</v>
       </c>
       <c r="H766" t="n">
         <v>1229876</v>
@@ -22612,7 +22612,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G767" t="n">
-        <v>4.18620538711548</v>
+        <v>4.18620586395264</v>
       </c>
       <c r="H767" t="n">
         <v>1902027</v>
@@ -22670,7 +22670,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G769" t="n">
-        <v>4.14117813110352</v>
+        <v>4.14117765426636</v>
       </c>
       <c r="H769" t="n">
         <v>2385144</v>
@@ -22699,7 +22699,7 @@
         <v>5.83400011062622</v>
       </c>
       <c r="G770" t="n">
-        <v>4.10459280014038</v>
+        <v>4.10459327697754</v>
       </c>
       <c r="H770" t="n">
         <v>2359300</v>
@@ -22728,7 +22728,7 @@
         <v>5.82200002670288</v>
       </c>
       <c r="G771" t="n">
-        <v>4.09614992141724</v>
+        <v>4.09615039825439</v>
       </c>
       <c r="H771" t="n">
         <v>1486107</v>
@@ -22786,7 +22786,7 @@
         <v>5.76599979400635</v>
       </c>
       <c r="G773" t="n">
-        <v>4.05675029754639</v>
+        <v>4.05674982070923</v>
       </c>
       <c r="H773" t="n">
         <v>1799150</v>
@@ -22815,7 +22815,7 @@
         <v>5.75</v>
       </c>
       <c r="G774" t="n">
-        <v>4.04549312591553</v>
+        <v>4.04549264907837</v>
       </c>
       <c r="H774" t="n">
         <v>1402877</v>
@@ -22873,7 +22873,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G776" t="n">
-        <v>4.06660032272339</v>
+        <v>4.06660079956055</v>
       </c>
       <c r="H776" t="n">
         <v>1321194</v>
@@ -22931,7 +22931,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G778" t="n">
-        <v>4.05534267425537</v>
+        <v>4.05534315109253</v>
       </c>
       <c r="H778" t="n">
         <v>1765558</v>
@@ -23018,7 +23018,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G781" t="n">
-        <v>3.83864521980286</v>
+        <v>3.83864569664001</v>
       </c>
       <c r="H781" t="n">
         <v>4756331</v>
@@ -23076,7 +23076,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G783" t="n">
-        <v>3.914630651474</v>
+        <v>3.91463041305542</v>
       </c>
       <c r="H783" t="n">
         <v>2410040</v>
@@ -23105,7 +23105,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G784" t="n">
-        <v>3.87663817405701</v>
+        <v>3.87663841247559</v>
       </c>
       <c r="H784" t="n">
         <v>1880712</v>
@@ -23134,7 +23134,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G785" t="n">
-        <v>3.8484947681427</v>
+        <v>3.84849524497986</v>
       </c>
       <c r="H785" t="n">
         <v>1765297</v>
@@ -23163,7 +23163,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G786" t="n">
-        <v>3.78517460823059</v>
+        <v>3.78517508506775</v>
       </c>
       <c r="H786" t="n">
         <v>2931931</v>
@@ -23192,7 +23192,7 @@
         <v>5.43599987030029</v>
       </c>
       <c r="G787" t="n">
-        <v>3.82457375526428</v>
+        <v>3.82457423210144</v>
       </c>
       <c r="H787" t="n">
         <v>3245860</v>
@@ -23221,7 +23221,7 @@
         <v>5.5</v>
       </c>
       <c r="G788" t="n">
-        <v>3.86960172653198</v>
+        <v>3.86960196495056</v>
       </c>
       <c r="H788" t="n">
         <v>1885870</v>
@@ -23250,7 +23250,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G789" t="n">
-        <v>3.82035303115845</v>
+        <v>3.82035279273987</v>
       </c>
       <c r="H789" t="n">
         <v>2128253</v>
@@ -23279,7 +23279,7 @@
         <v>5.43599987030029</v>
       </c>
       <c r="G790" t="n">
-        <v>3.82457375526428</v>
+        <v>3.82457423210144</v>
       </c>
       <c r="H790" t="n">
         <v>2623020</v>
@@ -23308,7 +23308,7 @@
         <v>5.49200010299683</v>
       </c>
       <c r="G791" t="n">
-        <v>3.86397361755371</v>
+        <v>3.86397337913513</v>
       </c>
       <c r="H791" t="n">
         <v>2307388</v>
@@ -23337,7 +23337,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G792" t="n">
-        <v>3.95403003692627</v>
+        <v>3.95403027534485</v>
       </c>
       <c r="H792" t="n">
         <v>3429073</v>
@@ -23366,7 +23366,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G793" t="n">
-        <v>3.93151569366455</v>
+        <v>3.93151545524597</v>
       </c>
       <c r="H793" t="n">
         <v>2352694</v>
@@ -23395,7 +23395,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G794" t="n">
-        <v>3.93855118751526</v>
+        <v>3.93855166435242</v>
       </c>
       <c r="H794" t="n">
         <v>2148060</v>
@@ -23424,7 +23424,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G795" t="n">
-        <v>3.98639416694641</v>
+        <v>3.98639440536499</v>
       </c>
       <c r="H795" t="n">
         <v>7441044</v>
@@ -23453,7 +23453,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G796" t="n">
-        <v>3.95121574401855</v>
+        <v>3.95121598243713</v>
       </c>
       <c r="H796" t="n">
         <v>945346</v>
@@ -23482,7 +23482,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>3.96106553077698</v>
+        <v>3.96106576919556</v>
       </c>
       <c r="H797" t="n">
         <v>1004925</v>
@@ -23540,7 +23540,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91744470596313</v>
+        <v>3.91744422912598</v>
       </c>
       <c r="H799" t="n">
         <v>2867974</v>
@@ -23569,7 +23569,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G800" t="n">
-        <v>3.91040873527527</v>
+        <v>3.91040921211243</v>
       </c>
       <c r="H800" t="n">
         <v>2353232</v>
@@ -23627,7 +23627,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G802" t="n">
-        <v>3.85130953788757</v>
+        <v>3.85131001472473</v>
       </c>
       <c r="H802" t="n">
         <v>2319002</v>
@@ -23656,7 +23656,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>3.92588758468628</v>
+        <v>3.92588686943054</v>
       </c>
       <c r="H803" t="n">
         <v>3693207</v>
@@ -23685,7 +23685,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G804" t="n">
-        <v>3.96810078620911</v>
+        <v>3.96810102462769</v>
       </c>
       <c r="H804" t="n">
         <v>3472905</v>
@@ -23772,7 +23772,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G807" t="n">
-        <v>3.96247315406799</v>
+        <v>3.96247267723083</v>
       </c>
       <c r="H807" t="n">
         <v>3565769</v>
@@ -23801,7 +23801,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G808" t="n">
-        <v>3.9920220375061</v>
+        <v>3.99202227592468</v>
       </c>
       <c r="H808" t="n">
         <v>2720971</v>
@@ -23830,7 +23830,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G809" t="n">
-        <v>3.9962432384491</v>
+        <v>3.99624347686768</v>
       </c>
       <c r="H809" t="n">
         <v>1734134</v>
@@ -23946,7 +23946,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G813" t="n">
-        <v>4.01031541824341</v>
+        <v>4.01031494140625</v>
       </c>
       <c r="H813" t="n">
         <v>1717511</v>
@@ -24033,7 +24033,7 @@
         <v>5.86199998855591</v>
       </c>
       <c r="G816" t="n">
-        <v>4.12429189682007</v>
+        <v>4.12429237365723</v>
       </c>
       <c r="H816" t="n">
         <v>4378895</v>
@@ -24062,7 +24062,7 @@
         <v>6.09800004959106</v>
       </c>
       <c r="G817" t="n">
-        <v>4.29033327102661</v>
+        <v>4.29033374786377</v>
       </c>
       <c r="H817" t="n">
         <v>5442318</v>
@@ -24120,7 +24120,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30581140518188</v>
+        <v>4.30581188201904</v>
       </c>
       <c r="H819" t="n">
         <v>2440838</v>
@@ -24149,7 +24149,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G820" t="n">
-        <v>4.2185697555542</v>
+        <v>4.21856927871704</v>
       </c>
       <c r="H820" t="n">
         <v>3588873</v>
@@ -24178,7 +24178,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G821" t="n">
-        <v>4.18620538711548</v>
+        <v>4.18620586395264</v>
       </c>
       <c r="H821" t="n">
         <v>3181264</v>
@@ -24207,7 +24207,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G822" t="n">
-        <v>4.22841930389404</v>
+        <v>4.22842025756836</v>
       </c>
       <c r="H822" t="n">
         <v>2927455</v>
@@ -24236,7 +24236,7 @@
         <v>6.07800006866455</v>
       </c>
       <c r="G823" t="n">
-        <v>4.27626276016235</v>
+        <v>4.27626180648804</v>
       </c>
       <c r="H823" t="n">
         <v>2652568</v>
@@ -24265,7 +24265,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G824" t="n">
-        <v>4.30018329620361</v>
+        <v>4.30018377304077</v>
       </c>
       <c r="H824" t="n">
         <v>2088908</v>
@@ -24294,7 +24294,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G825" t="n">
-        <v>4.27063417434692</v>
+        <v>4.27063369750977</v>
       </c>
       <c r="H825" t="n">
         <v>1721301</v>
@@ -24381,7 +24381,7 @@
         <v>6.09800004959106</v>
       </c>
       <c r="G828" t="n">
-        <v>4.29033327102661</v>
+        <v>4.29033374786377</v>
       </c>
       <c r="H828" t="n">
         <v>2069651</v>
@@ -24410,7 +24410,7 @@
         <v>6.05800008773804</v>
       </c>
       <c r="G829" t="n">
-        <v>4.26219081878662</v>
+        <v>4.26219129562378</v>
       </c>
       <c r="H829" t="n">
         <v>2297393</v>
@@ -24468,7 +24468,7 @@
         <v>6.10400009155273</v>
       </c>
       <c r="G831" t="n">
-        <v>4.29455471038818</v>
+        <v>4.29455518722534</v>
       </c>
       <c r="H831" t="n">
         <v>1364600</v>
@@ -24555,7 +24555,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>4.32691860198975</v>
+        <v>4.3269190788269</v>
       </c>
       <c r="H834" t="n">
         <v>2639151</v>
@@ -24613,7 +24613,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G836" t="n">
-        <v>4.1285138130188</v>
+        <v>4.12851333618164</v>
       </c>
       <c r="H836" t="n">
         <v>3944534</v>
@@ -24700,7 +24700,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G839" t="n">
-        <v>4.08067226409912</v>
+        <v>4.08067178726196</v>
       </c>
       <c r="H839" t="n">
         <v>4239735</v>
@@ -24729,7 +24729,7 @@
         <v>5.53200006484985</v>
       </c>
       <c r="G840" t="n">
-        <v>3.89211654663086</v>
+        <v>3.89211678504944</v>
       </c>
       <c r="H840" t="n">
         <v>5273255</v>
@@ -24787,7 +24787,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G842" t="n">
-        <v>3.96106553077698</v>
+        <v>3.96106576919556</v>
       </c>
       <c r="H842" t="n">
         <v>3104286</v>
@@ -24845,7 +24845,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G844" t="n">
-        <v>4.08067226409912</v>
+        <v>4.08067178726196</v>
       </c>
       <c r="H844" t="n">
         <v>5643990</v>
@@ -24874,7 +24874,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G845" t="n">
-        <v>3.91744470596313</v>
+        <v>3.91744422912598</v>
       </c>
       <c r="H845" t="n">
         <v>3403862</v>
@@ -24903,7 +24903,7 @@
         <v>5.07399988174438</v>
       </c>
       <c r="G846" t="n">
-        <v>3.5698835849762</v>
+        <v>3.56988382339478</v>
       </c>
       <c r="H846" t="n">
         <v>6000576</v>
@@ -25077,7 +25077,7 @@
         <v>4.44999980926514</v>
       </c>
       <c r="G852" t="n">
-        <v>3.13085961341858</v>
+        <v>3.13086009025574</v>
       </c>
       <c r="H852" t="n">
         <v>5086607</v>
@@ -25106,7 +25106,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G853" t="n">
-        <v>3.15478134155273</v>
+        <v>3.15478181838989</v>
       </c>
       <c r="H853" t="n">
         <v>3240645</v>
@@ -25193,7 +25193,7 @@
         <v>4.25899982452393</v>
       </c>
       <c r="G856" t="n">
-        <v>2.99647927284241</v>
+        <v>2.99647903442383</v>
       </c>
       <c r="H856" t="n">
         <v>4507664</v>
@@ -25222,7 +25222,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G857" t="n">
-        <v>3.21247339248657</v>
+        <v>3.21247363090515</v>
       </c>
       <c r="H857" t="n">
         <v>3721659</v>
@@ -25251,7 +25251,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G858" t="n">
-        <v>3.24483752250671</v>
+        <v>3.24483728408813</v>
       </c>
       <c r="H858" t="n">
         <v>3787328</v>
@@ -25280,7 +25280,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>3.20121622085571</v>
+        <v>3.20121645927429</v>
       </c>
       <c r="H859" t="n">
         <v>5661844</v>
@@ -25309,7 +25309,7 @@
         <v>4.57100009918213</v>
       </c>
       <c r="G860" t="n">
-        <v>3.21599149703979</v>
+        <v>3.21599125862122</v>
       </c>
       <c r="H860" t="n">
         <v>2461394</v>
@@ -25367,7 +25367,7 @@
         <v>4.98899984359741</v>
       </c>
       <c r="G862" t="n">
-        <v>3.51008081436157</v>
+        <v>3.51008105278015</v>
       </c>
       <c r="H862" t="n">
         <v>3920930</v>
@@ -25483,7 +25483,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G866" t="n">
-        <v>3.38555026054382</v>
+        <v>3.38555002212524</v>
       </c>
       <c r="H866" t="n">
         <v>2520981</v>
@@ -25541,7 +25541,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G868" t="n">
-        <v>3.3180079460144</v>
+        <v>3.31800818443298</v>
       </c>
       <c r="H868" t="n">
         <v>2606733</v>
@@ -25570,7 +25570,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G869" t="n">
-        <v>3.3968071937561</v>
+        <v>3.39680743217468</v>
       </c>
       <c r="H869" t="n">
         <v>1149332</v>
@@ -25599,7 +25599,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G870" t="n">
-        <v>3.41228580474854</v>
+        <v>3.41228556632996</v>
       </c>
       <c r="H870" t="n">
         <v>2460427</v>
@@ -25686,7 +25686,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G873" t="n">
-        <v>3.41932153701782</v>
+        <v>3.41932129859924</v>
       </c>
       <c r="H873" t="n">
         <v>1883840</v>
@@ -25715,7 +25715,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G874" t="n">
-        <v>3.42072820663452</v>
+        <v>3.42072868347168</v>
       </c>
       <c r="H874" t="n">
         <v>1580035</v>
@@ -25744,7 +25744,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G875" t="n">
-        <v>3.29408717155457</v>
+        <v>3.29408645629883</v>
       </c>
       <c r="H875" t="n">
         <v>1885170</v>
@@ -25831,7 +25831,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G878" t="n">
-        <v>3.42213535308838</v>
+        <v>3.42213559150696</v>
       </c>
       <c r="H878" t="n">
         <v>1632555</v>
@@ -25860,7 +25860,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G879" t="n">
-        <v>3.41228580474854</v>
+        <v>3.41228556632996</v>
       </c>
       <c r="H879" t="n">
         <v>2283546</v>
@@ -25918,7 +25918,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>3.42635726928711</v>
+        <v>3.42635655403137</v>
       </c>
       <c r="H881" t="n">
         <v>1909832</v>
@@ -25976,7 +25976,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G883" t="n">
-        <v>3.52485609054565</v>
+        <v>3.5248556137085</v>
       </c>
       <c r="H883" t="n">
         <v>2701652</v>
@@ -26005,7 +26005,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G884" t="n">
-        <v>3.54596257209778</v>
+        <v>3.54596281051636</v>
       </c>
       <c r="H884" t="n">
         <v>1901896</v>
@@ -26034,7 +26034,7 @@
         <v>4.90799999237061</v>
       </c>
       <c r="G885" t="n">
-        <v>3.45309233665466</v>
+        <v>3.45309209823608</v>
       </c>
       <c r="H885" t="n">
         <v>2233720</v>
@@ -26063,7 +26063,7 @@
         <v>4.91599988937378</v>
       </c>
       <c r="G886" t="n">
-        <v>3.45872116088867</v>
+        <v>3.45872092247009</v>
       </c>
       <c r="H886" t="n">
         <v>1673122</v>
@@ -26092,7 +26092,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G887" t="n">
-        <v>3.50797033309937</v>
+        <v>3.50797057151794</v>
       </c>
       <c r="H887" t="n">
         <v>939668</v>
@@ -26179,7 +26179,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G890" t="n">
-        <v>3.48264217376709</v>
+        <v>3.48264193534851</v>
       </c>
       <c r="H890" t="n">
         <v>1701329</v>
@@ -26237,7 +26237,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G892" t="n">
-        <v>3.5529990196228</v>
+        <v>3.55299830436707</v>
       </c>
       <c r="H892" t="n">
         <v>3832249</v>
@@ -26266,7 +26266,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G893" t="n">
-        <v>3.57692718505859</v>
+        <v>3.57692742347717</v>
       </c>
       <c r="H893" t="n">
         <v>5729697</v>
@@ -26295,7 +26295,7 @@
         <v>4.67399978637695</v>
       </c>
       <c r="G894" t="n">
-        <v>3.45282053947449</v>
+        <v>3.45282077789307</v>
       </c>
       <c r="H894" t="n">
         <v>5069170</v>
@@ -26382,7 +26382,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.52817130088806</v>
+        <v>3.52817153930664</v>
       </c>
       <c r="H897" t="n">
         <v>1536527</v>
@@ -26440,7 +26440,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G899" t="n">
-        <v>3.5710175037384</v>
+        <v>3.57101726531982</v>
       </c>
       <c r="H899" t="n">
         <v>1897548</v>
@@ -26469,7 +26469,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G900" t="n">
-        <v>3.54442286491394</v>
+        <v>3.5444233417511</v>
       </c>
       <c r="H900" t="n">
         <v>2992412</v>
@@ -26556,7 +26556,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>3.65670990943909</v>
+        <v>3.65671014785767</v>
       </c>
       <c r="H903" t="n">
         <v>2167799</v>
@@ -26614,7 +26614,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G905" t="n">
-        <v>3.82661700248718</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H905" t="n">
         <v>2792947</v>
@@ -26643,7 +26643,7 @@
         <v>5.25</v>
       </c>
       <c r="G906" t="n">
-        <v>3.87832927703857</v>
+        <v>3.87832856178284</v>
       </c>
       <c r="H906" t="n">
         <v>3272857</v>
@@ -26672,7 +26672,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G907" t="n">
-        <v>3.82661700248718</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H907" t="n">
         <v>3358447</v>
@@ -26701,7 +26701,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G908" t="n">
-        <v>3.85247349739075</v>
+        <v>3.85247397422791</v>
       </c>
       <c r="H908" t="n">
         <v>2032208</v>
@@ -26730,7 +26730,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G909" t="n">
-        <v>3.76013255119324</v>
+        <v>3.76013231277466</v>
       </c>
       <c r="H909" t="n">
         <v>3188797</v>
@@ -26788,7 +26788,7 @@
         <v>4.94600009918213</v>
       </c>
       <c r="G911" t="n">
-        <v>3.65375542640686</v>
+        <v>3.65375518798828</v>
       </c>
       <c r="H911" t="n">
         <v>4498942</v>
@@ -26817,7 +26817,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>3.75274467468262</v>
+        <v>3.7527449131012</v>
       </c>
       <c r="H912" t="n">
         <v>4391555</v>
@@ -26846,7 +26846,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G913" t="n">
-        <v>3.82661700248718</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H913" t="n">
         <v>4189234</v>
@@ -26875,7 +26875,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G914" t="n">
-        <v>3.91157150268555</v>
+        <v>3.91157197952271</v>
       </c>
       <c r="H914" t="n">
         <v>3512294</v>
@@ -26904,7 +26904,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G915" t="n">
-        <v>3.88571619987488</v>
+        <v>3.88571643829346</v>
       </c>
       <c r="H915" t="n">
         <v>3188279</v>
@@ -26933,7 +26933,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93373322486877</v>
+        <v>3.93373274803162</v>
       </c>
       <c r="H916" t="n">
         <v>2794030</v>
@@ -26962,7 +26962,7 @@
         <v>5.375</v>
       </c>
       <c r="G917" t="n">
-        <v>3.9706699848175</v>
+        <v>3.97067022323608</v>
       </c>
       <c r="H917" t="n">
         <v>5566875</v>
@@ -26991,7 +26991,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G918" t="n">
-        <v>3.88571619987488</v>
+        <v>3.88571643829346</v>
       </c>
       <c r="H918" t="n">
         <v>2502322</v>
@@ -27020,7 +27020,7 @@
         <v>5.25</v>
       </c>
       <c r="G919" t="n">
-        <v>3.87832927703857</v>
+        <v>3.87832856178284</v>
       </c>
       <c r="H919" t="n">
         <v>2128592</v>
@@ -27078,7 +27078,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G921" t="n">
-        <v>3.79706835746765</v>
+        <v>3.79706859588623</v>
       </c>
       <c r="H921" t="n">
         <v>3095595</v>
@@ -27194,7 +27194,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355423927307</v>
       </c>
       <c r="H925" t="n">
         <v>1571648</v>
@@ -27223,7 +27223,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G926" t="n">
-        <v>3.91526556015015</v>
+        <v>3.91526579856873</v>
       </c>
       <c r="H926" t="n">
         <v>1897590</v>
@@ -27281,7 +27281,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G928" t="n">
-        <v>3.89679741859436</v>
+        <v>3.89679765701294</v>
       </c>
       <c r="H928" t="n">
         <v>1385968</v>
@@ -27310,7 +27310,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G929" t="n">
-        <v>3.93742680549622</v>
+        <v>3.93742775917053</v>
       </c>
       <c r="H929" t="n">
         <v>2225983</v>
@@ -27339,7 +27339,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>3.88202238082886</v>
+        <v>3.88202285766602</v>
       </c>
       <c r="H930" t="n">
         <v>1410213</v>
@@ -27368,7 +27368,7 @@
         <v>5.125</v>
       </c>
       <c r="G931" t="n">
-        <v>3.78598809242249</v>
+        <v>3.78598737716675</v>
       </c>
       <c r="H931" t="n">
         <v>2346143</v>
@@ -27397,7 +27397,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G932" t="n">
-        <v>3.79337501525879</v>
+        <v>3.79337477684021</v>
       </c>
       <c r="H932" t="n">
         <v>2175651</v>
@@ -27426,7 +27426,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G933" t="n">
-        <v>3.79706835746765</v>
+        <v>3.79706859588623</v>
       </c>
       <c r="H933" t="n">
         <v>1504744</v>
@@ -27455,7 +27455,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>3.76751947402954</v>
+        <v>3.76751923561096</v>
       </c>
       <c r="H934" t="n">
         <v>2270850</v>
@@ -27484,7 +27484,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>3.80076193809509</v>
+        <v>3.80076217651367</v>
       </c>
       <c r="H935" t="n">
         <v>2443627</v>
@@ -27513,7 +27513,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G936" t="n">
-        <v>3.80445623397827</v>
+        <v>3.80445647239685</v>
       </c>
       <c r="H936" t="n">
         <v>1769531</v>
@@ -27542,7 +27542,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G937" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355423927307</v>
       </c>
       <c r="H937" t="n">
         <v>2386659</v>
@@ -27571,7 +27571,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G938" t="n">
-        <v>3.90049147605896</v>
+        <v>3.90049076080322</v>
       </c>
       <c r="H938" t="n">
         <v>1613100</v>
@@ -27600,7 +27600,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G939" t="n">
-        <v>3.94850778579712</v>
+        <v>3.9485080242157</v>
       </c>
       <c r="H939" t="n">
         <v>2557114</v>
@@ -27629,7 +27629,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G940" t="n">
-        <v>3.93004059791565</v>
+        <v>3.93004012107849</v>
       </c>
       <c r="H940" t="n">
         <v>1145389</v>
@@ -27658,7 +27658,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G941" t="n">
-        <v>3.91895866394043</v>
+        <v>3.91895890235901</v>
       </c>
       <c r="H941" t="n">
         <v>1621120</v>
@@ -27687,7 +27687,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G942" t="n">
-        <v>3.87463521957397</v>
+        <v>3.87463545799255</v>
       </c>
       <c r="H942" t="n">
         <v>2057182</v>
@@ -27716,7 +27716,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G943" t="n">
-        <v>3.95220136642456</v>
+        <v>3.95220184326172</v>
       </c>
       <c r="H943" t="n">
         <v>3126340</v>
@@ -27745,7 +27745,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G944" t="n">
-        <v>4.07778596878052</v>
+        <v>4.07778549194336</v>
       </c>
       <c r="H944" t="n">
         <v>3399468</v>
@@ -27774,7 +27774,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G945" t="n">
-        <v>4.08517360687256</v>
+        <v>4.0851731300354</v>
       </c>
       <c r="H945" t="n">
         <v>1985088</v>
@@ -27803,7 +27803,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>4.0334620475769</v>
+        <v>4.03346157073975</v>
       </c>
       <c r="H946" t="n">
         <v>2526362</v>
@@ -27890,7 +27890,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>4.0334620475769</v>
+        <v>4.03346157073975</v>
       </c>
       <c r="H949" t="n">
         <v>1923021</v>
@@ -27919,7 +27919,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>3.98544454574585</v>
+        <v>3.98544478416443</v>
       </c>
       <c r="H950" t="n">
         <v>2544347</v>
@@ -27948,7 +27948,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G951" t="n">
-        <v>3.98913812637329</v>
+        <v>3.98913836479187</v>
       </c>
       <c r="H951" t="n">
         <v>1899163</v>
@@ -28006,7 +28006,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>4.10364103317261</v>
+        <v>4.10364151000977</v>
       </c>
       <c r="H953" t="n">
         <v>1188557</v>
@@ -28035,7 +28035,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G954" t="n">
-        <v>4.18120765686035</v>
+        <v>4.18120813369751</v>
       </c>
       <c r="H954" t="n">
         <v>3125503</v>
@@ -28093,7 +28093,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>4.20336961746216</v>
+        <v>4.20337009429932</v>
       </c>
       <c r="H956" t="n">
         <v>2050585</v>
@@ -28122,7 +28122,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>4.18859577178955</v>
+        <v>4.18859481811523</v>
       </c>
       <c r="H957" t="n">
         <v>1720771</v>
@@ -28180,7 +28180,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>4.12210988998413</v>
+        <v>4.12210941314697</v>
       </c>
       <c r="H959" t="n">
         <v>1853234</v>
@@ -28209,7 +28209,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G960" t="n">
-        <v>4.18859577178955</v>
+        <v>4.18859481811523</v>
       </c>
       <c r="H960" t="n">
         <v>1985046</v>
@@ -28325,7 +28325,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G964" t="n">
-        <v>4.11841583251953</v>
+        <v>4.11841535568237</v>
       </c>
       <c r="H964" t="n">
         <v>1601622</v>
@@ -28354,7 +28354,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>4.0334620475769</v>
+        <v>4.03346157073975</v>
       </c>
       <c r="H965" t="n">
         <v>1639295</v>
@@ -28383,7 +28383,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G966" t="n">
-        <v>3.98913812637329</v>
+        <v>3.98913836479187</v>
       </c>
       <c r="H966" t="n">
         <v>1127368</v>
@@ -28412,7 +28412,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G967" t="n">
-        <v>3.95958971977234</v>
+        <v>3.95958948135376</v>
       </c>
       <c r="H967" t="n">
         <v>1898539</v>
@@ -28441,7 +28441,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>3.98544454574585</v>
+        <v>3.98544478416443</v>
       </c>
       <c r="H968" t="n">
         <v>2469349</v>
@@ -28470,7 +28470,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G969" t="n">
-        <v>3.95958971977234</v>
+        <v>3.95958948135376</v>
       </c>
       <c r="H969" t="n">
         <v>1553786</v>
@@ -28499,7 +28499,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G970" t="n">
-        <v>4.04823684692383</v>
+        <v>4.04823637008667</v>
       </c>
       <c r="H970" t="n">
         <v>1456690</v>
@@ -28528,7 +28528,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G971" t="n">
-        <v>4.00760698318481</v>
+        <v>4.00760650634766</v>
       </c>
       <c r="H971" t="n">
         <v>1247670</v>
@@ -28557,7 +28557,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G972" t="n">
-        <v>3.90049147605896</v>
+        <v>3.90049076080322</v>
       </c>
       <c r="H972" t="n">
         <v>2466907</v>
@@ -28586,7 +28586,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G973" t="n">
-        <v>3.99652528762817</v>
+        <v>3.99652552604675</v>
       </c>
       <c r="H973" t="n">
         <v>1022879</v>
@@ -28615,7 +28615,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G974" t="n">
-        <v>3.91895866394043</v>
+        <v>3.91895890235901</v>
       </c>
       <c r="H974" t="n">
         <v>1534527</v>
@@ -28644,7 +28644,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>4.01129961013794</v>
+        <v>4.0113000869751</v>
       </c>
       <c r="H975" t="n">
         <v>1291408</v>
@@ -28673,7 +28673,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G976" t="n">
-        <v>4.00760698318481</v>
+        <v>4.00760650634766</v>
       </c>
       <c r="H976" t="n">
         <v>1962131</v>
@@ -28702,7 +28702,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G977" t="n">
-        <v>4.01129961013794</v>
+        <v>4.0113000869751</v>
       </c>
       <c r="H977" t="n">
         <v>1569022</v>
@@ -28731,7 +28731,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.94112086296082</v>
+        <v>3.94112133979797</v>
       </c>
       <c r="H978" t="n">
         <v>1454082</v>
@@ -28760,7 +28760,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99652528762817</v>
+        <v>3.99652552604675</v>
       </c>
       <c r="H979" t="n">
         <v>1645876</v>
@@ -28789,7 +28789,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G980" t="n">
-        <v>4.00760698318481</v>
+        <v>4.00760650634766</v>
       </c>
       <c r="H980" t="n">
         <v>1519105</v>
@@ -28818,7 +28818,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G981" t="n">
-        <v>3.98913812637329</v>
+        <v>3.98913836479187</v>
       </c>
       <c r="H981" t="n">
         <v>1899740</v>
@@ -28847,7 +28847,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>4.00021934509277</v>
+        <v>4.00021886825562</v>
       </c>
       <c r="H982" t="n">
         <v>2939840</v>
@@ -28876,7 +28876,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G983" t="n">
-        <v>3.93742680549622</v>
+        <v>3.93742775917053</v>
       </c>
       <c r="H983" t="n">
         <v>2526310</v>
@@ -28905,7 +28905,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G984" t="n">
-        <v>3.97805762290955</v>
+        <v>3.97805738449097</v>
       </c>
       <c r="H984" t="n">
         <v>1253572</v>
@@ -28934,7 +28934,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G985" t="n">
-        <v>3.9743640422821</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H985" t="n">
         <v>1083034</v>
@@ -28992,7 +28992,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G987" t="n">
-        <v>3.95220136642456</v>
+        <v>3.95220184326172</v>
       </c>
       <c r="H987" t="n">
         <v>958950</v>
@@ -29079,7 +29079,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G990" t="n">
-        <v>3.97805762290955</v>
+        <v>3.97805738449097</v>
       </c>
       <c r="H990" t="n">
         <v>1250603</v>
@@ -29108,7 +29108,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G991" t="n">
-        <v>3.93373322486877</v>
+        <v>3.93373274803162</v>
       </c>
       <c r="H991" t="n">
         <v>1650357</v>
@@ -29137,7 +29137,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G992" t="n">
-        <v>3.91526556015015</v>
+        <v>3.91526579856873</v>
       </c>
       <c r="H992" t="n">
         <v>1317171</v>
@@ -29195,7 +29195,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G994" t="n">
-        <v>3.79706835746765</v>
+        <v>3.79706859588623</v>
       </c>
       <c r="H994" t="n">
         <v>5985952</v>
@@ -29253,7 +29253,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G996" t="n">
-        <v>3.80815005302429</v>
+        <v>3.80814981460571</v>
       </c>
       <c r="H996" t="n">
         <v>2614866</v>
@@ -29282,7 +29282,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G997" t="n">
-        <v>3.79337501525879</v>
+        <v>3.79337477684021</v>
       </c>
       <c r="H997" t="n">
         <v>1790034</v>
@@ -29311,7 +29311,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355423927307</v>
       </c>
       <c r="H998" t="n">
         <v>2779886</v>
@@ -29340,7 +29340,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355423927307</v>
       </c>
       <c r="H999" t="n">
         <v>2215137</v>
@@ -29369,7 +29369,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.88940978050232</v>
+        <v>3.88940954208374</v>
       </c>
       <c r="H1000" t="n">
         <v>2403958</v>
@@ -29398,7 +29398,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.79706835746765</v>
+        <v>3.79706859588623</v>
       </c>
       <c r="H1001" t="n">
         <v>1891362</v>
@@ -29456,7 +29456,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.77860045433044</v>
+        <v>3.77860021591187</v>
       </c>
       <c r="H1003" t="n">
         <v>1050566</v>
@@ -29485,7 +29485,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.81553673744202</v>
+        <v>3.81553649902344</v>
       </c>
       <c r="H1004" t="n">
         <v>1489183</v>
@@ -29514,7 +29514,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.76013255119324</v>
+        <v>3.76013231277466</v>
       </c>
       <c r="H1005" t="n">
         <v>1739532</v>
@@ -29572,7 +29572,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1007" t="n">
-        <v>3.811842918396</v>
+        <v>3.81184339523315</v>
       </c>
       <c r="H1007" t="n">
         <v>1145488</v>
@@ -29630,7 +29630,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.72319555282593</v>
+        <v>3.72319507598877</v>
       </c>
       <c r="H1009" t="n">
         <v>1279485</v>
@@ -29688,7 +29688,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.56806206703186</v>
+        <v>3.5680627822876</v>
       </c>
       <c r="H1011" t="n">
         <v>2665724</v>
@@ -29717,7 +29717,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.66557502746582</v>
+        <v>3.66557478904724</v>
       </c>
       <c r="H1012" t="n">
         <v>1986330</v>
@@ -29775,7 +29775,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.70103359222412</v>
+        <v>3.7010338306427</v>
       </c>
       <c r="H1014" t="n">
         <v>2774127</v>
@@ -29804,7 +29804,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.83400535583496</v>
+        <v>3.8340048789978</v>
       </c>
       <c r="H1015" t="n">
         <v>2422991</v>
@@ -29833,7 +29833,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.78229379653931</v>
+        <v>3.78229403495789</v>
       </c>
       <c r="H1016" t="n">
         <v>2424479</v>
@@ -29862,7 +29862,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.78229379653931</v>
+        <v>3.78229403495789</v>
       </c>
       <c r="H1017" t="n">
         <v>1109975</v>
@@ -29891,7 +29891,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.90787744522095</v>
+        <v>3.90787792205811</v>
       </c>
       <c r="H1018" t="n">
         <v>3067531</v>
@@ -29920,7 +29920,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.93004059791565</v>
+        <v>3.93004012107849</v>
       </c>
       <c r="H1019" t="n">
         <v>1796510</v>
@@ -29949,7 +29949,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.91895866394043</v>
+        <v>3.91895890235901</v>
       </c>
       <c r="H1020" t="n">
         <v>2327757</v>
@@ -29978,7 +29978,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.93373322486877</v>
+        <v>3.93373274803162</v>
       </c>
       <c r="H1021" t="n">
         <v>1911921</v>
@@ -30007,7 +30007,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.86724805831909</v>
+        <v>3.86724829673767</v>
       </c>
       <c r="H1022" t="n">
         <v>2014417</v>
@@ -30036,7 +30036,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1023" t="n">
-        <v>3.93742680549622</v>
+        <v>3.93742775917053</v>
       </c>
       <c r="H1023" t="n">
         <v>2555555</v>
@@ -30065,7 +30065,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.90049147605896</v>
+        <v>3.90049076080322</v>
       </c>
       <c r="H1024" t="n">
         <v>1912482</v>
@@ -30094,7 +30094,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.93373322486877</v>
+        <v>3.93373274803162</v>
       </c>
       <c r="H1025" t="n">
         <v>1560177</v>
@@ -30123,7 +30123,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.95958971977234</v>
+        <v>3.95958948135376</v>
       </c>
       <c r="H1026" t="n">
         <v>1785365</v>
@@ -30181,7 +30181,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.96328210830688</v>
+        <v>3.96328258514404</v>
       </c>
       <c r="H1028" t="n">
         <v>1394632</v>
@@ -30210,7 +30210,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.9743640422821</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H1029" t="n">
         <v>1375106</v>
@@ -30239,7 +30239,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.99283218383789</v>
+        <v>3.99283194541931</v>
       </c>
       <c r="H1030" t="n">
         <v>1587588</v>
@@ -30268,7 +30268,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.96697592735291</v>
+        <v>3.96697616577148</v>
       </c>
       <c r="H1031" t="n">
         <v>904133</v>
@@ -30297,7 +30297,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G1032" t="n">
-        <v>4.00760698318481</v>
+        <v>4.00760650634766</v>
       </c>
       <c r="H1032" t="n">
         <v>927282</v>
@@ -30326,7 +30326,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.9743640422821</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H1033" t="n">
         <v>2221291</v>
@@ -30355,7 +30355,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.95589590072632</v>
+        <v>3.955894947052</v>
       </c>
       <c r="H1034" t="n">
         <v>2699430</v>
@@ -30384,7 +30384,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.98913812637329</v>
+        <v>3.98913836479187</v>
       </c>
       <c r="H1035" t="n">
         <v>1652889</v>
@@ -30442,7 +30442,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.90787744522095</v>
+        <v>3.90787792205811</v>
       </c>
       <c r="H1037" t="n">
         <v>1571198</v>
@@ -30471,7 +30471,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.94850778579712</v>
+        <v>3.9485080242157</v>
       </c>
       <c r="H1038" t="n">
         <v>1605404</v>
@@ -30500,7 +30500,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.91157150268555</v>
+        <v>3.91157197952271</v>
       </c>
       <c r="H1039" t="n">
         <v>1245963</v>
@@ -30529,7 +30529,7 @@
         <v>5.25</v>
       </c>
       <c r="G1040" t="n">
-        <v>3.87832927703857</v>
+        <v>3.87832856178284</v>
       </c>
       <c r="H1040" t="n">
         <v>1647775</v>
@@ -30616,7 +30616,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1043" t="n">
-        <v>3.811842918396</v>
+        <v>3.81184339523315</v>
       </c>
       <c r="H1043" t="n">
         <v>1959948</v>
@@ -30645,7 +30645,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.75274467468262</v>
+        <v>3.7527449131012</v>
       </c>
       <c r="H1044" t="n">
         <v>1724521</v>
@@ -30674,7 +30674,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.75274467468262</v>
+        <v>3.7527449131012</v>
       </c>
       <c r="H1045" t="n">
         <v>2889221</v>
@@ -30703,7 +30703,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.80076193809509</v>
+        <v>3.80076217651367</v>
       </c>
       <c r="H1046" t="n">
         <v>3242125</v>
@@ -30819,7 +30819,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.78229379653931</v>
+        <v>3.78229403495789</v>
       </c>
       <c r="H1050" t="n">
         <v>1721378</v>
@@ -30848,7 +30848,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.79706835746765</v>
+        <v>3.79706859588623</v>
       </c>
       <c r="H1051" t="n">
         <v>864928</v>
@@ -30906,7 +30906,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.84139204025269</v>
+        <v>3.84139251708984</v>
       </c>
       <c r="H1053" t="n">
         <v>1483934</v>
@@ -30935,7 +30935,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.82661700248718</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H1054" t="n">
         <v>1737746</v>
@@ -30964,7 +30964,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.78968095779419</v>
+        <v>3.78968143463135</v>
       </c>
       <c r="H1055" t="n">
         <v>1338592</v>
@@ -30993,7 +30993,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355423927307</v>
       </c>
       <c r="H1056" t="n">
         <v>2123824</v>
@@ -31022,7 +31022,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.81553673744202</v>
+        <v>3.81553649902344</v>
       </c>
       <c r="H1057" t="n">
         <v>2170667</v>
@@ -31051,7 +31051,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.80445623397827</v>
+        <v>3.80445647239685</v>
       </c>
       <c r="H1058" t="n">
         <v>1626587</v>
@@ -31080,7 +31080,7 @@
         <v>5.125</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.78598809242249</v>
+        <v>3.78598737716675</v>
       </c>
       <c r="H1059" t="n">
         <v>1492843</v>
@@ -31109,7 +31109,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.7121148109436</v>
+        <v>3.71211528778076</v>
       </c>
       <c r="H1060" t="n">
         <v>2056469</v>
@@ -31138,7 +31138,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.81553673744202</v>
+        <v>3.81553649902344</v>
       </c>
       <c r="H1061" t="n">
         <v>2077033</v>
@@ -31167,7 +31167,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.76382541656494</v>
+        <v>3.76382517814636</v>
       </c>
       <c r="H1062" t="n">
         <v>1407675</v>
@@ -31196,7 +31196,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.75274467468262</v>
+        <v>3.7527449131012</v>
       </c>
       <c r="H1063" t="n">
         <v>1476058</v>
@@ -31225,7 +31225,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.75643849372864</v>
+        <v>3.7564389705658</v>
       </c>
       <c r="H1064" t="n">
         <v>1665111</v>
@@ -31312,7 +31312,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.65523266792297</v>
+        <v>3.65523242950439</v>
       </c>
       <c r="H1067" t="n">
         <v>2042790</v>
@@ -31341,7 +31341,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.64341306686401</v>
+        <v>3.64341282844543</v>
       </c>
       <c r="H1068" t="n">
         <v>1798815</v>
@@ -31370,7 +31370,7 @@
         <v>5</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.69364666938782</v>
+        <v>3.69364643096924</v>
       </c>
       <c r="H1069" t="n">
         <v>1936550</v>
@@ -31399,7 +31399,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.72319555282593</v>
+        <v>3.72319507598877</v>
       </c>
       <c r="H1070" t="n">
         <v>2008248</v>
@@ -31428,7 +31428,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.73058271408081</v>
+        <v>3.73058319091797</v>
       </c>
       <c r="H1071" t="n">
         <v>1816077</v>
@@ -31486,7 +31486,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G1073" t="n">
-        <v>3.65818810462952</v>
+        <v>3.65818738937378</v>
       </c>
       <c r="H1073" t="n">
         <v>2521086</v>
@@ -31515,7 +31515,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.67443990707397</v>
+        <v>3.6744396686554</v>
       </c>
       <c r="H1074" t="n">
         <v>1922675</v>
@@ -31544,7 +31544,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.65523266792297</v>
+        <v>3.65523242950439</v>
       </c>
       <c r="H1075" t="n">
         <v>1931556</v>
@@ -31573,7 +31573,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.75274467468262</v>
+        <v>3.7527449131012</v>
       </c>
       <c r="H1076" t="n">
         <v>4162150</v>
@@ -31631,7 +31631,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.77860045433044</v>
+        <v>3.77860021591187</v>
       </c>
       <c r="H1078" t="n">
         <v>2245609</v>
@@ -31689,7 +31689,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.774906873703</v>
+        <v>3.77490735054016</v>
       </c>
       <c r="H1080" t="n">
         <v>2155949</v>
@@ -31747,7 +31747,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.80445623397827</v>
+        <v>3.80445647239685</v>
       </c>
       <c r="H1082" t="n">
         <v>1112150</v>
@@ -31776,7 +31776,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.81553673744202</v>
+        <v>3.81553649902344</v>
       </c>
       <c r="H1083" t="n">
         <v>1123876</v>
@@ -31805,7 +31805,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.82661700248718</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H1084" t="n">
         <v>1656774</v>
@@ -31834,7 +31834,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.75274467468262</v>
+        <v>3.7527449131012</v>
       </c>
       <c r="H1085" t="n">
         <v>2269955</v>
@@ -31863,7 +31863,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.74166393280029</v>
+        <v>3.74166417121887</v>
       </c>
       <c r="H1086" t="n">
         <v>1637484</v>
@@ -31892,7 +31892,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.7121148109436</v>
+        <v>3.71211528778076</v>
       </c>
       <c r="H1087" t="n">
         <v>1534349</v>
@@ -31921,7 +31921,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.70103359222412</v>
+        <v>3.7010338306427</v>
       </c>
       <c r="H1088" t="n">
         <v>1677269</v>
@@ -31950,7 +31950,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.71950173377991</v>
+        <v>3.71950149536133</v>
       </c>
       <c r="H1089" t="n">
         <v>2147591</v>
@@ -31979,7 +31979,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.70103359222412</v>
+        <v>3.7010338306427</v>
       </c>
       <c r="H1090" t="n">
         <v>1683278</v>
@@ -32008,7 +32008,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.72319555282593</v>
+        <v>3.72319507598877</v>
       </c>
       <c r="H1091" t="n">
         <v>3177909</v>
@@ -32037,7 +32037,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.67148447036743</v>
+        <v>3.67148423194885</v>
       </c>
       <c r="H1092" t="n">
         <v>2201932</v>
@@ -32153,7 +32153,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.60204386711121</v>
+        <v>3.60204410552979</v>
       </c>
       <c r="H1096" t="n">
         <v>2719554</v>
@@ -32182,7 +32182,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.65966486930847</v>
+        <v>3.65966463088989</v>
       </c>
       <c r="H1097" t="n">
         <v>3749789</v>
@@ -32211,7 +32211,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.63602542877197</v>
+        <v>3.63602566719055</v>
       </c>
       <c r="H1098" t="n">
         <v>2381518</v>
@@ -32269,7 +32269,7 @@
         <v>5.125</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.78598809242249</v>
+        <v>3.78598737716675</v>
       </c>
       <c r="H1100" t="n">
         <v>4530532</v>
@@ -32356,7 +32356,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1103" t="n">
-        <v>3.87094163894653</v>
+        <v>3.87094187736511</v>
       </c>
       <c r="H1103" t="n">
         <v>2190062</v>
@@ -32385,7 +32385,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.90049147605896</v>
+        <v>3.90049076080322</v>
       </c>
       <c r="H1104" t="n">
         <v>2675850</v>
@@ -32414,7 +32414,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.93373322486877</v>
+        <v>3.93373274803162</v>
       </c>
       <c r="H1105" t="n">
         <v>2497840</v>
@@ -32443,7 +32443,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.94112086296082</v>
+        <v>3.94112133979797</v>
       </c>
       <c r="H1106" t="n">
         <v>2467377</v>
@@ -32472,7 +32472,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.90049147605896</v>
+        <v>3.90049076080322</v>
       </c>
       <c r="H1107" t="n">
         <v>2996418</v>
@@ -32501,7 +32501,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G1108" t="n">
-        <v>3.93742680549622</v>
+        <v>3.93742775917053</v>
       </c>
       <c r="H1108" t="n">
         <v>4601585</v>
@@ -32530,7 +32530,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.93373322486877</v>
+        <v>3.93373274803162</v>
       </c>
       <c r="H1109" t="n">
         <v>3123703</v>
@@ -32588,7 +32588,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.0334620475769</v>
+        <v>4.03346157073975</v>
       </c>
       <c r="H1111" t="n">
         <v>2094736</v>
@@ -32646,7 +32646,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.07409191131592</v>
+        <v>4.07409143447876</v>
       </c>
       <c r="H1113" t="n">
         <v>1946463</v>
@@ -32704,7 +32704,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.10364103317261</v>
+        <v>4.10364151000977</v>
       </c>
       <c r="H1115" t="n">
         <v>2218958</v>
@@ -32762,7 +32762,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.0807409286499</v>
+        <v>4.08074045181274</v>
       </c>
       <c r="H1117" t="n">
         <v>1466310</v>
@@ -32791,7 +32791,7 @@
         <v>5.55600023269653</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.10438060760498</v>
+        <v>4.10438013076782</v>
       </c>
       <c r="H1118" t="n">
         <v>1638396</v>
@@ -32878,7 +32878,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.98913812637329</v>
+        <v>3.98913836479187</v>
       </c>
       <c r="H1121" t="n">
         <v>2065025</v>
@@ -32936,7 +32936,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.95367980003357</v>
+        <v>3.95367908477783</v>
       </c>
       <c r="H1123" t="n">
         <v>4816518</v>
@@ -32965,7 +32965,7 @@
         <v>5.36600017547607</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.96402168273926</v>
+        <v>3.9640212059021</v>
       </c>
       <c r="H1124" t="n">
         <v>1759915</v>
@@ -32994,7 +32994,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.94776964187622</v>
+        <v>3.94776892662048</v>
       </c>
       <c r="H1125" t="n">
         <v>1564931</v>
@@ -33081,7 +33081,7 @@
         <v>5.4060001373291</v>
       </c>
       <c r="G1128" t="n">
-        <v>3.99357080459595</v>
+        <v>3.99357056617737</v>
       </c>
       <c r="H1128" t="n">
         <v>2794257</v>
@@ -33139,7 +33139,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1130" t="n">
-        <v>4.05562353134155</v>
+        <v>4.05562400817871</v>
       </c>
       <c r="H1130" t="n">
         <v>1660238</v>
@@ -33226,7 +33226,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.9994809627533</v>
+        <v>3.99948048591614</v>
       </c>
       <c r="H1133" t="n">
         <v>1193698</v>
@@ -33284,7 +33284,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.9994809627533</v>
+        <v>3.99948048591614</v>
       </c>
       <c r="H1135" t="n">
         <v>1428918</v>
@@ -33313,7 +33313,7 @@
         <v>5.42199993133545</v>
       </c>
       <c r="G1136" t="n">
-        <v>4.00539016723633</v>
+        <v>4.00539064407349</v>
       </c>
       <c r="H1136" t="n">
         <v>1582993</v>
@@ -33371,7 +33371,7 @@
         <v>5.44799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.02459764480591</v>
+        <v>4.02459716796875</v>
       </c>
       <c r="H1138" t="n">
         <v>2263497</v>
@@ -33400,7 +33400,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.00686740875244</v>
+        <v>4.0068678855896</v>
       </c>
       <c r="H1139" t="n">
         <v>4662672</v>
@@ -33429,7 +33429,7 @@
         <v>5.46400022506714</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.03641700744629</v>
+        <v>4.03641748428345</v>
       </c>
       <c r="H1140" t="n">
         <v>2351103</v>
@@ -33458,7 +33458,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1141" t="n">
-        <v>4.08517360687256</v>
+        <v>4.0851731300354</v>
       </c>
       <c r="H1141" t="n">
         <v>2438148</v>
@@ -33516,7 +33516,7 @@
         <v>5.48400020599365</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.05119180679321</v>
+        <v>4.05119228363037</v>
       </c>
       <c r="H1143" t="n">
         <v>3619513</v>
@@ -33574,7 +33574,7 @@
         <v>5.49200010299683</v>
       </c>
       <c r="G1145" t="n">
-        <v>4.05710172653198</v>
+        <v>4.05710124969482</v>
       </c>
       <c r="H1145" t="n">
         <v>1955193</v>
@@ -33603,7 +33603,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1146" t="n">
-        <v>4.0807409286499</v>
+        <v>4.08074045181274</v>
       </c>
       <c r="H1146" t="n">
         <v>2135034</v>
@@ -33632,7 +33632,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G1147" t="n">
-        <v>4.16495609283447</v>
+        <v>4.16495561599731</v>
       </c>
       <c r="H1147" t="n">
         <v>3027890</v>
@@ -33661,7 +33661,7 @@
         <v>5.62599992752075</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.15609073638916</v>
+        <v>4.15609121322632</v>
       </c>
       <c r="H1148" t="n">
         <v>1717707</v>
@@ -33690,7 +33690,7 @@
         <v>5.62599992752075</v>
       </c>
       <c r="G1149" t="n">
-        <v>4.15609073638916</v>
+        <v>4.15609121322632</v>
       </c>
       <c r="H1149" t="n">
         <v>2064703</v>
@@ -33719,7 +33719,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G1150" t="n">
-        <v>4.2063250541687</v>
+        <v>4.20632457733154</v>
       </c>
       <c r="H1150" t="n">
         <v>2615830</v>
@@ -33835,7 +33835,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G1154" t="n">
-        <v>4.20139217376709</v>
+        <v>4.20139169692993</v>
       </c>
       <c r="H1154" t="n">
         <v>1854970</v>
@@ -33922,7 +33922,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1157" t="n">
-        <v>4.18747043609619</v>
+        <v>4.18746995925903</v>
       </c>
       <c r="H1157" t="n">
         <v>1217874</v>
@@ -33951,7 +33951,7 @@
         <v>5.43400001525879</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.20293855667114</v>
+        <v>4.2029390335083</v>
       </c>
       <c r="H1158" t="n">
         <v>1718866</v>
@@ -34038,7 +34038,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1161" t="n">
-        <v>4.26172161102295</v>
+        <v>4.26172113418579</v>
       </c>
       <c r="H1161" t="n">
         <v>2431783</v>
@@ -34067,7 +34067,7 @@
         <v>5.53800010681152</v>
       </c>
       <c r="G1162" t="n">
-        <v>4.2833776473999</v>
+        <v>4.28337812423706</v>
       </c>
       <c r="H1162" t="n">
         <v>2006514</v>
@@ -34154,7 +34154,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.3096752166748</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1165" t="n">
         <v>1393951</v>
@@ -34270,7 +34270,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1169" t="n">
-        <v>4.42414617538452</v>
+        <v>4.42414569854736</v>
       </c>
       <c r="H1169" t="n">
         <v>2741388</v>
@@ -34299,7 +34299,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.38856744766235</v>
+        <v>4.3885669708252</v>
       </c>
       <c r="H1170" t="n">
         <v>1857442</v>
@@ -34328,7 +34328,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1171" t="n">
-        <v>4.37155103683472</v>
+        <v>4.37155151367188</v>
       </c>
       <c r="H1171" t="n">
         <v>2785219</v>
@@ -34357,7 +34357,7 @@
         <v>5.62599992752075</v>
       </c>
       <c r="G1172" t="n">
-        <v>4.35144138336182</v>
+        <v>4.35144186019897</v>
       </c>
       <c r="H1172" t="n">
         <v>1195350</v>
@@ -34589,7 +34589,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.27719068527222</v>
+        <v>4.27719020843506</v>
       </c>
       <c r="H1180" t="n">
         <v>1284403</v>
@@ -34647,7 +34647,7 @@
         <v>5.57800006866455</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.3143162727356</v>
+        <v>4.31431579589844</v>
       </c>
       <c r="H1182" t="n">
         <v>832865</v>
@@ -34676,7 +34676,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.3096752166748</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1183" t="n">
         <v>942466</v>
@@ -34705,7 +34705,7 @@
         <v>5.63600015640259</v>
       </c>
       <c r="G1184" t="n">
-        <v>4.35917663574219</v>
+        <v>4.35917615890503</v>
       </c>
       <c r="H1184" t="n">
         <v>1739013</v>
@@ -34763,7 +34763,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.28801870346069</v>
+        <v>4.28801918029785</v>
       </c>
       <c r="H1186" t="n">
         <v>1427850</v>
@@ -34792,7 +34792,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.32978487014771</v>
+        <v>4.32978582382202</v>
       </c>
       <c r="H1187" t="n">
         <v>1717049</v>
@@ -34821,7 +34821,7 @@
         <v>5.62200021743774</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.34834814071655</v>
+        <v>4.34834861755371</v>
       </c>
       <c r="H1188" t="n">
         <v>1218309</v>
@@ -34850,7 +34850,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.35298871994019</v>
+        <v>4.35298824310303</v>
       </c>
       <c r="H1189" t="n">
         <v>1139569</v>
@@ -34879,7 +34879,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.3096752166748</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1190" t="n">
         <v>1530588</v>
@@ -34937,7 +34937,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.19211053848267</v>
+        <v>4.19211006164551</v>
       </c>
       <c r="H1192" t="n">
         <v>3583053</v>
@@ -35024,7 +35024,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.27719068527222</v>
+        <v>4.27719020843506</v>
       </c>
       <c r="H1195" t="n">
         <v>1798087</v>
@@ -35053,7 +35053,7 @@
         <v>5.63600015640259</v>
       </c>
       <c r="G1196" t="n">
-        <v>4.35917663574219</v>
+        <v>4.35917615890503</v>
       </c>
       <c r="H1196" t="n">
         <v>1203821</v>
@@ -35227,7 +35227,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G1202" t="n">
-        <v>4.43033409118652</v>
+        <v>4.43033361434937</v>
       </c>
       <c r="H1202" t="n">
         <v>865108</v>
@@ -35256,7 +35256,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G1203" t="n">
-        <v>4.39784908294678</v>
+        <v>4.39784955978394</v>
       </c>
       <c r="H1203" t="n">
         <v>679597</v>
@@ -35343,7 +35343,7 @@
         <v>5.73199987411499</v>
       </c>
       <c r="G1206" t="n">
-        <v>4.43342733383179</v>
+        <v>4.43342781066895</v>
       </c>
       <c r="H1206" t="n">
         <v>1019225</v>
@@ -35372,7 +35372,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1207" t="n">
-        <v>4.45817804336548</v>
+        <v>4.45817852020264</v>
       </c>
       <c r="H1207" t="n">
         <v>798913</v>
@@ -35401,7 +35401,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.46591329574585</v>
+        <v>4.46591281890869</v>
       </c>
       <c r="H1208" t="n">
         <v>912025</v>
@@ -35459,7 +35459,7 @@
         <v>5.85799980163574</v>
       </c>
       <c r="G1210" t="n">
-        <v>4.53088283538818</v>
+        <v>4.53088235855103</v>
       </c>
       <c r="H1210" t="n">
         <v>896304</v>
@@ -35517,7 +35517,7 @@
         <v>5.94399976730347</v>
       </c>
       <c r="G1212" t="n">
-        <v>4.59739923477173</v>
+        <v>4.59739971160889</v>
       </c>
       <c r="H1212" t="n">
         <v>1352473</v>
@@ -35575,7 +35575,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.56646156311035</v>
+        <v>4.56646060943604</v>
       </c>
       <c r="H1214" t="n">
         <v>1560619</v>
@@ -35604,7 +35604,7 @@
         <v>5.97599983215332</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.62214994430542</v>
+        <v>4.62214946746826</v>
       </c>
       <c r="H1215" t="n">
         <v>1971571</v>
@@ -35662,7 +35662,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.63761949539185</v>
+        <v>4.63761901855469</v>
       </c>
       <c r="H1217" t="n">
         <v>846788</v>
@@ -35749,7 +35749,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G1220" t="n">
-        <v>4.37928676605225</v>
+        <v>4.37928628921509</v>
       </c>
       <c r="H1220" t="n">
         <v>2263938</v>
@@ -35894,7 +35894,7 @@
         <v>5.68400001525879</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.39630222320557</v>
+        <v>4.39630174636841</v>
       </c>
       <c r="H1225" t="n">
         <v>950072</v>
@@ -35923,7 +35923,7 @@
         <v>5.62400007247925</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.34989452362061</v>
+        <v>4.34989404678345</v>
       </c>
       <c r="H1226" t="n">
         <v>1092880</v>
@@ -35981,7 +35981,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G1228" t="n">
-        <v>4.29884719848633</v>
+        <v>4.29884672164917</v>
       </c>
       <c r="H1228" t="n">
         <v>1302422</v>
@@ -36184,7 +36184,7 @@
         <v>5.62200021743774</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.34834814071655</v>
+        <v>4.34834861755371</v>
       </c>
       <c r="H1235" t="n">
         <v>2086645</v>
@@ -36213,7 +36213,7 @@
         <v>5.67600011825562</v>
       </c>
       <c r="G1236" t="n">
-        <v>4.39011430740356</v>
+        <v>4.39011478424072</v>
       </c>
       <c r="H1236" t="n">
         <v>4396498</v>
@@ -36358,7 +36358,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1241" t="n">
-        <v>4.37619256973267</v>
+        <v>4.37619209289551</v>
       </c>
       <c r="H1241" t="n">
         <v>1426068</v>
@@ -36387,7 +36387,7 @@
         <v>5.65799999237061</v>
       </c>
       <c r="G1242" t="n">
-        <v>4.37619256973267</v>
+        <v>4.37619209289551</v>
       </c>
       <c r="H1242" t="n">
         <v>1439008</v>
@@ -36474,7 +36474,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.28492450714111</v>
+        <v>4.28492498397827</v>
       </c>
       <c r="H1245" t="n">
         <v>1456700</v>
@@ -36503,7 +36503,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.23387718200684</v>
+        <v>4.23387670516968</v>
       </c>
       <c r="H1246" t="n">
         <v>2088691</v>
@@ -36996,7 +36996,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.37155103683472</v>
+        <v>4.37155151367188</v>
       </c>
       <c r="H1263" t="n">
         <v>1329328</v>
@@ -37025,7 +37025,7 @@
         <v>5.62400007247925</v>
       </c>
       <c r="G1264" t="n">
-        <v>4.34989452362061</v>
+        <v>4.34989404678345</v>
       </c>
       <c r="H1264" t="n">
         <v>1336031</v>
@@ -37054,7 +37054,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.27255010604858</v>
+        <v>4.27254962921143</v>
       </c>
       <c r="H1265" t="n">
         <v>2499950</v>
@@ -37083,7 +37083,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1266" t="n">
-        <v>4.24625205993652</v>
+        <v>4.24625253677368</v>
       </c>
       <c r="H1266" t="n">
         <v>2523989</v>
@@ -37112,7 +37112,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G1267" t="n">
-        <v>4.29884719848633</v>
+        <v>4.29884672164917</v>
       </c>
       <c r="H1267" t="n">
         <v>1343978</v>
@@ -37141,7 +37141,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1268" t="n">
-        <v>4.30812835693359</v>
+        <v>4.30812788009644</v>
       </c>
       <c r="H1268" t="n">
         <v>952964</v>
@@ -37286,7 +37286,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1273" t="n">
-        <v>4.36226940155029</v>
+        <v>4.36226987838745</v>
       </c>
       <c r="H1273" t="n">
         <v>889879</v>
@@ -37344,7 +37344,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.35298871994019</v>
+        <v>4.35298824310303</v>
       </c>
       <c r="H1275" t="n">
         <v>910027</v>
@@ -37373,7 +37373,7 @@
         <v>5.60200023651123</v>
       </c>
       <c r="G1276" t="n">
-        <v>4.33287954330444</v>
+        <v>4.33287906646729</v>
       </c>
       <c r="H1276" t="n">
         <v>765113</v>
@@ -37431,7 +37431,7 @@
         <v>5.5460000038147</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.2895655632019</v>
+        <v>4.28956508636475</v>
       </c>
       <c r="H1278" t="n">
         <v>1177276</v>
@@ -37460,7 +37460,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G1279" t="n">
-        <v>4.29884719848633</v>
+        <v>4.29884672164917</v>
       </c>
       <c r="H1279" t="n">
         <v>1079275</v>
@@ -37547,7 +37547,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.35298871994019</v>
+        <v>4.35298824310303</v>
       </c>
       <c r="H1282" t="n">
         <v>1370173</v>
@@ -37576,7 +37576,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G1283" t="n">
-        <v>4.33906650543213</v>
+        <v>4.33906698226929</v>
       </c>
       <c r="H1283" t="n">
         <v>1777724</v>
@@ -37779,7 +37779,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G1290" t="n">
-        <v>4.31276988983154</v>
+        <v>4.31276941299438</v>
       </c>
       <c r="H1290" t="n">
         <v>1233501</v>
@@ -37808,7 +37808,7 @@
         <v>5.63600015640259</v>
       </c>
       <c r="G1291" t="n">
-        <v>4.35917663574219</v>
+        <v>4.35917615890503</v>
       </c>
       <c r="H1291" t="n">
         <v>1114087</v>
@@ -37837,7 +37837,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1292" t="n">
-        <v>4.51850700378418</v>
+        <v>4.51850748062134</v>
       </c>
       <c r="H1292" t="n">
         <v>2866024</v>
@@ -37895,7 +37895,7 @@
         <v>5.76599979400635</v>
       </c>
       <c r="G1294" t="n">
-        <v>4.45972537994385</v>
+        <v>4.45972490310669</v>
       </c>
       <c r="H1294" t="n">
         <v>1431091</v>
@@ -37924,7 +37924,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1295" t="n">
-        <v>4.46591329574585</v>
+        <v>4.46591281890869</v>
       </c>
       <c r="H1295" t="n">
         <v>1753198</v>
@@ -37982,7 +37982,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1297" t="n">
-        <v>4.45663118362427</v>
+        <v>4.45663070678711</v>
       </c>
       <c r="H1297" t="n">
         <v>1267446</v>
@@ -38069,7 +38069,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1300" t="n">
-        <v>4.48602294921875</v>
+        <v>4.48602247238159</v>
       </c>
       <c r="H1300" t="n">
         <v>1465334</v>
@@ -38098,7 +38098,7 @@
         <v>5.82200002670288</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.50303888320923</v>
+        <v>4.50303840637207</v>
       </c>
       <c r="H1301" t="n">
         <v>3253697</v>
@@ -38185,7 +38185,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1304" t="n">
-        <v>4.52469491958618</v>
+        <v>4.52469444274902</v>
       </c>
       <c r="H1304" t="n">
         <v>1298324</v>
@@ -38243,7 +38243,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1306" t="n">
-        <v>4.54789876937866</v>
+        <v>4.5478982925415</v>
       </c>
       <c r="H1306" t="n">
         <v>631434</v>
@@ -38301,7 +38301,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1308" t="n">
-        <v>4.66700983047485</v>
+        <v>4.66701030731201</v>
       </c>
       <c r="H1308" t="n">
         <v>1134168</v>
@@ -38330,7 +38330,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.68093204498291</v>
+        <v>4.68093252182007</v>
       </c>
       <c r="H1309" t="n">
         <v>1125437</v>
@@ -38417,7 +38417,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G1312" t="n">
-        <v>4.62524366378784</v>
+        <v>4.625244140625</v>
       </c>
       <c r="H1312" t="n">
         <v>1162606</v>
@@ -38446,7 +38446,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1313" t="n">
-        <v>4.51850700378418</v>
+        <v>4.51850748062134</v>
       </c>
       <c r="H1313" t="n">
         <v>1666783</v>
@@ -38533,7 +38533,7 @@
         <v>5.82200002670288</v>
       </c>
       <c r="G1316" t="n">
-        <v>4.50303888320923</v>
+        <v>4.50303840637207</v>
       </c>
       <c r="H1316" t="n">
         <v>1805777</v>
@@ -38649,7 +38649,7 @@
         <v>5.89200019836426</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.55718040466309</v>
+        <v>4.55717992782593</v>
       </c>
       <c r="H1320" t="n">
         <v>517814</v>
@@ -38736,7 +38736,7 @@
         <v>5.93800020217896</v>
       </c>
       <c r="G1323" t="n">
-        <v>4.59275913238525</v>
+        <v>4.5927586555481</v>
       </c>
       <c r="H1323" t="n">
         <v>932007</v>
@@ -38765,7 +38765,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G1324" t="n">
-        <v>4.51541376113892</v>
+        <v>4.51541328430176</v>
       </c>
       <c r="H1324" t="n">
         <v>1004702</v>
@@ -38823,7 +38823,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1326" t="n">
-        <v>4.45817804336548</v>
+        <v>4.45817852020264</v>
       </c>
       <c r="H1326" t="n">
         <v>1563858</v>
@@ -38968,7 +38968,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.56646156311035</v>
+        <v>4.56646060943604</v>
       </c>
       <c r="H1331" t="n">
         <v>1234389</v>
@@ -39055,7 +39055,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G1334" t="n">
-        <v>4.39784908294678</v>
+        <v>4.39784955978394</v>
       </c>
       <c r="H1334" t="n">
         <v>1292083</v>
@@ -39084,7 +39084,7 @@
         <v>5.58199977874756</v>
       </c>
       <c r="G1335" t="n">
-        <v>4.31740999221802</v>
+        <v>4.31740951538086</v>
       </c>
       <c r="H1335" t="n">
         <v>1411080</v>
@@ -39171,7 +39171,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.43188047409058</v>
+        <v>4.43188095092773</v>
       </c>
       <c r="H1338" t="n">
         <v>1465529</v>
@@ -39258,7 +39258,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.38856744766235</v>
+        <v>4.3885669708252</v>
       </c>
       <c r="H1341" t="n">
         <v>1355316</v>
@@ -39287,7 +39287,7 @@
         <v>5.63600015640259</v>
       </c>
       <c r="G1342" t="n">
-        <v>4.35917663574219</v>
+        <v>4.35917615890503</v>
       </c>
       <c r="H1342" t="n">
         <v>1001161</v>
@@ -39316,7 +39316,7 @@
         <v>5.64400005340576</v>
       </c>
       <c r="G1343" t="n">
-        <v>4.36536359786987</v>
+        <v>4.36536407470703</v>
       </c>
       <c r="H1343" t="n">
         <v>962909</v>
@@ -39345,7 +39345,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.35453605651855</v>
+        <v>4.3545355796814</v>
       </c>
       <c r="H1344" t="n">
         <v>962286</v>
@@ -39577,7 +39577,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.32978487014771</v>
+        <v>4.32978582382202</v>
       </c>
       <c r="H1352" t="n">
         <v>1858705</v>
@@ -39925,7 +39925,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G1364" t="n">
-        <v>4.28801870346069</v>
+        <v>4.28801918029785</v>
       </c>
       <c r="H1364" t="n">
         <v>3197624</v>
@@ -40012,7 +40012,7 @@
         <v>5.48799991607666</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.24470520019531</v>
+        <v>4.24470567703247</v>
       </c>
       <c r="H1367" t="n">
         <v>1259036</v>
@@ -40099,7 +40099,7 @@
         <v>5.73199987411499</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.43342733383179</v>
+        <v>4.43342781066895</v>
       </c>
       <c r="H1370" t="n">
         <v>1306736</v>
@@ -40128,7 +40128,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G1371" t="n">
-        <v>4.45817804336548</v>
+        <v>4.45817852020264</v>
       </c>
       <c r="H1371" t="n">
         <v>1138919</v>
@@ -40157,7 +40157,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G1372" t="n">
-        <v>4.48602294921875</v>
+        <v>4.48602247238159</v>
       </c>
       <c r="H1372" t="n">
         <v>1019198</v>
@@ -40360,7 +40360,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.68711948394775</v>
+        <v>4.68711996078491</v>
       </c>
       <c r="H1379" t="n">
         <v>1520621</v>
@@ -40476,7 +40476,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.79153633117676</v>
+        <v>4.7915358543396</v>
       </c>
       <c r="H1383" t="n">
         <v>1874085</v>
@@ -40505,7 +40505,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>4.83020830154419</v>
+        <v>4.83020782470703</v>
       </c>
       <c r="H1384" t="n">
         <v>3183045</v>
@@ -40534,7 +40534,7 @@
         <v>6.375</v>
       </c>
       <c r="G1385" t="n">
-        <v>4.93075704574585</v>
+        <v>4.93075752258301</v>
       </c>
       <c r="H1385" t="n">
         <v>2260746</v>
@@ -40563,7 +40563,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.87274885177612</v>
+        <v>4.87274837493896</v>
       </c>
       <c r="H1386" t="n">
         <v>3249152</v>
@@ -40621,7 +40621,7 @@
         <v>6.16499996185303</v>
       </c>
       <c r="G1388" t="n">
-        <v>4.76833248138428</v>
+        <v>4.76833295822144</v>
       </c>
       <c r="H1388" t="n">
         <v>1578523</v>
@@ -40969,7 +40969,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.83020830154419</v>
+        <v>4.83020782470703</v>
       </c>
       <c r="H1400" t="n">
         <v>1446658</v>
@@ -41056,7 +41056,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.87274885177612</v>
+        <v>4.87274837493896</v>
       </c>
       <c r="H1403" t="n">
         <v>1242481</v>
@@ -41085,7 +41085,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1404" t="n">
-        <v>4.88821792602539</v>
+        <v>4.88821744918823</v>
       </c>
       <c r="H1404" t="n">
         <v>1769932</v>
@@ -41114,7 +41114,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.88821792602539</v>
+        <v>4.88821744918823</v>
       </c>
       <c r="H1405" t="n">
         <v>1082943</v>
@@ -41317,7 +41317,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1412" t="n">
-        <v>4.88334941864014</v>
+        <v>4.88334989547729</v>
       </c>
       <c r="H1412" t="n">
         <v>884522</v>
@@ -41375,7 +41375,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1414" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909557342529</v>
       </c>
       <c r="H1414" t="n">
         <v>1962697</v>
@@ -41404,7 +41404,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>4.81462717056274</v>
+        <v>4.8146276473999</v>
       </c>
       <c r="H1415" t="n">
         <v>1272371</v>
@@ -41491,7 +41491,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1418" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909557342529</v>
       </c>
       <c r="H1418" t="n">
         <v>620812</v>
@@ -41607,7 +41607,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1422" t="n">
-        <v>4.50335454940796</v>
+        <v>4.5033540725708</v>
       </c>
       <c r="H1422" t="n">
         <v>2055692</v>
@@ -41665,7 +41665,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1424" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1424" t="n">
         <v>1270670</v>
@@ -41694,7 +41694,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.40633392333984</v>
+        <v>4.406334400177</v>
       </c>
       <c r="H1425" t="n">
         <v>2381256</v>
@@ -41781,7 +41781,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G1428" t="n">
-        <v>4.45080137252808</v>
+        <v>4.45080184936523</v>
       </c>
       <c r="H1428" t="n">
         <v>1316031</v>
@@ -41868,7 +41868,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.26888847351074</v>
+        <v>4.2688889503479</v>
       </c>
       <c r="H1431" t="n">
         <v>2802660</v>
@@ -41926,7 +41926,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1433" t="n">
-        <v>4.43463182449341</v>
+        <v>4.43463134765625</v>
       </c>
       <c r="H1433" t="n">
         <v>1570844</v>
@@ -42042,7 +42042,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1437" t="n">
-        <v>4.52760887145996</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1437" t="n">
         <v>1165445</v>
@@ -42071,7 +42071,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1438" t="n">
-        <v>4.52760887145996</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1438" t="n">
         <v>713087</v>
@@ -42158,7 +42158,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1441" t="n">
-        <v>4.43463182449341</v>
+        <v>4.43463134765625</v>
       </c>
       <c r="H1441" t="n">
         <v>1049671</v>
@@ -42187,7 +42187,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1442" t="n">
-        <v>4.41441917419434</v>
+        <v>4.41441869735718</v>
       </c>
       <c r="H1442" t="n">
         <v>1233053</v>
@@ -42245,7 +42245,7 @@
         <v>5.5</v>
       </c>
       <c r="G1444" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1444" t="n">
         <v>813805</v>
@@ -42390,7 +42390,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G1449" t="n">
-        <v>4.45080137252808</v>
+        <v>4.45080184936523</v>
       </c>
       <c r="H1449" t="n">
         <v>725498</v>
@@ -42448,7 +42448,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G1451" t="n">
-        <v>4.20016574859619</v>
+        <v>4.20016622543335</v>
       </c>
       <c r="H1451" t="n">
         <v>1487711</v>
@@ -42477,7 +42477,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>4.27293062210083</v>
+        <v>4.27293109893799</v>
       </c>
       <c r="H1452" t="n">
         <v>787321</v>
@@ -42506,7 +42506,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.27293062210083</v>
+        <v>4.27293109893799</v>
       </c>
       <c r="H1453" t="n">
         <v>768600</v>
@@ -42535,7 +42535,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1454" t="n">
-        <v>4.39824867248535</v>
+        <v>4.39824914932251</v>
       </c>
       <c r="H1454" t="n">
         <v>1670735</v>
@@ -42564,7 +42564,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.41441917419434</v>
+        <v>4.41441869735718</v>
       </c>
       <c r="H1455" t="n">
         <v>1501879</v>
@@ -42651,7 +42651,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1458" t="n">
-        <v>4.43463182449341</v>
+        <v>4.43463134765625</v>
       </c>
       <c r="H1458" t="n">
         <v>685505</v>
@@ -42680,7 +42680,7 @@
         <v>5.5</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1459" t="n">
         <v>477914</v>
@@ -42796,7 +42796,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1463" t="n">
-        <v>4.45888662338257</v>
+        <v>4.45888614654541</v>
       </c>
       <c r="H1463" t="n">
         <v>804156</v>
@@ -42912,7 +42912,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1467" t="n">
-        <v>4.43463182449341</v>
+        <v>4.43463134765625</v>
       </c>
       <c r="H1467" t="n">
         <v>766608</v>
@@ -42970,7 +42970,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G1469" t="n">
-        <v>4.57611894607544</v>
+        <v>4.5761194229126</v>
       </c>
       <c r="H1469" t="n">
         <v>984917</v>
@@ -43057,7 +43057,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1472" t="n">
-        <v>4.56803464889526</v>
+        <v>4.56803417205811</v>
       </c>
       <c r="H1472" t="n">
         <v>1539554</v>
@@ -43115,7 +43115,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1474" t="n">
-        <v>4.45888662338257</v>
+        <v>4.45888614654541</v>
       </c>
       <c r="H1474" t="n">
         <v>840017</v>
@@ -43202,7 +43202,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.26888847351074</v>
+        <v>4.2688889503479</v>
       </c>
       <c r="H1477" t="n">
         <v>678424</v>
@@ -43289,7 +43289,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.12740087509155</v>
+        <v>4.12740039825439</v>
       </c>
       <c r="H1480" t="n">
         <v>1592274</v>
@@ -43318,7 +43318,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G1481" t="n">
-        <v>4.232506275177</v>
+        <v>4.23250579833984</v>
       </c>
       <c r="H1481" t="n">
         <v>859987</v>
@@ -43492,7 +43492,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G1487" t="n">
-        <v>4.22442102432251</v>
+        <v>4.22442150115967</v>
       </c>
       <c r="H1487" t="n">
         <v>1158444</v>
@@ -43637,7 +43637,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1492" t="n">
-        <v>4.17591094970703</v>
+        <v>4.17591142654419</v>
       </c>
       <c r="H1492" t="n">
         <v>1409717</v>
@@ -43753,7 +43753,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1496" t="n">
-        <v>4.0910177230835</v>
+        <v>4.09101819992065</v>
       </c>
       <c r="H1496" t="n">
         <v>2064342</v>
@@ -43782,7 +43782,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1497" t="n">
-        <v>4.0910177230835</v>
+        <v>4.09101819992065</v>
       </c>
       <c r="H1497" t="n">
         <v>1666798</v>
@@ -43811,7 +43811,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.96650910377502</v>
+        <v>3.96650862693787</v>
       </c>
       <c r="H1498" t="n">
         <v>3821543</v>
@@ -43840,7 +43840,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.89859437942505</v>
+        <v>3.89859485626221</v>
       </c>
       <c r="H1499" t="n">
         <v>1854115</v>
@@ -43927,7 +43927,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G1502" t="n">
-        <v>3.95033884048462</v>
+        <v>3.95033931732178</v>
       </c>
       <c r="H1502" t="n">
         <v>1279609</v>
@@ -43956,7 +43956,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>4.04655075073242</v>
+        <v>4.04655122756958</v>
       </c>
       <c r="H1503" t="n">
         <v>1493218</v>
@@ -44043,7 +44043,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1506" t="n">
-        <v>3.86463809013367</v>
+        <v>3.86463832855225</v>
       </c>
       <c r="H1506" t="n">
         <v>823047</v>
@@ -44188,7 +44188,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.80157494544983</v>
+        <v>3.80157446861267</v>
       </c>
       <c r="H1511" t="n">
         <v>1571045</v>
@@ -44275,7 +44275,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G1514" t="n">
-        <v>3.86463809013367</v>
+        <v>3.86463832855225</v>
       </c>
       <c r="H1514" t="n">
         <v>875290</v>
@@ -44478,7 +44478,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1521" t="n">
-        <v>4.27293062210083</v>
+        <v>4.27293109893799</v>
       </c>
       <c r="H1521" t="n">
         <v>1561683</v>
@@ -44710,7 +44710,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G1529" t="n">
-        <v>4.36995220184326</v>
+        <v>4.3699517250061</v>
       </c>
       <c r="H1529" t="n">
         <v>1003519</v>
@@ -44768,7 +44768,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.40633392333984</v>
+        <v>4.406334400177</v>
       </c>
       <c r="H1531" t="n">
         <v>1010791</v>
@@ -44826,7 +44826,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G1533" t="n">
-        <v>4.43463182449341</v>
+        <v>4.43463134765625</v>
       </c>
       <c r="H1533" t="n">
         <v>1031900</v>
@@ -44855,7 +44855,7 @@
         <v>5.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1534" t="n">
         <v>921443</v>
@@ -44971,7 +44971,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.52760887145996</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1538" t="n">
         <v>645027</v>
@@ -45116,7 +45116,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>4.52760887145996</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1543" t="n">
         <v>850493</v>
@@ -45145,7 +45145,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G1544" t="n">
-        <v>4.53165149688721</v>
+        <v>4.53165197372437</v>
       </c>
       <c r="H1544" t="n">
         <v>1922600</v>
@@ -45174,7 +45174,7 @@
         <v>5.625</v>
       </c>
       <c r="G1545" t="n">
-        <v>4.54782199859619</v>
+        <v>4.54782152175903</v>
       </c>
       <c r="H1545" t="n">
         <v>1422376</v>
@@ -45290,7 +45290,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G1549" t="n">
-        <v>4.56399202346802</v>
+        <v>4.56399154663086</v>
       </c>
       <c r="H1549" t="n">
         <v>803941</v>
@@ -45435,7 +45435,7 @@
         <v>5.625</v>
       </c>
       <c r="G1554" t="n">
-        <v>4.54782199859619</v>
+        <v>4.54782152175903</v>
       </c>
       <c r="H1554" t="n">
         <v>1148827</v>
@@ -45551,7 +45551,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1558" t="n">
-        <v>4.27293062210083</v>
+        <v>4.27293109893799</v>
       </c>
       <c r="H1558" t="n">
         <v>1328954</v>
@@ -45870,7 +45870,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.25676155090332</v>
+        <v>4.25676107406616</v>
       </c>
       <c r="H1569" t="n">
         <v>1159957</v>
@@ -45957,7 +45957,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1572" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1572" t="n">
         <v>732182</v>
@@ -46015,7 +46015,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>4.41441917419434</v>
+        <v>4.41441869735718</v>
       </c>
       <c r="H1574" t="n">
         <v>1041388</v>
@@ -46073,7 +46073,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1576" t="n">
-        <v>4.39824867248535</v>
+        <v>4.39824914932251</v>
       </c>
       <c r="H1576" t="n">
         <v>679678</v>
@@ -46102,7 +46102,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.41441917419434</v>
+        <v>4.41441869735718</v>
       </c>
       <c r="H1577" t="n">
         <v>678604</v>
@@ -46479,7 +46479,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1590" t="n">
-        <v>4.41441917419434</v>
+        <v>4.41441869735718</v>
       </c>
       <c r="H1590" t="n">
         <v>1545936</v>
@@ -46566,7 +46566,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.56803464889526</v>
+        <v>4.56803417205811</v>
       </c>
       <c r="H1593" t="n">
         <v>842156</v>
@@ -46595,7 +46595,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G1594" t="n">
-        <v>4.58016157150269</v>
+        <v>4.58016204833984</v>
       </c>
       <c r="H1594" t="n">
         <v>653054</v>
@@ -46624,7 +46624,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1595" t="n">
-        <v>4.52760887145996</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1595" t="n">
         <v>834135</v>
@@ -46711,7 +46711,7 @@
         <v>5.5</v>
       </c>
       <c r="G1598" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1598" t="n">
         <v>3511367</v>
@@ -46740,7 +46740,7 @@
         <v>5.5</v>
       </c>
       <c r="G1599" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1599" t="n">
         <v>1445698</v>
@@ -46914,7 +46914,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1605" t="n">
-        <v>4.3295259475708</v>
+        <v>4.32952642440796</v>
       </c>
       <c r="H1605" t="n">
         <v>1023223</v>
@@ -46972,7 +46972,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1607" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1607" t="n">
         <v>1646514</v>
@@ -47030,7 +47030,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1609" t="n">
-        <v>4.26888847351074</v>
+        <v>4.2688889503479</v>
       </c>
       <c r="H1609" t="n">
         <v>1435892</v>
@@ -47088,7 +47088,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>4.27293062210083</v>
+        <v>4.27293109893799</v>
       </c>
       <c r="H1611" t="n">
         <v>1040363</v>
@@ -47117,7 +47117,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1612" t="n">
-        <v>4.25271892547607</v>
+        <v>4.25271844863892</v>
       </c>
       <c r="H1612" t="n">
         <v>1159127</v>
@@ -47146,7 +47146,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1613" t="n">
-        <v>4.25676155090332</v>
+        <v>4.25676107406616</v>
       </c>
       <c r="H1613" t="n">
         <v>864348</v>
@@ -47204,7 +47204,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G1615" t="n">
-        <v>4.23654842376709</v>
+        <v>4.23654794692993</v>
       </c>
       <c r="H1615" t="n">
         <v>2297716</v>
@@ -47233,7 +47233,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G1616" t="n">
-        <v>4.28101634979248</v>
+        <v>4.28101587295532</v>
       </c>
       <c r="H1616" t="n">
         <v>2139782</v>
@@ -47291,7 +47291,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1618" t="n">
-        <v>4.3295259475708</v>
+        <v>4.32952642440796</v>
       </c>
       <c r="H1618" t="n">
         <v>3053894</v>
@@ -47349,7 +47349,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1620" t="n">
         <v>6654047</v>
@@ -47407,7 +47407,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1622" t="n">
-        <v>4.50335454940796</v>
+        <v>4.5033540725708</v>
       </c>
       <c r="H1622" t="n">
         <v>1691354</v>
@@ -47436,7 +47436,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1623" t="n">
-        <v>4.45888662338257</v>
+        <v>4.45888614654541</v>
       </c>
       <c r="H1623" t="n">
         <v>2049447</v>
@@ -47494,7 +47494,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1625" t="n">
-        <v>4.36590909957886</v>
+        <v>4.3659086227417</v>
       </c>
       <c r="H1625" t="n">
         <v>1135265</v>
@@ -47581,7 +47581,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1628" t="n">
-        <v>4.50335454940796</v>
+        <v>4.5033540725708</v>
       </c>
       <c r="H1628" t="n">
         <v>1225883</v>
@@ -47610,7 +47610,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G1629" t="n">
-        <v>4.53165149688721</v>
+        <v>4.53165197372437</v>
       </c>
       <c r="H1629" t="n">
         <v>1110012</v>
@@ -47639,7 +47639,7 @@
         <v>5.625</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.54782199859619</v>
+        <v>4.54782152175903</v>
       </c>
       <c r="H1630" t="n">
         <v>907373</v>
@@ -47726,7 +47726,7 @@
         <v>5.80499982833862</v>
       </c>
       <c r="G1633" t="n">
-        <v>4.69335174560547</v>
+        <v>4.69335126876831</v>
       </c>
       <c r="H1633" t="n">
         <v>1756028</v>
@@ -47987,7 +47987,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1642" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909557342529</v>
       </c>
       <c r="H1642" t="n">
         <v>1008256</v>
@@ -48016,7 +48016,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G1643" t="n">
-        <v>4.87526512145996</v>
+        <v>4.8752646446228</v>
       </c>
       <c r="H1643" t="n">
         <v>1665568</v>
@@ -48103,7 +48103,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G1646" t="n">
-        <v>4.70952177047729</v>
+        <v>4.70952224731445</v>
       </c>
       <c r="H1646" t="n">
         <v>2045186</v>
@@ -48132,7 +48132,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G1647" t="n">
-        <v>4.74590492248535</v>
+        <v>4.74590444564819</v>
       </c>
       <c r="H1647" t="n">
         <v>3334279</v>
@@ -48451,7 +48451,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G1658" t="n">
-        <v>4.79037284851074</v>
+        <v>4.79037237167358</v>
       </c>
       <c r="H1658" t="n">
         <v>913392</v>
@@ -48509,7 +48509,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G1660" t="n">
-        <v>4.75803232192993</v>
+        <v>4.75803279876709</v>
       </c>
       <c r="H1660" t="n">
         <v>1836881</v>
@@ -73742,9 +73742,38 @@
         <v>8.81999969482422</v>
       </c>
       <c r="H2530" t="n">
-        <v>2415449</v>
+        <v>2423016</v>
       </c>
       <c r="I2530" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2531">
+      <c r="A2531" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2531" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2531" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="D2531" t="n">
+        <v>8.82199954986572</v>
+      </c>
+      <c r="E2531" t="n">
+        <v>8.72999954223633</v>
+      </c>
+      <c r="F2531" t="n">
+        <v>8.72999954223633</v>
+      </c>
+      <c r="G2531" t="n">
+        <v>8.72999954223633</v>
+      </c>
+      <c r="H2531" t="n">
+        <v>1862385</v>
+      </c>
+      <c r="I2531" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G2" t="n">
-        <v>2.47833752632141</v>
+        <v>2.47833728790283</v>
       </c>
       <c r="H2" t="n">
         <v>35612427</v>
@@ -456,7 +456,7 @@
         <v>3.83599996566772</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3946852684021</v>
+        <v>2.39468574523926</v>
       </c>
       <c r="H3" t="n">
         <v>11933789</v>
@@ -514,7 +514,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G5" t="n">
-        <v>2.07256436347961</v>
+        <v>2.07256388664246</v>
       </c>
       <c r="H5" t="n">
         <v>25466044</v>
@@ -601,7 +601,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G8" t="n">
-        <v>1.97393012046814</v>
+        <v>1.97393000125885</v>
       </c>
       <c r="H8" t="n">
         <v>14428295</v>
@@ -630,7 +630,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99765229225159</v>
+        <v>1.99765253067017</v>
       </c>
       <c r="H9" t="n">
         <v>7415318</v>
@@ -659,7 +659,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G10" t="n">
-        <v>1.95769941806793</v>
+        <v>1.95769917964935</v>
       </c>
       <c r="H10" t="n">
         <v>12484141</v>
@@ -688,7 +688,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G11" t="n">
-        <v>1.97268164157867</v>
+        <v>1.97268152236938</v>
       </c>
       <c r="H11" t="n">
         <v>9571640</v>
@@ -717,7 +717,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95645046234131</v>
+        <v>1.95645070075989</v>
       </c>
       <c r="H12" t="n">
         <v>4499554</v>
@@ -775,7 +775,7 @@
         <v>3.26600003242493</v>
       </c>
       <c r="G14" t="n">
-        <v>2.03885412216187</v>
+        <v>2.03885388374329</v>
       </c>
       <c r="H14" t="n">
         <v>7099278</v>
@@ -833,7 +833,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>2.08629822731018</v>
+        <v>2.0862979888916</v>
       </c>
       <c r="H16" t="n">
         <v>5224516</v>
@@ -891,7 +891,7 @@
         <v>3.37400007247925</v>
       </c>
       <c r="G18" t="n">
-        <v>2.10627484321594</v>
+        <v>2.10627460479736</v>
       </c>
       <c r="H18" t="n">
         <v>7328944</v>
@@ -1007,7 +1007,7 @@
         <v>3.21799993515015</v>
       </c>
       <c r="G22" t="n">
-        <v>2.00888895988464</v>
+        <v>2.00888872146606</v>
       </c>
       <c r="H22" t="n">
         <v>5833873</v>
@@ -1036,7 +1036,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12874817848206</v>
+        <v>2.12874841690063</v>
       </c>
       <c r="H23" t="n">
         <v>6586280</v>
@@ -1065,7 +1065,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G24" t="n">
-        <v>2.19367170333862</v>
+        <v>2.1936719417572</v>
       </c>
       <c r="H24" t="n">
         <v>6839861</v>
@@ -1210,7 +1210,7 @@
         <v>3.53399991989136</v>
       </c>
       <c r="G29" t="n">
-        <v>2.20615696907043</v>
+        <v>2.20615744590759</v>
       </c>
       <c r="H29" t="n">
         <v>7212643</v>
@@ -1268,7 +1268,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G31" t="n">
-        <v>2.24610996246338</v>
+        <v>2.24611020088196</v>
       </c>
       <c r="H31" t="n">
         <v>6356152</v>
@@ -1355,7 +1355,7 @@
         <v>3.67600011825562</v>
       </c>
       <c r="G34" t="n">
-        <v>2.29480338096619</v>
+        <v>2.29480314254761</v>
       </c>
       <c r="H34" t="n">
         <v>4189580</v>
@@ -1442,7 +1442,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G37" t="n">
-        <v>2.31852531433105</v>
+        <v>2.31852507591248</v>
       </c>
       <c r="H37" t="n">
         <v>1256671</v>
@@ -1471,7 +1471,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G38" t="n">
-        <v>2.30728840827942</v>
+        <v>2.307288646698</v>
       </c>
       <c r="H38" t="n">
         <v>1605686</v>
@@ -1529,7 +1529,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G40" t="n">
-        <v>2.33350777626038</v>
+        <v>2.3335075378418</v>
       </c>
       <c r="H40" t="n">
         <v>1373552</v>
@@ -1587,7 +1587,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G42" t="n">
-        <v>2.34599280357361</v>
+        <v>2.34599328041077</v>
       </c>
       <c r="H42" t="n">
         <v>2886613</v>
@@ -1616,7 +1616,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G43" t="n">
-        <v>2.38469743728638</v>
+        <v>2.3846971988678</v>
       </c>
       <c r="H43" t="n">
         <v>2605147</v>
@@ -1674,7 +1674,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G45" t="n">
-        <v>2.38469743728638</v>
+        <v>2.3846971988678</v>
       </c>
       <c r="H45" t="n">
         <v>1750587</v>
@@ -1703,7 +1703,7 @@
         <v>3.75</v>
       </c>
       <c r="G46" t="n">
-        <v>2.34099912643433</v>
+        <v>2.34099864959717</v>
       </c>
       <c r="H46" t="n">
         <v>3939834</v>
@@ -1732,7 +1732,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G47" t="n">
-        <v>2.36097526550293</v>
+        <v>2.36097550392151</v>
       </c>
       <c r="H47" t="n">
         <v>3063904</v>
@@ -1790,7 +1790,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G49" t="n">
-        <v>2.33600473403931</v>
+        <v>2.33600449562073</v>
       </c>
       <c r="H49" t="n">
         <v>2305779</v>
@@ -1964,7 +1964,7 @@
         <v>3.81599998474121</v>
       </c>
       <c r="G55" t="n">
-        <v>2.38220071792603</v>
+        <v>2.38220047950745</v>
       </c>
       <c r="H55" t="n">
         <v>3773445</v>
@@ -1993,7 +1993,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G56" t="n">
-        <v>2.31477975845337</v>
+        <v>2.31477952003479</v>
       </c>
       <c r="H56" t="n">
         <v>3360031</v>
@@ -2022,7 +2022,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G57" t="n">
-        <v>2.34599280357361</v>
+        <v>2.34599328041077</v>
       </c>
       <c r="H57" t="n">
         <v>2216469</v>
@@ -2051,7 +2051,7 @@
         <v>3.73399996757507</v>
       </c>
       <c r="G58" t="n">
-        <v>2.33101058006287</v>
+        <v>2.33101034164429</v>
       </c>
       <c r="H58" t="n">
         <v>1647322</v>
@@ -2109,7 +2109,7 @@
         <v>3.61400008201599</v>
       </c>
       <c r="G60" t="n">
-        <v>2.25609827041626</v>
+        <v>2.256098985672</v>
       </c>
       <c r="H60" t="n">
         <v>2504991</v>
@@ -2138,7 +2138,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17868947982788</v>
+        <v>2.1786892414093</v>
       </c>
       <c r="H61" t="n">
         <v>5521766</v>
@@ -2196,7 +2196,7 @@
         <v>3.5460000038147</v>
       </c>
       <c r="G63" t="n">
-        <v>2.21364855766296</v>
+        <v>2.21364808082581</v>
       </c>
       <c r="H63" t="n">
         <v>2357805</v>
@@ -2254,7 +2254,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G65" t="n">
-        <v>2.30604028701782</v>
+        <v>2.30603981018066</v>
       </c>
       <c r="H65" t="n">
         <v>2240137</v>
@@ -2341,7 +2341,7 @@
         <v>3.75600004196167</v>
       </c>
       <c r="G68" t="n">
-        <v>2.34474444389343</v>
+        <v>2.34474468231201</v>
       </c>
       <c r="H68" t="n">
         <v>2555015</v>
@@ -2399,7 +2399,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G70" t="n">
-        <v>2.36097526550293</v>
+        <v>2.36097550392151</v>
       </c>
       <c r="H70" t="n">
         <v>2975719</v>
@@ -2486,7 +2486,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G73" t="n">
-        <v>2.358478307724</v>
+        <v>2.35847854614258</v>
       </c>
       <c r="H73" t="n">
         <v>2244613</v>
@@ -2515,7 +2515,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.38469743728638</v>
+        <v>2.3846971988678</v>
       </c>
       <c r="H74" t="n">
         <v>1520764</v>
@@ -2573,7 +2573,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G76" t="n">
-        <v>2.36721801757812</v>
+        <v>2.36721777915955</v>
       </c>
       <c r="H76" t="n">
         <v>1733373</v>
@@ -2631,7 +2631,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.36596918106079</v>
+        <v>2.36596941947937</v>
       </c>
       <c r="H78" t="n">
         <v>3734574</v>
@@ -2660,7 +2660,7 @@
         <v>3.75</v>
       </c>
       <c r="G79" t="n">
-        <v>2.34099912643433</v>
+        <v>2.34099864959717</v>
       </c>
       <c r="H79" t="n">
         <v>1542324</v>
@@ -2689,7 +2689,7 @@
         <v>3.75</v>
       </c>
       <c r="G80" t="n">
-        <v>2.34099912643433</v>
+        <v>2.34099864959717</v>
       </c>
       <c r="H80" t="n">
         <v>1407964</v>
@@ -2718,7 +2718,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G81" t="n">
-        <v>2.36721801757812</v>
+        <v>2.36721777915955</v>
       </c>
       <c r="H81" t="n">
         <v>1985720</v>
@@ -2834,7 +2834,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>2.39094042778015</v>
+        <v>2.39093971252441</v>
       </c>
       <c r="H85" t="n">
         <v>1408585</v>
@@ -2921,7 +2921,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G88" t="n">
-        <v>2.40717101097107</v>
+        <v>2.40717124938965</v>
       </c>
       <c r="H88" t="n">
         <v>1733460</v>
@@ -3008,7 +3008,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>2.43963289260864</v>
+        <v>2.43963265419006</v>
       </c>
       <c r="H91" t="n">
         <v>4620752</v>
@@ -3037,7 +3037,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G92" t="n">
-        <v>2.44212985038757</v>
+        <v>2.44212961196899</v>
       </c>
       <c r="H92" t="n">
         <v>2904180</v>
@@ -3066,7 +3066,7 @@
         <v>3.89199995994568</v>
       </c>
       <c r="G93" t="n">
-        <v>2.42964458465576</v>
+        <v>2.42964434623718</v>
       </c>
       <c r="H93" t="n">
         <v>1529490</v>
@@ -3095,7 +3095,7 @@
         <v>3.96600008010864</v>
       </c>
       <c r="G94" t="n">
-        <v>2.4758403301239</v>
+        <v>2.47584056854248</v>
       </c>
       <c r="H94" t="n">
         <v>3428871</v>
@@ -3124,7 +3124,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G95" t="n">
-        <v>2.4671003818512</v>
+        <v>2.46710062026978</v>
       </c>
       <c r="H95" t="n">
         <v>9713560</v>
@@ -3153,7 +3153,7 @@
         <v>3.98399996757507</v>
       </c>
       <c r="G96" t="n">
-        <v>2.48707723617554</v>
+        <v>2.48707699775696</v>
       </c>
       <c r="H96" t="n">
         <v>3180469</v>
@@ -3240,7 +3240,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G99" t="n">
-        <v>2.4671003818512</v>
+        <v>2.46710062026978</v>
       </c>
       <c r="H99" t="n">
         <v>2383108</v>
@@ -3269,7 +3269,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G100" t="n">
-        <v>2.55574655532837</v>
+        <v>2.55574607849121</v>
       </c>
       <c r="H100" t="n">
         <v>3927765</v>
@@ -3298,7 +3298,7 @@
         <v>4.11600017547607</v>
       </c>
       <c r="G101" t="n">
-        <v>2.56948018074036</v>
+        <v>2.56948041915894</v>
       </c>
       <c r="H101" t="n">
         <v>3781999</v>
@@ -3327,7 +3327,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G102" t="n">
-        <v>2.58321404457092</v>
+        <v>2.5832142829895</v>
       </c>
       <c r="H102" t="n">
         <v>2760372</v>
@@ -3356,7 +3356,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G103" t="n">
-        <v>2.53576993942261</v>
+        <v>2.53576970100403</v>
       </c>
       <c r="H103" t="n">
         <v>2303291</v>
@@ -3414,7 +3414,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G105" t="n">
-        <v>2.56698298454285</v>
+        <v>2.56698322296143</v>
       </c>
       <c r="H105" t="n">
         <v>3011118</v>
@@ -3443,7 +3443,7 @@
         <v>4.10200023651123</v>
       </c>
       <c r="G106" t="n">
-        <v>2.56074047088623</v>
+        <v>2.56074070930481</v>
       </c>
       <c r="H106" t="n">
         <v>3106625</v>
@@ -3472,7 +3472,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G107" t="n">
-        <v>2.52203607559204</v>
+        <v>2.52203583717346</v>
       </c>
       <c r="H107" t="n">
         <v>1747900</v>
@@ -3530,7 +3530,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G109" t="n">
-        <v>2.58071684837341</v>
+        <v>2.58071660995483</v>
       </c>
       <c r="H109" t="n">
         <v>2152114</v>
@@ -3559,7 +3559,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G110" t="n">
-        <v>2.58446264266968</v>
+        <v>2.58446216583252</v>
       </c>
       <c r="H110" t="n">
         <v>1654975</v>
@@ -3617,7 +3617,7 @@
         <v>4.19399976730347</v>
       </c>
       <c r="G112" t="n">
-        <v>2.61817288398743</v>
+        <v>2.61817264556885</v>
       </c>
       <c r="H112" t="n">
         <v>4192093</v>
@@ -3675,7 +3675,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G114" t="n">
-        <v>2.63690114021301</v>
+        <v>2.63690090179443</v>
       </c>
       <c r="H114" t="n">
         <v>2609947</v>
@@ -3762,7 +3762,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G117" t="n">
-        <v>2.58695983886719</v>
+        <v>2.58696007728577</v>
       </c>
       <c r="H117" t="n">
         <v>1464984</v>
@@ -3791,7 +3791,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G118" t="n">
-        <v>2.54825520515442</v>
+        <v>2.54825496673584</v>
       </c>
       <c r="H118" t="n">
         <v>3067347</v>
@@ -3820,7 +3820,7 @@
         <v>4.26800012588501</v>
       </c>
       <c r="G119" t="n">
-        <v>2.66436886787415</v>
+        <v>2.66436910629272</v>
       </c>
       <c r="H119" t="n">
         <v>3299496</v>
@@ -3849,7 +3849,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G120" t="n">
-        <v>2.62816095352173</v>
+        <v>2.62816119194031</v>
       </c>
       <c r="H120" t="n">
         <v>2350140</v>
@@ -3878,7 +3878,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G121" t="n">
-        <v>2.57822012901306</v>
+        <v>2.57821989059448</v>
       </c>
       <c r="H121" t="n">
         <v>2971262</v>
@@ -3907,7 +3907,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>2.60319066047668</v>
+        <v>2.60319042205811</v>
       </c>
       <c r="H122" t="n">
         <v>2478837</v>
@@ -3936,7 +3936,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>2.59070563316345</v>
+        <v>2.59070515632629</v>
       </c>
       <c r="H123" t="n">
         <v>2382000</v>
@@ -3965,7 +3965,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G124" t="n">
-        <v>2.63190722465515</v>
+        <v>2.63190698623657</v>
       </c>
       <c r="H124" t="n">
         <v>2474697</v>
@@ -3994,7 +3994,7 @@
         <v>4.22399997711182</v>
       </c>
       <c r="G125" t="n">
-        <v>2.63690114021301</v>
+        <v>2.63690090179443</v>
       </c>
       <c r="H125" t="n">
         <v>1568341</v>
@@ -4052,7 +4052,7 @@
         <v>4.34800004959106</v>
       </c>
       <c r="G127" t="n">
-        <v>2.71431016921997</v>
+        <v>2.71430969238281</v>
       </c>
       <c r="H127" t="n">
         <v>3044744</v>
@@ -4081,7 +4081,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G128" t="n">
-        <v>2.71930432319641</v>
+        <v>2.71930408477783</v>
       </c>
       <c r="H128" t="n">
         <v>2807710</v>
@@ -4110,7 +4110,7 @@
         <v>4.42799997329712</v>
       </c>
       <c r="G129" t="n">
-        <v>2.7642514705658</v>
+        <v>2.76425123214722</v>
       </c>
       <c r="H129" t="n">
         <v>2632642</v>
@@ -4139,7 +4139,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G130" t="n">
-        <v>2.77299118041992</v>
+        <v>2.7729914188385</v>
       </c>
       <c r="H130" t="n">
         <v>2184181</v>
@@ -4197,7 +4197,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G132" t="n">
-        <v>2.79047036170959</v>
+        <v>2.79047060012817</v>
       </c>
       <c r="H132" t="n">
         <v>2165558</v>
@@ -4226,7 +4226,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G133" t="n">
-        <v>2.88036489486694</v>
+        <v>2.8803653717041</v>
       </c>
       <c r="H133" t="n">
         <v>4112711</v>
@@ -4255,7 +4255,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G134" t="n">
-        <v>2.89160180091858</v>
+        <v>2.8916015625</v>
       </c>
       <c r="H134" t="n">
         <v>4018664</v>
@@ -4284,7 +4284,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84166073799133</v>
+        <v>2.84166026115417</v>
       </c>
       <c r="H135" t="n">
         <v>4094332</v>
@@ -4313,7 +4313,7 @@
         <v>4.61199998855591</v>
       </c>
       <c r="G136" t="n">
-        <v>2.87911653518677</v>
+        <v>2.87911629676819</v>
       </c>
       <c r="H136" t="n">
         <v>3254919</v>
@@ -4371,7 +4371,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G138" t="n">
-        <v>2.96670079231262</v>
+        <v>2.9667010307312</v>
       </c>
       <c r="H138" t="n">
         <v>3149602</v>
@@ -4400,7 +4400,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G139" t="n">
-        <v>3.02132749557495</v>
+        <v>3.02132701873779</v>
       </c>
       <c r="H139" t="n">
         <v>2869145</v>
@@ -4458,7 +4458,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G141" t="n">
-        <v>3.00441932678223</v>
+        <v>3.00441908836365</v>
       </c>
       <c r="H141" t="n">
         <v>1874966</v>
@@ -4487,7 +4487,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G142" t="n">
-        <v>2.95889806747437</v>
+        <v>2.95889830589294</v>
       </c>
       <c r="H142" t="n">
         <v>2895383</v>
@@ -4574,7 +4574,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G145" t="n">
-        <v>3.06424760818481</v>
+        <v>3.06424736976624</v>
       </c>
       <c r="H145" t="n">
         <v>6488921</v>
@@ -4603,7 +4603,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G146" t="n">
-        <v>3.11106967926025</v>
+        <v>3.11106944084167</v>
       </c>
       <c r="H146" t="n">
         <v>5229765</v>
@@ -4661,7 +4661,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G148" t="n">
-        <v>3.09286117553711</v>
+        <v>3.09286093711853</v>
       </c>
       <c r="H148" t="n">
         <v>2668807</v>
@@ -4690,7 +4690,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G149" t="n">
-        <v>3.10716795921326</v>
+        <v>3.10716819763184</v>
       </c>
       <c r="H149" t="n">
         <v>2358075</v>
@@ -4777,7 +4777,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G152" t="n">
-        <v>3.05124115943909</v>
+        <v>3.05124139785767</v>
       </c>
       <c r="H152" t="n">
         <v>2693512</v>
@@ -4806,7 +4806,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G153" t="n">
-        <v>2.96279954910278</v>
+        <v>2.96280026435852</v>
       </c>
       <c r="H153" t="n">
         <v>3978290</v>
@@ -4835,7 +4835,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G154" t="n">
-        <v>2.98100829124451</v>
+        <v>2.98100876808167</v>
       </c>
       <c r="H154" t="n">
         <v>1741047</v>
@@ -4893,7 +4893,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G156" t="n">
-        <v>2.97190403938293</v>
+        <v>2.97190427780151</v>
       </c>
       <c r="H156" t="n">
         <v>3155336</v>
@@ -4922,7 +4922,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G157" t="n">
-        <v>2.9875111579895</v>
+        <v>2.98751139640808</v>
       </c>
       <c r="H157" t="n">
         <v>3210418</v>
@@ -4951,7 +4951,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G158" t="n">
-        <v>3.02262759208679</v>
+        <v>3.02262783050537</v>
       </c>
       <c r="H158" t="n">
         <v>1663568</v>
@@ -4980,7 +4980,7 @@
         <v>4.6560001373291</v>
       </c>
       <c r="G159" t="n">
-        <v>3.02783060073853</v>
+        <v>3.02783036231995</v>
       </c>
       <c r="H159" t="n">
         <v>1415379</v>
@@ -5009,7 +5009,7 @@
         <v>4.5939998626709</v>
       </c>
       <c r="G160" t="n">
-        <v>2.9875111579895</v>
+        <v>2.98751139640808</v>
       </c>
       <c r="H160" t="n">
         <v>1883587</v>
@@ -5038,7 +5038,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>3.01092267036438</v>
+        <v>3.01092290878296</v>
       </c>
       <c r="H161" t="n">
         <v>1440176</v>
@@ -5067,7 +5067,7 @@
         <v>4.64799976348877</v>
       </c>
       <c r="G162" t="n">
-        <v>3.02262759208679</v>
+        <v>3.02262783050537</v>
       </c>
       <c r="H162" t="n">
         <v>1812459</v>
@@ -5096,7 +5096,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G163" t="n">
-        <v>3.00441932678223</v>
+        <v>3.00441908836365</v>
       </c>
       <c r="H163" t="n">
         <v>1330854</v>
@@ -5125,7 +5125,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90947461128235</v>
+        <v>2.90947437286377</v>
       </c>
       <c r="H164" t="n">
         <v>2136959</v>
@@ -5154,7 +5154,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G165" t="n">
-        <v>2.8990695476532</v>
+        <v>2.89907002449036</v>
       </c>
       <c r="H165" t="n">
         <v>3287025</v>
@@ -5183,7 +5183,7 @@
         <v>4.36800003051758</v>
       </c>
       <c r="G166" t="n">
-        <v>2.84054231643677</v>
+        <v>2.84054207801819</v>
       </c>
       <c r="H166" t="n">
         <v>2317524</v>
@@ -5241,7 +5241,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90687322616577</v>
+        <v>2.90687298774719</v>
       </c>
       <c r="H168" t="n">
         <v>2203554</v>
@@ -5270,7 +5270,7 @@
         <v>4.44600009918213</v>
       </c>
       <c r="G169" t="n">
-        <v>2.89126586914062</v>
+        <v>2.89126563072205</v>
       </c>
       <c r="H169" t="n">
         <v>1777949</v>
@@ -5299,7 +5299,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G170" t="n">
-        <v>2.85094690322876</v>
+        <v>2.85094666481018</v>
       </c>
       <c r="H170" t="n">
         <v>1064924</v>
@@ -5328,7 +5328,7 @@
         <v>4.39599990844727</v>
       </c>
       <c r="G171" t="n">
-        <v>2.85875058174133</v>
+        <v>2.85875010490417</v>
       </c>
       <c r="H171" t="n">
         <v>1637236</v>
@@ -5357,7 +5357,7 @@
         <v>4.40999984741211</v>
       </c>
       <c r="G172" t="n">
-        <v>2.86785435676575</v>
+        <v>2.86785459518433</v>
       </c>
       <c r="H172" t="n">
         <v>1480885</v>
@@ -5415,7 +5415,7 @@
         <v>4.52799987792969</v>
       </c>
       <c r="G174" t="n">
-        <v>2.94459080696106</v>
+        <v>2.94459104537964</v>
       </c>
       <c r="H174" t="n">
         <v>1407321</v>
@@ -5444,7 +5444,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G175" t="n">
-        <v>2.97190403938293</v>
+        <v>2.97190427780151</v>
       </c>
       <c r="H175" t="n">
         <v>2547097</v>
@@ -5473,7 +5473,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>2.95239424705505</v>
+        <v>2.95239472389221</v>
       </c>
       <c r="H176" t="n">
         <v>2291148</v>
@@ -5531,7 +5531,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G178" t="n">
-        <v>2.97580599784851</v>
+        <v>2.97580575942993</v>
       </c>
       <c r="H178" t="n">
         <v>677556</v>
@@ -5560,7 +5560,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G179" t="n">
-        <v>2.97190403938293</v>
+        <v>2.97190427780151</v>
       </c>
       <c r="H179" t="n">
         <v>1152290</v>
@@ -5589,7 +5589,7 @@
         <v>4.60599994659424</v>
       </c>
       <c r="G180" t="n">
-        <v>2.99531507492065</v>
+        <v>2.99531483650208</v>
       </c>
       <c r="H180" t="n">
         <v>1233361</v>
@@ -5618,7 +5618,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.04343771934509</v>
+        <v>3.04343748092651</v>
       </c>
       <c r="H181" t="n">
         <v>2063226</v>
@@ -5676,7 +5676,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G183" t="n">
-        <v>3.04343771934509</v>
+        <v>3.04343748092651</v>
       </c>
       <c r="H183" t="n">
         <v>1602739</v>
@@ -5705,7 +5705,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>3.01092267036438</v>
+        <v>3.01092290878296</v>
       </c>
       <c r="H184" t="n">
         <v>1202620</v>
@@ -5821,7 +5821,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.02392864227295</v>
+        <v>3.02392840385437</v>
       </c>
       <c r="H188" t="n">
         <v>2591123</v>
@@ -5850,7 +5850,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G189" t="n">
-        <v>3.08765888214111</v>
+        <v>3.08765912055969</v>
       </c>
       <c r="H189" t="n">
         <v>1958346</v>
@@ -5879,7 +5879,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>3.12147450447083</v>
+        <v>3.12147521972656</v>
       </c>
       <c r="H190" t="n">
         <v>2336895</v>
@@ -5908,7 +5908,7 @@
         <v>4.78800010681152</v>
       </c>
       <c r="G191" t="n">
-        <v>3.11367106437683</v>
+        <v>3.11367082595825</v>
       </c>
       <c r="H191" t="n">
         <v>1110454</v>
@@ -5966,7 +5966,7 @@
         <v>4.82399988174438</v>
       </c>
       <c r="G193" t="n">
-        <v>3.13708186149597</v>
+        <v>3.13708162307739</v>
       </c>
       <c r="H193" t="n">
         <v>1245683</v>
@@ -5995,7 +5995,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G194" t="n">
-        <v>3.16569542884827</v>
+        <v>3.16569519042969</v>
       </c>
       <c r="H194" t="n">
         <v>1182663</v>
@@ -6053,7 +6053,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>3.14098358154297</v>
+        <v>3.14098405838013</v>
       </c>
       <c r="H196" t="n">
         <v>649672</v>
@@ -6082,7 +6082,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G197" t="n">
-        <v>3.07335162162781</v>
+        <v>3.07335138320923</v>
       </c>
       <c r="H197" t="n">
         <v>1172588</v>
@@ -6111,7 +6111,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G198" t="n">
-        <v>3.14358496665955</v>
+        <v>3.14358520507812</v>
       </c>
       <c r="H198" t="n">
         <v>1316763</v>
@@ -6140,7 +6140,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G199" t="n">
-        <v>3.15789175033569</v>
+        <v>3.15789198875427</v>
       </c>
       <c r="H199" t="n">
         <v>1018979</v>
@@ -6198,7 +6198,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G201" t="n">
-        <v>3.15789175033569</v>
+        <v>3.15789198875427</v>
       </c>
       <c r="H201" t="n">
         <v>1683946</v>
@@ -6285,7 +6285,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G204" t="n">
-        <v>3.11757302284241</v>
+        <v>3.11757278442383</v>
       </c>
       <c r="H204" t="n">
         <v>1282121</v>
@@ -6343,7 +6343,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.10846877098083</v>
+        <v>3.10846853256226</v>
       </c>
       <c r="H206" t="n">
         <v>937602</v>
@@ -6372,7 +6372,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G207" t="n">
-        <v>3.09546232223511</v>
+        <v>3.09546256065369</v>
       </c>
       <c r="H207" t="n">
         <v>479531</v>
@@ -6401,7 +6401,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G208" t="n">
-        <v>3.08245635032654</v>
+        <v>3.08245587348938</v>
       </c>
       <c r="H208" t="n">
         <v>1265229</v>
@@ -6430,7 +6430,7 @@
         <v>4.77199983596802</v>
       </c>
       <c r="G209" t="n">
-        <v>3.10326623916626</v>
+        <v>3.1032657623291</v>
       </c>
       <c r="H209" t="n">
         <v>1033833</v>
@@ -6488,7 +6488,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G211" t="n">
-        <v>3.12277483940125</v>
+        <v>3.12277507781982</v>
       </c>
       <c r="H211" t="n">
         <v>1352033</v>
@@ -6575,7 +6575,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G214" t="n">
-        <v>3.09936451911926</v>
+        <v>3.09936380386353</v>
       </c>
       <c r="H214" t="n">
         <v>2019085</v>
@@ -6604,7 +6604,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G215" t="n">
-        <v>3.10976934432983</v>
+        <v>3.10976886749268</v>
       </c>
       <c r="H215" t="n">
         <v>2759009</v>
@@ -6662,7 +6662,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G217" t="n">
-        <v>3.09936451911926</v>
+        <v>3.09936380386353</v>
       </c>
       <c r="H217" t="n">
         <v>2335811</v>
@@ -6691,7 +6691,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G218" t="n">
-        <v>3.08765888214111</v>
+        <v>3.08765912055969</v>
       </c>
       <c r="H218" t="n">
         <v>1410451</v>
@@ -6720,7 +6720,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G219" t="n">
-        <v>3.0577449798584</v>
+        <v>3.05774450302124</v>
       </c>
       <c r="H219" t="n">
         <v>1659908</v>
@@ -6749,7 +6749,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.02392864227295</v>
+        <v>3.02392840385437</v>
       </c>
       <c r="H220" t="n">
         <v>1539498</v>
@@ -6778,7 +6778,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G221" t="n">
-        <v>3.03043174743652</v>
+        <v>3.03043150901794</v>
       </c>
       <c r="H221" t="n">
         <v>1713520</v>
@@ -6807,7 +6807,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G222" t="n">
-        <v>3.03043174743652</v>
+        <v>3.03043150901794</v>
       </c>
       <c r="H222" t="n">
         <v>1111692</v>
@@ -6836,7 +6836,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G223" t="n">
-        <v>3.04864025115967</v>
+        <v>3.04864048957825</v>
       </c>
       <c r="H223" t="n">
         <v>1146321</v>
@@ -6865,7 +6865,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.02392864227295</v>
+        <v>3.02392840385437</v>
       </c>
       <c r="H224" t="n">
         <v>1103008</v>
@@ -6923,7 +6923,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G226" t="n">
-        <v>3.07075047492981</v>
+        <v>3.07075119018555</v>
       </c>
       <c r="H226" t="n">
         <v>1748215</v>
@@ -6981,7 +6981,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G228" t="n">
-        <v>3.12797737121582</v>
+        <v>3.12797784805298</v>
       </c>
       <c r="H228" t="n">
         <v>1859111</v>
@@ -7039,7 +7039,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G230" t="n">
-        <v>3.09546232223511</v>
+        <v>3.09546256065369</v>
       </c>
       <c r="H230" t="n">
         <v>1964842</v>
@@ -7126,7 +7126,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G233" t="n">
-        <v>3.06945013999939</v>
+        <v>3.06944990158081</v>
       </c>
       <c r="H233" t="n">
         <v>2513489</v>
@@ -7155,7 +7155,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G234" t="n">
-        <v>3.01222276687622</v>
+        <v>3.0122230052948</v>
       </c>
       <c r="H234" t="n">
         <v>2554522</v>
@@ -7213,7 +7213,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G236" t="n">
-        <v>2.96930265426636</v>
+        <v>2.96930289268494</v>
       </c>
       <c r="H236" t="n">
         <v>2237180</v>
@@ -7242,7 +7242,7 @@
         <v>4.65999984741211</v>
       </c>
       <c r="G237" t="n">
-        <v>3.03043174743652</v>
+        <v>3.03043150901794</v>
       </c>
       <c r="H237" t="n">
         <v>2780174</v>
@@ -7300,7 +7300,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G239" t="n">
-        <v>3.07985544204712</v>
+        <v>3.07985496520996</v>
       </c>
       <c r="H239" t="n">
         <v>2753804</v>
@@ -7387,7 +7387,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G242" t="n">
-        <v>3.07335162162781</v>
+        <v>3.07335138320923</v>
       </c>
       <c r="H242" t="n">
         <v>1121811</v>
@@ -7416,7 +7416,7 @@
         <v>4.73199987411499</v>
       </c>
       <c r="G243" t="n">
-        <v>3.07725405693054</v>
+        <v>3.07725381851196</v>
       </c>
       <c r="H243" t="n">
         <v>1769916</v>
@@ -7445,7 +7445,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G244" t="n">
-        <v>3.09546232223511</v>
+        <v>3.09546256065369</v>
       </c>
       <c r="H244" t="n">
         <v>906408</v>
@@ -7474,7 +7474,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G245" t="n">
-        <v>3.11497139930725</v>
+        <v>3.11497163772583</v>
       </c>
       <c r="H245" t="n">
         <v>1121552</v>
@@ -7503,7 +7503,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>3.14098358154297</v>
+        <v>3.14098405838013</v>
       </c>
       <c r="H246" t="n">
         <v>1767243</v>
@@ -7532,7 +7532,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G247" t="n">
-        <v>3.20861577987671</v>
+        <v>3.20861601829529</v>
       </c>
       <c r="H247" t="n">
         <v>3451526</v>
@@ -7590,7 +7590,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24893450737</v>
+        <v>3.24893498420715</v>
       </c>
       <c r="H249" t="n">
         <v>3278337</v>
@@ -7619,7 +7619,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>3.31656646728516</v>
+        <v>3.31656670570374</v>
       </c>
       <c r="H250" t="n">
         <v>2795501</v>
@@ -7677,7 +7677,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>3.27104544639587</v>
+        <v>3.27104520797729</v>
       </c>
       <c r="H252" t="n">
         <v>6428942</v>
@@ -7706,7 +7706,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G253" t="n">
-        <v>3.26129031181335</v>
+        <v>3.26129055023193</v>
       </c>
       <c r="H253" t="n">
         <v>1973997</v>
@@ -7735,7 +7735,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>3.30030941963196</v>
+        <v>3.3003089427948</v>
       </c>
       <c r="H254" t="n">
         <v>3004311</v>
@@ -7764,7 +7764,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G255" t="n">
-        <v>3.28730297088623</v>
+        <v>3.28730273246765</v>
       </c>
       <c r="H255" t="n">
         <v>1842881</v>
@@ -7793,7 +7793,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G256" t="n">
-        <v>3.28079986572266</v>
+        <v>3.28080010414124</v>
       </c>
       <c r="H256" t="n">
         <v>1188363</v>
@@ -7822,7 +7822,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G257" t="n">
-        <v>3.32307004928589</v>
+        <v>3.32307028770447</v>
       </c>
       <c r="H257" t="n">
         <v>2418189</v>
@@ -7909,7 +7909,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>3.31656646728516</v>
+        <v>3.31656670570374</v>
       </c>
       <c r="H260" t="n">
         <v>2506308</v>
@@ -8025,7 +8025,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G264" t="n">
-        <v>3.36208820343018</v>
+        <v>3.3620879650116</v>
       </c>
       <c r="H264" t="n">
         <v>3024002</v>
@@ -8054,7 +8054,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G265" t="n">
-        <v>3.39460349082947</v>
+        <v>3.39460372924805</v>
       </c>
       <c r="H265" t="n">
         <v>2474383</v>
@@ -8083,7 +8083,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G266" t="n">
-        <v>3.40760970115662</v>
+        <v>3.40760946273804</v>
       </c>
       <c r="H266" t="n">
         <v>3425548</v>
@@ -8141,7 +8141,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>3.44662880897522</v>
+        <v>3.44662857055664</v>
       </c>
       <c r="H268" t="n">
         <v>2838765</v>
@@ -8199,7 +8199,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>3.38159704208374</v>
+        <v>3.3815975189209</v>
       </c>
       <c r="H270" t="n">
         <v>1740172</v>
@@ -8228,7 +8228,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G271" t="n">
-        <v>3.33607625961304</v>
+        <v>3.33607602119446</v>
       </c>
       <c r="H271" t="n">
         <v>1843477</v>
@@ -8257,7 +8257,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.31656646728516</v>
+        <v>3.31656670570374</v>
       </c>
       <c r="H272" t="n">
         <v>1936166</v>
@@ -8286,7 +8286,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.40110683441162</v>
+        <v>3.4011070728302</v>
       </c>
       <c r="H273" t="n">
         <v>2058521</v>
@@ -8315,7 +8315,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>3.39460349082947</v>
+        <v>3.39460372924805</v>
       </c>
       <c r="H274" t="n">
         <v>1754265</v>
@@ -8344,7 +8344,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G275" t="n">
-        <v>3.45963478088379</v>
+        <v>3.45963430404663</v>
       </c>
       <c r="H275" t="n">
         <v>3167757</v>
@@ -8373,7 +8373,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>3.37509441375732</v>
+        <v>3.3750946521759</v>
       </c>
       <c r="H276" t="n">
         <v>3443370</v>
@@ -8402,7 +8402,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G277" t="n">
-        <v>3.39460349082947</v>
+        <v>3.39460372924805</v>
       </c>
       <c r="H277" t="n">
         <v>1741298</v>
@@ -8431,7 +8431,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G278" t="n">
-        <v>3.43687295913696</v>
+        <v>3.43687343597412</v>
       </c>
       <c r="H278" t="n">
         <v>4607010</v>
@@ -8460,7 +8460,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G279" t="n">
-        <v>3.44987940788269</v>
+        <v>3.44987964630127</v>
       </c>
       <c r="H279" t="n">
         <v>3731719</v>
@@ -8576,7 +8576,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G283" t="n">
-        <v>3.43687295913696</v>
+        <v>3.43687343597412</v>
       </c>
       <c r="H283" t="n">
         <v>1954309</v>
@@ -8605,7 +8605,7 @@
         <v>5.25</v>
       </c>
       <c r="G284" t="n">
-        <v>3.41411280632019</v>
+        <v>3.41411328315735</v>
       </c>
       <c r="H284" t="n">
         <v>2645545</v>
@@ -8634,7 +8634,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>3.38484859466553</v>
+        <v>3.38484930992126</v>
       </c>
       <c r="H285" t="n">
         <v>1879710</v>
@@ -8663,7 +8663,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38484859466553</v>
+        <v>3.38484930992126</v>
       </c>
       <c r="H286" t="n">
         <v>3135720</v>
@@ -8692,7 +8692,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>3.40110683441162</v>
+        <v>3.4011070728302</v>
       </c>
       <c r="H287" t="n">
         <v>1466206</v>
@@ -8750,7 +8750,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G289" t="n">
-        <v>3.37509441375732</v>
+        <v>3.3750946521759</v>
       </c>
       <c r="H289" t="n">
         <v>2203324</v>
@@ -8779,7 +8779,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G290" t="n">
-        <v>3.32307004928589</v>
+        <v>3.32307028770447</v>
       </c>
       <c r="H290" t="n">
         <v>1986354</v>
@@ -8808,7 +8808,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G291" t="n">
-        <v>3.30681228637695</v>
+        <v>3.30681180953979</v>
       </c>
       <c r="H291" t="n">
         <v>1233863</v>
@@ -8837,7 +8837,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G292" t="n">
-        <v>3.32307004928589</v>
+        <v>3.32307028770447</v>
       </c>
       <c r="H292" t="n">
         <v>1239019</v>
@@ -8866,7 +8866,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G293" t="n">
-        <v>3.33607625961304</v>
+        <v>3.33607602119446</v>
       </c>
       <c r="H293" t="n">
         <v>1087147</v>
@@ -8895,7 +8895,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G294" t="n">
-        <v>3.31006383895874</v>
+        <v>3.31006360054016</v>
       </c>
       <c r="H294" t="n">
         <v>1327314</v>
@@ -8982,7 +8982,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G297" t="n">
-        <v>3.23852944374084</v>
+        <v>3.23853015899658</v>
       </c>
       <c r="H297" t="n">
         <v>2508428</v>
@@ -9011,7 +9011,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G298" t="n">
-        <v>3.27104544639587</v>
+        <v>3.27104520797729</v>
       </c>
       <c r="H298" t="n">
         <v>1818628</v>
@@ -9040,7 +9040,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G299" t="n">
-        <v>3.2645423412323</v>
+        <v>3.26454210281372</v>
       </c>
       <c r="H299" t="n">
         <v>2225454</v>
@@ -9069,7 +9069,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G300" t="n">
-        <v>3.245032787323</v>
+        <v>3.24503207206726</v>
       </c>
       <c r="H300" t="n">
         <v>2694727</v>
@@ -9098,7 +9098,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>3.18650579452515</v>
+        <v>3.18650555610657</v>
       </c>
       <c r="H301" t="n">
         <v>3560333</v>
@@ -9127,7 +9127,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>3.16699600219727</v>
+        <v>3.16699624061584</v>
       </c>
       <c r="H302" t="n">
         <v>2028450</v>
@@ -9156,7 +9156,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G303" t="n">
-        <v>3.16959714889526</v>
+        <v>3.16959738731384</v>
       </c>
       <c r="H303" t="n">
         <v>1765252</v>
@@ -9185,7 +9185,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G304" t="n">
-        <v>3.16959714889526</v>
+        <v>3.16959738731384</v>
       </c>
       <c r="H304" t="n">
         <v>1332188</v>
@@ -9243,7 +9243,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G306" t="n">
-        <v>3.23202633857727</v>
+        <v>3.23202681541443</v>
       </c>
       <c r="H306" t="n">
         <v>1936665</v>
@@ -9301,7 +9301,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G308" t="n">
-        <v>3.22942543029785</v>
+        <v>3.22942590713501</v>
       </c>
       <c r="H308" t="n">
         <v>1536056</v>
@@ -9330,7 +9330,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G309" t="n">
-        <v>3.245032787323</v>
+        <v>3.24503207206726</v>
       </c>
       <c r="H309" t="n">
         <v>1332232</v>
@@ -9359,7 +9359,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G310" t="n">
-        <v>3.27104544639587</v>
+        <v>3.27104520797729</v>
       </c>
       <c r="H310" t="n">
         <v>1565332</v>
@@ -9388,7 +9388,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22942543029785</v>
+        <v>3.22942590713501</v>
       </c>
       <c r="H311" t="n">
         <v>1793873</v>
@@ -9446,7 +9446,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G313" t="n">
-        <v>3.2229220867157</v>
+        <v>3.22292280197144</v>
       </c>
       <c r="H313" t="n">
         <v>1435060</v>
@@ -9475,7 +9475,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>3.18650579452515</v>
+        <v>3.18650555610657</v>
       </c>
       <c r="H314" t="n">
         <v>2572604</v>
@@ -9504,7 +9504,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G315" t="n">
-        <v>3.16699600219727</v>
+        <v>3.16699624061584</v>
       </c>
       <c r="H315" t="n">
         <v>2426852</v>
@@ -9533,7 +9533,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G316" t="n">
-        <v>3.23462748527527</v>
+        <v>3.23462796211243</v>
       </c>
       <c r="H316" t="n">
         <v>3281061</v>
@@ -9562,7 +9562,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G317" t="n">
-        <v>3.2177197933197</v>
+        <v>3.21772027015686</v>
       </c>
       <c r="H317" t="n">
         <v>2118644</v>
@@ -9649,7 +9649,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>2.98816180229187</v>
+        <v>2.98816156387329</v>
       </c>
       <c r="H320" t="n">
         <v>3568087</v>
@@ -9678,7 +9678,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02913117408752</v>
+        <v>3.02913069725037</v>
       </c>
       <c r="H321" t="n">
         <v>2708506</v>
@@ -9765,7 +9765,7 @@
         <v>4.46400022506714</v>
       </c>
       <c r="G324" t="n">
-        <v>2.90297150611877</v>
+        <v>2.9029712677002</v>
       </c>
       <c r="H324" t="n">
         <v>1575080</v>
@@ -9794,7 +9794,7 @@
         <v>4.42000007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>2.8743577003479</v>
+        <v>2.87435793876648</v>
       </c>
       <c r="H325" t="n">
         <v>2067484</v>
@@ -9852,7 +9852,7 @@
         <v>4.4539999961853</v>
       </c>
       <c r="G327" t="n">
-        <v>2.89646816253662</v>
+        <v>2.8964684009552</v>
       </c>
       <c r="H327" t="n">
         <v>1295172</v>
@@ -9881,7 +9881,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G328" t="n">
-        <v>2.91662764549255</v>
+        <v>2.91662788391113</v>
       </c>
       <c r="H328" t="n">
         <v>1203275</v>
@@ -9968,7 +9968,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G331" t="n">
-        <v>2.85159707069397</v>
+        <v>2.85159730911255</v>
       </c>
       <c r="H331" t="n">
         <v>1725510</v>
@@ -9997,7 +9997,7 @@
         <v>4.46199989318848</v>
       </c>
       <c r="G332" t="n">
-        <v>2.9016706943512</v>
+        <v>2.90167045593262</v>
       </c>
       <c r="H332" t="n">
         <v>1748521</v>
@@ -10055,7 +10055,7 @@
         <v>4.51700019836426</v>
       </c>
       <c r="G334" t="n">
-        <v>2.93743777275085</v>
+        <v>2.93743801116943</v>
       </c>
       <c r="H334" t="n">
         <v>1748762</v>
@@ -10113,7 +10113,7 @@
         <v>4.41699981689453</v>
       </c>
       <c r="G336" t="n">
-        <v>2.87240672111511</v>
+        <v>2.87240648269653</v>
       </c>
       <c r="H336" t="n">
         <v>2115719</v>
@@ -10142,7 +10142,7 @@
         <v>4.36700010299683</v>
       </c>
       <c r="G337" t="n">
-        <v>2.8398916721344</v>
+        <v>2.83989143371582</v>
       </c>
       <c r="H337" t="n">
         <v>2476410</v>
@@ -10229,7 +10229,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G340" t="n">
-        <v>2.88476228713989</v>
+        <v>2.88476252555847</v>
       </c>
       <c r="H340" t="n">
         <v>2977096</v>
@@ -10258,7 +10258,7 @@
         <v>4.55499982833862</v>
       </c>
       <c r="G341" t="n">
-        <v>2.96214866638184</v>
+        <v>2.96214890480042</v>
       </c>
       <c r="H341" t="n">
         <v>2619175</v>
@@ -10287,7 +10287,7 @@
         <v>4.6269998550415</v>
       </c>
       <c r="G342" t="n">
-        <v>3.00897097587585</v>
+        <v>3.00897145271301</v>
       </c>
       <c r="H342" t="n">
         <v>2893991</v>
@@ -10316,7 +10316,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>2.95889806747437</v>
+        <v>2.95889830589294</v>
       </c>
       <c r="H343" t="n">
         <v>1778217</v>
@@ -10345,7 +10345,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.02913117408752</v>
+        <v>3.02913069725037</v>
       </c>
       <c r="H344" t="n">
         <v>3824795</v>
@@ -10403,7 +10403,7 @@
         <v>4.75099992752075</v>
       </c>
       <c r="G346" t="n">
-        <v>3.08960914611816</v>
+        <v>3.08960938453674</v>
       </c>
       <c r="H346" t="n">
         <v>5127661</v>
@@ -10461,7 +10461,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G348" t="n">
-        <v>3.05709433555603</v>
+        <v>3.05709409713745</v>
       </c>
       <c r="H348" t="n">
         <v>7156105</v>
@@ -10490,7 +10490,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>3.11497139930725</v>
+        <v>3.11497163772583</v>
       </c>
       <c r="H349" t="n">
         <v>3060245</v>
@@ -10519,7 +10519,7 @@
         <v>4.81899976730347</v>
       </c>
       <c r="G350" t="n">
-        <v>3.13383054733276</v>
+        <v>3.13383007049561</v>
       </c>
       <c r="H350" t="n">
         <v>1614575</v>
@@ -10577,7 +10577,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G352" t="n">
-        <v>3.06945013999939</v>
+        <v>3.06944990158081</v>
       </c>
       <c r="H352" t="n">
         <v>2541060</v>
@@ -10606,7 +10606,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G353" t="n">
-        <v>3.09936451911926</v>
+        <v>3.09936380386353</v>
       </c>
       <c r="H353" t="n">
         <v>1982170</v>
@@ -10664,7 +10664,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>3.11497139930725</v>
+        <v>3.11497163772583</v>
       </c>
       <c r="H355" t="n">
         <v>1626051</v>
@@ -10693,7 +10693,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G356" t="n">
-        <v>3.16959714889526</v>
+        <v>3.16959738731384</v>
       </c>
       <c r="H356" t="n">
         <v>2821934</v>
@@ -10722,7 +10722,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G357" t="n">
-        <v>3.15789175033569</v>
+        <v>3.15789198875427</v>
       </c>
       <c r="H357" t="n">
         <v>1742932</v>
@@ -10780,7 +10780,7 @@
         <v>4.83699989318848</v>
       </c>
       <c r="G359" t="n">
-        <v>3.14553594589233</v>
+        <v>3.14553570747375</v>
       </c>
       <c r="H359" t="n">
         <v>2245367</v>
@@ -10809,7 +10809,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G360" t="n">
-        <v>3.22032165527344</v>
+        <v>3.22032141685486</v>
       </c>
       <c r="H360" t="n">
         <v>2518130</v>
@@ -10867,7 +10867,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G362" t="n">
-        <v>3.31006383895874</v>
+        <v>3.31006360054016</v>
       </c>
       <c r="H362" t="n">
         <v>3413196</v>
@@ -10896,7 +10896,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G363" t="n">
-        <v>3.33087372779846</v>
+        <v>3.33087420463562</v>
       </c>
       <c r="H363" t="n">
         <v>2412747</v>
@@ -10925,7 +10925,7 @@
         <v>5.11600017547607</v>
       </c>
       <c r="G364" t="n">
-        <v>3.32697200775146</v>
+        <v>3.32697176933289</v>
       </c>
       <c r="H364" t="n">
         <v>1980411</v>
@@ -10954,7 +10954,7 @@
         <v>5.12599992752075</v>
       </c>
       <c r="G365" t="n">
-        <v>3.33347415924072</v>
+        <v>3.33347487449646</v>
       </c>
       <c r="H365" t="n">
         <v>1692898</v>
@@ -10983,7 +10983,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>3.29055428504944</v>
+        <v>3.29055404663086</v>
       </c>
       <c r="H366" t="n">
         <v>1867370</v>
@@ -11012,7 +11012,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G367" t="n">
-        <v>3.29705715179443</v>
+        <v>3.29705762863159</v>
       </c>
       <c r="H367" t="n">
         <v>1408912</v>
@@ -11041,7 +11041,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G368" t="n">
-        <v>3.35038304328918</v>
+        <v>3.35038328170776</v>
       </c>
       <c r="H368" t="n">
         <v>4112376</v>
@@ -11070,7 +11070,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G369" t="n">
-        <v>3.37769603729248</v>
+        <v>3.37769532203674</v>
       </c>
       <c r="H369" t="n">
         <v>1844080</v>
@@ -11099,7 +11099,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.32957315444946</v>
+        <v>3.3295726776123</v>
       </c>
       <c r="H370" t="n">
         <v>2607705</v>
@@ -11186,7 +11186,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G373" t="n">
-        <v>3.3763952255249</v>
+        <v>3.37639546394348</v>
       </c>
       <c r="H373" t="n">
         <v>3697566</v>
@@ -11244,7 +11244,7 @@
         <v>5.26399993896484</v>
       </c>
       <c r="G375" t="n">
-        <v>3.42321729660034</v>
+        <v>3.42321705818176</v>
       </c>
       <c r="H375" t="n">
         <v>1573143</v>
@@ -11273,7 +11273,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G376" t="n">
-        <v>3.47264003753662</v>
+        <v>3.47264051437378</v>
       </c>
       <c r="H376" t="n">
         <v>1857454</v>
@@ -11302,7 +11302,7 @@
         <v>5.36600017547607</v>
       </c>
       <c r="G377" t="n">
-        <v>3.4895486831665</v>
+        <v>3.48954892158508</v>
       </c>
       <c r="H377" t="n">
         <v>2580956</v>
@@ -11331,7 +11331,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G378" t="n">
-        <v>3.45053052902222</v>
+        <v>3.45053029060364</v>
       </c>
       <c r="H378" t="n">
         <v>2351824</v>
@@ -11389,7 +11389,7 @@
         <v>5.30399990081787</v>
       </c>
       <c r="G380" t="n">
-        <v>3.44922995567322</v>
+        <v>3.44922924041748</v>
       </c>
       <c r="H380" t="n">
         <v>1754549</v>
@@ -11447,7 +11447,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G382" t="n">
-        <v>3.34518074989319</v>
+        <v>3.34518027305603</v>
       </c>
       <c r="H382" t="n">
         <v>7376141</v>
@@ -11476,7 +11476,7 @@
         <v>5.08799982070923</v>
       </c>
       <c r="G383" t="n">
-        <v>3.30876326560974</v>
+        <v>3.30876278877258</v>
       </c>
       <c r="H383" t="n">
         <v>5272263</v>
@@ -11534,7 +11534,7 @@
         <v>5.08599996566772</v>
       </c>
       <c r="G385" t="n">
-        <v>3.30746221542358</v>
+        <v>3.307461977005</v>
       </c>
       <c r="H385" t="n">
         <v>1760932</v>
@@ -11563,7 +11563,7 @@
         <v>5.06799983978271</v>
       </c>
       <c r="G386" t="n">
-        <v>3.29575681686401</v>
+        <v>3.29575657844543</v>
       </c>
       <c r="H386" t="n">
         <v>2179242</v>
@@ -11592,7 +11592,7 @@
         <v>5.08599996566772</v>
       </c>
       <c r="G387" t="n">
-        <v>3.30746221542358</v>
+        <v>3.307461977005</v>
       </c>
       <c r="H387" t="n">
         <v>2188502</v>
@@ -11679,7 +11679,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>3.24828433990479</v>
+        <v>3.24828410148621</v>
       </c>
       <c r="H390" t="n">
         <v>4048165</v>
@@ -11708,7 +11708,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>3.24985361099243</v>
+        <v>3.24985432624817</v>
       </c>
       <c r="H391" t="n">
         <v>2600372</v>
@@ -11737,7 +11737,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G392" t="n">
-        <v>3.30670285224915</v>
+        <v>3.3067033290863</v>
       </c>
       <c r="H392" t="n">
         <v>2056574</v>
@@ -11766,7 +11766,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31347060203552</v>
+        <v>3.31347012519836</v>
       </c>
       <c r="H393" t="n">
         <v>2725352</v>
@@ -11824,7 +11824,7 @@
         <v>4.64200019836426</v>
       </c>
       <c r="G395" t="n">
-        <v>3.14157056808472</v>
+        <v>3.1415708065033</v>
       </c>
       <c r="H395" t="n">
         <v>3871076</v>
@@ -11911,7 +11911,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G398" t="n">
-        <v>3.03193402290344</v>
+        <v>3.03193354606628</v>
       </c>
       <c r="H398" t="n">
         <v>9267016</v>
@@ -11940,7 +11940,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G399" t="n">
-        <v>3.01839852333069</v>
+        <v>3.01839828491211</v>
       </c>
       <c r="H399" t="n">
         <v>5346504</v>
@@ -11998,7 +11998,7 @@
         <v>4.63800001144409</v>
       </c>
       <c r="G401" t="n">
-        <v>3.13886284828186</v>
+        <v>3.13886380195618</v>
       </c>
       <c r="H401" t="n">
         <v>4000775</v>
@@ -12027,7 +12027,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G402" t="n">
-        <v>3.11855983734131</v>
+        <v>3.11856031417847</v>
       </c>
       <c r="H402" t="n">
         <v>3095485</v>
@@ -12056,7 +12056,7 @@
         <v>4.5770001411438</v>
       </c>
       <c r="G403" t="n">
-        <v>3.09758043289185</v>
+        <v>3.097580909729</v>
       </c>
       <c r="H403" t="n">
         <v>2159901</v>
@@ -12085,7 +12085,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>3.09961080551147</v>
+        <v>3.09961104393005</v>
       </c>
       <c r="H404" t="n">
         <v>1736977</v>
@@ -12172,7 +12172,7 @@
         <v>4.86299991607666</v>
       </c>
       <c r="G407" t="n">
-        <v>3.29113721847534</v>
+        <v>3.29113698005676</v>
       </c>
       <c r="H407" t="n">
         <v>4461113</v>
@@ -12201,7 +12201,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G408" t="n">
-        <v>3.24579381942749</v>
+        <v>3.24579334259033</v>
       </c>
       <c r="H408" t="n">
         <v>3902612</v>
@@ -12259,7 +12259,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G410" t="n">
-        <v>3.23225784301758</v>
+        <v>3.23225808143616</v>
       </c>
       <c r="H410" t="n">
         <v>3867738</v>
@@ -12288,7 +12288,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G411" t="n">
-        <v>3.24511623382568</v>
+        <v>3.24511647224426</v>
       </c>
       <c r="H411" t="n">
         <v>1310689</v>
@@ -12317,7 +12317,7 @@
         <v>4.82299995422363</v>
       </c>
       <c r="G412" t="n">
-        <v>3.26406621932983</v>
+        <v>3.26406645774841</v>
       </c>
       <c r="H412" t="n">
         <v>2369613</v>
@@ -12375,7 +12375,7 @@
         <v>4.72100019454956</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19503569602966</v>
+        <v>3.1950352191925</v>
       </c>
       <c r="H414" t="n">
         <v>2771532</v>
@@ -12462,7 +12462,7 @@
         <v>4.73099994659424</v>
       </c>
       <c r="G417" t="n">
-        <v>3.20180296897888</v>
+        <v>3.20180320739746</v>
       </c>
       <c r="H417" t="n">
         <v>2797354</v>
@@ -12491,7 +12491,7 @@
         <v>4.74499988555908</v>
       </c>
       <c r="G418" t="n">
-        <v>3.21127772331238</v>
+        <v>3.21127796173096</v>
       </c>
       <c r="H418" t="n">
         <v>2248878</v>
@@ -12520,7 +12520,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G419" t="n">
-        <v>3.18759107589722</v>
+        <v>3.18759083747864</v>
       </c>
       <c r="H419" t="n">
         <v>1998018</v>
@@ -12549,7 +12549,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G420" t="n">
-        <v>3.19571232795715</v>
+        <v>3.19571256637573</v>
       </c>
       <c r="H420" t="n">
         <v>2199299</v>
@@ -12607,7 +12607,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G422" t="n">
-        <v>3.21330857276917</v>
+        <v>3.21330881118774</v>
       </c>
       <c r="H422" t="n">
         <v>1706417</v>
@@ -12665,7 +12665,7 @@
         <v>4.81099987030029</v>
       </c>
       <c r="G424" t="n">
-        <v>3.2559449672699</v>
+        <v>3.25594449043274</v>
       </c>
       <c r="H424" t="n">
         <v>1826570</v>
@@ -12694,7 +12694,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G425" t="n">
-        <v>3.27286410331726</v>
+        <v>3.2728636264801</v>
       </c>
       <c r="H425" t="n">
         <v>2008386</v>
@@ -12723,7 +12723,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G426" t="n">
-        <v>3.23361134529114</v>
+        <v>3.2336118221283</v>
       </c>
       <c r="H426" t="n">
         <v>1009632</v>
@@ -12781,7 +12781,7 @@
         <v>4.7039999961853</v>
       </c>
       <c r="G428" t="n">
-        <v>3.18353033065796</v>
+        <v>3.18353056907654</v>
       </c>
       <c r="H428" t="n">
         <v>1407066</v>
@@ -12810,7 +12810,7 @@
         <v>4.74700021743774</v>
       </c>
       <c r="G429" t="n">
-        <v>3.2126317024231</v>
+        <v>3.21263146400452</v>
       </c>
       <c r="H429" t="n">
         <v>1510889</v>
@@ -12868,7 +12868,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>3.25526785850525</v>
+        <v>3.25526809692383</v>
       </c>
       <c r="H431" t="n">
         <v>2483950</v>
@@ -12897,7 +12897,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G432" t="n">
-        <v>3.30534958839417</v>
+        <v>3.30534934997559</v>
       </c>
       <c r="H432" t="n">
         <v>1839177</v>
@@ -12984,7 +12984,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>3.29587435722351</v>
+        <v>3.29587459564209</v>
       </c>
       <c r="H435" t="n">
         <v>1955017</v>
@@ -13071,7 +13071,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.26203584671021</v>
+        <v>3.26203608512878</v>
       </c>
       <c r="H438" t="n">
         <v>1301307</v>
@@ -13129,7 +13129,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G440" t="n">
-        <v>3.31347060203552</v>
+        <v>3.31347012519836</v>
       </c>
       <c r="H440" t="n">
         <v>941165</v>
@@ -13216,7 +13216,7 @@
         <v>4.83900022506714</v>
       </c>
       <c r="G443" t="n">
-        <v>3.27489471435547</v>
+        <v>3.27489447593689</v>
       </c>
       <c r="H443" t="n">
         <v>3411353</v>
@@ -13245,7 +13245,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G444" t="n">
-        <v>3.2796323299408</v>
+        <v>3.27963209152222</v>
       </c>
       <c r="H444" t="n">
         <v>2129347</v>
@@ -13274,7 +13274,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G445" t="n">
-        <v>3.27286410331726</v>
+        <v>3.2728636264801</v>
       </c>
       <c r="H445" t="n">
         <v>1878974</v>
@@ -13303,7 +13303,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G446" t="n">
-        <v>3.2796323299408</v>
+        <v>3.27963209152222</v>
       </c>
       <c r="H446" t="n">
         <v>944767</v>
@@ -13332,7 +13332,7 @@
         <v>4.97200012207031</v>
       </c>
       <c r="G447" t="n">
-        <v>3.36490488052368</v>
+        <v>3.3649046421051</v>
       </c>
       <c r="H447" t="n">
         <v>1912325</v>
@@ -13361,7 +13361,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G448" t="n">
-        <v>3.34527897834778</v>
+        <v>3.34527826309204</v>
       </c>
       <c r="H448" t="n">
         <v>2299462</v>
@@ -13390,7 +13390,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G449" t="n">
-        <v>3.30670285224915</v>
+        <v>3.3067033290863</v>
       </c>
       <c r="H449" t="n">
         <v>1660537</v>
@@ -13419,7 +13419,7 @@
         <v>4.80299997329712</v>
       </c>
       <c r="G450" t="n">
-        <v>3.25053119659424</v>
+        <v>3.2505304813385</v>
       </c>
       <c r="H450" t="n">
         <v>1784763</v>
@@ -13448,7 +13448,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G451" t="n">
-        <v>3.27015662193298</v>
+        <v>3.27015686035156</v>
       </c>
       <c r="H451" t="n">
         <v>1321199</v>
@@ -13477,7 +13477,7 @@
         <v>4.85099983215332</v>
       </c>
       <c r="G452" t="n">
-        <v>3.28301572799683</v>
+        <v>3.28301548957825</v>
       </c>
       <c r="H452" t="n">
         <v>1483194</v>
@@ -13506,7 +13506,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G453" t="n">
-        <v>3.25729846954346</v>
+        <v>3.25729870796204</v>
       </c>
       <c r="H453" t="n">
         <v>2300362</v>
@@ -13593,7 +13593,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G456" t="n">
-        <v>3.28639984130859</v>
+        <v>3.28639960289001</v>
       </c>
       <c r="H456" t="n">
         <v>1593265</v>
@@ -13622,7 +13622,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G457" t="n">
-        <v>3.19368171691895</v>
+        <v>3.19368147850037</v>
       </c>
       <c r="H457" t="n">
         <v>1943294</v>
@@ -13680,7 +13680,7 @@
         <v>4.67399978637695</v>
       </c>
       <c r="G459" t="n">
-        <v>3.16322731971741</v>
+        <v>3.16322708129883</v>
       </c>
       <c r="H459" t="n">
         <v>1391304</v>
@@ -13709,7 +13709,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G460" t="n">
-        <v>3.16728782653809</v>
+        <v>3.16728806495667</v>
       </c>
       <c r="H460" t="n">
         <v>1168931</v>
@@ -13738,7 +13738,7 @@
         <v>4.65100002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>3.14766144752502</v>
+        <v>3.1476616859436</v>
       </c>
       <c r="H461" t="n">
         <v>2765596</v>
@@ -13767,7 +13767,7 @@
         <v>4.69099998474121</v>
       </c>
       <c r="G462" t="n">
-        <v>3.17473196983337</v>
+        <v>3.17473220825195</v>
       </c>
       <c r="H462" t="n">
         <v>1001054</v>
@@ -13796,7 +13796,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G463" t="n">
-        <v>3.11314630508423</v>
+        <v>3.11314606666565</v>
       </c>
       <c r="H463" t="n">
         <v>1536584</v>
@@ -13883,7 +13883,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G466" t="n">
-        <v>3.18894410133362</v>
+        <v>3.18894457817078</v>
       </c>
       <c r="H466" t="n">
         <v>1949181</v>
@@ -13912,7 +13912,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G467" t="n">
-        <v>3.19165182113647</v>
+        <v>3.1916515827179</v>
       </c>
       <c r="H467" t="n">
         <v>1729164</v>
@@ -13941,7 +13941,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G468" t="n">
-        <v>3.18488383293152</v>
+        <v>3.1848840713501</v>
       </c>
       <c r="H468" t="n">
         <v>1272146</v>
@@ -13970,7 +13970,7 @@
         <v>4.73400020599365</v>
       </c>
       <c r="G469" t="n">
-        <v>3.20383381843567</v>
+        <v>3.20383405685425</v>
       </c>
       <c r="H469" t="n">
         <v>1416699</v>
@@ -14028,7 +14028,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>3.35001611709595</v>
+        <v>3.35001587867737</v>
       </c>
       <c r="H471" t="n">
         <v>1495616</v>
@@ -14086,7 +14086,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G473" t="n">
-        <v>3.31482315063477</v>
+        <v>3.31482362747192</v>
       </c>
       <c r="H473" t="n">
         <v>1585806</v>
@@ -14144,7 +14144,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G475" t="n">
-        <v>3.30940985679626</v>
+        <v>3.30940914154053</v>
       </c>
       <c r="H475" t="n">
         <v>1828737</v>
@@ -14173,7 +14173,7 @@
         <v>4.88700008392334</v>
       </c>
       <c r="G476" t="n">
-        <v>3.30737948417664</v>
+        <v>3.30737924575806</v>
       </c>
       <c r="H476" t="n">
         <v>1146119</v>
@@ -14231,7 +14231,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G478" t="n">
-        <v>3.31008625030518</v>
+        <v>3.31008672714233</v>
       </c>
       <c r="H478" t="n">
         <v>2378226</v>
@@ -14318,7 +14318,7 @@
         <v>4.80100011825562</v>
       </c>
       <c r="G481" t="n">
-        <v>3.24917769432068</v>
+        <v>3.24917721748352</v>
       </c>
       <c r="H481" t="n">
         <v>1464371</v>
@@ -14347,7 +14347,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G482" t="n">
-        <v>3.27421760559082</v>
+        <v>3.2742178440094</v>
       </c>
       <c r="H482" t="n">
         <v>1373526</v>
@@ -14376,7 +14376,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G483" t="n">
-        <v>3.24511623382568</v>
+        <v>3.24511647224426</v>
       </c>
       <c r="H483" t="n">
         <v>1486476</v>
@@ -14405,7 +14405,7 @@
         <v>4.67399978637695</v>
       </c>
       <c r="G484" t="n">
-        <v>3.16322731971741</v>
+        <v>3.16322708129883</v>
       </c>
       <c r="H484" t="n">
         <v>2597690</v>
@@ -14434,7 +14434,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G485" t="n">
-        <v>3.16864156723022</v>
+        <v>3.16864109039307</v>
       </c>
       <c r="H485" t="n">
         <v>1484153</v>
@@ -14521,7 +14521,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G488" t="n">
-        <v>3.13818740844727</v>
+        <v>3.13818669319153</v>
       </c>
       <c r="H488" t="n">
         <v>1964476</v>
@@ -14550,7 +14550,7 @@
         <v>4.59600019454956</v>
       </c>
       <c r="G489" t="n">
-        <v>3.11043953895569</v>
+        <v>3.11043977737427</v>
       </c>
       <c r="H489" t="n">
         <v>2196021</v>
@@ -14579,7 +14579,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G490" t="n">
-        <v>3.07321691513062</v>
+        <v>3.07321667671204</v>
       </c>
       <c r="H490" t="n">
         <v>2048852</v>
@@ -14608,7 +14608,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G491" t="n">
-        <v>3.09690403938293</v>
+        <v>3.09690380096436</v>
       </c>
       <c r="H491" t="n">
         <v>2371411</v>
@@ -14637,7 +14637,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G492" t="n">
-        <v>3.06847953796387</v>
+        <v>3.06847929954529</v>
       </c>
       <c r="H492" t="n">
         <v>2212633</v>
@@ -14666,7 +14666,7 @@
         <v>4.46700000762939</v>
       </c>
       <c r="G493" t="n">
-        <v>3.02313590049744</v>
+        <v>3.02313566207886</v>
       </c>
       <c r="H493" t="n">
         <v>2373270</v>
@@ -14753,7 +14753,7 @@
         <v>4.59100008010864</v>
       </c>
       <c r="G496" t="n">
-        <v>3.1070556640625</v>
+        <v>3.10705542564392</v>
       </c>
       <c r="H496" t="n">
         <v>2125874</v>
@@ -14811,7 +14811,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G498" t="n">
-        <v>3.06171154975891</v>
+        <v>3.06171178817749</v>
       </c>
       <c r="H498" t="n">
         <v>1895816</v>
@@ -14898,7 +14898,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G501" t="n">
-        <v>3.09555006027222</v>
+        <v>3.09554982185364</v>
       </c>
       <c r="H501" t="n">
         <v>2496826</v>
@@ -14927,7 +14927,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>3.09961080551147</v>
+        <v>3.09961104393005</v>
       </c>
       <c r="H502" t="n">
         <v>2967574</v>
@@ -14956,7 +14956,7 @@
         <v>4.63600015640259</v>
       </c>
       <c r="G503" t="n">
-        <v>3.13751006126404</v>
+        <v>3.13751029968262</v>
       </c>
       <c r="H503" t="n">
         <v>2998067</v>
@@ -15014,7 +15014,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G505" t="n">
-        <v>3.11314630508423</v>
+        <v>3.11314606666565</v>
       </c>
       <c r="H505" t="n">
         <v>3009630</v>
@@ -15043,7 +15043,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G506" t="n">
-        <v>3.09148931503296</v>
+        <v>3.09148955345154</v>
       </c>
       <c r="H506" t="n">
         <v>2116842</v>
@@ -15072,7 +15072,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G507" t="n">
-        <v>3.08742880821228</v>
+        <v>3.0874285697937</v>
       </c>
       <c r="H507" t="n">
         <v>2891161</v>
@@ -15101,7 +15101,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G508" t="n">
-        <v>3.11855983734131</v>
+        <v>3.11856031417847</v>
       </c>
       <c r="H508" t="n">
         <v>3410234</v>
@@ -15130,7 +15130,7 @@
         <v>4.62900018692017</v>
       </c>
       <c r="G509" t="n">
-        <v>3.13277244567871</v>
+        <v>3.13277268409729</v>
       </c>
       <c r="H509" t="n">
         <v>1539652</v>
@@ -15159,7 +15159,7 @@
         <v>4.68900012969971</v>
       </c>
       <c r="G510" t="n">
-        <v>3.17337918281555</v>
+        <v>3.17337870597839</v>
       </c>
       <c r="H510" t="n">
         <v>2373885</v>
@@ -15217,7 +15217,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G512" t="n">
-        <v>3.27895450592041</v>
+        <v>3.27895474433899</v>
       </c>
       <c r="H512" t="n">
         <v>3534102</v>
@@ -15246,7 +15246,7 @@
         <v>4.85900020599365</v>
       </c>
       <c r="G513" t="n">
-        <v>3.28842949867249</v>
+        <v>3.28842997550964</v>
       </c>
       <c r="H513" t="n">
         <v>2192149</v>
@@ -15304,7 +15304,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G515" t="n">
-        <v>3.26203584671021</v>
+        <v>3.26203608512878</v>
       </c>
       <c r="H515" t="n">
         <v>2936871</v>
@@ -15333,7 +15333,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G516" t="n">
-        <v>3.29993510246277</v>
+        <v>3.29993486404419</v>
       </c>
       <c r="H516" t="n">
         <v>1635283</v>
@@ -15362,7 +15362,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G517" t="n">
-        <v>3.24308586120605</v>
+        <v>3.24308609962463</v>
       </c>
       <c r="H517" t="n">
         <v>1997692</v>
@@ -15391,7 +15391,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G518" t="n">
-        <v>3.19368171691895</v>
+        <v>3.19368147850037</v>
       </c>
       <c r="H518" t="n">
         <v>2274690</v>
@@ -15420,7 +15420,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G519" t="n">
-        <v>3.21601533889771</v>
+        <v>3.21601510047913</v>
       </c>
       <c r="H519" t="n">
         <v>1641709</v>
@@ -15449,7 +15449,7 @@
         <v>4.72700023651123</v>
       </c>
       <c r="G520" t="n">
-        <v>3.19909620285034</v>
+        <v>3.1990966796875</v>
       </c>
       <c r="H520" t="n">
         <v>1807479</v>
@@ -15507,7 +15507,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G522" t="n">
-        <v>3.1639039516449</v>
+        <v>3.16390371322632</v>
       </c>
       <c r="H522" t="n">
         <v>1528824</v>
@@ -15594,7 +15594,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G525" t="n">
-        <v>3.24308586120605</v>
+        <v>3.24308609962463</v>
       </c>
       <c r="H525" t="n">
         <v>1846766</v>
@@ -15710,7 +15710,7 @@
         <v>4.72700023651123</v>
       </c>
       <c r="G529" t="n">
-        <v>3.19909620285034</v>
+        <v>3.1990966796875</v>
       </c>
       <c r="H529" t="n">
         <v>1450343</v>
@@ -15797,7 +15797,7 @@
         <v>4.82299995422363</v>
       </c>
       <c r="G532" t="n">
-        <v>3.26406621932983</v>
+        <v>3.26406645774841</v>
       </c>
       <c r="H532" t="n">
         <v>1349990</v>
@@ -15826,7 +15826,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G533" t="n">
-        <v>3.24714708328247</v>
+        <v>3.24714660644531</v>
       </c>
       <c r="H533" t="n">
         <v>2020327</v>
@@ -15855,7 +15855,7 @@
         <v>4.88700008392334</v>
       </c>
       <c r="G534" t="n">
-        <v>3.30737948417664</v>
+        <v>3.30737924575806</v>
       </c>
       <c r="H534" t="n">
         <v>1901945</v>
@@ -15884,7 +15884,7 @@
         <v>4.83300018310547</v>
       </c>
       <c r="G535" t="n">
-        <v>3.27083420753479</v>
+        <v>3.27083396911621</v>
       </c>
       <c r="H535" t="n">
         <v>1725682</v>
@@ -15942,7 +15942,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G537" t="n">
-        <v>3.37302660942078</v>
+        <v>3.37302684783936</v>
       </c>
       <c r="H537" t="n">
         <v>2305052</v>
@@ -15971,7 +15971,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G538" t="n">
-        <v>3.43799614906311</v>
+        <v>3.43799638748169</v>
       </c>
       <c r="H538" t="n">
         <v>2263118</v>
@@ -16000,7 +16000,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G539" t="n">
-        <v>3.45829916000366</v>
+        <v>3.45829963684082</v>
       </c>
       <c r="H539" t="n">
         <v>1917483</v>
@@ -16058,7 +16058,7 @@
         <v>5.10799980163574</v>
       </c>
       <c r="G541" t="n">
-        <v>3.45694589614868</v>
+        <v>3.4569456577301</v>
       </c>
       <c r="H541" t="n">
         <v>3139338</v>
@@ -16116,7 +16116,7 @@
         <v>5.0939998626709</v>
       </c>
       <c r="G543" t="n">
-        <v>3.44747066497803</v>
+        <v>3.44747090339661</v>
       </c>
       <c r="H543" t="n">
         <v>2157833</v>
@@ -16145,7 +16145,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G544" t="n">
-        <v>3.44611740112305</v>
+        <v>3.44611763954163</v>
       </c>
       <c r="H544" t="n">
         <v>2699606</v>
@@ -16174,7 +16174,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G545" t="n">
-        <v>3.360844373703</v>
+        <v>3.36084461212158</v>
       </c>
       <c r="H545" t="n">
         <v>2043930</v>
@@ -16203,7 +16203,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G546" t="n">
-        <v>3.3811469078064</v>
+        <v>3.38114714622498</v>
       </c>
       <c r="H546" t="n">
         <v>1085876</v>
@@ -16232,7 +16232,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G547" t="n">
-        <v>3.42581391334534</v>
+        <v>3.4258143901825</v>
       </c>
       <c r="H547" t="n">
         <v>1842177</v>
@@ -16261,7 +16261,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G548" t="n">
-        <v>3.46506714820862</v>
+        <v>3.46506690979004</v>
       </c>
       <c r="H548" t="n">
         <v>2083576</v>
@@ -16290,7 +16290,7 @@
         <v>5.16200017929077</v>
       </c>
       <c r="G549" t="n">
-        <v>3.49349188804626</v>
+        <v>3.49349164962769</v>
       </c>
       <c r="H549" t="n">
         <v>2357386</v>
@@ -16319,7 +16319,7 @@
         <v>5.2039999961853</v>
       </c>
       <c r="G550" t="n">
-        <v>3.52191591262817</v>
+        <v>3.52191615104675</v>
       </c>
       <c r="H550" t="n">
         <v>2534910</v>
@@ -16348,7 +16348,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G551" t="n">
-        <v>3.46642088890076</v>
+        <v>3.4664204120636</v>
       </c>
       <c r="H551" t="n">
         <v>5238374</v>
@@ -16406,7 +16406,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G553" t="n">
-        <v>3.52868390083313</v>
+        <v>3.52868318557739</v>
       </c>
       <c r="H553" t="n">
         <v>2232096</v>
@@ -16435,7 +16435,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G554" t="n">
-        <v>3.5503396987915</v>
+        <v>3.55033993721008</v>
       </c>
       <c r="H554" t="n">
         <v>1779745</v>
@@ -16464,7 +16464,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G555" t="n">
-        <v>3.49755239486694</v>
+        <v>3.49755191802979</v>
       </c>
       <c r="H555" t="n">
         <v>2295662</v>
@@ -16493,7 +16493,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G556" t="n">
-        <v>3.52597665786743</v>
+        <v>3.52597641944885</v>
       </c>
       <c r="H556" t="n">
         <v>1458761</v>
@@ -16522,7 +16522,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G557" t="n">
-        <v>3.53003668785095</v>
+        <v>3.53003692626953</v>
       </c>
       <c r="H557" t="n">
         <v>1783120</v>
@@ -16551,7 +16551,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G558" t="n">
-        <v>3.52056241035461</v>
+        <v>3.52056264877319</v>
       </c>
       <c r="H558" t="n">
         <v>1626237</v>
@@ -16609,7 +16609,7 @@
         <v>5.25</v>
       </c>
       <c r="G560" t="n">
-        <v>3.55304741859436</v>
+        <v>3.55304789543152</v>
       </c>
       <c r="H560" t="n">
         <v>1235834</v>
@@ -16638,7 +16638,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G561" t="n">
-        <v>3.52597665786743</v>
+        <v>3.52597641944885</v>
       </c>
       <c r="H561" t="n">
         <v>1874069</v>
@@ -16667,7 +16667,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G562" t="n">
-        <v>3.52597665786743</v>
+        <v>3.52597641944885</v>
       </c>
       <c r="H562" t="n">
         <v>2322938</v>
@@ -16696,7 +16696,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G563" t="n">
-        <v>3.5516939163208</v>
+        <v>3.55169367790222</v>
       </c>
       <c r="H563" t="n">
         <v>2286330</v>
@@ -16725,7 +16725,7 @@
         <v>5.25</v>
       </c>
       <c r="G564" t="n">
-        <v>3.55304741859436</v>
+        <v>3.55304789543152</v>
       </c>
       <c r="H564" t="n">
         <v>1436011</v>
@@ -16754,7 +16754,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G565" t="n">
-        <v>3.49755239486694</v>
+        <v>3.49755191802979</v>
       </c>
       <c r="H565" t="n">
         <v>2827660</v>
@@ -16783,7 +16783,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G566" t="n">
-        <v>3.56658267974854</v>
+        <v>3.56658244132996</v>
       </c>
       <c r="H566" t="n">
         <v>2847559</v>
@@ -16841,7 +16841,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G568" t="n">
-        <v>3.57199692726135</v>
+        <v>3.57199668884277</v>
       </c>
       <c r="H568" t="n">
         <v>2087253</v>
@@ -16870,7 +16870,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G569" t="n">
-        <v>3.51514840126038</v>
+        <v>3.51514863967896</v>
       </c>
       <c r="H569" t="n">
         <v>1833579</v>
@@ -16899,7 +16899,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G570" t="n">
-        <v>3.53545165061951</v>
+        <v>3.53545093536377</v>
       </c>
       <c r="H570" t="n">
         <v>1542313</v>
@@ -16928,7 +16928,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G571" t="n">
-        <v>3.57199692726135</v>
+        <v>3.57199668884277</v>
       </c>
       <c r="H571" t="n">
         <v>1790300</v>
@@ -16957,7 +16957,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G572" t="n">
-        <v>3.56116819381714</v>
+        <v>3.56116890907288</v>
       </c>
       <c r="H572" t="n">
         <v>1415150</v>
@@ -16986,7 +16986,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G573" t="n">
-        <v>3.48266291618347</v>
+        <v>3.48266315460205</v>
       </c>
       <c r="H573" t="n">
         <v>1783474</v>
@@ -17102,7 +17102,7 @@
         <v>5.22800016403198</v>
       </c>
       <c r="G577" t="n">
-        <v>3.53815841674805</v>
+        <v>3.53815865516663</v>
       </c>
       <c r="H577" t="n">
         <v>1120215</v>
@@ -17131,7 +17131,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G578" t="n">
-        <v>3.52868390083313</v>
+        <v>3.52868318557739</v>
       </c>
       <c r="H578" t="n">
         <v>1509818</v>
@@ -17160,7 +17160,7 @@
         <v>5.22599983215332</v>
       </c>
       <c r="G579" t="n">
-        <v>3.53680467605591</v>
+        <v>3.53680515289307</v>
       </c>
       <c r="H579" t="n">
         <v>1824415</v>
@@ -17218,7 +17218,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G581" t="n">
-        <v>3.52462291717529</v>
+        <v>3.52462339401245</v>
       </c>
       <c r="H581" t="n">
         <v>885610</v>
@@ -17247,7 +17247,7 @@
         <v>5.2039999961853</v>
       </c>
       <c r="G582" t="n">
-        <v>3.52191591262817</v>
+        <v>3.52191615104675</v>
       </c>
       <c r="H582" t="n">
         <v>832020</v>
@@ -17276,7 +17276,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>3.52597665786743</v>
+        <v>3.52597641944885</v>
       </c>
       <c r="H583" t="n">
         <v>1461214</v>
@@ -17305,7 +17305,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G584" t="n">
-        <v>3.57199692726135</v>
+        <v>3.57199668884277</v>
       </c>
       <c r="H584" t="n">
         <v>1630171</v>
@@ -17334,7 +17334,7 @@
         <v>5.30800008773804</v>
       </c>
       <c r="G585" t="n">
-        <v>3.59229969978333</v>
+        <v>3.5922999382019</v>
       </c>
       <c r="H585" t="n">
         <v>1423370</v>
@@ -17363,7 +17363,7 @@
         <v>5.2960000038147</v>
       </c>
       <c r="G586" t="n">
-        <v>3.58417868614197</v>
+        <v>3.58417892456055</v>
       </c>
       <c r="H586" t="n">
         <v>1279020</v>
@@ -17421,7 +17421,7 @@
         <v>5.32600021362305</v>
       </c>
       <c r="G588" t="n">
-        <v>3.6044819355011</v>
+        <v>3.60448217391968</v>
       </c>
       <c r="H588" t="n">
         <v>1839170</v>
@@ -17450,7 +17450,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G589" t="n">
-        <v>3.59906792640686</v>
+        <v>3.59906768798828</v>
       </c>
       <c r="H589" t="n">
         <v>1973752</v>
@@ -17508,7 +17508,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G591" t="n">
-        <v>3.56658267974854</v>
+        <v>3.56658244132996</v>
       </c>
       <c r="H591" t="n">
         <v>1538701</v>
@@ -17537,7 +17537,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G592" t="n">
-        <v>3.62207794189453</v>
+        <v>3.62207841873169</v>
       </c>
       <c r="H592" t="n">
         <v>2529959</v>
@@ -17566,7 +17566,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G593" t="n">
-        <v>3.67621994018555</v>
+        <v>3.67621970176697</v>
       </c>
       <c r="H593" t="n">
         <v>2817879</v>
@@ -17595,7 +17595,7 @@
         <v>5.46799993515015</v>
       </c>
       <c r="G594" t="n">
-        <v>3.7005832195282</v>
+        <v>3.70058345794678</v>
       </c>
       <c r="H594" t="n">
         <v>2310453</v>
@@ -17624,7 +17624,7 @@
         <v>5.42600011825562</v>
       </c>
       <c r="G595" t="n">
-        <v>3.67215919494629</v>
+        <v>3.67215895652771</v>
       </c>
       <c r="H595" t="n">
         <v>1706877</v>
@@ -17682,7 +17682,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G597" t="n">
-        <v>3.63561391830444</v>
+        <v>3.63561344146729</v>
       </c>
       <c r="H597" t="n">
         <v>1711423</v>
@@ -17798,7 +17798,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.69516921043396</v>
+        <v>3.6951687335968</v>
       </c>
       <c r="H601" t="n">
         <v>1443702</v>
@@ -17827,7 +17827,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G602" t="n">
-        <v>3.7046434879303</v>
+        <v>3.70464396476746</v>
       </c>
       <c r="H602" t="n">
         <v>2150629</v>
@@ -17885,7 +17885,7 @@
         <v>5.48199987411499</v>
       </c>
       <c r="G604" t="n">
-        <v>3.71005797386169</v>
+        <v>3.71005821228027</v>
       </c>
       <c r="H604" t="n">
         <v>1629370</v>
@@ -17943,7 +17943,7 @@
         <v>5.5</v>
       </c>
       <c r="G606" t="n">
-        <v>3.72223973274231</v>
+        <v>3.72224020957947</v>
       </c>
       <c r="H606" t="n">
         <v>1602470</v>
@@ -17972,7 +17972,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G607" t="n">
-        <v>3.68840098381042</v>
+        <v>3.68840146064758</v>
       </c>
       <c r="H607" t="n">
         <v>1876065</v>
@@ -18059,7 +18059,7 @@
         <v>5.43400001525879</v>
       </c>
       <c r="G610" t="n">
-        <v>3.67757368087769</v>
+        <v>3.67757320404053</v>
       </c>
       <c r="H610" t="n">
         <v>2056524</v>
@@ -18088,7 +18088,7 @@
         <v>5.49200010299683</v>
       </c>
       <c r="G611" t="n">
-        <v>3.71682572364807</v>
+        <v>3.71682548522949</v>
       </c>
       <c r="H611" t="n">
         <v>1932836</v>
@@ -18175,7 +18175,7 @@
         <v>5.52199983596802</v>
       </c>
       <c r="G614" t="n">
-        <v>3.73712873458862</v>
+        <v>3.73712849617004</v>
       </c>
       <c r="H614" t="n">
         <v>2119896</v>
@@ -18233,7 +18233,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G616" t="n">
-        <v>3.75201725959778</v>
+        <v>3.75201845169067</v>
       </c>
       <c r="H616" t="n">
         <v>1891956</v>
@@ -18291,7 +18291,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G618" t="n">
-        <v>3.78856348991394</v>
+        <v>3.78856372833252</v>
       </c>
       <c r="H618" t="n">
         <v>1967546</v>
@@ -18320,7 +18320,7 @@
         <v>5.53200006484985</v>
       </c>
       <c r="G619" t="n">
-        <v>3.743896484375</v>
+        <v>3.74389624595642</v>
       </c>
       <c r="H619" t="n">
         <v>1713013</v>
@@ -18349,7 +18349,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G620" t="n">
-        <v>3.76555299758911</v>
+        <v>3.76555347442627</v>
       </c>
       <c r="H620" t="n">
         <v>1306555</v>
@@ -18407,7 +18407,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G622" t="n">
-        <v>3.7046434879303</v>
+        <v>3.70464396476746</v>
       </c>
       <c r="H622" t="n">
         <v>2574109</v>
@@ -18436,7 +18436,7 @@
         <v>5.52600002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>3.73983597755432</v>
+        <v>3.7398362159729</v>
       </c>
       <c r="H623" t="n">
         <v>1474177</v>
@@ -18465,7 +18465,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G624" t="n">
-        <v>3.76555299758911</v>
+        <v>3.76555347442627</v>
       </c>
       <c r="H624" t="n">
         <v>1476786</v>
@@ -18494,7 +18494,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G625" t="n">
-        <v>3.73848295211792</v>
+        <v>3.73848247528076</v>
       </c>
       <c r="H625" t="n">
         <v>1213856</v>
@@ -18523,7 +18523,7 @@
         <v>5.5479998588562</v>
       </c>
       <c r="G626" t="n">
-        <v>3.75472521781921</v>
+        <v>3.75472450256348</v>
       </c>
       <c r="H626" t="n">
         <v>1113837</v>
@@ -18552,7 +18552,7 @@
         <v>5.5479998588562</v>
       </c>
       <c r="G627" t="n">
-        <v>3.75472521781921</v>
+        <v>3.75472450256348</v>
       </c>
       <c r="H627" t="n">
         <v>1184740</v>
@@ -18581,7 +18581,7 @@
         <v>5.53399991989136</v>
       </c>
       <c r="G628" t="n">
-        <v>3.74525046348572</v>
+        <v>3.7452507019043</v>
       </c>
       <c r="H628" t="n">
         <v>1443005</v>
@@ -18610,7 +18610,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G629" t="n">
-        <v>3.76284623146057</v>
+        <v>3.76284646987915</v>
       </c>
       <c r="H629" t="n">
         <v>1922645</v>
@@ -18639,7 +18639,7 @@
         <v>5.48799991607666</v>
       </c>
       <c r="G630" t="n">
-        <v>3.71411895751953</v>
+        <v>3.71411871910095</v>
       </c>
       <c r="H630" t="n">
         <v>2010281</v>
@@ -18668,7 +18668,7 @@
         <v>5.51399993896484</v>
       </c>
       <c r="G631" t="n">
-        <v>3.73171472549438</v>
+        <v>3.73171496391296</v>
       </c>
       <c r="H631" t="n">
         <v>1085790</v>
@@ -18697,7 +18697,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G632" t="n">
-        <v>3.71547222137451</v>
+        <v>3.71547198295593</v>
       </c>
       <c r="H632" t="n">
         <v>1133632</v>
@@ -18726,7 +18726,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G633" t="n">
-        <v>3.77908825874329</v>
+        <v>3.77908849716187</v>
       </c>
       <c r="H633" t="n">
         <v>2716436</v>
@@ -18784,7 +18784,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G635" t="n">
-        <v>3.70870494842529</v>
+        <v>3.70870471000671</v>
       </c>
       <c r="H635" t="n">
         <v>1383579</v>
@@ -18842,7 +18842,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G637" t="n">
-        <v>3.7817964553833</v>
+        <v>3.78179550170898</v>
       </c>
       <c r="H637" t="n">
         <v>2256127</v>
@@ -18871,7 +18871,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G638" t="n">
-        <v>3.81157398223877</v>
+        <v>3.81157374382019</v>
       </c>
       <c r="H638" t="n">
         <v>2561720</v>
@@ -18900,7 +18900,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G639" t="n">
-        <v>3.83864426612854</v>
+        <v>3.83864450454712</v>
       </c>
       <c r="H639" t="n">
         <v>3190537</v>
@@ -18929,7 +18929,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G640" t="n">
-        <v>3.90632200241089</v>
+        <v>3.90632176399231</v>
       </c>
       <c r="H640" t="n">
         <v>2212740</v>
@@ -18987,7 +18987,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>3.95403027534485</v>
+        <v>3.95402979850769</v>
       </c>
       <c r="H642" t="n">
         <v>2173043</v>
@@ -19045,7 +19045,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G644" t="n">
-        <v>4.03142166137695</v>
+        <v>4.03142213821411</v>
       </c>
       <c r="H644" t="n">
         <v>1861798</v>
@@ -19074,7 +19074,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G645" t="n">
-        <v>4.03423643112183</v>
+        <v>4.03423690795898</v>
       </c>
       <c r="H645" t="n">
         <v>1881231</v>
@@ -19103,7 +19103,7 @@
         <v>5.78200006484985</v>
       </c>
       <c r="G646" t="n">
-        <v>4.06800699234009</v>
+        <v>4.06800746917725</v>
       </c>
       <c r="H646" t="n">
         <v>2196920</v>
@@ -19132,7 +19132,7 @@
         <v>5.72200012207031</v>
       </c>
       <c r="G647" t="n">
-        <v>4.02579307556152</v>
+        <v>4.02579355239868</v>
       </c>
       <c r="H647" t="n">
         <v>1241978</v>
@@ -19161,7 +19161,7 @@
         <v>5.70800018310547</v>
       </c>
       <c r="G648" t="n">
-        <v>4.01594400405884</v>
+        <v>4.01594352722168</v>
       </c>
       <c r="H648" t="n">
         <v>1888164</v>
@@ -19190,7 +19190,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94699430465698</v>
+        <v>3.94699478149414</v>
       </c>
       <c r="H649" t="n">
         <v>2336188</v>
@@ -19248,7 +19248,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G651" t="n">
-        <v>3.98780107498169</v>
+        <v>3.98780059814453</v>
       </c>
       <c r="H651" t="n">
         <v>1959746</v>
@@ -19306,7 +19306,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>4.08770751953125</v>
+        <v>4.08770704269409</v>
       </c>
       <c r="H653" t="n">
         <v>2342463</v>
@@ -19335,7 +19335,7 @@
         <v>5.85799980163574</v>
       </c>
       <c r="G654" t="n">
-        <v>4.12147760391235</v>
+        <v>4.12147855758667</v>
       </c>
       <c r="H654" t="n">
         <v>2577078</v>
@@ -19364,7 +19364,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G655" t="n">
-        <v>4.13695669174194</v>
+        <v>4.1369571685791</v>
       </c>
       <c r="H655" t="n">
         <v>2552046</v>
@@ -19422,7 +19422,7 @@
         <v>5.89400005340576</v>
       </c>
       <c r="G657" t="n">
-        <v>4.14680624008179</v>
+        <v>4.14680671691895</v>
       </c>
       <c r="H657" t="n">
         <v>1210457</v>
@@ -19451,7 +19451,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G658" t="n">
-        <v>4.14117765426636</v>
+        <v>4.14117813110352</v>
       </c>
       <c r="H658" t="n">
         <v>1808264</v>
@@ -19480,7 +19480,7 @@
         <v>5.83599996566772</v>
       </c>
       <c r="G659" t="n">
-        <v>4.10599994659424</v>
+        <v>4.10599946975708</v>
       </c>
       <c r="H659" t="n">
         <v>1770544</v>
@@ -19509,7 +19509,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G660" t="n">
-        <v>4.13695669174194</v>
+        <v>4.1369571685791</v>
       </c>
       <c r="H660" t="n">
         <v>2035992</v>
@@ -19596,7 +19596,7 @@
         <v>6.12200021743774</v>
       </c>
       <c r="G663" t="n">
-        <v>4.3072190284729</v>
+        <v>4.30721950531006</v>
       </c>
       <c r="H663" t="n">
         <v>3197524</v>
@@ -19625,7 +19625,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G664" t="n">
-        <v>4.25796937942505</v>
+        <v>4.25796985626221</v>
       </c>
       <c r="H664" t="n">
         <v>2726415</v>
@@ -19741,7 +19741,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>4.26359844207764</v>
+        <v>4.26359796524048</v>
       </c>
       <c r="H668" t="n">
         <v>1452344</v>
@@ -19799,7 +19799,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G670" t="n">
-        <v>4.16650629043579</v>
+        <v>4.16650581359863</v>
       </c>
       <c r="H670" t="n">
         <v>2526378</v>
@@ -19828,7 +19828,7 @@
         <v>5.90799999237061</v>
       </c>
       <c r="G671" t="n">
-        <v>4.15665721893311</v>
+        <v>4.15665626525879</v>
       </c>
       <c r="H671" t="n">
         <v>2723118</v>
@@ -19857,7 +19857,7 @@
         <v>5.89799976348877</v>
       </c>
       <c r="G672" t="n">
-        <v>4.14962005615234</v>
+        <v>4.14962100982666</v>
       </c>
       <c r="H672" t="n">
         <v>1584912</v>
@@ -19886,7 +19886,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G673" t="n">
-        <v>4.24249124526978</v>
+        <v>4.24249172210693</v>
       </c>
       <c r="H673" t="n">
         <v>3177119</v>
@@ -19915,7 +19915,7 @@
         <v>6.09600019454956</v>
       </c>
       <c r="G674" t="n">
-        <v>4.28892612457275</v>
+        <v>4.28892660140991</v>
       </c>
       <c r="H674" t="n">
         <v>4501297</v>
@@ -19973,7 +19973,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G676" t="n">
-        <v>4.24952602386475</v>
+        <v>4.2495265007019</v>
       </c>
       <c r="H676" t="n">
         <v>1557634</v>
@@ -20002,7 +20002,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G677" t="n">
-        <v>4.30299711227417</v>
+        <v>4.30299806594849</v>
       </c>
       <c r="H677" t="n">
         <v>1999919</v>
@@ -20060,7 +20060,7 @@
         <v>6.12799978256226</v>
       </c>
       <c r="G679" t="n">
-        <v>4.31144046783447</v>
+        <v>4.31143999099731</v>
       </c>
       <c r="H679" t="n">
         <v>2050886</v>
@@ -20089,7 +20089,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G680" t="n">
-        <v>4.34943246841431</v>
+        <v>4.34943342208862</v>
       </c>
       <c r="H680" t="n">
         <v>2137342</v>
@@ -20118,7 +20118,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G681" t="n">
-        <v>4.36772584915161</v>
+        <v>4.36772537231445</v>
       </c>
       <c r="H681" t="n">
         <v>2306319</v>
@@ -20176,7 +20176,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G683" t="n">
-        <v>4.33395433425903</v>
+        <v>4.33395481109619</v>
       </c>
       <c r="H683" t="n">
         <v>1794099</v>
@@ -20263,7 +20263,7 @@
         <v>5.98999977111816</v>
       </c>
       <c r="G686" t="n">
-        <v>4.21434879302979</v>
+        <v>4.21434831619263</v>
       </c>
       <c r="H686" t="n">
         <v>2662580</v>
@@ -20292,7 +20292,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G687" t="n">
-        <v>4.24671220779419</v>
+        <v>4.24671268463135</v>
       </c>
       <c r="H687" t="n">
         <v>1790145</v>
@@ -20321,7 +20321,7 @@
         <v>6.02199983596802</v>
       </c>
       <c r="G688" t="n">
-        <v>4.23686218261719</v>
+        <v>4.23686265945435</v>
       </c>
       <c r="H688" t="n">
         <v>1209817</v>
@@ -20350,7 +20350,7 @@
         <v>5.97200012207031</v>
       </c>
       <c r="G689" t="n">
-        <v>4.20168447494507</v>
+        <v>4.20168399810791</v>
       </c>
       <c r="H689" t="n">
         <v>1594823</v>
@@ -20379,7 +20379,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G690" t="n">
-        <v>4.19464826583862</v>
+        <v>4.19464874267578</v>
       </c>
       <c r="H690" t="n">
         <v>2000465</v>
@@ -20408,7 +20408,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G691" t="n">
-        <v>4.14117765426636</v>
+        <v>4.14117813110352</v>
       </c>
       <c r="H691" t="n">
         <v>1961556</v>
@@ -20437,7 +20437,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G692" t="n">
-        <v>4.13695669174194</v>
+        <v>4.1369571685791</v>
       </c>
       <c r="H692" t="n">
         <v>1951320</v>
@@ -20466,7 +20466,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G693" t="n">
-        <v>4.06378602981567</v>
+        <v>4.06378650665283</v>
       </c>
       <c r="H693" t="n">
         <v>3390209</v>
@@ -20495,7 +20495,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G694" t="n">
-        <v>4.02297925949097</v>
+        <v>4.02297878265381</v>
       </c>
       <c r="H694" t="n">
         <v>3651847</v>
@@ -20582,7 +20582,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G697" t="n">
-        <v>4.09192895889282</v>
+        <v>4.09192848205566</v>
       </c>
       <c r="H697" t="n">
         <v>2123629</v>
@@ -20611,7 +20611,7 @@
         <v>5.7979998588562</v>
       </c>
       <c r="G698" t="n">
-        <v>4.07926416397095</v>
+        <v>4.07926464080811</v>
       </c>
       <c r="H698" t="n">
         <v>1588223</v>
@@ -20640,7 +20640,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>4.10177850723267</v>
+        <v>4.10177898406982</v>
       </c>
       <c r="H699" t="n">
         <v>1720119</v>
@@ -20698,7 +20698,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G701" t="n">
-        <v>3.93855094909668</v>
+        <v>3.93855166435242</v>
       </c>
       <c r="H701" t="n">
         <v>5230571</v>
@@ -20727,7 +20727,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G702" t="n">
-        <v>3.98357963562012</v>
+        <v>3.98358011245728</v>
       </c>
       <c r="H702" t="n">
         <v>1900172</v>
@@ -20756,7 +20756,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G703" t="n">
-        <v>4.06097173690796</v>
+        <v>4.0609712600708</v>
       </c>
       <c r="H703" t="n">
         <v>2347600</v>
@@ -20785,7 +20785,7 @@
         <v>5.6560001373291</v>
       </c>
       <c r="G704" t="n">
-        <v>3.97935795783997</v>
+        <v>3.97935843467712</v>
       </c>
       <c r="H704" t="n">
         <v>3234030</v>
@@ -20843,7 +20843,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G706" t="n">
-        <v>4.1200704574585</v>
+        <v>4.12007093429565</v>
       </c>
       <c r="H706" t="n">
         <v>1986363</v>
@@ -20901,7 +20901,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G708" t="n">
-        <v>4.09192895889282</v>
+        <v>4.09192848205566</v>
       </c>
       <c r="H708" t="n">
         <v>1143161</v>
@@ -20930,7 +20930,7 @@
         <v>5.72200012207031</v>
       </c>
       <c r="G709" t="n">
-        <v>4.02579307556152</v>
+        <v>4.02579355239868</v>
       </c>
       <c r="H709" t="n">
         <v>1515013</v>
@@ -20959,7 +20959,7 @@
         <v>5.71600008010864</v>
       </c>
       <c r="G710" t="n">
-        <v>4.02157211303711</v>
+        <v>4.02157258987427</v>
       </c>
       <c r="H710" t="n">
         <v>958675</v>
@@ -21046,7 +21046,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G713" t="n">
-        <v>4.03423643112183</v>
+        <v>4.03423690795898</v>
       </c>
       <c r="H713" t="n">
         <v>1504144</v>
@@ -21075,7 +21075,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G714" t="n">
-        <v>4.15525007247925</v>
+        <v>4.15524959564209</v>
       </c>
       <c r="H714" t="n">
         <v>2551492</v>
@@ -21104,7 +21104,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G715" t="n">
-        <v>4.15102767944336</v>
+        <v>4.15102815628052</v>
       </c>
       <c r="H715" t="n">
         <v>2968608</v>
@@ -21220,7 +21220,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>4.12992095947266</v>
+        <v>4.12992143630981</v>
       </c>
       <c r="H719" t="n">
         <v>1890783</v>
@@ -21278,7 +21278,7 @@
         <v>5.72599983215332</v>
       </c>
       <c r="G721" t="n">
-        <v>4.02860736846924</v>
+        <v>4.0286078453064</v>
       </c>
       <c r="H721" t="n">
         <v>2105949</v>
@@ -21307,7 +21307,7 @@
         <v>5.63600015640259</v>
       </c>
       <c r="G722" t="n">
-        <v>3.96528720855713</v>
+        <v>3.96528697013855</v>
       </c>
       <c r="H722" t="n">
         <v>2591482</v>
@@ -21365,7 +21365,7 @@
         <v>5.69199991226196</v>
       </c>
       <c r="G724" t="n">
-        <v>4.00468683242798</v>
+        <v>4.00468635559082</v>
       </c>
       <c r="H724" t="n">
         <v>2590263</v>
@@ -21394,7 +21394,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G725" t="n">
-        <v>3.96388006210327</v>
+        <v>3.96388030052185</v>
       </c>
       <c r="H725" t="n">
         <v>1624360</v>
@@ -21423,7 +21423,7 @@
         <v>5.61399984359741</v>
       </c>
       <c r="G726" t="n">
-        <v>3.94980883598328</v>
+        <v>3.94980788230896</v>
       </c>
       <c r="H726" t="n">
         <v>2078476</v>
@@ -21481,7 +21481,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>4.00328016281128</v>
+        <v>4.00327920913696</v>
       </c>
       <c r="H728" t="n">
         <v>2005242</v>
@@ -21510,7 +21510,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G729" t="n">
-        <v>4.00328016281128</v>
+        <v>4.00327920913696</v>
       </c>
       <c r="H729" t="n">
         <v>2079379</v>
@@ -21539,7 +21539,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G730" t="n">
-        <v>4.00609397888184</v>
+        <v>4.00609445571899</v>
       </c>
       <c r="H730" t="n">
         <v>5585827</v>
@@ -21568,7 +21568,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G731" t="n">
-        <v>4.07082176208496</v>
+        <v>4.0708212852478</v>
       </c>
       <c r="H731" t="n">
         <v>2893830</v>
@@ -21597,7 +21597,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G732" t="n">
-        <v>4.15525007247925</v>
+        <v>4.15524959564209</v>
       </c>
       <c r="H732" t="n">
         <v>3095858</v>
@@ -21684,7 +21684,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G735" t="n">
-        <v>4.14258480072021</v>
+        <v>4.14258527755737</v>
       </c>
       <c r="H735" t="n">
         <v>2133876</v>
@@ -21713,7 +21713,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G736" t="n">
-        <v>4.16650629043579</v>
+        <v>4.16650581359863</v>
       </c>
       <c r="H736" t="n">
         <v>1760492</v>
@@ -21916,7 +21916,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G743" t="n">
-        <v>4.06660079956055</v>
+        <v>4.06659984588623</v>
       </c>
       <c r="H743" t="n">
         <v>1924712</v>
@@ -21945,7 +21945,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G744" t="n">
-        <v>4.01031494140625</v>
+        <v>4.01031446456909</v>
       </c>
       <c r="H744" t="n">
         <v>1958168</v>
@@ -22032,7 +22032,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G747" t="n">
-        <v>4.00890827178955</v>
+        <v>4.00890779495239</v>
       </c>
       <c r="H747" t="n">
         <v>1847746</v>
@@ -22177,7 +22177,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G752" t="n">
-        <v>4.02297925949097</v>
+        <v>4.02297878265381</v>
       </c>
       <c r="H752" t="n">
         <v>1504461</v>
@@ -22206,7 +22206,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G753" t="n">
-        <v>3.9906153678894</v>
+        <v>3.99061512947083</v>
       </c>
       <c r="H753" t="n">
         <v>1519156</v>
@@ -22235,7 +22235,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>4.03142166137695</v>
+        <v>4.03142213821411</v>
       </c>
       <c r="H754" t="n">
         <v>1468194</v>
@@ -22264,7 +22264,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G755" t="n">
-        <v>4.03142166137695</v>
+        <v>4.03142213821411</v>
       </c>
       <c r="H755" t="n">
         <v>1178469</v>
@@ -22293,7 +22293,7 @@
         <v>5.71799993515015</v>
       </c>
       <c r="G756" t="n">
-        <v>4.02297925949097</v>
+        <v>4.02297878265381</v>
       </c>
       <c r="H756" t="n">
         <v>1303279</v>
@@ -22322,7 +22322,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G757" t="n">
-        <v>4.00187301635742</v>
+        <v>4.00187253952026</v>
       </c>
       <c r="H757" t="n">
         <v>2492570</v>
@@ -22351,7 +22351,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G758" t="n">
-        <v>4.06660079956055</v>
+        <v>4.06659984588623</v>
       </c>
       <c r="H758" t="n">
         <v>2043707</v>
@@ -22380,7 +22380,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G759" t="n">
-        <v>4.0581579208374</v>
+        <v>4.05815744400024</v>
       </c>
       <c r="H759" t="n">
         <v>2104505</v>
@@ -22496,7 +22496,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G763" t="n">
-        <v>4.16509866714478</v>
+        <v>4.16509914398193</v>
       </c>
       <c r="H763" t="n">
         <v>1824296</v>
@@ -22583,7 +22583,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G766" t="n">
-        <v>4.12288522720337</v>
+        <v>4.12288570404053</v>
       </c>
       <c r="H766" t="n">
         <v>1229876</v>
@@ -22641,7 +22641,7 @@
         <v>5.97599983215332</v>
       </c>
       <c r="G768" t="n">
-        <v>4.20449876785278</v>
+        <v>4.20449829101562</v>
       </c>
       <c r="H768" t="n">
         <v>1631192</v>
@@ -22670,7 +22670,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G769" t="n">
-        <v>4.14117765426636</v>
+        <v>4.14117813110352</v>
       </c>
       <c r="H769" t="n">
         <v>2385144</v>
@@ -22728,7 +22728,7 @@
         <v>5.82200002670288</v>
       </c>
       <c r="G771" t="n">
-        <v>4.09614992141724</v>
+        <v>4.09614944458008</v>
       </c>
       <c r="H771" t="n">
         <v>1486107</v>
@@ -22786,7 +22786,7 @@
         <v>5.76599979400635</v>
       </c>
       <c r="G773" t="n">
-        <v>4.05675029754639</v>
+        <v>4.05674982070923</v>
       </c>
       <c r="H773" t="n">
         <v>1799150</v>
@@ -22815,7 +22815,7 @@
         <v>5.75</v>
       </c>
       <c r="G774" t="n">
-        <v>4.04549360275269</v>
+        <v>4.04549312591553</v>
       </c>
       <c r="H774" t="n">
         <v>1402877</v>
@@ -22873,7 +22873,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G776" t="n">
-        <v>4.06660079956055</v>
+        <v>4.06659984588623</v>
       </c>
       <c r="H776" t="n">
         <v>1321194</v>
@@ -22902,7 +22902,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G777" t="n">
-        <v>4.0412712097168</v>
+        <v>4.04127216339111</v>
       </c>
       <c r="H777" t="n">
         <v>1890089</v>
@@ -22960,7 +22960,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G779" t="n">
-        <v>4.04689979553223</v>
+        <v>4.04690027236938</v>
       </c>
       <c r="H779" t="n">
         <v>1034560</v>
@@ -23018,7 +23018,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G781" t="n">
-        <v>3.83864521980286</v>
+        <v>3.83864593505859</v>
       </c>
       <c r="H781" t="n">
         <v>4756331</v>
@@ -23047,7 +23047,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G782" t="n">
-        <v>3.90055990219116</v>
+        <v>3.900559425354</v>
       </c>
       <c r="H782" t="n">
         <v>3299250</v>
@@ -23105,7 +23105,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G784" t="n">
-        <v>3.87663793563843</v>
+        <v>3.87663841247559</v>
       </c>
       <c r="H784" t="n">
         <v>1880712</v>
@@ -23134,7 +23134,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G785" t="n">
-        <v>3.8484947681427</v>
+        <v>3.84849548339844</v>
       </c>
       <c r="H785" t="n">
         <v>1765297</v>
@@ -23163,7 +23163,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G786" t="n">
-        <v>3.78517460823059</v>
+        <v>3.78517484664917</v>
       </c>
       <c r="H786" t="n">
         <v>2931931</v>
@@ -23192,7 +23192,7 @@
         <v>5.43599987030029</v>
       </c>
       <c r="G787" t="n">
-        <v>3.82457423210144</v>
+        <v>3.82457399368286</v>
       </c>
       <c r="H787" t="n">
         <v>3245860</v>
@@ -23221,7 +23221,7 @@
         <v>5.5</v>
       </c>
       <c r="G788" t="n">
-        <v>3.86960196495056</v>
+        <v>3.8696026802063</v>
       </c>
       <c r="H788" t="n">
         <v>1885870</v>
@@ -23250,7 +23250,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G789" t="n">
-        <v>3.82035231590271</v>
+        <v>3.82035303115845</v>
       </c>
       <c r="H789" t="n">
         <v>2128253</v>
@@ -23279,7 +23279,7 @@
         <v>5.43599987030029</v>
       </c>
       <c r="G790" t="n">
-        <v>3.82457423210144</v>
+        <v>3.82457399368286</v>
       </c>
       <c r="H790" t="n">
         <v>2623020</v>
@@ -23308,7 +23308,7 @@
         <v>5.49200010299683</v>
       </c>
       <c r="G791" t="n">
-        <v>3.86397433280945</v>
+        <v>3.86397361755371</v>
       </c>
       <c r="H791" t="n">
         <v>2307388</v>
@@ -23337,7 +23337,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G792" t="n">
-        <v>3.95403027534485</v>
+        <v>3.95402979850769</v>
       </c>
       <c r="H792" t="n">
         <v>3429073</v>
@@ -23366,7 +23366,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G793" t="n">
-        <v>3.93151545524597</v>
+        <v>3.93151617050171</v>
       </c>
       <c r="H793" t="n">
         <v>2352694</v>
@@ -23395,7 +23395,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G794" t="n">
-        <v>3.93855094909668</v>
+        <v>3.93855166435242</v>
       </c>
       <c r="H794" t="n">
         <v>2148060</v>
@@ -23424,7 +23424,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G795" t="n">
-        <v>3.98639345169067</v>
+        <v>3.98639464378357</v>
       </c>
       <c r="H795" t="n">
         <v>7441044</v>
@@ -23453,7 +23453,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G796" t="n">
-        <v>3.95121598243713</v>
+        <v>3.95121669769287</v>
       </c>
       <c r="H796" t="n">
         <v>945346</v>
@@ -23482,7 +23482,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G797" t="n">
-        <v>3.96106600761414</v>
+        <v>3.9610652923584</v>
       </c>
       <c r="H797" t="n">
         <v>1004925</v>
@@ -23511,7 +23511,7 @@
         <v>5.44399976730347</v>
       </c>
       <c r="G798" t="n">
-        <v>3.83020210266113</v>
+        <v>3.83020257949829</v>
       </c>
       <c r="H798" t="n">
         <v>4716102</v>
@@ -23540,7 +23540,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91744422912598</v>
+        <v>3.91744446754456</v>
       </c>
       <c r="H799" t="n">
         <v>2867974</v>
@@ -23569,7 +23569,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G800" t="n">
-        <v>3.91040921211243</v>
+        <v>3.91040897369385</v>
       </c>
       <c r="H800" t="n">
         <v>2353232</v>
@@ -23598,7 +23598,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>3.85553121566772</v>
+        <v>3.85553169250488</v>
       </c>
       <c r="H801" t="n">
         <v>2175694</v>
@@ -23627,7 +23627,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G802" t="n">
-        <v>3.85130977630615</v>
+        <v>3.85130953788757</v>
       </c>
       <c r="H802" t="n">
         <v>2319002</v>
@@ -23656,7 +23656,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>3.92588710784912</v>
+        <v>3.92588758468628</v>
       </c>
       <c r="H803" t="n">
         <v>3693207</v>
@@ -23743,7 +23743,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G806" t="n">
-        <v>3.9906153678894</v>
+        <v>3.99061512947083</v>
       </c>
       <c r="H806" t="n">
         <v>2564951</v>
@@ -23859,7 +23859,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G810" t="n">
-        <v>4.0581579208374</v>
+        <v>4.05815744400024</v>
       </c>
       <c r="H810" t="n">
         <v>2220985</v>
@@ -23946,7 +23946,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G813" t="n">
-        <v>4.01031494140625</v>
+        <v>4.01031446456909</v>
       </c>
       <c r="H813" t="n">
         <v>1717511</v>
@@ -23975,7 +23975,7 @@
         <v>5.77600002288818</v>
       </c>
       <c r="G814" t="n">
-        <v>4.06378602981567</v>
+        <v>4.06378650665283</v>
       </c>
       <c r="H814" t="n">
         <v>4365856</v>
@@ -24265,7 +24265,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G824" t="n">
-        <v>4.30018281936646</v>
+        <v>4.30018329620361</v>
       </c>
       <c r="H824" t="n">
         <v>2088908</v>
@@ -24294,7 +24294,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G825" t="n">
-        <v>4.27063369750977</v>
+        <v>4.27063322067261</v>
       </c>
       <c r="H825" t="n">
         <v>1721301</v>
@@ -24323,7 +24323,7 @@
         <v>6.07200002670288</v>
       </c>
       <c r="G826" t="n">
-        <v>4.27204132080078</v>
+        <v>4.27204084396362</v>
       </c>
       <c r="H826" t="n">
         <v>1331440</v>
@@ -24352,7 +24352,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G827" t="n">
-        <v>4.31988382339478</v>
+        <v>4.31988334655762</v>
       </c>
       <c r="H827" t="n">
         <v>1725683</v>
@@ -24410,7 +24410,7 @@
         <v>6.05800008773804</v>
       </c>
       <c r="G829" t="n">
-        <v>4.26219129562378</v>
+        <v>4.26219081878662</v>
       </c>
       <c r="H829" t="n">
         <v>2297393</v>
@@ -24468,7 +24468,7 @@
         <v>6.10400009155273</v>
       </c>
       <c r="G831" t="n">
-        <v>4.29455471038818</v>
+        <v>4.29455518722534</v>
       </c>
       <c r="H831" t="n">
         <v>1364600</v>
@@ -24642,7 +24642,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G837" t="n">
-        <v>4.0412712097168</v>
+        <v>4.04127216339111</v>
       </c>
       <c r="H837" t="n">
         <v>4004963</v>
@@ -24671,7 +24671,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G838" t="n">
-        <v>4.08348512649536</v>
+        <v>4.08348560333252</v>
       </c>
       <c r="H838" t="n">
         <v>2885826</v>
@@ -24700,7 +24700,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G839" t="n">
-        <v>4.0806713104248</v>
+        <v>4.08067178726196</v>
       </c>
       <c r="H839" t="n">
         <v>4239735</v>
@@ -24729,7 +24729,7 @@
         <v>5.53200006484985</v>
       </c>
       <c r="G840" t="n">
-        <v>3.89211630821228</v>
+        <v>3.89211583137512</v>
       </c>
       <c r="H840" t="n">
         <v>5273255</v>
@@ -24758,7 +24758,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>3.91181635856628</v>
+        <v>3.91181564331055</v>
       </c>
       <c r="H841" t="n">
         <v>4148352</v>
@@ -24787,7 +24787,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G842" t="n">
-        <v>3.96106600761414</v>
+        <v>3.9610652923584</v>
       </c>
       <c r="H842" t="n">
         <v>3104286</v>
@@ -24816,7 +24816,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G843" t="n">
-        <v>4.09192895889282</v>
+        <v>4.09192848205566</v>
       </c>
       <c r="H843" t="n">
         <v>4384629</v>
@@ -24845,7 +24845,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G844" t="n">
-        <v>4.0806713104248</v>
+        <v>4.08067178726196</v>
       </c>
       <c r="H844" t="n">
         <v>5643990</v>
@@ -24874,7 +24874,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G845" t="n">
-        <v>3.91744422912598</v>
+        <v>3.91744446754456</v>
       </c>
       <c r="H845" t="n">
         <v>3403862</v>
@@ -24932,7 +24932,7 @@
         <v>4.78700017929077</v>
       </c>
       <c r="G847" t="n">
-        <v>3.36796140670776</v>
+        <v>3.36796116828918</v>
       </c>
       <c r="H847" t="n">
         <v>5662703</v>
@@ -24990,7 +24990,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>2.89305567741394</v>
+        <v>2.89305543899536</v>
       </c>
       <c r="H849" t="n">
         <v>7919024</v>
@@ -25048,7 +25048,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G851" t="n">
-        <v>3.01688241958618</v>
+        <v>3.01688265800476</v>
       </c>
       <c r="H851" t="n">
         <v>6418167</v>
@@ -25135,7 +25135,7 @@
         <v>4.56099987030029</v>
       </c>
       <c r="G854" t="n">
-        <v>3.20895552635193</v>
+        <v>3.20895576477051</v>
       </c>
       <c r="H854" t="n">
         <v>6496730</v>
@@ -25164,7 +25164,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G855" t="n">
-        <v>3.07457518577576</v>
+        <v>3.07457494735718</v>
       </c>
       <c r="H855" t="n">
         <v>10545254</v>
@@ -25193,7 +25193,7 @@
         <v>4.25899982452393</v>
       </c>
       <c r="G856" t="n">
-        <v>2.99647927284241</v>
+        <v>2.99647903442383</v>
       </c>
       <c r="H856" t="n">
         <v>4507664</v>
@@ -25222,7 +25222,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G857" t="n">
-        <v>3.21247339248657</v>
+        <v>3.21247363090515</v>
       </c>
       <c r="H857" t="n">
         <v>3721659</v>
@@ -25280,7 +25280,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>3.20121669769287</v>
+        <v>3.20121645927429</v>
       </c>
       <c r="H859" t="n">
         <v>5661844</v>
@@ -25309,7 +25309,7 @@
         <v>4.57100009918213</v>
       </c>
       <c r="G860" t="n">
-        <v>3.21599125862122</v>
+        <v>3.21599102020264</v>
       </c>
       <c r="H860" t="n">
         <v>2461394</v>
@@ -25367,7 +25367,7 @@
         <v>4.98899984359741</v>
       </c>
       <c r="G862" t="n">
-        <v>3.51008129119873</v>
+        <v>3.51008105278015</v>
       </c>
       <c r="H862" t="n">
         <v>3920930</v>
@@ -25396,7 +25396,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G863" t="n">
-        <v>3.30252933502197</v>
+        <v>3.30253005027771</v>
       </c>
       <c r="H863" t="n">
         <v>2955236</v>
@@ -25425,7 +25425,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G864" t="n">
-        <v>3.40525031089783</v>
+        <v>3.40525007247925</v>
       </c>
       <c r="H864" t="n">
         <v>1508109</v>
@@ -25483,7 +25483,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G866" t="n">
-        <v>3.38554978370667</v>
+        <v>3.38555002212524</v>
       </c>
       <c r="H866" t="n">
         <v>2520981</v>
@@ -25512,7 +25512,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>3.39821410179138</v>
+        <v>3.39821457862854</v>
       </c>
       <c r="H867" t="n">
         <v>3567898</v>
@@ -25570,7 +25570,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G869" t="n">
-        <v>3.39680695533752</v>
+        <v>3.39680743217468</v>
       </c>
       <c r="H869" t="n">
         <v>1149332</v>
@@ -25628,7 +25628,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G871" t="n">
-        <v>3.44042778015137</v>
+        <v>3.44042754173279</v>
       </c>
       <c r="H871" t="n">
         <v>2347024</v>
@@ -25657,7 +25657,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G872" t="n">
-        <v>3.47138500213623</v>
+        <v>3.47138524055481</v>
       </c>
       <c r="H872" t="n">
         <v>2886869</v>
@@ -25686,7 +25686,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G873" t="n">
-        <v>3.41932106018066</v>
+        <v>3.41932153701782</v>
       </c>
       <c r="H873" t="n">
         <v>1883840</v>
@@ -25715,7 +25715,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G874" t="n">
-        <v>3.42072820663452</v>
+        <v>3.42072868347168</v>
       </c>
       <c r="H874" t="n">
         <v>1580035</v>
@@ -25773,7 +25773,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G876" t="n">
-        <v>3.46294236183167</v>
+        <v>3.46294212341309</v>
       </c>
       <c r="H876" t="n">
         <v>1912585</v>
@@ -25802,7 +25802,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G877" t="n">
-        <v>3.37710762023926</v>
+        <v>3.37710738182068</v>
       </c>
       <c r="H877" t="n">
         <v>2311934</v>
@@ -25831,7 +25831,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G878" t="n">
-        <v>3.42213559150696</v>
+        <v>3.42213535308838</v>
       </c>
       <c r="H878" t="n">
         <v>1632555</v>
@@ -25889,7 +25889,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G880" t="n">
-        <v>3.41510057449341</v>
+        <v>3.41510009765625</v>
       </c>
       <c r="H880" t="n">
         <v>2751793</v>
@@ -25976,7 +25976,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G883" t="n">
-        <v>3.5248556137085</v>
+        <v>3.52485632896423</v>
       </c>
       <c r="H883" t="n">
         <v>2701652</v>
@@ -26034,7 +26034,7 @@
         <v>4.90799999237061</v>
       </c>
       <c r="G885" t="n">
-        <v>3.45309257507324</v>
+        <v>3.4530918598175</v>
       </c>
       <c r="H885" t="n">
         <v>2233720</v>
@@ -26121,7 +26121,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G888" t="n">
-        <v>3.47701358795166</v>
+        <v>3.47701334953308</v>
       </c>
       <c r="H888" t="n">
         <v>1537490</v>
@@ -26150,7 +26150,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G889" t="n">
-        <v>3.46997809410095</v>
+        <v>3.46997785568237</v>
       </c>
       <c r="H889" t="n">
         <v>1627305</v>
@@ -26179,7 +26179,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G890" t="n">
-        <v>3.48264145851135</v>
+        <v>3.48264169692993</v>
       </c>
       <c r="H890" t="n">
         <v>1701329</v>
@@ -26208,7 +26208,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G891" t="n">
-        <v>3.46857070922852</v>
+        <v>3.46857118606567</v>
       </c>
       <c r="H891" t="n">
         <v>2602511</v>
@@ -26237,7 +26237,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G892" t="n">
-        <v>3.55299878120422</v>
+        <v>3.55299830436707</v>
       </c>
       <c r="H892" t="n">
         <v>3832249</v>
@@ -26324,7 +26324,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G895" t="n">
-        <v>3.50748705863953</v>
+        <v>3.50748682022095</v>
       </c>
       <c r="H895" t="n">
         <v>2423241</v>
@@ -26353,7 +26353,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>3.47941493988037</v>
+        <v>3.47941517829895</v>
       </c>
       <c r="H896" t="n">
         <v>2114648</v>
@@ -26382,7 +26382,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.5281708240509</v>
+        <v>3.52817106246948</v>
       </c>
       <c r="H897" t="n">
         <v>1536527</v>
@@ -26411,7 +26411,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G898" t="n">
-        <v>3.59022450447083</v>
+        <v>3.59022426605225</v>
       </c>
       <c r="H898" t="n">
         <v>1285941</v>
@@ -26440,7 +26440,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G899" t="n">
-        <v>3.57101774215698</v>
+        <v>3.57101726531982</v>
       </c>
       <c r="H899" t="n">
         <v>1897548</v>
@@ -26469,7 +26469,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G900" t="n">
-        <v>3.54442310333252</v>
+        <v>3.5444233417511</v>
       </c>
       <c r="H900" t="n">
         <v>2992412</v>
@@ -26527,7 +26527,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G902" t="n">
-        <v>3.60943198204041</v>
+        <v>3.60943174362183</v>
       </c>
       <c r="H902" t="n">
         <v>4042772</v>
@@ -26556,7 +26556,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G903" t="n">
-        <v>3.65670967102051</v>
+        <v>3.65670990943909</v>
       </c>
       <c r="H903" t="n">
         <v>2167799</v>
@@ -26585,7 +26585,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G904" t="n">
-        <v>3.73797011375427</v>
+        <v>3.73797059059143</v>
       </c>
       <c r="H904" t="n">
         <v>2834004</v>
@@ -26614,7 +26614,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G905" t="n">
-        <v>3.82661747932434</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H905" t="n">
         <v>2792947</v>
@@ -26672,7 +26672,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G907" t="n">
-        <v>3.82661747932434</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H907" t="n">
         <v>3358447</v>
@@ -26788,7 +26788,7 @@
         <v>4.94600009918213</v>
       </c>
       <c r="G911" t="n">
-        <v>3.65375542640686</v>
+        <v>3.65375566482544</v>
       </c>
       <c r="H911" t="n">
         <v>4498942</v>
@@ -26846,7 +26846,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G913" t="n">
-        <v>3.82661747932434</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H913" t="n">
         <v>4189234</v>
@@ -26904,7 +26904,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G915" t="n">
-        <v>3.88571643829346</v>
+        <v>3.88571619987488</v>
       </c>
       <c r="H915" t="n">
         <v>3188279</v>
@@ -26991,7 +26991,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G918" t="n">
-        <v>3.88571643829346</v>
+        <v>3.88571619987488</v>
       </c>
       <c r="H918" t="n">
         <v>2502322</v>
@@ -27049,7 +27049,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G920" t="n">
-        <v>3.84877943992615</v>
+        <v>3.84877991676331</v>
       </c>
       <c r="H920" t="n">
         <v>2233213</v>
@@ -27078,7 +27078,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G921" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706835746765</v>
       </c>
       <c r="H921" t="n">
         <v>3095595</v>
@@ -27107,7 +27107,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G922" t="n">
-        <v>3.81923055648804</v>
+        <v>3.81923031806946</v>
       </c>
       <c r="H922" t="n">
         <v>1877418</v>
@@ -27136,7 +27136,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G923" t="n">
-        <v>3.84877943992615</v>
+        <v>3.84877991676331</v>
       </c>
       <c r="H923" t="n">
         <v>1408843</v>
@@ -27165,7 +27165,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>3.81923055648804</v>
+        <v>3.81923031806946</v>
       </c>
       <c r="H924" t="n">
         <v>1851655</v>
@@ -27194,7 +27194,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G925" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355376243591</v>
       </c>
       <c r="H925" t="n">
         <v>1571648</v>
@@ -27252,7 +27252,7 @@
         <v>5.22499990463257</v>
       </c>
       <c r="G927" t="n">
-        <v>3.85986042022705</v>
+        <v>3.85986018180847</v>
       </c>
       <c r="H927" t="n">
         <v>790824</v>
@@ -27281,7 +27281,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G928" t="n">
-        <v>3.8967969417572</v>
+        <v>3.89679741859436</v>
       </c>
       <c r="H928" t="n">
         <v>1385968</v>
@@ -27339,7 +27339,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>3.88202238082886</v>
+        <v>3.88202261924744</v>
       </c>
       <c r="H930" t="n">
         <v>1410213</v>
@@ -27368,7 +27368,7 @@
         <v>5.125</v>
       </c>
       <c r="G931" t="n">
-        <v>3.78598809242249</v>
+        <v>3.78598785400391</v>
       </c>
       <c r="H931" t="n">
         <v>2346143</v>
@@ -27397,7 +27397,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G932" t="n">
-        <v>3.79337501525879</v>
+        <v>3.79337453842163</v>
       </c>
       <c r="H932" t="n">
         <v>2175651</v>
@@ -27426,7 +27426,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G933" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706835746765</v>
       </c>
       <c r="H933" t="n">
         <v>1504744</v>
@@ -27455,7 +27455,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G934" t="n">
-        <v>3.76751971244812</v>
+        <v>3.76751923561096</v>
       </c>
       <c r="H934" t="n">
         <v>2270850</v>
@@ -27484,7 +27484,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>3.80076217651367</v>
+        <v>3.80076241493225</v>
       </c>
       <c r="H935" t="n">
         <v>2443627</v>
@@ -27542,7 +27542,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G937" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355376243591</v>
       </c>
       <c r="H937" t="n">
         <v>2386659</v>
@@ -27571,7 +27571,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G938" t="n">
-        <v>3.90049076080322</v>
+        <v>3.9004909992218</v>
       </c>
       <c r="H938" t="n">
         <v>1613100</v>
@@ -27600,7 +27600,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G939" t="n">
-        <v>3.94850826263428</v>
+        <v>3.94850778579712</v>
       </c>
       <c r="H939" t="n">
         <v>2557114</v>
@@ -27629,7 +27629,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G940" t="n">
-        <v>3.93003988265991</v>
+        <v>3.93004012107849</v>
       </c>
       <c r="H940" t="n">
         <v>1145389</v>
@@ -27687,7 +27687,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G942" t="n">
-        <v>3.87463545799255</v>
+        <v>3.8746349811554</v>
       </c>
       <c r="H942" t="n">
         <v>2057182</v>
@@ -27716,7 +27716,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G943" t="n">
-        <v>3.9522020816803</v>
+        <v>3.95220136642456</v>
       </c>
       <c r="H943" t="n">
         <v>3126340</v>
@@ -27745,7 +27745,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G944" t="n">
-        <v>4.0777850151062</v>
+        <v>4.07778549194336</v>
       </c>
       <c r="H944" t="n">
         <v>3399468</v>
@@ -27803,7 +27803,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H946" t="n">
         <v>2526362</v>
@@ -27832,7 +27832,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G947" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868772506714</v>
       </c>
       <c r="H947" t="n">
         <v>5104622</v>
@@ -27861,7 +27861,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G948" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868772506714</v>
       </c>
       <c r="H948" t="n">
         <v>2449394</v>
@@ -27890,7 +27890,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H949" t="n">
         <v>1923021</v>
@@ -27948,7 +27948,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G951" t="n">
-        <v>3.98913764953613</v>
+        <v>3.98913812637329</v>
       </c>
       <c r="H951" t="n">
         <v>1899163</v>
@@ -28006,7 +28006,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>4.10364151000977</v>
+        <v>4.10364103317261</v>
       </c>
       <c r="H953" t="n">
         <v>1188557</v>
@@ -28064,7 +28064,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G955" t="n">
-        <v>4.23291873931885</v>
+        <v>4.23291921615601</v>
       </c>
       <c r="H955" t="n">
         <v>2175172</v>
@@ -28093,7 +28093,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>4.20337009429932</v>
+        <v>4.20336961746216</v>
       </c>
       <c r="H956" t="n">
         <v>2050585</v>
@@ -28296,7 +28296,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G963" t="n">
-        <v>4.12949752807617</v>
+        <v>4.12949705123901</v>
       </c>
       <c r="H963" t="n">
         <v>1881728</v>
@@ -28354,7 +28354,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H965" t="n">
         <v>1639295</v>
@@ -28383,7 +28383,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G966" t="n">
-        <v>3.98913764953613</v>
+        <v>3.98913812637329</v>
       </c>
       <c r="H966" t="n">
         <v>1127368</v>
@@ -28412,7 +28412,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G967" t="n">
-        <v>3.95958924293518</v>
+        <v>3.9595890045166</v>
       </c>
       <c r="H967" t="n">
         <v>1898539</v>
@@ -28470,7 +28470,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G969" t="n">
-        <v>3.95958924293518</v>
+        <v>3.9595890045166</v>
       </c>
       <c r="H969" t="n">
         <v>1553786</v>
@@ -28557,7 +28557,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G972" t="n">
-        <v>3.90049076080322</v>
+        <v>3.9004909992218</v>
       </c>
       <c r="H972" t="n">
         <v>2466907</v>
@@ -28586,7 +28586,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G973" t="n">
-        <v>3.99652552604675</v>
+        <v>3.99652576446533</v>
       </c>
       <c r="H973" t="n">
         <v>1022879</v>
@@ -28644,7 +28644,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G975" t="n">
-        <v>4.01129961013794</v>
+        <v>4.0113000869751</v>
       </c>
       <c r="H975" t="n">
         <v>1291408</v>
@@ -28702,7 +28702,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G977" t="n">
-        <v>4.01129961013794</v>
+        <v>4.0113000869751</v>
       </c>
       <c r="H977" t="n">
         <v>1569022</v>
@@ -28731,7 +28731,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.94112086296082</v>
+        <v>3.94112062454224</v>
       </c>
       <c r="H978" t="n">
         <v>1454082</v>
@@ -28760,7 +28760,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99652552604675</v>
+        <v>3.99652576446533</v>
       </c>
       <c r="H979" t="n">
         <v>1645876</v>
@@ -28818,7 +28818,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G981" t="n">
-        <v>3.98913764953613</v>
+        <v>3.98913812637329</v>
       </c>
       <c r="H981" t="n">
         <v>1899740</v>
@@ -28905,7 +28905,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G984" t="n">
-        <v>3.97805714607239</v>
+        <v>3.97805786132812</v>
       </c>
       <c r="H984" t="n">
         <v>1253572</v>
@@ -28934,7 +28934,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G985" t="n">
-        <v>3.97436356544495</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H985" t="n">
         <v>1083034</v>
@@ -28963,7 +28963,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G986" t="n">
-        <v>3.98175024986267</v>
+        <v>3.98175048828125</v>
       </c>
       <c r="H986" t="n">
         <v>993070</v>
@@ -28992,7 +28992,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G987" t="n">
-        <v>3.9522020816803</v>
+        <v>3.95220136642456</v>
       </c>
       <c r="H987" t="n">
         <v>958950</v>
@@ -29079,7 +29079,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G990" t="n">
-        <v>3.97805714607239</v>
+        <v>3.97805786132812</v>
       </c>
       <c r="H990" t="n">
         <v>1250603</v>
@@ -29166,7 +29166,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G993" t="n">
-        <v>3.90418386459351</v>
+        <v>3.90418410301208</v>
       </c>
       <c r="H993" t="n">
         <v>949710</v>
@@ -29195,7 +29195,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G994" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706835746765</v>
       </c>
       <c r="H994" t="n">
         <v>5985952</v>
@@ -29224,7 +29224,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>3.72688961029053</v>
+        <v>3.72688937187195</v>
       </c>
       <c r="H995" t="n">
         <v>2989212</v>
@@ -29282,7 +29282,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G997" t="n">
-        <v>3.79337501525879</v>
+        <v>3.79337453842163</v>
       </c>
       <c r="H997" t="n">
         <v>1790034</v>
@@ -29311,7 +29311,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355376243591</v>
       </c>
       <c r="H998" t="n">
         <v>2779886</v>
@@ -29340,7 +29340,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355376243591</v>
       </c>
       <c r="H999" t="n">
         <v>2215137</v>
@@ -29369,7 +29369,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.88940978050232</v>
+        <v>3.88940930366516</v>
       </c>
       <c r="H1000" t="n">
         <v>2403958</v>
@@ -29398,7 +29398,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706835746765</v>
       </c>
       <c r="H1001" t="n">
         <v>1891362</v>
@@ -29427,7 +29427,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1002" t="n">
-        <v>3.81923055648804</v>
+        <v>3.81923031806946</v>
       </c>
       <c r="H1002" t="n">
         <v>1355764</v>
@@ -29456,7 +29456,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1003" t="n">
-        <v>3.77860021591187</v>
+        <v>3.77859997749329</v>
       </c>
       <c r="H1003" t="n">
         <v>1050566</v>
@@ -29543,7 +29543,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.73797011375427</v>
+        <v>3.73797059059143</v>
       </c>
       <c r="H1006" t="n">
         <v>1078704</v>
@@ -29601,7 +29601,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.72688961029053</v>
+        <v>3.72688937187195</v>
       </c>
       <c r="H1008" t="n">
         <v>1959502</v>
@@ -29630,7 +29630,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.72319602966309</v>
+        <v>3.72319555282593</v>
       </c>
       <c r="H1009" t="n">
         <v>1279485</v>
@@ -29659,7 +29659,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.55328798294067</v>
+        <v>3.55328822135925</v>
       </c>
       <c r="H1010" t="n">
         <v>2471336</v>
@@ -29688,7 +29688,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.56806230545044</v>
+        <v>3.56806254386902</v>
       </c>
       <c r="H1011" t="n">
         <v>2665724</v>
@@ -29717,7 +29717,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.66557502746582</v>
+        <v>3.6655752658844</v>
       </c>
       <c r="H1012" t="n">
         <v>1986330</v>
@@ -29746,7 +29746,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.66853022575378</v>
+        <v>3.66852974891663</v>
       </c>
       <c r="H1013" t="n">
         <v>2470620</v>
@@ -29775,7 +29775,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1014" t="n">
-        <v>3.7010338306427</v>
+        <v>3.70103359222412</v>
       </c>
       <c r="H1014" t="n">
         <v>2774127</v>
@@ -29804,7 +29804,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.83400511741638</v>
+        <v>3.83400583267212</v>
       </c>
       <c r="H1015" t="n">
         <v>2422991</v>
@@ -29833,7 +29833,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1016" t="n">
-        <v>3.78229379653931</v>
+        <v>3.78229427337646</v>
       </c>
       <c r="H1016" t="n">
         <v>2424479</v>
@@ -29862,7 +29862,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1017" t="n">
-        <v>3.78229379653931</v>
+        <v>3.78229427337646</v>
       </c>
       <c r="H1017" t="n">
         <v>1109975</v>
@@ -29891,7 +29891,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.90787792205811</v>
+        <v>3.90787768363953</v>
       </c>
       <c r="H1018" t="n">
         <v>3067531</v>
@@ -29920,7 +29920,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.93003988265991</v>
+        <v>3.93004012107849</v>
       </c>
       <c r="H1019" t="n">
         <v>1796510</v>
@@ -30007,7 +30007,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G1022" t="n">
-        <v>3.86724805831909</v>
+        <v>3.86724781990051</v>
       </c>
       <c r="H1022" t="n">
         <v>2014417</v>
@@ -30065,7 +30065,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.90049076080322</v>
+        <v>3.9004909992218</v>
       </c>
       <c r="H1024" t="n">
         <v>1912482</v>
@@ -30123,7 +30123,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.95958924293518</v>
+        <v>3.9595890045166</v>
       </c>
       <c r="H1026" t="n">
         <v>1785365</v>
@@ -30152,7 +30152,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.98175024986267</v>
+        <v>3.98175048828125</v>
       </c>
       <c r="H1027" t="n">
         <v>886438</v>
@@ -30181,7 +30181,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G1028" t="n">
-        <v>3.9632830619812</v>
+        <v>3.96328258514404</v>
       </c>
       <c r="H1028" t="n">
         <v>1394632</v>
@@ -30210,7 +30210,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.97436356544495</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H1029" t="n">
         <v>1375106</v>
@@ -30239,7 +30239,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.99283146858215</v>
+        <v>3.99283218383789</v>
       </c>
       <c r="H1030" t="n">
         <v>1587588</v>
@@ -30326,7 +30326,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.97436356544495</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H1033" t="n">
         <v>2221291</v>
@@ -30355,7 +30355,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.95589566230774</v>
+        <v>3.95589542388916</v>
       </c>
       <c r="H1034" t="n">
         <v>2699430</v>
@@ -30384,7 +30384,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.98913764953613</v>
+        <v>3.98913812637329</v>
       </c>
       <c r="H1035" t="n">
         <v>1652889</v>
@@ -30413,7 +30413,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.90418386459351</v>
+        <v>3.90418410301208</v>
       </c>
       <c r="H1036" t="n">
         <v>2023466</v>
@@ -30442,7 +30442,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.90787792205811</v>
+        <v>3.90787768363953</v>
       </c>
       <c r="H1037" t="n">
         <v>1571198</v>
@@ -30471,7 +30471,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.94850826263428</v>
+        <v>3.94850778579712</v>
       </c>
       <c r="H1038" t="n">
         <v>1605404</v>
@@ -30558,7 +30558,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1041" t="n">
-        <v>3.81923055648804</v>
+        <v>3.81923031806946</v>
       </c>
       <c r="H1041" t="n">
         <v>2823001</v>
@@ -30587,7 +30587,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.77121329307556</v>
+        <v>3.77121305465698</v>
       </c>
       <c r="H1042" t="n">
         <v>1471582</v>
@@ -30703,7 +30703,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.80076217651367</v>
+        <v>3.80076241493225</v>
       </c>
       <c r="H1046" t="n">
         <v>3242125</v>
@@ -30732,7 +30732,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.73427653312683</v>
+        <v>3.73427677154541</v>
       </c>
       <c r="H1047" t="n">
         <v>3293551</v>
@@ -30761,7 +30761,7 @@
         <v>4.93599987030029</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.64636778831482</v>
+        <v>3.64636731147766</v>
       </c>
       <c r="H1048" t="n">
         <v>2603514</v>
@@ -30790,7 +30790,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.73427653312683</v>
+        <v>3.73427677154541</v>
       </c>
       <c r="H1049" t="n">
         <v>1976003</v>
@@ -30819,7 +30819,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1050" t="n">
-        <v>3.78229379653931</v>
+        <v>3.78229427337646</v>
       </c>
       <c r="H1050" t="n">
         <v>1721378</v>
@@ -30848,7 +30848,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706835746765</v>
       </c>
       <c r="H1051" t="n">
         <v>864928</v>
@@ -30877,7 +30877,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.82292413711548</v>
+        <v>3.82292437553406</v>
       </c>
       <c r="H1052" t="n">
         <v>997301</v>
@@ -30906,7 +30906,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1053" t="n">
-        <v>3.84139204025269</v>
+        <v>3.84139156341553</v>
       </c>
       <c r="H1053" t="n">
         <v>1483934</v>
@@ -30935,7 +30935,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.82661747932434</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H1054" t="n">
         <v>1737746</v>
@@ -30993,7 +30993,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>3.86355447769165</v>
+        <v>3.86355376243591</v>
       </c>
       <c r="H1056" t="n">
         <v>2123824</v>
@@ -31080,7 +31080,7 @@
         <v>5.125</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.78598809242249</v>
+        <v>3.78598785400391</v>
       </c>
       <c r="H1059" t="n">
         <v>1492843</v>
@@ -31109,7 +31109,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G1060" t="n">
-        <v>3.71211504936218</v>
+        <v>3.7121148109436</v>
       </c>
       <c r="H1060" t="n">
         <v>2056469</v>
@@ -31167,7 +31167,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G1062" t="n">
-        <v>3.76382613182068</v>
+        <v>3.76382565498352</v>
       </c>
       <c r="H1062" t="n">
         <v>1407675</v>
@@ -31225,7 +31225,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.75643825531006</v>
+        <v>3.75643873214722</v>
       </c>
       <c r="H1064" t="n">
         <v>1665111</v>
@@ -31254,7 +31254,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G1065" t="n">
-        <v>3.69734001159668</v>
+        <v>3.6973397731781</v>
       </c>
       <c r="H1065" t="n">
         <v>1531944</v>
@@ -31312,7 +31312,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.65523219108582</v>
+        <v>3.65523266792297</v>
       </c>
       <c r="H1067" t="n">
         <v>2042790</v>
@@ -31341,7 +31341,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.64341306686401</v>
+        <v>3.64341378211975</v>
       </c>
       <c r="H1068" t="n">
         <v>1798815</v>
@@ -31370,7 +31370,7 @@
         <v>5</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.69364595413208</v>
+        <v>3.69364666938782</v>
       </c>
       <c r="H1069" t="n">
         <v>1936550</v>
@@ -31399,7 +31399,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.72319602966309</v>
+        <v>3.72319555282593</v>
       </c>
       <c r="H1070" t="n">
         <v>2008248</v>
@@ -31428,7 +31428,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.73058319091797</v>
+        <v>3.73058295249939</v>
       </c>
       <c r="H1071" t="n">
         <v>1816077</v>
@@ -31515,7 +31515,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.67443943023682</v>
+        <v>3.67443919181824</v>
       </c>
       <c r="H1074" t="n">
         <v>1922675</v>
@@ -31544,7 +31544,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.65523219108582</v>
+        <v>3.65523266792297</v>
       </c>
       <c r="H1075" t="n">
         <v>1931556</v>
@@ -31602,7 +31602,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.77121329307556</v>
+        <v>3.77121305465698</v>
       </c>
       <c r="H1077" t="n">
         <v>3016029</v>
@@ -31631,7 +31631,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1078" t="n">
-        <v>3.77860021591187</v>
+        <v>3.77859997749329</v>
       </c>
       <c r="H1078" t="n">
         <v>2245609</v>
@@ -31660,7 +31660,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.82292413711548</v>
+        <v>3.82292437553406</v>
       </c>
       <c r="H1079" t="n">
         <v>3127369</v>
@@ -31689,7 +31689,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.77490711212158</v>
+        <v>3.77490639686584</v>
       </c>
       <c r="H1080" t="n">
         <v>2155949</v>
@@ -31718,7 +31718,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.82292413711548</v>
+        <v>3.82292437553406</v>
       </c>
       <c r="H1081" t="n">
         <v>2606261</v>
@@ -31805,7 +31805,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.82661747932434</v>
+        <v>3.82661771774292</v>
       </c>
       <c r="H1084" t="n">
         <v>1656774</v>
@@ -31863,7 +31863,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.74166440963745</v>
+        <v>3.74166417121887</v>
       </c>
       <c r="H1086" t="n">
         <v>1637484</v>
@@ -31892,7 +31892,7 @@
         <v>5.02500009536743</v>
       </c>
       <c r="G1087" t="n">
-        <v>3.71211504936218</v>
+        <v>3.7121148109436</v>
       </c>
       <c r="H1087" t="n">
         <v>1534349</v>
@@ -31921,7 +31921,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1088" t="n">
-        <v>3.7010338306427</v>
+        <v>3.70103359222412</v>
       </c>
       <c r="H1088" t="n">
         <v>1677269</v>
@@ -31979,7 +31979,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G1090" t="n">
-        <v>3.7010338306427</v>
+        <v>3.70103359222412</v>
       </c>
       <c r="H1090" t="n">
         <v>1683278</v>
@@ -32008,7 +32008,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.72319602966309</v>
+        <v>3.72319555282593</v>
       </c>
       <c r="H1091" t="n">
         <v>3177909</v>
@@ -32037,7 +32037,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1092" t="n">
-        <v>3.67148423194885</v>
+        <v>3.67148470878601</v>
       </c>
       <c r="H1092" t="n">
         <v>2201932</v>
@@ -32095,7 +32095,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G1094" t="n">
-        <v>3.69734001159668</v>
+        <v>3.6973397731781</v>
       </c>
       <c r="H1094" t="n">
         <v>2549290</v>
@@ -32153,7 +32153,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.60204410552979</v>
+        <v>3.60204434394836</v>
       </c>
       <c r="H1096" t="n">
         <v>2719554</v>
@@ -32182,7 +32182,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.65966510772705</v>
+        <v>3.65966486930847</v>
       </c>
       <c r="H1097" t="n">
         <v>3749789</v>
@@ -32211,7 +32211,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.63602590560913</v>
+        <v>3.63602542877197</v>
       </c>
       <c r="H1098" t="n">
         <v>2381518</v>
@@ -32269,7 +32269,7 @@
         <v>5.125</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.78598809242249</v>
+        <v>3.78598785400391</v>
       </c>
       <c r="H1100" t="n">
         <v>4530532</v>
@@ -32298,7 +32298,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G1101" t="n">
-        <v>3.81923055648804</v>
+        <v>3.81923031806946</v>
       </c>
       <c r="H1101" t="n">
         <v>1996314</v>
@@ -32385,7 +32385,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.90049076080322</v>
+        <v>3.9004909992218</v>
       </c>
       <c r="H1104" t="n">
         <v>2675850</v>
@@ -32443,7 +32443,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.94112086296082</v>
+        <v>3.94112062454224</v>
       </c>
       <c r="H1106" t="n">
         <v>2467377</v>
@@ -32472,7 +32472,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.90049076080322</v>
+        <v>3.9004909992218</v>
       </c>
       <c r="H1107" t="n">
         <v>2996418</v>
@@ -32559,7 +32559,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1110" t="n">
-        <v>4.0297679901123</v>
+        <v>4.02976846694946</v>
       </c>
       <c r="H1110" t="n">
         <v>3021013</v>
@@ -32588,7 +32588,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.03346157073975</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H1111" t="n">
         <v>2094736</v>
@@ -32646,7 +32646,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1113" t="n">
-        <v>4.07409143447876</v>
+        <v>4.07409191131592</v>
       </c>
       <c r="H1113" t="n">
         <v>1946463</v>
@@ -32675,7 +32675,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.13319063186646</v>
+        <v>4.1331901550293</v>
       </c>
       <c r="H1114" t="n">
         <v>1962864</v>
@@ -32704,7 +32704,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.10364151000977</v>
+        <v>4.10364103317261</v>
       </c>
       <c r="H1115" t="n">
         <v>2218958</v>
@@ -32733,7 +32733,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G1116" t="n">
-        <v>4.08886623382568</v>
+        <v>4.08886671066284</v>
       </c>
       <c r="H1116" t="n">
         <v>1978671</v>
@@ -32762,7 +32762,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1117" t="n">
-        <v>4.08074045181274</v>
+        <v>4.0807409286499</v>
       </c>
       <c r="H1117" t="n">
         <v>1466310</v>
@@ -32791,7 +32791,7 @@
         <v>5.55600023269653</v>
       </c>
       <c r="G1118" t="n">
-        <v>4.10438013076782</v>
+        <v>4.10438060760498</v>
       </c>
       <c r="H1118" t="n">
         <v>1638396</v>
@@ -32878,7 +32878,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.98913764953613</v>
+        <v>3.98913812637329</v>
       </c>
       <c r="H1121" t="n">
         <v>2065025</v>
@@ -32936,7 +32936,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.95367980003357</v>
+        <v>3.95367908477783</v>
       </c>
       <c r="H1123" t="n">
         <v>4816518</v>
@@ -32965,7 +32965,7 @@
         <v>5.36600017547607</v>
       </c>
       <c r="G1124" t="n">
-        <v>3.96402215957642</v>
+        <v>3.96402168273926</v>
       </c>
       <c r="H1124" t="n">
         <v>1759915</v>
@@ -32994,7 +32994,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.94776964187622</v>
+        <v>3.9477698802948</v>
       </c>
       <c r="H1125" t="n">
         <v>1564931</v>
@@ -33023,7 +33023,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.9906153678894</v>
+        <v>3.99061608314514</v>
       </c>
       <c r="H1126" t="n">
         <v>2028839</v>
@@ -33052,7 +33052,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1127" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868772506714</v>
       </c>
       <c r="H1127" t="n">
         <v>2005279</v>
@@ -33110,7 +33110,7 @@
         <v>5.44199991226196</v>
       </c>
       <c r="G1129" t="n">
-        <v>4.02016496658325</v>
+        <v>4.02016448974609</v>
       </c>
       <c r="H1129" t="n">
         <v>2210950</v>
@@ -33139,7 +33139,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1130" t="n">
-        <v>4.05562353134155</v>
+        <v>4.05562400817871</v>
       </c>
       <c r="H1130" t="n">
         <v>1660238</v>
@@ -33168,7 +33168,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1131" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868772506714</v>
       </c>
       <c r="H1131" t="n">
         <v>1960723</v>
@@ -33226,7 +33226,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.99948048591614</v>
+        <v>3.99948024749756</v>
       </c>
       <c r="H1133" t="n">
         <v>1193698</v>
@@ -33284,7 +33284,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.99948048591614</v>
+        <v>3.99948024749756</v>
       </c>
       <c r="H1135" t="n">
         <v>1428918</v>
@@ -33313,7 +33313,7 @@
         <v>5.42199993133545</v>
       </c>
       <c r="G1136" t="n">
-        <v>4.00539016723633</v>
+        <v>4.00538969039917</v>
       </c>
       <c r="H1136" t="n">
         <v>1582993</v>
@@ -33371,7 +33371,7 @@
         <v>5.44799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.02459764480591</v>
+        <v>4.02459716796875</v>
       </c>
       <c r="H1138" t="n">
         <v>2263497</v>
@@ -33400,7 +33400,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.0068678855896</v>
+        <v>4.00686740875244</v>
       </c>
       <c r="H1139" t="n">
         <v>4662672</v>
@@ -33603,7 +33603,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1146" t="n">
-        <v>4.08074045181274</v>
+        <v>4.0807409286499</v>
       </c>
       <c r="H1146" t="n">
         <v>2135034</v>
@@ -33632,7 +33632,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G1147" t="n">
-        <v>4.16495513916016</v>
+        <v>4.16495561599731</v>
       </c>
       <c r="H1147" t="n">
         <v>3027890</v>
@@ -33719,7 +33719,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G1150" t="n">
-        <v>4.20632457733154</v>
+        <v>4.2063250541687</v>
       </c>
       <c r="H1150" t="n">
         <v>2615830</v>
@@ -33748,7 +33748,7 @@
         <v>5.79400014877319</v>
       </c>
       <c r="G1151" t="n">
-        <v>4.28019762039185</v>
+        <v>4.28019714355469</v>
       </c>
       <c r="H1151" t="n">
         <v>5383718</v>
@@ -33806,7 +33806,7 @@
         <v>5.49599981307983</v>
       </c>
       <c r="G1153" t="n">
-        <v>4.25089311599731</v>
+        <v>4.25089263916016</v>
       </c>
       <c r="H1153" t="n">
         <v>2692523</v>
@@ -33893,7 +33893,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1156" t="n">
-        <v>4.19829845428467</v>
+        <v>4.19829797744751</v>
       </c>
       <c r="H1156" t="n">
         <v>1532118</v>
@@ -33980,7 +33980,7 @@
         <v>5.41800022125244</v>
       </c>
       <c r="G1159" t="n">
-        <v>4.19056463241577</v>
+        <v>4.19056415557861</v>
       </c>
       <c r="H1159" t="n">
         <v>1067155</v>
@@ -34038,7 +34038,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G1161" t="n">
-        <v>4.26172161102295</v>
+        <v>4.26172113418579</v>
       </c>
       <c r="H1161" t="n">
         <v>2431783</v>
@@ -34299,7 +34299,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G1170" t="n">
-        <v>4.3885669708252</v>
+        <v>4.38856744766235</v>
       </c>
       <c r="H1170" t="n">
         <v>1857442</v>
@@ -34328,7 +34328,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1171" t="n">
-        <v>4.37155103683472</v>
+        <v>4.37155199050903</v>
       </c>
       <c r="H1171" t="n">
         <v>2785219</v>
@@ -34444,7 +34444,7 @@
         <v>5.56599998474121</v>
       </c>
       <c r="G1175" t="n">
-        <v>4.30503416061401</v>
+        <v>4.30503463745117</v>
       </c>
       <c r="H1175" t="n">
         <v>1325369</v>
@@ -34473,7 +34473,7 @@
         <v>5.56599998474121</v>
       </c>
       <c r="G1176" t="n">
-        <v>4.30503416061401</v>
+        <v>4.30503463745117</v>
       </c>
       <c r="H1176" t="n">
         <v>1470297</v>
@@ -34531,7 +34531,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.29575252532959</v>
+        <v>4.29575300216675</v>
       </c>
       <c r="H1178" t="n">
         <v>725516</v>
@@ -34560,7 +34560,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G1179" t="n">
-        <v>4.26326847076416</v>
+        <v>4.263267993927</v>
       </c>
       <c r="H1179" t="n">
         <v>1866419</v>
@@ -34589,7 +34589,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.27719068527222</v>
+        <v>4.27719020843506</v>
       </c>
       <c r="H1180" t="n">
         <v>1284403</v>
@@ -34647,7 +34647,7 @@
         <v>5.57800006866455</v>
       </c>
       <c r="G1182" t="n">
-        <v>4.31431674957275</v>
+        <v>4.3143162727356</v>
       </c>
       <c r="H1182" t="n">
         <v>832865</v>
@@ -34763,7 +34763,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G1186" t="n">
-        <v>4.28801870346069</v>
+        <v>4.28801918029785</v>
       </c>
       <c r="H1186" t="n">
         <v>1427850</v>
@@ -34792,7 +34792,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G1187" t="n">
-        <v>4.32978534698486</v>
+        <v>4.32978487014771</v>
       </c>
       <c r="H1187" t="n">
         <v>1717049</v>
@@ -34821,7 +34821,7 @@
         <v>5.62200021743774</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.34834861755371</v>
+        <v>4.34834814071655</v>
       </c>
       <c r="H1188" t="n">
         <v>1218309</v>
@@ -34850,7 +34850,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1189" t="n">
-        <v>4.35298824310303</v>
+        <v>4.35298871994019</v>
       </c>
       <c r="H1189" t="n">
         <v>1139569</v>
@@ -34966,7 +34966,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.16890668869019</v>
+        <v>4.16890716552734</v>
       </c>
       <c r="H1193" t="n">
         <v>2467655</v>
@@ -35024,7 +35024,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.27719068527222</v>
+        <v>4.27719020843506</v>
       </c>
       <c r="H1195" t="n">
         <v>1798087</v>
@@ -35082,7 +35082,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.34370756149292</v>
+        <v>4.34370803833008</v>
       </c>
       <c r="H1197" t="n">
         <v>1310045</v>
@@ -35140,7 +35140,7 @@
         <v>5.70800018310547</v>
       </c>
       <c r="G1199" t="n">
-        <v>4.4148645401001</v>
+        <v>4.41486501693726</v>
       </c>
       <c r="H1199" t="n">
         <v>1301251</v>
@@ -35169,7 +35169,7 @@
         <v>5.71199989318848</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.41795873641968</v>
+        <v>4.41795825958252</v>
       </c>
       <c r="H1200" t="n">
         <v>1137264</v>
@@ -35227,7 +35227,7 @@
         <v>5.72800016403198</v>
       </c>
       <c r="G1202" t="n">
-        <v>4.43033361434937</v>
+        <v>4.43033409118652</v>
       </c>
       <c r="H1202" t="n">
         <v>865108</v>
@@ -35285,7 +35285,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1204" t="n">
-        <v>4.41177082061768</v>
+        <v>4.41177129745483</v>
       </c>
       <c r="H1204" t="n">
         <v>931012</v>
@@ -35314,7 +35314,7 @@
         <v>5.7039999961853</v>
       </c>
       <c r="G1205" t="n">
-        <v>4.41177082061768</v>
+        <v>4.41177129745483</v>
       </c>
       <c r="H1205" t="n">
         <v>767708</v>
@@ -35401,7 +35401,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1208" t="n">
-        <v>4.46591281890869</v>
+        <v>4.46591234207153</v>
       </c>
       <c r="H1208" t="n">
         <v>912025</v>
@@ -35488,7 +35488,7 @@
         <v>5.89799976348877</v>
       </c>
       <c r="G1211" t="n">
-        <v>4.5618200302124</v>
+        <v>4.56182050704956</v>
       </c>
       <c r="H1211" t="n">
         <v>1022094</v>
@@ -35575,7 +35575,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.56646156311035</v>
+        <v>4.56646108627319</v>
       </c>
       <c r="H1214" t="n">
         <v>1560619</v>
@@ -35604,7 +35604,7 @@
         <v>5.97599983215332</v>
       </c>
       <c r="G1215" t="n">
-        <v>4.62214994430542</v>
+        <v>4.62214946746826</v>
       </c>
       <c r="H1215" t="n">
         <v>1971571</v>
@@ -35662,7 +35662,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.63761901855469</v>
+        <v>4.63761854171753</v>
       </c>
       <c r="H1217" t="n">
         <v>846788</v>
@@ -35720,7 +35720,7 @@
         <v>5.81199979782104</v>
       </c>
       <c r="G1219" t="n">
-        <v>4.49530363082886</v>
+        <v>4.4953031539917</v>
       </c>
       <c r="H1219" t="n">
         <v>1548563</v>
@@ -35865,7 +35865,7 @@
         <v>5.70800018310547</v>
       </c>
       <c r="G1224" t="n">
-        <v>4.4148645401001</v>
+        <v>4.41486501693726</v>
       </c>
       <c r="H1224" t="n">
         <v>1988029</v>
@@ -35894,7 +35894,7 @@
         <v>5.68400001525879</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.39630174636841</v>
+        <v>4.39630222320557</v>
       </c>
       <c r="H1225" t="n">
         <v>950072</v>
@@ -35952,7 +35952,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.34370756149292</v>
+        <v>4.34370803833008</v>
       </c>
       <c r="H1227" t="n">
         <v>2221372</v>
@@ -36010,7 +36010,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1229" t="n">
-        <v>4.30039358139038</v>
+        <v>4.30039405822754</v>
       </c>
       <c r="H1229" t="n">
         <v>2431673</v>
@@ -36039,7 +36039,7 @@
         <v>5.55200004577637</v>
       </c>
       <c r="G1230" t="n">
-        <v>4.29420614242554</v>
+        <v>4.29420566558838</v>
       </c>
       <c r="H1230" t="n">
         <v>1372530</v>
@@ -36068,7 +36068,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G1231" t="n">
-        <v>4.269455909729</v>
+        <v>4.26945543289185</v>
       </c>
       <c r="H1231" t="n">
         <v>2728071</v>
@@ -36097,7 +36097,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1232" t="n">
-        <v>4.31895637512207</v>
+        <v>4.31895685195923</v>
       </c>
       <c r="H1232" t="n">
         <v>2153425</v>
@@ -36155,7 +36155,7 @@
         <v>5.52199983596802</v>
       </c>
       <c r="G1234" t="n">
-        <v>4.27100276947021</v>
+        <v>4.27100229263306</v>
       </c>
       <c r="H1234" t="n">
         <v>1519331</v>
@@ -36184,7 +36184,7 @@
         <v>5.62200021743774</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.34834861755371</v>
+        <v>4.34834814071655</v>
       </c>
       <c r="H1235" t="n">
         <v>2086645</v>
@@ -36329,7 +36329,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.45508480072021</v>
+        <v>4.45508432388306</v>
       </c>
       <c r="H1240" t="n">
         <v>1716303</v>
@@ -36445,7 +36445,7 @@
         <v>5.55200004577637</v>
       </c>
       <c r="G1244" t="n">
-        <v>4.29420614242554</v>
+        <v>4.29420566558838</v>
       </c>
       <c r="H1244" t="n">
         <v>1630612</v>
@@ -36503,7 +36503,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.23387718200684</v>
+        <v>4.23387670516968</v>
       </c>
       <c r="H1246" t="n">
         <v>2088691</v>
@@ -36532,7 +36532,7 @@
         <v>5.49599981307983</v>
       </c>
       <c r="G1247" t="n">
-        <v>4.25089311599731</v>
+        <v>4.25089263916016</v>
       </c>
       <c r="H1247" t="n">
         <v>1406076</v>
@@ -36561,7 +36561,7 @@
         <v>5.53200006484985</v>
       </c>
       <c r="G1248" t="n">
-        <v>4.27873754501343</v>
+        <v>4.27873706817627</v>
       </c>
       <c r="H1248" t="n">
         <v>1473363</v>
@@ -36677,7 +36677,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.21222019195557</v>
+        <v>4.21222066879272</v>
       </c>
       <c r="H1252" t="n">
         <v>1695886</v>
@@ -36706,7 +36706,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1253" t="n">
-        <v>4.18437576293945</v>
+        <v>4.18437623977661</v>
       </c>
       <c r="H1253" t="n">
         <v>2395248</v>
@@ -36735,7 +36735,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1254" t="n">
-        <v>4.18437576293945</v>
+        <v>4.18437623977661</v>
       </c>
       <c r="H1254" t="n">
         <v>1279452</v>
@@ -36764,7 +36764,7 @@
         <v>5.44199991226196</v>
       </c>
       <c r="G1255" t="n">
-        <v>4.20912647247314</v>
+        <v>4.2091269493103</v>
       </c>
       <c r="H1255" t="n">
         <v>1458684</v>
@@ -36793,7 +36793,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1256" t="n">
-        <v>4.22304821014404</v>
+        <v>4.2230486869812</v>
       </c>
       <c r="H1256" t="n">
         <v>1755024</v>
@@ -36822,7 +36822,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1257" t="n">
-        <v>4.22304821014404</v>
+        <v>4.2230486869812</v>
       </c>
       <c r="H1257" t="n">
         <v>1186601</v>
@@ -36851,7 +36851,7 @@
         <v>5.41800022125244</v>
       </c>
       <c r="G1258" t="n">
-        <v>4.19056463241577</v>
+        <v>4.19056415557861</v>
       </c>
       <c r="H1258" t="n">
         <v>1729140</v>
@@ -36909,7 +36909,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.32205104827881</v>
+        <v>4.32205009460449</v>
       </c>
       <c r="H1260" t="n">
         <v>1687840</v>
@@ -36996,7 +36996,7 @@
         <v>5.65199995040894</v>
       </c>
       <c r="G1263" t="n">
-        <v>4.37155103683472</v>
+        <v>4.37155199050903</v>
       </c>
       <c r="H1263" t="n">
         <v>1329328</v>
@@ -37054,7 +37054,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.27254915237427</v>
+        <v>4.27254962921143</v>
       </c>
       <c r="H1265" t="n">
         <v>2499950</v>
@@ -37083,7 +37083,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1266" t="n">
-        <v>4.24625205993652</v>
+        <v>4.24625158309937</v>
       </c>
       <c r="H1266" t="n">
         <v>2523989</v>
@@ -37141,7 +37141,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G1268" t="n">
-        <v>4.30812835693359</v>
+        <v>4.30812883377075</v>
       </c>
       <c r="H1268" t="n">
         <v>952964</v>
@@ -37228,7 +37228,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1271" t="n">
-        <v>4.43497467041016</v>
+        <v>4.434974193573</v>
       </c>
       <c r="H1271" t="n">
         <v>1322224</v>
@@ -37257,7 +37257,7 @@
         <v>5.69399976730347</v>
       </c>
       <c r="G1272" t="n">
-        <v>4.40403604507446</v>
+        <v>4.40403699874878</v>
       </c>
       <c r="H1272" t="n">
         <v>1109380</v>
@@ -37286,7 +37286,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1273" t="n">
-        <v>4.36226940155029</v>
+        <v>4.36227035522461</v>
       </c>
       <c r="H1273" t="n">
         <v>889879</v>
@@ -37315,7 +37315,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G1274" t="n">
-        <v>4.38392686843872</v>
+        <v>4.38392734527588</v>
       </c>
       <c r="H1274" t="n">
         <v>1009280</v>
@@ -37344,7 +37344,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1275" t="n">
-        <v>4.35298824310303</v>
+        <v>4.35298871994019</v>
       </c>
       <c r="H1275" t="n">
         <v>910027</v>
@@ -37373,7 +37373,7 @@
         <v>5.60200023651123</v>
       </c>
       <c r="G1276" t="n">
-        <v>4.33287954330444</v>
+        <v>4.33287906646729</v>
       </c>
       <c r="H1276" t="n">
         <v>765113</v>
@@ -37547,7 +37547,7 @@
         <v>5.62799978256226</v>
       </c>
       <c r="G1282" t="n">
-        <v>4.35298824310303</v>
+        <v>4.35298871994019</v>
       </c>
       <c r="H1282" t="n">
         <v>1370173</v>
@@ -37605,7 +37605,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G1284" t="n">
-        <v>4.38392686843872</v>
+        <v>4.38392734527588</v>
       </c>
       <c r="H1284" t="n">
         <v>1242131</v>
@@ -37750,7 +37750,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.32205104827881</v>
+        <v>4.32205009460449</v>
       </c>
       <c r="H1289" t="n">
         <v>1160885</v>
@@ -37837,7 +37837,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1292" t="n">
-        <v>4.51850700378418</v>
+        <v>4.51850748062134</v>
       </c>
       <c r="H1292" t="n">
         <v>2866024</v>
@@ -37866,7 +37866,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G1293" t="n">
-        <v>4.52160167694092</v>
+        <v>4.52160120010376</v>
       </c>
       <c r="H1293" t="n">
         <v>1495847</v>
@@ -37924,7 +37924,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G1295" t="n">
-        <v>4.46591281890869</v>
+        <v>4.46591234207153</v>
       </c>
       <c r="H1295" t="n">
         <v>1753198</v>
@@ -37982,7 +37982,7 @@
         <v>5.76200008392334</v>
       </c>
       <c r="G1297" t="n">
-        <v>4.45663166046143</v>
+        <v>4.45663118362427</v>
       </c>
       <c r="H1297" t="n">
         <v>1267446</v>
@@ -38011,7 +38011,7 @@
         <v>5.7480001449585</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.44580316543579</v>
+        <v>4.44580268859863</v>
       </c>
       <c r="H1298" t="n">
         <v>2108694</v>
@@ -38098,7 +38098,7 @@
         <v>5.82200002670288</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.50303792953491</v>
+        <v>4.50303840637207</v>
       </c>
       <c r="H1301" t="n">
         <v>3253697</v>
@@ -38127,7 +38127,7 @@
         <v>5.77799987792969</v>
       </c>
       <c r="G1302" t="n">
-        <v>4.46900653839111</v>
+        <v>4.46900606155396</v>
       </c>
       <c r="H1302" t="n">
         <v>1022208</v>
@@ -38156,7 +38156,7 @@
         <v>5.75</v>
       </c>
       <c r="G1303" t="n">
-        <v>4.447350025177</v>
+        <v>4.44734954833984</v>
       </c>
       <c r="H1303" t="n">
         <v>2054709</v>
@@ -38185,7 +38185,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1304" t="n">
-        <v>4.52469539642334</v>
+        <v>4.52469491958618</v>
       </c>
       <c r="H1304" t="n">
         <v>1298324</v>
@@ -38214,7 +38214,7 @@
         <v>5.89400005340576</v>
       </c>
       <c r="G1305" t="n">
-        <v>4.55872678756714</v>
+        <v>4.5587272644043</v>
       </c>
       <c r="H1305" t="n">
         <v>1057215</v>
@@ -38243,7 +38243,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1306" t="n">
-        <v>4.54789876937866</v>
+        <v>4.54789924621582</v>
       </c>
       <c r="H1306" t="n">
         <v>631434</v>
@@ -38301,7 +38301,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1308" t="n">
-        <v>4.66701030731201</v>
+        <v>4.66700983047485</v>
       </c>
       <c r="H1308" t="n">
         <v>1134168</v>
@@ -38359,7 +38359,7 @@
         <v>6.08799982070923</v>
       </c>
       <c r="G1310" t="n">
-        <v>4.70877695083618</v>
+        <v>4.70877647399902</v>
       </c>
       <c r="H1310" t="n">
         <v>996941</v>
@@ -38446,7 +38446,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1313" t="n">
-        <v>4.51850700378418</v>
+        <v>4.51850748062134</v>
       </c>
       <c r="H1313" t="n">
         <v>1666783</v>
@@ -38504,7 +38504,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G1315" t="n">
-        <v>4.44270944595337</v>
+        <v>4.44270896911621</v>
       </c>
       <c r="H1315" t="n">
         <v>962142</v>
@@ -38533,7 +38533,7 @@
         <v>5.82200002670288</v>
       </c>
       <c r="G1316" t="n">
-        <v>4.50303792953491</v>
+        <v>4.50303840637207</v>
       </c>
       <c r="H1316" t="n">
         <v>1805777</v>
@@ -38562,7 +38562,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.5277886390686</v>
+        <v>4.52778911590576</v>
       </c>
       <c r="H1317" t="n">
         <v>1300408</v>
@@ -38620,7 +38620,7 @@
         <v>5.89799976348877</v>
       </c>
       <c r="G1319" t="n">
-        <v>4.5618200302124</v>
+        <v>4.56182050704956</v>
       </c>
       <c r="H1319" t="n">
         <v>1390004</v>
@@ -38765,7 +38765,7 @@
         <v>5.83799982070923</v>
       </c>
       <c r="G1324" t="n">
-        <v>4.51541328430176</v>
+        <v>4.51541376113892</v>
       </c>
       <c r="H1324" t="n">
         <v>1004702</v>
@@ -38794,7 +38794,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1325" t="n">
-        <v>4.45508480072021</v>
+        <v>4.45508432388306</v>
       </c>
       <c r="H1325" t="n">
         <v>1934280</v>
@@ -38881,7 +38881,7 @@
         <v>5.93599987030029</v>
       </c>
       <c r="G1328" t="n">
-        <v>4.59121179580688</v>
+        <v>4.59121227264404</v>
       </c>
       <c r="H1328" t="n">
         <v>1235229</v>
@@ -38910,7 +38910,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G1329" t="n">
-        <v>4.5277886390686</v>
+        <v>4.52778911590576</v>
       </c>
       <c r="H1329" t="n">
         <v>1302096</v>
@@ -38968,7 +38968,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.56646156311035</v>
+        <v>4.56646108627319</v>
       </c>
       <c r="H1331" t="n">
         <v>1234389</v>
@@ -38997,7 +38997,7 @@
         <v>5.98400020599365</v>
       </c>
       <c r="G1332" t="n">
-        <v>4.62833786010742</v>
+        <v>4.62833738327026</v>
       </c>
       <c r="H1332" t="n">
         <v>889529</v>
@@ -39171,7 +39171,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.43188047409058</v>
+        <v>4.43188095092773</v>
       </c>
       <c r="H1338" t="n">
         <v>1465529</v>
@@ -39200,7 +39200,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G1339" t="n">
-        <v>4.38392686843872</v>
+        <v>4.38392734527588</v>
       </c>
       <c r="H1339" t="n">
         <v>1124410</v>
@@ -39258,7 +39258,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G1341" t="n">
-        <v>4.3885669708252</v>
+        <v>4.38856744766235</v>
       </c>
       <c r="H1341" t="n">
         <v>1355316</v>
@@ -39345,7 +39345,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G1344" t="n">
-        <v>4.35453510284424</v>
+        <v>4.3545355796814</v>
       </c>
       <c r="H1344" t="n">
         <v>962286</v>
@@ -39374,7 +39374,7 @@
         <v>5.56599998474121</v>
       </c>
       <c r="G1345" t="n">
-        <v>4.30503416061401</v>
+        <v>4.30503463745117</v>
       </c>
       <c r="H1345" t="n">
         <v>979209</v>
@@ -39490,7 +39490,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.45508480072021</v>
+        <v>4.45508432388306</v>
       </c>
       <c r="H1349" t="n">
         <v>2859179</v>
@@ -39519,7 +39519,7 @@
         <v>5.77799987792969</v>
       </c>
       <c r="G1350" t="n">
-        <v>4.46900653839111</v>
+        <v>4.46900606155396</v>
       </c>
       <c r="H1350" t="n">
         <v>1850604</v>
@@ -39577,7 +39577,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G1352" t="n">
-        <v>4.32978534698486</v>
+        <v>4.32978487014771</v>
       </c>
       <c r="H1352" t="n">
         <v>1858705</v>
@@ -39606,7 +39606,7 @@
         <v>5.53200006484985</v>
       </c>
       <c r="G1353" t="n">
-        <v>4.27873754501343</v>
+        <v>4.27873706817627</v>
       </c>
       <c r="H1353" t="n">
         <v>1559031</v>
@@ -39664,7 +39664,7 @@
         <v>5.34800004959106</v>
       </c>
       <c r="G1355" t="n">
-        <v>4.13642263412476</v>
+        <v>4.1364221572876</v>
       </c>
       <c r="H1355" t="n">
         <v>2866264</v>
@@ -39693,7 +39693,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1356" t="n">
-        <v>4.16890668869019</v>
+        <v>4.16890716552734</v>
       </c>
       <c r="H1356" t="n">
         <v>2103223</v>
@@ -39751,7 +39751,7 @@
         <v>5.52199983596802</v>
       </c>
       <c r="G1358" t="n">
-        <v>4.27100276947021</v>
+        <v>4.27100229263306</v>
       </c>
       <c r="H1358" t="n">
         <v>1898076</v>
@@ -39780,7 +39780,7 @@
         <v>5.59200000762939</v>
       </c>
       <c r="G1359" t="n">
-        <v>4.32514476776123</v>
+        <v>4.32514429092407</v>
       </c>
       <c r="H1359" t="n">
         <v>1699674</v>
@@ -39925,7 +39925,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G1364" t="n">
-        <v>4.28801870346069</v>
+        <v>4.28801918029785</v>
       </c>
       <c r="H1364" t="n">
         <v>3197624</v>
@@ -40244,7 +40244,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.45508480072021</v>
+        <v>4.45508432388306</v>
       </c>
       <c r="H1375" t="n">
         <v>1102525</v>
@@ -40302,7 +40302,7 @@
         <v>5.79500007629395</v>
       </c>
       <c r="G1377" t="n">
-        <v>4.48215532302856</v>
+        <v>4.48215579986572</v>
       </c>
       <c r="H1377" t="n">
         <v>1875254</v>
@@ -40418,7 +40418,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G1381" t="n">
-        <v>4.70645666122437</v>
+        <v>4.70645570755005</v>
       </c>
       <c r="H1381" t="n">
         <v>1660147</v>
@@ -40534,7 +40534,7 @@
         <v>6.375</v>
       </c>
       <c r="G1385" t="n">
-        <v>4.93075752258301</v>
+        <v>4.93075704574585</v>
       </c>
       <c r="H1385" t="n">
         <v>2260746</v>
@@ -40679,7 +40679,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.77993392944336</v>
+        <v>4.77993440628052</v>
       </c>
       <c r="H1390" t="n">
         <v>1169448</v>
@@ -40708,7 +40708,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.80313777923584</v>
+        <v>4.803138256073</v>
       </c>
       <c r="H1391" t="n">
         <v>1131913</v>
@@ -40737,7 +40737,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.77993392944336</v>
+        <v>4.77993440628052</v>
       </c>
       <c r="H1392" t="n">
         <v>855211</v>
@@ -40998,7 +40998,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G1401" t="n">
-        <v>4.71032428741455</v>
+        <v>4.71032381057739</v>
       </c>
       <c r="H1401" t="n">
         <v>1308144</v>
@@ -41027,7 +41027,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.77993392944336</v>
+        <v>4.77993440628052</v>
       </c>
       <c r="H1402" t="n">
         <v>1402848</v>
@@ -41230,7 +41230,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1409" t="n">
-        <v>4.89952039718628</v>
+        <v>4.89951992034912</v>
       </c>
       <c r="H1409" t="n">
         <v>1322157</v>
@@ -41375,7 +41375,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1414" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909461975098</v>
       </c>
       <c r="H1414" t="n">
         <v>1962697</v>
@@ -41491,7 +41491,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1418" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909461975098</v>
       </c>
       <c r="H1418" t="n">
         <v>620812</v>
@@ -41578,7 +41578,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1421" t="n">
-        <v>4.66505432128906</v>
+        <v>4.66505479812622</v>
       </c>
       <c r="H1421" t="n">
         <v>1819823</v>
@@ -41636,7 +41636,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1423" t="n">
-        <v>4.39016342163086</v>
+        <v>4.39016389846802</v>
       </c>
       <c r="H1423" t="n">
         <v>1313609</v>
@@ -41665,7 +41665,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1424" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1424" t="n">
         <v>1270670</v>
@@ -41723,7 +41723,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1426" t="n">
-        <v>4.34165334701538</v>
+        <v>4.34165382385254</v>
       </c>
       <c r="H1426" t="n">
         <v>2221165</v>
@@ -41839,7 +41839,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1430" t="n">
-        <v>4.15569829940796</v>
+        <v>4.1556978225708</v>
       </c>
       <c r="H1430" t="n">
         <v>2903693</v>
@@ -41868,7 +41868,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1431" t="n">
-        <v>4.2688889503479</v>
+        <v>4.26888847351074</v>
       </c>
       <c r="H1431" t="n">
         <v>2802660</v>
@@ -41897,7 +41897,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1432" t="n">
-        <v>4.49526882171631</v>
+        <v>4.49526929855347</v>
       </c>
       <c r="H1432" t="n">
         <v>3261356</v>
@@ -41955,7 +41955,7 @@
         <v>5.61499977111816</v>
       </c>
       <c r="G1434" t="n">
-        <v>4.53973627090454</v>
+        <v>4.5397367477417</v>
       </c>
       <c r="H1434" t="n">
         <v>1667308</v>
@@ -42013,7 +42013,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.49122619628906</v>
+        <v>4.49122667312622</v>
       </c>
       <c r="H1436" t="n">
         <v>2205200</v>
@@ -42100,7 +42100,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G1439" t="n">
-        <v>4.44271612167358</v>
+        <v>4.44271659851074</v>
       </c>
       <c r="H1439" t="n">
         <v>1605594</v>
@@ -42129,7 +42129,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1440" t="n">
-        <v>4.42250347137451</v>
+        <v>4.42250394821167</v>
       </c>
       <c r="H1440" t="n">
         <v>1861474</v>
@@ -42216,7 +42216,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1443" t="n">
-        <v>4.41037607192993</v>
+        <v>4.41037654876709</v>
       </c>
       <c r="H1443" t="n">
         <v>607592</v>
@@ -42274,7 +42274,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>4.41037607192993</v>
+        <v>4.41037654876709</v>
       </c>
       <c r="H1445" t="n">
         <v>1041891</v>
@@ -42332,7 +42332,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.32548379898071</v>
+        <v>4.32548332214355</v>
       </c>
       <c r="H1447" t="n">
         <v>1617049</v>
@@ -42361,7 +42361,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1448" t="n">
-        <v>4.39016342163086</v>
+        <v>4.39016389846802</v>
       </c>
       <c r="H1448" t="n">
         <v>925324</v>
@@ -42419,7 +42419,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.26484680175781</v>
+        <v>4.26484632492065</v>
       </c>
       <c r="H1450" t="n">
         <v>1355393</v>
@@ -42477,7 +42477,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>4.27293109893799</v>
+        <v>4.27293062210083</v>
       </c>
       <c r="H1452" t="n">
         <v>787321</v>
@@ -42506,7 +42506,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.27293109893799</v>
+        <v>4.27293062210083</v>
       </c>
       <c r="H1453" t="n">
         <v>768600</v>
@@ -42709,7 +42709,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.41846179962158</v>
+        <v>4.41846132278442</v>
       </c>
       <c r="H1460" t="n">
         <v>832876</v>
@@ -42738,7 +42738,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1461" t="n">
-        <v>4.430588722229</v>
+        <v>4.43058919906616</v>
       </c>
       <c r="H1461" t="n">
         <v>580139</v>
@@ -42767,7 +42767,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1462" t="n">
-        <v>4.42250347137451</v>
+        <v>4.42250394821167</v>
       </c>
       <c r="H1462" t="n">
         <v>620839</v>
@@ -42941,7 +42941,7 @@
         <v>5.61499977111816</v>
       </c>
       <c r="G1468" t="n">
-        <v>4.53973627090454</v>
+        <v>4.5397367477417</v>
       </c>
       <c r="H1468" t="n">
         <v>823712</v>
@@ -43057,7 +43057,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1472" t="n">
-        <v>4.56803464889526</v>
+        <v>4.56803417205811</v>
       </c>
       <c r="H1472" t="n">
         <v>1539554</v>
@@ -43202,7 +43202,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1477" t="n">
-        <v>4.2688889503479</v>
+        <v>4.26888847351074</v>
       </c>
       <c r="H1477" t="n">
         <v>678424</v>
@@ -43289,7 +43289,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G1480" t="n">
-        <v>4.12740135192871</v>
+        <v>4.12740087509155</v>
       </c>
       <c r="H1480" t="n">
         <v>1592274</v>
@@ -43463,7 +43463,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>4.20420837402344</v>
+        <v>4.20420789718628</v>
       </c>
       <c r="H1486" t="n">
         <v>1293238</v>
@@ -43550,7 +43550,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G1489" t="n">
-        <v>4.13952827453613</v>
+        <v>4.13952875137329</v>
       </c>
       <c r="H1489" t="n">
         <v>1224062</v>
@@ -43579,7 +43579,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1490" t="n">
-        <v>4.17186880111694</v>
+        <v>4.17186832427979</v>
       </c>
       <c r="H1490" t="n">
         <v>1375840</v>
@@ -43608,7 +43608,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1491" t="n">
-        <v>4.13548564910889</v>
+        <v>4.13548517227173</v>
       </c>
       <c r="H1491" t="n">
         <v>2769308</v>
@@ -43666,7 +43666,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G1493" t="n">
-        <v>4.09506130218506</v>
+        <v>4.0950608253479</v>
       </c>
       <c r="H1493" t="n">
         <v>1311231</v>
@@ -43724,7 +43724,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G1495" t="n">
-        <v>4.15974092483521</v>
+        <v>4.15974140167236</v>
       </c>
       <c r="H1495" t="n">
         <v>1464599</v>
@@ -43753,7 +43753,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1496" t="n">
-        <v>4.09101819992065</v>
+        <v>4.09101867675781</v>
       </c>
       <c r="H1496" t="n">
         <v>2064342</v>
@@ -43782,7 +43782,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1497" t="n">
-        <v>4.09101819992065</v>
+        <v>4.09101867675781</v>
       </c>
       <c r="H1497" t="n">
         <v>1666798</v>
@@ -43811,7 +43811,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.9665093421936</v>
+        <v>3.96650910377502</v>
       </c>
       <c r="H1498" t="n">
         <v>3821543</v>
@@ -43840,7 +43840,7 @@
         <v>4.82200002670288</v>
       </c>
       <c r="G1499" t="n">
-        <v>3.89859509468079</v>
+        <v>3.89859461784363</v>
       </c>
       <c r="H1499" t="n">
         <v>1854115</v>
@@ -43869,7 +43869,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G1500" t="n">
-        <v>3.85493588447571</v>
+        <v>3.85493564605713</v>
       </c>
       <c r="H1500" t="n">
         <v>1392315</v>
@@ -44014,7 +44014,7 @@
         <v>4.76800012588501</v>
       </c>
       <c r="G1505" t="n">
-        <v>3.85493588447571</v>
+        <v>3.85493564605713</v>
       </c>
       <c r="H1505" t="n">
         <v>1339694</v>
@@ -44101,7 +44101,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G1508" t="n">
-        <v>3.84200000762939</v>
+        <v>3.84199953079224</v>
       </c>
       <c r="H1508" t="n">
         <v>1823559</v>
@@ -44159,7 +44159,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68353343009949</v>
+        <v>3.68353366851807</v>
       </c>
       <c r="H1510" t="n">
         <v>2103298</v>
@@ -44188,7 +44188,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G1511" t="n">
-        <v>3.80157494544983</v>
+        <v>3.80157518386841</v>
       </c>
       <c r="H1511" t="n">
         <v>1571045</v>
@@ -44217,7 +44217,7 @@
         <v>4.81599998474121</v>
       </c>
       <c r="G1512" t="n">
-        <v>3.89374375343323</v>
+        <v>3.89374399185181</v>
       </c>
       <c r="H1512" t="n">
         <v>1179137</v>
@@ -44246,7 +44246,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1513" t="n">
-        <v>3.86787152290344</v>
+        <v>3.86787176132202</v>
       </c>
       <c r="H1513" t="n">
         <v>1307537</v>
@@ -44304,7 +44304,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.91961574554443</v>
+        <v>3.91961598396301</v>
       </c>
       <c r="H1515" t="n">
         <v>1359512</v>
@@ -44333,7 +44333,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G1516" t="n">
-        <v>3.8436164855957</v>
+        <v>3.84361696243286</v>
       </c>
       <c r="H1516" t="n">
         <v>1206345</v>
@@ -44362,7 +44362,7 @@
         <v>4.91800022125244</v>
       </c>
       <c r="G1517" t="n">
-        <v>3.97621130943298</v>
+        <v>3.9762110710144</v>
       </c>
       <c r="H1517" t="n">
         <v>1436410</v>
@@ -44420,7 +44420,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1519" t="n">
-        <v>4.08293342590332</v>
+        <v>4.08293294906616</v>
       </c>
       <c r="H1519" t="n">
         <v>1247281</v>
@@ -44449,7 +44449,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1520" t="n">
-        <v>4.30122852325439</v>
+        <v>4.30122900009155</v>
       </c>
       <c r="H1520" t="n">
         <v>1917323</v>
@@ -44478,7 +44478,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1521" t="n">
-        <v>4.27293109893799</v>
+        <v>4.27293062210083</v>
       </c>
       <c r="H1521" t="n">
         <v>1561683</v>
@@ -44536,7 +44536,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1523" t="n">
-        <v>4.19612407684326</v>
+        <v>4.1961236000061</v>
       </c>
       <c r="H1523" t="n">
         <v>844298</v>
@@ -44565,7 +44565,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.26484680175781</v>
+        <v>4.26484632492065</v>
       </c>
       <c r="H1524" t="n">
         <v>1623441</v>
@@ -44594,7 +44594,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G1525" t="n">
-        <v>4.15974092483521</v>
+        <v>4.15974140167236</v>
       </c>
       <c r="H1525" t="n">
         <v>1016646</v>
@@ -44623,7 +44623,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1526" t="n">
-        <v>4.30122852325439</v>
+        <v>4.30122900009155</v>
       </c>
       <c r="H1526" t="n">
         <v>1854425</v>
@@ -44652,7 +44652,7 @@
         <v>5.25</v>
       </c>
       <c r="G1527" t="n">
-        <v>4.24463415145874</v>
+        <v>4.24463367462158</v>
       </c>
       <c r="H1527" t="n">
         <v>985241</v>
@@ -44710,7 +44710,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G1529" t="n">
-        <v>4.36995124816895</v>
+        <v>4.3699517250061</v>
       </c>
       <c r="H1529" t="n">
         <v>1003519</v>
@@ -44739,7 +44739,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1530" t="n">
-        <v>4.49122619628906</v>
+        <v>4.49122667312622</v>
       </c>
       <c r="H1530" t="n">
         <v>1546905</v>
@@ -44797,7 +44797,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G1532" t="n">
-        <v>4.41846179962158</v>
+        <v>4.41846132278442</v>
       </c>
       <c r="H1532" t="n">
         <v>949813</v>
@@ -44884,7 +44884,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1535" t="n">
-        <v>4.39016342163086</v>
+        <v>4.39016389846802</v>
       </c>
       <c r="H1535" t="n">
         <v>969598</v>
@@ -45174,7 +45174,7 @@
         <v>5.625</v>
       </c>
       <c r="G1545" t="n">
-        <v>4.54782152175903</v>
+        <v>4.54782199859619</v>
       </c>
       <c r="H1545" t="n">
         <v>1422376</v>
@@ -45203,7 +45203,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1546" t="n">
-        <v>4.55994892120361</v>
+        <v>4.55994939804077</v>
       </c>
       <c r="H1546" t="n">
         <v>903509</v>
@@ -45232,7 +45232,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1547" t="n">
-        <v>4.55994892120361</v>
+        <v>4.55994939804077</v>
       </c>
       <c r="H1547" t="n">
         <v>877583</v>
@@ -45290,7 +45290,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G1549" t="n">
-        <v>4.56399154663086</v>
+        <v>4.56399202346802</v>
       </c>
       <c r="H1549" t="n">
         <v>803941</v>
@@ -45435,7 +45435,7 @@
         <v>5.625</v>
       </c>
       <c r="G1554" t="n">
-        <v>4.54782152175903</v>
+        <v>4.54782199859619</v>
       </c>
       <c r="H1554" t="n">
         <v>1148827</v>
@@ -45464,7 +45464,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G1555" t="n">
-        <v>4.41846179962158</v>
+        <v>4.41846132278442</v>
       </c>
       <c r="H1555" t="n">
         <v>1637089</v>
@@ -45493,7 +45493,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>4.32548379898071</v>
+        <v>4.32548332214355</v>
       </c>
       <c r="H1556" t="n">
         <v>4183479</v>
@@ -45551,7 +45551,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1558" t="n">
-        <v>4.27293109893799</v>
+        <v>4.27293062210083</v>
       </c>
       <c r="H1558" t="n">
         <v>1328954</v>
@@ -45638,7 +45638,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1561" t="n">
-        <v>4.32548379898071</v>
+        <v>4.32548332214355</v>
       </c>
       <c r="H1561" t="n">
         <v>561433</v>
@@ -45667,7 +45667,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G1562" t="n">
-        <v>4.28910160064697</v>
+        <v>4.28910112380981</v>
       </c>
       <c r="H1562" t="n">
         <v>1496786</v>
@@ -45696,7 +45696,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G1563" t="n">
-        <v>4.24059152603149</v>
+        <v>4.24059104919434</v>
       </c>
       <c r="H1563" t="n">
         <v>685775</v>
@@ -45754,7 +45754,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1565" t="n">
-        <v>4.19612407684326</v>
+        <v>4.1961236000061</v>
       </c>
       <c r="H1565" t="n">
         <v>1024402</v>
@@ -45783,7 +45783,7 @@
         <v>5.25</v>
       </c>
       <c r="G1566" t="n">
-        <v>4.24463415145874</v>
+        <v>4.24463367462158</v>
       </c>
       <c r="H1566" t="n">
         <v>641444</v>
@@ -45812,7 +45812,7 @@
         <v>5.25</v>
       </c>
       <c r="G1567" t="n">
-        <v>4.24463415145874</v>
+        <v>4.24463367462158</v>
       </c>
       <c r="H1567" t="n">
         <v>1516581</v>
@@ -45870,7 +45870,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.25676155090332</v>
+        <v>4.256760597229</v>
       </c>
       <c r="H1569" t="n">
         <v>1159957</v>
@@ -45899,7 +45899,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G1570" t="n">
-        <v>4.36186599731445</v>
+        <v>4.36186647415161</v>
       </c>
       <c r="H1570" t="n">
         <v>731170</v>
@@ -45957,7 +45957,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1572" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1572" t="n">
         <v>732182</v>
@@ -45986,7 +45986,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1573" t="n">
-        <v>4.41037607192993</v>
+        <v>4.41037654876709</v>
       </c>
       <c r="H1573" t="n">
         <v>912828</v>
@@ -46044,7 +46044,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G1575" t="n">
-        <v>4.39016342163086</v>
+        <v>4.39016389846802</v>
       </c>
       <c r="H1575" t="n">
         <v>618267</v>
@@ -46160,7 +46160,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G1579" t="n">
-        <v>4.36186599731445</v>
+        <v>4.36186647415161</v>
       </c>
       <c r="H1579" t="n">
         <v>961829</v>
@@ -46218,7 +46218,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>4.44271612167358</v>
+        <v>4.44271659851074</v>
       </c>
       <c r="H1581" t="n">
         <v>1402787</v>
@@ -46247,7 +46247,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G1582" t="n">
-        <v>4.44271612167358</v>
+        <v>4.44271659851074</v>
       </c>
       <c r="H1582" t="n">
         <v>636333</v>
@@ -46276,7 +46276,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1583" t="n">
-        <v>4.49526882171631</v>
+        <v>4.49526929855347</v>
       </c>
       <c r="H1583" t="n">
         <v>969811</v>
@@ -46305,7 +46305,7 @@
         <v>5.49499988555908</v>
       </c>
       <c r="G1584" t="n">
-        <v>4.44271612167358</v>
+        <v>4.44271659851074</v>
       </c>
       <c r="H1584" t="n">
         <v>1124059</v>
@@ -46363,7 +46363,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>4.37399339675903</v>
+        <v>4.37399387359619</v>
       </c>
       <c r="H1586" t="n">
         <v>1297340</v>
@@ -46508,7 +46508,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G1591" t="n">
-        <v>4.49526882171631</v>
+        <v>4.49526929855347</v>
       </c>
       <c r="H1591" t="n">
         <v>1284240</v>
@@ -46566,7 +46566,7 @@
         <v>5.65000009536743</v>
       </c>
       <c r="G1593" t="n">
-        <v>4.56803464889526</v>
+        <v>4.56803417205811</v>
       </c>
       <c r="H1593" t="n">
         <v>842156</v>
@@ -46595,7 +46595,7 @@
         <v>5.66499996185303</v>
       </c>
       <c r="G1594" t="n">
-        <v>4.58016157150269</v>
+        <v>4.58016204833984</v>
       </c>
       <c r="H1594" t="n">
         <v>653054</v>
@@ -46653,7 +46653,7 @@
         <v>5.61499977111816</v>
       </c>
       <c r="G1596" t="n">
-        <v>4.53973627090454</v>
+        <v>4.5397367477417</v>
       </c>
       <c r="H1596" t="n">
         <v>507040</v>
@@ -46798,7 +46798,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G1601" t="n">
-        <v>4.430588722229</v>
+        <v>4.43058919906616</v>
       </c>
       <c r="H1601" t="n">
         <v>1127741</v>
@@ -46827,7 +46827,7 @@
         <v>5.45499992370605</v>
       </c>
       <c r="G1602" t="n">
-        <v>4.41037607192993</v>
+        <v>4.41037654876709</v>
       </c>
       <c r="H1602" t="n">
         <v>929946</v>
@@ -46914,7 +46914,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1605" t="n">
-        <v>4.3295259475708</v>
+        <v>4.32952642440796</v>
       </c>
       <c r="H1605" t="n">
         <v>1023223</v>
@@ -46972,7 +46972,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1607" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1607" t="n">
         <v>1646514</v>
@@ -47001,7 +47001,7 @@
         <v>5.25</v>
       </c>
       <c r="G1608" t="n">
-        <v>4.24463415145874</v>
+        <v>4.24463367462158</v>
       </c>
       <c r="H1608" t="n">
         <v>1501691</v>
@@ -47030,7 +47030,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1609" t="n">
-        <v>4.2688889503479</v>
+        <v>4.26888847351074</v>
       </c>
       <c r="H1609" t="n">
         <v>1435892</v>
@@ -47088,7 +47088,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>4.27293109893799</v>
+        <v>4.27293062210083</v>
       </c>
       <c r="H1611" t="n">
         <v>1040363</v>
@@ -47146,7 +47146,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1613" t="n">
-        <v>4.25676155090332</v>
+        <v>4.256760597229</v>
       </c>
       <c r="H1613" t="n">
         <v>864348</v>
@@ -47291,7 +47291,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1618" t="n">
-        <v>4.3295259475708</v>
+        <v>4.32952642440796</v>
       </c>
       <c r="H1618" t="n">
         <v>3053894</v>
@@ -47349,7 +47349,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1620" t="n">
         <v>6654047</v>
@@ -47465,7 +47465,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1624" t="n">
-        <v>4.42250347137451</v>
+        <v>4.42250394821167</v>
       </c>
       <c r="H1624" t="n">
         <v>1754976</v>
@@ -47552,7 +47552,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.49122619628906</v>
+        <v>4.49122667312622</v>
       </c>
       <c r="H1627" t="n">
         <v>973647</v>
@@ -47639,7 +47639,7 @@
         <v>5.625</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.54782152175903</v>
+        <v>4.54782199859619</v>
       </c>
       <c r="H1630" t="n">
         <v>907373</v>
@@ -47755,7 +47755,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G1634" t="n">
-        <v>4.76611709594727</v>
+        <v>4.76611661911011</v>
       </c>
       <c r="H1634" t="n">
         <v>1703140</v>
@@ -47871,7 +47871,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1638" t="n">
-        <v>4.78632974624634</v>
+        <v>4.78632926940918</v>
       </c>
       <c r="H1638" t="n">
         <v>1266527</v>
@@ -47987,7 +47987,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1642" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909461975098</v>
       </c>
       <c r="H1642" t="n">
         <v>1008256</v>
@@ -48045,7 +48045,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G1644" t="n">
-        <v>4.79845762252808</v>
+        <v>4.79845714569092</v>
       </c>
       <c r="H1644" t="n">
         <v>2019385</v>
@@ -48074,7 +48074,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G1645" t="n">
-        <v>4.77420282363892</v>
+        <v>4.77420234680176</v>
       </c>
       <c r="H1645" t="n">
         <v>2097226</v>
@@ -48219,7 +48219,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1650" t="n">
-        <v>4.72973489761353</v>
+        <v>4.72973442077637</v>
       </c>
       <c r="H1650" t="n">
         <v>1455029</v>
@@ -48277,7 +48277,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1652" t="n">
-        <v>4.75398969650269</v>
+        <v>4.75399017333984</v>
       </c>
       <c r="H1652" t="n">
         <v>1715375</v>
@@ -48335,7 +48335,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1654" t="n">
-        <v>4.75398969650269</v>
+        <v>4.75399017333984</v>
       </c>
       <c r="H1654" t="n">
         <v>1218622</v>
@@ -48393,7 +48393,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G1656" t="n">
-        <v>4.78632974624634</v>
+        <v>4.78632926940918</v>
       </c>
       <c r="H1656" t="n">
         <v>1416020</v>
@@ -48538,7 +48538,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1661" t="n">
-        <v>4.63271427154541</v>
+        <v>4.63271474838257</v>
       </c>
       <c r="H1661" t="n">
         <v>2400821</v>
@@ -48567,7 +48567,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1662" t="n">
-        <v>4.68122482299805</v>
+        <v>4.68122434616089</v>
       </c>
       <c r="H1662" t="n">
         <v>2378742</v>
@@ -48625,7 +48625,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G1664" t="n">
-        <v>4.62383985519409</v>
+        <v>4.62384033203125</v>
       </c>
       <c r="H1664" t="n">
         <v>1324929</v>
@@ -48683,7 +48683,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G1666" t="n">
-        <v>4.47042274475098</v>
+        <v>4.47042226791382</v>
       </c>
       <c r="H1666" t="n">
         <v>2102275</v>
@@ -48857,7 +48857,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1672" t="n">
-        <v>4.70054864883423</v>
+        <v>4.70054912567139</v>
       </c>
       <c r="H1672" t="n">
         <v>2050602</v>
@@ -48886,7 +48886,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G1673" t="n">
-        <v>4.70054864883423</v>
+        <v>4.70054912567139</v>
       </c>
       <c r="H1673" t="n">
         <v>1541904</v>
@@ -48944,7 +48944,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1675" t="n">
-        <v>4.72185707092285</v>
+        <v>4.72185754776001</v>
       </c>
       <c r="H1675" t="n">
         <v>1322091</v>
@@ -49118,7 +49118,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1681" t="n">
-        <v>4.66219425201416</v>
+        <v>4.66219472885132</v>
       </c>
       <c r="H1681" t="n">
         <v>3252351</v>
@@ -49437,7 +49437,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G1692" t="n">
-        <v>4.62383985519409</v>
+        <v>4.62384033203125</v>
       </c>
       <c r="H1692" t="n">
         <v>1441791</v>
@@ -49669,7 +49669,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1700" t="n">
-        <v>4.48746919631958</v>
+        <v>4.48746871948242</v>
       </c>
       <c r="H1700" t="n">
         <v>2387659</v>
@@ -49872,7 +49872,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1707" t="n">
-        <v>4.56843948364258</v>
+        <v>4.56843996047974</v>
       </c>
       <c r="H1707" t="n">
         <v>1457718</v>
@@ -50017,7 +50017,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1712" t="n">
-        <v>4.57696199417114</v>
+        <v>4.5769624710083</v>
       </c>
       <c r="H1712" t="n">
         <v>1525220</v>
@@ -50046,7 +50046,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1713" t="n">
-        <v>4.56843948364258</v>
+        <v>4.56843996047974</v>
       </c>
       <c r="H1713" t="n">
         <v>1988065</v>
@@ -50075,7 +50075,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1714" t="n">
-        <v>4.50877714157104</v>
+        <v>4.50877666473389</v>
       </c>
       <c r="H1714" t="n">
         <v>1546281</v>
@@ -50220,7 +50220,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1719" t="n">
-        <v>4.3979754447937</v>
+        <v>4.39797496795654</v>
       </c>
       <c r="H1719" t="n">
         <v>1927099</v>
@@ -50249,7 +50249,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1720" t="n">
-        <v>4.44911479949951</v>
+        <v>4.44911432266235</v>
       </c>
       <c r="H1720" t="n">
         <v>1563773</v>
@@ -50423,7 +50423,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G1726" t="n">
-        <v>4.30848121643066</v>
+        <v>4.30848169326782</v>
       </c>
       <c r="H1726" t="n">
         <v>1910118</v>
@@ -50452,7 +50452,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1727" t="n">
-        <v>4.30422019958496</v>
+        <v>4.3042197227478</v>
       </c>
       <c r="H1727" t="n">
         <v>1350694</v>
@@ -50626,7 +50626,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1733" t="n">
-        <v>4.50025415420532</v>
+        <v>4.50025367736816</v>
       </c>
       <c r="H1733" t="n">
         <v>1069788</v>
@@ -50655,7 +50655,7 @@
         <v>5.25</v>
       </c>
       <c r="G1734" t="n">
-        <v>4.474684715271</v>
+        <v>4.47468423843384</v>
       </c>
       <c r="H1734" t="n">
         <v>1318348</v>
@@ -50684,7 +50684,7 @@
         <v>5.25</v>
       </c>
       <c r="G1735" t="n">
-        <v>4.474684715271</v>
+        <v>4.47468423843384</v>
       </c>
       <c r="H1735" t="n">
         <v>1212793</v>
@@ -50771,7 +50771,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G1738" t="n">
-        <v>4.46189975738525</v>
+        <v>4.4618992805481</v>
       </c>
       <c r="H1738" t="n">
         <v>631020</v>
@@ -50800,7 +50800,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G1739" t="n">
-        <v>4.42780685424805</v>
+        <v>4.42780637741089</v>
       </c>
       <c r="H1739" t="n">
         <v>1166591</v>
@@ -50829,7 +50829,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1740" t="n">
-        <v>4.50025415420532</v>
+        <v>4.50025367736816</v>
       </c>
       <c r="H1740" t="n">
         <v>1760127</v>
@@ -50858,7 +50858,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1741" t="n">
-        <v>4.48746919631958</v>
+        <v>4.48746871948242</v>
       </c>
       <c r="H1741" t="n">
         <v>1738340</v>
@@ -50887,7 +50887,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1742" t="n">
-        <v>4.50877714157104</v>
+        <v>4.50877666473389</v>
       </c>
       <c r="H1742" t="n">
         <v>1362760</v>
@@ -50945,7 +50945,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G1744" t="n">
-        <v>4.47042274475098</v>
+        <v>4.47042226791382</v>
       </c>
       <c r="H1744" t="n">
         <v>1815807</v>
@@ -51032,7 +51032,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1747" t="n">
-        <v>4.44911479949951</v>
+        <v>4.44911432266235</v>
       </c>
       <c r="H1747" t="n">
         <v>1418093</v>
@@ -51061,7 +51061,7 @@
         <v>5.25</v>
       </c>
       <c r="G1748" t="n">
-        <v>4.474684715271</v>
+        <v>4.47468423843384</v>
       </c>
       <c r="H1748" t="n">
         <v>794067</v>
@@ -51090,7 +51090,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G1749" t="n">
-        <v>4.52156209945679</v>
+        <v>4.52156162261963</v>
       </c>
       <c r="H1749" t="n">
         <v>1341662</v>
@@ -51206,7 +51206,7 @@
         <v>4.99399995803833</v>
       </c>
       <c r="G1753" t="n">
-        <v>4.2564902305603</v>
+        <v>4.25648975372314</v>
       </c>
       <c r="H1753" t="n">
         <v>3520916</v>
@@ -51264,7 +51264,7 @@
         <v>4.81400012969971</v>
       </c>
       <c r="G1755" t="n">
-        <v>4.10307216644287</v>
+        <v>4.10307264328003</v>
       </c>
       <c r="H1755" t="n">
         <v>2318148</v>
@@ -51293,7 +51293,7 @@
         <v>4.85200023651123</v>
       </c>
       <c r="G1756" t="n">
-        <v>4.13546085357666</v>
+        <v>4.1354603767395</v>
       </c>
       <c r="H1756" t="n">
         <v>2230921</v>
@@ -51322,7 +51322,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G1757" t="n">
-        <v>4.04681968688965</v>
+        <v>4.04681921005249</v>
       </c>
       <c r="H1757" t="n">
         <v>1751768</v>
@@ -51380,7 +51380,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1759" t="n">
-        <v>4.09966325759888</v>
+        <v>4.09966278076172</v>
       </c>
       <c r="H1759" t="n">
         <v>2615910</v>
@@ -51467,7 +51467,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G1762" t="n">
-        <v>4.15762042999268</v>
+        <v>4.15762090682983</v>
       </c>
       <c r="H1762" t="n">
         <v>1211245</v>
@@ -51641,7 +51641,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1768" t="n">
-        <v>4.30422019958496</v>
+        <v>4.3042197227478</v>
       </c>
       <c r="H1768" t="n">
         <v>3656588</v>
@@ -51786,7 +51786,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G1773" t="n">
-        <v>4.08432102203369</v>
+        <v>4.08432054519653</v>
       </c>
       <c r="H1773" t="n">
         <v>2136607</v>
@@ -51815,7 +51815,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G1774" t="n">
-        <v>4.09454870223999</v>
+        <v>4.09454917907715</v>
       </c>
       <c r="H1774" t="n">
         <v>1879953</v>
@@ -51902,7 +51902,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G1777" t="n">
-        <v>4.03999996185303</v>
+        <v>4.04000043869019</v>
       </c>
       <c r="H1777" t="n">
         <v>1986204</v>
@@ -52047,7 +52047,7 @@
         <v>4.92799997329712</v>
       </c>
       <c r="G1782" t="n">
-        <v>4.20023632049561</v>
+        <v>4.20023679733276</v>
       </c>
       <c r="H1782" t="n">
         <v>1630080</v>
@@ -52163,7 +52163,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G1786" t="n">
-        <v>4.1252326965332</v>
+        <v>4.12523317337036</v>
       </c>
       <c r="H1786" t="n">
         <v>1645922</v>
@@ -52221,7 +52221,7 @@
         <v>4.93599987030029</v>
       </c>
       <c r="G1788" t="n">
-        <v>4.20705556869507</v>
+        <v>4.20705509185791</v>
       </c>
       <c r="H1788" t="n">
         <v>2087689</v>
@@ -52424,7 +52424,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1795" t="n">
-        <v>4.30422019958496</v>
+        <v>4.3042197227478</v>
       </c>
       <c r="H1795" t="n">
         <v>996539</v>
@@ -52482,7 +52482,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G1797" t="n">
-        <v>4.30848121643066</v>
+        <v>4.30848169326782</v>
       </c>
       <c r="H1797" t="n">
         <v>1499740</v>
@@ -52714,7 +52714,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G1805" t="n">
-        <v>4.42780685424805</v>
+        <v>4.42780637741089</v>
       </c>
       <c r="H1805" t="n">
         <v>1388007</v>
@@ -52743,7 +52743,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G1806" t="n">
-        <v>4.46189975738525</v>
+        <v>4.4618992805481</v>
       </c>
       <c r="H1806" t="n">
         <v>1493495</v>
@@ -52946,7 +52946,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1813" t="n">
-        <v>4.4150218963623</v>
+        <v>4.41502141952515</v>
       </c>
       <c r="H1813" t="n">
         <v>1436080</v>
@@ -52975,7 +52975,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1814" t="n">
-        <v>4.4150218963623</v>
+        <v>4.41502141952515</v>
       </c>
       <c r="H1814" t="n">
         <v>1194169</v>
@@ -53120,7 +53120,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1819" t="n">
-        <v>4.4150218963623</v>
+        <v>4.41502141952515</v>
       </c>
       <c r="H1819" t="n">
         <v>795050</v>
@@ -53178,7 +53178,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1821" t="n">
-        <v>4.30422019958496</v>
+        <v>4.3042197227478</v>
       </c>
       <c r="H1821" t="n">
         <v>2549442</v>
@@ -53294,7 +53294,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1825" t="n">
-        <v>4.50877714157104</v>
+        <v>4.50877666473389</v>
       </c>
       <c r="H1825" t="n">
         <v>2487573</v>
@@ -53497,7 +53497,7 @@
         <v>5.2350001335144</v>
       </c>
       <c r="G1832" t="n">
-        <v>4.46189975738525</v>
+        <v>4.4618992805481</v>
       </c>
       <c r="H1832" t="n">
         <v>963372</v>
@@ -53526,7 +53526,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1833" t="n">
-        <v>4.50025415420532</v>
+        <v>4.50025367736816</v>
       </c>
       <c r="H1833" t="n">
         <v>1695778</v>
@@ -53584,7 +53584,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.42780685424805</v>
+        <v>4.42780637741089</v>
       </c>
       <c r="H1835" t="n">
         <v>1654845</v>
@@ -53613,7 +53613,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.44911479949951</v>
+        <v>4.44911432266235</v>
       </c>
       <c r="H1836" t="n">
         <v>1149985</v>
@@ -53700,7 +53700,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.4150218963623</v>
+        <v>4.41502141952515</v>
       </c>
       <c r="H1839" t="n">
         <v>1490733</v>
@@ -53758,7 +53758,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.50877714157104</v>
+        <v>4.50877666473389</v>
       </c>
       <c r="H1841" t="n">
         <v>1782092</v>
@@ -53845,7 +53845,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.38945245742798</v>
+        <v>4.38945198059082</v>
       </c>
       <c r="H1844" t="n">
         <v>2653936</v>
@@ -53874,7 +53874,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.4150218963623</v>
+        <v>4.41502141952515</v>
       </c>
       <c r="H1845" t="n">
         <v>2063216</v>
@@ -54135,7 +54135,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1854" t="n">
-        <v>4.38945245742798</v>
+        <v>4.38945198059082</v>
       </c>
       <c r="H1854" t="n">
         <v>993834</v>
@@ -54164,7 +54164,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G1855" t="n">
-        <v>4.42780685424805</v>
+        <v>4.42780637741089</v>
       </c>
       <c r="H1855" t="n">
         <v>1670726</v>
@@ -54251,7 +54251,7 @@
         <v>5.09499979019165</v>
       </c>
       <c r="G1858" t="n">
-        <v>4.34257459640503</v>
+        <v>4.34257411956787</v>
       </c>
       <c r="H1858" t="n">
         <v>2918106</v>
@@ -54309,7 +54309,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G1860" t="n">
-        <v>4.32552814483643</v>
+        <v>4.32552766799927</v>
       </c>
       <c r="H1860" t="n">
         <v>1936775</v>
@@ -54454,7 +54454,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G1865" t="n">
-        <v>4.42780685424805</v>
+        <v>4.42780637741089</v>
       </c>
       <c r="H1865" t="n">
         <v>2237111</v>
@@ -54483,7 +54483,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G1866" t="n">
-        <v>4.43632984161377</v>
+        <v>4.43632936477661</v>
       </c>
       <c r="H1866" t="n">
         <v>2626377</v>
@@ -54512,7 +54512,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1867" t="n">
-        <v>4.50877714157104</v>
+        <v>4.50877666473389</v>
       </c>
       <c r="H1867" t="n">
         <v>3175155</v>
@@ -54773,7 +54773,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G1876" t="n">
-        <v>4.43632984161377</v>
+        <v>4.43632936477661</v>
       </c>
       <c r="H1876" t="n">
         <v>3434914</v>
@@ -54802,7 +54802,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1877" t="n">
-        <v>4.3979754447937</v>
+        <v>4.39797496795654</v>
       </c>
       <c r="H1877" t="n">
         <v>3203860</v>
@@ -54831,7 +54831,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1878" t="n">
-        <v>4.49173069000244</v>
+        <v>4.49173021316528</v>
       </c>
       <c r="H1878" t="n">
         <v>2244129</v>
@@ -55382,7 +55382,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G1897" t="n">
-        <v>4.37666749954224</v>
+        <v>4.37666702270508</v>
       </c>
       <c r="H1897" t="n">
         <v>2429389</v>
@@ -55440,7 +55440,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G1899" t="n">
-        <v>4.3979754447937</v>
+        <v>4.39797496795654</v>
       </c>
       <c r="H1899" t="n">
         <v>2104566</v>
@@ -55498,7 +55498,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G1901" t="n">
-        <v>4.42780685424805</v>
+        <v>4.42780637741089</v>
       </c>
       <c r="H1901" t="n">
         <v>2336262</v>
@@ -55527,7 +55527,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G1902" t="n">
-        <v>4.47042274475098</v>
+        <v>4.47042226791382</v>
       </c>
       <c r="H1902" t="n">
         <v>1826427</v>
@@ -55585,7 +55585,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G1904" t="n">
-        <v>4.43632984161377</v>
+        <v>4.43632936477661</v>
       </c>
       <c r="H1904" t="n">
         <v>2194273</v>
@@ -55614,7 +55614,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G1905" t="n">
-        <v>4.47042274475098</v>
+        <v>4.47042226791382</v>
       </c>
       <c r="H1905" t="n">
         <v>2234186</v>
@@ -55643,7 +55643,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1906" t="n">
-        <v>4.50877714157104</v>
+        <v>4.50877666473389</v>
       </c>
       <c r="H1906" t="n">
         <v>2599906</v>
@@ -55672,7 +55672,7 @@
         <v>5.25</v>
       </c>
       <c r="G1907" t="n">
-        <v>4.474684715271</v>
+        <v>4.47468423843384</v>
       </c>
       <c r="H1907" t="n">
         <v>6302113</v>
@@ -55730,7 +55730,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1909" t="n">
-        <v>4.49173069000244</v>
+        <v>4.49173021316528</v>
       </c>
       <c r="H1909" t="n">
         <v>2814628</v>
@@ -55788,7 +55788,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1911" t="n">
-        <v>4.58974742889404</v>
+        <v>4.5897479057312</v>
       </c>
       <c r="H1911" t="n">
         <v>3273989</v>
@@ -55846,7 +55846,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G1913" t="n">
-        <v>4.59827041625977</v>
+        <v>4.59827089309692</v>
       </c>
       <c r="H1913" t="n">
         <v>4153917</v>
@@ -73861,6 +73861,35 @@
         <v>3150219</v>
       </c>
       <c r="I2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2535" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>8.92000007629395</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>8.96199989318848</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>8.85200023651123</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>8.92399978637695</v>
+      </c>
+      <c r="G2535" t="n">
+        <v>8.92399978637695</v>
+      </c>
+      <c r="H2535" t="n">
+        <v>2616666</v>
+      </c>
+      <c r="I2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G4" t="n">
-        <v>2.22863054275513</v>
+        <v>2.22863078117371</v>
       </c>
       <c r="H4" t="n">
         <v>21739065</v>
@@ -514,7 +514,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G5" t="n">
-        <v>2.07256460189819</v>
+        <v>2.07256436347961</v>
       </c>
       <c r="H5" t="n">
         <v>25466044</v>
@@ -543,7 +543,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08005547523499</v>
+        <v>2.08005571365356</v>
       </c>
       <c r="H6" t="n">
         <v>30431584</v>
@@ -572,7 +572,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0038948059082</v>
+        <v>2.00389504432678</v>
       </c>
       <c r="H7" t="n">
         <v>20054402</v>
@@ -601,7 +601,7 @@
         <v>3.16199994087219</v>
       </c>
       <c r="G8" t="n">
-        <v>1.97393023967743</v>
+        <v>1.97393012046814</v>
       </c>
       <c r="H8" t="n">
         <v>14428295</v>
@@ -630,7 +630,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G9" t="n">
-        <v>1.99765229225159</v>
+        <v>1.99765241146088</v>
       </c>
       <c r="H9" t="n">
         <v>7415318</v>
@@ -659,7 +659,7 @@
         <v>3.13599991798401</v>
       </c>
       <c r="G10" t="n">
-        <v>1.95769917964935</v>
+        <v>1.95769941806793</v>
       </c>
       <c r="H10" t="n">
         <v>12484141</v>
@@ -688,7 +688,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G11" t="n">
-        <v>1.97268152236938</v>
+        <v>1.97268176078796</v>
       </c>
       <c r="H11" t="n">
         <v>9571640</v>
@@ -717,7 +717,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G12" t="n">
-        <v>1.95645070075989</v>
+        <v>1.95645081996918</v>
       </c>
       <c r="H12" t="n">
         <v>4499554</v>
@@ -746,7 +746,7 @@
         <v>3.2279999256134</v>
       </c>
       <c r="G13" t="n">
-        <v>2.01513171195984</v>
+        <v>2.01513147354126</v>
       </c>
       <c r="H13" t="n">
         <v>6390924</v>
@@ -804,7 +804,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G15" t="n">
-        <v>2.05383634567261</v>
+        <v>2.05383610725403</v>
       </c>
       <c r="H15" t="n">
         <v>2202715</v>
@@ -833,7 +833,7 @@
         <v>3.34200000762939</v>
       </c>
       <c r="G16" t="n">
-        <v>2.08629775047302</v>
+        <v>2.08629822731018</v>
       </c>
       <c r="H16" t="n">
         <v>5224516</v>
@@ -862,7 +862,7 @@
         <v>3.33200001716614</v>
       </c>
       <c r="G17" t="n">
-        <v>2.08005547523499</v>
+        <v>2.08005571365356</v>
       </c>
       <c r="H17" t="n">
         <v>5610251</v>
@@ -949,7 +949,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G20" t="n">
-        <v>2.08504986763</v>
+        <v>2.08504962921143</v>
       </c>
       <c r="H20" t="n">
         <v>5666890</v>
@@ -978,7 +978,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G21" t="n">
-        <v>2.0413510799408</v>
+        <v>2.04135084152222</v>
       </c>
       <c r="H21" t="n">
         <v>6033410</v>
@@ -1036,7 +1036,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12874841690063</v>
+        <v>2.12874817848206</v>
       </c>
       <c r="H23" t="n">
         <v>6586280</v>
@@ -1065,7 +1065,7 @@
         <v>3.51399993896484</v>
       </c>
       <c r="G24" t="n">
-        <v>2.1936719417572</v>
+        <v>2.19367218017578</v>
       </c>
       <c r="H24" t="n">
         <v>6839861</v>
@@ -1123,7 +1123,7 @@
         <v>3.5239999294281</v>
       </c>
       <c r="G26" t="n">
-        <v>2.19991421699524</v>
+        <v>2.19991445541382</v>
       </c>
       <c r="H26" t="n">
         <v>4376808</v>
@@ -1152,7 +1152,7 @@
         <v>3.43199992179871</v>
       </c>
       <c r="G27" t="n">
-        <v>2.14248180389404</v>
+        <v>2.14248204231262</v>
       </c>
       <c r="H27" t="n">
         <v>5168471</v>
@@ -1181,7 +1181,7 @@
         <v>3.52800011634827</v>
       </c>
       <c r="G28" t="n">
-        <v>2.20241189002991</v>
+        <v>2.20241165161133</v>
       </c>
       <c r="H28" t="n">
         <v>5589161</v>
@@ -1268,7 +1268,7 @@
         <v>3.59800004959106</v>
       </c>
       <c r="G31" t="n">
-        <v>2.24611020088196</v>
+        <v>2.24611067771912</v>
       </c>
       <c r="H31" t="n">
         <v>6356152</v>
@@ -1297,7 +1297,7 @@
         <v>3.67400002479553</v>
       </c>
       <c r="G32" t="n">
-        <v>2.29355478286743</v>
+        <v>2.29355454444885</v>
       </c>
       <c r="H32" t="n">
         <v>4092166</v>
@@ -1384,7 +1384,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G35" t="n">
-        <v>2.27857232093811</v>
+        <v>2.27857208251953</v>
       </c>
       <c r="H35" t="n">
         <v>3208639</v>
@@ -1413,7 +1413,7 @@
         <v>3.67199993133545</v>
       </c>
       <c r="G36" t="n">
-        <v>2.29230570793152</v>
+        <v>2.2923059463501</v>
       </c>
       <c r="H36" t="n">
         <v>1759291</v>
@@ -1442,7 +1442,7 @@
         <v>3.71399998664856</v>
       </c>
       <c r="G37" t="n">
-        <v>2.31852531433105</v>
+        <v>2.3185248374939</v>
       </c>
       <c r="H37" t="n">
         <v>1256671</v>
@@ -1471,7 +1471,7 @@
         <v>3.69600009918213</v>
       </c>
       <c r="G38" t="n">
-        <v>2.30728840827942</v>
+        <v>2.307288646698</v>
       </c>
       <c r="H38" t="n">
         <v>1605686</v>
@@ -1500,7 +1500,7 @@
         <v>3.7279999256134</v>
       </c>
       <c r="G39" t="n">
-        <v>2.32726502418518</v>
+        <v>2.3272647857666</v>
       </c>
       <c r="H39" t="n">
         <v>1980797</v>
@@ -1529,7 +1529,7 @@
         <v>3.73799991607666</v>
       </c>
       <c r="G40" t="n">
-        <v>2.3335075378418</v>
+        <v>2.33350777626038</v>
       </c>
       <c r="H40" t="n">
         <v>1373552</v>
@@ -1558,7 +1558,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G41" t="n">
-        <v>2.38095188140869</v>
+        <v>2.38095164299011</v>
       </c>
       <c r="H41" t="n">
         <v>2062784</v>
@@ -1587,7 +1587,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G42" t="n">
-        <v>2.34599280357361</v>
+        <v>2.34599304199219</v>
       </c>
       <c r="H42" t="n">
         <v>2886613</v>
@@ -1616,7 +1616,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G43" t="n">
-        <v>2.3846971988678</v>
+        <v>2.38469743728638</v>
       </c>
       <c r="H43" t="n">
         <v>2605147</v>
@@ -1645,7 +1645,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G44" t="n">
-        <v>2.38095188140869</v>
+        <v>2.38095164299011</v>
       </c>
       <c r="H44" t="n">
         <v>3468958</v>
@@ -1674,7 +1674,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G45" t="n">
-        <v>2.3846971988678</v>
+        <v>2.38469743728638</v>
       </c>
       <c r="H45" t="n">
         <v>1750587</v>
@@ -1703,7 +1703,7 @@
         <v>3.75</v>
       </c>
       <c r="G46" t="n">
-        <v>2.34099841117859</v>
+        <v>2.34099888801575</v>
       </c>
       <c r="H46" t="n">
         <v>3939834</v>
@@ -1732,7 +1732,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G47" t="n">
-        <v>2.36097550392151</v>
+        <v>2.36097526550293</v>
       </c>
       <c r="H47" t="n">
         <v>3063904</v>
@@ -1761,7 +1761,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>2.32851338386536</v>
+        <v>2.32851362228394</v>
       </c>
       <c r="H48" t="n">
         <v>3129507</v>
@@ -1790,7 +1790,7 @@
         <v>3.74200010299683</v>
       </c>
       <c r="G49" t="n">
-        <v>2.33600497245789</v>
+        <v>2.33600449562073</v>
       </c>
       <c r="H49" t="n">
         <v>2305779</v>
@@ -1877,7 +1877,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G52" t="n">
-        <v>2.32851338386536</v>
+        <v>2.32851362228394</v>
       </c>
       <c r="H52" t="n">
         <v>3089208</v>
@@ -1993,7 +1993,7 @@
         <v>3.70799994468689</v>
       </c>
       <c r="G56" t="n">
-        <v>2.31477975845337</v>
+        <v>2.31477952003479</v>
       </c>
       <c r="H56" t="n">
         <v>3360031</v>
@@ -2022,7 +2022,7 @@
         <v>3.75799989700317</v>
       </c>
       <c r="G57" t="n">
-        <v>2.34599280357361</v>
+        <v>2.34599304199219</v>
       </c>
       <c r="H57" t="n">
         <v>2216469</v>
@@ -2080,7 +2080,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G59" t="n">
-        <v>2.30978536605835</v>
+        <v>2.30978560447693</v>
       </c>
       <c r="H59" t="n">
         <v>1834154</v>
@@ -2138,7 +2138,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G61" t="n">
-        <v>2.17868971824646</v>
+        <v>2.1786892414093</v>
       </c>
       <c r="H61" t="n">
         <v>5521766</v>
@@ -2225,7 +2225,7 @@
         <v>3.65199995040894</v>
       </c>
       <c r="G64" t="n">
-        <v>2.27982068061829</v>
+        <v>2.27982044219971</v>
       </c>
       <c r="H64" t="n">
         <v>2737943</v>
@@ -2254,7 +2254,7 @@
         <v>3.69400000572205</v>
       </c>
       <c r="G65" t="n">
-        <v>2.30604004859924</v>
+        <v>2.30603981018066</v>
       </c>
       <c r="H65" t="n">
         <v>2240137</v>
@@ -2283,7 +2283,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G66" t="n">
-        <v>2.27857232093811</v>
+        <v>2.27857208251953</v>
       </c>
       <c r="H66" t="n">
         <v>1964602</v>
@@ -2312,7 +2312,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G67" t="n">
-        <v>2.29105734825134</v>
+        <v>2.29105758666992</v>
       </c>
       <c r="H67" t="n">
         <v>2558214</v>
@@ -2370,7 +2370,7 @@
         <v>3.78399991989136</v>
       </c>
       <c r="G69" t="n">
-        <v>2.36222386360168</v>
+        <v>2.36222362518311</v>
       </c>
       <c r="H69" t="n">
         <v>2429548</v>
@@ -2399,7 +2399,7 @@
         <v>3.78200006484985</v>
       </c>
       <c r="G70" t="n">
-        <v>2.36097550392151</v>
+        <v>2.36097526550293</v>
       </c>
       <c r="H70" t="n">
         <v>2975719</v>
@@ -2486,7 +2486,7 @@
         <v>3.77800011634827</v>
       </c>
       <c r="G73" t="n">
-        <v>2.358478307724</v>
+        <v>2.35847806930542</v>
       </c>
       <c r="H73" t="n">
         <v>2244613</v>
@@ -2515,7 +2515,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G74" t="n">
-        <v>2.3846971988678</v>
+        <v>2.38469743728638</v>
       </c>
       <c r="H74" t="n">
         <v>1520764</v>
@@ -2573,7 +2573,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G76" t="n">
-        <v>2.36721801757812</v>
+        <v>2.36721777915955</v>
       </c>
       <c r="H76" t="n">
         <v>1733373</v>
@@ -2602,7 +2602,7 @@
         <v>3.81399989128113</v>
       </c>
       <c r="G77" t="n">
-        <v>2.38095188140869</v>
+        <v>2.38095164299011</v>
       </c>
       <c r="H77" t="n">
         <v>2013014</v>
@@ -2631,7 +2631,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G78" t="n">
-        <v>2.36596918106079</v>
+        <v>2.36596965789795</v>
       </c>
       <c r="H78" t="n">
         <v>3734574</v>
@@ -2660,7 +2660,7 @@
         <v>3.75</v>
       </c>
       <c r="G79" t="n">
-        <v>2.34099841117859</v>
+        <v>2.34099888801575</v>
       </c>
       <c r="H79" t="n">
         <v>1542324</v>
@@ -2689,7 +2689,7 @@
         <v>3.75</v>
       </c>
       <c r="G80" t="n">
-        <v>2.34099841117859</v>
+        <v>2.34099888801575</v>
       </c>
       <c r="H80" t="n">
         <v>1407964</v>
@@ -2718,7 +2718,7 @@
         <v>3.79200005531311</v>
       </c>
       <c r="G81" t="n">
-        <v>2.36721801757812</v>
+        <v>2.36721777915955</v>
       </c>
       <c r="H81" t="n">
         <v>1985720</v>
@@ -2805,7 +2805,7 @@
         <v>3.82800006866455</v>
       </c>
       <c r="G84" t="n">
-        <v>2.3896918296814</v>
+        <v>2.38969135284424</v>
       </c>
       <c r="H84" t="n">
         <v>1165087</v>
@@ -2834,7 +2834,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G85" t="n">
-        <v>2.39093995094299</v>
+        <v>2.39094018936157</v>
       </c>
       <c r="H85" t="n">
         <v>1408585</v>
@@ -2863,7 +2863,7 @@
         <v>3.85800004005432</v>
       </c>
       <c r="G86" t="n">
-        <v>2.40841960906982</v>
+        <v>2.40841913223267</v>
       </c>
       <c r="H86" t="n">
         <v>1569946</v>
@@ -2921,7 +2921,7 @@
         <v>3.85599994659424</v>
       </c>
       <c r="G88" t="n">
-        <v>2.40717101097107</v>
+        <v>2.40717124938965</v>
       </c>
       <c r="H88" t="n">
         <v>1733460</v>
@@ -2950,7 +2950,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G89" t="n">
-        <v>2.42839574813843</v>
+        <v>2.42839622497559</v>
       </c>
       <c r="H89" t="n">
         <v>2000160</v>
@@ -2979,7 +2979,7 @@
         <v>3.87599992752075</v>
       </c>
       <c r="G90" t="n">
-        <v>2.41965651512146</v>
+        <v>2.41965627670288</v>
       </c>
       <c r="H90" t="n">
         <v>1840732</v>
@@ -3008,7 +3008,7 @@
         <v>3.90799999237061</v>
       </c>
       <c r="G91" t="n">
-        <v>2.43963313102722</v>
+        <v>2.43963289260864</v>
       </c>
       <c r="H91" t="n">
         <v>4620752</v>
@@ -3037,7 +3037,7 @@
         <v>3.91199994087219</v>
       </c>
       <c r="G92" t="n">
-        <v>2.44212985038757</v>
+        <v>2.44212961196899</v>
       </c>
       <c r="H92" t="n">
         <v>2904180</v>
@@ -3124,7 +3124,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G95" t="n">
-        <v>2.4671003818512</v>
+        <v>2.46710014343262</v>
       </c>
       <c r="H95" t="n">
         <v>9713560</v>
@@ -3211,7 +3211,7 @@
         <v>3.94600009918213</v>
       </c>
       <c r="G98" t="n">
-        <v>2.46335530281067</v>
+        <v>2.46335506439209</v>
       </c>
       <c r="H98" t="n">
         <v>2677473</v>
@@ -3240,7 +3240,7 @@
         <v>3.95199990272522</v>
       </c>
       <c r="G99" t="n">
-        <v>2.4671003818512</v>
+        <v>2.46710014343262</v>
       </c>
       <c r="H99" t="n">
         <v>2383108</v>
@@ -3269,7 +3269,7 @@
         <v>4.0939998626709</v>
       </c>
       <c r="G100" t="n">
-        <v>2.55574607849121</v>
+        <v>2.55574631690979</v>
       </c>
       <c r="H100" t="n">
         <v>3927765</v>
@@ -3327,7 +3327,7 @@
         <v>4.13800001144409</v>
       </c>
       <c r="G102" t="n">
-        <v>2.5832142829895</v>
+        <v>2.58321404457092</v>
       </c>
       <c r="H102" t="n">
         <v>2760372</v>
@@ -3356,7 +3356,7 @@
         <v>4.06199979782104</v>
       </c>
       <c r="G103" t="n">
-        <v>2.53576970100403</v>
+        <v>2.53576993942261</v>
       </c>
       <c r="H103" t="n">
         <v>2303291</v>
@@ -3414,7 +3414,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G105" t="n">
-        <v>2.56698298454285</v>
+        <v>2.56698346138</v>
       </c>
       <c r="H105" t="n">
         <v>3011118</v>
@@ -3530,7 +3530,7 @@
         <v>4.13399982452393</v>
       </c>
       <c r="G109" t="n">
-        <v>2.58071708679199</v>
+        <v>2.58071684837341</v>
       </c>
       <c r="H109" t="n">
         <v>2152114</v>
@@ -3588,7 +3588,7 @@
         <v>4.10799980163574</v>
       </c>
       <c r="G111" t="n">
-        <v>2.56448578834534</v>
+        <v>2.5644862651825</v>
       </c>
       <c r="H111" t="n">
         <v>1505349</v>
@@ -3704,7 +3704,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G115" t="n">
-        <v>2.59694766998291</v>
+        <v>2.59694790840149</v>
       </c>
       <c r="H115" t="n">
         <v>2393218</v>
@@ -3733,7 +3733,7 @@
         <v>4.14200019836426</v>
       </c>
       <c r="G116" t="n">
-        <v>2.58571147918701</v>
+        <v>2.58571171760559</v>
       </c>
       <c r="H116" t="n">
         <v>2970660</v>
@@ -3762,7 +3762,7 @@
         <v>4.14400005340576</v>
       </c>
       <c r="G117" t="n">
-        <v>2.58695983886719</v>
+        <v>2.58695960044861</v>
       </c>
       <c r="H117" t="n">
         <v>1464984</v>
@@ -3791,7 +3791,7 @@
         <v>4.08199977874756</v>
       </c>
       <c r="G118" t="n">
-        <v>2.54825520515442</v>
+        <v>2.54825496673584</v>
       </c>
       <c r="H118" t="n">
         <v>3067347</v>
@@ -3878,7 +3878,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G121" t="n">
-        <v>2.57822012901306</v>
+        <v>2.57821989059448</v>
       </c>
       <c r="H121" t="n">
         <v>2971262</v>
@@ -3907,7 +3907,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G122" t="n">
-        <v>2.60319137573242</v>
+        <v>2.60319042205811</v>
       </c>
       <c r="H122" t="n">
         <v>2478837</v>
@@ -3936,7 +3936,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G123" t="n">
-        <v>2.59070587158203</v>
+        <v>2.59070539474487</v>
       </c>
       <c r="H123" t="n">
         <v>2382000</v>
@@ -3965,7 +3965,7 @@
         <v>4.21600008010864</v>
       </c>
       <c r="G124" t="n">
-        <v>2.63190722465515</v>
+        <v>2.63190698623657</v>
       </c>
       <c r="H124" t="n">
         <v>2474697</v>
@@ -4023,7 +4023,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G126" t="n">
-        <v>2.65937471389771</v>
+        <v>2.65937423706055</v>
       </c>
       <c r="H126" t="n">
         <v>3604147</v>
@@ -4052,7 +4052,7 @@
         <v>4.34800004959106</v>
       </c>
       <c r="G127" t="n">
-        <v>2.71431016921997</v>
+        <v>2.71430993080139</v>
       </c>
       <c r="H127" t="n">
         <v>3044744</v>
@@ -4081,7 +4081,7 @@
         <v>4.35599994659424</v>
       </c>
       <c r="G128" t="n">
-        <v>2.71930384635925</v>
+        <v>2.71930432319641</v>
       </c>
       <c r="H128" t="n">
         <v>2807710</v>
@@ -4139,7 +4139,7 @@
         <v>4.44199991226196</v>
       </c>
       <c r="G130" t="n">
-        <v>2.77299118041992</v>
+        <v>2.77299070358276</v>
       </c>
       <c r="H130" t="n">
         <v>2184181</v>
@@ -4168,7 +4168,7 @@
         <v>4.37599992752075</v>
       </c>
       <c r="G131" t="n">
-        <v>2.73178935050964</v>
+        <v>2.73178911209106</v>
       </c>
       <c r="H131" t="n">
         <v>2678363</v>
@@ -4197,7 +4197,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G132" t="n">
-        <v>2.79047036170959</v>
+        <v>2.79047012329102</v>
       </c>
       <c r="H132" t="n">
         <v>2165558</v>
@@ -4226,7 +4226,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G133" t="n">
-        <v>2.88036465644836</v>
+        <v>2.88036489486694</v>
       </c>
       <c r="H133" t="n">
         <v>4112711</v>
@@ -4284,7 +4284,7 @@
         <v>4.55200004577637</v>
       </c>
       <c r="G135" t="n">
-        <v>2.84166073799133</v>
+        <v>2.84166026115417</v>
       </c>
       <c r="H135" t="n">
         <v>4094332</v>
@@ -4342,7 +4342,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G137" t="n">
-        <v>2.92780947685242</v>
+        <v>2.92780923843384</v>
       </c>
       <c r="H137" t="n">
         <v>3356588</v>
@@ -4371,7 +4371,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G138" t="n">
-        <v>2.9667010307312</v>
+        <v>2.96670150756836</v>
       </c>
       <c r="H138" t="n">
         <v>3149602</v>
@@ -4400,7 +4400,7 @@
         <v>4.64599990844727</v>
       </c>
       <c r="G139" t="n">
-        <v>3.02132725715637</v>
+        <v>3.02132749557495</v>
       </c>
       <c r="H139" t="n">
         <v>2869145</v>
@@ -4545,7 +4545,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G144" t="n">
-        <v>3.00051689147949</v>
+        <v>3.00051712989807</v>
       </c>
       <c r="H144" t="n">
         <v>4692148</v>
@@ -4574,7 +4574,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G145" t="n">
-        <v>3.06424713134766</v>
+        <v>3.06424784660339</v>
       </c>
       <c r="H145" t="n">
         <v>6488921</v>
@@ -4603,7 +4603,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G146" t="n">
-        <v>3.1110692024231</v>
+        <v>3.11106967926025</v>
       </c>
       <c r="H146" t="n">
         <v>5229765</v>
@@ -4632,7 +4632,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G147" t="n">
-        <v>3.1474871635437</v>
+        <v>3.14748692512512</v>
       </c>
       <c r="H147" t="n">
         <v>3102001</v>
@@ -4661,7 +4661,7 @@
         <v>4.75600004196167</v>
       </c>
       <c r="G148" t="n">
-        <v>3.09286093711853</v>
+        <v>3.09286141395569</v>
       </c>
       <c r="H148" t="n">
         <v>2668807</v>
@@ -4690,7 +4690,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G149" t="n">
-        <v>3.10716772079468</v>
+        <v>3.10716795921326</v>
       </c>
       <c r="H149" t="n">
         <v>2358075</v>
@@ -4719,7 +4719,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G150" t="n">
-        <v>3.08505725860596</v>
+        <v>3.08505749702454</v>
       </c>
       <c r="H150" t="n">
         <v>1877264</v>
@@ -4748,7 +4748,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G151" t="n">
-        <v>3.11237049102783</v>
+        <v>3.11237001419067</v>
       </c>
       <c r="H151" t="n">
         <v>4202424</v>
@@ -4777,7 +4777,7 @@
         <v>4.69199991226196</v>
       </c>
       <c r="G152" t="n">
-        <v>3.05124163627625</v>
+        <v>3.05124115943909</v>
       </c>
       <c r="H152" t="n">
         <v>2693512</v>
@@ -4806,7 +4806,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G153" t="n">
-        <v>2.96279978752136</v>
+        <v>2.96280002593994</v>
       </c>
       <c r="H153" t="n">
         <v>3978290</v>
@@ -4835,7 +4835,7 @@
         <v>4.58400011062622</v>
       </c>
       <c r="G154" t="n">
-        <v>2.98100829124451</v>
+        <v>2.98100805282593</v>
       </c>
       <c r="H154" t="n">
         <v>1741047</v>
@@ -4864,7 +4864,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G155" t="n">
-        <v>3.06294703483582</v>
+        <v>3.06294727325439</v>
       </c>
       <c r="H155" t="n">
         <v>4104980</v>
@@ -5038,7 +5038,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>3.0109224319458</v>
+        <v>3.01092267036438</v>
       </c>
       <c r="H161" t="n">
         <v>1440176</v>
@@ -5125,7 +5125,7 @@
         <v>4.47399997711182</v>
       </c>
       <c r="G164" t="n">
-        <v>2.90947437286377</v>
+        <v>2.90947484970093</v>
       </c>
       <c r="H164" t="n">
         <v>2136959</v>
@@ -5154,7 +5154,7 @@
         <v>4.45800018310547</v>
       </c>
       <c r="G165" t="n">
-        <v>2.89907002449036</v>
+        <v>2.89906978607178</v>
       </c>
       <c r="H165" t="n">
         <v>3287025</v>
@@ -5241,7 +5241,7 @@
         <v>4.46999979019165</v>
       </c>
       <c r="G168" t="n">
-        <v>2.90687322616577</v>
+        <v>2.90687298774719</v>
       </c>
       <c r="H168" t="n">
         <v>2203554</v>
@@ -5299,7 +5299,7 @@
         <v>4.38399982452393</v>
       </c>
       <c r="G170" t="n">
-        <v>2.85094666481018</v>
+        <v>2.85094690322876</v>
       </c>
       <c r="H170" t="n">
         <v>1064924</v>
@@ -5473,7 +5473,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G176" t="n">
-        <v>2.95239472389221</v>
+        <v>2.95239496231079</v>
       </c>
       <c r="H176" t="n">
         <v>2291148</v>
@@ -5531,7 +5531,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G178" t="n">
-        <v>2.97580623626709</v>
+        <v>2.97580552101135</v>
       </c>
       <c r="H178" t="n">
         <v>677556</v>
@@ -5618,7 +5618,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>3.04343795776367</v>
+        <v>3.04343771934509</v>
       </c>
       <c r="H181" t="n">
         <v>2063226</v>
@@ -5647,7 +5647,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G182" t="n">
-        <v>3.03693461418152</v>
+        <v>3.0369348526001</v>
       </c>
       <c r="H182" t="n">
         <v>1063094</v>
@@ -5676,7 +5676,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G183" t="n">
-        <v>3.04343795776367</v>
+        <v>3.04343771934509</v>
       </c>
       <c r="H183" t="n">
         <v>1602739</v>
@@ -5705,7 +5705,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G184" t="n">
-        <v>3.0109224319458</v>
+        <v>3.01092267036438</v>
       </c>
       <c r="H184" t="n">
         <v>1202620</v>
@@ -5734,7 +5734,7 @@
         <v>4.60200023651123</v>
       </c>
       <c r="G185" t="n">
-        <v>2.99271368980408</v>
+        <v>2.99271416664124</v>
       </c>
       <c r="H185" t="n">
         <v>1171053</v>
@@ -5763,7 +5763,7 @@
         <v>4.61399984359741</v>
       </c>
       <c r="G186" t="n">
-        <v>3.00051689147949</v>
+        <v>3.00051712989807</v>
       </c>
       <c r="H186" t="n">
         <v>943190</v>
@@ -5821,7 +5821,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G188" t="n">
-        <v>3.02392816543579</v>
+        <v>3.02392888069153</v>
       </c>
       <c r="H188" t="n">
         <v>2591123</v>
@@ -5850,7 +5850,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G189" t="n">
-        <v>3.08765840530396</v>
+        <v>3.08765888214111</v>
       </c>
       <c r="H189" t="n">
         <v>1958346</v>
@@ -5879,7 +5879,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G190" t="n">
-        <v>3.12147426605225</v>
+        <v>3.12147498130798</v>
       </c>
       <c r="H190" t="n">
         <v>2336895</v>
@@ -5908,7 +5908,7 @@
         <v>4.78800010681152</v>
       </c>
       <c r="G191" t="n">
-        <v>3.11367082595825</v>
+        <v>3.11367106437683</v>
       </c>
       <c r="H191" t="n">
         <v>1110454</v>
@@ -5937,7 +5937,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G192" t="n">
-        <v>3.1474871635437</v>
+        <v>3.14748692512512</v>
       </c>
       <c r="H192" t="n">
         <v>1481236</v>
@@ -5995,7 +5995,7 @@
         <v>4.86800003051758</v>
       </c>
       <c r="G194" t="n">
-        <v>3.16569566726685</v>
+        <v>3.16569542884827</v>
       </c>
       <c r="H194" t="n">
         <v>1182663</v>
@@ -6024,7 +6024,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G195" t="n">
-        <v>3.16179347038269</v>
+        <v>3.16179370880127</v>
       </c>
       <c r="H195" t="n">
         <v>1627563</v>
@@ -6053,7 +6053,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G196" t="n">
-        <v>3.14098381996155</v>
+        <v>3.14098334312439</v>
       </c>
       <c r="H196" t="n">
         <v>649672</v>
@@ -6082,7 +6082,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G197" t="n">
-        <v>3.07335209846497</v>
+        <v>3.07335186004639</v>
       </c>
       <c r="H197" t="n">
         <v>1172588</v>
@@ -6140,7 +6140,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G199" t="n">
-        <v>3.15789198875427</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H199" t="n">
         <v>1018979</v>
@@ -6169,7 +6169,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G200" t="n">
-        <v>3.14228367805481</v>
+        <v>3.14228415489197</v>
       </c>
       <c r="H200" t="n">
         <v>1062261</v>
@@ -6198,7 +6198,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G201" t="n">
-        <v>3.15789198875427</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H201" t="n">
         <v>1683946</v>
@@ -6227,7 +6227,7 @@
         <v>4.83199977874756</v>
       </c>
       <c r="G202" t="n">
-        <v>3.14228367805481</v>
+        <v>3.14228415489197</v>
       </c>
       <c r="H202" t="n">
         <v>1384943</v>
@@ -6256,7 +6256,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G203" t="n">
-        <v>3.12407565116882</v>
+        <v>3.12407612800598</v>
       </c>
       <c r="H203" t="n">
         <v>767697</v>
@@ -6285,7 +6285,7 @@
         <v>4.79400014877319</v>
       </c>
       <c r="G204" t="n">
-        <v>3.11757278442383</v>
+        <v>3.11757254600525</v>
       </c>
       <c r="H204" t="n">
         <v>1282121</v>
@@ -6314,7 +6314,7 @@
         <v>4.81400012969971</v>
       </c>
       <c r="G205" t="n">
-        <v>3.1305787563324</v>
+        <v>3.13057923316956</v>
       </c>
       <c r="H205" t="n">
         <v>612186</v>
@@ -6343,7 +6343,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G206" t="n">
-        <v>3.10846900939941</v>
+        <v>3.10846877098083</v>
       </c>
       <c r="H206" t="n">
         <v>937602</v>
@@ -6372,7 +6372,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G207" t="n">
-        <v>3.09546208381653</v>
+        <v>3.09546279907227</v>
       </c>
       <c r="H207" t="n">
         <v>479531</v>
@@ -6401,7 +6401,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G208" t="n">
-        <v>3.08245635032654</v>
+        <v>3.08245611190796</v>
       </c>
       <c r="H208" t="n">
         <v>1265229</v>
@@ -6459,7 +6459,7 @@
         <v>4.74399995803833</v>
       </c>
       <c r="G210" t="n">
-        <v>3.08505725860596</v>
+        <v>3.08505749702454</v>
       </c>
       <c r="H210" t="n">
         <v>1269558</v>
@@ -6488,7 +6488,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G211" t="n">
-        <v>3.12277483940125</v>
+        <v>3.12277507781982</v>
       </c>
       <c r="H211" t="n">
         <v>1352033</v>
@@ -6546,7 +6546,7 @@
         <v>4.70800018310547</v>
       </c>
       <c r="G213" t="n">
-        <v>3.06164646148682</v>
+        <v>3.06164622306824</v>
       </c>
       <c r="H213" t="n">
         <v>1372679</v>
@@ -6575,7 +6575,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G214" t="n">
-        <v>3.09936380386353</v>
+        <v>3.09936356544495</v>
       </c>
       <c r="H214" t="n">
         <v>2019085</v>
@@ -6604,7 +6604,7 @@
         <v>4.78200006484985</v>
       </c>
       <c r="G215" t="n">
-        <v>3.10976910591125</v>
+        <v>3.10976958274841</v>
       </c>
       <c r="H215" t="n">
         <v>2759009</v>
@@ -6633,7 +6633,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G216" t="n">
-        <v>3.09025979042053</v>
+        <v>3.09025955200195</v>
       </c>
       <c r="H216" t="n">
         <v>1133242</v>
@@ -6662,7 +6662,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G217" t="n">
-        <v>3.09936380386353</v>
+        <v>3.09936356544495</v>
       </c>
       <c r="H217" t="n">
         <v>2335811</v>
@@ -6691,7 +6691,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G218" t="n">
-        <v>3.08765840530396</v>
+        <v>3.08765888214111</v>
       </c>
       <c r="H218" t="n">
         <v>1410451</v>
@@ -6720,7 +6720,7 @@
         <v>4.7020001411438</v>
       </c>
       <c r="G219" t="n">
-        <v>3.0577449798584</v>
+        <v>3.05774474143982</v>
       </c>
       <c r="H219" t="n">
         <v>1659908</v>
@@ -6749,7 +6749,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G220" t="n">
-        <v>3.02392816543579</v>
+        <v>3.02392888069153</v>
       </c>
       <c r="H220" t="n">
         <v>1539498</v>
@@ -6836,7 +6836,7 @@
         <v>4.68800020217896</v>
       </c>
       <c r="G223" t="n">
-        <v>3.04864001274109</v>
+        <v>3.04864025115967</v>
       </c>
       <c r="H223" t="n">
         <v>1146321</v>
@@ -6865,7 +6865,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G224" t="n">
-        <v>3.02392816543579</v>
+        <v>3.02392888069153</v>
       </c>
       <c r="H224" t="n">
         <v>1103008</v>
@@ -6923,7 +6923,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G226" t="n">
-        <v>3.07075095176697</v>
+        <v>3.07075047492981</v>
       </c>
       <c r="H226" t="n">
         <v>1748215</v>
@@ -6981,7 +6981,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G228" t="n">
-        <v>3.12797784805298</v>
+        <v>3.1279776096344</v>
       </c>
       <c r="H228" t="n">
         <v>1859111</v>
@@ -7010,7 +7010,7 @@
         <v>4.77400016784668</v>
       </c>
       <c r="G229" t="n">
-        <v>3.10456681251526</v>
+        <v>3.10456657409668</v>
       </c>
       <c r="H229" t="n">
         <v>2084802</v>
@@ -7039,7 +7039,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G230" t="n">
-        <v>3.09546208381653</v>
+        <v>3.09546279907227</v>
       </c>
       <c r="H230" t="n">
         <v>1964842</v>
@@ -7068,7 +7068,7 @@
         <v>4.75</v>
       </c>
       <c r="G231" t="n">
-        <v>3.08895874023438</v>
+        <v>3.08895897865295</v>
       </c>
       <c r="H231" t="n">
         <v>1731154</v>
@@ -7126,7 +7126,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G233" t="n">
-        <v>3.06944990158081</v>
+        <v>3.06945013999939</v>
       </c>
       <c r="H233" t="n">
         <v>2513489</v>
@@ -7155,7 +7155,7 @@
         <v>4.63199996948242</v>
       </c>
       <c r="G234" t="n">
-        <v>3.01222276687622</v>
+        <v>3.01222324371338</v>
       </c>
       <c r="H234" t="n">
         <v>2554522</v>
@@ -7184,7 +7184,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G235" t="n">
-        <v>3.03303289413452</v>
+        <v>3.03303265571594</v>
       </c>
       <c r="H235" t="n">
         <v>2592607</v>
@@ -7213,7 +7213,7 @@
         <v>4.56599998474121</v>
       </c>
       <c r="G236" t="n">
-        <v>2.96930289268494</v>
+        <v>2.96930265426636</v>
       </c>
       <c r="H236" t="n">
         <v>2237180</v>
@@ -7271,7 +7271,7 @@
         <v>4.66200017929077</v>
       </c>
       <c r="G238" t="n">
-        <v>3.03173208236694</v>
+        <v>3.0317325592041</v>
       </c>
       <c r="H238" t="n">
         <v>1498059</v>
@@ -7300,7 +7300,7 @@
         <v>4.73600006103516</v>
       </c>
       <c r="G239" t="n">
-        <v>3.07985472679138</v>
+        <v>3.07985496520996</v>
       </c>
       <c r="H239" t="n">
         <v>2753804</v>
@@ -7329,7 +7329,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G240" t="n">
-        <v>3.09156036376953</v>
+        <v>3.09156060218811</v>
       </c>
       <c r="H240" t="n">
         <v>3955428</v>
@@ -7387,7 +7387,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G242" t="n">
-        <v>3.07335209846497</v>
+        <v>3.07335186004639</v>
       </c>
       <c r="H242" t="n">
         <v>1121811</v>
@@ -7445,7 +7445,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G244" t="n">
-        <v>3.09546208381653</v>
+        <v>3.09546279907227</v>
       </c>
       <c r="H244" t="n">
         <v>906408</v>
@@ -7474,7 +7474,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G245" t="n">
-        <v>3.11497163772583</v>
+        <v>3.11497187614441</v>
       </c>
       <c r="H245" t="n">
         <v>1121552</v>
@@ -7503,7 +7503,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G246" t="n">
-        <v>3.14098381996155</v>
+        <v>3.14098334312439</v>
       </c>
       <c r="H246" t="n">
         <v>1767243</v>
@@ -7561,7 +7561,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G248" t="n">
-        <v>3.34257888793945</v>
+        <v>3.34257912635803</v>
       </c>
       <c r="H248" t="n">
         <v>8302472</v>
@@ -7590,7 +7590,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G249" t="n">
-        <v>3.24893450737</v>
+        <v>3.24893474578857</v>
       </c>
       <c r="H249" t="n">
         <v>3278337</v>
@@ -7619,7 +7619,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G250" t="n">
-        <v>3.31656670570374</v>
+        <v>3.31656622886658</v>
       </c>
       <c r="H250" t="n">
         <v>2795501</v>
@@ -7648,7 +7648,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G251" t="n">
-        <v>3.35558557510376</v>
+        <v>3.35558533668518</v>
       </c>
       <c r="H251" t="n">
         <v>3184591</v>
@@ -7677,7 +7677,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G252" t="n">
-        <v>3.27104544639587</v>
+        <v>3.27104520797729</v>
       </c>
       <c r="H252" t="n">
         <v>6428942</v>
@@ -7706,7 +7706,7 @@
         <v>5.0149998664856</v>
       </c>
       <c r="G253" t="n">
-        <v>3.26129078865051</v>
+        <v>3.26129055023193</v>
       </c>
       <c r="H253" t="n">
         <v>1973997</v>
@@ -7735,7 +7735,7 @@
         <v>5.07499980926514</v>
       </c>
       <c r="G254" t="n">
-        <v>3.30030918121338</v>
+        <v>3.3003089427948</v>
       </c>
       <c r="H254" t="n">
         <v>3004311</v>
@@ -7764,7 +7764,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G255" t="n">
-        <v>3.28730273246765</v>
+        <v>3.28730320930481</v>
       </c>
       <c r="H255" t="n">
         <v>1842881</v>
@@ -7793,7 +7793,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G256" t="n">
-        <v>3.28080010414124</v>
+        <v>3.28079962730408</v>
       </c>
       <c r="H256" t="n">
         <v>1188363</v>
@@ -7851,7 +7851,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G258" t="n">
-        <v>3.31981801986694</v>
+        <v>3.31981825828552</v>
       </c>
       <c r="H258" t="n">
         <v>2955797</v>
@@ -7909,7 +7909,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>3.31656670570374</v>
+        <v>3.31656622886658</v>
       </c>
       <c r="H260" t="n">
         <v>2506308</v>
@@ -7938,7 +7938,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G261" t="n">
-        <v>3.35233402252197</v>
+        <v>3.35233378410339</v>
       </c>
       <c r="H261" t="n">
         <v>2738338</v>
@@ -7967,7 +7967,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G262" t="n">
-        <v>3.35233402252197</v>
+        <v>3.35233378410339</v>
       </c>
       <c r="H262" t="n">
         <v>2922943</v>
@@ -8025,7 +8025,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G264" t="n">
-        <v>3.36208844184875</v>
+        <v>3.36208820343018</v>
       </c>
       <c r="H264" t="n">
         <v>3024002</v>
@@ -8054,7 +8054,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G265" t="n">
-        <v>3.39460372924805</v>
+        <v>3.39460325241089</v>
       </c>
       <c r="H265" t="n">
         <v>2474383</v>
@@ -8112,7 +8112,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G267" t="n">
-        <v>3.47914385795593</v>
+        <v>3.47914361953735</v>
       </c>
       <c r="H267" t="n">
         <v>2730053</v>
@@ -8141,7 +8141,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>3.44662809371948</v>
+        <v>3.44662880897522</v>
       </c>
       <c r="H268" t="n">
         <v>2838765</v>
@@ -8170,7 +8170,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G269" t="n">
-        <v>3.35558557510376</v>
+        <v>3.35558533668518</v>
       </c>
       <c r="H269" t="n">
         <v>2919056</v>
@@ -8199,7 +8199,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G270" t="n">
-        <v>3.38159775733948</v>
+        <v>3.3815975189209</v>
       </c>
       <c r="H270" t="n">
         <v>1740172</v>
@@ -8257,7 +8257,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G272" t="n">
-        <v>3.31656670570374</v>
+        <v>3.31656622886658</v>
       </c>
       <c r="H272" t="n">
         <v>1936166</v>
@@ -8286,7 +8286,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G273" t="n">
-        <v>3.40110659599304</v>
+        <v>3.4011070728302</v>
       </c>
       <c r="H273" t="n">
         <v>2058521</v>
@@ -8315,7 +8315,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G274" t="n">
-        <v>3.39460372924805</v>
+        <v>3.39460325241089</v>
       </c>
       <c r="H274" t="n">
         <v>1754265</v>
@@ -8344,7 +8344,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G275" t="n">
-        <v>3.45963430404663</v>
+        <v>3.45963478088379</v>
       </c>
       <c r="H275" t="n">
         <v>3167757</v>
@@ -8373,7 +8373,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G276" t="n">
-        <v>3.3750946521759</v>
+        <v>3.37509441375732</v>
       </c>
       <c r="H276" t="n">
         <v>3443370</v>
@@ -8402,7 +8402,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G277" t="n">
-        <v>3.39460372924805</v>
+        <v>3.39460325241089</v>
       </c>
       <c r="H277" t="n">
         <v>1741298</v>
@@ -8431,7 +8431,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G278" t="n">
-        <v>3.43687343597412</v>
+        <v>3.4368736743927</v>
       </c>
       <c r="H278" t="n">
         <v>4607010</v>
@@ -8460,7 +8460,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G279" t="n">
-        <v>3.44987964630127</v>
+        <v>3.44987988471985</v>
       </c>
       <c r="H279" t="n">
         <v>3731719</v>
@@ -8489,7 +8489,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G280" t="n">
-        <v>3.44012522697449</v>
+        <v>3.44012498855591</v>
       </c>
       <c r="H280" t="n">
         <v>5567621</v>
@@ -8518,7 +8518,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G281" t="n">
-        <v>3.46613693237305</v>
+        <v>3.46613669395447</v>
       </c>
       <c r="H281" t="n">
         <v>3172733</v>
@@ -8547,7 +8547,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G282" t="n">
-        <v>3.4433765411377</v>
+        <v>3.44337630271912</v>
       </c>
       <c r="H282" t="n">
         <v>1589890</v>
@@ -8576,7 +8576,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G283" t="n">
-        <v>3.43687343597412</v>
+        <v>3.4368736743927</v>
       </c>
       <c r="H283" t="n">
         <v>1954309</v>
@@ -8605,7 +8605,7 @@
         <v>5.25</v>
       </c>
       <c r="G284" t="n">
-        <v>3.41411304473877</v>
+        <v>3.41411256790161</v>
       </c>
       <c r="H284" t="n">
         <v>2645545</v>
@@ -8634,7 +8634,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G285" t="n">
-        <v>3.38484859466553</v>
+        <v>3.38484930992126</v>
       </c>
       <c r="H285" t="n">
         <v>1879710</v>
@@ -8663,7 +8663,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G286" t="n">
-        <v>3.38484859466553</v>
+        <v>3.38484930992126</v>
       </c>
       <c r="H286" t="n">
         <v>3135720</v>
@@ -8692,7 +8692,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G287" t="n">
-        <v>3.40110659599304</v>
+        <v>3.4011070728302</v>
       </c>
       <c r="H287" t="n">
         <v>1466206</v>
@@ -8721,7 +8721,7 @@
         <v>5.15999984741211</v>
       </c>
       <c r="G288" t="n">
-        <v>3.35558557510376</v>
+        <v>3.35558533668518</v>
       </c>
       <c r="H288" t="n">
         <v>2485222</v>
@@ -8750,7 +8750,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G289" t="n">
-        <v>3.3750946521759</v>
+        <v>3.37509441375732</v>
       </c>
       <c r="H289" t="n">
         <v>2203324</v>
@@ -8895,7 +8895,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G294" t="n">
-        <v>3.31006383895874</v>
+        <v>3.31006407737732</v>
       </c>
       <c r="H294" t="n">
         <v>1327314</v>
@@ -8924,7 +8924,7 @@
         <v>5</v>
       </c>
       <c r="G295" t="n">
-        <v>3.25153613090515</v>
+        <v>3.25153589248657</v>
       </c>
       <c r="H295" t="n">
         <v>2285101</v>
@@ -9011,7 +9011,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G298" t="n">
-        <v>3.27104544639587</v>
+        <v>3.27104520797729</v>
       </c>
       <c r="H298" t="n">
         <v>1818628</v>
@@ -9040,7 +9040,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G299" t="n">
-        <v>3.26454210281372</v>
+        <v>3.2645423412323</v>
       </c>
       <c r="H299" t="n">
         <v>2225454</v>
@@ -9069,7 +9069,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G300" t="n">
-        <v>3.24503254890442</v>
+        <v>3.245032787323</v>
       </c>
       <c r="H300" t="n">
         <v>2694727</v>
@@ -9098,7 +9098,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G301" t="n">
-        <v>3.18650579452515</v>
+        <v>3.18650555610657</v>
       </c>
       <c r="H301" t="n">
         <v>3560333</v>
@@ -9127,7 +9127,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G302" t="n">
-        <v>3.16699600219727</v>
+        <v>3.16699624061584</v>
       </c>
       <c r="H302" t="n">
         <v>2028450</v>
@@ -9156,7 +9156,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G303" t="n">
-        <v>3.16959714889526</v>
+        <v>3.16959691047668</v>
       </c>
       <c r="H303" t="n">
         <v>1765252</v>
@@ -9185,7 +9185,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G304" t="n">
-        <v>3.16959714889526</v>
+        <v>3.16959691047668</v>
       </c>
       <c r="H304" t="n">
         <v>1332188</v>
@@ -9214,7 +9214,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G305" t="n">
-        <v>3.20731496810913</v>
+        <v>3.20731520652771</v>
       </c>
       <c r="H305" t="n">
         <v>2083690</v>
@@ -9301,7 +9301,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G308" t="n">
-        <v>3.22942566871643</v>
+        <v>3.22942614555359</v>
       </c>
       <c r="H308" t="n">
         <v>1536056</v>
@@ -9330,7 +9330,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G309" t="n">
-        <v>3.24503254890442</v>
+        <v>3.245032787323</v>
       </c>
       <c r="H309" t="n">
         <v>1332232</v>
@@ -9359,7 +9359,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G310" t="n">
-        <v>3.27104544639587</v>
+        <v>3.27104520797729</v>
       </c>
       <c r="H310" t="n">
         <v>1565332</v>
@@ -9388,7 +9388,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G311" t="n">
-        <v>3.22942566871643</v>
+        <v>3.22942614555359</v>
       </c>
       <c r="H311" t="n">
         <v>1793873</v>
@@ -9417,7 +9417,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G312" t="n">
-        <v>3.20081186294556</v>
+        <v>3.20081210136414</v>
       </c>
       <c r="H312" t="n">
         <v>1847100</v>
@@ -9446,7 +9446,7 @@
         <v>4.95599985122681</v>
       </c>
       <c r="G313" t="n">
-        <v>3.22292232513428</v>
+        <v>3.2229220867157</v>
       </c>
       <c r="H313" t="n">
         <v>1435060</v>
@@ -9475,7 +9475,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>3.18650579452515</v>
+        <v>3.18650555610657</v>
       </c>
       <c r="H314" t="n">
         <v>2572604</v>
@@ -9504,7 +9504,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G315" t="n">
-        <v>3.16699600219727</v>
+        <v>3.16699624061584</v>
       </c>
       <c r="H315" t="n">
         <v>2426852</v>
@@ -9533,7 +9533,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G316" t="n">
-        <v>3.23462796211243</v>
+        <v>3.23462843894958</v>
       </c>
       <c r="H316" t="n">
         <v>3281061</v>
@@ -9562,7 +9562,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G317" t="n">
-        <v>3.2177197933197</v>
+        <v>3.21772003173828</v>
       </c>
       <c r="H317" t="n">
         <v>2118644</v>
@@ -9591,7 +9591,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G318" t="n">
-        <v>3.1474871635437</v>
+        <v>3.14748692512512</v>
       </c>
       <c r="H318" t="n">
         <v>3105576</v>
@@ -9620,7 +9620,7 @@
         <v>4.78599977493286</v>
       </c>
       <c r="G319" t="n">
-        <v>3.11237049102783</v>
+        <v>3.11237001419067</v>
       </c>
       <c r="H319" t="n">
         <v>3378437</v>
@@ -9649,7 +9649,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G320" t="n">
-        <v>2.98816156387329</v>
+        <v>2.98816132545471</v>
       </c>
       <c r="H320" t="n">
         <v>3568087</v>
@@ -9678,7 +9678,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G321" t="n">
-        <v>3.02913069725037</v>
+        <v>3.0291314125061</v>
       </c>
       <c r="H321" t="n">
         <v>2708506</v>
@@ -9765,7 +9765,7 @@
         <v>4.46400022506714</v>
       </c>
       <c r="G324" t="n">
-        <v>2.90297174453735</v>
+        <v>2.9029712677002</v>
       </c>
       <c r="H324" t="n">
         <v>1575080</v>
@@ -9823,7 +9823,7 @@
         <v>4.44899988174438</v>
       </c>
       <c r="G326" t="n">
-        <v>2.89321637153625</v>
+        <v>2.89321660995483</v>
       </c>
       <c r="H326" t="n">
         <v>2452173</v>
@@ -9881,7 +9881,7 @@
         <v>4.4850001335144</v>
       </c>
       <c r="G328" t="n">
-        <v>2.91662740707397</v>
+        <v>2.91662788391113</v>
       </c>
       <c r="H328" t="n">
         <v>1203275</v>
@@ -9939,7 +9939,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>2.83533978462219</v>
+        <v>2.83533954620361</v>
       </c>
       <c r="H330" t="n">
         <v>1994170</v>
@@ -9968,7 +9968,7 @@
         <v>4.38500022888184</v>
       </c>
       <c r="G331" t="n">
-        <v>2.85159730911255</v>
+        <v>2.85159707069397</v>
       </c>
       <c r="H331" t="n">
         <v>1725510</v>
@@ -10026,7 +10026,7 @@
         <v>4.58799982070923</v>
       </c>
       <c r="G333" t="n">
-        <v>2.98360919952393</v>
+        <v>2.9836094379425</v>
       </c>
       <c r="H333" t="n">
         <v>2476508</v>
@@ -10055,7 +10055,7 @@
         <v>4.51700019836426</v>
       </c>
       <c r="G334" t="n">
-        <v>2.93743824958801</v>
+        <v>2.93743753433228</v>
       </c>
       <c r="H334" t="n">
         <v>1748762</v>
@@ -10113,7 +10113,7 @@
         <v>4.41699981689453</v>
       </c>
       <c r="G336" t="n">
-        <v>2.87240672111511</v>
+        <v>2.87240695953369</v>
       </c>
       <c r="H336" t="n">
         <v>2115719</v>
@@ -10142,7 +10142,7 @@
         <v>4.36700010299683</v>
       </c>
       <c r="G337" t="n">
-        <v>2.83989143371582</v>
+        <v>2.83989191055298</v>
       </c>
       <c r="H337" t="n">
         <v>2476410</v>
@@ -10200,7 +10200,7 @@
         <v>4.30600023269653</v>
       </c>
       <c r="G339" t="n">
-        <v>2.80022311210632</v>
+        <v>2.80022287368774</v>
       </c>
       <c r="H339" t="n">
         <v>2824441</v>
@@ -10229,7 +10229,7 @@
         <v>4.43599987030029</v>
       </c>
       <c r="G340" t="n">
-        <v>2.88476252555847</v>
+        <v>2.88476276397705</v>
       </c>
       <c r="H340" t="n">
         <v>2977096</v>
@@ -10287,7 +10287,7 @@
         <v>4.6269998550415</v>
       </c>
       <c r="G342" t="n">
-        <v>3.00897121429443</v>
+        <v>3.00897097587585</v>
       </c>
       <c r="H342" t="n">
         <v>2893991</v>
@@ -10345,7 +10345,7 @@
         <v>4.65799999237061</v>
       </c>
       <c r="G344" t="n">
-        <v>3.02913069725037</v>
+        <v>3.0291314125061</v>
       </c>
       <c r="H344" t="n">
         <v>3824795</v>
@@ -10374,7 +10374,7 @@
         <v>4.76300001144409</v>
       </c>
       <c r="G345" t="n">
-        <v>3.09741306304932</v>
+        <v>3.09741353988647</v>
       </c>
       <c r="H345" t="n">
         <v>5092398</v>
@@ -10403,7 +10403,7 @@
         <v>4.75099992752075</v>
       </c>
       <c r="G346" t="n">
-        <v>3.08960914611816</v>
+        <v>3.08960890769958</v>
       </c>
       <c r="H346" t="n">
         <v>5127661</v>
@@ -10432,7 +10432,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>3.07595324516296</v>
+        <v>3.07595300674438</v>
       </c>
       <c r="H347" t="n">
         <v>2942590</v>
@@ -10461,7 +10461,7 @@
         <v>4.70100021362305</v>
       </c>
       <c r="G348" t="n">
-        <v>3.05709385871887</v>
+        <v>3.05709433555603</v>
       </c>
       <c r="H348" t="n">
         <v>7156105</v>
@@ -10490,7 +10490,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G349" t="n">
-        <v>3.11497163772583</v>
+        <v>3.11497187614441</v>
       </c>
       <c r="H349" t="n">
         <v>3060245</v>
@@ -10519,7 +10519,7 @@
         <v>4.81899976730347</v>
       </c>
       <c r="G350" t="n">
-        <v>3.13383030891418</v>
+        <v>3.13383007049561</v>
       </c>
       <c r="H350" t="n">
         <v>1614575</v>
@@ -10577,7 +10577,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G352" t="n">
-        <v>3.06944990158081</v>
+        <v>3.06945013999939</v>
       </c>
       <c r="H352" t="n">
         <v>2541060</v>
@@ -10606,7 +10606,7 @@
         <v>4.76599979400635</v>
       </c>
       <c r="G353" t="n">
-        <v>3.09936380386353</v>
+        <v>3.09936356544495</v>
       </c>
       <c r="H353" t="n">
         <v>1982170</v>
@@ -10635,7 +10635,7 @@
         <v>4.71700000762939</v>
       </c>
       <c r="G354" t="n">
-        <v>3.06749939918518</v>
+        <v>3.0674991607666</v>
       </c>
       <c r="H354" t="n">
         <v>2504013</v>
@@ -10664,7 +10664,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G355" t="n">
-        <v>3.11497163772583</v>
+        <v>3.11497187614441</v>
       </c>
       <c r="H355" t="n">
         <v>1626051</v>
@@ -10693,7 +10693,7 @@
         <v>4.87400007247925</v>
       </c>
       <c r="G356" t="n">
-        <v>3.16959714889526</v>
+        <v>3.16959691047668</v>
       </c>
       <c r="H356" t="n">
         <v>2821934</v>
@@ -10722,7 +10722,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G357" t="n">
-        <v>3.15789198875427</v>
+        <v>3.15789175033569</v>
       </c>
       <c r="H357" t="n">
         <v>1742932</v>
@@ -10809,7 +10809,7 @@
         <v>4.9520001411438</v>
       </c>
       <c r="G360" t="n">
-        <v>3.22032141685486</v>
+        <v>3.22032117843628</v>
       </c>
       <c r="H360" t="n">
         <v>2518130</v>
@@ -10838,7 +10838,7 @@
         <v>5.00400018692017</v>
       </c>
       <c r="G361" t="n">
-        <v>3.25413751602173</v>
+        <v>3.25413703918457</v>
       </c>
       <c r="H361" t="n">
         <v>1842202</v>
@@ -10867,7 +10867,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G362" t="n">
-        <v>3.31006383895874</v>
+        <v>3.31006407737732</v>
       </c>
       <c r="H362" t="n">
         <v>3413196</v>
@@ -10896,7 +10896,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G363" t="n">
-        <v>3.33087348937988</v>
+        <v>3.33087396621704</v>
       </c>
       <c r="H363" t="n">
         <v>2412747</v>
@@ -10954,7 +10954,7 @@
         <v>5.12599992752075</v>
       </c>
       <c r="G365" t="n">
-        <v>3.33347487449646</v>
+        <v>3.33347511291504</v>
       </c>
       <c r="H365" t="n">
         <v>1692898</v>
@@ -10983,7 +10983,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G366" t="n">
-        <v>3.29055380821228</v>
+        <v>3.29055428504944</v>
       </c>
       <c r="H366" t="n">
         <v>1867370</v>
@@ -11041,7 +11041,7 @@
         <v>5.15199995040894</v>
       </c>
       <c r="G368" t="n">
-        <v>3.35038304328918</v>
+        <v>3.35038280487061</v>
       </c>
       <c r="H368" t="n">
         <v>4112376</v>
@@ -11070,7 +11070,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G369" t="n">
-        <v>3.37769532203674</v>
+        <v>3.37769556045532</v>
       </c>
       <c r="H369" t="n">
         <v>1844080</v>
@@ -11099,7 +11099,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G370" t="n">
-        <v>3.32957291603088</v>
+        <v>3.3295726776123</v>
       </c>
       <c r="H370" t="n">
         <v>2607705</v>
@@ -11128,7 +11128,7 @@
         <v>5.17399978637695</v>
       </c>
       <c r="G371" t="n">
-        <v>3.36468935012817</v>
+        <v>3.36468911170959</v>
       </c>
       <c r="H371" t="n">
         <v>3253120</v>
@@ -11157,7 +11157,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G372" t="n">
-        <v>3.31136465072632</v>
+        <v>3.311363697052</v>
       </c>
       <c r="H372" t="n">
         <v>2889659</v>
@@ -11186,7 +11186,7 @@
         <v>5.19199991226196</v>
       </c>
       <c r="G373" t="n">
-        <v>3.37639498710632</v>
+        <v>3.37639474868774</v>
       </c>
       <c r="H373" t="n">
         <v>3697566</v>
@@ -11215,7 +11215,7 @@
         <v>5.18200016021729</v>
       </c>
       <c r="G374" t="n">
-        <v>3.36989212036133</v>
+        <v>3.36989188194275</v>
       </c>
       <c r="H374" t="n">
         <v>1389515</v>
@@ -11244,7 +11244,7 @@
         <v>5.26399993896484</v>
       </c>
       <c r="G375" t="n">
-        <v>3.42321681976318</v>
+        <v>3.42321705818176</v>
       </c>
       <c r="H375" t="n">
         <v>1573143</v>
@@ -11273,7 +11273,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G376" t="n">
-        <v>3.47264051437378</v>
+        <v>3.47264075279236</v>
       </c>
       <c r="H376" t="n">
         <v>1857454</v>
@@ -11302,7 +11302,7 @@
         <v>5.36600017547607</v>
       </c>
       <c r="G377" t="n">
-        <v>3.4895486831665</v>
+        <v>3.48954844474792</v>
       </c>
       <c r="H377" t="n">
         <v>2580956</v>
@@ -11331,7 +11331,7 @@
         <v>5.30600023269653</v>
       </c>
       <c r="G378" t="n">
-        <v>3.45052981376648</v>
+        <v>3.45053029060364</v>
       </c>
       <c r="H378" t="n">
         <v>2351824</v>
@@ -11360,7 +11360,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G379" t="n">
-        <v>3.44012522697449</v>
+        <v>3.44012498855591</v>
       </c>
       <c r="H379" t="n">
         <v>1895196</v>
@@ -11418,7 +11418,7 @@
         <v>5.33799982070923</v>
       </c>
       <c r="G381" t="n">
-        <v>3.47134017944336</v>
+        <v>3.47133946418762</v>
       </c>
       <c r="H381" t="n">
         <v>1497682</v>
@@ -11447,7 +11447,7 @@
         <v>5.14400005340576</v>
       </c>
       <c r="G382" t="n">
-        <v>3.34518027305603</v>
+        <v>3.34518003463745</v>
       </c>
       <c r="H382" t="n">
         <v>7376141</v>
@@ -11476,7 +11476,7 @@
         <v>5.08799982070923</v>
       </c>
       <c r="G383" t="n">
-        <v>3.30876302719116</v>
+        <v>3.30876278877258</v>
       </c>
       <c r="H383" t="n">
         <v>5272263</v>
@@ -11534,7 +11534,7 @@
         <v>5.08599996566772</v>
       </c>
       <c r="G385" t="n">
-        <v>3.30746269226074</v>
+        <v>3.30746245384216</v>
       </c>
       <c r="H385" t="n">
         <v>1760932</v>
@@ -11592,7 +11592,7 @@
         <v>5.08599996566772</v>
       </c>
       <c r="G387" t="n">
-        <v>3.30746269226074</v>
+        <v>3.30746245384216</v>
       </c>
       <c r="H387" t="n">
         <v>2188502</v>
@@ -11650,7 +11650,7 @@
         <v>5</v>
       </c>
       <c r="G389" t="n">
-        <v>3.25153613090515</v>
+        <v>3.25153589248657</v>
       </c>
       <c r="H389" t="n">
         <v>2087897</v>
@@ -11679,7 +11679,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G390" t="n">
-        <v>3.24828410148621</v>
+        <v>3.24828457832336</v>
       </c>
       <c r="H390" t="n">
         <v>4048165</v>
@@ -11708,7 +11708,7 @@
         <v>4.80200004577637</v>
       </c>
       <c r="G391" t="n">
-        <v>3.24985408782959</v>
+        <v>3.24985384941101</v>
       </c>
       <c r="H391" t="n">
         <v>2600372</v>
@@ -11737,7 +11737,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G392" t="n">
-        <v>3.30670285224915</v>
+        <v>3.30670309066772</v>
       </c>
       <c r="H392" t="n">
         <v>2056574</v>
@@ -11766,7 +11766,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G393" t="n">
-        <v>3.31347012519836</v>
+        <v>3.31347060203552</v>
       </c>
       <c r="H393" t="n">
         <v>2725352</v>
@@ -11795,7 +11795,7 @@
         <v>4.75699996948242</v>
       </c>
       <c r="G394" t="n">
-        <v>3.21939921379089</v>
+        <v>3.21939945220947</v>
       </c>
       <c r="H394" t="n">
         <v>2650692</v>
@@ -11853,7 +11853,7 @@
         <v>4.57499980926514</v>
       </c>
       <c r="G396" t="n">
-        <v>3.09622669219971</v>
+        <v>3.09622693061829</v>
       </c>
       <c r="H396" t="n">
         <v>2935650</v>
@@ -11911,7 +11911,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G398" t="n">
-        <v>3.03193378448486</v>
+        <v>3.03193354606628</v>
       </c>
       <c r="H398" t="n">
         <v>9267016</v>
@@ -11969,7 +11969,7 @@
         <v>4.51200008392334</v>
       </c>
       <c r="G400" t="n">
-        <v>3.05359029769897</v>
+        <v>3.05359053611755</v>
       </c>
       <c r="H400" t="n">
         <v>3701214</v>
@@ -11998,7 +11998,7 @@
         <v>4.63800001144409</v>
       </c>
       <c r="G401" t="n">
-        <v>3.13886332511902</v>
+        <v>3.13886380195618</v>
       </c>
       <c r="H401" t="n">
         <v>4000775</v>
@@ -12027,7 +12027,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G402" t="n">
-        <v>3.11856007575989</v>
+        <v>3.11856055259705</v>
       </c>
       <c r="H402" t="n">
         <v>3095485</v>
@@ -12056,7 +12056,7 @@
         <v>4.5770001411438</v>
       </c>
       <c r="G403" t="n">
-        <v>3.09758043289185</v>
+        <v>3.09758067131042</v>
       </c>
       <c r="H403" t="n">
         <v>2159901</v>
@@ -12085,7 +12085,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G404" t="n">
-        <v>3.0996105670929</v>
+        <v>3.09961080551147</v>
       </c>
       <c r="H404" t="n">
         <v>1736977</v>
@@ -12114,7 +12114,7 @@
         <v>4.52899980545044</v>
       </c>
       <c r="G405" t="n">
-        <v>3.06509566307068</v>
+        <v>3.0650954246521</v>
       </c>
       <c r="H405" t="n">
         <v>2327673</v>
@@ -12143,7 +12143,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G406" t="n">
-        <v>3.19841909408569</v>
+        <v>3.19841933250427</v>
       </c>
       <c r="H406" t="n">
         <v>2827673</v>
@@ -12172,7 +12172,7 @@
         <v>4.86299991607666</v>
       </c>
       <c r="G407" t="n">
-        <v>3.29113721847534</v>
+        <v>3.29113674163818</v>
       </c>
       <c r="H407" t="n">
         <v>4461113</v>
@@ -12201,7 +12201,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G408" t="n">
-        <v>3.24579334259033</v>
+        <v>3.24579310417175</v>
       </c>
       <c r="H408" t="n">
         <v>3902612</v>
@@ -12317,7 +12317,7 @@
         <v>4.82299995422363</v>
       </c>
       <c r="G412" t="n">
-        <v>3.26406621932983</v>
+        <v>3.26406598091125</v>
       </c>
       <c r="H412" t="n">
         <v>2369613</v>
@@ -12346,7 +12346,7 @@
         <v>4.89900016784668</v>
       </c>
       <c r="G413" t="n">
-        <v>3.31550073623657</v>
+        <v>3.31550049781799</v>
       </c>
       <c r="H413" t="n">
         <v>2936084</v>
@@ -12375,7 +12375,7 @@
         <v>4.72100019454956</v>
       </c>
       <c r="G414" t="n">
-        <v>3.19503545761108</v>
+        <v>3.19503569602966</v>
       </c>
       <c r="H414" t="n">
         <v>2771532</v>
@@ -12433,7 +12433,7 @@
         <v>4.66800022125244</v>
       </c>
       <c r="G416" t="n">
-        <v>3.15916705131531</v>
+        <v>3.15916728973389</v>
       </c>
       <c r="H416" t="n">
         <v>2121412</v>
@@ -12549,7 +12549,7 @@
         <v>4.72200012207031</v>
       </c>
       <c r="G420" t="n">
-        <v>3.19571232795715</v>
+        <v>3.19571208953857</v>
       </c>
       <c r="H420" t="n">
         <v>2199299</v>
@@ -12607,7 +12607,7 @@
         <v>4.7480001449585</v>
       </c>
       <c r="G422" t="n">
-        <v>3.21330809593201</v>
+        <v>3.21330857276917</v>
       </c>
       <c r="H422" t="n">
         <v>1706417</v>
@@ -12636,7 +12636,7 @@
         <v>4.74200010299683</v>
       </c>
       <c r="G423" t="n">
-        <v>3.20924806594849</v>
+        <v>3.20924758911133</v>
       </c>
       <c r="H423" t="n">
         <v>967378</v>
@@ -12665,7 +12665,7 @@
         <v>4.81099987030029</v>
       </c>
       <c r="G424" t="n">
-        <v>3.25594472885132</v>
+        <v>3.2559449672699</v>
       </c>
       <c r="H424" t="n">
         <v>1826570</v>
@@ -12694,7 +12694,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G425" t="n">
-        <v>3.27286386489868</v>
+        <v>3.27286410331726</v>
       </c>
       <c r="H425" t="n">
         <v>2008386</v>
@@ -12723,7 +12723,7 @@
         <v>4.77799987792969</v>
       </c>
       <c r="G426" t="n">
-        <v>3.23361110687256</v>
+        <v>3.23361134529114</v>
       </c>
       <c r="H426" t="n">
         <v>1009632</v>
@@ -12752,7 +12752,7 @@
         <v>4.72599983215332</v>
       </c>
       <c r="G427" t="n">
-        <v>3.19841909408569</v>
+        <v>3.19841933250427</v>
       </c>
       <c r="H427" t="n">
         <v>1835351</v>
@@ -12781,7 +12781,7 @@
         <v>4.7039999961853</v>
       </c>
       <c r="G428" t="n">
-        <v>3.18353056907654</v>
+        <v>3.18353009223938</v>
       </c>
       <c r="H428" t="n">
         <v>1407066</v>
@@ -12810,7 +12810,7 @@
         <v>4.74700021743774</v>
       </c>
       <c r="G429" t="n">
-        <v>3.2126317024231</v>
+        <v>3.21263217926025</v>
       </c>
       <c r="H429" t="n">
         <v>1510889</v>
@@ -12839,7 +12839,7 @@
         <v>4.72800016403198</v>
       </c>
       <c r="G430" t="n">
-        <v>3.19977331161499</v>
+        <v>3.19977307319641</v>
       </c>
       <c r="H430" t="n">
         <v>1634802</v>
@@ -12868,7 +12868,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G431" t="n">
-        <v>3.25526809692383</v>
+        <v>3.25526785850525</v>
       </c>
       <c r="H431" t="n">
         <v>2483950</v>
@@ -12897,7 +12897,7 @@
         <v>4.88399982452393</v>
       </c>
       <c r="G432" t="n">
-        <v>3.30534863471985</v>
+        <v>3.30534887313843</v>
       </c>
       <c r="H432" t="n">
         <v>1839177</v>
@@ -12926,7 +12926,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G433" t="n">
-        <v>3.30128836631775</v>
+        <v>3.30128860473633</v>
       </c>
       <c r="H433" t="n">
         <v>1687533</v>
@@ -12955,7 +12955,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G434" t="n">
-        <v>3.30128836631775</v>
+        <v>3.30128860473633</v>
       </c>
       <c r="H434" t="n">
         <v>1560000</v>
@@ -12984,7 +12984,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G435" t="n">
-        <v>3.29587435722351</v>
+        <v>3.29587459564209</v>
       </c>
       <c r="H435" t="n">
         <v>1955017</v>
@@ -13013,7 +13013,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G436" t="n">
-        <v>3.30399537086487</v>
+        <v>3.30399513244629</v>
       </c>
       <c r="H436" t="n">
         <v>1511295</v>
@@ -13042,7 +13042,7 @@
         <v>4.8270001411438</v>
       </c>
       <c r="G437" t="n">
-        <v>3.26677346229553</v>
+        <v>3.26677322387695</v>
       </c>
       <c r="H437" t="n">
         <v>1711303</v>
@@ -13071,7 +13071,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G438" t="n">
-        <v>3.26203584671021</v>
+        <v>3.26203608512878</v>
       </c>
       <c r="H438" t="n">
         <v>1301307</v>
@@ -13100,7 +13100,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G439" t="n">
-        <v>3.31279325485229</v>
+        <v>3.31279349327087</v>
       </c>
       <c r="H439" t="n">
         <v>1709004</v>
@@ -13129,7 +13129,7 @@
         <v>4.89599990844727</v>
       </c>
       <c r="G440" t="n">
-        <v>3.31347012519836</v>
+        <v>3.31347060203552</v>
       </c>
       <c r="H440" t="n">
         <v>941165</v>
@@ -13158,7 +13158,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G441" t="n">
-        <v>3.28504610061646</v>
+        <v>3.28504586219788</v>
       </c>
       <c r="H441" t="n">
         <v>1233016</v>
@@ -13187,7 +13187,7 @@
         <v>4.9210000038147</v>
       </c>
       <c r="G442" t="n">
-        <v>3.33039021492004</v>
+        <v>3.33038949966431</v>
       </c>
       <c r="H442" t="n">
         <v>2566951</v>
@@ -13216,7 +13216,7 @@
         <v>4.83900022506714</v>
       </c>
       <c r="G443" t="n">
-        <v>3.27489471435547</v>
+        <v>3.27489447593689</v>
       </c>
       <c r="H443" t="n">
         <v>3411353</v>
@@ -13245,7 +13245,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G444" t="n">
-        <v>3.27963209152222</v>
+        <v>3.27963161468506</v>
       </c>
       <c r="H444" t="n">
         <v>2129347</v>
@@ -13274,7 +13274,7 @@
         <v>4.83599996566772</v>
       </c>
       <c r="G445" t="n">
-        <v>3.27286386489868</v>
+        <v>3.27286410331726</v>
       </c>
       <c r="H445" t="n">
         <v>1878974</v>
@@ -13303,7 +13303,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G446" t="n">
-        <v>3.27963209152222</v>
+        <v>3.27963161468506</v>
       </c>
       <c r="H446" t="n">
         <v>944767</v>
@@ -13361,7 +13361,7 @@
         <v>4.94299983978271</v>
       </c>
       <c r="G448" t="n">
-        <v>3.34527826309204</v>
+        <v>3.34527850151062</v>
       </c>
       <c r="H448" t="n">
         <v>2299462</v>
@@ -13390,7 +13390,7 @@
         <v>4.88600015640259</v>
       </c>
       <c r="G449" t="n">
-        <v>3.30670285224915</v>
+        <v>3.30670309066772</v>
       </c>
       <c r="H449" t="n">
         <v>1660537</v>
@@ -13419,7 +13419,7 @@
         <v>4.80299997329712</v>
       </c>
       <c r="G450" t="n">
-        <v>3.25053071975708</v>
+        <v>3.25053024291992</v>
       </c>
       <c r="H450" t="n">
         <v>1784763</v>
@@ -13477,7 +13477,7 @@
         <v>4.85099983215332</v>
       </c>
       <c r="G452" t="n">
-        <v>3.28301620483398</v>
+        <v>3.28301596641541</v>
       </c>
       <c r="H452" t="n">
         <v>1483194</v>
@@ -13506,7 +13506,7 @@
         <v>4.81300020217896</v>
       </c>
       <c r="G453" t="n">
-        <v>3.25729846954346</v>
+        <v>3.25729870796204</v>
       </c>
       <c r="H453" t="n">
         <v>2300362</v>
@@ -13564,7 +13564,7 @@
         <v>4.79300022125244</v>
       </c>
       <c r="G455" t="n">
-        <v>3.24376320838928</v>
+        <v>3.2437629699707</v>
       </c>
       <c r="H455" t="n">
         <v>1781968</v>
@@ -13593,7 +13593,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G456" t="n">
-        <v>3.28640007972717</v>
+        <v>3.28639984130859</v>
       </c>
       <c r="H456" t="n">
         <v>1593265</v>
@@ -13622,7 +13622,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G457" t="n">
-        <v>3.19368171691895</v>
+        <v>3.19368195533752</v>
       </c>
       <c r="H457" t="n">
         <v>1943294</v>
@@ -13651,7 +13651,7 @@
         <v>4.66400003433228</v>
       </c>
       <c r="G458" t="n">
-        <v>3.15645956993103</v>
+        <v>3.15645933151245</v>
       </c>
       <c r="H458" t="n">
         <v>3075593</v>
@@ -13709,7 +13709,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G460" t="n">
-        <v>3.16728830337524</v>
+        <v>3.16728782653809</v>
       </c>
       <c r="H460" t="n">
         <v>1168931</v>
@@ -13738,7 +13738,7 @@
         <v>4.65100002288818</v>
       </c>
       <c r="G461" t="n">
-        <v>3.1476616859436</v>
+        <v>3.14766120910645</v>
       </c>
       <c r="H461" t="n">
         <v>2765596</v>
@@ -13767,7 +13767,7 @@
         <v>4.69099998474121</v>
       </c>
       <c r="G462" t="n">
-        <v>3.17473220825195</v>
+        <v>3.17473244667053</v>
       </c>
       <c r="H462" t="n">
         <v>1001054</v>
@@ -13796,7 +13796,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G463" t="n">
-        <v>3.11314606666565</v>
+        <v>3.11314654350281</v>
       </c>
       <c r="H463" t="n">
         <v>1536584</v>
@@ -13825,7 +13825,7 @@
         <v>4.65399980545044</v>
       </c>
       <c r="G464" t="n">
-        <v>3.14969158172607</v>
+        <v>3.14969205856323</v>
       </c>
       <c r="H464" t="n">
         <v>2108233</v>
@@ -13854,7 +13854,7 @@
         <v>4.71500015258789</v>
       </c>
       <c r="G465" t="n">
-        <v>3.19097518920898</v>
+        <v>3.19097447395325</v>
       </c>
       <c r="H465" t="n">
         <v>1623544</v>
@@ -13883,7 +13883,7 @@
         <v>4.71199989318848</v>
       </c>
       <c r="G466" t="n">
-        <v>3.1889443397522</v>
+        <v>3.18894481658936</v>
       </c>
       <c r="H466" t="n">
         <v>1949181</v>
@@ -13912,7 +13912,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G467" t="n">
-        <v>3.1916515827179</v>
+        <v>3.19165182113647</v>
       </c>
       <c r="H467" t="n">
         <v>1729164</v>
@@ -13941,7 +13941,7 @@
         <v>4.70599985122681</v>
       </c>
       <c r="G468" t="n">
-        <v>3.1848840713501</v>
+        <v>3.18488383293152</v>
       </c>
       <c r="H468" t="n">
         <v>1272146</v>
@@ -14028,7 +14028,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>3.35001587867737</v>
+        <v>3.35001611709595</v>
       </c>
       <c r="H471" t="n">
         <v>1495616</v>
@@ -14086,7 +14086,7 @@
         <v>4.89799976348877</v>
       </c>
       <c r="G473" t="n">
-        <v>3.3148238658905</v>
+        <v>3.31482315063477</v>
       </c>
       <c r="H473" t="n">
         <v>1585806</v>
@@ -14115,7 +14115,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G474" t="n">
-        <v>3.30128836631775</v>
+        <v>3.30128860473633</v>
       </c>
       <c r="H474" t="n">
         <v>1802455</v>
@@ -14144,7 +14144,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G475" t="n">
-        <v>3.30940985679626</v>
+        <v>3.30940937995911</v>
       </c>
       <c r="H475" t="n">
         <v>1828737</v>
@@ -14173,7 +14173,7 @@
         <v>4.88700008392334</v>
       </c>
       <c r="G476" t="n">
-        <v>3.30737948417664</v>
+        <v>3.30737996101379</v>
       </c>
       <c r="H476" t="n">
         <v>1146119</v>
@@ -14202,7 +14202,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G477" t="n">
-        <v>3.24173259735107</v>
+        <v>3.24173307418823</v>
       </c>
       <c r="H477" t="n">
         <v>1901964</v>
@@ -14231,7 +14231,7 @@
         <v>4.89099979400635</v>
       </c>
       <c r="G478" t="n">
-        <v>3.31008672714233</v>
+        <v>3.31008625030518</v>
       </c>
       <c r="H478" t="n">
         <v>2378226</v>
@@ -14289,7 +14289,7 @@
         <v>4.77299976348877</v>
       </c>
       <c r="G480" t="n">
-        <v>3.23022723197937</v>
+        <v>3.23022747039795</v>
       </c>
       <c r="H480" t="n">
         <v>1732034</v>
@@ -14318,7 +14318,7 @@
         <v>4.80100011825562</v>
       </c>
       <c r="G481" t="n">
-        <v>3.24917721748352</v>
+        <v>3.24917697906494</v>
       </c>
       <c r="H481" t="n">
         <v>1464371</v>
@@ -14347,7 +14347,7 @@
         <v>4.83799982070923</v>
       </c>
       <c r="G482" t="n">
-        <v>3.2742178440094</v>
+        <v>3.27421712875366</v>
       </c>
       <c r="H482" t="n">
         <v>1373526</v>
@@ -14434,7 +14434,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G485" t="n">
-        <v>3.1686418056488</v>
+        <v>3.16864132881165</v>
       </c>
       <c r="H485" t="n">
         <v>1484153</v>
@@ -14521,7 +14521,7 @@
         <v>4.63700008392334</v>
       </c>
       <c r="G488" t="n">
-        <v>3.13818645477295</v>
+        <v>3.13818693161011</v>
       </c>
       <c r="H488" t="n">
         <v>1964476</v>
@@ -14579,7 +14579,7 @@
         <v>4.54099988937378</v>
       </c>
       <c r="G490" t="n">
-        <v>3.07321691513062</v>
+        <v>3.07321667671204</v>
       </c>
       <c r="H490" t="n">
         <v>2048852</v>
@@ -14608,7 +14608,7 @@
         <v>4.57600021362305</v>
       </c>
       <c r="G491" t="n">
-        <v>3.09690403938293</v>
+        <v>3.0969033241272</v>
       </c>
       <c r="H491" t="n">
         <v>2371411</v>
@@ -14637,7 +14637,7 @@
         <v>4.53399991989136</v>
       </c>
       <c r="G492" t="n">
-        <v>3.06847929954529</v>
+        <v>3.06847953796387</v>
       </c>
       <c r="H492" t="n">
         <v>2212633</v>
@@ -14695,7 +14695,7 @@
         <v>4.42899990081787</v>
       </c>
       <c r="G494" t="n">
-        <v>2.99741840362549</v>
+        <v>2.99741816520691</v>
       </c>
       <c r="H494" t="n">
         <v>1532051</v>
@@ -14724,7 +14724,7 @@
         <v>4.46099996566772</v>
       </c>
       <c r="G495" t="n">
-        <v>3.0190749168396</v>
+        <v>3.01907515525818</v>
       </c>
       <c r="H495" t="n">
         <v>1580807</v>
@@ -14782,7 +14782,7 @@
         <v>4.48299980163574</v>
       </c>
       <c r="G497" t="n">
-        <v>3.03396415710449</v>
+        <v>3.03396391868591</v>
       </c>
       <c r="H497" t="n">
         <v>1643380</v>
@@ -14811,7 +14811,7 @@
         <v>4.52400016784668</v>
       </c>
       <c r="G498" t="n">
-        <v>3.06171178817749</v>
+        <v>3.06171154975891</v>
       </c>
       <c r="H498" t="n">
         <v>1895816</v>
@@ -14840,7 +14840,7 @@
         <v>4.51100015640259</v>
       </c>
       <c r="G499" t="n">
-        <v>3.05291390419006</v>
+        <v>3.05291366577148</v>
       </c>
       <c r="H499" t="n">
         <v>5324720</v>
@@ -14869,7 +14869,7 @@
         <v>4.58199977874756</v>
       </c>
       <c r="G500" t="n">
-        <v>3.10096406936646</v>
+        <v>3.10096430778503</v>
       </c>
       <c r="H500" t="n">
         <v>5398178</v>
@@ -14898,7 +14898,7 @@
         <v>4.57399988174438</v>
       </c>
       <c r="G501" t="n">
-        <v>3.09554982185364</v>
+        <v>3.09555006027222</v>
       </c>
       <c r="H501" t="n">
         <v>2496826</v>
@@ -14927,7 +14927,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G502" t="n">
-        <v>3.0996105670929</v>
+        <v>3.09961080551147</v>
       </c>
       <c r="H502" t="n">
         <v>2967574</v>
@@ -15014,7 +15014,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G505" t="n">
-        <v>3.11314606666565</v>
+        <v>3.11314654350281</v>
       </c>
       <c r="H505" t="n">
         <v>3009630</v>
@@ -15043,7 +15043,7 @@
         <v>4.56799983978271</v>
       </c>
       <c r="G506" t="n">
-        <v>3.09148955345154</v>
+        <v>3.09148931503296</v>
       </c>
       <c r="H506" t="n">
         <v>2116842</v>
@@ -15072,7 +15072,7 @@
         <v>4.56199979782104</v>
       </c>
       <c r="G507" t="n">
-        <v>3.08742880821228</v>
+        <v>3.08742904663086</v>
       </c>
       <c r="H507" t="n">
         <v>2891161</v>
@@ -15101,7 +15101,7 @@
         <v>4.60799980163574</v>
       </c>
       <c r="G508" t="n">
-        <v>3.11856007575989</v>
+        <v>3.11856055259705</v>
       </c>
       <c r="H508" t="n">
         <v>3410234</v>
@@ -15159,7 +15159,7 @@
         <v>4.68900012969971</v>
       </c>
       <c r="G510" t="n">
-        <v>3.17337870597839</v>
+        <v>3.17337918281555</v>
       </c>
       <c r="H510" t="n">
         <v>2373885</v>
@@ -15246,7 +15246,7 @@
         <v>4.85900020599365</v>
       </c>
       <c r="G513" t="n">
-        <v>3.28843021392822</v>
+        <v>3.28842997550964</v>
       </c>
       <c r="H513" t="n">
         <v>2192149</v>
@@ -15304,7 +15304,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G515" t="n">
-        <v>3.26203584671021</v>
+        <v>3.26203608512878</v>
       </c>
       <c r="H515" t="n">
         <v>2936871</v>
@@ -15362,7 +15362,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G517" t="n">
-        <v>3.24308657646179</v>
+        <v>3.24308609962463</v>
       </c>
       <c r="H517" t="n">
         <v>1997692</v>
@@ -15391,7 +15391,7 @@
         <v>4.7189998626709</v>
       </c>
       <c r="G518" t="n">
-        <v>3.19368171691895</v>
+        <v>3.19368195533752</v>
       </c>
       <c r="H518" t="n">
         <v>2274690</v>
@@ -15420,7 +15420,7 @@
         <v>4.7519998550415</v>
       </c>
       <c r="G519" t="n">
-        <v>3.21601533889771</v>
+        <v>3.21601510047913</v>
       </c>
       <c r="H519" t="n">
         <v>1641709</v>
@@ -15449,7 +15449,7 @@
         <v>4.72700023651123</v>
       </c>
       <c r="G520" t="n">
-        <v>3.1990966796875</v>
+        <v>3.19909644126892</v>
       </c>
       <c r="H520" t="n">
         <v>1807479</v>
@@ -15478,7 +15478,7 @@
         <v>4.66900014877319</v>
       </c>
       <c r="G521" t="n">
-        <v>3.1598436832428</v>
+        <v>3.15984344482422</v>
       </c>
       <c r="H521" t="n">
         <v>2101028</v>
@@ -15594,7 +15594,7 @@
         <v>4.79199981689453</v>
       </c>
       <c r="G525" t="n">
-        <v>3.24308657646179</v>
+        <v>3.24308609962463</v>
       </c>
       <c r="H525" t="n">
         <v>1846766</v>
@@ -15623,7 +15623,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G526" t="n">
-        <v>3.25120806694031</v>
+        <v>3.25120782852173</v>
       </c>
       <c r="H526" t="n">
         <v>2223187</v>
@@ -15652,7 +15652,7 @@
         <v>4.73799991607666</v>
       </c>
       <c r="G527" t="n">
-        <v>3.20654010772705</v>
+        <v>3.20654082298279</v>
       </c>
       <c r="H527" t="n">
         <v>2520823</v>
@@ -15710,7 +15710,7 @@
         <v>4.72700023651123</v>
       </c>
       <c r="G529" t="n">
-        <v>3.1990966796875</v>
+        <v>3.19909644126892</v>
       </c>
       <c r="H529" t="n">
         <v>1450343</v>
@@ -15739,7 +15739,7 @@
         <v>4.75400018692017</v>
       </c>
       <c r="G530" t="n">
-        <v>3.21736884117126</v>
+        <v>3.21736907958984</v>
       </c>
       <c r="H530" t="n">
         <v>2817438</v>
@@ -15768,7 +15768,7 @@
         <v>4.76300001144409</v>
       </c>
       <c r="G531" t="n">
-        <v>3.22345995903015</v>
+        <v>3.22346019744873</v>
       </c>
       <c r="H531" t="n">
         <v>1028637</v>
@@ -15797,7 +15797,7 @@
         <v>4.82299995422363</v>
       </c>
       <c r="G532" t="n">
-        <v>3.26406621932983</v>
+        <v>3.26406598091125</v>
       </c>
       <c r="H532" t="n">
         <v>1349990</v>
@@ -15855,7 +15855,7 @@
         <v>4.88700008392334</v>
       </c>
       <c r="G534" t="n">
-        <v>3.30737948417664</v>
+        <v>3.30737996101379</v>
       </c>
       <c r="H534" t="n">
         <v>1901945</v>
@@ -15913,7 +15913,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G536" t="n">
-        <v>3.30602598190308</v>
+        <v>3.30602622032166</v>
       </c>
       <c r="H536" t="n">
         <v>1643389</v>
@@ -16000,7 +16000,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G539" t="n">
-        <v>3.45829916000366</v>
+        <v>3.45829963684082</v>
       </c>
       <c r="H539" t="n">
         <v>1917483</v>
@@ -16029,7 +16029,7 @@
         <v>5.13600015640259</v>
       </c>
       <c r="G540" t="n">
-        <v>3.47589540481567</v>
+        <v>3.47589564323425</v>
       </c>
       <c r="H540" t="n">
         <v>3297195</v>
@@ -16058,7 +16058,7 @@
         <v>5.10799980163574</v>
       </c>
       <c r="G541" t="n">
-        <v>3.45694541931152</v>
+        <v>3.4569456577301</v>
       </c>
       <c r="H541" t="n">
         <v>3139338</v>
@@ -16087,7 +16087,7 @@
         <v>5.13199996948242</v>
       </c>
       <c r="G542" t="n">
-        <v>3.47318816184998</v>
+        <v>3.47318840026855</v>
       </c>
       <c r="H542" t="n">
         <v>2196030</v>
@@ -16116,7 +16116,7 @@
         <v>5.0939998626709</v>
       </c>
       <c r="G543" t="n">
-        <v>3.44747090339661</v>
+        <v>3.44747114181519</v>
       </c>
       <c r="H543" t="n">
         <v>2157833</v>
@@ -16145,7 +16145,7 @@
         <v>5.09200000762939</v>
       </c>
       <c r="G544" t="n">
-        <v>3.44611763954163</v>
+        <v>3.44611716270447</v>
       </c>
       <c r="H544" t="n">
         <v>2699606</v>
@@ -16174,7 +16174,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G545" t="n">
-        <v>3.360844373703</v>
+        <v>3.36084485054016</v>
       </c>
       <c r="H545" t="n">
         <v>2043930</v>
@@ -16203,7 +16203,7 @@
         <v>4.99599981307983</v>
       </c>
       <c r="G546" t="n">
-        <v>3.38114714622498</v>
+        <v>3.38114738464355</v>
       </c>
       <c r="H546" t="n">
         <v>1085876</v>
@@ -16232,7 +16232,7 @@
         <v>5.06199979782104</v>
       </c>
       <c r="G547" t="n">
-        <v>3.42581415176392</v>
+        <v>3.4258143901825</v>
       </c>
       <c r="H547" t="n">
         <v>1842177</v>
@@ -16261,7 +16261,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G548" t="n">
-        <v>3.46506714820862</v>
+        <v>3.46506690979004</v>
       </c>
       <c r="H548" t="n">
         <v>2083576</v>
@@ -16319,7 +16319,7 @@
         <v>5.2039999961853</v>
       </c>
       <c r="G550" t="n">
-        <v>3.52191615104675</v>
+        <v>3.52191591262817</v>
       </c>
       <c r="H550" t="n">
         <v>2534910</v>
@@ -16348,7 +16348,7 @@
         <v>5.12200021743774</v>
       </c>
       <c r="G551" t="n">
-        <v>3.46642088890076</v>
+        <v>3.46642112731934</v>
       </c>
       <c r="H551" t="n">
         <v>5238374</v>
@@ -16377,7 +16377,7 @@
         <v>5.13199996948242</v>
       </c>
       <c r="G552" t="n">
-        <v>3.47318816184998</v>
+        <v>3.47318840026855</v>
       </c>
       <c r="H552" t="n">
         <v>2635040</v>
@@ -16406,7 +16406,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G553" t="n">
-        <v>3.52868390083313</v>
+        <v>3.52868342399597</v>
       </c>
       <c r="H553" t="n">
         <v>2232096</v>
@@ -16435,7 +16435,7 @@
         <v>5.24599981307983</v>
       </c>
       <c r="G554" t="n">
-        <v>3.55033993721008</v>
+        <v>3.55034017562866</v>
       </c>
       <c r="H554" t="n">
         <v>1779745</v>
@@ -16464,7 +16464,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G555" t="n">
-        <v>3.49755215644836</v>
+        <v>3.49755239486694</v>
       </c>
       <c r="H555" t="n">
         <v>2295662</v>
@@ -16522,7 +16522,7 @@
         <v>5.21600008010864</v>
       </c>
       <c r="G557" t="n">
-        <v>3.53003764152527</v>
+        <v>3.53003692626953</v>
       </c>
       <c r="H557" t="n">
         <v>1783120</v>
@@ -16551,7 +16551,7 @@
         <v>5.2020001411438</v>
       </c>
       <c r="G558" t="n">
-        <v>3.52056264877319</v>
+        <v>3.52056241035461</v>
       </c>
       <c r="H558" t="n">
         <v>1626237</v>
@@ -16580,7 +16580,7 @@
         <v>5.25400018692017</v>
       </c>
       <c r="G559" t="n">
-        <v>3.55575442314148</v>
+        <v>3.55575489997864</v>
       </c>
       <c r="H559" t="n">
         <v>2277905</v>
@@ -16609,7 +16609,7 @@
         <v>5.25</v>
       </c>
       <c r="G560" t="n">
-        <v>3.55304789543152</v>
+        <v>3.5530469417572</v>
       </c>
       <c r="H560" t="n">
         <v>1235834</v>
@@ -16696,7 +16696,7 @@
         <v>5.2480001449585</v>
       </c>
       <c r="G563" t="n">
-        <v>3.5516939163208</v>
+        <v>3.55169439315796</v>
       </c>
       <c r="H563" t="n">
         <v>2286330</v>
@@ -16725,7 +16725,7 @@
         <v>5.25</v>
       </c>
       <c r="G564" t="n">
-        <v>3.55304789543152</v>
+        <v>3.5530469417572</v>
       </c>
       <c r="H564" t="n">
         <v>1436011</v>
@@ -16754,7 +16754,7 @@
         <v>5.16800022125244</v>
       </c>
       <c r="G565" t="n">
-        <v>3.49755215644836</v>
+        <v>3.49755239486694</v>
       </c>
       <c r="H565" t="n">
         <v>2827660</v>
@@ -16783,7 +16783,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G566" t="n">
-        <v>3.56658220291138</v>
+        <v>3.56658267974854</v>
       </c>
       <c r="H566" t="n">
         <v>2847559</v>
@@ -16812,7 +16812,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G567" t="n">
-        <v>3.57335090637207</v>
+        <v>3.57335042953491</v>
       </c>
       <c r="H567" t="n">
         <v>2865590</v>
@@ -16841,7 +16841,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G568" t="n">
-        <v>3.57199692726135</v>
+        <v>3.57199668884277</v>
       </c>
       <c r="H568" t="n">
         <v>2087253</v>
@@ -16870,7 +16870,7 @@
         <v>5.19399976730347</v>
       </c>
       <c r="G569" t="n">
-        <v>3.51514768600464</v>
+        <v>3.5151481628418</v>
       </c>
       <c r="H569" t="n">
         <v>1833579</v>
@@ -16899,7 +16899,7 @@
         <v>5.22399997711182</v>
       </c>
       <c r="G570" t="n">
-        <v>3.53545165061951</v>
+        <v>3.53545141220093</v>
       </c>
       <c r="H570" t="n">
         <v>1542313</v>
@@ -16928,7 +16928,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G571" t="n">
-        <v>3.57199692726135</v>
+        <v>3.57199668884277</v>
       </c>
       <c r="H571" t="n">
         <v>1790300</v>
@@ -16957,7 +16957,7 @@
         <v>5.26200008392334</v>
       </c>
       <c r="G572" t="n">
-        <v>3.5611686706543</v>
+        <v>3.56116890907288</v>
       </c>
       <c r="H572" t="n">
         <v>1415150</v>
@@ -16986,7 +16986,7 @@
         <v>5.14599990844727</v>
       </c>
       <c r="G573" t="n">
-        <v>3.48266291618347</v>
+        <v>3.48266267776489</v>
       </c>
       <c r="H573" t="n">
         <v>1783474</v>
@@ -17015,7 +17015,7 @@
         <v>5.11399984359741</v>
       </c>
       <c r="G574" t="n">
-        <v>3.46100687980652</v>
+        <v>3.46100664138794</v>
       </c>
       <c r="H574" t="n">
         <v>1543318</v>
@@ -17102,7 +17102,7 @@
         <v>5.22800016403198</v>
       </c>
       <c r="G577" t="n">
-        <v>3.53815865516663</v>
+        <v>3.53815817832947</v>
       </c>
       <c r="H577" t="n">
         <v>1120215</v>
@@ -17131,7 +17131,7 @@
         <v>5.21400022506714</v>
       </c>
       <c r="G578" t="n">
-        <v>3.52868390083313</v>
+        <v>3.52868342399597</v>
       </c>
       <c r="H578" t="n">
         <v>1509818</v>
@@ -17160,7 +17160,7 @@
         <v>5.22599983215332</v>
       </c>
       <c r="G579" t="n">
-        <v>3.53680515289307</v>
+        <v>3.53680491447449</v>
       </c>
       <c r="H579" t="n">
         <v>1824415</v>
@@ -17189,7 +17189,7 @@
         <v>5.23000001907349</v>
       </c>
       <c r="G580" t="n">
-        <v>3.53951168060303</v>
+        <v>3.53951239585876</v>
       </c>
       <c r="H580" t="n">
         <v>1222175</v>
@@ -17218,7 +17218,7 @@
         <v>5.20800018310547</v>
       </c>
       <c r="G581" t="n">
-        <v>3.52462291717529</v>
+        <v>3.52462315559387</v>
       </c>
       <c r="H581" t="n">
         <v>885610</v>
@@ -17247,7 +17247,7 @@
         <v>5.2039999961853</v>
       </c>
       <c r="G582" t="n">
-        <v>3.52191615104675</v>
+        <v>3.52191591262817</v>
       </c>
       <c r="H582" t="n">
         <v>832020</v>
@@ -17305,7 +17305,7 @@
         <v>5.27799987792969</v>
       </c>
       <c r="G584" t="n">
-        <v>3.57199692726135</v>
+        <v>3.57199668884277</v>
       </c>
       <c r="H584" t="n">
         <v>1630171</v>
@@ -17363,7 +17363,7 @@
         <v>5.2960000038147</v>
       </c>
       <c r="G586" t="n">
-        <v>3.58417844772339</v>
+        <v>3.58417892456055</v>
       </c>
       <c r="H586" t="n">
         <v>1279020</v>
@@ -17392,7 +17392,7 @@
         <v>5.26599979400635</v>
       </c>
       <c r="G587" t="n">
-        <v>3.56387543678284</v>
+        <v>3.56387567520142</v>
       </c>
       <c r="H587" t="n">
         <v>1702241</v>
@@ -17450,7 +17450,7 @@
         <v>5.31799983978271</v>
       </c>
       <c r="G589" t="n">
-        <v>3.59906768798828</v>
+        <v>3.59906792640686</v>
       </c>
       <c r="H589" t="n">
         <v>1973752</v>
@@ -17479,7 +17479,7 @@
         <v>5.25799989700317</v>
       </c>
       <c r="G590" t="n">
-        <v>3.55846095085144</v>
+        <v>3.5584614276886</v>
       </c>
       <c r="H590" t="n">
         <v>1762263</v>
@@ -17508,7 +17508,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G591" t="n">
-        <v>3.56658220291138</v>
+        <v>3.56658267974854</v>
       </c>
       <c r="H591" t="n">
         <v>1538701</v>
@@ -17595,7 +17595,7 @@
         <v>5.46799993515015</v>
       </c>
       <c r="G594" t="n">
-        <v>3.70058345794678</v>
+        <v>3.7005832195282</v>
       </c>
       <c r="H594" t="n">
         <v>2310453</v>
@@ -17624,7 +17624,7 @@
         <v>5.42600011825562</v>
       </c>
       <c r="G595" t="n">
-        <v>3.67215919494629</v>
+        <v>3.67215871810913</v>
       </c>
       <c r="H595" t="n">
         <v>1706877</v>
@@ -17653,7 +17653,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G596" t="n">
-        <v>3.66133069992065</v>
+        <v>3.66133093833923</v>
       </c>
       <c r="H596" t="n">
         <v>1826392</v>
@@ -17682,7 +17682,7 @@
         <v>5.37200021743774</v>
       </c>
       <c r="G597" t="n">
-        <v>3.63561344146729</v>
+        <v>3.63561391830444</v>
       </c>
       <c r="H597" t="n">
         <v>1711423</v>
@@ -17711,7 +17711,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G598" t="n">
-        <v>3.6545627117157</v>
+        <v>3.65456295013428</v>
       </c>
       <c r="H598" t="n">
         <v>1477720</v>
@@ -17740,7 +17740,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G599" t="n">
-        <v>3.6545627117157</v>
+        <v>3.65456295013428</v>
       </c>
       <c r="H599" t="n">
         <v>3456376</v>
@@ -17769,7 +17769,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G600" t="n">
-        <v>3.6545627117157</v>
+        <v>3.65456295013428</v>
       </c>
       <c r="H600" t="n">
         <v>1001970</v>
@@ -17798,7 +17798,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G601" t="n">
-        <v>3.69516968727112</v>
+        <v>3.69516921043396</v>
       </c>
       <c r="H601" t="n">
         <v>1443702</v>
@@ -17827,7 +17827,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G602" t="n">
-        <v>3.70464396476746</v>
+        <v>3.70464372634888</v>
       </c>
       <c r="H602" t="n">
         <v>2150629</v>
@@ -17856,7 +17856,7 @@
         <v>5.49399995803833</v>
       </c>
       <c r="G603" t="n">
-        <v>3.71817898750305</v>
+        <v>3.71817970275879</v>
       </c>
       <c r="H603" t="n">
         <v>1154586</v>
@@ -17885,7 +17885,7 @@
         <v>5.48199987411499</v>
       </c>
       <c r="G604" t="n">
-        <v>3.71005797386169</v>
+        <v>3.71005821228027</v>
       </c>
       <c r="H604" t="n">
         <v>1629370</v>
@@ -17914,7 +17914,7 @@
         <v>5.50799989700317</v>
       </c>
       <c r="G605" t="n">
-        <v>3.72765421867371</v>
+        <v>3.72765374183655</v>
       </c>
       <c r="H605" t="n">
         <v>1275899</v>
@@ -17943,7 +17943,7 @@
         <v>5.5</v>
       </c>
       <c r="G606" t="n">
-        <v>3.72224020957947</v>
+        <v>3.72223997116089</v>
       </c>
       <c r="H606" t="n">
         <v>1602470</v>
@@ -17972,7 +17972,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G607" t="n">
-        <v>3.688401222229</v>
+        <v>3.68840169906616</v>
       </c>
       <c r="H607" t="n">
         <v>1876065</v>
@@ -18030,7 +18030,7 @@
         <v>5.50400018692017</v>
       </c>
       <c r="G609" t="n">
-        <v>3.72494697570801</v>
+        <v>3.72494745254517</v>
       </c>
       <c r="H609" t="n">
         <v>2248836</v>
@@ -18059,7 +18059,7 @@
         <v>5.43400001525879</v>
       </c>
       <c r="G610" t="n">
-        <v>3.67757296562195</v>
+        <v>3.67757344245911</v>
       </c>
       <c r="H610" t="n">
         <v>2056524</v>
@@ -18088,7 +18088,7 @@
         <v>5.49200010299683</v>
       </c>
       <c r="G611" t="n">
-        <v>3.71682596206665</v>
+        <v>3.71682548522949</v>
       </c>
       <c r="H611" t="n">
         <v>1932836</v>
@@ -18117,7 +18117,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G612" t="n">
-        <v>3.75607919692993</v>
+        <v>3.75607824325562</v>
       </c>
       <c r="H612" t="n">
         <v>1506760</v>
@@ -18146,7 +18146,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G613" t="n">
-        <v>3.72359323501587</v>
+        <v>3.72359418869019</v>
       </c>
       <c r="H613" t="n">
         <v>1644649</v>
@@ -18175,7 +18175,7 @@
         <v>5.52199983596802</v>
       </c>
       <c r="G614" t="n">
-        <v>3.7371289730072</v>
+        <v>3.73712921142578</v>
       </c>
       <c r="H614" t="n">
         <v>2119896</v>
@@ -18204,7 +18204,7 @@
         <v>5.5460000038147</v>
       </c>
       <c r="G615" t="n">
-        <v>3.75337219238281</v>
+        <v>3.75337171554565</v>
       </c>
       <c r="H615" t="n">
         <v>1536356</v>
@@ -18233,7 +18233,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G616" t="n">
-        <v>3.75201773643494</v>
+        <v>3.75201821327209</v>
       </c>
       <c r="H616" t="n">
         <v>1891956</v>
@@ -18291,7 +18291,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G618" t="n">
-        <v>3.78856348991394</v>
+        <v>3.78856372833252</v>
       </c>
       <c r="H618" t="n">
         <v>1967546</v>
@@ -18349,7 +18349,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G620" t="n">
-        <v>3.76555299758911</v>
+        <v>3.76555323600769</v>
       </c>
       <c r="H620" t="n">
         <v>1306555</v>
@@ -18378,7 +18378,7 @@
         <v>5.5019998550415</v>
       </c>
       <c r="G621" t="n">
-        <v>3.72359323501587</v>
+        <v>3.72359418869019</v>
       </c>
       <c r="H621" t="n">
         <v>1285528</v>
@@ -18407,7 +18407,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G622" t="n">
-        <v>3.70464396476746</v>
+        <v>3.70464372634888</v>
       </c>
       <c r="H622" t="n">
         <v>2574109</v>
@@ -18436,7 +18436,7 @@
         <v>5.52600002288818</v>
       </c>
       <c r="G623" t="n">
-        <v>3.73983573913574</v>
+        <v>3.7398362159729</v>
       </c>
       <c r="H623" t="n">
         <v>1474177</v>
@@ -18465,7 +18465,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G624" t="n">
-        <v>3.76555299758911</v>
+        <v>3.76555323600769</v>
       </c>
       <c r="H624" t="n">
         <v>1476786</v>
@@ -18581,7 +18581,7 @@
         <v>5.53399991989136</v>
       </c>
       <c r="G628" t="n">
-        <v>3.74525046348572</v>
+        <v>3.74525022506714</v>
       </c>
       <c r="H628" t="n">
         <v>1443005</v>
@@ -18639,7 +18639,7 @@
         <v>5.48799991607666</v>
       </c>
       <c r="G630" t="n">
-        <v>3.71411895751953</v>
+        <v>3.71411871910095</v>
       </c>
       <c r="H630" t="n">
         <v>2010281</v>
@@ -18697,7 +18697,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G632" t="n">
-        <v>3.71547174453735</v>
+        <v>3.71547198295593</v>
       </c>
       <c r="H632" t="n">
         <v>1133632</v>
@@ -18726,7 +18726,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G633" t="n">
-        <v>3.77908897399902</v>
+        <v>3.77908873558044</v>
       </c>
       <c r="H633" t="n">
         <v>2716436</v>
@@ -18755,7 +18755,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G634" t="n">
-        <v>3.72630000114441</v>
+        <v>3.72630023956299</v>
       </c>
       <c r="H634" t="n">
         <v>1954633</v>
@@ -18784,7 +18784,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G635" t="n">
-        <v>3.70870423316956</v>
+        <v>3.70870494842529</v>
       </c>
       <c r="H635" t="n">
         <v>1383579</v>
@@ -18813,7 +18813,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G636" t="n">
-        <v>3.74254322052002</v>
+        <v>3.7425434589386</v>
       </c>
       <c r="H636" t="n">
         <v>1612433</v>
@@ -18842,7 +18842,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G637" t="n">
-        <v>3.78179502487183</v>
+        <v>3.78179574012756</v>
       </c>
       <c r="H637" t="n">
         <v>2256127</v>
@@ -18871,7 +18871,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G638" t="n">
-        <v>3.81157374382019</v>
+        <v>3.81157398223877</v>
       </c>
       <c r="H638" t="n">
         <v>2561720</v>
@@ -18900,7 +18900,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G639" t="n">
-        <v>3.83864498138428</v>
+        <v>3.83864426612854</v>
       </c>
       <c r="H639" t="n">
         <v>3190537</v>
@@ -18929,7 +18929,7 @@
         <v>5.77199983596802</v>
       </c>
       <c r="G640" t="n">
-        <v>3.90632176399231</v>
+        <v>3.90632128715515</v>
       </c>
       <c r="H640" t="n">
         <v>2212740</v>
@@ -18958,7 +18958,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>3.90496873855591</v>
+        <v>3.90496802330017</v>
       </c>
       <c r="H641" t="n">
         <v>3062452</v>
@@ -18987,7 +18987,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G642" t="n">
-        <v>3.95402979850769</v>
+        <v>3.95403075218201</v>
       </c>
       <c r="H642" t="n">
         <v>2173043</v>
@@ -19016,7 +19016,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G643" t="n">
-        <v>3.99202299118042</v>
+        <v>3.99202251434326</v>
       </c>
       <c r="H643" t="n">
         <v>1845403</v>
@@ -19132,7 +19132,7 @@
         <v>5.72200012207031</v>
       </c>
       <c r="G647" t="n">
-        <v>4.02579307556152</v>
+        <v>4.02579355239868</v>
       </c>
       <c r="H647" t="n">
         <v>1241978</v>
@@ -19161,7 +19161,7 @@
         <v>5.70800018310547</v>
       </c>
       <c r="G648" t="n">
-        <v>4.01594352722168</v>
+        <v>4.01594400405884</v>
       </c>
       <c r="H648" t="n">
         <v>1888164</v>
@@ -19190,7 +19190,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G649" t="n">
-        <v>3.94699382781982</v>
+        <v>3.9469940662384</v>
       </c>
       <c r="H649" t="n">
         <v>2336188</v>
@@ -19219,7 +19219,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G650" t="n">
-        <v>3.93292331695557</v>
+        <v>3.93292284011841</v>
       </c>
       <c r="H650" t="n">
         <v>1268362</v>
@@ -19248,7 +19248,7 @@
         <v>5.66800022125244</v>
       </c>
       <c r="G651" t="n">
-        <v>3.98780155181885</v>
+        <v>3.98780131340027</v>
       </c>
       <c r="H651" t="n">
         <v>1959746</v>
@@ -19277,7 +19277,7 @@
         <v>5.73600006103516</v>
       </c>
       <c r="G652" t="n">
-        <v>4.03564357757568</v>
+        <v>4.03564310073853</v>
       </c>
       <c r="H652" t="n">
         <v>2387126</v>
@@ -19306,7 +19306,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G653" t="n">
-        <v>4.08770751953125</v>
+        <v>4.08770704269409</v>
       </c>
       <c r="H653" t="n">
         <v>2342463</v>
@@ -19393,7 +19393,7 @@
         <v>5.94399976730347</v>
       </c>
       <c r="G656" t="n">
-        <v>4.18198490142822</v>
+        <v>4.18198442459106</v>
       </c>
       <c r="H656" t="n">
         <v>1992667</v>
@@ -19451,7 +19451,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G658" t="n">
-        <v>4.14117813110352</v>
+        <v>4.14117765426636</v>
       </c>
       <c r="H658" t="n">
         <v>1808264</v>
@@ -19480,7 +19480,7 @@
         <v>5.83599996566772</v>
       </c>
       <c r="G659" t="n">
-        <v>4.10599946975708</v>
+        <v>4.10599994659424</v>
       </c>
       <c r="H659" t="n">
         <v>1770544</v>
@@ -19538,7 +19538,7 @@
         <v>5.92799997329712</v>
       </c>
       <c r="G661" t="n">
-        <v>4.17072725296021</v>
+        <v>4.17072772979736</v>
       </c>
       <c r="H661" t="n">
         <v>2282492</v>
@@ -19567,7 +19567,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G662" t="n">
-        <v>4.15806293487549</v>
+        <v>4.15806341171265</v>
       </c>
       <c r="H662" t="n">
         <v>1559189</v>
@@ -19625,7 +19625,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G664" t="n">
-        <v>4.25796985626221</v>
+        <v>4.25796937942505</v>
       </c>
       <c r="H664" t="n">
         <v>2726415</v>
@@ -19712,7 +19712,7 @@
         <v>6.10599994659424</v>
       </c>
       <c r="G667" t="n">
-        <v>4.29596185684204</v>
+        <v>4.2959623336792</v>
       </c>
       <c r="H667" t="n">
         <v>1422499</v>
@@ -19741,7 +19741,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G668" t="n">
-        <v>4.26359748840332</v>
+        <v>4.26359796524048</v>
       </c>
       <c r="H668" t="n">
         <v>1452344</v>
@@ -19828,7 +19828,7 @@
         <v>5.90799999237061</v>
       </c>
       <c r="G671" t="n">
-        <v>4.15665674209595</v>
+        <v>4.15665578842163</v>
       </c>
       <c r="H671" t="n">
         <v>2723118</v>
@@ -20002,7 +20002,7 @@
         <v>6.11600017547607</v>
       </c>
       <c r="G677" t="n">
-        <v>4.30299854278564</v>
+        <v>4.30299711227417</v>
       </c>
       <c r="H677" t="n">
         <v>1999919</v>
@@ -20031,7 +20031,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G678" t="n">
-        <v>4.32691860198975</v>
+        <v>4.3269190788269</v>
       </c>
       <c r="H678" t="n">
         <v>2624174</v>
@@ -20060,7 +20060,7 @@
         <v>6.12799978256226</v>
       </c>
       <c r="G679" t="n">
-        <v>4.31144094467163</v>
+        <v>4.31143999099731</v>
       </c>
       <c r="H679" t="n">
         <v>2050886</v>
@@ -20089,7 +20089,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G680" t="n">
-        <v>4.34943294525146</v>
+        <v>4.34943342208862</v>
       </c>
       <c r="H680" t="n">
         <v>2137342</v>
@@ -20118,7 +20118,7 @@
         <v>6.20800018310547</v>
       </c>
       <c r="G681" t="n">
-        <v>4.36772537231445</v>
+        <v>4.36772584915161</v>
       </c>
       <c r="H681" t="n">
         <v>2306319</v>
@@ -20234,7 +20234,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G685" t="n">
-        <v>4.35506153106689</v>
+        <v>4.35506200790405</v>
       </c>
       <c r="H685" t="n">
         <v>1975271</v>
@@ -20292,7 +20292,7 @@
         <v>6.03599977493286</v>
       </c>
       <c r="G687" t="n">
-        <v>4.24671220779419</v>
+        <v>4.24671268463135</v>
       </c>
       <c r="H687" t="n">
         <v>1790145</v>
@@ -20321,7 +20321,7 @@
         <v>6.02199983596802</v>
       </c>
       <c r="G688" t="n">
-        <v>4.23686265945435</v>
+        <v>4.2368631362915</v>
       </c>
       <c r="H688" t="n">
         <v>1209817</v>
@@ -20379,7 +20379,7 @@
         <v>5.96199989318848</v>
       </c>
       <c r="G690" t="n">
-        <v>4.19464826583862</v>
+        <v>4.19464874267578</v>
       </c>
       <c r="H690" t="n">
         <v>2000465</v>
@@ -20408,7 +20408,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G691" t="n">
-        <v>4.14117813110352</v>
+        <v>4.14117765426636</v>
       </c>
       <c r="H691" t="n">
         <v>1961556</v>
@@ -20582,7 +20582,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G697" t="n">
-        <v>4.09192752838135</v>
+        <v>4.09192800521851</v>
       </c>
       <c r="H697" t="n">
         <v>2123629</v>
@@ -20640,7 +20640,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>4.10177803039551</v>
+        <v>4.10177850723267</v>
       </c>
       <c r="H699" t="n">
         <v>1720119</v>
@@ -20669,7 +20669,7 @@
         <v>5.83400011062622</v>
       </c>
       <c r="G700" t="n">
-        <v>4.10459232330322</v>
+        <v>4.10459280014038</v>
       </c>
       <c r="H700" t="n">
         <v>1324347</v>
@@ -20698,7 +20698,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G701" t="n">
-        <v>3.93855118751526</v>
+        <v>3.93855166435242</v>
       </c>
       <c r="H701" t="n">
         <v>5230571</v>
@@ -20727,7 +20727,7 @@
         <v>5.66200017929077</v>
       </c>
       <c r="G702" t="n">
-        <v>3.98358011245728</v>
+        <v>3.98357963562012</v>
       </c>
       <c r="H702" t="n">
         <v>1900172</v>
@@ -20814,7 +20814,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G705" t="n">
-        <v>3.99202299118042</v>
+        <v>3.99202251434326</v>
       </c>
       <c r="H705" t="n">
         <v>2966146</v>
@@ -20843,7 +20843,7 @@
         <v>5.85599994659424</v>
       </c>
       <c r="G706" t="n">
-        <v>4.12007141113281</v>
+        <v>4.12007093429565</v>
       </c>
       <c r="H706" t="n">
         <v>1986363</v>
@@ -20901,7 +20901,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G708" t="n">
-        <v>4.09192752838135</v>
+        <v>4.09192800521851</v>
       </c>
       <c r="H708" t="n">
         <v>1143161</v>
@@ -20930,7 +20930,7 @@
         <v>5.72200012207031</v>
       </c>
       <c r="G709" t="n">
-        <v>4.02579307556152</v>
+        <v>4.02579355239868</v>
       </c>
       <c r="H709" t="n">
         <v>1515013</v>
@@ -20959,7 +20959,7 @@
         <v>5.71600008010864</v>
       </c>
       <c r="G710" t="n">
-        <v>4.02157211303711</v>
+        <v>4.02157258987427</v>
       </c>
       <c r="H710" t="n">
         <v>958675</v>
@@ -21075,7 +21075,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G714" t="n">
-        <v>4.15525007247925</v>
+        <v>4.15524911880493</v>
       </c>
       <c r="H714" t="n">
         <v>2551492</v>
@@ -21133,7 +21133,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G716" t="n">
-        <v>4.15806293487549</v>
+        <v>4.15806341171265</v>
       </c>
       <c r="H716" t="n">
         <v>1279957</v>
@@ -21191,7 +21191,7 @@
         <v>5.91800022125244</v>
       </c>
       <c r="G718" t="n">
-        <v>4.16369247436523</v>
+        <v>4.16369199752808</v>
       </c>
       <c r="H718" t="n">
         <v>1297130</v>
@@ -21220,7 +21220,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>4.12992191314697</v>
+        <v>4.1299204826355</v>
       </c>
       <c r="H719" t="n">
         <v>1890783</v>
@@ -21307,7 +21307,7 @@
         <v>5.63600015640259</v>
       </c>
       <c r="G722" t="n">
-        <v>3.96528697013855</v>
+        <v>3.96528768539429</v>
       </c>
       <c r="H722" t="n">
         <v>2591482</v>
@@ -21336,7 +21336,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G723" t="n">
-        <v>3.92870211601257</v>
+        <v>3.92870163917542</v>
       </c>
       <c r="H723" t="n">
         <v>3759513</v>
@@ -21423,7 +21423,7 @@
         <v>5.61399984359741</v>
       </c>
       <c r="G726" t="n">
-        <v>3.94980835914612</v>
+        <v>3.9498085975647</v>
       </c>
       <c r="H726" t="n">
         <v>2078476</v>
@@ -21452,7 +21452,7 @@
         <v>5.70599985122681</v>
       </c>
       <c r="G727" t="n">
-        <v>4.01453685760498</v>
+        <v>4.01453638076782</v>
       </c>
       <c r="H727" t="n">
         <v>2047080</v>
@@ -21481,7 +21481,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G728" t="n">
-        <v>4.00327968597412</v>
+        <v>4.00328016281128</v>
       </c>
       <c r="H728" t="n">
         <v>2005242</v>
@@ -21510,7 +21510,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G729" t="n">
-        <v>4.00327968597412</v>
+        <v>4.00328016281128</v>
       </c>
       <c r="H729" t="n">
         <v>2079379</v>
@@ -21597,7 +21597,7 @@
         <v>5.9060001373291</v>
       </c>
       <c r="G732" t="n">
-        <v>4.15525007247925</v>
+        <v>4.15524911880493</v>
       </c>
       <c r="H732" t="n">
         <v>3095858</v>
@@ -21684,7 +21684,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G735" t="n">
-        <v>4.14258527755737</v>
+        <v>4.14258480072021</v>
       </c>
       <c r="H735" t="n">
         <v>2133876</v>
@@ -21742,7 +21742,7 @@
         <v>5.85200023651123</v>
       </c>
       <c r="G737" t="n">
-        <v>4.11725664138794</v>
+        <v>4.1172571182251</v>
       </c>
       <c r="H737" t="n">
         <v>1979133</v>
@@ -21829,7 +21829,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G740" t="n">
-        <v>4.12851428985596</v>
+        <v>4.12851333618164</v>
       </c>
       <c r="H740" t="n">
         <v>1788578</v>
@@ -21858,7 +21858,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G741" t="n">
-        <v>4.18339204788208</v>
+        <v>4.18339252471924</v>
       </c>
       <c r="H741" t="n">
         <v>1616448</v>
@@ -21945,7 +21945,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G744" t="n">
-        <v>4.01031494140625</v>
+        <v>4.01031446456909</v>
       </c>
       <c r="H744" t="n">
         <v>1958168</v>
@@ -21974,7 +21974,7 @@
         <v>5.75600004196167</v>
       </c>
       <c r="G745" t="n">
-        <v>4.0497145652771</v>
+        <v>4.04971504211426</v>
       </c>
       <c r="H745" t="n">
         <v>1957667</v>
@@ -22032,7 +22032,7 @@
         <v>5.69799995422363</v>
       </c>
       <c r="G747" t="n">
-        <v>4.00890827178955</v>
+        <v>4.00890779495239</v>
       </c>
       <c r="H747" t="n">
         <v>1847746</v>
@@ -22061,7 +22061,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G748" t="n">
-        <v>3.99624371528625</v>
+        <v>3.99624347686768</v>
       </c>
       <c r="H748" t="n">
         <v>1909085</v>
@@ -22090,7 +22090,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G749" t="n">
-        <v>3.99202299118042</v>
+        <v>3.99202251434326</v>
       </c>
       <c r="H749" t="n">
         <v>1654695</v>
@@ -22119,7 +22119,7 @@
         <v>5.67799997329712</v>
       </c>
       <c r="G750" t="n">
-        <v>3.99483704566956</v>
+        <v>3.9948365688324</v>
       </c>
       <c r="H750" t="n">
         <v>3183705</v>
@@ -22206,7 +22206,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G753" t="n">
-        <v>3.99061512947083</v>
+        <v>3.99061560630798</v>
       </c>
       <c r="H753" t="n">
         <v>1519156</v>
@@ -22322,7 +22322,7 @@
         <v>5.68800020217896</v>
       </c>
       <c r="G757" t="n">
-        <v>4.00187253952026</v>
+        <v>4.00187301635742</v>
       </c>
       <c r="H757" t="n">
         <v>2492570</v>
@@ -22380,7 +22380,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G759" t="n">
-        <v>4.0581579208374</v>
+        <v>4.05815744400024</v>
       </c>
       <c r="H759" t="n">
         <v>2104505</v>
@@ -22496,7 +22496,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G763" t="n">
-        <v>4.16509962081909</v>
+        <v>4.16509914398193</v>
       </c>
       <c r="H763" t="n">
         <v>1824296</v>
@@ -22525,7 +22525,7 @@
         <v>5.82800006866455</v>
       </c>
       <c r="G764" t="n">
-        <v>4.10037088394165</v>
+        <v>4.10037136077881</v>
       </c>
       <c r="H764" t="n">
         <v>2677873</v>
@@ -22641,7 +22641,7 @@
         <v>5.97599983215332</v>
       </c>
       <c r="G768" t="n">
-        <v>4.20449829101562</v>
+        <v>4.20449876785278</v>
       </c>
       <c r="H768" t="n">
         <v>1631192</v>
@@ -22670,7 +22670,7 @@
         <v>5.88600015640259</v>
       </c>
       <c r="G769" t="n">
-        <v>4.14117813110352</v>
+        <v>4.14117765426636</v>
       </c>
       <c r="H769" t="n">
         <v>2385144</v>
@@ -22699,7 +22699,7 @@
         <v>5.83400011062622</v>
       </c>
       <c r="G770" t="n">
-        <v>4.10459232330322</v>
+        <v>4.10459280014038</v>
       </c>
       <c r="H770" t="n">
         <v>2359300</v>
@@ -22786,7 +22786,7 @@
         <v>5.76599979400635</v>
       </c>
       <c r="G773" t="n">
-        <v>4.05675029754639</v>
+        <v>4.05674982070923</v>
       </c>
       <c r="H773" t="n">
         <v>1799150</v>
@@ -22815,7 +22815,7 @@
         <v>5.75</v>
       </c>
       <c r="G774" t="n">
-        <v>4.04549312591553</v>
+        <v>4.04549264907837</v>
       </c>
       <c r="H774" t="n">
         <v>1402877</v>
@@ -22902,7 +22902,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G777" t="n">
-        <v>4.04127168655396</v>
+        <v>4.0412712097168</v>
       </c>
       <c r="H777" t="n">
         <v>1890089</v>
@@ -22931,7 +22931,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G778" t="n">
-        <v>4.05534267425537</v>
+        <v>4.05534315109253</v>
       </c>
       <c r="H778" t="n">
         <v>1765558</v>
@@ -22960,7 +22960,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G779" t="n">
-        <v>4.04690027236938</v>
+        <v>4.04689979553223</v>
       </c>
       <c r="H779" t="n">
         <v>1034560</v>
@@ -23018,7 +23018,7 @@
         <v>5.45599985122681</v>
       </c>
       <c r="G781" t="n">
-        <v>3.83864545822144</v>
+        <v>3.83864521980286</v>
       </c>
       <c r="H781" t="n">
         <v>4756331</v>
@@ -23047,7 +23047,7 @@
         <v>5.54400014877319</v>
       </c>
       <c r="G782" t="n">
-        <v>3.90055894851685</v>
+        <v>3.90055871009827</v>
       </c>
       <c r="H782" t="n">
         <v>3299250</v>
@@ -23076,7 +23076,7 @@
         <v>5.56400012969971</v>
       </c>
       <c r="G783" t="n">
-        <v>3.91462969779968</v>
+        <v>3.91462993621826</v>
       </c>
       <c r="H783" t="n">
         <v>2410040</v>
@@ -23105,7 +23105,7 @@
         <v>5.51000022888184</v>
       </c>
       <c r="G784" t="n">
-        <v>3.87663841247559</v>
+        <v>3.87663793563843</v>
       </c>
       <c r="H784" t="n">
         <v>1880712</v>
@@ -23134,7 +23134,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G785" t="n">
-        <v>3.84849548339844</v>
+        <v>3.84849524497986</v>
       </c>
       <c r="H785" t="n">
         <v>1765297</v>
@@ -23163,7 +23163,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G786" t="n">
-        <v>3.78517484664917</v>
+        <v>3.78517460823059</v>
       </c>
       <c r="H786" t="n">
         <v>2931931</v>
@@ -23192,7 +23192,7 @@
         <v>5.43599987030029</v>
       </c>
       <c r="G787" t="n">
-        <v>3.8245747089386</v>
+        <v>3.82457399368286</v>
       </c>
       <c r="H787" t="n">
         <v>3245860</v>
@@ -23221,7 +23221,7 @@
         <v>5.5</v>
       </c>
       <c r="G788" t="n">
-        <v>3.86960220336914</v>
+        <v>3.8696014881134</v>
       </c>
       <c r="H788" t="n">
         <v>1885870</v>
@@ -23279,7 +23279,7 @@
         <v>5.43599987030029</v>
       </c>
       <c r="G790" t="n">
-        <v>3.8245747089386</v>
+        <v>3.82457399368286</v>
       </c>
       <c r="H790" t="n">
         <v>2623020</v>
@@ -23308,7 +23308,7 @@
         <v>5.49200010299683</v>
       </c>
       <c r="G791" t="n">
-        <v>3.86397361755371</v>
+        <v>3.86397385597229</v>
       </c>
       <c r="H791" t="n">
         <v>2307388</v>
@@ -23337,7 +23337,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G792" t="n">
-        <v>3.95402979850769</v>
+        <v>3.95403075218201</v>
       </c>
       <c r="H792" t="n">
         <v>3429073</v>
@@ -23366,7 +23366,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G793" t="n">
-        <v>3.93151521682739</v>
+        <v>3.93151545524597</v>
       </c>
       <c r="H793" t="n">
         <v>2352694</v>
@@ -23395,7 +23395,7 @@
         <v>5.59800004959106</v>
       </c>
       <c r="G794" t="n">
-        <v>3.93855118751526</v>
+        <v>3.93855166435242</v>
       </c>
       <c r="H794" t="n">
         <v>2148060</v>
@@ -23424,7 +23424,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G795" t="n">
-        <v>3.98639369010925</v>
+        <v>3.98639392852783</v>
       </c>
       <c r="H795" t="n">
         <v>7441044</v>
@@ -23453,7 +23453,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G796" t="n">
-        <v>3.95121574401855</v>
+        <v>3.95121550559998</v>
       </c>
       <c r="H796" t="n">
         <v>945346</v>
@@ -23540,7 +23540,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G799" t="n">
-        <v>3.91744446754456</v>
+        <v>3.91744470596313</v>
       </c>
       <c r="H799" t="n">
         <v>2867974</v>
@@ -23569,7 +23569,7 @@
         <v>5.55800008773804</v>
       </c>
       <c r="G800" t="n">
-        <v>3.91040897369385</v>
+        <v>3.91040873527527</v>
       </c>
       <c r="H800" t="n">
         <v>2353232</v>
@@ -23656,7 +23656,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G803" t="n">
-        <v>3.92588710784912</v>
+        <v>3.92588686943054</v>
       </c>
       <c r="H803" t="n">
         <v>3693207</v>
@@ -23743,7 +23743,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G806" t="n">
-        <v>3.99061512947083</v>
+        <v>3.99061560630798</v>
       </c>
       <c r="H806" t="n">
         <v>2564951</v>
@@ -23772,7 +23772,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G807" t="n">
-        <v>3.96247291564941</v>
+        <v>3.96247267723083</v>
       </c>
       <c r="H807" t="n">
         <v>3565769</v>
@@ -23801,7 +23801,7 @@
         <v>5.67399978637695</v>
       </c>
       <c r="G808" t="n">
-        <v>3.99202299118042</v>
+        <v>3.99202251434326</v>
       </c>
       <c r="H808" t="n">
         <v>2720971</v>
@@ -23830,7 +23830,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G809" t="n">
-        <v>3.99624371528625</v>
+        <v>3.99624347686768</v>
       </c>
       <c r="H809" t="n">
         <v>1734134</v>
@@ -23859,7 +23859,7 @@
         <v>5.76800012588501</v>
       </c>
       <c r="G810" t="n">
-        <v>4.0581579208374</v>
+        <v>4.05815744400024</v>
       </c>
       <c r="H810" t="n">
         <v>2220985</v>
@@ -23946,7 +23946,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G813" t="n">
-        <v>4.01031494140625</v>
+        <v>4.01031446456909</v>
       </c>
       <c r="H813" t="n">
         <v>1717511</v>
@@ -24004,7 +24004,7 @@
         <v>5.80200004577637</v>
       </c>
       <c r="G815" t="n">
-        <v>4.0820779800415</v>
+        <v>4.08207845687866</v>
       </c>
       <c r="H815" t="n">
         <v>3271476</v>
@@ -24120,7 +24120,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G819" t="n">
-        <v>4.30581140518188</v>
+        <v>4.30581188201904</v>
       </c>
       <c r="H819" t="n">
         <v>2440838</v>
@@ -24149,7 +24149,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G820" t="n">
-        <v>4.2185697555542</v>
+        <v>4.21857023239136</v>
       </c>
       <c r="H820" t="n">
         <v>3588873</v>
@@ -24207,7 +24207,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G822" t="n">
-        <v>4.2284197807312</v>
+        <v>4.22842025756836</v>
       </c>
       <c r="H822" t="n">
         <v>2927455</v>
@@ -24265,7 +24265,7 @@
         <v>6.11199998855591</v>
       </c>
       <c r="G824" t="n">
-        <v>4.30018377304077</v>
+        <v>4.30018329620361</v>
       </c>
       <c r="H824" t="n">
         <v>2088908</v>
@@ -24294,7 +24294,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G825" t="n">
-        <v>4.27063369750977</v>
+        <v>4.27063417434692</v>
       </c>
       <c r="H825" t="n">
         <v>1721301</v>
@@ -24352,7 +24352,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G827" t="n">
-        <v>4.31988382339478</v>
+        <v>4.31988286972046</v>
       </c>
       <c r="H827" t="n">
         <v>1725683</v>
@@ -24497,7 +24497,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G832" t="n">
-        <v>4.35506153106689</v>
+        <v>4.35506200790405</v>
       </c>
       <c r="H832" t="n">
         <v>2276022</v>
@@ -24555,7 +24555,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G834" t="n">
-        <v>4.32691860198975</v>
+        <v>4.3269190788269</v>
       </c>
       <c r="H834" t="n">
         <v>2639151</v>
@@ -24613,7 +24613,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G836" t="n">
-        <v>4.12851428985596</v>
+        <v>4.12851333618164</v>
       </c>
       <c r="H836" t="n">
         <v>3944534</v>
@@ -24642,7 +24642,7 @@
         <v>5.74399995803833</v>
       </c>
       <c r="G837" t="n">
-        <v>4.04127168655396</v>
+        <v>4.0412712097168</v>
       </c>
       <c r="H837" t="n">
         <v>4004963</v>
@@ -24671,7 +24671,7 @@
         <v>5.80399990081787</v>
       </c>
       <c r="G838" t="n">
-        <v>4.08348560333252</v>
+        <v>4.08348608016968</v>
       </c>
       <c r="H838" t="n">
         <v>2885826</v>
@@ -24758,7 +24758,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G841" t="n">
-        <v>3.91181612014771</v>
+        <v>3.91181564331055</v>
       </c>
       <c r="H841" t="n">
         <v>4148352</v>
@@ -24816,7 +24816,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G843" t="n">
-        <v>4.09192752838135</v>
+        <v>4.09192800521851</v>
       </c>
       <c r="H843" t="n">
         <v>4384629</v>
@@ -24874,7 +24874,7 @@
         <v>5.56799983978271</v>
       </c>
       <c r="G845" t="n">
-        <v>3.91744446754456</v>
+        <v>3.91744470596313</v>
       </c>
       <c r="H845" t="n">
         <v>3403862</v>
@@ -24932,7 +24932,7 @@
         <v>4.78700017929077</v>
       </c>
       <c r="G847" t="n">
-        <v>3.36796116828918</v>
+        <v>3.36796164512634</v>
       </c>
       <c r="H847" t="n">
         <v>5662703</v>
@@ -24961,7 +24961,7 @@
         <v>4.7649998664856</v>
       </c>
       <c r="G848" t="n">
-        <v>3.35248255729675</v>
+        <v>3.35248231887817</v>
       </c>
       <c r="H848" t="n">
         <v>5813229</v>
@@ -24990,7 +24990,7 @@
         <v>4.11199998855591</v>
       </c>
       <c r="G849" t="n">
-        <v>2.89305520057678</v>
+        <v>2.89305543899536</v>
       </c>
       <c r="H849" t="n">
         <v>7919024</v>
@@ -25019,7 +25019,7 @@
         <v>4.41900014877319</v>
       </c>
       <c r="G850" t="n">
-        <v>3.10904955863953</v>
+        <v>3.10905003547668</v>
       </c>
       <c r="H850" t="n">
         <v>7450820</v>
@@ -25048,7 +25048,7 @@
         <v>4.28800010681152</v>
       </c>
       <c r="G851" t="n">
-        <v>3.01688289642334</v>
+        <v>3.01688241958618</v>
       </c>
       <c r="H851" t="n">
         <v>6418167</v>
@@ -25106,7 +25106,7 @@
         <v>4.48400020599365</v>
       </c>
       <c r="G853" t="n">
-        <v>3.15478134155273</v>
+        <v>3.15478157997131</v>
       </c>
       <c r="H853" t="n">
         <v>3240645</v>
@@ -25135,7 +25135,7 @@
         <v>4.56099987030029</v>
       </c>
       <c r="G854" t="n">
-        <v>3.20895504951477</v>
+        <v>3.20895600318909</v>
       </c>
       <c r="H854" t="n">
         <v>6496730</v>
@@ -25164,7 +25164,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G855" t="n">
-        <v>3.07457518577576</v>
+        <v>3.0745747089386</v>
       </c>
       <c r="H855" t="n">
         <v>10545254</v>
@@ -25193,7 +25193,7 @@
         <v>4.25899982452393</v>
       </c>
       <c r="G856" t="n">
-        <v>2.99647927284241</v>
+        <v>2.99647903442383</v>
       </c>
       <c r="H856" t="n">
         <v>4507664</v>
@@ -25280,7 +25280,7 @@
         <v>4.55000019073486</v>
       </c>
       <c r="G859" t="n">
-        <v>3.20121622085571</v>
+        <v>3.20121669769287</v>
       </c>
       <c r="H859" t="n">
         <v>5661844</v>
@@ -25309,7 +25309,7 @@
         <v>4.57100009918213</v>
       </c>
       <c r="G860" t="n">
-        <v>3.21599125862122</v>
+        <v>3.21599173545837</v>
       </c>
       <c r="H860" t="n">
         <v>2461394</v>
@@ -25338,7 +25338,7 @@
         <v>4.85900020599365</v>
       </c>
       <c r="G861" t="n">
-        <v>3.41861796379089</v>
+        <v>3.41861772537231</v>
       </c>
       <c r="H861" t="n">
         <v>2743317</v>
@@ -25367,7 +25367,7 @@
         <v>4.98899984359741</v>
       </c>
       <c r="G862" t="n">
-        <v>3.51008057594299</v>
+        <v>3.51008105278015</v>
       </c>
       <c r="H862" t="n">
         <v>3920930</v>
@@ -25396,7 +25396,7 @@
         <v>4.69399976730347</v>
       </c>
       <c r="G863" t="n">
-        <v>3.30252957344055</v>
+        <v>3.30252933502197</v>
       </c>
       <c r="H863" t="n">
         <v>2955236</v>
@@ -25425,7 +25425,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G864" t="n">
-        <v>3.40525054931641</v>
+        <v>3.40525007247925</v>
       </c>
       <c r="H864" t="n">
         <v>1508109</v>
@@ -25454,7 +25454,7 @@
         <v>4.88199996948242</v>
       </c>
       <c r="G865" t="n">
-        <v>3.4347996711731</v>
+        <v>3.43480014801025</v>
       </c>
       <c r="H865" t="n">
         <v>2776350</v>
@@ -25483,7 +25483,7 @@
         <v>4.81199979782104</v>
       </c>
       <c r="G866" t="n">
-        <v>3.38554978370667</v>
+        <v>3.38555002212524</v>
       </c>
       <c r="H866" t="n">
         <v>2520981</v>
@@ -25541,7 +25541,7 @@
         <v>4.71600008010864</v>
       </c>
       <c r="G868" t="n">
-        <v>3.31800842285156</v>
+        <v>3.31800818443298</v>
       </c>
       <c r="H868" t="n">
         <v>2606733</v>
@@ -25570,7 +25570,7 @@
         <v>4.82800006866455</v>
       </c>
       <c r="G869" t="n">
-        <v>3.39680767059326</v>
+        <v>3.39680695533752</v>
       </c>
       <c r="H869" t="n">
         <v>1149332</v>
@@ -25628,7 +25628,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G871" t="n">
-        <v>3.44042825698853</v>
+        <v>3.44042778015137</v>
       </c>
       <c r="H871" t="n">
         <v>2347024</v>
@@ -25657,7 +25657,7 @@
         <v>4.93400001525879</v>
       </c>
       <c r="G872" t="n">
-        <v>3.47138500213623</v>
+        <v>3.47138524055481</v>
       </c>
       <c r="H872" t="n">
         <v>2886869</v>
@@ -25686,7 +25686,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G873" t="n">
-        <v>3.41932129859924</v>
+        <v>3.4193217754364</v>
       </c>
       <c r="H873" t="n">
         <v>1883840</v>
@@ -25715,7 +25715,7 @@
         <v>4.86199998855591</v>
       </c>
       <c r="G874" t="n">
-        <v>3.42072820663452</v>
+        <v>3.4207284450531</v>
       </c>
       <c r="H874" t="n">
         <v>1580035</v>
@@ -25744,7 +25744,7 @@
         <v>4.68200016021729</v>
       </c>
       <c r="G875" t="n">
-        <v>3.29408717155457</v>
+        <v>3.29408669471741</v>
       </c>
       <c r="H875" t="n">
         <v>1885170</v>
@@ -25802,7 +25802,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G877" t="n">
-        <v>3.3771071434021</v>
+        <v>3.37710762023926</v>
       </c>
       <c r="H877" t="n">
         <v>2311934</v>
@@ -25831,7 +25831,7 @@
         <v>4.86399984359741</v>
       </c>
       <c r="G878" t="n">
-        <v>3.42213582992554</v>
+        <v>3.42213535308838</v>
       </c>
       <c r="H878" t="n">
         <v>1632555</v>
@@ -25889,7 +25889,7 @@
         <v>4.85400009155273</v>
       </c>
       <c r="G880" t="n">
-        <v>3.41510009765625</v>
+        <v>3.41510033607483</v>
       </c>
       <c r="H880" t="n">
         <v>2751793</v>
@@ -25918,7 +25918,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G881" t="n">
-        <v>3.42635655403137</v>
+        <v>3.42635679244995</v>
       </c>
       <c r="H881" t="n">
         <v>1909832</v>
@@ -25947,7 +25947,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G882" t="n">
-        <v>3.59169411659241</v>
+        <v>3.59169435501099</v>
       </c>
       <c r="H882" t="n">
         <v>3976280</v>
@@ -26092,7 +26092,7 @@
         <v>4.98600006103516</v>
       </c>
       <c r="G887" t="n">
-        <v>3.50797033309937</v>
+        <v>3.50797057151794</v>
       </c>
       <c r="H887" t="n">
         <v>939668</v>
@@ -26121,7 +26121,7 @@
         <v>4.94199991226196</v>
       </c>
       <c r="G888" t="n">
-        <v>3.47701334953308</v>
+        <v>3.47701358795166</v>
       </c>
       <c r="H888" t="n">
         <v>1537490</v>
@@ -26150,7 +26150,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G889" t="n">
-        <v>3.46997809410095</v>
+        <v>3.46997785568237</v>
       </c>
       <c r="H889" t="n">
         <v>1627305</v>
@@ -26179,7 +26179,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G890" t="n">
-        <v>3.48264241218567</v>
+        <v>3.48264217376709</v>
       </c>
       <c r="H890" t="n">
         <v>1701329</v>
@@ -26237,7 +26237,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G892" t="n">
-        <v>3.5529990196228</v>
+        <v>3.55299830436707</v>
       </c>
       <c r="H892" t="n">
         <v>3832249</v>
@@ -26266,7 +26266,7 @@
         <v>4.84200000762939</v>
       </c>
       <c r="G893" t="n">
-        <v>3.57692742347717</v>
+        <v>3.57692718505859</v>
       </c>
       <c r="H893" t="n">
         <v>5729697</v>
@@ -26295,7 +26295,7 @@
         <v>4.67399978637695</v>
       </c>
       <c r="G894" t="n">
-        <v>3.45282053947449</v>
+        <v>3.45282030105591</v>
       </c>
       <c r="H894" t="n">
         <v>5069170</v>
@@ -26353,7 +26353,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G896" t="n">
-        <v>3.47941541671753</v>
+        <v>3.47941470146179</v>
       </c>
       <c r="H896" t="n">
         <v>2114648</v>
@@ -26382,7 +26382,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G897" t="n">
-        <v>3.52817106246948</v>
+        <v>3.52817130088806</v>
       </c>
       <c r="H897" t="n">
         <v>1536527</v>
@@ -26411,7 +26411,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G898" t="n">
-        <v>3.59022426605225</v>
+        <v>3.59022498130798</v>
       </c>
       <c r="H898" t="n">
         <v>1285941</v>
@@ -26440,7 +26440,7 @@
         <v>4.83400011062622</v>
       </c>
       <c r="G899" t="n">
-        <v>3.57101726531982</v>
+        <v>3.5710175037384</v>
       </c>
       <c r="H899" t="n">
         <v>1897548</v>
@@ -26469,7 +26469,7 @@
         <v>4.7979998588562</v>
       </c>
       <c r="G900" t="n">
-        <v>3.5444233417511</v>
+        <v>3.54442310333252</v>
       </c>
       <c r="H900" t="n">
         <v>2992412</v>
@@ -26585,7 +26585,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G904" t="n">
-        <v>3.73796987533569</v>
+        <v>3.73797011375427</v>
       </c>
       <c r="H904" t="n">
         <v>2834004</v>
@@ -26614,7 +26614,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G905" t="n">
-        <v>3.82661819458008</v>
+        <v>3.8266179561615</v>
       </c>
       <c r="H905" t="n">
         <v>2792947</v>
@@ -26672,7 +26672,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G907" t="n">
-        <v>3.82661819458008</v>
+        <v>3.8266179561615</v>
       </c>
       <c r="H907" t="n">
         <v>3358447</v>
@@ -26701,7 +26701,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G908" t="n">
-        <v>3.85247349739075</v>
+        <v>3.85247302055359</v>
       </c>
       <c r="H908" t="n">
         <v>2032208</v>
@@ -26730,7 +26730,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G909" t="n">
-        <v>3.76013207435608</v>
+        <v>3.76013231277466</v>
       </c>
       <c r="H909" t="n">
         <v>3188797</v>
@@ -26759,7 +26759,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G910" t="n">
-        <v>3.71580862998962</v>
+        <v>3.71580910682678</v>
       </c>
       <c r="H910" t="n">
         <v>2743541</v>
@@ -26817,7 +26817,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G912" t="n">
-        <v>3.7527449131012</v>
+        <v>3.75274467468262</v>
       </c>
       <c r="H912" t="n">
         <v>4391555</v>
@@ -26846,7 +26846,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G913" t="n">
-        <v>3.82661819458008</v>
+        <v>3.8266179561615</v>
       </c>
       <c r="H913" t="n">
         <v>4189234</v>
@@ -26875,7 +26875,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G914" t="n">
-        <v>3.91157174110413</v>
+        <v>3.91157150268555</v>
       </c>
       <c r="H914" t="n">
         <v>3512294</v>
@@ -26904,7 +26904,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G915" t="n">
-        <v>3.88571619987488</v>
+        <v>3.88571643829346</v>
       </c>
       <c r="H915" t="n">
         <v>3188279</v>
@@ -26933,7 +26933,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G916" t="n">
-        <v>3.93373346328735</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H916" t="n">
         <v>2794030</v>
@@ -26962,7 +26962,7 @@
         <v>5.375</v>
       </c>
       <c r="G917" t="n">
-        <v>3.97067022323608</v>
+        <v>3.97066974639893</v>
       </c>
       <c r="H917" t="n">
         <v>5566875</v>
@@ -26991,7 +26991,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G918" t="n">
-        <v>3.88571619987488</v>
+        <v>3.88571643829346</v>
       </c>
       <c r="H918" t="n">
         <v>2502322</v>
@@ -27049,7 +27049,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G920" t="n">
-        <v>3.84877943992615</v>
+        <v>3.84877991676331</v>
       </c>
       <c r="H920" t="n">
         <v>2233213</v>
@@ -27078,7 +27078,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G921" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H921" t="n">
         <v>3095595</v>
@@ -27136,7 +27136,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G923" t="n">
-        <v>3.84877943992615</v>
+        <v>3.84877991676331</v>
       </c>
       <c r="H923" t="n">
         <v>1408843</v>
@@ -27281,7 +27281,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G928" t="n">
-        <v>3.89679741859436</v>
+        <v>3.89679718017578</v>
       </c>
       <c r="H928" t="n">
         <v>1385968</v>
@@ -27339,7 +27339,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G930" t="n">
-        <v>3.88202261924744</v>
+        <v>3.88202285766602</v>
       </c>
       <c r="H930" t="n">
         <v>1410213</v>
@@ -27368,7 +27368,7 @@
         <v>5.125</v>
       </c>
       <c r="G931" t="n">
-        <v>3.78598761558533</v>
+        <v>3.78598713874817</v>
       </c>
       <c r="H931" t="n">
         <v>2346143</v>
@@ -27397,7 +27397,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G932" t="n">
-        <v>3.79337525367737</v>
+        <v>3.79337501525879</v>
       </c>
       <c r="H932" t="n">
         <v>2175651</v>
@@ -27426,7 +27426,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G933" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H933" t="n">
         <v>1504744</v>
@@ -27484,7 +27484,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G935" t="n">
-        <v>3.80076217651367</v>
+        <v>3.80076241493225</v>
       </c>
       <c r="H935" t="n">
         <v>2443627</v>
@@ -27513,7 +27513,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G936" t="n">
-        <v>3.80445599555969</v>
+        <v>3.80445575714111</v>
       </c>
       <c r="H936" t="n">
         <v>1769531</v>
@@ -27571,7 +27571,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G938" t="n">
-        <v>3.90049052238464</v>
+        <v>3.90049076080322</v>
       </c>
       <c r="H938" t="n">
         <v>1613100</v>
@@ -27600,7 +27600,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G939" t="n">
-        <v>3.94850778579712</v>
+        <v>3.9485080242157</v>
       </c>
       <c r="H939" t="n">
         <v>2557114</v>
@@ -27629,7 +27629,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G940" t="n">
-        <v>3.93004012107849</v>
+        <v>3.93004059791565</v>
       </c>
       <c r="H940" t="n">
         <v>1145389</v>
@@ -27658,7 +27658,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G941" t="n">
-        <v>3.91895890235901</v>
+        <v>3.91895842552185</v>
       </c>
       <c r="H941" t="n">
         <v>1621120</v>
@@ -27687,7 +27687,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G942" t="n">
-        <v>3.87463450431824</v>
+        <v>3.87463545799255</v>
       </c>
       <c r="H942" t="n">
         <v>2057182</v>
@@ -27716,7 +27716,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G943" t="n">
-        <v>3.95220184326172</v>
+        <v>3.95220136642456</v>
       </c>
       <c r="H943" t="n">
         <v>3126340</v>
@@ -27745,7 +27745,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G944" t="n">
-        <v>4.07778549194336</v>
+        <v>4.0777850151062</v>
       </c>
       <c r="H944" t="n">
         <v>3399468</v>
@@ -27803,7 +27803,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>4.03346252441406</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H946" t="n">
         <v>2526362</v>
@@ -27832,7 +27832,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G947" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868677139282</v>
       </c>
       <c r="H947" t="n">
         <v>5104622</v>
@@ -27861,7 +27861,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G948" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868677139282</v>
       </c>
       <c r="H948" t="n">
         <v>2449394</v>
@@ -27890,7 +27890,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>4.03346252441406</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H949" t="n">
         <v>1923021</v>
@@ -27919,7 +27919,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G950" t="n">
-        <v>3.98544454574585</v>
+        <v>3.98544478416443</v>
       </c>
       <c r="H950" t="n">
         <v>2544347</v>
@@ -27948,7 +27948,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G951" t="n">
-        <v>3.98913860321045</v>
+        <v>3.98913836479187</v>
       </c>
       <c r="H951" t="n">
         <v>1899163</v>
@@ -27977,7 +27977,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G952" t="n">
-        <v>4.04454326629639</v>
+        <v>4.04454278945923</v>
       </c>
       <c r="H952" t="n">
         <v>2144893</v>
@@ -28006,7 +28006,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G953" t="n">
-        <v>4.10364055633545</v>
+        <v>4.10364103317261</v>
       </c>
       <c r="H953" t="n">
         <v>1188557</v>
@@ -28064,7 +28064,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G955" t="n">
-        <v>4.23291921615601</v>
+        <v>4.23291873931885</v>
       </c>
       <c r="H955" t="n">
         <v>2175172</v>
@@ -28093,7 +28093,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>4.20336961746216</v>
+        <v>4.20337009429932</v>
       </c>
       <c r="H956" t="n">
         <v>2050585</v>
@@ -28122,7 +28122,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G957" t="n">
-        <v>4.18859577178955</v>
+        <v>4.18859529495239</v>
       </c>
       <c r="H957" t="n">
         <v>1720771</v>
@@ -28151,7 +28151,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G958" t="n">
-        <v>4.17751455307007</v>
+        <v>4.17751407623291</v>
       </c>
       <c r="H958" t="n">
         <v>2277890</v>
@@ -28180,7 +28180,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G959" t="n">
-        <v>4.12210893630981</v>
+        <v>4.12210941314697</v>
       </c>
       <c r="H959" t="n">
         <v>1853234</v>
@@ -28209,7 +28209,7 @@
         <v>5.67000007629395</v>
       </c>
       <c r="G960" t="n">
-        <v>4.18859577178955</v>
+        <v>4.18859529495239</v>
       </c>
       <c r="H960" t="n">
         <v>1985046</v>
@@ -28296,7 +28296,7 @@
         <v>5.59000015258789</v>
       </c>
       <c r="G963" t="n">
-        <v>4.12949657440186</v>
+        <v>4.12949705123901</v>
       </c>
       <c r="H963" t="n">
         <v>1881728</v>
@@ -28325,7 +28325,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G964" t="n">
-        <v>4.11841583251953</v>
+        <v>4.11841630935669</v>
       </c>
       <c r="H964" t="n">
         <v>1601622</v>
@@ -28354,7 +28354,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>4.03346252441406</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H965" t="n">
         <v>1639295</v>
@@ -28383,7 +28383,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G966" t="n">
-        <v>3.98913860321045</v>
+        <v>3.98913836479187</v>
       </c>
       <c r="H966" t="n">
         <v>1127368</v>
@@ -28412,7 +28412,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G967" t="n">
-        <v>3.95958948135376</v>
+        <v>3.9595890045166</v>
       </c>
       <c r="H967" t="n">
         <v>1898539</v>
@@ -28441,7 +28441,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>3.98544454574585</v>
+        <v>3.98544478416443</v>
       </c>
       <c r="H968" t="n">
         <v>2469349</v>
@@ -28470,7 +28470,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G969" t="n">
-        <v>3.95958948135376</v>
+        <v>3.9595890045166</v>
       </c>
       <c r="H969" t="n">
         <v>1553786</v>
@@ -28557,7 +28557,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G972" t="n">
-        <v>3.90049052238464</v>
+        <v>3.90049076080322</v>
       </c>
       <c r="H972" t="n">
         <v>2466907</v>
@@ -28586,7 +28586,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G973" t="n">
-        <v>3.99652528762817</v>
+        <v>3.99652504920959</v>
       </c>
       <c r="H973" t="n">
         <v>1022879</v>
@@ -28615,7 +28615,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G974" t="n">
-        <v>3.91895890235901</v>
+        <v>3.91895842552185</v>
       </c>
       <c r="H974" t="n">
         <v>1534527</v>
@@ -28731,7 +28731,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>3.94112110137939</v>
+        <v>3.94112086296082</v>
       </c>
       <c r="H978" t="n">
         <v>1454082</v>
@@ -28760,7 +28760,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G979" t="n">
-        <v>3.99652528762817</v>
+        <v>3.99652504920959</v>
       </c>
       <c r="H979" t="n">
         <v>1645876</v>
@@ -28818,7 +28818,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G981" t="n">
-        <v>3.98913860321045</v>
+        <v>3.98913836479187</v>
       </c>
       <c r="H981" t="n">
         <v>1899740</v>
@@ -28847,7 +28847,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G982" t="n">
-        <v>4.00021886825562</v>
+        <v>4.00021934509277</v>
       </c>
       <c r="H982" t="n">
         <v>2939840</v>
@@ -28905,7 +28905,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G984" t="n">
-        <v>3.97805738449097</v>
+        <v>3.97805786132812</v>
       </c>
       <c r="H984" t="n">
         <v>1253572</v>
@@ -28934,7 +28934,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G985" t="n">
-        <v>3.97436332702637</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H985" t="n">
         <v>1083034</v>
@@ -28963,7 +28963,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G986" t="n">
-        <v>3.98175096511841</v>
+        <v>3.98175048828125</v>
       </c>
       <c r="H986" t="n">
         <v>993070</v>
@@ -28992,7 +28992,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G987" t="n">
-        <v>3.95220184326172</v>
+        <v>3.95220136642456</v>
       </c>
       <c r="H987" t="n">
         <v>958950</v>
@@ -29050,7 +29050,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G989" t="n">
-        <v>4.0149941444397</v>
+        <v>4.01499366760254</v>
       </c>
       <c r="H989" t="n">
         <v>1082552</v>
@@ -29079,7 +29079,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G990" t="n">
-        <v>3.97805738449097</v>
+        <v>3.97805786132812</v>
       </c>
       <c r="H990" t="n">
         <v>1250603</v>
@@ -29108,7 +29108,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G991" t="n">
-        <v>3.93373346328735</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H991" t="n">
         <v>1650357</v>
@@ -29166,7 +29166,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G993" t="n">
-        <v>3.90418410301208</v>
+        <v>3.90418434143066</v>
       </c>
       <c r="H993" t="n">
         <v>949710</v>
@@ -29195,7 +29195,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G994" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H994" t="n">
         <v>5985952</v>
@@ -29224,7 +29224,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>3.72688937187195</v>
+        <v>3.72688889503479</v>
       </c>
       <c r="H995" t="n">
         <v>2989212</v>
@@ -29253,7 +29253,7 @@
         <v>5.15500020980835</v>
       </c>
       <c r="G996" t="n">
-        <v>3.80814981460571</v>
+        <v>3.80814957618713</v>
       </c>
       <c r="H996" t="n">
         <v>2614866</v>
@@ -29282,7 +29282,7 @@
         <v>5.13500022888184</v>
       </c>
       <c r="G997" t="n">
-        <v>3.79337525367737</v>
+        <v>3.79337501525879</v>
       </c>
       <c r="H997" t="n">
         <v>1790034</v>
@@ -29369,7 +29369,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1000" t="n">
-        <v>3.88941025733948</v>
+        <v>3.88940954208374</v>
       </c>
       <c r="H1000" t="n">
         <v>2403958</v>
@@ -29398,7 +29398,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1001" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H1001" t="n">
         <v>1891362</v>
@@ -29485,7 +29485,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1004" t="n">
-        <v>3.8155369758606</v>
+        <v>3.81553673744202</v>
       </c>
       <c r="H1004" t="n">
         <v>1489183</v>
@@ -29514,7 +29514,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1005" t="n">
-        <v>3.76013207435608</v>
+        <v>3.76013231277466</v>
       </c>
       <c r="H1005" t="n">
         <v>1739532</v>
@@ -29543,7 +29543,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1006" t="n">
-        <v>3.73796987533569</v>
+        <v>3.73797011375427</v>
       </c>
       <c r="H1006" t="n">
         <v>1078704</v>
@@ -29601,7 +29601,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1008" t="n">
-        <v>3.72688937187195</v>
+        <v>3.72688889503479</v>
       </c>
       <c r="H1008" t="n">
         <v>1959502</v>
@@ -29630,7 +29630,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1009" t="n">
-        <v>3.72319555282593</v>
+        <v>3.72319507598877</v>
       </c>
       <c r="H1009" t="n">
         <v>1279485</v>
@@ -29659,7 +29659,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G1010" t="n">
-        <v>3.55328750610352</v>
+        <v>3.55328798294067</v>
       </c>
       <c r="H1010" t="n">
         <v>2471336</v>
@@ -29688,7 +29688,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G1011" t="n">
-        <v>3.5680627822876</v>
+        <v>3.56806254386902</v>
       </c>
       <c r="H1011" t="n">
         <v>2665724</v>
@@ -29717,7 +29717,7 @@
         <v>4.96199989318848</v>
       </c>
       <c r="G1012" t="n">
-        <v>3.66557478904724</v>
+        <v>3.66557502746582</v>
       </c>
       <c r="H1012" t="n">
         <v>1986330</v>
@@ -29746,7 +29746,7 @@
         <v>4.96600008010864</v>
       </c>
       <c r="G1013" t="n">
-        <v>3.66852951049805</v>
+        <v>3.66852974891663</v>
       </c>
       <c r="H1013" t="n">
         <v>2470620</v>
@@ -29804,7 +29804,7 @@
         <v>5.19000005722046</v>
       </c>
       <c r="G1015" t="n">
-        <v>3.8340048789978</v>
+        <v>3.83400535583496</v>
       </c>
       <c r="H1015" t="n">
         <v>2422991</v>
@@ -29891,7 +29891,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1018" t="n">
-        <v>3.90787816047668</v>
+        <v>3.90787839889526</v>
       </c>
       <c r="H1018" t="n">
         <v>3067531</v>
@@ -29920,7 +29920,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G1019" t="n">
-        <v>3.93004012107849</v>
+        <v>3.93004059791565</v>
       </c>
       <c r="H1019" t="n">
         <v>1796510</v>
@@ -29949,7 +29949,7 @@
         <v>5.30499982833862</v>
       </c>
       <c r="G1020" t="n">
-        <v>3.91895890235901</v>
+        <v>3.91895842552185</v>
       </c>
       <c r="H1020" t="n">
         <v>2327757</v>
@@ -29978,7 +29978,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1021" t="n">
-        <v>3.93373346328735</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H1021" t="n">
         <v>1911921</v>
@@ -30065,7 +30065,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1024" t="n">
-        <v>3.90049052238464</v>
+        <v>3.90049076080322</v>
       </c>
       <c r="H1024" t="n">
         <v>1912482</v>
@@ -30094,7 +30094,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1025" t="n">
-        <v>3.93373346328735</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H1025" t="n">
         <v>1560177</v>
@@ -30123,7 +30123,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1026" t="n">
-        <v>3.95958948135376</v>
+        <v>3.9595890045166</v>
       </c>
       <c r="H1026" t="n">
         <v>1785365</v>
@@ -30152,7 +30152,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1027" t="n">
-        <v>3.98175096511841</v>
+        <v>3.98175048828125</v>
       </c>
       <c r="H1027" t="n">
         <v>886438</v>
@@ -30210,7 +30210,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1029" t="n">
-        <v>3.97436332702637</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H1029" t="n">
         <v>1375106</v>
@@ -30239,7 +30239,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G1030" t="n">
-        <v>3.99283266067505</v>
+        <v>3.99283194541931</v>
       </c>
       <c r="H1030" t="n">
         <v>1587588</v>
@@ -30268,7 +30268,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G1031" t="n">
-        <v>3.96697568893433</v>
+        <v>3.96697616577148</v>
       </c>
       <c r="H1031" t="n">
         <v>904133</v>
@@ -30326,7 +30326,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G1033" t="n">
-        <v>3.97436332702637</v>
+        <v>3.97436380386353</v>
       </c>
       <c r="H1033" t="n">
         <v>2221291</v>
@@ -30355,7 +30355,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G1034" t="n">
-        <v>3.955894947052</v>
+        <v>3.95589542388916</v>
       </c>
       <c r="H1034" t="n">
         <v>2699430</v>
@@ -30384,7 +30384,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1035" t="n">
-        <v>3.98913860321045</v>
+        <v>3.98913836479187</v>
       </c>
       <c r="H1035" t="n">
         <v>1652889</v>
@@ -30413,7 +30413,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1036" t="n">
-        <v>3.90418410301208</v>
+        <v>3.90418434143066</v>
       </c>
       <c r="H1036" t="n">
         <v>2023466</v>
@@ -30442,7 +30442,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G1037" t="n">
-        <v>3.90787816047668</v>
+        <v>3.90787839889526</v>
       </c>
       <c r="H1037" t="n">
         <v>1571198</v>
@@ -30471,7 +30471,7 @@
         <v>5.34499979019165</v>
       </c>
       <c r="G1038" t="n">
-        <v>3.94850778579712</v>
+        <v>3.9485080242157</v>
       </c>
       <c r="H1038" t="n">
         <v>1605404</v>
@@ -30500,7 +30500,7 @@
         <v>5.29500007629395</v>
       </c>
       <c r="G1039" t="n">
-        <v>3.91157174110413</v>
+        <v>3.91157150268555</v>
       </c>
       <c r="H1039" t="n">
         <v>1245963</v>
@@ -30587,7 +30587,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G1042" t="n">
-        <v>3.77121305465698</v>
+        <v>3.77121329307556</v>
       </c>
       <c r="H1042" t="n">
         <v>1471582</v>
@@ -30645,7 +30645,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1044" t="n">
-        <v>3.7527449131012</v>
+        <v>3.75274467468262</v>
       </c>
       <c r="H1044" t="n">
         <v>1724521</v>
@@ -30674,7 +30674,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1045" t="n">
-        <v>3.7527449131012</v>
+        <v>3.75274467468262</v>
       </c>
       <c r="H1045" t="n">
         <v>2889221</v>
@@ -30703,7 +30703,7 @@
         <v>5.14499998092651</v>
       </c>
       <c r="G1046" t="n">
-        <v>3.80076217651367</v>
+        <v>3.80076241493225</v>
       </c>
       <c r="H1046" t="n">
         <v>3242125</v>
@@ -30732,7 +30732,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G1047" t="n">
-        <v>3.73427653312683</v>
+        <v>3.73427677154541</v>
       </c>
       <c r="H1047" t="n">
         <v>3293551</v>
@@ -30761,7 +30761,7 @@
         <v>4.93599987030029</v>
       </c>
       <c r="G1048" t="n">
-        <v>3.64636778831482</v>
+        <v>3.64636754989624</v>
       </c>
       <c r="H1048" t="n">
         <v>2603514</v>
@@ -30790,7 +30790,7 @@
         <v>5.05499982833862</v>
       </c>
       <c r="G1049" t="n">
-        <v>3.73427653312683</v>
+        <v>3.73427677154541</v>
       </c>
       <c r="H1049" t="n">
         <v>1976003</v>
@@ -30848,7 +30848,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1051" t="n">
-        <v>3.79706859588623</v>
+        <v>3.79706883430481</v>
       </c>
       <c r="H1051" t="n">
         <v>864928</v>
@@ -30877,7 +30877,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1052" t="n">
-        <v>3.82292437553406</v>
+        <v>3.82292461395264</v>
       </c>
       <c r="H1052" t="n">
         <v>997301</v>
@@ -30935,7 +30935,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1054" t="n">
-        <v>3.82661819458008</v>
+        <v>3.8266179561615</v>
       </c>
       <c r="H1054" t="n">
         <v>1737746</v>
@@ -30964,7 +30964,7 @@
         <v>5.13000011444092</v>
       </c>
       <c r="G1055" t="n">
-        <v>3.78968143463135</v>
+        <v>3.78968119621277</v>
       </c>
       <c r="H1055" t="n">
         <v>1338592</v>
@@ -31022,7 +31022,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1057" t="n">
-        <v>3.8155369758606</v>
+        <v>3.81553673744202</v>
       </c>
       <c r="H1057" t="n">
         <v>2170667</v>
@@ -31051,7 +31051,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1058" t="n">
-        <v>3.80445599555969</v>
+        <v>3.80445575714111</v>
       </c>
       <c r="H1058" t="n">
         <v>1626587</v>
@@ -31080,7 +31080,7 @@
         <v>5.125</v>
       </c>
       <c r="G1059" t="n">
-        <v>3.78598761558533</v>
+        <v>3.78598713874817</v>
       </c>
       <c r="H1059" t="n">
         <v>1492843</v>
@@ -31138,7 +31138,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1061" t="n">
-        <v>3.8155369758606</v>
+        <v>3.81553673744202</v>
       </c>
       <c r="H1061" t="n">
         <v>2077033</v>
@@ -31196,7 +31196,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1063" t="n">
-        <v>3.7527449131012</v>
+        <v>3.75274467468262</v>
       </c>
       <c r="H1063" t="n">
         <v>1476058</v>
@@ -31225,7 +31225,7 @@
         <v>5.08500003814697</v>
       </c>
       <c r="G1064" t="n">
-        <v>3.75643873214722</v>
+        <v>3.75643849372864</v>
       </c>
       <c r="H1064" t="n">
         <v>1665111</v>
@@ -31283,7 +31283,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G1066" t="n">
-        <v>3.71580862998962</v>
+        <v>3.71580910682678</v>
       </c>
       <c r="H1066" t="n">
         <v>1548248</v>
@@ -31312,7 +31312,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1067" t="n">
-        <v>3.65523266792297</v>
+        <v>3.65523290634155</v>
       </c>
       <c r="H1067" t="n">
         <v>2042790</v>
@@ -31341,7 +31341,7 @@
         <v>4.93200016021729</v>
       </c>
       <c r="G1068" t="n">
-        <v>3.64341306686401</v>
+        <v>3.64341282844543</v>
       </c>
       <c r="H1068" t="n">
         <v>1798815</v>
@@ -31370,7 +31370,7 @@
         <v>5</v>
       </c>
       <c r="G1069" t="n">
-        <v>3.69364643096924</v>
+        <v>3.6936469078064</v>
       </c>
       <c r="H1069" t="n">
         <v>1936550</v>
@@ -31399,7 +31399,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1070" t="n">
-        <v>3.72319555282593</v>
+        <v>3.72319507598877</v>
       </c>
       <c r="H1070" t="n">
         <v>2008248</v>
@@ -31428,7 +31428,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1071" t="n">
-        <v>3.73058319091797</v>
+        <v>3.73058295249939</v>
       </c>
       <c r="H1071" t="n">
         <v>1816077</v>
@@ -31457,7 +31457,7 @@
         <v>4.9980001449585</v>
       </c>
       <c r="G1072" t="n">
-        <v>3.69216895103455</v>
+        <v>3.69216871261597</v>
       </c>
       <c r="H1072" t="n">
         <v>2258732</v>
@@ -31515,7 +31515,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G1074" t="n">
-        <v>3.6744396686554</v>
+        <v>3.67443943023682</v>
       </c>
       <c r="H1074" t="n">
         <v>1922675</v>
@@ -31544,7 +31544,7 @@
         <v>4.94799995422363</v>
       </c>
       <c r="G1075" t="n">
-        <v>3.65523266792297</v>
+        <v>3.65523290634155</v>
       </c>
       <c r="H1075" t="n">
         <v>1931556</v>
@@ -31573,7 +31573,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1076" t="n">
-        <v>3.7527449131012</v>
+        <v>3.75274467468262</v>
       </c>
       <c r="H1076" t="n">
         <v>4162150</v>
@@ -31602,7 +31602,7 @@
         <v>5.10500001907349</v>
       </c>
       <c r="G1077" t="n">
-        <v>3.77121305465698</v>
+        <v>3.77121329307556</v>
       </c>
       <c r="H1077" t="n">
         <v>3016029</v>
@@ -31660,7 +31660,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1079" t="n">
-        <v>3.82292437553406</v>
+        <v>3.82292461395264</v>
       </c>
       <c r="H1079" t="n">
         <v>3127369</v>
@@ -31689,7 +31689,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G1080" t="n">
-        <v>3.774906873703</v>
+        <v>3.77490663528442</v>
       </c>
       <c r="H1080" t="n">
         <v>2155949</v>
@@ -31718,7 +31718,7 @@
         <v>5.17500019073486</v>
       </c>
       <c r="G1081" t="n">
-        <v>3.82292437553406</v>
+        <v>3.82292461395264</v>
       </c>
       <c r="H1081" t="n">
         <v>2606261</v>
@@ -31747,7 +31747,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G1082" t="n">
-        <v>3.80445599555969</v>
+        <v>3.80445575714111</v>
       </c>
       <c r="H1082" t="n">
         <v>1112150</v>
@@ -31776,7 +31776,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1083" t="n">
-        <v>3.8155369758606</v>
+        <v>3.81553673744202</v>
       </c>
       <c r="H1083" t="n">
         <v>1123876</v>
@@ -31805,7 +31805,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G1084" t="n">
-        <v>3.82661819458008</v>
+        <v>3.8266179561615</v>
       </c>
       <c r="H1084" t="n">
         <v>1656774</v>
@@ -31834,7 +31834,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1085" t="n">
-        <v>3.7527449131012</v>
+        <v>3.75274467468262</v>
       </c>
       <c r="H1085" t="n">
         <v>2269955</v>
@@ -31863,7 +31863,7 @@
         <v>5.06500005722046</v>
       </c>
       <c r="G1086" t="n">
-        <v>3.74166393280029</v>
+        <v>3.74166417121887</v>
       </c>
       <c r="H1086" t="n">
         <v>1637484</v>
@@ -31950,7 +31950,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G1089" t="n">
-        <v>3.71950197219849</v>
+        <v>3.71950244903564</v>
       </c>
       <c r="H1089" t="n">
         <v>2147591</v>
@@ -32008,7 +32008,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>3.72319555282593</v>
+        <v>3.72319507598877</v>
       </c>
       <c r="H1091" t="n">
         <v>3177909</v>
@@ -32153,7 +32153,7 @@
         <v>4.87599992752075</v>
       </c>
       <c r="G1096" t="n">
-        <v>3.60204434394836</v>
+        <v>3.60204410552979</v>
       </c>
       <c r="H1096" t="n">
         <v>2719554</v>
@@ -32182,7 +32182,7 @@
         <v>4.9539999961853</v>
       </c>
       <c r="G1097" t="n">
-        <v>3.65966510772705</v>
+        <v>3.65966534614563</v>
       </c>
       <c r="H1097" t="n">
         <v>3749789</v>
@@ -32211,7 +32211,7 @@
         <v>4.92199993133545</v>
       </c>
       <c r="G1098" t="n">
-        <v>3.63602542877197</v>
+        <v>3.63602590560913</v>
       </c>
       <c r="H1098" t="n">
         <v>2381518</v>
@@ -32269,7 +32269,7 @@
         <v>5.125</v>
       </c>
       <c r="G1100" t="n">
-        <v>3.78598761558533</v>
+        <v>3.78598713874817</v>
       </c>
       <c r="H1100" t="n">
         <v>4530532</v>
@@ -32385,7 +32385,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1104" t="n">
-        <v>3.90049052238464</v>
+        <v>3.90049076080322</v>
       </c>
       <c r="H1104" t="n">
         <v>2675850</v>
@@ -32414,7 +32414,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1105" t="n">
-        <v>3.93373346328735</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H1105" t="n">
         <v>2497840</v>
@@ -32443,7 +32443,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G1106" t="n">
-        <v>3.94112110137939</v>
+        <v>3.94112086296082</v>
       </c>
       <c r="H1106" t="n">
         <v>2467377</v>
@@ -32472,7 +32472,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G1107" t="n">
-        <v>3.90049052238464</v>
+        <v>3.90049076080322</v>
       </c>
       <c r="H1107" t="n">
         <v>2996418</v>
@@ -32530,7 +32530,7 @@
         <v>5.32499980926514</v>
       </c>
       <c r="G1109" t="n">
-        <v>3.93373346328735</v>
+        <v>3.93373370170593</v>
       </c>
       <c r="H1109" t="n">
         <v>3123703</v>
@@ -32588,7 +32588,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>4.03346252441406</v>
+        <v>4.0334620475769</v>
       </c>
       <c r="H1111" t="n">
         <v>2094736</v>
@@ -32675,7 +32675,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G1114" t="n">
-        <v>4.1331901550293</v>
+        <v>4.13319063186646</v>
       </c>
       <c r="H1114" t="n">
         <v>1962864</v>
@@ -32704,7 +32704,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1115" t="n">
-        <v>4.10364055633545</v>
+        <v>4.10364103317261</v>
       </c>
       <c r="H1115" t="n">
         <v>2218958</v>
@@ -32820,7 +32820,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1119" t="n">
-        <v>4.07483005523682</v>
+        <v>4.07483053207397</v>
       </c>
       <c r="H1119" t="n">
         <v>2019828</v>
@@ -32878,7 +32878,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1121" t="n">
-        <v>3.98913860321045</v>
+        <v>3.98913836479187</v>
       </c>
       <c r="H1121" t="n">
         <v>2065025</v>
@@ -32907,7 +32907,7 @@
         <v>5.37799978256226</v>
       </c>
       <c r="G1122" t="n">
-        <v>3.97288632392883</v>
+        <v>3.97288608551025</v>
       </c>
       <c r="H1122" t="n">
         <v>1740931</v>
@@ -32936,7 +32936,7 @@
         <v>5.35200023651123</v>
       </c>
       <c r="G1123" t="n">
-        <v>3.95367932319641</v>
+        <v>3.95367908477783</v>
       </c>
       <c r="H1123" t="n">
         <v>4816518</v>
@@ -32994,7 +32994,7 @@
         <v>5.3439998626709</v>
       </c>
       <c r="G1125" t="n">
-        <v>3.9477698802948</v>
+        <v>3.94776940345764</v>
       </c>
       <c r="H1125" t="n">
         <v>1564931</v>
@@ -33023,7 +33023,7 @@
         <v>5.40199995040894</v>
       </c>
       <c r="G1126" t="n">
-        <v>3.99061560630798</v>
+        <v>3.99061608314514</v>
       </c>
       <c r="H1126" t="n">
         <v>2028839</v>
@@ -33052,7 +33052,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1127" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868677139282</v>
       </c>
       <c r="H1127" t="n">
         <v>2005279</v>
@@ -33168,7 +33168,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G1131" t="n">
-        <v>4.01868724822998</v>
+        <v>4.01868677139282</v>
       </c>
       <c r="H1131" t="n">
         <v>1960723</v>
@@ -33197,7 +33197,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1132" t="n">
-        <v>4.00982284545898</v>
+        <v>4.00982236862183</v>
       </c>
       <c r="H1132" t="n">
         <v>824423</v>
@@ -33226,7 +33226,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1133" t="n">
-        <v>3.99948024749756</v>
+        <v>3.9994809627533</v>
       </c>
       <c r="H1133" t="n">
         <v>1193698</v>
@@ -33255,7 +33255,7 @@
         <v>5.41599988937378</v>
       </c>
       <c r="G1134" t="n">
-        <v>4.00095844268799</v>
+        <v>4.00095796585083</v>
       </c>
       <c r="H1134" t="n">
         <v>1133816</v>
@@ -33284,7 +33284,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1135" t="n">
-        <v>3.99948024749756</v>
+        <v>3.9994809627533</v>
       </c>
       <c r="H1135" t="n">
         <v>1428918</v>
@@ -33313,7 +33313,7 @@
         <v>5.42199993133545</v>
       </c>
       <c r="G1136" t="n">
-        <v>4.00539064407349</v>
+        <v>4.00539016723633</v>
       </c>
       <c r="H1136" t="n">
         <v>1582993</v>
@@ -33371,7 +33371,7 @@
         <v>5.44799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>4.02459669113159</v>
+        <v>4.02459716796875</v>
       </c>
       <c r="H1138" t="n">
         <v>2263497</v>
@@ -33400,7 +33400,7 @@
         <v>5.42399978637695</v>
       </c>
       <c r="G1139" t="n">
-        <v>4.0068678855896</v>
+        <v>4.00686740875244</v>
       </c>
       <c r="H1139" t="n">
         <v>4662672</v>
@@ -33429,7 +33429,7 @@
         <v>5.46400022506714</v>
       </c>
       <c r="G1140" t="n">
-        <v>4.03641748428345</v>
+        <v>4.03641700744629</v>
       </c>
       <c r="H1140" t="n">
         <v>2351103</v>
@@ -33516,7 +33516,7 @@
         <v>5.48400020599365</v>
       </c>
       <c r="G1143" t="n">
-        <v>4.05119228363037</v>
+        <v>4.05119180679321</v>
       </c>
       <c r="H1143" t="n">
         <v>3619513</v>
@@ -33632,7 +33632,7 @@
         <v>5.63800001144409</v>
       </c>
       <c r="G1147" t="n">
-        <v>4.16495609283447</v>
+        <v>4.16495561599731</v>
       </c>
       <c r="H1147" t="n">
         <v>3027890</v>
@@ -33661,7 +33661,7 @@
         <v>5.62599992752075</v>
       </c>
       <c r="G1148" t="n">
-        <v>4.15609121322632</v>
+        <v>4.15609073638916</v>
       </c>
       <c r="H1148" t="n">
         <v>1717707</v>
@@ -33690,7 +33690,7 @@
         <v>5.62599992752075</v>
       </c>
       <c r="G1149" t="n">
-        <v>4.15609121322632</v>
+        <v>4.15609073638916</v>
       </c>
       <c r="H1149" t="n">
         <v>2064703</v>
@@ -33835,7 +33835,7 @@
         <v>5.43200016021729</v>
       </c>
       <c r="G1154" t="n">
-        <v>4.20139217376709</v>
+        <v>4.20139169692993</v>
       </c>
       <c r="H1154" t="n">
         <v>1854970</v>
@@ -33864,7 +33864,7 @@
         <v>5.39200019836426</v>
       </c>
       <c r="G1155" t="n">
-        <v>4.17045450210571</v>
+        <v>4.17045402526855</v>
       </c>
       <c r="H1155" t="n">
         <v>3144738</v>
@@ -33893,7 +33893,7 @@
         <v>5.42799997329712</v>
       </c>
       <c r="G1156" t="n">
-        <v>4.19829845428467</v>
+        <v>4.19829797744751</v>
       </c>
       <c r="H1156" t="n">
         <v>1532118</v>
@@ -33922,7 +33922,7 @@
         <v>5.41400003433228</v>
       </c>
       <c r="G1157" t="n">
-        <v>4.18746995925903</v>
+        <v>4.18747043609619</v>
       </c>
       <c r="H1157" t="n">
         <v>1217874</v>
@@ -33951,7 +33951,7 @@
         <v>5.43400001525879</v>
       </c>
       <c r="G1158" t="n">
-        <v>4.2029390335083</v>
+        <v>4.20293855667114</v>
       </c>
       <c r="H1158" t="n">
         <v>1718866</v>
@@ -34154,7 +34154,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1165" t="n">
-        <v>4.3096752166748</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1165" t="n">
         <v>1393951</v>
@@ -34183,7 +34183,7 @@
         <v>5.60599994659424</v>
       </c>
       <c r="G1166" t="n">
-        <v>4.33597230911255</v>
+        <v>4.33597278594971</v>
       </c>
       <c r="H1166" t="n">
         <v>1231867</v>
@@ -34241,7 +34241,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G1168" t="n">
-        <v>4.35608291625977</v>
+        <v>4.35608196258545</v>
       </c>
       <c r="H1168" t="n">
         <v>1659780</v>
@@ -34270,7 +34270,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G1169" t="n">
-        <v>4.42414569854736</v>
+        <v>4.42414617538452</v>
       </c>
       <c r="H1169" t="n">
         <v>2741388</v>
@@ -34357,7 +34357,7 @@
         <v>5.62599992752075</v>
       </c>
       <c r="G1172" t="n">
-        <v>4.35144186019897</v>
+        <v>4.35144138336182</v>
       </c>
       <c r="H1172" t="n">
         <v>1195350</v>
@@ -34386,7 +34386,7 @@
         <v>5.60400009155273</v>
       </c>
       <c r="G1173" t="n">
-        <v>4.33442640304565</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H1173" t="n">
         <v>1090170</v>
@@ -34415,7 +34415,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1174" t="n">
-        <v>4.26636123657227</v>
+        <v>4.26636171340942</v>
       </c>
       <c r="H1174" t="n">
         <v>1518206</v>
@@ -34531,7 +34531,7 @@
         <v>5.55399990081787</v>
       </c>
       <c r="G1178" t="n">
-        <v>4.29575300216675</v>
+        <v>4.29575347900391</v>
       </c>
       <c r="H1178" t="n">
         <v>725516</v>
@@ -34560,7 +34560,7 @@
         <v>5.51200008392334</v>
       </c>
       <c r="G1179" t="n">
-        <v>4.263267993927</v>
+        <v>4.26326847076416</v>
       </c>
       <c r="H1179" t="n">
         <v>1866419</v>
@@ -34589,7 +34589,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1180" t="n">
-        <v>4.27719068527222</v>
+        <v>4.27719020843506</v>
       </c>
       <c r="H1180" t="n">
         <v>1284403</v>
@@ -34676,7 +34676,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1183" t="n">
-        <v>4.3096752166748</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1183" t="n">
         <v>942466</v>
@@ -34734,7 +34734,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1185" t="n">
-        <v>4.26636123657227</v>
+        <v>4.26636171340942</v>
       </c>
       <c r="H1185" t="n">
         <v>2720593</v>
@@ -34821,7 +34821,7 @@
         <v>5.62200021743774</v>
       </c>
       <c r="G1188" t="n">
-        <v>4.34834814071655</v>
+        <v>4.34834861755371</v>
       </c>
       <c r="H1188" t="n">
         <v>1218309</v>
@@ -34879,7 +34879,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G1190" t="n">
-        <v>4.3096752166748</v>
+        <v>4.30967569351196</v>
       </c>
       <c r="H1190" t="n">
         <v>1530588</v>
@@ -34908,7 +34908,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G1191" t="n">
-        <v>4.31586265563965</v>
+        <v>4.31586313247681</v>
       </c>
       <c r="H1191" t="n">
         <v>1923267</v>
@@ -34937,7 +34937,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G1192" t="n">
-        <v>4.19211101531982</v>
+        <v>4.19211053848267</v>
       </c>
       <c r="H1192" t="n">
         <v>3583053</v>
@@ -34966,7 +34966,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1193" t="n">
-        <v>4.16890716552734</v>
+        <v>4.16890668869019</v>
       </c>
       <c r="H1193" t="n">
         <v>2467655</v>
@@ -34995,7 +34995,7 @@
         <v>5.41200017929077</v>
       </c>
       <c r="G1194" t="n">
-        <v>4.18592357635498</v>
+        <v>4.18592309951782</v>
       </c>
       <c r="H1194" t="n">
         <v>1940332</v>
@@ -35024,7 +35024,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1195" t="n">
-        <v>4.27719068527222</v>
+        <v>4.27719020843506</v>
       </c>
       <c r="H1195" t="n">
         <v>1798087</v>
@@ -35082,7 +35082,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1197" t="n">
-        <v>4.34370756149292</v>
+        <v>4.34370708465576</v>
       </c>
       <c r="H1197" t="n">
         <v>1310045</v>
@@ -35111,7 +35111,7 @@
         <v>5.65399980545044</v>
       </c>
       <c r="G1198" t="n">
-        <v>4.37309885025024</v>
+        <v>4.37309837341309</v>
       </c>
       <c r="H1198" t="n">
         <v>1632970</v>
@@ -35169,7 +35169,7 @@
         <v>5.71199989318848</v>
       </c>
       <c r="G1200" t="n">
-        <v>4.41795825958252</v>
+        <v>4.41795873641968</v>
       </c>
       <c r="H1200" t="n">
         <v>1137264</v>
@@ -35198,7 +35198,7 @@
         <v>5.71400022506714</v>
       </c>
       <c r="G1201" t="n">
-        <v>4.41950511932373</v>
+        <v>4.41950559616089</v>
       </c>
       <c r="H1201" t="n">
         <v>1171933</v>
@@ -35256,7 +35256,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G1203" t="n">
-        <v>4.39784860610962</v>
+        <v>4.39784908294678</v>
       </c>
       <c r="H1203" t="n">
         <v>679597</v>
@@ -35343,7 +35343,7 @@
         <v>5.73199987411499</v>
       </c>
       <c r="G1206" t="n">
-        <v>4.43342733383179</v>
+        <v>4.4334282875061</v>
       </c>
       <c r="H1206" t="n">
         <v>1019225</v>
@@ -35430,7 +35430,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G1209" t="n">
-        <v>4.49066352844238</v>
+        <v>4.49066305160522</v>
       </c>
       <c r="H1209" t="n">
         <v>1030178</v>
@@ -35575,7 +35575,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1214" t="n">
-        <v>4.56646156311035</v>
+        <v>4.56646108627319</v>
       </c>
       <c r="H1214" t="n">
         <v>1560619</v>
@@ -35633,7 +35633,7 @@
         <v>5.97200012207031</v>
       </c>
       <c r="G1216" t="n">
-        <v>4.61905574798584</v>
+        <v>4.619056224823</v>
       </c>
       <c r="H1216" t="n">
         <v>1323543</v>
@@ -35662,7 +35662,7 @@
         <v>5.99599981307983</v>
       </c>
       <c r="G1217" t="n">
-        <v>4.63761854171753</v>
+        <v>4.63761901855469</v>
       </c>
       <c r="H1217" t="n">
         <v>846788</v>
@@ -35691,7 +35691,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G1218" t="n">
-        <v>4.60204029083252</v>
+        <v>4.60203981399536</v>
       </c>
       <c r="H1218" t="n">
         <v>1107426</v>
@@ -35807,7 +35807,7 @@
         <v>5.60400009155273</v>
       </c>
       <c r="G1222" t="n">
-        <v>4.33442640304565</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H1222" t="n">
         <v>1114889</v>
@@ -35894,7 +35894,7 @@
         <v>5.68400001525879</v>
       </c>
       <c r="G1225" t="n">
-        <v>4.39630222320557</v>
+        <v>4.39630174636841</v>
       </c>
       <c r="H1225" t="n">
         <v>950072</v>
@@ -35923,7 +35923,7 @@
         <v>5.62400007247925</v>
       </c>
       <c r="G1226" t="n">
-        <v>4.34989500045776</v>
+        <v>4.34989452362061</v>
       </c>
       <c r="H1226" t="n">
         <v>1092880</v>
@@ -35952,7 +35952,7 @@
         <v>5.61600017547607</v>
       </c>
       <c r="G1227" t="n">
-        <v>4.34370756149292</v>
+        <v>4.34370708465576</v>
       </c>
       <c r="H1227" t="n">
         <v>2221372</v>
@@ -36097,7 +36097,7 @@
         <v>5.58400011062622</v>
       </c>
       <c r="G1232" t="n">
-        <v>4.31895637512207</v>
+        <v>4.31895685195923</v>
       </c>
       <c r="H1232" t="n">
         <v>2153425</v>
@@ -36126,7 +36126,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>4.33133172988892</v>
+        <v>4.33133220672607</v>
       </c>
       <c r="H1233" t="n">
         <v>1241734</v>
@@ -36184,7 +36184,7 @@
         <v>5.62200021743774</v>
       </c>
       <c r="G1235" t="n">
-        <v>4.34834814071655</v>
+        <v>4.34834861755371</v>
       </c>
       <c r="H1235" t="n">
         <v>2086645</v>
@@ -36242,7 +36242,7 @@
         <v>5.63199996948242</v>
       </c>
       <c r="G1237" t="n">
-        <v>4.35608291625977</v>
+        <v>4.35608196258545</v>
       </c>
       <c r="H1237" t="n">
         <v>2406077</v>
@@ -36329,7 +36329,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1240" t="n">
-        <v>4.45508432388306</v>
+        <v>4.45508480072021</v>
       </c>
       <c r="H1240" t="n">
         <v>1716303</v>
@@ -36474,7 +36474,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>4.28492450714111</v>
+        <v>4.28492546081543</v>
       </c>
       <c r="H1245" t="n">
         <v>1456700</v>
@@ -36503,7 +36503,7 @@
         <v>5.47399997711182</v>
       </c>
       <c r="G1246" t="n">
-        <v>4.23387670516968</v>
+        <v>4.23387718200684</v>
       </c>
       <c r="H1246" t="n">
         <v>2088691</v>
@@ -36677,7 +36677,7 @@
         <v>5.44600009918213</v>
       </c>
       <c r="G1252" t="n">
-        <v>4.21222066879272</v>
+        <v>4.21222019195557</v>
       </c>
       <c r="H1252" t="n">
         <v>1695886</v>
@@ -36909,7 +36909,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1260" t="n">
-        <v>4.32205009460449</v>
+        <v>4.32205057144165</v>
       </c>
       <c r="H1260" t="n">
         <v>1687840</v>
@@ -36938,7 +36938,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1261" t="n">
-        <v>4.33133172988892</v>
+        <v>4.33133220672607</v>
       </c>
       <c r="H1261" t="n">
         <v>1051490</v>
@@ -36967,7 +36967,7 @@
         <v>5.60400009155273</v>
       </c>
       <c r="G1262" t="n">
-        <v>4.33442640304565</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H1262" t="n">
         <v>1526278</v>
@@ -37025,7 +37025,7 @@
         <v>5.62400007247925</v>
       </c>
       <c r="G1264" t="n">
-        <v>4.34989500045776</v>
+        <v>4.34989452362061</v>
       </c>
       <c r="H1264" t="n">
         <v>1336031</v>
@@ -37054,7 +37054,7 @@
         <v>5.52400016784668</v>
       </c>
       <c r="G1265" t="n">
-        <v>4.27254962921143</v>
+        <v>4.27255010604858</v>
       </c>
       <c r="H1265" t="n">
         <v>2499950</v>
@@ -37083,7 +37083,7 @@
         <v>5.48999977111816</v>
       </c>
       <c r="G1266" t="n">
-        <v>4.24625205993652</v>
+        <v>4.24625253677368</v>
       </c>
       <c r="H1266" t="n">
         <v>2523989</v>
@@ -37199,7 +37199,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G1270" t="n">
-        <v>4.41641139984131</v>
+        <v>4.41641187667847</v>
       </c>
       <c r="H1270" t="n">
         <v>2101433</v>
@@ -37228,7 +37228,7 @@
         <v>5.73400020599365</v>
       </c>
       <c r="G1271" t="n">
-        <v>4.43497467041016</v>
+        <v>4.434974193573</v>
       </c>
       <c r="H1271" t="n">
         <v>1322224</v>
@@ -37286,7 +37286,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G1273" t="n">
-        <v>4.36227035522461</v>
+        <v>4.36226987838745</v>
       </c>
       <c r="H1273" t="n">
         <v>889879</v>
@@ -37402,7 +37402,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1277" t="n">
-        <v>4.33133172988892</v>
+        <v>4.33133220672607</v>
       </c>
       <c r="H1277" t="n">
         <v>1902172</v>
@@ -37431,7 +37431,7 @@
         <v>5.5460000038147</v>
       </c>
       <c r="G1278" t="n">
-        <v>4.2895655632019</v>
+        <v>4.28956604003906</v>
       </c>
       <c r="H1278" t="n">
         <v>1177276</v>
@@ -37489,7 +37489,7 @@
         <v>5.60400009155273</v>
       </c>
       <c r="G1280" t="n">
-        <v>4.33442640304565</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H1280" t="n">
         <v>1912958</v>
@@ -37634,7 +37634,7 @@
         <v>5.65399980545044</v>
       </c>
       <c r="G1285" t="n">
-        <v>4.37309885025024</v>
+        <v>4.37309837341309</v>
       </c>
       <c r="H1285" t="n">
         <v>855413</v>
@@ -37663,7 +37663,7 @@
         <v>5.50600004196167</v>
       </c>
       <c r="G1286" t="n">
-        <v>4.25862693786621</v>
+        <v>4.25862741470337</v>
       </c>
       <c r="H1286" t="n">
         <v>2649412</v>
@@ -37750,7 +37750,7 @@
         <v>5.58799982070923</v>
       </c>
       <c r="G1289" t="n">
-        <v>4.32205009460449</v>
+        <v>4.32205057144165</v>
       </c>
       <c r="H1289" t="n">
         <v>1160885</v>
@@ -37779,7 +37779,7 @@
         <v>5.57600021362305</v>
       </c>
       <c r="G1290" t="n">
-        <v>4.31276893615723</v>
+        <v>4.31276941299438</v>
       </c>
       <c r="H1290" t="n">
         <v>1233501</v>
@@ -37837,7 +37837,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1292" t="n">
-        <v>4.51850748062134</v>
+        <v>4.5185079574585</v>
       </c>
       <c r="H1292" t="n">
         <v>2866024</v>
@@ -37866,7 +37866,7 @@
         <v>5.84600019454956</v>
       </c>
       <c r="G1293" t="n">
-        <v>4.52160167694092</v>
+        <v>4.52160120010376</v>
       </c>
       <c r="H1293" t="n">
         <v>1495847</v>
@@ -38011,7 +38011,7 @@
         <v>5.7480001449585</v>
       </c>
       <c r="G1298" t="n">
-        <v>4.44580221176147</v>
+        <v>4.44580268859863</v>
       </c>
       <c r="H1298" t="n">
         <v>2108694</v>
@@ -38040,7 +38040,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G1299" t="n">
-        <v>4.5014910697937</v>
+        <v>4.50149154663086</v>
       </c>
       <c r="H1299" t="n">
         <v>1594043</v>
@@ -38098,7 +38098,7 @@
         <v>5.82200002670288</v>
       </c>
       <c r="G1301" t="n">
-        <v>4.50303792953491</v>
+        <v>4.50303840637207</v>
       </c>
       <c r="H1301" t="n">
         <v>3253697</v>
@@ -38185,7 +38185,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1304" t="n">
-        <v>4.52469444274902</v>
+        <v>4.52469491958618</v>
       </c>
       <c r="H1304" t="n">
         <v>1298324</v>
@@ -38214,7 +38214,7 @@
         <v>5.89400005340576</v>
       </c>
       <c r="G1305" t="n">
-        <v>4.55872678756714</v>
+        <v>4.5587272644043</v>
       </c>
       <c r="H1305" t="n">
         <v>1057215</v>
@@ -38243,7 +38243,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G1306" t="n">
-        <v>4.54789924621582</v>
+        <v>4.54789876937866</v>
       </c>
       <c r="H1306" t="n">
         <v>631434</v>
@@ -38301,7 +38301,7 @@
         <v>6.03399991989136</v>
       </c>
       <c r="G1308" t="n">
-        <v>4.66701030731201</v>
+        <v>4.66701078414917</v>
       </c>
       <c r="H1308" t="n">
         <v>1134168</v>
@@ -38330,7 +38330,7 @@
         <v>6.05200004577637</v>
       </c>
       <c r="G1309" t="n">
-        <v>4.68093252182007</v>
+        <v>4.68093204498291</v>
       </c>
       <c r="H1309" t="n">
         <v>1125437</v>
@@ -38359,7 +38359,7 @@
         <v>6.08799982070923</v>
       </c>
       <c r="G1310" t="n">
-        <v>4.70877695083618</v>
+        <v>4.70877647399902</v>
       </c>
       <c r="H1310" t="n">
         <v>996941</v>
@@ -38446,7 +38446,7 @@
         <v>5.84200000762939</v>
       </c>
       <c r="G1313" t="n">
-        <v>4.51850748062134</v>
+        <v>4.5185079574585</v>
       </c>
       <c r="H1313" t="n">
         <v>1666783</v>
@@ -38533,7 +38533,7 @@
         <v>5.82200002670288</v>
       </c>
       <c r="G1316" t="n">
-        <v>4.50303792953491</v>
+        <v>4.50303840637207</v>
       </c>
       <c r="H1316" t="n">
         <v>1805777</v>
@@ -38562,7 +38562,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G1317" t="n">
-        <v>4.5277886390686</v>
+        <v>4.52778911590576</v>
       </c>
       <c r="H1317" t="n">
         <v>1300408</v>
@@ -38649,7 +38649,7 @@
         <v>5.89200019836426</v>
       </c>
       <c r="G1320" t="n">
-        <v>4.55717992782593</v>
+        <v>4.55717945098877</v>
       </c>
       <c r="H1320" t="n">
         <v>517814</v>
@@ -38678,7 +38678,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1321" t="n">
-        <v>4.5386176109314</v>
+        <v>4.53861713409424</v>
       </c>
       <c r="H1321" t="n">
         <v>1062972</v>
@@ -38707,7 +38707,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1322" t="n">
-        <v>4.5386176109314</v>
+        <v>4.53861713409424</v>
       </c>
       <c r="H1322" t="n">
         <v>890715</v>
@@ -38794,7 +38794,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1325" t="n">
-        <v>4.45508432388306</v>
+        <v>4.45508480072021</v>
       </c>
       <c r="H1325" t="n">
         <v>1934280</v>
@@ -38852,7 +38852,7 @@
         <v>5.80600023269653</v>
       </c>
       <c r="G1327" t="n">
-        <v>4.49066352844238</v>
+        <v>4.49066305160522</v>
       </c>
       <c r="H1327" t="n">
         <v>1114675</v>
@@ -38881,7 +38881,7 @@
         <v>5.93599987030029</v>
       </c>
       <c r="G1328" t="n">
-        <v>4.59121227264404</v>
+        <v>4.59121179580688</v>
       </c>
       <c r="H1328" t="n">
         <v>1235229</v>
@@ -38910,7 +38910,7 @@
         <v>5.85400009155273</v>
       </c>
       <c r="G1329" t="n">
-        <v>4.5277886390686</v>
+        <v>4.52778911590576</v>
       </c>
       <c r="H1329" t="n">
         <v>1302096</v>
@@ -38939,7 +38939,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G1330" t="n">
-        <v>4.5386176109314</v>
+        <v>4.53861713409424</v>
       </c>
       <c r="H1330" t="n">
         <v>863041</v>
@@ -38968,7 +38968,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G1331" t="n">
-        <v>4.56646156311035</v>
+        <v>4.56646108627319</v>
       </c>
       <c r="H1331" t="n">
         <v>1234389</v>
@@ -39026,7 +39026,7 @@
         <v>5.87400007247925</v>
       </c>
       <c r="G1333" t="n">
-        <v>4.54325866699219</v>
+        <v>4.54325819015503</v>
       </c>
       <c r="H1333" t="n">
         <v>916172</v>
@@ -39055,7 +39055,7 @@
         <v>5.68599987030029</v>
       </c>
       <c r="G1334" t="n">
-        <v>4.39784860610962</v>
+        <v>4.39784908294678</v>
       </c>
       <c r="H1334" t="n">
         <v>1292083</v>
@@ -39142,7 +39142,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G1337" t="n">
-        <v>4.38238000869751</v>
+        <v>4.38237953186035</v>
       </c>
       <c r="H1337" t="n">
         <v>1667829</v>
@@ -39171,7 +39171,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1338" t="n">
-        <v>4.43188095092773</v>
+        <v>4.43188047409058</v>
       </c>
       <c r="H1338" t="n">
         <v>1465529</v>
@@ -39316,7 +39316,7 @@
         <v>5.64400005340576</v>
       </c>
       <c r="G1343" t="n">
-        <v>4.36536407470703</v>
+        <v>4.36536359786987</v>
       </c>
       <c r="H1343" t="n">
         <v>962909</v>
@@ -39403,7 +39403,7 @@
         <v>5.51599979400635</v>
       </c>
       <c r="G1346" t="n">
-        <v>4.26636123657227</v>
+        <v>4.26636171340942</v>
       </c>
       <c r="H1346" t="n">
         <v>1668922</v>
@@ -39490,7 +39490,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1349" t="n">
-        <v>4.45508432388306</v>
+        <v>4.45508480072021</v>
       </c>
       <c r="H1349" t="n">
         <v>2859179</v>
@@ -39635,7 +39635,7 @@
         <v>5.38800001144409</v>
       </c>
       <c r="G1354" t="n">
-        <v>4.16736078262329</v>
+        <v>4.16735982894897</v>
       </c>
       <c r="H1354" t="n">
         <v>2249392</v>
@@ -39664,7 +39664,7 @@
         <v>5.34800004959106</v>
       </c>
       <c r="G1355" t="n">
-        <v>4.13642168045044</v>
+        <v>4.1364221572876</v>
       </c>
       <c r="H1355" t="n">
         <v>2866264</v>
@@ -39693,7 +39693,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G1356" t="n">
-        <v>4.16890716552734</v>
+        <v>4.16890668869019</v>
       </c>
       <c r="H1356" t="n">
         <v>2103223</v>
@@ -39722,7 +39722,7 @@
         <v>5.64200019836426</v>
       </c>
       <c r="G1357" t="n">
-        <v>4.36381721496582</v>
+        <v>4.36381769180298</v>
       </c>
       <c r="H1357" t="n">
         <v>2566365</v>
@@ -39780,7 +39780,7 @@
         <v>5.59200000762939</v>
       </c>
       <c r="G1359" t="n">
-        <v>4.32514429092407</v>
+        <v>4.32514476776123</v>
       </c>
       <c r="H1359" t="n">
         <v>1699674</v>
@@ -39954,7 +39954,7 @@
         <v>5.60400009155273</v>
       </c>
       <c r="G1365" t="n">
-        <v>4.33442640304565</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H1365" t="n">
         <v>1104569</v>
@@ -39983,7 +39983,7 @@
         <v>5.64200019836426</v>
       </c>
       <c r="G1366" t="n">
-        <v>4.36381721496582</v>
+        <v>4.36381769180298</v>
       </c>
       <c r="H1366" t="n">
         <v>1344597</v>
@@ -40012,7 +40012,7 @@
         <v>5.48799991607666</v>
       </c>
       <c r="G1367" t="n">
-        <v>4.24470520019531</v>
+        <v>4.24470567703247</v>
       </c>
       <c r="H1367" t="n">
         <v>1259036</v>
@@ -40070,7 +40070,7 @@
         <v>5.66599988937378</v>
       </c>
       <c r="G1369" t="n">
-        <v>4.38238000869751</v>
+        <v>4.38237953186035</v>
       </c>
       <c r="H1369" t="n">
         <v>1134945</v>
@@ -40099,7 +40099,7 @@
         <v>5.73199987411499</v>
       </c>
       <c r="G1370" t="n">
-        <v>4.43342733383179</v>
+        <v>4.4334282875061</v>
       </c>
       <c r="H1370" t="n">
         <v>1306736</v>
@@ -40215,7 +40215,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G1374" t="n">
-        <v>4.52856206893921</v>
+        <v>4.52856254577637</v>
       </c>
       <c r="H1374" t="n">
         <v>1129081</v>
@@ -40244,7 +40244,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1375" t="n">
-        <v>4.45508432388306</v>
+        <v>4.45508480072021</v>
       </c>
       <c r="H1375" t="n">
         <v>1102525</v>
@@ -40302,7 +40302,7 @@
         <v>5.79500007629395</v>
       </c>
       <c r="G1377" t="n">
-        <v>4.48215579986572</v>
+        <v>4.48215532302856</v>
       </c>
       <c r="H1377" t="n">
         <v>1875254</v>
@@ -40360,7 +40360,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1379" t="n">
-        <v>4.68711996078491</v>
+        <v>4.68711948394775</v>
       </c>
       <c r="H1379" t="n">
         <v>1520621</v>
@@ -40476,7 +40476,7 @@
         <v>6.19500017166138</v>
       </c>
       <c r="G1383" t="n">
-        <v>4.79153633117676</v>
+        <v>4.7915358543396</v>
       </c>
       <c r="H1383" t="n">
         <v>1874085</v>
@@ -40505,7 +40505,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1384" t="n">
-        <v>4.83020877838135</v>
+        <v>4.83020830154419</v>
       </c>
       <c r="H1384" t="n">
         <v>3183045</v>
@@ -40563,7 +40563,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1386" t="n">
-        <v>4.87274837493896</v>
+        <v>4.87274885177612</v>
       </c>
       <c r="H1386" t="n">
         <v>3249152</v>
@@ -40650,7 +40650,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G1389" t="n">
-        <v>4.74899625778198</v>
+        <v>4.74899578094482</v>
       </c>
       <c r="H1389" t="n">
         <v>1400826</v>
@@ -40679,7 +40679,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1390" t="n">
-        <v>4.77993440628052</v>
+        <v>4.77993392944336</v>
       </c>
       <c r="H1390" t="n">
         <v>1169448</v>
@@ -40708,7 +40708,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G1391" t="n">
-        <v>4.80313730239868</v>
+        <v>4.80313777923584</v>
       </c>
       <c r="H1391" t="n">
         <v>1131913</v>
@@ -40737,7 +40737,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1392" t="n">
-        <v>4.77993440628052</v>
+        <v>4.77993392944336</v>
       </c>
       <c r="H1392" t="n">
         <v>855211</v>
@@ -40824,7 +40824,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G1395" t="n">
-        <v>4.76059770584106</v>
+        <v>4.76059818267822</v>
       </c>
       <c r="H1395" t="n">
         <v>1393936</v>
@@ -40911,7 +40911,7 @@
         <v>6.06500005722046</v>
       </c>
       <c r="G1398" t="n">
-        <v>4.6909875869751</v>
+        <v>4.69098711013794</v>
       </c>
       <c r="H1398" t="n">
         <v>1376953</v>
@@ -40940,7 +40940,7 @@
         <v>6.125</v>
       </c>
       <c r="G1399" t="n">
-        <v>4.73739385604858</v>
+        <v>4.73739433288574</v>
       </c>
       <c r="H1399" t="n">
         <v>1401626</v>
@@ -40969,7 +40969,7 @@
         <v>6.24499988555908</v>
       </c>
       <c r="G1400" t="n">
-        <v>4.83020877838135</v>
+        <v>4.83020830154419</v>
       </c>
       <c r="H1400" t="n">
         <v>1446658</v>
@@ -40998,7 +40998,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G1401" t="n">
-        <v>4.71032381057739</v>
+        <v>4.71032333374023</v>
       </c>
       <c r="H1401" t="n">
         <v>1308144</v>
@@ -41027,7 +41027,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G1402" t="n">
-        <v>4.77993440628052</v>
+        <v>4.77993392944336</v>
       </c>
       <c r="H1402" t="n">
         <v>1402848</v>
@@ -41056,7 +41056,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G1403" t="n">
-        <v>4.87274837493896</v>
+        <v>4.87274885177612</v>
       </c>
       <c r="H1403" t="n">
         <v>1242481</v>
@@ -41085,7 +41085,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1404" t="n">
-        <v>4.88821792602539</v>
+        <v>4.88821744918823</v>
       </c>
       <c r="H1404" t="n">
         <v>1769932</v>
@@ -41114,7 +41114,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G1405" t="n">
-        <v>4.88821792602539</v>
+        <v>4.88821744918823</v>
       </c>
       <c r="H1405" t="n">
         <v>1082943</v>
@@ -41172,7 +41172,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G1407" t="n">
-        <v>4.94235944747925</v>
+        <v>4.94235897064209</v>
       </c>
       <c r="H1407" t="n">
         <v>1771579</v>
@@ -41230,7 +41230,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G1409" t="n">
-        <v>4.89951992034912</v>
+        <v>4.89951944351196</v>
       </c>
       <c r="H1409" t="n">
         <v>1322157</v>
@@ -41317,7 +41317,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G1412" t="n">
-        <v>4.88334941864014</v>
+        <v>4.88334989547729</v>
       </c>
       <c r="H1412" t="n">
         <v>884522</v>
@@ -41375,7 +41375,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1414" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909557342529</v>
       </c>
       <c r="H1414" t="n">
         <v>1962697</v>
@@ -41404,7 +41404,7 @@
         <v>5.95499992370605</v>
       </c>
       <c r="G1415" t="n">
-        <v>4.81462717056274</v>
+        <v>4.8146276473999</v>
       </c>
       <c r="H1415" t="n">
         <v>1272371</v>
@@ -41433,7 +41433,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1416" t="n">
-        <v>4.83079719543457</v>
+        <v>4.83079671859741</v>
       </c>
       <c r="H1416" t="n">
         <v>500769</v>
@@ -41462,7 +41462,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1417" t="n">
-        <v>4.83079719543457</v>
+        <v>4.83079671859741</v>
       </c>
       <c r="H1417" t="n">
         <v>667677</v>
@@ -41491,7 +41491,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1418" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909557342529</v>
       </c>
       <c r="H1418" t="n">
         <v>620812</v>
@@ -41549,7 +41549,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1420" t="n">
-        <v>4.83079719543457</v>
+        <v>4.83079671859741</v>
       </c>
       <c r="H1420" t="n">
         <v>1063586</v>
@@ -41578,7 +41578,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G1421" t="n">
-        <v>4.66505432128906</v>
+        <v>4.66505479812622</v>
       </c>
       <c r="H1421" t="n">
         <v>1819823</v>
@@ -41665,7 +41665,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1424" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1424" t="n">
         <v>1270670</v>
@@ -41694,7 +41694,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1425" t="n">
-        <v>4.40633392333984</v>
+        <v>4.40633344650269</v>
       </c>
       <c r="H1425" t="n">
         <v>2381256</v>
@@ -41752,7 +41752,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>4.51548147201538</v>
+        <v>4.51548194885254</v>
       </c>
       <c r="H1427" t="n">
         <v>3316711</v>
@@ -42013,7 +42013,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1436" t="n">
-        <v>4.49122619628906</v>
+        <v>4.49122667312622</v>
       </c>
       <c r="H1436" t="n">
         <v>2205200</v>
@@ -42042,7 +42042,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1437" t="n">
-        <v>4.52760887145996</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1437" t="n">
         <v>1165445</v>
@@ -42071,7 +42071,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1438" t="n">
-        <v>4.52760887145996</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1438" t="n">
         <v>713087</v>
@@ -42129,7 +42129,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1440" t="n">
-        <v>4.42250347137451</v>
+        <v>4.42250394821167</v>
       </c>
       <c r="H1440" t="n">
         <v>1861474</v>
@@ -42187,7 +42187,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1442" t="n">
-        <v>4.41441917419434</v>
+        <v>4.41441869735718</v>
       </c>
       <c r="H1442" t="n">
         <v>1233053</v>
@@ -42245,7 +42245,7 @@
         <v>5.5</v>
       </c>
       <c r="G1444" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1444" t="n">
         <v>813805</v>
@@ -42303,7 +42303,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G1446" t="n">
-        <v>4.26080369949341</v>
+        <v>4.26080322265625</v>
       </c>
       <c r="H1446" t="n">
         <v>1252526</v>
@@ -42332,7 +42332,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1447" t="n">
-        <v>4.32548379898071</v>
+        <v>4.32548332214355</v>
       </c>
       <c r="H1447" t="n">
         <v>1617049</v>
@@ -42419,7 +42419,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1450" t="n">
-        <v>4.26484632492065</v>
+        <v>4.2648458480835</v>
       </c>
       <c r="H1450" t="n">
         <v>1355393</v>
@@ -42448,7 +42448,7 @@
         <v>5.19500017166138</v>
       </c>
       <c r="G1451" t="n">
-        <v>4.20016574859619</v>
+        <v>4.20016622543335</v>
       </c>
       <c r="H1451" t="n">
         <v>1487711</v>
@@ -42477,7 +42477,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1452" t="n">
-        <v>4.27293062210083</v>
+        <v>4.27293109893799</v>
       </c>
       <c r="H1452" t="n">
         <v>787321</v>
@@ -42506,7 +42506,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1453" t="n">
-        <v>4.27293062210083</v>
+        <v>4.27293109893799</v>
       </c>
       <c r="H1453" t="n">
         <v>768600</v>
@@ -42564,7 +42564,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>4.41441917419434</v>
+        <v>4.41441869735718</v>
       </c>
       <c r="H1455" t="n">
         <v>1501879</v>
@@ -42593,7 +42593,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G1456" t="n">
-        <v>4.47101449966431</v>
+        <v>4.47101402282715</v>
       </c>
       <c r="H1456" t="n">
         <v>742411</v>
@@ -42680,7 +42680,7 @@
         <v>5.5</v>
       </c>
       <c r="G1459" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1459" t="n">
         <v>477914</v>
@@ -42709,7 +42709,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G1460" t="n">
-        <v>4.41846132278442</v>
+        <v>4.41846179962158</v>
       </c>
       <c r="H1460" t="n">
         <v>832876</v>
@@ -42767,7 +42767,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1462" t="n">
-        <v>4.42250347137451</v>
+        <v>4.42250394821167</v>
       </c>
       <c r="H1462" t="n">
         <v>620839</v>
@@ -42999,7 +42999,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G1470" t="n">
-        <v>4.59633159637451</v>
+        <v>4.59633207321167</v>
       </c>
       <c r="H1470" t="n">
         <v>537994</v>
@@ -43231,7 +43231,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1478" t="n">
-        <v>4.28505849838257</v>
+        <v>4.28505897521973</v>
       </c>
       <c r="H1478" t="n">
         <v>723903</v>
@@ -43463,7 +43463,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G1486" t="n">
-        <v>4.20420789718628</v>
+        <v>4.20420837402344</v>
       </c>
       <c r="H1486" t="n">
         <v>1293238</v>
@@ -43608,7 +43608,7 @@
         <v>5.11499977111816</v>
       </c>
       <c r="G1491" t="n">
-        <v>4.13548564910889</v>
+        <v>4.13548612594604</v>
       </c>
       <c r="H1491" t="n">
         <v>2769308</v>
@@ -43753,7 +43753,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1496" t="n">
-        <v>4.0910177230835</v>
+        <v>4.09101819992065</v>
       </c>
       <c r="H1496" t="n">
         <v>2064342</v>
@@ -43782,7 +43782,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G1497" t="n">
-        <v>4.0910177230835</v>
+        <v>4.09101819992065</v>
       </c>
       <c r="H1497" t="n">
         <v>1666798</v>
@@ -43811,7 +43811,7 @@
         <v>4.9060001373291</v>
       </c>
       <c r="G1498" t="n">
-        <v>3.96650910377502</v>
+        <v>3.96650862693787</v>
       </c>
       <c r="H1498" t="n">
         <v>3821543</v>
@@ -43898,7 +43898,7 @@
         <v>4.77600002288818</v>
       </c>
       <c r="G1501" t="n">
-        <v>3.86140370368958</v>
+        <v>3.86140418052673</v>
       </c>
       <c r="H1501" t="n">
         <v>1461342</v>
@@ -43956,7 +43956,7 @@
         <v>5.00500011444092</v>
       </c>
       <c r="G1503" t="n">
-        <v>4.04655075073242</v>
+        <v>4.04655027389526</v>
       </c>
       <c r="H1503" t="n">
         <v>1493218</v>
@@ -43985,7 +43985,7 @@
         <v>4.85599994659424</v>
       </c>
       <c r="G1504" t="n">
-        <v>3.9260835647583</v>
+        <v>3.92608404159546</v>
       </c>
       <c r="H1504" t="n">
         <v>1924799</v>
@@ -44159,7 +44159,7 @@
         <v>4.55600023269653</v>
       </c>
       <c r="G1510" t="n">
-        <v>3.68353343009949</v>
+        <v>3.68353366851807</v>
       </c>
       <c r="H1510" t="n">
         <v>2103298</v>
@@ -44304,7 +44304,7 @@
         <v>4.84800004959106</v>
       </c>
       <c r="G1515" t="n">
-        <v>3.91961598396301</v>
+        <v>3.91961646080017</v>
       </c>
       <c r="H1515" t="n">
         <v>1359512</v>
@@ -44478,7 +44478,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1521" t="n">
-        <v>4.27293062210083</v>
+        <v>4.27293109893799</v>
       </c>
       <c r="H1521" t="n">
         <v>1561683</v>
@@ -44565,7 +44565,7 @@
         <v>5.27500009536743</v>
       </c>
       <c r="G1524" t="n">
-        <v>4.26484632492065</v>
+        <v>4.2648458480835</v>
       </c>
       <c r="H1524" t="n">
         <v>1623441</v>
@@ -44710,7 +44710,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G1529" t="n">
-        <v>4.36995220184326</v>
+        <v>4.3699517250061</v>
       </c>
       <c r="H1529" t="n">
         <v>1003519</v>
@@ -44739,7 +44739,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1530" t="n">
-        <v>4.49122619628906</v>
+        <v>4.49122667312622</v>
       </c>
       <c r="H1530" t="n">
         <v>1546905</v>
@@ -44768,7 +44768,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G1531" t="n">
-        <v>4.40633392333984</v>
+        <v>4.40633344650269</v>
       </c>
       <c r="H1531" t="n">
         <v>1010791</v>
@@ -44797,7 +44797,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G1532" t="n">
-        <v>4.41846132278442</v>
+        <v>4.41846179962158</v>
       </c>
       <c r="H1532" t="n">
         <v>949813</v>
@@ -44855,7 +44855,7 @@
         <v>5.5</v>
       </c>
       <c r="G1534" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1534" t="n">
         <v>921443</v>
@@ -44971,7 +44971,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1538" t="n">
-        <v>4.52760887145996</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1538" t="n">
         <v>645027</v>
@@ -45029,7 +45029,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G1540" t="n">
-        <v>4.59633159637451</v>
+        <v>4.59633207321167</v>
       </c>
       <c r="H1540" t="n">
         <v>615561</v>
@@ -45116,7 +45116,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1543" t="n">
-        <v>4.52760887145996</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1543" t="n">
         <v>850493</v>
@@ -45174,7 +45174,7 @@
         <v>5.625</v>
       </c>
       <c r="G1545" t="n">
-        <v>4.54782199859619</v>
+        <v>4.54782152175903</v>
       </c>
       <c r="H1545" t="n">
         <v>1422376</v>
@@ -45406,7 +45406,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G1553" t="n">
-        <v>4.54377937316895</v>
+        <v>4.54377889633179</v>
       </c>
       <c r="H1553" t="n">
         <v>1267082</v>
@@ -45435,7 +45435,7 @@
         <v>5.625</v>
       </c>
       <c r="G1554" t="n">
-        <v>4.54782199859619</v>
+        <v>4.54782152175903</v>
       </c>
       <c r="H1554" t="n">
         <v>1148827</v>
@@ -45464,7 +45464,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G1555" t="n">
-        <v>4.41846132278442</v>
+        <v>4.41846179962158</v>
       </c>
       <c r="H1555" t="n">
         <v>1637089</v>
@@ -45493,7 +45493,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1556" t="n">
-        <v>4.32548379898071</v>
+        <v>4.32548332214355</v>
       </c>
       <c r="H1556" t="n">
         <v>4183479</v>
@@ -45551,7 +45551,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1558" t="n">
-        <v>4.27293062210083</v>
+        <v>4.27293109893799</v>
       </c>
       <c r="H1558" t="n">
         <v>1328954</v>
@@ -45609,7 +45609,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G1560" t="n">
-        <v>4.33761119842529</v>
+        <v>4.33761072158813</v>
       </c>
       <c r="H1560" t="n">
         <v>968371</v>
@@ -45638,7 +45638,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G1561" t="n">
-        <v>4.32548379898071</v>
+        <v>4.32548332214355</v>
       </c>
       <c r="H1561" t="n">
         <v>561433</v>
@@ -45696,7 +45696,7 @@
         <v>5.24499988555908</v>
       </c>
       <c r="G1563" t="n">
-        <v>4.24059057235718</v>
+        <v>4.24059104919434</v>
       </c>
       <c r="H1563" t="n">
         <v>685775</v>
@@ -45725,7 +45725,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G1564" t="n">
-        <v>4.28505849838257</v>
+        <v>4.28505897521973</v>
       </c>
       <c r="H1564" t="n">
         <v>599188</v>
@@ -45841,7 +45841,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G1568" t="n">
-        <v>4.33356904983521</v>
+        <v>4.33356857299805</v>
       </c>
       <c r="H1568" t="n">
         <v>2077805</v>
@@ -45870,7 +45870,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.25676155090332</v>
+        <v>4.25676107406616</v>
       </c>
       <c r="H1569" t="n">
         <v>1159957</v>
@@ -45928,7 +45928,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G1571" t="n">
-        <v>4.33761119842529</v>
+        <v>4.33761072158813</v>
       </c>
       <c r="H1571" t="n">
         <v>1103434</v>
@@ -45957,7 +45957,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1572" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1572" t="n">
         <v>732182</v>
@@ -46015,7 +46015,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1574" t="n">
-        <v>4.41441917419434</v>
+        <v>4.41441869735718</v>
       </c>
       <c r="H1574" t="n">
         <v>1041388</v>
@@ -46102,7 +46102,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1577" t="n">
-        <v>4.41441917419434</v>
+        <v>4.41441869735718</v>
       </c>
       <c r="H1577" t="n">
         <v>678604</v>
@@ -46363,7 +46363,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G1586" t="n">
-        <v>4.37399339675903</v>
+        <v>4.37399387359619</v>
       </c>
       <c r="H1586" t="n">
         <v>1297340</v>
@@ -46392,7 +46392,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G1587" t="n">
-        <v>4.33761119842529</v>
+        <v>4.33761072158813</v>
       </c>
       <c r="H1587" t="n">
         <v>1664361</v>
@@ -46479,7 +46479,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G1590" t="n">
-        <v>4.41441917419434</v>
+        <v>4.41441869735718</v>
       </c>
       <c r="H1590" t="n">
         <v>1545936</v>
@@ -46624,7 +46624,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G1595" t="n">
-        <v>4.52760887145996</v>
+        <v>4.52760934829712</v>
       </c>
       <c r="H1595" t="n">
         <v>834135</v>
@@ -46711,7 +46711,7 @@
         <v>5.5</v>
       </c>
       <c r="G1598" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1598" t="n">
         <v>3511367</v>
@@ -46740,7 +46740,7 @@
         <v>5.5</v>
       </c>
       <c r="G1599" t="n">
-        <v>4.44675874710083</v>
+        <v>4.44675922393799</v>
       </c>
       <c r="H1599" t="n">
         <v>1445698</v>
@@ -46769,7 +46769,7 @@
         <v>5.43499994277954</v>
       </c>
       <c r="G1600" t="n">
-        <v>4.39420652389526</v>
+        <v>4.39420604705811</v>
       </c>
       <c r="H1600" t="n">
         <v>1557745</v>
@@ -46885,7 +46885,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G1604" t="n">
-        <v>4.33761119842529</v>
+        <v>4.33761072158813</v>
       </c>
       <c r="H1604" t="n">
         <v>799525</v>
@@ -46972,7 +46972,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1607" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1607" t="n">
         <v>1646514</v>
@@ -47088,7 +47088,7 @@
         <v>5.28499984741211</v>
       </c>
       <c r="G1611" t="n">
-        <v>4.27293062210083</v>
+        <v>4.27293109893799</v>
       </c>
       <c r="H1611" t="n">
         <v>1040363</v>
@@ -47117,7 +47117,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G1612" t="n">
-        <v>4.25271892547607</v>
+        <v>4.25271844863892</v>
       </c>
       <c r="H1612" t="n">
         <v>1159127</v>
@@ -47146,7 +47146,7 @@
         <v>5.2649998664856</v>
       </c>
       <c r="G1613" t="n">
-        <v>4.25676155090332</v>
+        <v>4.25676107406616</v>
       </c>
       <c r="H1613" t="n">
         <v>864348</v>
@@ -47349,7 +47349,7 @@
         <v>5.38500022888184</v>
       </c>
       <c r="G1620" t="n">
-        <v>4.35378122329712</v>
+        <v>4.35378170013428</v>
       </c>
       <c r="H1620" t="n">
         <v>6654047</v>
@@ -47465,7 +47465,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G1624" t="n">
-        <v>4.42250347137451</v>
+        <v>4.42250394821167</v>
       </c>
       <c r="H1624" t="n">
         <v>1754976</v>
@@ -47552,7 +47552,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G1627" t="n">
-        <v>4.49122619628906</v>
+        <v>4.49122667312622</v>
       </c>
       <c r="H1627" t="n">
         <v>973647</v>
@@ -47639,7 +47639,7 @@
         <v>5.625</v>
       </c>
       <c r="G1630" t="n">
-        <v>4.54782199859619</v>
+        <v>4.54782152175903</v>
       </c>
       <c r="H1630" t="n">
         <v>907373</v>
@@ -47784,7 +47784,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1635" t="n">
-        <v>4.83079719543457</v>
+        <v>4.83079671859741</v>
       </c>
       <c r="H1635" t="n">
         <v>1664843</v>
@@ -47987,7 +47987,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G1642" t="n">
-        <v>4.85909509658813</v>
+        <v>4.85909557342529</v>
       </c>
       <c r="H1642" t="n">
         <v>1008256</v>
@@ -48103,7 +48103,7 @@
         <v>5.82499980926514</v>
       </c>
       <c r="G1646" t="n">
-        <v>4.70952177047729</v>
+        <v>4.70952224731445</v>
       </c>
       <c r="H1646" t="n">
         <v>2045186</v>
@@ -48219,7 +48219,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G1650" t="n">
-        <v>4.72973394393921</v>
+        <v>4.72973442077637</v>
       </c>
       <c r="H1650" t="n">
         <v>1455029</v>
@@ -48248,7 +48248,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G1651" t="n">
-        <v>4.72569227218628</v>
+        <v>4.72569179534912</v>
       </c>
       <c r="H1651" t="n">
         <v>1741480</v>
@@ -48306,7 +48306,7 @@
         <v>5.84499979019165</v>
       </c>
       <c r="G1653" t="n">
-        <v>4.72569227218628</v>
+        <v>4.72569179534912</v>
       </c>
       <c r="H1653" t="n">
         <v>1113446</v>
@@ -48422,7 +48422,7 @@
         <v>5.97499990463257</v>
       </c>
       <c r="G1657" t="n">
-        <v>4.83079719543457</v>
+        <v>4.83079671859741</v>
       </c>
       <c r="H1657" t="n">
         <v>1184647</v>
@@ -48509,7 +48509,7 @@
         <v>5.88500022888184</v>
       </c>
       <c r="G1660" t="n">
-        <v>4.75803232192993</v>
+        <v>4.75803184509277</v>
       </c>
       <c r="H1660" t="n">
         <v>1836881</v>
@@ -48538,7 +48538,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G1661" t="n">
-        <v>4.63271474838257</v>
+        <v>4.63271427154541</v>
       </c>
       <c r="H1661" t="n">
         <v>2400821</v>
@@ -48567,7 +48567,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G1662" t="n">
-        <v>4.68122482299805</v>
+        <v>4.68122434616089</v>
       </c>
       <c r="H1662" t="n">
         <v>2378742</v>
@@ -73919,6 +73919,35 @@
         <v>2757423</v>
       </c>
       <c r="I2536" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2537">
+      <c r="A2537" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2537" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2537" t="n">
+        <v>8.93200016021729</v>
+      </c>
+      <c r="D2537" t="n">
+        <v>8.9980001449585</v>
+      </c>
+      <c r="E2537" t="n">
+        <v>8.89200019836426</v>
+      </c>
+      <c r="F2537" t="n">
+        <v>8.94799995422363</v>
+      </c>
+      <c r="G2537" t="n">
+        <v>8.94799995422363</v>
+      </c>
+      <c r="H2537" t="n">
+        <v>2563064</v>
+      </c>
+      <c r="I2537" t="s">
         <v>9</v>
       </c>
     </row>
